--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1195,6 +1195,756 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>e715895a-7a8a-47c1-857c-e87a64fb2118</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>95</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>c6d56985-5a6a-49e6-b8e8-860c6dc07e10</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>95</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1a23d3a8-52b9-437e-913e-581a97eee8cc</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>95</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>f6081d35-4bc5-4f01-b297-da420817bf42</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>95</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>162938ad-c468-4930-b7f5-9496fa97cb6d</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>95</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>d55b4bf2-8aac-4f8e-a876-3066518f442f</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>95</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>9588dd77-b44f-4bf3-99f6-007d91bcf8be</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>95</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20af1d8a-3d5b-492a-a2ce-1c385c06bfef</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>95</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>6877568a-cbe1-48be-a8ae-9a2912009768</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>95</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>100f9133-3187-40ff-95f7-3381c810ecbe</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>95</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>59668d0a-3955-4b53-ba0f-e278e92dd3eb</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>95</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>3b1ea915-a4cb-46f3-8469-42dee4357ff4</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>95</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>70e66201-db63-4fa9-ae20-29c7b57463de</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>95</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0e7ff1a5-67ac-475b-9d7d-0009a21dd50f</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>95</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>71c0efec-c333-4ff7-a09b-e7e4545e8f93</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>95</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>1e194daa-45ea-4822-b8a8-8e7937ff95bd</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>95</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>a2b02321-c657-4cf4-a44c-696320598cbc</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>95</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>75b2ee11-1a96-4125-82e6-3bed8b18d3ec</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>95</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>6c69de8b-13ff-49d1-b8e8-fb733d1441fd</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>95</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>b4b087ef-560f-41de-b9df-394e0ccecbd5</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>95</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>dd10f970-adb3-439b-a7c0-f782639e5b91</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>95</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20f0ca84-badc-4dd4-91e0-ea426296dc34</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>95</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>061a5d8d-db2c-4eb2-8dab-0d3022a37074</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>95</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>bb339521-073d-415c-8193-35cd41b24a8a</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>95</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>a8eb50ee-b5ff-4191-a0a6-cd163a09d918</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>95</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>066a0461-853e-4d63-8876-8fb3d41a1f54</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>95</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>995349d6-0520-40f2-b77d-5734b81dcf25</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>95</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>fe29a209-e7d6-4290-a402-cc0050182210</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>95</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>a9d59163-e9e3-4602-8f6f-d8ee471fc731</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>95</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>98f4be1e-4f41-44ad-84f8-4993472c4f92</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>95</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>72c9447c-5584-4d93-ac79-04097139e5cd</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>95</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>84730c28-9465-4801-8092-05f9cd78cc5b</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>95</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>fd499e9e-741b-4826-848a-b0360d2d2cad</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>95</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>8a7ebb39-c7f9-40fd-a82f-3b4057d25bda</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>95</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>14e8167e-ccf0-4e6a-9c33-3a9f6ecc1a79</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>95</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>24a73fe1-4c8d-4d08-b850-e07a3c653910</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>95</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>97556e77-3a71-4e0e-9b49-d84af964b598</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>95</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>cbee731f-b14d-4743-9b87-fb5aeddf7d84</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>95</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>baed2d45-70d0-467a-a088-f25779fdae91</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>95</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>aeba1ce1-3306-4f81-acb0-b81b4e30925f</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>95</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1a6a020a-171d-4bfe-b6ab-348ae858d2ec</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>95</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>61a36c48-8a6b-44e8-9d99-91cb11828130</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>95</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ff77c13e-e11d-47b0-a19e-83a916c763ae</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>95</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>34d2e99c-8962-49cb-85a3-f0480403d7e4</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>95</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>3df449ec-e9f5-4939-9471-b3ba82db3d19</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>95</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>5a2ba8e5-04e6-47d2-93a9-d27736a0a1a4</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>95</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>e13a4ded-3395-4fc7-81e8-dc16bcc5f87e</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>95</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>32be64a1-f03c-482a-a52b-4efc49632624</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>95</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>c44bcb78-1735-4a9d-b5fb-862fef33f1f9</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>95</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>a93c4311-1888-4651-827e-20c3b73c9cd4</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>95</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H501"/>
+  <dimension ref="A1:H551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,7 +505,7 @@
         <v>4.67</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>46080.27338435522</v>
+        <v>46080.27338435185</v>
       </c>
     </row>
     <row r="3">
@@ -539,7 +539,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>46091.2733843597</v>
+        <v>46091.27338436343</v>
       </c>
     </row>
     <row r="4">
@@ -573,7 +573,7 @@
         <v>4.89</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>46091.2733843631</v>
+        <v>46091.27338436343</v>
       </c>
     </row>
     <row r="5">
@@ -607,7 +607,7 @@
         <v>0.57</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>46081.27338436617</v>
+        <v>46081.27338436343</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         <v>1.62</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>46077.27338436958</v>
+        <v>46077.273384375</v>
       </c>
     </row>
     <row r="7">
@@ -675,7 +675,7 @@
         <v>3.54</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>46075.27338437267</v>
+        <v>46075.273384375</v>
       </c>
     </row>
     <row r="8">
@@ -709,7 +709,7 @@
         <v>3.32</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>46079.27338437577</v>
+        <v>46079.273384375</v>
       </c>
     </row>
     <row r="9">
@@ -743,7 +743,7 @@
         <v>0.32</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>46093.27338437885</v>
+        <v>46093.273384375</v>
       </c>
     </row>
     <row r="10">
@@ -777,7 +777,7 @@
         <v>1.18</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>46081.27338438256</v>
+        <v>46081.27338438657</v>
       </c>
     </row>
     <row r="11">
@@ -811,7 +811,7 @@
         <v>2.52</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>46081.27338438571</v>
+        <v>46081.27338438657</v>
       </c>
     </row>
     <row r="12">
@@ -845,7 +845,7 @@
         <v>2.97</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>46073.27338438889</v>
+        <v>46073.27338438657</v>
       </c>
     </row>
     <row r="13">
@@ -879,7 +879,7 @@
         <v>1.61</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>46076.27338439228</v>
+        <v>46076.27338438657</v>
       </c>
     </row>
     <row r="14">
@@ -913,7 +913,7 @@
         <v>0.72</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>46079.27338439552</v>
+        <v>46079.27338439815</v>
       </c>
     </row>
     <row r="15">
@@ -947,7 +947,7 @@
         <v>4.53</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>46072.27338439874</v>
+        <v>46072.27338439815</v>
       </c>
     </row>
     <row r="16">
@@ -981,7 +981,7 @@
         <v>0.4</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>46066.27338440189</v>
+        <v>46066.27338439815</v>
       </c>
     </row>
     <row r="17">
@@ -1015,7 +1015,7 @@
         <v>1.57</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>46073.27338440515</v>
+        <v>46073.27338440972</v>
       </c>
     </row>
     <row r="18">
@@ -1049,7 +1049,7 @@
         <v>2.98</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>46080.27338440831</v>
+        <v>46080.27338440972</v>
       </c>
     </row>
     <row r="19">
@@ -1083,7 +1083,7 @@
         <v>4.89</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>46084.27338441137</v>
+        <v>46084.27338440972</v>
       </c>
     </row>
     <row r="20">
@@ -1117,7 +1117,7 @@
         <v>3.95</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>46094.27338441468</v>
+        <v>46094.27338440972</v>
       </c>
     </row>
     <row r="21">
@@ -1151,7 +1151,7 @@
         <v>4.29</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>46073.27338441776</v>
+        <v>46073.2733844213</v>
       </c>
     </row>
     <row r="22">
@@ -1185,7 +1185,7 @@
         <v>2.31</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>46075.27338442076</v>
+        <v>46075.2733844213</v>
       </c>
     </row>
     <row r="23">
@@ -1219,7 +1219,7 @@
         <v>2.8</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>46070.2733844238</v>
+        <v>46070.2733844213</v>
       </c>
     </row>
     <row r="24">
@@ -1253,7 +1253,7 @@
         <v>4.06</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>46079.2733844274</v>
+        <v>46079.27338443287</v>
       </c>
     </row>
     <row r="25">
@@ -1287,7 +1287,7 @@
         <v>2.05</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>46072.27338443044</v>
+        <v>46072.27338443287</v>
       </c>
     </row>
     <row r="26">
@@ -1321,7 +1321,7 @@
         <v>0.15</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>46090.27338443367</v>
+        <v>46090.27338443287</v>
       </c>
     </row>
     <row r="27">
@@ -1355,7 +1355,7 @@
         <v>4.62</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>46068.27338443667</v>
+        <v>46068.27338443287</v>
       </c>
     </row>
     <row r="28">
@@ -1389,7 +1389,7 @@
         <v>3.7</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>46082.27338444004</v>
+        <v>46082.27338444444</v>
       </c>
     </row>
     <row r="29">
@@ -1423,7 +1423,7 @@
         <v>4.95</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>46089.27338444308</v>
+        <v>46089.27338444444</v>
       </c>
     </row>
     <row r="30">
@@ -1457,7 +1457,7 @@
         <v>3.61</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>46066.27338444629</v>
+        <v>46066.27338444444</v>
       </c>
     </row>
     <row r="31">
@@ -1491,7 +1491,7 @@
         <v>1.49</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>46092.27338444969</v>
+        <v>46092.27338444444</v>
       </c>
     </row>
     <row r="32">
@@ -1525,7 +1525,7 @@
         <v>4.8</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>46082.27338445273</v>
+        <v>46082.27338445602</v>
       </c>
     </row>
     <row r="33">
@@ -1559,7 +1559,7 @@
         <v>1.32</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>46075.27338445574</v>
+        <v>46075.27338445602</v>
       </c>
     </row>
     <row r="34">
@@ -1593,7 +1593,7 @@
         <v>2.39</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>46068.27338445879</v>
+        <v>46068.27338445602</v>
       </c>
     </row>
     <row r="35">
@@ -1627,7 +1627,7 @@
         <v>4.04</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>46081.27338446208</v>
+        <v>46081.27338446759</v>
       </c>
     </row>
     <row r="36">
@@ -1661,7 +1661,7 @@
         <v>1.14</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>46068.27338446513</v>
+        <v>46068.27338446759</v>
       </c>
     </row>
     <row r="37">
@@ -1695,7 +1695,7 @@
         <v>2.37</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>46071.27338446827</v>
+        <v>46071.27338446759</v>
       </c>
     </row>
     <row r="38">
@@ -1729,7 +1729,7 @@
         <v>0.6</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>46072.27338447125</v>
+        <v>46072.27338446759</v>
       </c>
     </row>
     <row r="39">
@@ -1763,7 +1763,7 @@
         <v>1.54</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>46065.27338447501</v>
+        <v>46065.27338447917</v>
       </c>
     </row>
     <row r="40">
@@ -1797,7 +1797,7 @@
         <v>4.18</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>46084.27338447809</v>
+        <v>46084.27338447917</v>
       </c>
     </row>
     <row r="41">
@@ -1831,7 +1831,7 @@
         <v>2.07</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>46090.27338448114</v>
+        <v>46090.27338447917</v>
       </c>
     </row>
     <row r="42">
@@ -1865,7 +1865,7 @@
         <v>4.18</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>46093.27338448448</v>
+        <v>46093.27338447917</v>
       </c>
     </row>
     <row r="43">
@@ -1899,7 +1899,7 @@
         <v>2</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>46075.2733844875</v>
+        <v>46075.27338449074</v>
       </c>
     </row>
     <row r="44">
@@ -1933,7 +1933,7 @@
         <v>4.25</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>46083.27338449075</v>
+        <v>46083.27338449074</v>
       </c>
     </row>
     <row r="45">
@@ -1967,7 +1967,7 @@
         <v>2.81</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>46073.27338449394</v>
+        <v>46073.27338449074</v>
       </c>
     </row>
     <row r="46">
@@ -2001,7 +2001,7 @@
         <v>2.55</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>46074.27338449729</v>
+        <v>46074.27338450232</v>
       </c>
     </row>
     <row r="47">
@@ -2035,7 +2035,7 @@
         <v>4.31</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>46093.27338450032</v>
+        <v>46093.27338450232</v>
       </c>
     </row>
     <row r="48">
@@ -2069,7 +2069,7 @@
         <v>2.23</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>46085.27338450334</v>
+        <v>46085.27338450232</v>
       </c>
     </row>
     <row r="49">
@@ -2103,7 +2103,7 @@
         <v>4.5</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>46077.27338450641</v>
+        <v>46077.27338450232</v>
       </c>
     </row>
     <row r="50">
@@ -2137,7 +2137,7 @@
         <v>4.27</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>46074.27338450967</v>
+        <v>46074.27338451389</v>
       </c>
     </row>
     <row r="51">
@@ -2171,7 +2171,7 @@
         <v>2.91</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>46084.27338451269</v>
+        <v>46084.27338451389</v>
       </c>
     </row>
     <row r="52">
@@ -2205,7 +2205,7 @@
         <v>4.79</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>46092.27338451582</v>
+        <v>46092.27338451389</v>
       </c>
     </row>
     <row r="53">
@@ -2239,7 +2239,7 @@
         <v>2.86</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>46084.27338451966</v>
+        <v>46084.27338451389</v>
       </c>
     </row>
     <row r="54">
@@ -2273,7 +2273,7 @@
         <v>4.15</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>46087.27338452276</v>
+        <v>46087.27338452546</v>
       </c>
     </row>
     <row r="55">
@@ -2307,7 +2307,7 @@
         <v>2.99</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>46073.27338452591</v>
+        <v>46073.27338452546</v>
       </c>
     </row>
     <row r="56">
@@ -2341,7 +2341,7 @@
         <v>0.23</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>46075.27338452911</v>
+        <v>46075.27338452546</v>
       </c>
     </row>
     <row r="57">
@@ -2375,7 +2375,7 @@
         <v>4.57</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>46073.27338453226</v>
+        <v>46073.27338453704</v>
       </c>
     </row>
     <row r="58">
@@ -2409,7 +2409,7 @@
         <v>4.74</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>46091.2733845353</v>
+        <v>46091.27338453704</v>
       </c>
     </row>
     <row r="59">
@@ -2443,7 +2443,7 @@
         <v>0.7</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>46084.27338453836</v>
+        <v>46084.27338453704</v>
       </c>
     </row>
     <row r="60">
@@ -2477,7 +2477,7 @@
         <v>1.25</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>46068.27338454135</v>
+        <v>46068.27338453704</v>
       </c>
     </row>
     <row r="61">
@@ -2511,7 +2511,7 @@
         <v>4.16</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>46077.2733845446</v>
+        <v>46077.27338454861</v>
       </c>
     </row>
     <row r="62">
@@ -2545,7 +2545,7 @@
         <v>4.01</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>46080.27338454758</v>
+        <v>46080.27338454861</v>
       </c>
     </row>
     <row r="63">
@@ -2579,7 +2579,7 @@
         <v>2.21</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>46079.27338455062</v>
+        <v>46079.27338454861</v>
       </c>
     </row>
     <row r="64">
@@ -2613,7 +2613,7 @@
         <v>0.5</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>46065.27338455387</v>
+        <v>46065.27338454861</v>
       </c>
     </row>
     <row r="65">
@@ -2647,7 +2647,7 @@
         <v>2.67</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>46072.27338455687</v>
+        <v>46072.27338456018</v>
       </c>
     </row>
     <row r="66">
@@ -2681,7 +2681,7 @@
         <v>3.83</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>46081.27338455992</v>
+        <v>46081.27338456018</v>
       </c>
     </row>
     <row r="67">
@@ -2715,7 +2715,7 @@
         <v>1.12</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>46087.273384563</v>
+        <v>46087.27338456018</v>
       </c>
     </row>
     <row r="68">
@@ -2749,7 +2749,7 @@
         <v>0.06</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>46072.27338456657</v>
+        <v>46072.27338457176</v>
       </c>
     </row>
     <row r="69">
@@ -2783,7 +2783,7 @@
         <v>3.92</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>46071.27338457005</v>
+        <v>46071.27338457176</v>
       </c>
     </row>
     <row r="70">
@@ -2817,7 +2817,7 @@
         <v>2.85</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>46084.27338457308</v>
+        <v>46084.27338457176</v>
       </c>
     </row>
     <row r="71">
@@ -2851,7 +2851,7 @@
         <v>2.07</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>46065.27338457853</v>
+        <v>46065.27338458334</v>
       </c>
     </row>
     <row r="72">
@@ -2885,7 +2885,7 @@
         <v>0.48</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>46086.27338458171</v>
+        <v>46086.27338458334</v>
       </c>
     </row>
     <row r="73">
@@ -2919,7 +2919,7 @@
         <v>1.54</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>46090.27338458481</v>
+        <v>46090.27338458334</v>
       </c>
     </row>
     <row r="74">
@@ -2953,7 +2953,7 @@
         <v>3.2</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>46083.27338458824</v>
+        <v>46083.27338458334</v>
       </c>
     </row>
     <row r="75">
@@ -2987,7 +2987,7 @@
         <v>4.19</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>46084.27338459133</v>
+        <v>46084.2733845949</v>
       </c>
     </row>
     <row r="76">
@@ -3021,7 +3021,7 @@
         <v>2.89</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>46086.27338459431</v>
+        <v>46086.2733845949</v>
       </c>
     </row>
     <row r="77">
@@ -3055,7 +3055,7 @@
         <v>3.44</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>46067.27338459737</v>
+        <v>46067.2733845949</v>
       </c>
     </row>
     <row r="78">
@@ -3089,7 +3089,7 @@
         <v>3.21</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>46066.27338460072</v>
+        <v>46066.27338460648</v>
       </c>
     </row>
     <row r="79">
@@ -3123,7 +3123,7 @@
         <v>0.28</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>46065.2733846038</v>
+        <v>46065.27338460648</v>
       </c>
     </row>
     <row r="80">
@@ -3157,7 +3157,7 @@
         <v>2.73</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>46092.27338460687</v>
+        <v>46092.27338460648</v>
       </c>
     </row>
     <row r="81">
@@ -3191,7 +3191,7 @@
         <v>1.11</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>46091.27338461</v>
+        <v>46091.27338460648</v>
       </c>
     </row>
     <row r="82">
@@ -3225,7 +3225,7 @@
         <v>4.89</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>46091.27338461322</v>
+        <v>46091.27338461806</v>
       </c>
     </row>
     <row r="83">
@@ -3259,7 +3259,7 @@
         <v>2.37</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>46071.27338461625</v>
+        <v>46071.27338461806</v>
       </c>
     </row>
     <row r="84">
@@ -3293,7 +3293,7 @@
         <v>3.1</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>46083.27338461937</v>
+        <v>46083.27338461806</v>
       </c>
     </row>
     <row r="85">
@@ -3327,7 +3327,7 @@
         <v>4.67</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>46066.27338462249</v>
+        <v>46066.27338461806</v>
       </c>
     </row>
     <row r="86">
@@ -3361,7 +3361,7 @@
         <v>2.72</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>46072.27338462568</v>
+        <v>46072.27338462963</v>
       </c>
     </row>
     <row r="87">
@@ -3395,7 +3395,7 @@
         <v>3.1</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>46087.27338462888</v>
+        <v>46087.27338462963</v>
       </c>
     </row>
     <row r="88">
@@ -3429,7 +3429,7 @@
         <v>1.73</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>46079.2733846319</v>
+        <v>46079.27338462963</v>
       </c>
     </row>
     <row r="89">
@@ -3463,7 +3463,7 @@
         <v>0.89</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>46074.27338463524</v>
+        <v>46074.27338462963</v>
       </c>
     </row>
     <row r="90">
@@ -3497,7 +3497,7 @@
         <v>4.74</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>46082.27338463837</v>
+        <v>46082.2733846412</v>
       </c>
     </row>
     <row r="91">
@@ -3531,7 +3531,7 @@
         <v>2.03</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>46065.27338464149</v>
+        <v>46065.2733846412</v>
       </c>
     </row>
     <row r="92">
@@ -3565,7 +3565,7 @@
         <v>3.48</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>46091.27338464457</v>
+        <v>46091.2733846412</v>
       </c>
     </row>
     <row r="93">
@@ -3599,7 +3599,7 @@
         <v>0.65</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>46080.27338464774</v>
+        <v>46080.27338465278</v>
       </c>
     </row>
     <row r="94">
@@ -3633,7 +3633,7 @@
         <v>1.07</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>46067.27338465104</v>
+        <v>46067.27338465278</v>
       </c>
     </row>
     <row r="95">
@@ -3667,7 +3667,7 @@
         <v>1.17</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>46088.27338465423</v>
+        <v>46088.27338465278</v>
       </c>
     </row>
     <row r="96">
@@ -3701,7 +3701,7 @@
         <v>2.44</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>46072.27338465724</v>
+        <v>46072.27338465278</v>
       </c>
     </row>
     <row r="97">
@@ -3735,7 +3735,7 @@
         <v>0.63</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>46083.27338466064</v>
+        <v>46083.27338466435</v>
       </c>
     </row>
     <row r="98">
@@ -3769,7 +3769,7 @@
         <v>4.7</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>46069.27338466371</v>
+        <v>46069.27338466435</v>
       </c>
     </row>
     <row r="99">
@@ -3803,7 +3803,7 @@
         <v>2.5</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>46071.2733846669</v>
+        <v>46071.27338466435</v>
       </c>
     </row>
     <row r="100">
@@ -3837,7 +3837,7 @@
         <v>4.52</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>46091.27338467008</v>
+        <v>46091.27338466435</v>
       </c>
     </row>
     <row r="101">
@@ -3871,7 +3871,7 @@
         <v>1.07</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>46089.27338467317</v>
+        <v>46089.27338467593</v>
       </c>
     </row>
     <row r="102">
@@ -3905,7 +3905,7 @@
         <v>4.4</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>46094.27338467625</v>
+        <v>46094.27338467593</v>
       </c>
     </row>
     <row r="103">
@@ -3939,7 +3939,7 @@
         <v>4.64</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>46073.27338467928</v>
+        <v>46073.27338467593</v>
       </c>
     </row>
     <row r="104">
@@ -3973,7 +3973,7 @@
         <v>3.7</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>46078.27338468272</v>
+        <v>46078.2733846875</v>
       </c>
     </row>
     <row r="105">
@@ -4007,7 +4007,7 @@
         <v>1.42</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>46093.27338468585</v>
+        <v>46093.2733846875</v>
       </c>
     </row>
     <row r="106">
@@ -4041,7 +4041,7 @@
         <v>0.28</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>46077.273384689</v>
+        <v>46077.2733846875</v>
       </c>
     </row>
     <row r="107">
@@ -4075,7 +4075,7 @@
         <v>3.87</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>46072.273384692</v>
+        <v>46072.2733846875</v>
       </c>
     </row>
     <row r="108">
@@ -4109,7 +4109,7 @@
         <v>3.56</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>46069.2733846952</v>
+        <v>46069.27338469907</v>
       </c>
     </row>
     <row r="109">
@@ -4143,7 +4143,7 @@
         <v>4.03</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>46073.27338469839</v>
+        <v>46073.27338469907</v>
       </c>
     </row>
     <row r="110">
@@ -4177,7 +4177,7 @@
         <v>2.06</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>46092.27338470152</v>
+        <v>46092.27338469907</v>
       </c>
     </row>
     <row r="111">
@@ -4211,7 +4211,7 @@
         <v>2.94</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>46090.27338470478</v>
+        <v>46090.27338469907</v>
       </c>
     </row>
     <row r="112">
@@ -4245,7 +4245,7 @@
         <v>0.46</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>46066.27338470781</v>
+        <v>46066.27338471065</v>
       </c>
     </row>
     <row r="113">
@@ -4279,7 +4279,7 @@
         <v>4.9</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>46091.27338471083</v>
+        <v>46091.27338471065</v>
       </c>
     </row>
     <row r="114">
@@ -4313,7 +4313,7 @@
         <v>3.27</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>46069.27338471399</v>
+        <v>46069.27338471065</v>
       </c>
     </row>
     <row r="115">
@@ -4347,7 +4347,7 @@
         <v>3.95</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>46093.27338471733</v>
+        <v>46093.27338472222</v>
       </c>
     </row>
     <row r="116">
@@ -4381,7 +4381,7 @@
         <v>0.84</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>46067.27338472043</v>
+        <v>46067.27338472222</v>
       </c>
     </row>
     <row r="117">
@@ -4415,7 +4415,7 @@
         <v>3.46</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>46094.27338472347</v>
+        <v>46094.27338472222</v>
       </c>
     </row>
     <row r="118">
@@ -4449,7 +4449,7 @@
         <v>3.87</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>46074.27338472652</v>
+        <v>46074.27338472222</v>
       </c>
     </row>
     <row r="119">
@@ -4483,7 +4483,7 @@
         <v>2.18</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>46072.2733847297</v>
+        <v>46072.27338473379</v>
       </c>
     </row>
     <row r="120">
@@ -4517,7 +4517,7 @@
         <v>3.71</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>46066.27338473285</v>
+        <v>46066.27338473379</v>
       </c>
     </row>
     <row r="121">
@@ -4551,7 +4551,7 @@
         <v>2.28</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>46069.27338473588</v>
+        <v>46069.27338473379</v>
       </c>
     </row>
     <row r="122">
@@ -4585,7 +4585,7 @@
         <v>4.77</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>46090.27338473911</v>
+        <v>46090.27338473379</v>
       </c>
     </row>
     <row r="123">
@@ -4619,7 +4619,7 @@
         <v>3.32</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>46081.27338474216</v>
+        <v>46081.27338474537</v>
       </c>
     </row>
     <row r="124">
@@ -4653,7 +4653,7 @@
         <v>3.98</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>46082.27338474516</v>
+        <v>46082.27338474537</v>
       </c>
     </row>
     <row r="125">
@@ -4687,7 +4687,7 @@
         <v>2.57</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>46084.27338474819</v>
+        <v>46084.27338474537</v>
       </c>
     </row>
     <row r="126">
@@ -4721,7 +4721,7 @@
         <v>4.38</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>46083.27338475158</v>
+        <v>46083.27338475695</v>
       </c>
     </row>
     <row r="127">
@@ -4755,7 +4755,7 @@
         <v>4</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>46082.27338475458</v>
+        <v>46082.27338475695</v>
       </c>
     </row>
     <row r="128">
@@ -4789,7 +4789,7 @@
         <v>0.19</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>46085.27338475785</v>
+        <v>46085.27338475695</v>
       </c>
     </row>
     <row r="129">
@@ -4823,7 +4823,7 @@
         <v>0.7</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>46080.27338476091</v>
+        <v>46080.27338475695</v>
       </c>
     </row>
     <row r="130">
@@ -4857,7 +4857,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>46084.27338476406</v>
+        <v>46084.27338476852</v>
       </c>
     </row>
     <row r="131">
@@ -4891,7 +4891,7 @@
         <v>4.57</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>46066.27338476727</v>
+        <v>46066.27338476852</v>
       </c>
     </row>
     <row r="132">
@@ -4925,7 +4925,7 @@
         <v>3.56</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>46065.27338477036</v>
+        <v>46065.27338476852</v>
       </c>
     </row>
     <row r="133">
@@ -4959,7 +4959,7 @@
         <v>2.56</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>46076.27338477359</v>
+        <v>46076.27338476852</v>
       </c>
     </row>
     <row r="134">
@@ -4993,7 +4993,7 @@
         <v>0.38</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>46083.2733847766</v>
+        <v>46083.27338478009</v>
       </c>
     </row>
     <row r="135">
@@ -5027,7 +5027,7 @@
         <v>0.64</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>46093.27338477968</v>
+        <v>46093.27338478009</v>
       </c>
     </row>
     <row r="136">
@@ -5061,7 +5061,7 @@
         <v>2.45</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>46066.27338478278</v>
+        <v>46066.27338478009</v>
       </c>
     </row>
     <row r="137">
@@ -5095,7 +5095,7 @@
         <v>1.8</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>46071.27338478607</v>
+        <v>46071.27338479167</v>
       </c>
     </row>
     <row r="138">
@@ -5129,7 +5129,7 @@
         <v>2.11</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>46081.27338478912</v>
+        <v>46081.27338479167</v>
       </c>
     </row>
     <row r="139">
@@ -5163,7 +5163,7 @@
         <v>2.73</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>46080.27338479216</v>
+        <v>46080.27338479167</v>
       </c>
     </row>
     <row r="140">
@@ -5197,7 +5197,7 @@
         <v>0.42</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>46067.27338479521</v>
+        <v>46067.27338479167</v>
       </c>
     </row>
     <row r="141">
@@ -5231,7 +5231,7 @@
         <v>1.11</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>46072.27338479837</v>
+        <v>46072.27338480324</v>
       </c>
     </row>
     <row r="142">
@@ -5265,7 +5265,7 @@
         <v>2.86</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>46092.27338480143</v>
+        <v>46092.27338480324</v>
       </c>
     </row>
     <row r="143">
@@ -5299,7 +5299,7 @@
         <v>1.45</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>46077.27338480449</v>
+        <v>46077.27338480324</v>
       </c>
     </row>
     <row r="144">
@@ -5333,7 +5333,7 @@
         <v>2.95</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>46085.2733848076</v>
+        <v>46085.27338480324</v>
       </c>
     </row>
     <row r="145">
@@ -5367,7 +5367,7 @@
         <v>2.93</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>46068.27338481087</v>
+        <v>46068.27338481481</v>
       </c>
     </row>
     <row r="146">
@@ -5401,7 +5401,7 @@
         <v>3.12</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>46079.27338481397</v>
+        <v>46079.27338481481</v>
       </c>
     </row>
     <row r="147">
@@ -5435,7 +5435,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>46094.273384817</v>
+        <v>46094.27338481481</v>
       </c>
     </row>
     <row r="148">
@@ -5469,7 +5469,7 @@
         <v>0.91</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>46092.27338482049</v>
+        <v>46092.27338481481</v>
       </c>
     </row>
     <row r="149">
@@ -5503,7 +5503,7 @@
         <v>0.26</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>46094.27338482362</v>
+        <v>46094.27338482639</v>
       </c>
     </row>
     <row r="150">
@@ -5537,7 +5537,7 @@
         <v>4.06</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>46087.27338482685</v>
+        <v>46087.27338482639</v>
       </c>
     </row>
     <row r="151">
@@ -5571,7 +5571,7 @@
         <v>4.14</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>46070.27338483003</v>
+        <v>46070.27338482639</v>
       </c>
     </row>
     <row r="152">
@@ -5605,7 +5605,7 @@
         <v>4.2</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>46089.27338483315</v>
+        <v>46089.27338483796</v>
       </c>
     </row>
     <row r="153">
@@ -5639,7 +5639,7 @@
         <v>1.59</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>46082.27338483638</v>
+        <v>46082.27338483796</v>
       </c>
     </row>
     <row r="154">
@@ -5673,7 +5673,7 @@
         <v>0.21</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>46078.27338484034</v>
+        <v>46078.27338483796</v>
       </c>
     </row>
     <row r="155">
@@ -5707,7 +5707,7 @@
         <v>4.42</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>46073.27338484353</v>
+        <v>46073.27338483796</v>
       </c>
     </row>
     <row r="156">
@@ -5741,7 +5741,7 @@
         <v>1.23</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>46084.27338484659</v>
+        <v>46084.27338484953</v>
       </c>
     </row>
     <row r="157">
@@ -5775,7 +5775,7 @@
         <v>3.52</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>46079.27338484964</v>
+        <v>46079.27338484953</v>
       </c>
     </row>
     <row r="158">
@@ -5809,7 +5809,7 @@
         <v>1.08</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>46093.27338485274</v>
+        <v>46093.27338484953</v>
       </c>
     </row>
     <row r="159">
@@ -5843,7 +5843,7 @@
         <v>4.68</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>46093.2733848559</v>
+        <v>46093.27338486111</v>
       </c>
     </row>
     <row r="160">
@@ -5877,7 +5877,7 @@
         <v>1.74</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>46092.27338485909</v>
+        <v>46092.27338486111</v>
       </c>
     </row>
     <row r="161">
@@ -5911,7 +5911,7 @@
         <v>1.88</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>46086.27338486214</v>
+        <v>46086.27338486111</v>
       </c>
     </row>
     <row r="162">
@@ -5945,7 +5945,7 @@
         <v>2.25</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>46093.27338486532</v>
+        <v>46093.27338486111</v>
       </c>
     </row>
     <row r="163">
@@ -5979,7 +5979,7 @@
         <v>1.75</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>46079.27338486865</v>
+        <v>46079.27338487269</v>
       </c>
     </row>
     <row r="164">
@@ -6013,7 +6013,7 @@
         <v>4.56</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>46066.27338487169</v>
+        <v>46066.27338487269</v>
       </c>
     </row>
     <row r="165">
@@ -6047,7 +6047,7 @@
         <v>1.31</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>46076.27338487473</v>
+        <v>46076.27338487269</v>
       </c>
     </row>
     <row r="166">
@@ -6081,7 +6081,7 @@
         <v>2.89</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>46092.27338487795</v>
+        <v>46092.27338487269</v>
       </c>
     </row>
     <row r="167">
@@ -6115,7 +6115,7 @@
         <v>2.54</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>46074.27338488098</v>
+        <v>46074.27338488426</v>
       </c>
     </row>
     <row r="168">
@@ -6149,7 +6149,7 @@
         <v>3.87</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>46065.27338488404</v>
+        <v>46065.27338488426</v>
       </c>
     </row>
     <row r="169">
@@ -6183,7 +6183,7 @@
         <v>0.99</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>46067.27338488706</v>
+        <v>46067.27338488426</v>
       </c>
     </row>
     <row r="170">
@@ -6217,7 +6217,7 @@
         <v>1.89</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>46091.27338489032</v>
+        <v>46091.27338489583</v>
       </c>
     </row>
     <row r="171">
@@ -6251,7 +6251,7 @@
         <v>2.79</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>46078.27338489333</v>
+        <v>46078.27338489583</v>
       </c>
     </row>
     <row r="172">
@@ -6285,7 +6285,7 @@
         <v>4.27</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>46070.27338489651</v>
+        <v>46070.27338489583</v>
       </c>
     </row>
     <row r="173">
@@ -6319,7 +6319,7 @@
         <v>2.16</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>46092.27338489959</v>
+        <v>46092.27338489583</v>
       </c>
     </row>
     <row r="174">
@@ -6353,7 +6353,7 @@
         <v>4.24</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>46066.27338490276</v>
+        <v>46066.27338490741</v>
       </c>
     </row>
     <row r="175">
@@ -6387,7 +6387,7 @@
         <v>3.92</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>46077.27338490596</v>
+        <v>46077.27338490741</v>
       </c>
     </row>
     <row r="176">
@@ -6421,7 +6421,7 @@
         <v>2.36</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>46088.27338490923</v>
+        <v>46088.27338490741</v>
       </c>
     </row>
     <row r="177">
@@ -6455,7 +6455,7 @@
         <v>0.41</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>46079.27338491259</v>
+        <v>46079.27338490741</v>
       </c>
     </row>
     <row r="178">
@@ -6489,7 +6489,7 @@
         <v>3.27</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>46080.27338491573</v>
+        <v>46080.27338491898</v>
       </c>
     </row>
     <row r="179">
@@ -6523,7 +6523,7 @@
         <v>0.71</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>46092.27338491873</v>
+        <v>46092.27338491898</v>
       </c>
     </row>
     <row r="180">
@@ -6557,7 +6557,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>46067.2733849219</v>
+        <v>46067.27338491898</v>
       </c>
     </row>
     <row r="181">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>46087.27338492509</v>
+        <v>46087.27338493056</v>
       </c>
     </row>
     <row r="182">
@@ -6625,7 +6625,7 @@
         <v>2.03</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>46094.27338492814</v>
+        <v>46094.27338493056</v>
       </c>
     </row>
     <row r="183">
@@ -6659,7 +6659,7 @@
         <v>4.67</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>46075.27338493121</v>
+        <v>46075.27338493056</v>
       </c>
     </row>
     <row r="184">
@@ -6693,7 +6693,7 @@
         <v>3.34</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>46069.2733849342</v>
+        <v>46069.27338493056</v>
       </c>
     </row>
     <row r="185">
@@ -6727,7 +6727,7 @@
         <v>0.89</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>46087.27338493785</v>
+        <v>46087.27338494213</v>
       </c>
     </row>
     <row r="186">
@@ -6761,7 +6761,7 @@
         <v>0.48</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>46073.27338494105</v>
+        <v>46073.27338494213</v>
       </c>
     </row>
     <row r="187">
@@ -6795,7 +6795,7 @@
         <v>2.46</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>46085.27338494424</v>
+        <v>46085.27338494213</v>
       </c>
     </row>
     <row r="188">
@@ -6829,7 +6829,7 @@
         <v>4.46</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>46085.27338494758</v>
+        <v>46085.27338494213</v>
       </c>
     </row>
     <row r="189">
@@ -6863,7 +6863,7 @@
         <v>5</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>46086.27338495065</v>
+        <v>46086.2733849537</v>
       </c>
     </row>
     <row r="190">
@@ -6897,7 +6897,7 @@
         <v>1.36</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>46069.27338495386</v>
+        <v>46069.2733849537</v>
       </c>
     </row>
     <row r="191">
@@ -6931,7 +6931,7 @@
         <v>4.32</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>46072.273384957</v>
+        <v>46072.2733849537</v>
       </c>
     </row>
     <row r="192">
@@ -6965,7 +6965,7 @@
         <v>3.72</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>46091.27338496036</v>
+        <v>46091.27338496528</v>
       </c>
     </row>
     <row r="193">
@@ -6999,7 +6999,7 @@
         <v>3.11</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>46076.27338496348</v>
+        <v>46076.27338496528</v>
       </c>
     </row>
     <row r="194">
@@ -7033,7 +7033,7 @@
         <v>3.91</v>
       </c>
       <c r="H194" s="2" t="n">
-        <v>46080.27338496669</v>
+        <v>46080.27338496528</v>
       </c>
     </row>
     <row r="195">
@@ -7067,7 +7067,7 @@
         <v>2.43</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>46072.27338496994</v>
+        <v>46072.27338496528</v>
       </c>
     </row>
     <row r="196">
@@ -7101,7 +7101,7 @@
         <v>4.24</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>46084.27338497298</v>
+        <v>46084.27338497685</v>
       </c>
     </row>
     <row r="197">
@@ -7135,7 +7135,7 @@
         <v>1.14</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>46094.27338497622</v>
+        <v>46094.27338497685</v>
       </c>
     </row>
     <row r="198">
@@ -7169,7 +7169,7 @@
         <v>0.03</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>46068.27338497937</v>
+        <v>46068.27338497685</v>
       </c>
     </row>
     <row r="199">
@@ -7203,7 +7203,7 @@
         <v>3.7</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>46090.27338498276</v>
+        <v>46090.27338498842</v>
       </c>
     </row>
     <row r="200">
@@ -7237,7 +7237,7 @@
         <v>1.07</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>46084.27338498595</v>
+        <v>46084.27338498842</v>
       </c>
     </row>
     <row r="201">
@@ -7271,7 +7271,7 @@
         <v>3.94</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>46082.27338498909</v>
+        <v>46082.27338498842</v>
       </c>
     </row>
     <row r="202">
@@ -7305,7 +7305,7 @@
         <v>1.63</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>46072.27338499224</v>
+        <v>46072.27338498842</v>
       </c>
     </row>
     <row r="203">
@@ -7339,7 +7339,7 @@
         <v>2.98</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>46073.27338499543</v>
+        <v>46073.273385</v>
       </c>
     </row>
     <row r="204">
@@ -7373,7 +7373,7 @@
         <v>1.04</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>46074.27338499867</v>
+        <v>46074.273385</v>
       </c>
     </row>
     <row r="205">
@@ -7407,7 +7407,7 @@
         <v>2.28</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>46083.27338500168</v>
+        <v>46083.273385</v>
       </c>
     </row>
     <row r="206">
@@ -7441,7 +7441,7 @@
         <v>0.89</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>46087.2733850049</v>
+        <v>46087.273385</v>
       </c>
     </row>
     <row r="207">
@@ -7475,7 +7475,7 @@
         <v>3.5</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>46094.27338500804</v>
+        <v>46094.27338501158</v>
       </c>
     </row>
     <row r="208">
@@ -7509,7 +7509,7 @@
         <v>4.71</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>46089.27338501107</v>
+        <v>46089.27338501158</v>
       </c>
     </row>
     <row r="209">
@@ -7543,7 +7543,7 @@
         <v>3.52</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>46069.27338501429</v>
+        <v>46069.27338501158</v>
       </c>
     </row>
     <row r="210">
@@ -7577,7 +7577,7 @@
         <v>3.65</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>46086.27338501746</v>
+        <v>46086.27338502315</v>
       </c>
     </row>
     <row r="211">
@@ -7611,7 +7611,7 @@
         <v>3.45</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>46077.27338502064</v>
+        <v>46077.27338502315</v>
       </c>
     </row>
     <row r="212">
@@ -7645,7 +7645,7 @@
         <v>4.85</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>46075.27338502379</v>
+        <v>46075.27338502315</v>
       </c>
     </row>
     <row r="213">
@@ -7679,7 +7679,7 @@
         <v>1.37</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>46089.27338502691</v>
+        <v>46089.27338502315</v>
       </c>
     </row>
     <row r="214">
@@ -7713,7 +7713,7 @@
         <v>0.13</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>46076.27338503033</v>
+        <v>46076.27338503472</v>
       </c>
     </row>
     <row r="215">
@@ -7747,7 +7747,7 @@
         <v>2.76</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>46090.27338503335</v>
+        <v>46090.27338503472</v>
       </c>
     </row>
     <row r="216">
@@ -7781,7 +7781,7 @@
         <v>4.76</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>46093.27338503638</v>
+        <v>46093.27338503472</v>
       </c>
     </row>
     <row r="217">
@@ -7815,7 +7815,7 @@
         <v>2.62</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>46066.2733850396</v>
+        <v>46066.27338503472</v>
       </c>
     </row>
     <row r="218">
@@ -7849,7 +7849,7 @@
         <v>1.11</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>46065.27338504278</v>
+        <v>46065.2733850463</v>
       </c>
     </row>
     <row r="219">
@@ -7883,7 +7883,7 @@
         <v>3.64</v>
       </c>
       <c r="H219" s="2" t="n">
-        <v>46068.27338504589</v>
+        <v>46068.2733850463</v>
       </c>
     </row>
     <row r="220">
@@ -7917,7 +7917,7 @@
         <v>0.31</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>46073.27338504892</v>
+        <v>46073.2733850463</v>
       </c>
     </row>
     <row r="221">
@@ -7951,7 +7951,7 @@
         <v>2.83</v>
       </c>
       <c r="H221" s="2" t="n">
-        <v>46084.27338505227</v>
+        <v>46084.27338505787</v>
       </c>
     </row>
     <row r="222">
@@ -7985,7 +7985,7 @@
         <v>3.81</v>
       </c>
       <c r="H222" s="2" t="n">
-        <v>46072.2733850553</v>
+        <v>46072.27338505787</v>
       </c>
     </row>
     <row r="223">
@@ -8019,7 +8019,7 @@
         <v>2.56</v>
       </c>
       <c r="H223" s="2" t="n">
-        <v>46091.2733850583</v>
+        <v>46091.27338505787</v>
       </c>
     </row>
     <row r="224">
@@ -8053,7 +8053,7 @@
         <v>2.25</v>
       </c>
       <c r="H224" s="2" t="n">
-        <v>46080.27338506135</v>
+        <v>46080.27338505787</v>
       </c>
     </row>
     <row r="225">
@@ -8087,7 +8087,7 @@
         <v>4.33</v>
       </c>
       <c r="H225" s="2" t="n">
-        <v>46080.27338506468</v>
+        <v>46080.27338506944</v>
       </c>
     </row>
     <row r="226">
@@ -8121,7 +8121,7 @@
         <v>4.72</v>
       </c>
       <c r="H226" s="2" t="n">
-        <v>46083.27338506793</v>
+        <v>46083.27338506944</v>
       </c>
     </row>
     <row r="227">
@@ -8155,7 +8155,7 @@
         <v>4.55</v>
       </c>
       <c r="H227" s="2" t="n">
-        <v>46077.27338507105</v>
+        <v>46077.27338506944</v>
       </c>
     </row>
     <row r="228">
@@ -8189,7 +8189,7 @@
         <v>3.03</v>
       </c>
       <c r="H228" s="2" t="n">
-        <v>46094.27338507432</v>
+        <v>46094.27338506944</v>
       </c>
     </row>
     <row r="229">
@@ -8223,7 +8223,7 @@
         <v>3.39</v>
       </c>
       <c r="H229" s="2" t="n">
-        <v>46068.27338507743</v>
+        <v>46068.27338508102</v>
       </c>
     </row>
     <row r="230">
@@ -8257,7 +8257,7 @@
         <v>3.17</v>
       </c>
       <c r="H230" s="2" t="n">
-        <v>46072.27338508043</v>
+        <v>46072.27338508102</v>
       </c>
     </row>
     <row r="231">
@@ -8291,7 +8291,7 @@
         <v>4.62</v>
       </c>
       <c r="H231" s="2" t="n">
-        <v>46070.27338508346</v>
+        <v>46070.27338508102</v>
       </c>
     </row>
     <row r="232">
@@ -8325,7 +8325,7 @@
         <v>3.8</v>
       </c>
       <c r="H232" s="2" t="n">
-        <v>46087.2733850868</v>
+        <v>46087.27338508102</v>
       </c>
     </row>
     <row r="233">
@@ -8359,7 +8359,7 @@
         <v>2.75</v>
       </c>
       <c r="H233" s="2" t="n">
-        <v>46073.27338509</v>
+        <v>46073.27338509259</v>
       </c>
     </row>
     <row r="234">
@@ -8393,7 +8393,7 @@
         <v>1.85</v>
       </c>
       <c r="H234" s="2" t="n">
-        <v>46077.27338509307</v>
+        <v>46077.27338509259</v>
       </c>
     </row>
     <row r="235">
@@ -8427,7 +8427,7 @@
         <v>2.43</v>
       </c>
       <c r="H235" s="2" t="n">
-        <v>46085.27338509616</v>
+        <v>46085.27338509259</v>
       </c>
     </row>
     <row r="236">
@@ -8461,7 +8461,7 @@
         <v>3.31</v>
       </c>
       <c r="H236" s="2" t="n">
-        <v>46079.27338509941</v>
+        <v>46079.27338510417</v>
       </c>
     </row>
     <row r="237">
@@ -8495,7 +8495,7 @@
         <v>2.08</v>
       </c>
       <c r="H237" s="2" t="n">
-        <v>46066.27338510251</v>
+        <v>46066.27338510417</v>
       </c>
     </row>
     <row r="238">
@@ -8529,7 +8529,7 @@
         <v>0.13</v>
       </c>
       <c r="H238" s="2" t="n">
-        <v>46083.27338510558</v>
+        <v>46083.27338510417</v>
       </c>
     </row>
     <row r="239">
@@ -8563,7 +8563,7 @@
         <v>3.04</v>
       </c>
       <c r="H239" s="2" t="n">
-        <v>46073.27338510856</v>
+        <v>46073.27338510417</v>
       </c>
     </row>
     <row r="240">
@@ -8597,7 +8597,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H240" s="2" t="n">
-        <v>46086.27338511192</v>
+        <v>46086.27338511574</v>
       </c>
     </row>
     <row r="241">
@@ -8631,7 +8631,7 @@
         <v>3.8</v>
       </c>
       <c r="H241" s="2" t="n">
-        <v>46087.27338511511</v>
+        <v>46087.27338511574</v>
       </c>
     </row>
     <row r="242">
@@ -8665,7 +8665,7 @@
         <v>2.24</v>
       </c>
       <c r="H242" s="2" t="n">
-        <v>46071.27338511809</v>
+        <v>46071.27338511574</v>
       </c>
     </row>
     <row r="243">
@@ -8699,7 +8699,7 @@
         <v>3.29</v>
       </c>
       <c r="H243" s="2" t="n">
-        <v>46074.27338512147</v>
+        <v>46074.27338511574</v>
       </c>
     </row>
     <row r="244">
@@ -8733,7 +8733,7 @@
         <v>0.85</v>
       </c>
       <c r="H244" s="2" t="n">
-        <v>46066.27338512448</v>
+        <v>46066.27338512732</v>
       </c>
     </row>
     <row r="245">
@@ -8767,7 +8767,7 @@
         <v>4.51</v>
       </c>
       <c r="H245" s="2" t="n">
-        <v>46069.27338512751</v>
+        <v>46069.27338512732</v>
       </c>
     </row>
     <row r="246">
@@ -8801,7 +8801,7 @@
         <v>4.78</v>
       </c>
       <c r="H246" s="2" t="n">
-        <v>46085.27338513055</v>
+        <v>46085.27338512732</v>
       </c>
     </row>
     <row r="247">
@@ -8835,7 +8835,7 @@
         <v>3.87</v>
       </c>
       <c r="H247" s="2" t="n">
-        <v>46086.27338513376</v>
+        <v>46086.27338513889</v>
       </c>
     </row>
     <row r="248">
@@ -8869,7 +8869,7 @@
         <v>1.81</v>
       </c>
       <c r="H248" s="2" t="n">
-        <v>46069.27338513682</v>
+        <v>46069.27338513889</v>
       </c>
     </row>
     <row r="249">
@@ -8903,7 +8903,7 @@
         <v>2.65</v>
       </c>
       <c r="H249" s="2" t="n">
-        <v>46066.27338513995</v>
+        <v>46066.27338513889</v>
       </c>
     </row>
     <row r="250">
@@ -8937,7 +8937,7 @@
         <v>0.64</v>
       </c>
       <c r="H250" s="2" t="n">
-        <v>46072.27338514305</v>
+        <v>46072.27338513889</v>
       </c>
     </row>
     <row r="251">
@@ -8971,7 +8971,7 @@
         <v>4.42</v>
       </c>
       <c r="H251" s="2" t="n">
-        <v>46073.27338514624</v>
+        <v>46073.27338515046</v>
       </c>
     </row>
     <row r="252">
@@ -9005,7 +9005,7 @@
         <v>4.14</v>
       </c>
       <c r="H252" s="2" t="n">
-        <v>46073.27338514926</v>
+        <v>46073.27338515046</v>
       </c>
     </row>
     <row r="253">
@@ -9039,7 +9039,7 @@
         <v>3.54</v>
       </c>
       <c r="H253" s="2" t="n">
-        <v>46084.2733851523</v>
+        <v>46084.27338515046</v>
       </c>
     </row>
     <row r="254">
@@ -9073,7 +9073,7 @@
         <v>0.49</v>
       </c>
       <c r="H254" s="2" t="n">
-        <v>46085.27338515559</v>
+        <v>46085.27338515046</v>
       </c>
     </row>
     <row r="255">
@@ -9107,7 +9107,7 @@
         <v>0.85</v>
       </c>
       <c r="H255" s="2" t="n">
-        <v>46093.27338515866</v>
+        <v>46093.27338516204</v>
       </c>
     </row>
     <row r="256">
@@ -9141,7 +9141,7 @@
         <v>2.84</v>
       </c>
       <c r="H256" s="2" t="n">
-        <v>46072.27338516166</v>
+        <v>46072.27338516204</v>
       </c>
     </row>
     <row r="257">
@@ -9175,7 +9175,7 @@
         <v>4.53</v>
       </c>
       <c r="H257" s="2" t="n">
-        <v>46076.27338516464</v>
+        <v>46076.27338516204</v>
       </c>
     </row>
     <row r="258">
@@ -9209,7 +9209,7 @@
         <v>2.49</v>
       </c>
       <c r="H258" s="2" t="n">
-        <v>46077.27338516799</v>
+        <v>46077.27338517361</v>
       </c>
     </row>
     <row r="259">
@@ -9243,7 +9243,7 @@
         <v>2.84</v>
       </c>
       <c r="H259" s="2" t="n">
-        <v>46077.27338517116</v>
+        <v>46077.27338517361</v>
       </c>
     </row>
     <row r="260">
@@ -9277,7 +9277,7 @@
         <v>1.83</v>
       </c>
       <c r="H260" s="2" t="n">
-        <v>46071.27338517434</v>
+        <v>46071.27338517361</v>
       </c>
     </row>
     <row r="261">
@@ -9311,7 +9311,7 @@
         <v>0.54</v>
       </c>
       <c r="H261" s="2" t="n">
-        <v>46071.27338517747</v>
+        <v>46071.27338517361</v>
       </c>
     </row>
     <row r="262">
@@ -9345,7 +9345,7 @@
         <v>1.25</v>
       </c>
       <c r="H262" s="2" t="n">
-        <v>46086.27338518075</v>
+        <v>46086.27338518519</v>
       </c>
     </row>
     <row r="263">
@@ -9379,7 +9379,7 @@
         <v>2.34</v>
       </c>
       <c r="H263" s="2" t="n">
-        <v>46072.27338518508</v>
+        <v>46072.27338518519</v>
       </c>
     </row>
     <row r="264">
@@ -9413,7 +9413,7 @@
         <v>4.87</v>
       </c>
       <c r="H264" s="2" t="n">
-        <v>46067.27338518827</v>
+        <v>46067.27338518519</v>
       </c>
     </row>
     <row r="265">
@@ -9447,7 +9447,7 @@
         <v>2.28</v>
       </c>
       <c r="H265" s="2" t="n">
-        <v>46088.27338519215</v>
+        <v>46088.27338519676</v>
       </c>
     </row>
     <row r="266">
@@ -9481,7 +9481,7 @@
         <v>4.49</v>
       </c>
       <c r="H266" s="2" t="n">
-        <v>46086.27338519534</v>
+        <v>46086.27338519676</v>
       </c>
     </row>
     <row r="267">
@@ -9515,7 +9515,7 @@
         <v>3.87</v>
       </c>
       <c r="H267" s="2" t="n">
-        <v>46067.27338519838</v>
+        <v>46067.27338519676</v>
       </c>
     </row>
     <row r="268">
@@ -9549,7 +9549,7 @@
         <v>1.41</v>
       </c>
       <c r="H268" s="2" t="n">
-        <v>46088.27338520168</v>
+        <v>46088.27338519676</v>
       </c>
     </row>
     <row r="269">
@@ -9583,7 +9583,7 @@
         <v>3.89</v>
       </c>
       <c r="H269" s="2" t="n">
-        <v>46069.27338520473</v>
+        <v>46069.27338520833</v>
       </c>
     </row>
     <row r="270">
@@ -9617,7 +9617,7 @@
         <v>2.21</v>
       </c>
       <c r="H270" s="2" t="n">
-        <v>46072.27338520788</v>
+        <v>46072.27338520833</v>
       </c>
     </row>
     <row r="271">
@@ -9651,7 +9651,7 @@
         <v>3.93</v>
       </c>
       <c r="H271" s="2" t="n">
-        <v>46065.27338521123</v>
+        <v>46065.27338520833</v>
       </c>
     </row>
     <row r="272">
@@ -9685,7 +9685,7 @@
         <v>1.12</v>
       </c>
       <c r="H272" s="2" t="n">
-        <v>46070.2733852145</v>
+        <v>46070.27338521991</v>
       </c>
     </row>
     <row r="273">
@@ -9719,7 +9719,7 @@
         <v>0.26</v>
       </c>
       <c r="H273" s="2" t="n">
-        <v>46074.27338521754</v>
+        <v>46074.27338521991</v>
       </c>
     </row>
     <row r="274">
@@ -9753,7 +9753,7 @@
         <v>4.34</v>
       </c>
       <c r="H274" s="2" t="n">
-        <v>46090.27338522072</v>
+        <v>46090.27338521991</v>
       </c>
     </row>
     <row r="275">
@@ -9787,7 +9787,7 @@
         <v>2.8</v>
       </c>
       <c r="H275" s="2" t="n">
-        <v>46079.27338522377</v>
+        <v>46079.27338521991</v>
       </c>
     </row>
     <row r="276">
@@ -9821,7 +9821,7 @@
         <v>4.3</v>
       </c>
       <c r="H276" s="2" t="n">
-        <v>46088.27338522718</v>
+        <v>46088.27338523149</v>
       </c>
     </row>
     <row r="277">
@@ -9855,7 +9855,7 @@
         <v>3.39</v>
       </c>
       <c r="H277" s="2" t="n">
-        <v>46090.27338523039</v>
+        <v>46090.27338523149</v>
       </c>
     </row>
     <row r="278">
@@ -9889,7 +9889,7 @@
         <v>1.62</v>
       </c>
       <c r="H278" s="2" t="n">
-        <v>46072.27338523365</v>
+        <v>46072.27338523149</v>
       </c>
     </row>
     <row r="279">
@@ -9923,7 +9923,7 @@
         <v>4.76</v>
       </c>
       <c r="H279" s="2" t="n">
-        <v>46087.27338523684</v>
+        <v>46087.27338523149</v>
       </c>
     </row>
     <row r="280">
@@ -9957,7 +9957,7 @@
         <v>3.35</v>
       </c>
       <c r="H280" s="2" t="n">
-        <v>46067.27338523992</v>
+        <v>46067.27338524305</v>
       </c>
     </row>
     <row r="281">
@@ -9991,7 +9991,7 @@
         <v>4.4</v>
       </c>
       <c r="H281" s="2" t="n">
-        <v>46077.27338524309</v>
+        <v>46077.27338524305</v>
       </c>
     </row>
     <row r="282">
@@ -10025,7 +10025,7 @@
         <v>2.27</v>
       </c>
       <c r="H282" s="2" t="n">
-        <v>46072.27338524616</v>
+        <v>46072.27338524305</v>
       </c>
     </row>
     <row r="283">
@@ -10059,7 +10059,7 @@
         <v>2.57</v>
       </c>
       <c r="H283" s="2" t="n">
-        <v>46066.27338524933</v>
+        <v>46066.27338525463</v>
       </c>
     </row>
     <row r="284">
@@ -10093,7 +10093,7 @@
         <v>3.51</v>
       </c>
       <c r="H284" s="2" t="n">
-        <v>46091.27338525236</v>
+        <v>46091.27338525463</v>
       </c>
     </row>
     <row r="285">
@@ -10127,7 +10127,7 @@
         <v>2.18</v>
       </c>
       <c r="H285" s="2" t="n">
-        <v>46088.27338525549</v>
+        <v>46088.27338525463</v>
       </c>
     </row>
     <row r="286">
@@ -10161,7 +10161,7 @@
         <v>3.57</v>
       </c>
       <c r="H286" s="2" t="n">
-        <v>46065.27338525849</v>
+        <v>46065.27338525463</v>
       </c>
     </row>
     <row r="287">
@@ -10195,7 +10195,7 @@
         <v>1.33</v>
       </c>
       <c r="H287" s="2" t="n">
-        <v>46090.27338526186</v>
+        <v>46090.27338526621</v>
       </c>
     </row>
     <row r="288">
@@ -10229,7 +10229,7 @@
         <v>2.3</v>
       </c>
       <c r="H288" s="2" t="n">
-        <v>46066.27338526488</v>
+        <v>46066.27338526621</v>
       </c>
     </row>
     <row r="289">
@@ -10263,7 +10263,7 @@
         <v>1.63</v>
       </c>
       <c r="H289" s="2" t="n">
-        <v>46091.27338526789</v>
+        <v>46091.27338526621</v>
       </c>
     </row>
     <row r="290">
@@ -10297,7 +10297,7 @@
         <v>1.33</v>
       </c>
       <c r="H290" s="2" t="n">
-        <v>46072.2733852711</v>
+        <v>46072.27338526621</v>
       </c>
     </row>
     <row r="291">
@@ -10331,7 +10331,7 @@
         <v>4.74</v>
       </c>
       <c r="H291" s="2" t="n">
-        <v>46082.27338527414</v>
+        <v>46082.27338527777</v>
       </c>
     </row>
     <row r="292">
@@ -10365,7 +10365,7 @@
         <v>2.98</v>
       </c>
       <c r="H292" s="2" t="n">
-        <v>46066.27338527722</v>
+        <v>46066.27338527777</v>
       </c>
     </row>
     <row r="293">
@@ -10399,7 +10399,7 @@
         <v>0.51</v>
       </c>
       <c r="H293" s="2" t="n">
-        <v>46071.27338528029</v>
+        <v>46071.27338527777</v>
       </c>
     </row>
     <row r="294">
@@ -10433,7 +10433,7 @@
         <v>4.7</v>
       </c>
       <c r="H294" s="2" t="n">
-        <v>46066.27338528349</v>
+        <v>46066.27338527777</v>
       </c>
     </row>
     <row r="295">
@@ -10467,7 +10467,7 @@
         <v>4.29</v>
       </c>
       <c r="H295" s="2" t="n">
-        <v>46085.27338528657</v>
+        <v>46085.27338528935</v>
       </c>
     </row>
     <row r="296">
@@ -10501,7 +10501,7 @@
         <v>2.97</v>
       </c>
       <c r="H296" s="2" t="n">
-        <v>46072.27338528957</v>
+        <v>46072.27338528935</v>
       </c>
     </row>
     <row r="297">
@@ -10535,7 +10535,7 @@
         <v>4.41</v>
       </c>
       <c r="H297" s="2" t="n">
-        <v>46085.27338529281</v>
+        <v>46085.27338528935</v>
       </c>
     </row>
     <row r="298">
@@ -10569,7 +10569,7 @@
         <v>2.36</v>
       </c>
       <c r="H298" s="2" t="n">
-        <v>46086.27338529602</v>
+        <v>46086.27338530093</v>
       </c>
     </row>
     <row r="299">
@@ -10603,7 +10603,7 @@
         <v>1.9</v>
       </c>
       <c r="H299" s="2" t="n">
-        <v>46071.2733852993</v>
+        <v>46071.27338530093</v>
       </c>
     </row>
     <row r="300">
@@ -10637,7 +10637,7 @@
         <v>3.02</v>
       </c>
       <c r="H300" s="2" t="n">
-        <v>46082.27338530245</v>
+        <v>46082.27338530093</v>
       </c>
     </row>
     <row r="301">
@@ -10671,7 +10671,7 @@
         <v>2.05</v>
       </c>
       <c r="H301" s="2" t="n">
-        <v>46078.27338530582</v>
+        <v>46078.27338530093</v>
       </c>
     </row>
     <row r="302">
@@ -10705,7 +10705,7 @@
         <v>4.58</v>
       </c>
       <c r="H302" s="2" t="n">
-        <v>46083.27338530904</v>
+        <v>46083.2733853125</v>
       </c>
     </row>
     <row r="303">
@@ -10739,7 +10739,7 @@
         <v>2.1</v>
       </c>
       <c r="H303" s="2" t="n">
-        <v>46067.27338531227</v>
+        <v>46067.2733853125</v>
       </c>
     </row>
     <row r="304">
@@ -10773,7 +10773,7 @@
         <v>1.09</v>
       </c>
       <c r="H304" s="2" t="n">
-        <v>46069.27338531531</v>
+        <v>46069.2733853125</v>
       </c>
     </row>
     <row r="305">
@@ -10807,7 +10807,7 @@
         <v>2.04</v>
       </c>
       <c r="H305" s="2" t="n">
-        <v>46088.27338531856</v>
+        <v>46088.27338532407</v>
       </c>
     </row>
     <row r="306">
@@ -10841,7 +10841,7 @@
         <v>4.32</v>
       </c>
       <c r="H306" s="2" t="n">
-        <v>46073.27338532171</v>
+        <v>46073.27338532407</v>
       </c>
     </row>
     <row r="307">
@@ -10875,7 +10875,7 @@
         <v>1.36</v>
       </c>
       <c r="H307" s="2" t="n">
-        <v>46088.27338532489</v>
+        <v>46088.27338532407</v>
       </c>
     </row>
     <row r="308">
@@ -10909,7 +10909,7 @@
         <v>4.24</v>
       </c>
       <c r="H308" s="2" t="n">
-        <v>46072.27338532791</v>
+        <v>46072.27338532407</v>
       </c>
     </row>
     <row r="309">
@@ -10943,7 +10943,7 @@
         <v>0.28</v>
       </c>
       <c r="H309" s="2" t="n">
-        <v>46093.2733853313</v>
+        <v>46093.27338533565</v>
       </c>
     </row>
     <row r="310">
@@ -10977,7 +10977,7 @@
         <v>2.04</v>
       </c>
       <c r="H310" s="2" t="n">
-        <v>46077.27338533432</v>
+        <v>46077.27338533565</v>
       </c>
     </row>
     <row r="311">
@@ -11011,7 +11011,7 @@
         <v>0.19</v>
       </c>
       <c r="H311" s="2" t="n">
-        <v>46083.27338533768</v>
+        <v>46083.27338533565</v>
       </c>
     </row>
     <row r="312">
@@ -11045,7 +11045,7 @@
         <v>0.32</v>
       </c>
       <c r="H312" s="2" t="n">
-        <v>46073.27338534082</v>
+        <v>46073.27338533565</v>
       </c>
     </row>
     <row r="313">
@@ -11079,7 +11079,7 @@
         <v>0.64</v>
       </c>
       <c r="H313" s="2" t="n">
-        <v>46065.27338534386</v>
+        <v>46065.27338534722</v>
       </c>
     </row>
     <row r="314">
@@ -11113,7 +11113,7 @@
         <v>4.42</v>
       </c>
       <c r="H314" s="2" t="n">
-        <v>46089.27338534707</v>
+        <v>46089.27338534722</v>
       </c>
     </row>
     <row r="315">
@@ -11147,7 +11147,7 @@
         <v>1.93</v>
       </c>
       <c r="H315" s="2" t="n">
-        <v>46073.27338535023</v>
+        <v>46073.27338534722</v>
       </c>
     </row>
     <row r="316">
@@ -11181,7 +11181,7 @@
         <v>3.9</v>
       </c>
       <c r="H316" s="2" t="n">
-        <v>46091.27338535359</v>
+        <v>46091.2733853588</v>
       </c>
     </row>
     <row r="317">
@@ -11215,7 +11215,7 @@
         <v>0.64</v>
       </c>
       <c r="H317" s="2" t="n">
-        <v>46079.27338535673</v>
+        <v>46079.2733853588</v>
       </c>
     </row>
     <row r="318">
@@ -11249,7 +11249,7 @@
         <v>2.59</v>
       </c>
       <c r="H318" s="2" t="n">
-        <v>46073.27338535972</v>
+        <v>46073.2733853588</v>
       </c>
     </row>
     <row r="319">
@@ -11283,7 +11283,7 @@
         <v>4.04</v>
       </c>
       <c r="H319" s="2" t="n">
-        <v>46090.27338536282</v>
+        <v>46090.2733853588</v>
       </c>
     </row>
     <row r="320">
@@ -11317,7 +11317,7 @@
         <v>3.96</v>
       </c>
       <c r="H320" s="2" t="n">
-        <v>46087.27338536603</v>
+        <v>46087.27338537037</v>
       </c>
     </row>
     <row r="321">
@@ -11351,7 +11351,7 @@
         <v>2.66</v>
       </c>
       <c r="H321" s="2" t="n">
-        <v>46092.27338536912</v>
+        <v>46092.27338537037</v>
       </c>
     </row>
     <row r="322">
@@ -11385,7 +11385,7 @@
         <v>3.13</v>
       </c>
       <c r="H322" s="2" t="n">
-        <v>46079.2733853722</v>
+        <v>46079.27338537037</v>
       </c>
     </row>
     <row r="323">
@@ -11419,7 +11419,7 @@
         <v>2.14</v>
       </c>
       <c r="H323" s="2" t="n">
-        <v>46070.27338537537</v>
+        <v>46070.27338537037</v>
       </c>
     </row>
     <row r="324">
@@ -11453,7 +11453,7 @@
         <v>4.61</v>
       </c>
       <c r="H324" s="2" t="n">
-        <v>46084.27338537854</v>
+        <v>46084.27338538194</v>
       </c>
     </row>
     <row r="325">
@@ -11487,7 +11487,7 @@
         <v>4.45</v>
       </c>
       <c r="H325" s="2" t="n">
-        <v>46090.2733853817</v>
+        <v>46090.27338538194</v>
       </c>
     </row>
     <row r="326">
@@ -11521,7 +11521,7 @@
         <v>1.95</v>
       </c>
       <c r="H326" s="2" t="n">
-        <v>46074.27338538492</v>
+        <v>46074.27338538194</v>
       </c>
     </row>
     <row r="327">
@@ -11555,7 +11555,7 @@
         <v>3.2</v>
       </c>
       <c r="H327" s="2" t="n">
-        <v>46085.27338538808</v>
+        <v>46085.27338539352</v>
       </c>
     </row>
     <row r="328">
@@ -11589,7 +11589,7 @@
         <v>2.57</v>
       </c>
       <c r="H328" s="2" t="n">
-        <v>46091.27338539127</v>
+        <v>46091.27338539352</v>
       </c>
     </row>
     <row r="329">
@@ -11623,7 +11623,7 @@
         <v>2.53</v>
       </c>
       <c r="H329" s="2" t="n">
-        <v>46070.27338539435</v>
+        <v>46070.27338539352</v>
       </c>
     </row>
     <row r="330">
@@ -11657,7 +11657,7 @@
         <v>0.12</v>
       </c>
       <c r="H330" s="2" t="n">
-        <v>46094.2733853973</v>
+        <v>46094.27338539352</v>
       </c>
     </row>
     <row r="331">
@@ -11691,7 +11691,7 @@
         <v>1.57</v>
       </c>
       <c r="H331" s="2" t="n">
-        <v>46075.27338540064</v>
+        <v>46075.27338540509</v>
       </c>
     </row>
     <row r="332">
@@ -11725,7 +11725,7 @@
         <v>3.24</v>
       </c>
       <c r="H332" s="2" t="n">
-        <v>46068.27338540367</v>
+        <v>46068.27338540509</v>
       </c>
     </row>
     <row r="333">
@@ -11759,7 +11759,7 @@
         <v>0.41</v>
       </c>
       <c r="H333" s="2" t="n">
-        <v>46078.27338540673</v>
+        <v>46078.27338540509</v>
       </c>
     </row>
     <row r="334">
@@ -11793,7 +11793,7 @@
         <v>1.03</v>
       </c>
       <c r="H334" s="2" t="n">
-        <v>46088.27338541006</v>
+        <v>46088.27338540509</v>
       </c>
     </row>
     <row r="335">
@@ -11827,7 +11827,7 @@
         <v>0.16</v>
       </c>
       <c r="H335" s="2" t="n">
-        <v>46083.27338541315</v>
+        <v>46083.27338541667</v>
       </c>
     </row>
     <row r="336">
@@ -11861,7 +11861,7 @@
         <v>2.04</v>
       </c>
       <c r="H336" s="2" t="n">
-        <v>46085.27338541641</v>
+        <v>46085.27338541667</v>
       </c>
     </row>
     <row r="337">
@@ -11895,7 +11895,7 @@
         <v>3.31</v>
       </c>
       <c r="H337" s="2" t="n">
-        <v>46071.27338541944</v>
+        <v>46071.27338541667</v>
       </c>
     </row>
     <row r="338">
@@ -11929,7 +11929,7 @@
         <v>3.15</v>
       </c>
       <c r="H338" s="2" t="n">
-        <v>46072.2733854228</v>
+        <v>46072.27338542824</v>
       </c>
     </row>
     <row r="339">
@@ -11963,7 +11963,7 @@
         <v>3.67</v>
       </c>
       <c r="H339" s="2" t="n">
-        <v>46090.27338542591</v>
+        <v>46090.27338542824</v>
       </c>
     </row>
     <row r="340">
@@ -11997,7 +11997,7 @@
         <v>4.14</v>
       </c>
       <c r="H340" s="2" t="n">
-        <v>46085.27338542897</v>
+        <v>46085.27338542824</v>
       </c>
     </row>
     <row r="341">
@@ -12031,7 +12031,7 @@
         <v>1.53</v>
       </c>
       <c r="H341" s="2" t="n">
-        <v>46075.27338543216</v>
+        <v>46075.27338542824</v>
       </c>
     </row>
     <row r="342">
@@ -12065,7 +12065,7 @@
         <v>2.24</v>
       </c>
       <c r="H342" s="2" t="n">
-        <v>46091.2733854355</v>
+        <v>46091.27338543982</v>
       </c>
     </row>
     <row r="343">
@@ -12099,7 +12099,7 @@
         <v>4.42</v>
       </c>
       <c r="H343" s="2" t="n">
-        <v>46078.27338543857</v>
+        <v>46078.27338543982</v>
       </c>
     </row>
     <row r="344">
@@ -12133,7 +12133,7 @@
         <v>1.4</v>
       </c>
       <c r="H344" s="2" t="n">
-        <v>46075.27338544155</v>
+        <v>46075.27338543982</v>
       </c>
     </row>
     <row r="345">
@@ -12167,7 +12167,7 @@
         <v>1.47</v>
       </c>
       <c r="H345" s="2" t="n">
-        <v>46085.2733854449</v>
+        <v>46085.27338543982</v>
       </c>
     </row>
     <row r="346">
@@ -12201,7 +12201,7 @@
         <v>4.84</v>
       </c>
       <c r="H346" s="2" t="n">
-        <v>46094.27338544797</v>
+        <v>46094.27338545139</v>
       </c>
     </row>
     <row r="347">
@@ -12235,7 +12235,7 @@
         <v>0.21</v>
       </c>
       <c r="H347" s="2" t="n">
-        <v>46065.27338545102</v>
+        <v>46065.27338545139</v>
       </c>
     </row>
     <row r="348">
@@ -12269,7 +12269,7 @@
         <v>2.27</v>
       </c>
       <c r="H348" s="2" t="n">
-        <v>46093.27338545422</v>
+        <v>46093.27338545139</v>
       </c>
     </row>
     <row r="349">
@@ -12303,7 +12303,7 @@
         <v>1</v>
       </c>
       <c r="H349" s="2" t="n">
-        <v>46079.27338545902</v>
+        <v>46079.27338546296</v>
       </c>
     </row>
     <row r="350">
@@ -12337,7 +12337,7 @@
         <v>4.99</v>
       </c>
       <c r="H350" s="2" t="n">
-        <v>46090.27338546223</v>
+        <v>46090.27338546296</v>
       </c>
     </row>
     <row r="351">
@@ -12371,7 +12371,7 @@
         <v>1.38</v>
       </c>
       <c r="H351" s="2" t="n">
-        <v>46068.27338546528</v>
+        <v>46068.27338546296</v>
       </c>
     </row>
     <row r="352">
@@ -12405,7 +12405,7 @@
         <v>4.31</v>
       </c>
       <c r="H352" s="2" t="n">
-        <v>46083.2733854686</v>
+        <v>46083.27338546296</v>
       </c>
     </row>
     <row r="353">
@@ -12439,7 +12439,7 @@
         <v>4.5</v>
       </c>
       <c r="H353" s="2" t="n">
-        <v>46088.2733854717</v>
+        <v>46088.27338547454</v>
       </c>
     </row>
     <row r="354">
@@ -12473,7 +12473,7 @@
         <v>4.59</v>
       </c>
       <c r="H354" s="2" t="n">
-        <v>46081.27338547476</v>
+        <v>46081.27338547454</v>
       </c>
     </row>
     <row r="355">
@@ -12507,7 +12507,7 @@
         <v>0.38</v>
       </c>
       <c r="H355" s="2" t="n">
-        <v>46084.27338547802</v>
+        <v>46084.27338547454</v>
       </c>
     </row>
     <row r="356">
@@ -12541,7 +12541,7 @@
         <v>2.56</v>
       </c>
       <c r="H356" s="2" t="n">
-        <v>46077.27338548119</v>
+        <v>46077.27338548611</v>
       </c>
     </row>
     <row r="357">
@@ -12575,7 +12575,7 @@
         <v>1.48</v>
       </c>
       <c r="H357" s="2" t="n">
-        <v>46083.27338548433</v>
+        <v>46083.27338548611</v>
       </c>
     </row>
     <row r="358">
@@ -12609,7 +12609,7 @@
         <v>1.44</v>
       </c>
       <c r="H358" s="2" t="n">
-        <v>46069.27338548753</v>
+        <v>46069.27338548611</v>
       </c>
     </row>
     <row r="359">
@@ -12643,7 +12643,7 @@
         <v>0</v>
       </c>
       <c r="H359" s="2" t="n">
-        <v>46069.27338549082</v>
+        <v>46069.27338548611</v>
       </c>
     </row>
     <row r="360">
@@ -12677,7 +12677,7 @@
         <v>0.58</v>
       </c>
       <c r="H360" s="2" t="n">
-        <v>46069.27338549398</v>
+        <v>46069.27338549768</v>
       </c>
     </row>
     <row r="361">
@@ -12711,7 +12711,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="H361" s="2" t="n">
-        <v>46089.27338549703</v>
+        <v>46089.27338549768</v>
       </c>
     </row>
     <row r="362">
@@ -12745,7 +12745,7 @@
         <v>2.38</v>
       </c>
       <c r="H362" s="2" t="n">
-        <v>46081.27338550008</v>
+        <v>46081.27338549768</v>
       </c>
     </row>
     <row r="363">
@@ -12779,7 +12779,7 @@
         <v>4.19</v>
       </c>
       <c r="H363" s="2" t="n">
-        <v>46072.27338550336</v>
+        <v>46072.27338549768</v>
       </c>
     </row>
     <row r="364">
@@ -12813,7 +12813,7 @@
         <v>4.54</v>
       </c>
       <c r="H364" s="2" t="n">
-        <v>46073.27338550641</v>
+        <v>46073.27338550926</v>
       </c>
     </row>
     <row r="365">
@@ -12847,7 +12847,7 @@
         <v>0.15</v>
       </c>
       <c r="H365" s="2" t="n">
-        <v>46076.27338550953</v>
+        <v>46076.27338550926</v>
       </c>
     </row>
     <row r="366">
@@ -12881,7 +12881,7 @@
         <v>3.63</v>
       </c>
       <c r="H366" s="2" t="n">
-        <v>46086.27338551251</v>
+        <v>46086.27338550926</v>
       </c>
     </row>
     <row r="367">
@@ -12915,7 +12915,7 @@
         <v>3.14</v>
       </c>
       <c r="H367" s="2" t="n">
-        <v>46076.27338551587</v>
+        <v>46076.27338552084</v>
       </c>
     </row>
     <row r="368">
@@ -12949,7 +12949,7 @@
         <v>3.46</v>
       </c>
       <c r="H368" s="2" t="n">
-        <v>46070.27338551888</v>
+        <v>46070.27338552084</v>
       </c>
     </row>
     <row r="369">
@@ -12983,7 +12983,7 @@
         <v>0.64</v>
       </c>
       <c r="H369" s="2" t="n">
-        <v>46071.27338552188</v>
+        <v>46071.27338552084</v>
       </c>
     </row>
     <row r="370">
@@ -13017,7 +13017,7 @@
         <v>1.08</v>
       </c>
       <c r="H370" s="2" t="n">
-        <v>46074.27338552497</v>
+        <v>46074.27338552084</v>
       </c>
     </row>
     <row r="371">
@@ -13051,7 +13051,7 @@
         <v>2.19</v>
       </c>
       <c r="H371" s="2" t="n">
-        <v>46078.27338552813</v>
+        <v>46078.2733855324</v>
       </c>
     </row>
     <row r="372">
@@ -13085,7 +13085,7 @@
         <v>3.09</v>
       </c>
       <c r="H372" s="2" t="n">
-        <v>46076.27338553128</v>
+        <v>46076.2733855324</v>
       </c>
     </row>
     <row r="373">
@@ -13119,7 +13119,7 @@
         <v>2.99</v>
       </c>
       <c r="H373" s="2" t="n">
-        <v>46067.27338553428</v>
+        <v>46067.2733855324</v>
       </c>
     </row>
     <row r="374">
@@ -13153,7 +13153,7 @@
         <v>4.21</v>
       </c>
       <c r="H374" s="2" t="n">
-        <v>46083.27338553743</v>
+        <v>46083.2733855324</v>
       </c>
     </row>
     <row r="375">
@@ -13187,7 +13187,7 @@
         <v>3.2</v>
       </c>
       <c r="H375" s="2" t="n">
-        <v>46094.27338554053</v>
+        <v>46094.27338554398</v>
       </c>
     </row>
     <row r="376">
@@ -13221,7 +13221,7 @@
         <v>1.94</v>
       </c>
       <c r="H376" s="2" t="n">
-        <v>46087.27338554369</v>
+        <v>46087.27338554398</v>
       </c>
     </row>
     <row r="377">
@@ -13255,7 +13255,7 @@
         <v>1.84</v>
       </c>
       <c r="H377" s="2" t="n">
-        <v>46082.27338554677</v>
+        <v>46082.27338554398</v>
       </c>
     </row>
     <row r="378">
@@ -13289,7 +13289,7 @@
         <v>0.06</v>
       </c>
       <c r="H378" s="2" t="n">
-        <v>46075.27338555005</v>
+        <v>46075.27338555556</v>
       </c>
     </row>
     <row r="379">
@@ -13323,7 +13323,7 @@
         <v>2.35</v>
       </c>
       <c r="H379" s="2" t="n">
-        <v>46081.27338555313</v>
+        <v>46081.27338555556</v>
       </c>
     </row>
     <row r="380">
@@ -13357,7 +13357,7 @@
         <v>4.23</v>
       </c>
       <c r="H380" s="2" t="n">
-        <v>46071.27338555619</v>
+        <v>46071.27338555556</v>
       </c>
     </row>
     <row r="381">
@@ -13391,7 +13391,7 @@
         <v>1.57</v>
       </c>
       <c r="H381" s="2" t="n">
-        <v>46073.27338555941</v>
+        <v>46073.27338555556</v>
       </c>
     </row>
     <row r="382">
@@ -13425,7 +13425,7 @@
         <v>0.29</v>
       </c>
       <c r="H382" s="2" t="n">
-        <v>46078.27338556272</v>
+        <v>46078.27338556713</v>
       </c>
     </row>
     <row r="383">
@@ -13459,7 +13459,7 @@
         <v>0.86</v>
       </c>
       <c r="H383" s="2" t="n">
-        <v>46067.27338556587</v>
+        <v>46067.27338556713</v>
       </c>
     </row>
     <row r="384">
@@ -13493,7 +13493,7 @@
         <v>4.5</v>
       </c>
       <c r="H384" s="2" t="n">
-        <v>46075.27338556896</v>
+        <v>46075.27338556713</v>
       </c>
     </row>
     <row r="385">
@@ -13527,7 +13527,7 @@
         <v>0.02</v>
       </c>
       <c r="H385" s="2" t="n">
-        <v>46081.27338557212</v>
+        <v>46081.27338556713</v>
       </c>
     </row>
     <row r="386">
@@ -13561,7 +13561,7 @@
         <v>1.89</v>
       </c>
       <c r="H386" s="2" t="n">
-        <v>46072.27338557515</v>
+        <v>46072.2733855787</v>
       </c>
     </row>
     <row r="387">
@@ -13595,7 +13595,7 @@
         <v>0.51</v>
       </c>
       <c r="H387" s="2" t="n">
-        <v>46081.27338557821</v>
+        <v>46081.2733855787</v>
       </c>
     </row>
     <row r="388">
@@ -13629,7 +13629,7 @@
         <v>3.14</v>
       </c>
       <c r="H388" s="2" t="n">
-        <v>46084.27338558131</v>
+        <v>46084.2733855787</v>
       </c>
     </row>
     <row r="389">
@@ -13663,7 +13663,7 @@
         <v>1.13</v>
       </c>
       <c r="H389" s="2" t="n">
-        <v>46082.27338558457</v>
+        <v>46082.27338559028</v>
       </c>
     </row>
     <row r="390">
@@ -13697,7 +13697,7 @@
         <v>3.2</v>
       </c>
       <c r="H390" s="2" t="n">
-        <v>46066.27338558766</v>
+        <v>46066.27338559028</v>
       </c>
     </row>
     <row r="391">
@@ -13731,7 +13731,7 @@
         <v>4.18</v>
       </c>
       <c r="H391" s="2" t="n">
-        <v>46079.27338559068</v>
+        <v>46079.27338559028</v>
       </c>
     </row>
     <row r="392">
@@ -13765,7 +13765,7 @@
         <v>1.81</v>
       </c>
       <c r="H392" s="2" t="n">
-        <v>46080.27338559375</v>
+        <v>46080.27338559028</v>
       </c>
     </row>
     <row r="393">
@@ -13799,7 +13799,7 @@
         <v>0.39</v>
       </c>
       <c r="H393" s="2" t="n">
-        <v>46069.27338559704</v>
+        <v>46069.27338560185</v>
       </c>
     </row>
     <row r="394">
@@ -13833,7 +13833,7 @@
         <v>2.23</v>
       </c>
       <c r="H394" s="2" t="n">
-        <v>46067.27338560009</v>
+        <v>46067.27338560185</v>
       </c>
     </row>
     <row r="395">
@@ -13867,7 +13867,7 @@
         <v>4.78</v>
       </c>
       <c r="H395" s="2" t="n">
-        <v>46075.27338560327</v>
+        <v>46075.27338560185</v>
       </c>
     </row>
     <row r="396">
@@ -13901,7 +13901,7 @@
         <v>2.65</v>
       </c>
       <c r="H396" s="2" t="n">
-        <v>46076.27338560624</v>
+        <v>46076.27338560185</v>
       </c>
     </row>
     <row r="397">
@@ -13935,7 +13935,7 @@
         <v>0.64</v>
       </c>
       <c r="H397" s="2" t="n">
-        <v>46067.2733856095</v>
+        <v>46067.27338561343</v>
       </c>
     </row>
     <row r="398">
@@ -13969,7 +13969,7 @@
         <v>4.66</v>
       </c>
       <c r="H398" s="2" t="n">
-        <v>46075.27338561265</v>
+        <v>46075.27338561343</v>
       </c>
     </row>
     <row r="399">
@@ -14003,7 +14003,7 @@
         <v>1.48</v>
       </c>
       <c r="H399" s="2" t="n">
-        <v>46076.27338561569</v>
+        <v>46076.27338561343</v>
       </c>
     </row>
     <row r="400">
@@ -14037,7 +14037,7 @@
         <v>0.84</v>
       </c>
       <c r="H400" s="2" t="n">
-        <v>46083.2733856189</v>
+        <v>46083.27338561343</v>
       </c>
     </row>
     <row r="401">
@@ -14071,7 +14071,7 @@
         <v>2.7</v>
       </c>
       <c r="H401" s="2" t="n">
-        <v>46065.27338562201</v>
+        <v>46065.273385625</v>
       </c>
     </row>
     <row r="402">
@@ -14105,7 +14105,7 @@
         <v>2.28</v>
       </c>
       <c r="H402" s="2" t="n">
-        <v>46088.27338562506</v>
+        <v>46088.273385625</v>
       </c>
     </row>
     <row r="403">
@@ -14139,7 +14139,7 @@
         <v>1.01</v>
       </c>
       <c r="H403" s="2" t="n">
-        <v>46067.27338562808</v>
+        <v>46067.273385625</v>
       </c>
     </row>
     <row r="404">
@@ -14173,7 +14173,7 @@
         <v>4.41</v>
       </c>
       <c r="H404" s="2" t="n">
-        <v>46079.27338563131</v>
+        <v>46079.27338563657</v>
       </c>
     </row>
     <row r="405">
@@ -14207,7 +14207,7 @@
         <v>1.57</v>
       </c>
       <c r="H405" s="2" t="n">
-        <v>46090.27338563434</v>
+        <v>46090.27338563657</v>
       </c>
     </row>
     <row r="406">
@@ -14241,7 +14241,7 @@
         <v>4.75</v>
       </c>
       <c r="H406" s="2" t="n">
-        <v>46065.27338563747</v>
+        <v>46065.27338563657</v>
       </c>
     </row>
     <row r="407">
@@ -14275,7 +14275,7 @@
         <v>0.61</v>
       </c>
       <c r="H407" s="2" t="n">
-        <v>46081.27338564061</v>
+        <v>46081.27338563657</v>
       </c>
     </row>
     <row r="408">
@@ -14309,7 +14309,7 @@
         <v>2.48</v>
       </c>
       <c r="H408" s="2" t="n">
-        <v>46090.27338564388</v>
+        <v>46090.27338564815</v>
       </c>
     </row>
     <row r="409">
@@ -14343,7 +14343,7 @@
         <v>4.69</v>
       </c>
       <c r="H409" s="2" t="n">
-        <v>46071.27338564718</v>
+        <v>46071.27338564815</v>
       </c>
     </row>
     <row r="410">
@@ -14377,7 +14377,7 @@
         <v>1.17</v>
       </c>
       <c r="H410" s="2" t="n">
-        <v>46094.27338565017</v>
+        <v>46094.27338564815</v>
       </c>
     </row>
     <row r="411">
@@ -14411,7 +14411,7 @@
         <v>4.39</v>
       </c>
       <c r="H411" s="2" t="n">
-        <v>46066.27338565344</v>
+        <v>46066.27338564815</v>
       </c>
     </row>
     <row r="412">
@@ -14445,7 +14445,7 @@
         <v>2.62</v>
       </c>
       <c r="H412" s="2" t="n">
-        <v>46093.27338565647</v>
+        <v>46093.27338565972</v>
       </c>
     </row>
     <row r="413">
@@ -14479,7 +14479,7 @@
         <v>4.55</v>
       </c>
       <c r="H413" s="2" t="n">
-        <v>46084.27338565941</v>
+        <v>46084.27338565972</v>
       </c>
     </row>
     <row r="414">
@@ -14513,7 +14513,7 @@
         <v>0.98</v>
       </c>
       <c r="H414" s="2" t="n">
-        <v>46074.27338566261</v>
+        <v>46074.27338565972</v>
       </c>
     </row>
     <row r="415">
@@ -14547,7 +14547,7 @@
         <v>2.91</v>
       </c>
       <c r="H415" s="2" t="n">
-        <v>46067.27338566577</v>
+        <v>46067.27338567129</v>
       </c>
     </row>
     <row r="416">
@@ -14581,7 +14581,7 @@
         <v>2.63</v>
       </c>
       <c r="H416" s="2" t="n">
-        <v>46069.27338566884</v>
+        <v>46069.27338567129</v>
       </c>
     </row>
     <row r="417">
@@ -14615,7 +14615,7 @@
         <v>4.02</v>
       </c>
       <c r="H417" s="2" t="n">
-        <v>46094.27338567198</v>
+        <v>46094.27338567129</v>
       </c>
     </row>
     <row r="418">
@@ -14649,7 +14649,7 @@
         <v>1.37</v>
       </c>
       <c r="H418" s="2" t="n">
-        <v>46074.27338567578</v>
+        <v>46074.27338567129</v>
       </c>
     </row>
     <row r="419">
@@ -14683,7 +14683,7 @@
         <v>0.38</v>
       </c>
       <c r="H419" s="2" t="n">
-        <v>46091.27338567901</v>
+        <v>46091.27338568287</v>
       </c>
     </row>
     <row r="420">
@@ -14717,7 +14717,7 @@
         <v>0.89</v>
       </c>
       <c r="H420" s="2" t="n">
-        <v>46069.27338568201</v>
+        <v>46069.27338568287</v>
       </c>
     </row>
     <row r="421">
@@ -14751,7 +14751,7 @@
         <v>1.27</v>
       </c>
       <c r="H421" s="2" t="n">
-        <v>46073.27338568516</v>
+        <v>46073.27338568287</v>
       </c>
     </row>
     <row r="422">
@@ -14785,7 +14785,7 @@
         <v>3.62</v>
       </c>
       <c r="H422" s="2" t="n">
-        <v>46082.27338568861</v>
+        <v>46082.27338568287</v>
       </c>
     </row>
     <row r="423">
@@ -14819,7 +14819,7 @@
         <v>0.52</v>
       </c>
       <c r="H423" s="2" t="n">
-        <v>46070.27338569181</v>
+        <v>46070.27338569445</v>
       </c>
     </row>
     <row r="424">
@@ -14853,7 +14853,7 @@
         <v>0.9</v>
       </c>
       <c r="H424" s="2" t="n">
-        <v>46086.27338569484</v>
+        <v>46086.27338569445</v>
       </c>
     </row>
     <row r="425">
@@ -14887,7 +14887,7 @@
         <v>4.5</v>
       </c>
       <c r="H425" s="2" t="n">
-        <v>46080.27338569798</v>
+        <v>46080.27338569445</v>
       </c>
     </row>
     <row r="426">
@@ -14921,7 +14921,7 @@
         <v>3.86</v>
       </c>
       <c r="H426" s="2" t="n">
-        <v>46088.27338570207</v>
+        <v>46088.27338570602</v>
       </c>
     </row>
     <row r="427">
@@ -14955,7 +14955,7 @@
         <v>4.19</v>
       </c>
       <c r="H427" s="2" t="n">
-        <v>46078.27338570528</v>
+        <v>46078.27338570602</v>
       </c>
     </row>
     <row r="428">
@@ -14989,7 +14989,7 @@
         <v>1.36</v>
       </c>
       <c r="H428" s="2" t="n">
-        <v>46094.27338570838</v>
+        <v>46094.27338570602</v>
       </c>
     </row>
     <row r="429">
@@ -15023,7 +15023,7 @@
         <v>0.25</v>
       </c>
       <c r="H429" s="2" t="n">
-        <v>46083.2733857116</v>
+        <v>46083.27338570602</v>
       </c>
     </row>
     <row r="430">
@@ -15057,7 +15057,7 @@
         <v>4.98</v>
       </c>
       <c r="H430" s="2" t="n">
-        <v>46078.27338571467</v>
+        <v>46078.27338571759</v>
       </c>
     </row>
     <row r="431">
@@ -15091,7 +15091,7 @@
         <v>2.64</v>
       </c>
       <c r="H431" s="2" t="n">
-        <v>46094.27338571779</v>
+        <v>46094.27338571759</v>
       </c>
     </row>
     <row r="432">
@@ -15125,7 +15125,7 @@
         <v>4.84</v>
       </c>
       <c r="H432" s="2" t="n">
-        <v>46072.27338572087</v>
+        <v>46072.27338571759</v>
       </c>
     </row>
     <row r="433">
@@ -15159,7 +15159,7 @@
         <v>3.4</v>
       </c>
       <c r="H433" s="2" t="n">
-        <v>46081.27338572413</v>
+        <v>46081.27338572917</v>
       </c>
     </row>
     <row r="434">
@@ -15193,7 +15193,7 @@
         <v>4.86</v>
       </c>
       <c r="H434" s="2" t="n">
-        <v>46075.27338572729</v>
+        <v>46075.27338572917</v>
       </c>
     </row>
     <row r="435">
@@ -15227,7 +15227,7 @@
         <v>2.04</v>
       </c>
       <c r="H435" s="2" t="n">
-        <v>46072.27338573028</v>
+        <v>46072.27338572917</v>
       </c>
     </row>
     <row r="436">
@@ -15261,7 +15261,7 @@
         <v>2.68</v>
       </c>
       <c r="H436" s="2" t="n">
-        <v>46084.27338573334</v>
+        <v>46084.27338572917</v>
       </c>
     </row>
     <row r="437">
@@ -15295,7 +15295,7 @@
         <v>0.8</v>
       </c>
       <c r="H437" s="2" t="n">
-        <v>46070.27338573664</v>
+        <v>46070.27338574074</v>
       </c>
     </row>
     <row r="438">
@@ -15329,7 +15329,7 @@
         <v>1.55</v>
       </c>
       <c r="H438" s="2" t="n">
-        <v>46088.27338573973</v>
+        <v>46088.27338574074</v>
       </c>
     </row>
     <row r="439">
@@ -15363,7 +15363,7 @@
         <v>1.57</v>
       </c>
       <c r="H439" s="2" t="n">
-        <v>46077.27338574269</v>
+        <v>46077.27338574074</v>
       </c>
     </row>
     <row r="440">
@@ -15397,7 +15397,7 @@
         <v>1.34</v>
       </c>
       <c r="H440" s="2" t="n">
-        <v>46068.273385746</v>
+        <v>46068.27338574074</v>
       </c>
     </row>
     <row r="441">
@@ -15431,7 +15431,7 @@
         <v>3.58</v>
       </c>
       <c r="H441" s="2" t="n">
-        <v>46094.27338574929</v>
+        <v>46094.27338575231</v>
       </c>
     </row>
     <row r="442">
@@ -15465,7 +15465,7 @@
         <v>0.77</v>
       </c>
       <c r="H442" s="2" t="n">
-        <v>46093.27338575255</v>
+        <v>46093.27338575231</v>
       </c>
     </row>
     <row r="443">
@@ -15499,7 +15499,7 @@
         <v>3.87</v>
       </c>
       <c r="H443" s="2" t="n">
-        <v>46082.27338575554</v>
+        <v>46082.27338575231</v>
       </c>
     </row>
     <row r="444">
@@ -15533,7 +15533,7 @@
         <v>4.96</v>
       </c>
       <c r="H444" s="2" t="n">
-        <v>46077.27338575873</v>
+        <v>46077.27338576389</v>
       </c>
     </row>
     <row r="445">
@@ -15567,7 +15567,7 @@
         <v>0.26</v>
       </c>
       <c r="H445" s="2" t="n">
-        <v>46079.27338576193</v>
+        <v>46079.27338576389</v>
       </c>
     </row>
     <row r="446">
@@ -15601,7 +15601,7 @@
         <v>3.05</v>
       </c>
       <c r="H446" s="2" t="n">
-        <v>46094.27338576509</v>
+        <v>46094.27338576389</v>
       </c>
     </row>
     <row r="447">
@@ -15635,7 +15635,7 @@
         <v>3.67</v>
       </c>
       <c r="H447" s="2" t="n">
-        <v>46085.27338576828</v>
+        <v>46085.27338576389</v>
       </c>
     </row>
     <row r="448">
@@ -15669,7 +15669,7 @@
         <v>3.34</v>
       </c>
       <c r="H448" s="2" t="n">
-        <v>46074.27338577151</v>
+        <v>46074.27338577546</v>
       </c>
     </row>
     <row r="449">
@@ -15703,7 +15703,7 @@
         <v>4.32</v>
       </c>
       <c r="H449" s="2" t="n">
-        <v>46077.27338577453</v>
+        <v>46077.27338577546</v>
       </c>
     </row>
     <row r="450">
@@ -15737,7 +15737,7 @@
         <v>1.99</v>
       </c>
       <c r="H450" s="2" t="n">
-        <v>46089.2733857777</v>
+        <v>46089.27338577546</v>
       </c>
     </row>
     <row r="451">
@@ -15771,7 +15771,7 @@
         <v>3.07</v>
       </c>
       <c r="H451" s="2" t="n">
-        <v>46090.27338578107</v>
+        <v>46090.27338577546</v>
       </c>
     </row>
     <row r="452">
@@ -15805,7 +15805,7 @@
         <v>4.84</v>
       </c>
       <c r="H452" s="2" t="n">
-        <v>46074.27338578409</v>
+        <v>46074.27338578703</v>
       </c>
     </row>
     <row r="453">
@@ -15839,7 +15839,7 @@
         <v>3.83</v>
       </c>
       <c r="H453" s="2" t="n">
-        <v>46083.27338578716</v>
+        <v>46083.27338578703</v>
       </c>
     </row>
     <row r="454">
@@ -15873,7 +15873,7 @@
         <v>0.12</v>
       </c>
       <c r="H454" s="2" t="n">
-        <v>46091.27338579018</v>
+        <v>46091.27338578703</v>
       </c>
     </row>
     <row r="455">
@@ -15907,7 +15907,7 @@
         <v>0.6</v>
       </c>
       <c r="H455" s="2" t="n">
-        <v>46071.27338579338</v>
+        <v>46071.27338579861</v>
       </c>
     </row>
     <row r="456">
@@ -15941,7 +15941,7 @@
         <v>4.29</v>
       </c>
       <c r="H456" s="2" t="n">
-        <v>46081.27338579653</v>
+        <v>46081.27338579861</v>
       </c>
     </row>
     <row r="457">
@@ -15975,7 +15975,7 @@
         <v>4.8</v>
       </c>
       <c r="H457" s="2" t="n">
-        <v>46071.27338579959</v>
+        <v>46071.27338579861</v>
       </c>
     </row>
     <row r="458">
@@ -16009,7 +16009,7 @@
         <v>4.74</v>
       </c>
       <c r="H458" s="2" t="n">
-        <v>46089.27338580263</v>
+        <v>46089.27338579861</v>
       </c>
     </row>
     <row r="459">
@@ -16043,7 +16043,7 @@
         <v>2.97</v>
       </c>
       <c r="H459" s="2" t="n">
-        <v>46081.27338580583</v>
+        <v>46081.27338581019</v>
       </c>
     </row>
     <row r="460">
@@ -16077,7 +16077,7 @@
         <v>2.3</v>
       </c>
       <c r="H460" s="2" t="n">
-        <v>46093.27338580904</v>
+        <v>46093.27338581019</v>
       </c>
     </row>
     <row r="461">
@@ -16111,7 +16111,7 @@
         <v>1.05</v>
       </c>
       <c r="H461" s="2" t="n">
-        <v>46087.27338581206</v>
+        <v>46087.27338581019</v>
       </c>
     </row>
     <row r="462">
@@ -16145,7 +16145,7 @@
         <v>4.85</v>
       </c>
       <c r="H462" s="2" t="n">
-        <v>46087.27338581526</v>
+        <v>46087.27338581019</v>
       </c>
     </row>
     <row r="463">
@@ -16179,7 +16179,7 @@
         <v>2.41</v>
       </c>
       <c r="H463" s="2" t="n">
-        <v>46078.27338581848</v>
+        <v>46078.27338582176</v>
       </c>
     </row>
     <row r="464">
@@ -16213,7 +16213,7 @@
         <v>2.45</v>
       </c>
       <c r="H464" s="2" t="n">
-        <v>46084.27338582161</v>
+        <v>46084.27338582176</v>
       </c>
     </row>
     <row r="465">
@@ -16247,7 +16247,7 @@
         <v>4.08</v>
       </c>
       <c r="H465" s="2" t="n">
-        <v>46081.27338582482</v>
+        <v>46081.27338582176</v>
       </c>
     </row>
     <row r="466">
@@ -16281,7 +16281,7 @@
         <v>0.42</v>
       </c>
       <c r="H466" s="2" t="n">
-        <v>46084.27338582811</v>
+        <v>46084.27338583333</v>
       </c>
     </row>
     <row r="467">
@@ -16315,7 +16315,7 @@
         <v>0.97</v>
       </c>
       <c r="H467" s="2" t="n">
-        <v>46080.27338583134</v>
+        <v>46080.27338583333</v>
       </c>
     </row>
     <row r="468">
@@ -16349,7 +16349,7 @@
         <v>0.5</v>
       </c>
       <c r="H468" s="2" t="n">
-        <v>46069.27338583438</v>
+        <v>46069.27338583333</v>
       </c>
     </row>
     <row r="469">
@@ -16383,7 +16383,7 @@
         <v>4.8</v>
       </c>
       <c r="H469" s="2" t="n">
-        <v>46079.27338583751</v>
+        <v>46079.27338583333</v>
       </c>
     </row>
     <row r="470">
@@ -16417,7 +16417,7 @@
         <v>0.18</v>
       </c>
       <c r="H470" s="2" t="n">
-        <v>46078.27338584072</v>
+        <v>46078.27338584491</v>
       </c>
     </row>
     <row r="471">
@@ -16451,7 +16451,7 @@
         <v>0.37</v>
       </c>
       <c r="H471" s="2" t="n">
-        <v>46088.27338584371</v>
+        <v>46088.27338584491</v>
       </c>
     </row>
     <row r="472">
@@ -16485,7 +16485,7 @@
         <v>3.72</v>
       </c>
       <c r="H472" s="2" t="n">
-        <v>46079.27338584681</v>
+        <v>46079.27338584491</v>
       </c>
     </row>
     <row r="473">
@@ -16519,7 +16519,7 @@
         <v>1.11</v>
       </c>
       <c r="H473" s="2" t="n">
-        <v>46093.27338584996</v>
+        <v>46093.27338584491</v>
       </c>
     </row>
     <row r="474">
@@ -16553,7 +16553,7 @@
         <v>0.52</v>
       </c>
       <c r="H474" s="2" t="n">
-        <v>46068.27338585298</v>
+        <v>46068.27338585648</v>
       </c>
     </row>
     <row r="475">
@@ -16587,7 +16587,7 @@
         <v>4.88</v>
       </c>
       <c r="H475" s="2" t="n">
-        <v>46071.27338585602</v>
+        <v>46071.27338585648</v>
       </c>
     </row>
     <row r="476">
@@ -16621,7 +16621,7 @@
         <v>4.47</v>
       </c>
       <c r="H476" s="2" t="n">
-        <v>46083.2733858592</v>
+        <v>46083.27338585648</v>
       </c>
     </row>
     <row r="477">
@@ -16655,7 +16655,7 @@
         <v>1.43</v>
       </c>
       <c r="H477" s="2" t="n">
-        <v>46092.27338586249</v>
+        <v>46092.27338586806</v>
       </c>
     </row>
     <row r="478">
@@ -16689,7 +16689,7 @@
         <v>2.33</v>
       </c>
       <c r="H478" s="2" t="n">
-        <v>46071.2733858655</v>
+        <v>46071.27338586806</v>
       </c>
     </row>
     <row r="479">
@@ -16723,7 +16723,7 @@
         <v>0.36</v>
       </c>
       <c r="H479" s="2" t="n">
-        <v>46080.27338586863</v>
+        <v>46080.27338586806</v>
       </c>
     </row>
     <row r="480">
@@ -16757,7 +16757,7 @@
         <v>4.6</v>
       </c>
       <c r="H480" s="2" t="n">
-        <v>46087.27338587165</v>
+        <v>46087.27338586806</v>
       </c>
     </row>
     <row r="481">
@@ -16791,7 +16791,7 @@
         <v>1.05</v>
       </c>
       <c r="H481" s="2" t="n">
-        <v>46072.27338587499</v>
+        <v>46072.27338587963</v>
       </c>
     </row>
     <row r="482">
@@ -16825,7 +16825,7 @@
         <v>2.23</v>
       </c>
       <c r="H482" s="2" t="n">
-        <v>46084.27338587823</v>
+        <v>46084.27338587963</v>
       </c>
     </row>
     <row r="483">
@@ -16859,7 +16859,7 @@
         <v>2.41</v>
       </c>
       <c r="H483" s="2" t="n">
-        <v>46089.27338588129</v>
+        <v>46089.27338587963</v>
       </c>
     </row>
     <row r="484">
@@ -16893,7 +16893,7 @@
         <v>0.6</v>
       </c>
       <c r="H484" s="2" t="n">
-        <v>46084.2733858845</v>
+        <v>46084.27338587963</v>
       </c>
     </row>
     <row r="485">
@@ -16927,7 +16927,7 @@
         <v>3.87</v>
       </c>
       <c r="H485" s="2" t="n">
-        <v>46094.27338588757</v>
+        <v>46094.2733858912</v>
       </c>
     </row>
     <row r="486">
@@ -16961,7 +16961,7 @@
         <v>2.87</v>
       </c>
       <c r="H486" s="2" t="n">
-        <v>46079.27338589061</v>
+        <v>46079.2733858912</v>
       </c>
     </row>
     <row r="487">
@@ -16995,7 +16995,7 @@
         <v>3.33</v>
       </c>
       <c r="H487" s="2" t="n">
-        <v>46093.27338589379</v>
+        <v>46093.2733858912</v>
       </c>
     </row>
     <row r="488">
@@ -17029,7 +17029,7 @@
         <v>0.19</v>
       </c>
       <c r="H488" s="2" t="n">
-        <v>46071.27338589696</v>
+        <v>46071.2733858912</v>
       </c>
     </row>
     <row r="489">
@@ -17063,7 +17063,7 @@
         <v>1.47</v>
       </c>
       <c r="H489" s="2" t="n">
-        <v>46069.27338589999</v>
+        <v>46069.27338590278</v>
       </c>
     </row>
     <row r="490">
@@ -17097,7 +17097,7 @@
         <v>3.67</v>
       </c>
       <c r="H490" s="2" t="n">
-        <v>46091.27338590302</v>
+        <v>46091.27338590278</v>
       </c>
     </row>
     <row r="491">
@@ -17131,7 +17131,7 @@
         <v>1.37</v>
       </c>
       <c r="H491" s="2" t="n">
-        <v>46089.27338590602</v>
+        <v>46089.27338590278</v>
       </c>
     </row>
     <row r="492">
@@ -17165,7 +17165,7 @@
         <v>0.71</v>
       </c>
       <c r="H492" s="2" t="n">
-        <v>46079.27338590936</v>
+        <v>46079.27338591436</v>
       </c>
     </row>
     <row r="493">
@@ -17199,7 +17199,7 @@
         <v>4.38</v>
       </c>
       <c r="H493" s="2" t="n">
-        <v>46091.27338591238</v>
+        <v>46091.27338591436</v>
       </c>
     </row>
     <row r="494">
@@ -17233,7 +17233,7 @@
         <v>0.02</v>
       </c>
       <c r="H494" s="2" t="n">
-        <v>46085.27338591542</v>
+        <v>46085.27338591436</v>
       </c>
     </row>
     <row r="495">
@@ -17267,7 +17267,7 @@
         <v>3.73</v>
       </c>
       <c r="H495" s="2" t="n">
-        <v>46072.27338591854</v>
+        <v>46072.27338591436</v>
       </c>
     </row>
     <row r="496">
@@ -17301,7 +17301,7 @@
         <v>1.07</v>
       </c>
       <c r="H496" s="2" t="n">
-        <v>46090.27338592173</v>
+        <v>46090.27338592592</v>
       </c>
     </row>
     <row r="497">
@@ -17335,7 +17335,7 @@
         <v>0.89</v>
       </c>
       <c r="H497" s="2" t="n">
-        <v>46092.27338592478</v>
+        <v>46092.27338592592</v>
       </c>
     </row>
     <row r="498">
@@ -17369,7 +17369,7 @@
         <v>3.91</v>
       </c>
       <c r="H498" s="2" t="n">
-        <v>46076.2733859278</v>
+        <v>46076.27338592592</v>
       </c>
     </row>
     <row r="499">
@@ -17403,7 +17403,7 @@
         <v>2.2</v>
       </c>
       <c r="H499" s="2" t="n">
-        <v>46092.273385931</v>
+        <v>46092.27338592592</v>
       </c>
     </row>
     <row r="500">
@@ -17437,7 +17437,7 @@
         <v>2.76</v>
       </c>
       <c r="H500" s="2" t="n">
-        <v>46068.27338593402</v>
+        <v>46068.2733859375</v>
       </c>
     </row>
     <row r="501">
@@ -17471,7 +17471,1707 @@
         <v>1.34</v>
       </c>
       <c r="H501" s="2" t="n">
-        <v>46073.27338593706</v>
+        <v>46073.2733859375</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>b08c82bb-4677-4021-8bab-7788d0a276c8</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>95</v>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F502" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="G502" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H502" s="2" t="n">
+        <v>46093.28937713445</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>30b0cfb4-420c-4cd9-9570-0a8fe1893aef</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>95</v>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F503" t="n">
+        <v>207.25</v>
+      </c>
+      <c r="G503" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="H503" s="2" t="n">
+        <v>46094.28937713874</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>536c7b76-0b35-47fe-8090-e94300839e5d</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>95</v>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F504" t="n">
+        <v>301.28</v>
+      </c>
+      <c r="G504" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="H504" s="2" t="n">
+        <v>46070.28937714201</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>9ea37706-10e4-4525-b363-9770dde6d763</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>95</v>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F505" t="n">
+        <v>363.65</v>
+      </c>
+      <c r="G505" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="H505" s="2" t="n">
+        <v>46071.2893771453</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>1c8ecd1c-d0bb-4630-a2e4-2655f6bdaca3</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>95</v>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F506" t="n">
+        <v>240.05</v>
+      </c>
+      <c r="G506" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H506" s="2" t="n">
+        <v>46076.28937714858</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>47faa697-70a8-413d-abe3-16d329f90f21</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>95</v>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F507" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="G507" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H507" s="2" t="n">
+        <v>46065.28937715171</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>acc5d158-3c79-45e9-859f-592a1dee32c3</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>95</v>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F508" t="n">
+        <v>280.31</v>
+      </c>
+      <c r="G508" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H508" s="2" t="n">
+        <v>46076.28937715492</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>61cf9ef7-621e-42d9-8fd9-dcfdf569ac33</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>95</v>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F509" t="n">
+        <v>77.05</v>
+      </c>
+      <c r="G509" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="H509" s="2" t="n">
+        <v>46067.28937715817</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>aebbfc87-2e57-4bd8-8b84-8d979a122de3</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>95</v>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F510" t="n">
+        <v>467.25</v>
+      </c>
+      <c r="G510" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="H510" s="2" t="n">
+        <v>46094.28937716169</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>caf94a38-e5b1-4a09-ad6a-263e2bdfb05d</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>95</v>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F511" t="n">
+        <v>193.63</v>
+      </c>
+      <c r="G511" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H511" s="2" t="n">
+        <v>46087.28937716501</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>9aabe525-6ec2-4c92-b084-1be588dfa603</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>95</v>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F512" t="n">
+        <v>332.29</v>
+      </c>
+      <c r="G512" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="H512" s="2" t="n">
+        <v>46071.2893771681</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>e342557d-a276-4f10-955b-ec102abce62b</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>95</v>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F513" t="n">
+        <v>415.08</v>
+      </c>
+      <c r="G513" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="H513" s="2" t="n">
+        <v>46091.28937717142</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>45edb267-a2bd-4af4-998f-c10c8084c51d</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>95</v>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F514" t="n">
+        <v>436.15</v>
+      </c>
+      <c r="G514" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="H514" s="2" t="n">
+        <v>46073.28937717469</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2bd70b43-a67f-4fb4-9462-f7266685bf22</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>95</v>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F515" t="n">
+        <v>356.31</v>
+      </c>
+      <c r="G515" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="H515" s="2" t="n">
+        <v>46094.28937717786</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>8df11d50-da85-471b-92ef-0e551f2a2ae9</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>95</v>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F516" t="n">
+        <v>449.4</v>
+      </c>
+      <c r="G516" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="H516" s="2" t="n">
+        <v>46082.28937718103</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>595d25cd-8e49-4b59-bb7f-535414497cdf</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>95</v>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F517" t="n">
+        <v>253.13</v>
+      </c>
+      <c r="G517" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="H517" s="2" t="n">
+        <v>46081.28937718428</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>802ce0b6-6807-430d-8d5f-2f61d3e51bb1</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>95</v>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F518" t="n">
+        <v>419.11</v>
+      </c>
+      <c r="G518" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="H518" s="2" t="n">
+        <v>46072.28937718735</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>6bd4d6f9-d830-4412-be07-f12d9656d121</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>95</v>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F519" t="n">
+        <v>327.24</v>
+      </c>
+      <c r="G519" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="H519" s="2" t="n">
+        <v>46073.28937719043</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>ba9b0064-d2c9-4366-88ea-6ee7f5f70bb0</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>95</v>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F520" t="n">
+        <v>191.34</v>
+      </c>
+      <c r="G520" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H520" s="2" t="n">
+        <v>46065.28937719367</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>85e55dc1-c799-4492-8a6a-fe9bd72323b1</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>95</v>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F521" t="n">
+        <v>52.08</v>
+      </c>
+      <c r="G521" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H521" s="2" t="n">
+        <v>46070.28937719674</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>ee509a87-34e6-493e-8d00-529ef4fd0759</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>95</v>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F522" t="n">
+        <v>81.75</v>
+      </c>
+      <c r="G522" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H522" s="2" t="n">
+        <v>46088.28937719977</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>ca327c3c-9a1b-41af-b66f-99d9a0d22cbf</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>95</v>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F523" t="n">
+        <v>294.17</v>
+      </c>
+      <c r="G523" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H523" s="2" t="n">
+        <v>46082.2893772028</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>f98000d5-f06a-4f64-b173-0a4e45a69242</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>95</v>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F524" t="n">
+        <v>104.85</v>
+      </c>
+      <c r="G524" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H524" s="2" t="n">
+        <v>46077.28937720609</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>a0ec6fe9-ad94-40e0-bf94-9d4ce7d7ebcc</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>95</v>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F525" t="n">
+        <v>71.13</v>
+      </c>
+      <c r="G525" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H525" s="2" t="n">
+        <v>46083.28937720925</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>526c8661-27be-4a19-9b0d-f1806a1b4929</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>95</v>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F526" t="n">
+        <v>449.08</v>
+      </c>
+      <c r="G526" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="H526" s="2" t="n">
+        <v>46094.28937721228</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>7bb684f9-d4e1-4d65-8b5b-fd5a72597f68</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>95</v>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F527" t="n">
+        <v>238.21</v>
+      </c>
+      <c r="G527" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H527" s="2" t="n">
+        <v>46091.28937721553</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>a1617060-221e-4ace-863f-814a4f7df61f</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>95</v>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F528" t="n">
+        <v>329.4</v>
+      </c>
+      <c r="G528" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="H528" s="2" t="n">
+        <v>46085.28937721903</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>53748711-6386-4b79-a899-33fb7f1790d6</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>95</v>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F529" t="n">
+        <v>426.88</v>
+      </c>
+      <c r="G529" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="H529" s="2" t="n">
+        <v>46090.28937722214</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>c8bfd8e2-fc2d-4a1d-88dd-6385d1e56223</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>95</v>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F530" t="n">
+        <v>194.12</v>
+      </c>
+      <c r="G530" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H530" s="2" t="n">
+        <v>46067.28937722528</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>92093c53-a175-4a9f-a1d3-c47dc1f5f59c</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>95</v>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F531" t="n">
+        <v>325.88</v>
+      </c>
+      <c r="G531" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="H531" s="2" t="n">
+        <v>46084.28937722873</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>3f6a66f6-0cc4-4faf-9a9a-a6ca6da5f49e</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>95</v>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F532" t="n">
+        <v>193.1</v>
+      </c>
+      <c r="G532" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H532" s="2" t="n">
+        <v>46067.28937723182</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>6c74d833-67e4-4ba1-9201-e106355fa46a</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>95</v>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F533" t="n">
+        <v>168.96</v>
+      </c>
+      <c r="G533" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H533" s="2" t="n">
+        <v>46075.28937723486</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>847c524c-b2f1-4938-a7f4-8bd5798ed010</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>95</v>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F534" t="n">
+        <v>131.76</v>
+      </c>
+      <c r="G534" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H534" s="2" t="n">
+        <v>46082.28937723796</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>9774cb84-086c-40db-865b-c976b64475a2</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>95</v>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F535" t="n">
+        <v>401.12</v>
+      </c>
+      <c r="G535" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="H535" s="2" t="n">
+        <v>46077.28937724121</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>0d779aa8-c4f0-45da-8844-f567af0f8547</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>95</v>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F536" t="n">
+        <v>201.26</v>
+      </c>
+      <c r="G536" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="H536" s="2" t="n">
+        <v>46088.28937724436</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>726a1bdc-4d06-41fb-a09e-4a3d8c5e7e2d</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>95</v>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F537" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="G537" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H537" s="2" t="n">
+        <v>46068.28937724741</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>908ff0e0-f310-40fe-8b84-bcb2d57ad229</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>95</v>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F538" t="n">
+        <v>123.66</v>
+      </c>
+      <c r="G538" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="H538" s="2" t="n">
+        <v>46074.28937725046</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>135ff89b-d2fc-4935-9b2e-93553ce79319</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>95</v>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F539" t="n">
+        <v>370.98</v>
+      </c>
+      <c r="G539" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="H539" s="2" t="n">
+        <v>46067.28937725391</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>1e969486-84aa-4a88-b040-ac5139d7e23a</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>95</v>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F540" t="n">
+        <v>166.09</v>
+      </c>
+      <c r="G540" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H540" s="2" t="n">
+        <v>46070.2893772571</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>f033f3d2-1684-411f-86ff-0d627471bfc3</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>95</v>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F541" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="G541" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H541" s="2" t="n">
+        <v>46079.28937726014</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>8a90a5d8-615a-414d-b948-ef092bb3d01f</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>95</v>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F542" t="n">
+        <v>43.85</v>
+      </c>
+      <c r="G542" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H542" s="2" t="n">
+        <v>46078.28937726333</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>8bc3055e-1d7a-470f-939d-71683953f6c2</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>95</v>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F543" t="n">
+        <v>274.68</v>
+      </c>
+      <c r="G543" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H543" s="2" t="n">
+        <v>46084.28937726654</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>42c94772-d4d2-48c3-a8ad-338a048d326e</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>95</v>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F544" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="G544" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H544" s="2" t="n">
+        <v>46076.2893772696</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>aa2007bf-5feb-46c8-94fe-bc80c14947be</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>95</v>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F545" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="G545" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H545" s="2" t="n">
+        <v>46076.28937727264</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>c4175400-89a6-4a00-83d2-a5b72a96bb72</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>95</v>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F546" t="n">
+        <v>181.96</v>
+      </c>
+      <c r="G546" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="H546" s="2" t="n">
+        <v>46066.28937727593</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>01e09385-4abb-4812-b1ea-404f354439d1</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>95</v>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F547" t="n">
+        <v>370.31</v>
+      </c>
+      <c r="G547" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H547" s="2" t="n">
+        <v>46077.28937727897</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>7fa8ff52-3eee-464e-8f49-19665668962a</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>95</v>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F548" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="G548" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H548" s="2" t="n">
+        <v>46086.28937728214</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>c5e5ec90-e2a0-4736-9a78-a7a000a7d918</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>95</v>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F549" t="n">
+        <v>350.52</v>
+      </c>
+      <c r="G549" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="H549" s="2" t="n">
+        <v>46090.28937728524</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>0bb29069-9141-4a52-b71b-a2f6cae240de</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>95</v>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F550" t="n">
+        <v>218.32</v>
+      </c>
+      <c r="G550" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H550" s="2" t="n">
+        <v>46072.28937728846</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>e79ed416-2b36-485d-b7a8-c2747f1b5ebb</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>95</v>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F551" t="n">
+        <v>475.61</v>
+      </c>
+      <c r="G551" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="H551" s="2" t="n">
+        <v>46067.28937729153</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H551"/>
+  <dimension ref="A1:H601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17505,7 +17505,7 @@
         <v>0.27</v>
       </c>
       <c r="H502" s="2" t="n">
-        <v>46093.28937713445</v>
+        <v>46093.28937712963</v>
       </c>
     </row>
     <row r="503">
@@ -17539,7 +17539,7 @@
         <v>2.07</v>
       </c>
       <c r="H503" s="2" t="n">
-        <v>46094.28937713874</v>
+        <v>46094.28937714121</v>
       </c>
     </row>
     <row r="504">
@@ -17573,7 +17573,7 @@
         <v>3.01</v>
       </c>
       <c r="H504" s="2" t="n">
-        <v>46070.28937714201</v>
+        <v>46070.28937714121</v>
       </c>
     </row>
     <row r="505">
@@ -17607,7 +17607,7 @@
         <v>3.64</v>
       </c>
       <c r="H505" s="2" t="n">
-        <v>46071.2893771453</v>
+        <v>46071.28937714121</v>
       </c>
     </row>
     <row r="506">
@@ -17641,7 +17641,7 @@
         <v>2.4</v>
       </c>
       <c r="H506" s="2" t="n">
-        <v>46076.28937714858</v>
+        <v>46076.28937715277</v>
       </c>
     </row>
     <row r="507">
@@ -17675,7 +17675,7 @@
         <v>0.66</v>
       </c>
       <c r="H507" s="2" t="n">
-        <v>46065.28937715171</v>
+        <v>46065.28937715277</v>
       </c>
     </row>
     <row r="508">
@@ -17709,7 +17709,7 @@
         <v>2.8</v>
       </c>
       <c r="H508" s="2" t="n">
-        <v>46076.28937715492</v>
+        <v>46076.28937715277</v>
       </c>
     </row>
     <row r="509">
@@ -17743,7 +17743,7 @@
         <v>0.77</v>
       </c>
       <c r="H509" s="2" t="n">
-        <v>46067.28937715817</v>
+        <v>46067.28937715277</v>
       </c>
     </row>
     <row r="510">
@@ -17777,7 +17777,7 @@
         <v>4.67</v>
       </c>
       <c r="H510" s="2" t="n">
-        <v>46094.28937716169</v>
+        <v>46094.28937716435</v>
       </c>
     </row>
     <row r="511">
@@ -17811,7 +17811,7 @@
         <v>1.94</v>
       </c>
       <c r="H511" s="2" t="n">
-        <v>46087.28937716501</v>
+        <v>46087.28937716435</v>
       </c>
     </row>
     <row r="512">
@@ -17845,7 +17845,7 @@
         <v>3.32</v>
       </c>
       <c r="H512" s="2" t="n">
-        <v>46071.2893771681</v>
+        <v>46071.28937716435</v>
       </c>
     </row>
     <row r="513">
@@ -17879,7 +17879,7 @@
         <v>4.15</v>
       </c>
       <c r="H513" s="2" t="n">
-        <v>46091.28937717142</v>
+        <v>46091.28937717593</v>
       </c>
     </row>
     <row r="514">
@@ -17913,7 +17913,7 @@
         <v>4.36</v>
       </c>
       <c r="H514" s="2" t="n">
-        <v>46073.28937717469</v>
+        <v>46073.28937717593</v>
       </c>
     </row>
     <row r="515">
@@ -17947,7 +17947,7 @@
         <v>3.56</v>
       </c>
       <c r="H515" s="2" t="n">
-        <v>46094.28937717786</v>
+        <v>46094.28937717593</v>
       </c>
     </row>
     <row r="516">
@@ -17981,7 +17981,7 @@
         <v>4.49</v>
       </c>
       <c r="H516" s="2" t="n">
-        <v>46082.28937718103</v>
+        <v>46082.28937717593</v>
       </c>
     </row>
     <row r="517">
@@ -18015,7 +18015,7 @@
         <v>2.53</v>
       </c>
       <c r="H517" s="2" t="n">
-        <v>46081.28937718428</v>
+        <v>46081.2893771875</v>
       </c>
     </row>
     <row r="518">
@@ -18049,7 +18049,7 @@
         <v>4.19</v>
       </c>
       <c r="H518" s="2" t="n">
-        <v>46072.28937718735</v>
+        <v>46072.2893771875</v>
       </c>
     </row>
     <row r="519">
@@ -18083,7 +18083,7 @@
         <v>3.27</v>
       </c>
       <c r="H519" s="2" t="n">
-        <v>46073.28937719043</v>
+        <v>46073.2893771875</v>
       </c>
     </row>
     <row r="520">
@@ -18117,7 +18117,7 @@
         <v>1.91</v>
       </c>
       <c r="H520" s="2" t="n">
-        <v>46065.28937719367</v>
+        <v>46065.28937719907</v>
       </c>
     </row>
     <row r="521">
@@ -18151,7 +18151,7 @@
         <v>0.52</v>
       </c>
       <c r="H521" s="2" t="n">
-        <v>46070.28937719674</v>
+        <v>46070.28937719907</v>
       </c>
     </row>
     <row r="522">
@@ -18185,7 +18185,7 @@
         <v>0.82</v>
       </c>
       <c r="H522" s="2" t="n">
-        <v>46088.28937719977</v>
+        <v>46088.28937719907</v>
       </c>
     </row>
     <row r="523">
@@ -18219,7 +18219,7 @@
         <v>2.94</v>
       </c>
       <c r="H523" s="2" t="n">
-        <v>46082.2893772028</v>
+        <v>46082.28937719907</v>
       </c>
     </row>
     <row r="524">
@@ -18253,7 +18253,7 @@
         <v>1.05</v>
       </c>
       <c r="H524" s="2" t="n">
-        <v>46077.28937720609</v>
+        <v>46077.28937721065</v>
       </c>
     </row>
     <row r="525">
@@ -18287,7 +18287,7 @@
         <v>0.71</v>
       </c>
       <c r="H525" s="2" t="n">
-        <v>46083.28937720925</v>
+        <v>46083.28937721065</v>
       </c>
     </row>
     <row r="526">
@@ -18321,7 +18321,7 @@
         <v>4.49</v>
       </c>
       <c r="H526" s="2" t="n">
-        <v>46094.28937721228</v>
+        <v>46094.28937721065</v>
       </c>
     </row>
     <row r="527">
@@ -18355,7 +18355,7 @@
         <v>2.38</v>
       </c>
       <c r="H527" s="2" t="n">
-        <v>46091.28937721553</v>
+        <v>46091.28937721065</v>
       </c>
     </row>
     <row r="528">
@@ -18389,7 +18389,7 @@
         <v>3.29</v>
       </c>
       <c r="H528" s="2" t="n">
-        <v>46085.28937721903</v>
+        <v>46085.28937722222</v>
       </c>
     </row>
     <row r="529">
@@ -18423,7 +18423,7 @@
         <v>4.27</v>
       </c>
       <c r="H529" s="2" t="n">
-        <v>46090.28937722214</v>
+        <v>46090.28937722222</v>
       </c>
     </row>
     <row r="530">
@@ -18457,7 +18457,7 @@
         <v>1.94</v>
       </c>
       <c r="H530" s="2" t="n">
-        <v>46067.28937722528</v>
+        <v>46067.28937722222</v>
       </c>
     </row>
     <row r="531">
@@ -18491,7 +18491,7 @@
         <v>3.26</v>
       </c>
       <c r="H531" s="2" t="n">
-        <v>46084.28937722873</v>
+        <v>46084.2893772338</v>
       </c>
     </row>
     <row r="532">
@@ -18525,7 +18525,7 @@
         <v>1.93</v>
       </c>
       <c r="H532" s="2" t="n">
-        <v>46067.28937723182</v>
+        <v>46067.2893772338</v>
       </c>
     </row>
     <row r="533">
@@ -18559,7 +18559,7 @@
         <v>1.69</v>
       </c>
       <c r="H533" s="2" t="n">
-        <v>46075.28937723486</v>
+        <v>46075.2893772338</v>
       </c>
     </row>
     <row r="534">
@@ -18593,7 +18593,7 @@
         <v>1.32</v>
       </c>
       <c r="H534" s="2" t="n">
-        <v>46082.28937723796</v>
+        <v>46082.2893772338</v>
       </c>
     </row>
     <row r="535">
@@ -18627,7 +18627,7 @@
         <v>4.01</v>
       </c>
       <c r="H535" s="2" t="n">
-        <v>46077.28937724121</v>
+        <v>46077.28937724537</v>
       </c>
     </row>
     <row r="536">
@@ -18661,7 +18661,7 @@
         <v>2.01</v>
       </c>
       <c r="H536" s="2" t="n">
-        <v>46088.28937724436</v>
+        <v>46088.28937724537</v>
       </c>
     </row>
     <row r="537">
@@ -18695,7 +18695,7 @@
         <v>0.11</v>
       </c>
       <c r="H537" s="2" t="n">
-        <v>46068.28937724741</v>
+        <v>46068.28937724537</v>
       </c>
     </row>
     <row r="538">
@@ -18729,7 +18729,7 @@
         <v>1.24</v>
       </c>
       <c r="H538" s="2" t="n">
-        <v>46074.28937725046</v>
+        <v>46074.28937724537</v>
       </c>
     </row>
     <row r="539">
@@ -18763,7 +18763,7 @@
         <v>3.71</v>
       </c>
       <c r="H539" s="2" t="n">
-        <v>46067.28937725391</v>
+        <v>46067.28937725694</v>
       </c>
     </row>
     <row r="540">
@@ -18797,7 +18797,7 @@
         <v>1.66</v>
       </c>
       <c r="H540" s="2" t="n">
-        <v>46070.2893772571</v>
+        <v>46070.28937725694</v>
       </c>
     </row>
     <row r="541">
@@ -18831,7 +18831,7 @@
         <v>0.11</v>
       </c>
       <c r="H541" s="2" t="n">
-        <v>46079.28937726014</v>
+        <v>46079.28937725694</v>
       </c>
     </row>
     <row r="542">
@@ -18865,7 +18865,7 @@
         <v>0.44</v>
       </c>
       <c r="H542" s="2" t="n">
-        <v>46078.28937726333</v>
+        <v>46078.28937726852</v>
       </c>
     </row>
     <row r="543">
@@ -18899,7 +18899,7 @@
         <v>2.75</v>
       </c>
       <c r="H543" s="2" t="n">
-        <v>46084.28937726654</v>
+        <v>46084.28937726852</v>
       </c>
     </row>
     <row r="544">
@@ -18933,7 +18933,7 @@
         <v>0.95</v>
       </c>
       <c r="H544" s="2" t="n">
-        <v>46076.2893772696</v>
+        <v>46076.28937726852</v>
       </c>
     </row>
     <row r="545">
@@ -18967,7 +18967,7 @@
         <v>0.13</v>
       </c>
       <c r="H545" s="2" t="n">
-        <v>46076.28937727264</v>
+        <v>46076.28937726852</v>
       </c>
     </row>
     <row r="546">
@@ -19001,7 +19001,7 @@
         <v>1.82</v>
       </c>
       <c r="H546" s="2" t="n">
-        <v>46066.28937727593</v>
+        <v>46066.28937728009</v>
       </c>
     </row>
     <row r="547">
@@ -19035,7 +19035,7 @@
         <v>3.7</v>
       </c>
       <c r="H547" s="2" t="n">
-        <v>46077.28937727897</v>
+        <v>46077.28937728009</v>
       </c>
     </row>
     <row r="548">
@@ -19069,7 +19069,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="H548" s="2" t="n">
-        <v>46086.28937728214</v>
+        <v>46086.28937728009</v>
       </c>
     </row>
     <row r="549">
@@ -19103,7 +19103,7 @@
         <v>3.51</v>
       </c>
       <c r="H549" s="2" t="n">
-        <v>46090.28937728524</v>
+        <v>46090.28937728009</v>
       </c>
     </row>
     <row r="550">
@@ -19137,7 +19137,7 @@
         <v>2.18</v>
       </c>
       <c r="H550" s="2" t="n">
-        <v>46072.28937728846</v>
+        <v>46072.28937729167</v>
       </c>
     </row>
     <row r="551">
@@ -19171,7 +19171,1707 @@
         <v>4.76</v>
       </c>
       <c r="H551" s="2" t="n">
-        <v>46067.28937729153</v>
+        <v>46067.28937729167</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>857d0806-0f10-4330-b2ed-de37b27b20a9</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>95</v>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F552" t="n">
+        <v>386.92</v>
+      </c>
+      <c r="G552" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="H552" s="2" t="n">
+        <v>46066.54629734754</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>eb4f135f-8fa3-4324-93b0-bf69a241c5ac</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>95</v>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F553" t="n">
+        <v>384.7</v>
+      </c>
+      <c r="G553" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H553" s="2" t="n">
+        <v>46087.54629735218</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>6c633a38-fa58-48b4-84a9-cde12968c4af</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>95</v>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F554" t="n">
+        <v>336.78</v>
+      </c>
+      <c r="G554" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="H554" s="2" t="n">
+        <v>46073.54629735544</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>d7f36b98-11ed-4cbb-bb59-667f7df12f6a</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>95</v>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F555" t="n">
+        <v>467.84</v>
+      </c>
+      <c r="G555" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="H555" s="2" t="n">
+        <v>46075.54629735871</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>b74b4d9e-99cc-49de-9026-9be19d543019</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>95</v>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F556" t="n">
+        <v>298.91</v>
+      </c>
+      <c r="G556" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H556" s="2" t="n">
+        <v>46085.5462973621</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>9445f8fd-7161-4c7f-8fea-4db374579ad8</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>95</v>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F557" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="G557" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H557" s="2" t="n">
+        <v>46070.5462973658</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>f6fed973-70e2-4efe-a175-86f338d5d1b4</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>95</v>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F558" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="G558" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H558" s="2" t="n">
+        <v>46082.54629736891</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>51628fa4-128b-42ab-9dfa-66d55d3213f1</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>95</v>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F559" t="n">
+        <v>290.43</v>
+      </c>
+      <c r="G559" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H559" s="2" t="n">
+        <v>46083.54629737206</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>b1c8d170-cc99-40af-a96d-6635ca9be7d2</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>95</v>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F560" t="n">
+        <v>400.92</v>
+      </c>
+      <c r="G560" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="H560" s="2" t="n">
+        <v>46094.54629737534</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>61360ffd-a88c-4ad0-a464-3a300c2c0aab</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>95</v>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F561" t="n">
+        <v>104.31</v>
+      </c>
+      <c r="G561" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H561" s="2" t="n">
+        <v>46075.54629737847</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>09a58def-7756-4ede-9f0a-af3b60374bd7</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>95</v>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F562" t="n">
+        <v>17.03</v>
+      </c>
+      <c r="G562" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H562" s="2" t="n">
+        <v>46083.54629738196</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>c0bb005f-031d-45b9-ae7b-7849d437915c</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>95</v>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F563" t="n">
+        <v>477.42</v>
+      </c>
+      <c r="G563" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="H563" s="2" t="n">
+        <v>46065.54629738504</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>71bad39d-82c4-4838-8ba5-50e0e33b7f01</t>
+        </is>
+      </c>
+      <c r="B564" t="n">
+        <v>95</v>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F564" t="n">
+        <v>303.59</v>
+      </c>
+      <c r="G564" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="H564" s="2" t="n">
+        <v>46077.54629738865</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>b875e5c8-7728-412d-9b81-f2e669aa7ff0</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>95</v>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F565" t="n">
+        <v>300.28</v>
+      </c>
+      <c r="G565" t="n">
+        <v>3</v>
+      </c>
+      <c r="H565" s="2" t="n">
+        <v>46085.54629739174</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>fa40a6ee-08f8-417d-a633-a760fad3092b</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>95</v>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F566" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="G566" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H566" s="2" t="n">
+        <v>46093.5462973949</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>e4333b0f-b2a4-4be8-9efb-44e28f82761e</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>95</v>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F567" t="n">
+        <v>463.53</v>
+      </c>
+      <c r="G567" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="H567" s="2" t="n">
+        <v>46073.54629739834</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>f88ba1b0-f075-43ff-8aa2-4f366bf9b2eb</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>95</v>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F568" t="n">
+        <v>281.85</v>
+      </c>
+      <c r="G568" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H568" s="2" t="n">
+        <v>46090.54629740229</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>fd95471f-48b8-4311-a108-ed46dca8e2b2</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>95</v>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F569" t="n">
+        <v>404.65</v>
+      </c>
+      <c r="G569" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="H569" s="2" t="n">
+        <v>46079.5462974054</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>11e37fbf-706a-4ad0-b9bd-134a2bbdcf03</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>95</v>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F570" t="n">
+        <v>471.79</v>
+      </c>
+      <c r="G570" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="H570" s="2" t="n">
+        <v>46081.54629740853</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>050659a0-ca13-4690-bd39-f6d0fe86ccbc</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>95</v>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F571" t="n">
+        <v>446.52</v>
+      </c>
+      <c r="G571" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="H571" s="2" t="n">
+        <v>46065.54629741182</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>3decbe6f-feb8-4242-9aac-1efb05f7a6ed</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>95</v>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F572" t="n">
+        <v>223.33</v>
+      </c>
+      <c r="G572" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H572" s="2" t="n">
+        <v>46077.54629741496</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>75620955-b8a1-4cfd-b93d-3737aa4e4ca1</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>95</v>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F573" t="n">
+        <v>249.46</v>
+      </c>
+      <c r="G573" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H573" s="2" t="n">
+        <v>46090.54629741821</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>cf99d64b-36dd-4621-9f62-d18c7be066c1</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>95</v>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F574" t="n">
+        <v>252.32</v>
+      </c>
+      <c r="G574" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H574" s="2" t="n">
+        <v>46089.54629742145</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>43351dfe-fa9b-4f09-be50-a716542d3a47</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
+        <v>95</v>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F575" t="n">
+        <v>60.06</v>
+      </c>
+      <c r="G575" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H575" s="2" t="n">
+        <v>46073.54629742468</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>0be1c8d4-3702-47dd-a82d-9014c688e352</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>95</v>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F576" t="n">
+        <v>37.63</v>
+      </c>
+      <c r="G576" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H576" s="2" t="n">
+        <v>46075.54629742775</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>352bc9c0-e473-4f44-9c4e-34e92f74c107</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>95</v>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F577" t="n">
+        <v>255.62</v>
+      </c>
+      <c r="G577" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H577" s="2" t="n">
+        <v>46085.54629743101</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>c1353d4a-e856-4a88-98f9-f735cab6e869</t>
+        </is>
+      </c>
+      <c r="B578" t="n">
+        <v>95</v>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F578" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="G578" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H578" s="2" t="n">
+        <v>46077.54629743465</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>87626a0e-0c5e-4d23-8538-1eb671eaa3a7</t>
+        </is>
+      </c>
+      <c r="B579" t="n">
+        <v>95</v>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F579" t="n">
+        <v>324.4</v>
+      </c>
+      <c r="G579" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="H579" s="2" t="n">
+        <v>46073.54629743786</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>5e2d5d1c-9749-4099-829b-fcf41f7754cb</t>
+        </is>
+      </c>
+      <c r="B580" t="n">
+        <v>95</v>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F580" t="n">
+        <v>158.58</v>
+      </c>
+      <c r="G580" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H580" s="2" t="n">
+        <v>46092.54629744092</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>7a3042fb-ac42-468c-ae74-471addfd3050</t>
+        </is>
+      </c>
+      <c r="B581" t="n">
+        <v>95</v>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F581" t="n">
+        <v>51.24</v>
+      </c>
+      <c r="G581" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H581" s="2" t="n">
+        <v>46072.54629744399</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>a2b947cd-5653-42d6-933d-dd5fdecb4f6c</t>
+        </is>
+      </c>
+      <c r="B582" t="n">
+        <v>95</v>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F582" t="n">
+        <v>269.93</v>
+      </c>
+      <c r="G582" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H582" s="2" t="n">
+        <v>46094.5462974475</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>642f472d-2963-4870-a708-3e6cfe013157</t>
+        </is>
+      </c>
+      <c r="B583" t="n">
+        <v>95</v>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F583" t="n">
+        <v>324.35</v>
+      </c>
+      <c r="G583" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="H583" s="2" t="n">
+        <v>46082.54629745054</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>d78c8701-5c91-491d-960e-fa7e50fc5f95</t>
+        </is>
+      </c>
+      <c r="B584" t="n">
+        <v>95</v>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F584" t="n">
+        <v>43.93</v>
+      </c>
+      <c r="G584" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H584" s="2" t="n">
+        <v>46073.54629745373</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>3c4bda8b-4d61-470f-81bc-ac3410ffb05a</t>
+        </is>
+      </c>
+      <c r="B585" t="n">
+        <v>95</v>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F585" t="n">
+        <v>426.51</v>
+      </c>
+      <c r="G585" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="H585" s="2" t="n">
+        <v>46079.54629745705</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>b39f60fd-2d5e-4745-a505-349e3c08912b</t>
+        </is>
+      </c>
+      <c r="B586" t="n">
+        <v>95</v>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F586" t="n">
+        <v>383.21</v>
+      </c>
+      <c r="G586" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="H586" s="2" t="n">
+        <v>46081.54629746026</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>3bad2eb8-0e7a-4958-a82e-45ee1cfa3e75</t>
+        </is>
+      </c>
+      <c r="B587" t="n">
+        <v>95</v>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F587" t="n">
+        <v>490.1</v>
+      </c>
+      <c r="G587" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H587" s="2" t="n">
+        <v>46068.54629746337</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>4c0c5e7f-1307-49b9-a3fc-37bafcd1ec64</t>
+        </is>
+      </c>
+      <c r="B588" t="n">
+        <v>95</v>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F588" t="n">
+        <v>437.87</v>
+      </c>
+      <c r="G588" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="H588" s="2" t="n">
+        <v>46075.5462974664</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>fc1bb941-e2a7-434a-86fb-c9d476559f3f</t>
+        </is>
+      </c>
+      <c r="B589" t="n">
+        <v>95</v>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F589" t="n">
+        <v>499.11</v>
+      </c>
+      <c r="G589" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="H589" s="2" t="n">
+        <v>46080.54629746974</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2743224a-c38b-45fe-b4af-bd238ef77cdb</t>
+        </is>
+      </c>
+      <c r="B590" t="n">
+        <v>95</v>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F590" t="n">
+        <v>273.15</v>
+      </c>
+      <c r="G590" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H590" s="2" t="n">
+        <v>46094.54629747287</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>0d34b840-4a4b-42cc-8f1a-25de96dc0458</t>
+        </is>
+      </c>
+      <c r="B591" t="n">
+        <v>95</v>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F591" t="n">
+        <v>372.45</v>
+      </c>
+      <c r="G591" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="H591" s="2" t="n">
+        <v>46081.54629747595</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>953f8dd7-1efc-4020-bbc7-4f1fab2a68ee</t>
+        </is>
+      </c>
+      <c r="B592" t="n">
+        <v>95</v>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F592" t="n">
+        <v>410.67</v>
+      </c>
+      <c r="G592" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="H592" s="2" t="n">
+        <v>46089.54629747938</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>55744d16-dd40-4b24-a479-2241a1e83a67</t>
+        </is>
+      </c>
+      <c r="B593" t="n">
+        <v>95</v>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F593" t="n">
+        <v>460.63</v>
+      </c>
+      <c r="G593" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="H593" s="2" t="n">
+        <v>46068.54629748264</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>77beae8d-b1ff-449c-9e6c-ee5fe115b020</t>
+        </is>
+      </c>
+      <c r="B594" t="n">
+        <v>95</v>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F594" t="n">
+        <v>452.52</v>
+      </c>
+      <c r="G594" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="H594" s="2" t="n">
+        <v>46079.54629748569</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>cc659dc5-0296-485a-979d-074e4b27294d</t>
+        </is>
+      </c>
+      <c r="B595" t="n">
+        <v>95</v>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F595" t="n">
+        <v>329.9</v>
+      </c>
+      <c r="G595" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H595" s="2" t="n">
+        <v>46081.54629748885</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>669b8b1a-0341-428d-97a3-b4e7169f7cd0</t>
+        </is>
+      </c>
+      <c r="B596" t="n">
+        <v>95</v>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F596" t="n">
+        <v>302.2</v>
+      </c>
+      <c r="G596" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="H596" s="2" t="n">
+        <v>46084.54629749214</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>4524f329-85e0-4838-99ef-063f2d97aec9</t>
+        </is>
+      </c>
+      <c r="B597" t="n">
+        <v>95</v>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F597" t="n">
+        <v>172.66</v>
+      </c>
+      <c r="G597" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H597" s="2" t="n">
+        <v>46083.54629749537</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>7e358781-1a40-4444-a375-286af92691c0</t>
+        </is>
+      </c>
+      <c r="B598" t="n">
+        <v>95</v>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F598" t="n">
+        <v>164.32</v>
+      </c>
+      <c r="G598" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H598" s="2" t="n">
+        <v>46093.54629749839</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>0e3b467c-d658-4c4d-ab9b-f395d55ef1f8</t>
+        </is>
+      </c>
+      <c r="B599" t="n">
+        <v>95</v>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F599" t="n">
+        <v>285.99</v>
+      </c>
+      <c r="G599" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H599" s="2" t="n">
+        <v>46070.5462975016</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>d328b2dc-a7de-4b46-83f1-1808496a8d0c</t>
+        </is>
+      </c>
+      <c r="B600" t="n">
+        <v>95</v>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F600" t="n">
+        <v>394.82</v>
+      </c>
+      <c r="G600" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H600" s="2" t="n">
+        <v>46071.54629750497</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>a2b32d8e-f6fb-4f74-bd5d-9ea01cf17cdb</t>
+        </is>
+      </c>
+      <c r="B601" t="n">
+        <v>95</v>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F601" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="G601" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H601" s="2" t="n">
+        <v>46085.54629750804</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H601"/>
+  <dimension ref="A1:H651"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19205,7 +19205,7 @@
         <v>3.87</v>
       </c>
       <c r="H552" s="2" t="n">
-        <v>46066.54629734754</v>
+        <v>46066.54629734954</v>
       </c>
     </row>
     <row r="553">
@@ -19239,7 +19239,7 @@
         <v>3.85</v>
       </c>
       <c r="H553" s="2" t="n">
-        <v>46087.54629735218</v>
+        <v>46087.54629734954</v>
       </c>
     </row>
     <row r="554">
@@ -19273,7 +19273,7 @@
         <v>3.37</v>
       </c>
       <c r="H554" s="2" t="n">
-        <v>46073.54629735544</v>
+        <v>46073.54629736111</v>
       </c>
     </row>
     <row r="555">
@@ -19307,7 +19307,7 @@
         <v>4.68</v>
       </c>
       <c r="H555" s="2" t="n">
-        <v>46075.54629735871</v>
+        <v>46075.54629736111</v>
       </c>
     </row>
     <row r="556">
@@ -19341,7 +19341,7 @@
         <v>2.99</v>
       </c>
       <c r="H556" s="2" t="n">
-        <v>46085.5462973621</v>
+        <v>46085.54629736111</v>
       </c>
     </row>
     <row r="557">
@@ -19375,7 +19375,7 @@
         <v>0.14</v>
       </c>
       <c r="H557" s="2" t="n">
-        <v>46070.5462973658</v>
+        <v>46070.54629736111</v>
       </c>
     </row>
     <row r="558">
@@ -19409,7 +19409,7 @@
         <v>1.62</v>
       </c>
       <c r="H558" s="2" t="n">
-        <v>46082.54629736891</v>
+        <v>46082.54629737268</v>
       </c>
     </row>
     <row r="559">
@@ -19443,7 +19443,7 @@
         <v>2.9</v>
       </c>
       <c r="H559" s="2" t="n">
-        <v>46083.54629737206</v>
+        <v>46083.54629737268</v>
       </c>
     </row>
     <row r="560">
@@ -19477,7 +19477,7 @@
         <v>4.01</v>
       </c>
       <c r="H560" s="2" t="n">
-        <v>46094.54629737534</v>
+        <v>46094.54629737268</v>
       </c>
     </row>
     <row r="561">
@@ -19511,7 +19511,7 @@
         <v>1.04</v>
       </c>
       <c r="H561" s="2" t="n">
-        <v>46075.54629737847</v>
+        <v>46075.54629737268</v>
       </c>
     </row>
     <row r="562">
@@ -19545,7 +19545,7 @@
         <v>0.17</v>
       </c>
       <c r="H562" s="2" t="n">
-        <v>46083.54629738196</v>
+        <v>46083.54629738426</v>
       </c>
     </row>
     <row r="563">
@@ -19579,7 +19579,7 @@
         <v>4.77</v>
       </c>
       <c r="H563" s="2" t="n">
-        <v>46065.54629738504</v>
+        <v>46065.54629738426</v>
       </c>
     </row>
     <row r="564">
@@ -19613,7 +19613,7 @@
         <v>3.04</v>
       </c>
       <c r="H564" s="2" t="n">
-        <v>46077.54629738865</v>
+        <v>46077.54629738426</v>
       </c>
     </row>
     <row r="565">
@@ -19647,7 +19647,7 @@
         <v>3</v>
       </c>
       <c r="H565" s="2" t="n">
-        <v>46085.54629739174</v>
+        <v>46085.54629739583</v>
       </c>
     </row>
     <row r="566">
@@ -19681,7 +19681,7 @@
         <v>0.06</v>
       </c>
       <c r="H566" s="2" t="n">
-        <v>46093.5462973949</v>
+        <v>46093.54629739583</v>
       </c>
     </row>
     <row r="567">
@@ -19715,7 +19715,7 @@
         <v>4.64</v>
       </c>
       <c r="H567" s="2" t="n">
-        <v>46073.54629739834</v>
+        <v>46073.54629739583</v>
       </c>
     </row>
     <row r="568">
@@ -19749,7 +19749,7 @@
         <v>2.82</v>
       </c>
       <c r="H568" s="2" t="n">
-        <v>46090.54629740229</v>
+        <v>46090.54629740741</v>
       </c>
     </row>
     <row r="569">
@@ -19783,7 +19783,7 @@
         <v>4.05</v>
       </c>
       <c r="H569" s="2" t="n">
-        <v>46079.5462974054</v>
+        <v>46079.54629740741</v>
       </c>
     </row>
     <row r="570">
@@ -19817,7 +19817,7 @@
         <v>4.72</v>
       </c>
       <c r="H570" s="2" t="n">
-        <v>46081.54629740853</v>
+        <v>46081.54629740741</v>
       </c>
     </row>
     <row r="571">
@@ -19851,7 +19851,7 @@
         <v>4.47</v>
       </c>
       <c r="H571" s="2" t="n">
-        <v>46065.54629741182</v>
+        <v>46065.54629740741</v>
       </c>
     </row>
     <row r="572">
@@ -19885,7 +19885,7 @@
         <v>2.23</v>
       </c>
       <c r="H572" s="2" t="n">
-        <v>46077.54629741496</v>
+        <v>46077.54629741898</v>
       </c>
     </row>
     <row r="573">
@@ -19919,7 +19919,7 @@
         <v>2.49</v>
       </c>
       <c r="H573" s="2" t="n">
-        <v>46090.54629741821</v>
+        <v>46090.54629741898</v>
       </c>
     </row>
     <row r="574">
@@ -19953,7 +19953,7 @@
         <v>2.52</v>
       </c>
       <c r="H574" s="2" t="n">
-        <v>46089.54629742145</v>
+        <v>46089.54629741898</v>
       </c>
     </row>
     <row r="575">
@@ -19987,7 +19987,7 @@
         <v>0.6</v>
       </c>
       <c r="H575" s="2" t="n">
-        <v>46073.54629742468</v>
+        <v>46073.54629741898</v>
       </c>
     </row>
     <row r="576">
@@ -20021,7 +20021,7 @@
         <v>0.38</v>
       </c>
       <c r="H576" s="2" t="n">
-        <v>46075.54629742775</v>
+        <v>46075.54629743056</v>
       </c>
     </row>
     <row r="577">
@@ -20055,7 +20055,7 @@
         <v>2.56</v>
       </c>
       <c r="H577" s="2" t="n">
-        <v>46085.54629743101</v>
+        <v>46085.54629743056</v>
       </c>
     </row>
     <row r="578">
@@ -20089,7 +20089,7 @@
         <v>0.02</v>
       </c>
       <c r="H578" s="2" t="n">
-        <v>46077.54629743465</v>
+        <v>46077.54629743056</v>
       </c>
     </row>
     <row r="579">
@@ -20123,7 +20123,7 @@
         <v>3.24</v>
       </c>
       <c r="H579" s="2" t="n">
-        <v>46073.54629743786</v>
+        <v>46073.54629744213</v>
       </c>
     </row>
     <row r="580">
@@ -20157,7 +20157,7 @@
         <v>1.59</v>
       </c>
       <c r="H580" s="2" t="n">
-        <v>46092.54629744092</v>
+        <v>46092.54629744213</v>
       </c>
     </row>
     <row r="581">
@@ -20191,7 +20191,7 @@
         <v>0.51</v>
       </c>
       <c r="H581" s="2" t="n">
-        <v>46072.54629744399</v>
+        <v>46072.54629744213</v>
       </c>
     </row>
     <row r="582">
@@ -20225,7 +20225,7 @@
         <v>2.7</v>
       </c>
       <c r="H582" s="2" t="n">
-        <v>46094.5462974475</v>
+        <v>46094.54629744213</v>
       </c>
     </row>
     <row r="583">
@@ -20259,7 +20259,7 @@
         <v>3.24</v>
       </c>
       <c r="H583" s="2" t="n">
-        <v>46082.54629745054</v>
+        <v>46082.5462974537</v>
       </c>
     </row>
     <row r="584">
@@ -20293,7 +20293,7 @@
         <v>0.44</v>
       </c>
       <c r="H584" s="2" t="n">
-        <v>46073.54629745373</v>
+        <v>46073.5462974537</v>
       </c>
     </row>
     <row r="585">
@@ -20327,7 +20327,7 @@
         <v>4.27</v>
       </c>
       <c r="H585" s="2" t="n">
-        <v>46079.54629745705</v>
+        <v>46079.5462974537</v>
       </c>
     </row>
     <row r="586">
@@ -20361,7 +20361,7 @@
         <v>3.83</v>
       </c>
       <c r="H586" s="2" t="n">
-        <v>46081.54629746026</v>
+        <v>46081.54629746528</v>
       </c>
     </row>
     <row r="587">
@@ -20395,7 +20395,7 @@
         <v>4.9</v>
       </c>
       <c r="H587" s="2" t="n">
-        <v>46068.54629746337</v>
+        <v>46068.54629746528</v>
       </c>
     </row>
     <row r="588">
@@ -20429,7 +20429,7 @@
         <v>4.38</v>
       </c>
       <c r="H588" s="2" t="n">
-        <v>46075.5462974664</v>
+        <v>46075.54629746528</v>
       </c>
     </row>
     <row r="589">
@@ -20463,7 +20463,7 @@
         <v>4.99</v>
       </c>
       <c r="H589" s="2" t="n">
-        <v>46080.54629746974</v>
+        <v>46080.54629746528</v>
       </c>
     </row>
     <row r="590">
@@ -20497,7 +20497,7 @@
         <v>2.73</v>
       </c>
       <c r="H590" s="2" t="n">
-        <v>46094.54629747287</v>
+        <v>46094.54629747685</v>
       </c>
     </row>
     <row r="591">
@@ -20531,7 +20531,7 @@
         <v>3.72</v>
       </c>
       <c r="H591" s="2" t="n">
-        <v>46081.54629747595</v>
+        <v>46081.54629747685</v>
       </c>
     </row>
     <row r="592">
@@ -20565,7 +20565,7 @@
         <v>4.11</v>
       </c>
       <c r="H592" s="2" t="n">
-        <v>46089.54629747938</v>
+        <v>46089.54629747685</v>
       </c>
     </row>
     <row r="593">
@@ -20599,7 +20599,7 @@
         <v>4.61</v>
       </c>
       <c r="H593" s="2" t="n">
-        <v>46068.54629748264</v>
+        <v>46068.54629747685</v>
       </c>
     </row>
     <row r="594">
@@ -20633,7 +20633,7 @@
         <v>4.53</v>
       </c>
       <c r="H594" s="2" t="n">
-        <v>46079.54629748569</v>
+        <v>46079.54629748843</v>
       </c>
     </row>
     <row r="595">
@@ -20667,7 +20667,7 @@
         <v>3.3</v>
       </c>
       <c r="H595" s="2" t="n">
-        <v>46081.54629748885</v>
+        <v>46081.54629748843</v>
       </c>
     </row>
     <row r="596">
@@ -20701,7 +20701,7 @@
         <v>3.02</v>
       </c>
       <c r="H596" s="2" t="n">
-        <v>46084.54629749214</v>
+        <v>46084.54629748843</v>
       </c>
     </row>
     <row r="597">
@@ -20735,7 +20735,7 @@
         <v>1.73</v>
       </c>
       <c r="H597" s="2" t="n">
-        <v>46083.54629749537</v>
+        <v>46083.5462975</v>
       </c>
     </row>
     <row r="598">
@@ -20769,7 +20769,7 @@
         <v>1.64</v>
       </c>
       <c r="H598" s="2" t="n">
-        <v>46093.54629749839</v>
+        <v>46093.5462975</v>
       </c>
     </row>
     <row r="599">
@@ -20803,7 +20803,7 @@
         <v>2.86</v>
       </c>
       <c r="H599" s="2" t="n">
-        <v>46070.5462975016</v>
+        <v>46070.5462975</v>
       </c>
     </row>
     <row r="600">
@@ -20837,7 +20837,7 @@
         <v>3.95</v>
       </c>
       <c r="H600" s="2" t="n">
-        <v>46071.54629750497</v>
+        <v>46071.5462975</v>
       </c>
     </row>
     <row r="601">
@@ -20871,7 +20871,1707 @@
         <v>1.39</v>
       </c>
       <c r="H601" s="2" t="n">
-        <v>46085.54629750804</v>
+        <v>46085.54629751157</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>baa7ed4a-8c68-4e77-aa14-524f47a81a93</t>
+        </is>
+      </c>
+      <c r="B602" t="n">
+        <v>95</v>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F602" t="n">
+        <v>445.47</v>
+      </c>
+      <c r="G602" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="H602" s="2" t="n">
+        <v>46072.59608732769</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>4c59bf3e-035d-4908-9763-6d5ec796f45c</t>
+        </is>
+      </c>
+      <c r="B603" t="n">
+        <v>95</v>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F603" t="n">
+        <v>378.49</v>
+      </c>
+      <c r="G603" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="H603" s="2" t="n">
+        <v>46085.5960873319</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>29f2432f-2ed0-4ba2-b0b6-7b4a407aeb59</t>
+        </is>
+      </c>
+      <c r="B604" t="n">
+        <v>95</v>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F604" t="n">
+        <v>117.99</v>
+      </c>
+      <c r="G604" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H604" s="2" t="n">
+        <v>46087.5960873353</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>61e7dcd8-aeb7-4992-9db3-d06e9ab7cf61</t>
+        </is>
+      </c>
+      <c r="B605" t="n">
+        <v>95</v>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F605" t="n">
+        <v>136.76</v>
+      </c>
+      <c r="G605" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H605" s="2" t="n">
+        <v>46069.59608733867</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>41107f68-3a74-4c9c-823c-daeeca3f891a</t>
+        </is>
+      </c>
+      <c r="B606" t="n">
+        <v>95</v>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F606" t="n">
+        <v>190.24</v>
+      </c>
+      <c r="G606" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H606" s="2" t="n">
+        <v>46091.59608734177</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>b0976afb-6758-4dd8-a226-184be379d329</t>
+        </is>
+      </c>
+      <c r="B607" t="n">
+        <v>95</v>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F607" t="n">
+        <v>233.31</v>
+      </c>
+      <c r="G607" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="H607" s="2" t="n">
+        <v>46068.5960873451</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>68ada10e-146b-4b24-889a-e9d0b30756cb</t>
+        </is>
+      </c>
+      <c r="B608" t="n">
+        <v>95</v>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F608" t="n">
+        <v>93.01000000000001</v>
+      </c>
+      <c r="G608" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H608" s="2" t="n">
+        <v>46078.59608734838</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>dcd2491e-29ba-4405-981d-8df9b2ecb71b</t>
+        </is>
+      </c>
+      <c r="B609" t="n">
+        <v>95</v>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F609" t="n">
+        <v>443.79</v>
+      </c>
+      <c r="G609" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="H609" s="2" t="n">
+        <v>46087.59608735154</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>f1de66b3-f38c-43fa-bead-8cff6084d01c</t>
+        </is>
+      </c>
+      <c r="B610" t="n">
+        <v>95</v>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F610" t="n">
+        <v>340.39</v>
+      </c>
+      <c r="G610" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H610" s="2" t="n">
+        <v>46066.59608735476</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>a33344f8-d610-43c2-a475-fd55e64ccfb4</t>
+        </is>
+      </c>
+      <c r="B611" t="n">
+        <v>95</v>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F611" t="n">
+        <v>123.85</v>
+      </c>
+      <c r="G611" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="H611" s="2" t="n">
+        <v>46073.59608735793</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>9d88e637-9ff3-4fd6-874c-0aba4f9b3275</t>
+        </is>
+      </c>
+      <c r="B612" t="n">
+        <v>95</v>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F612" t="n">
+        <v>425.2</v>
+      </c>
+      <c r="G612" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="H612" s="2" t="n">
+        <v>46092.59608736123</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>adcdabae-b7cf-4d5b-9f69-52978aeef469</t>
+        </is>
+      </c>
+      <c r="B613" t="n">
+        <v>95</v>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F613" t="n">
+        <v>378.53</v>
+      </c>
+      <c r="G613" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="H613" s="2" t="n">
+        <v>46083.59608736446</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>4ba1722b-390e-4c3d-9142-1b8f5755a988</t>
+        </is>
+      </c>
+      <c r="B614" t="n">
+        <v>95</v>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F614" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="G614" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H614" s="2" t="n">
+        <v>46076.59608736759</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>ac0483b3-194a-4dfc-8079-85023b436f98</t>
+        </is>
+      </c>
+      <c r="B615" t="n">
+        <v>95</v>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F615" t="n">
+        <v>138.17</v>
+      </c>
+      <c r="G615" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H615" s="2" t="n">
+        <v>46066.59608737077</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>fb96b029-8c21-4453-b234-a0276c3a8a59</t>
+        </is>
+      </c>
+      <c r="B616" t="n">
+        <v>95</v>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F616" t="n">
+        <v>238.85</v>
+      </c>
+      <c r="G616" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H616" s="2" t="n">
+        <v>46094.59608737432</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>c0609d05-9aef-4938-9534-6d10ba871786</t>
+        </is>
+      </c>
+      <c r="B617" t="n">
+        <v>95</v>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F617" t="n">
+        <v>22.47</v>
+      </c>
+      <c r="G617" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H617" s="2" t="n">
+        <v>46074.59608737735</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>7370c5a6-8f21-41ad-a2ee-ab44036e761f</t>
+        </is>
+      </c>
+      <c r="B618" t="n">
+        <v>95</v>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F618" t="n">
+        <v>302.85</v>
+      </c>
+      <c r="G618" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="H618" s="2" t="n">
+        <v>46091.59608738041</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>72bf69ad-02ae-4718-8921-564c5b8037d4</t>
+        </is>
+      </c>
+      <c r="B619" t="n">
+        <v>95</v>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F619" t="n">
+        <v>101.49</v>
+      </c>
+      <c r="G619" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="H619" s="2" t="n">
+        <v>46081.59608738368</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>97f693f5-f0d1-403d-8a52-890a47f47cf4</t>
+        </is>
+      </c>
+      <c r="B620" t="n">
+        <v>95</v>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F620" t="n">
+        <v>488.65</v>
+      </c>
+      <c r="G620" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="H620" s="2" t="n">
+        <v>46072.59608738678</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>22d307d5-d678-4305-bdf6-f4ae79d29b68</t>
+        </is>
+      </c>
+      <c r="B621" t="n">
+        <v>95</v>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F621" t="n">
+        <v>126.02</v>
+      </c>
+      <c r="G621" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="H621" s="2" t="n">
+        <v>46073.59608738997</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>7af6b38f-e383-48d6-8ad7-71aeb4ebef90</t>
+        </is>
+      </c>
+      <c r="B622" t="n">
+        <v>95</v>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F622" t="n">
+        <v>27.12</v>
+      </c>
+      <c r="G622" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H622" s="2" t="n">
+        <v>46090.59608739295</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>5d6c6746-0f34-430c-b84a-6b2575338f46</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>95</v>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F623" t="n">
+        <v>237.88</v>
+      </c>
+      <c r="G623" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H623" s="2" t="n">
+        <v>46093.59608739618</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>82ecfcad-7a3a-4a83-a42a-443cd817740c</t>
+        </is>
+      </c>
+      <c r="B624" t="n">
+        <v>95</v>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F624" t="n">
+        <v>343.43</v>
+      </c>
+      <c r="G624" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="H624" s="2" t="n">
+        <v>46066.59608739933</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>1165e8f2-28ab-43bd-b674-fae44f057c04</t>
+        </is>
+      </c>
+      <c r="B625" t="n">
+        <v>95</v>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F625" t="n">
+        <v>383.65</v>
+      </c>
+      <c r="G625" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="H625" s="2" t="n">
+        <v>46091.59608740231</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>26af686a-b539-47c3-abb2-f355aecd3e82</t>
+        </is>
+      </c>
+      <c r="B626" t="n">
+        <v>95</v>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F626" t="n">
+        <v>356.13</v>
+      </c>
+      <c r="G626" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="H626" s="2" t="n">
+        <v>46078.59608740543</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>81f276ed-7123-4305-97f9-69112175e560</t>
+        </is>
+      </c>
+      <c r="B627" t="n">
+        <v>95</v>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F627" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G627" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H627" s="2" t="n">
+        <v>46084.5960874088</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>d61729d3-61ce-421c-a487-8fad73eed802</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>95</v>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F628" t="n">
+        <v>203.05</v>
+      </c>
+      <c r="G628" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="H628" s="2" t="n">
+        <v>46075.59608741204</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>c35738d5-c36d-4f1b-a63c-0316fc7f54c3</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>95</v>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F629" t="n">
+        <v>402.05</v>
+      </c>
+      <c r="G629" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="H629" s="2" t="n">
+        <v>46072.59608741507</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>b44b84a0-2a4a-446a-85e3-e9876384cf05</t>
+        </is>
+      </c>
+      <c r="B630" t="n">
+        <v>95</v>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F630" t="n">
+        <v>416.31</v>
+      </c>
+      <c r="G630" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="H630" s="2" t="n">
+        <v>46087.59608741837</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>97ec28a1-4680-48f2-9f72-04d3b3d0b9fe</t>
+        </is>
+      </c>
+      <c r="B631" t="n">
+        <v>95</v>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F631" t="n">
+        <v>436.25</v>
+      </c>
+      <c r="G631" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="H631" s="2" t="n">
+        <v>46068.59608742173</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>3dfe2580-5fd7-48ff-8b31-71433ae784c8</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>95</v>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F632" t="n">
+        <v>77.09</v>
+      </c>
+      <c r="G632" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="H632" s="2" t="n">
+        <v>46072.59608742501</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>0e0173eb-459d-43ed-bca7-c54dc8c9bcef</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>95</v>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F633" t="n">
+        <v>444.63</v>
+      </c>
+      <c r="G633" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="H633" s="2" t="n">
+        <v>46089.59608742806</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>ae59944b-181d-4187-b886-a1e6b05df5a8</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>95</v>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F634" t="n">
+        <v>322.03</v>
+      </c>
+      <c r="G634" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="H634" s="2" t="n">
+        <v>46071.59608743135</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>523cf0a8-0e7c-4952-afa2-d2314c99fa35</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>95</v>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F635" t="n">
+        <v>165.42</v>
+      </c>
+      <c r="G635" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H635" s="2" t="n">
+        <v>46080.59608743447</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>c1e06220-dba5-4cef-9a7d-f0e6a18b86c8</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>95</v>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F636" t="n">
+        <v>70.42</v>
+      </c>
+      <c r="G636" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H636" s="2" t="n">
+        <v>46090.5960874376</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>fa700996-3763-4bdc-b464-bee1e3fff5b4</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>95</v>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F637" t="n">
+        <v>147.98</v>
+      </c>
+      <c r="G637" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H637" s="2" t="n">
+        <v>46086.59608744081</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>22212b79-aa1e-49f8-bac3-84feebe30114</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>95</v>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F638" t="n">
+        <v>388.36</v>
+      </c>
+      <c r="G638" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="H638" s="2" t="n">
+        <v>46085.59608744404</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>a648b3b3-ea19-48ff-824d-8c137a79086d</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>95</v>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F639" t="n">
+        <v>183.24</v>
+      </c>
+      <c r="G639" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H639" s="2" t="n">
+        <v>46080.5960874472</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>c92240f0-3e68-424c-8f73-01df622bbb1e</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>95</v>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F640" t="n">
+        <v>88.28</v>
+      </c>
+      <c r="G640" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H640" s="2" t="n">
+        <v>46091.59608745036</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>6909372d-c959-4d73-a0aa-7c4129adc2a7</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>95</v>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F641" t="n">
+        <v>472.78</v>
+      </c>
+      <c r="G641" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="H641" s="2" t="n">
+        <v>46066.59608745373</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>25114fce-f940-4e56-b657-c9c19741a6ce</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>95</v>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F642" t="n">
+        <v>117.28</v>
+      </c>
+      <c r="G642" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H642" s="2" t="n">
+        <v>46074.59608745688</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>5fe61a1f-f21e-4469-9717-1f6f45471fb5</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>95</v>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F643" t="n">
+        <v>211.31</v>
+      </c>
+      <c r="G643" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H643" s="2" t="n">
+        <v>46065.59608745999</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>51e0b758-950f-4a4a-ab93-0835fe84b9f8</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>95</v>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F644" t="n">
+        <v>415.89</v>
+      </c>
+      <c r="G644" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="H644" s="2" t="n">
+        <v>46070.5960874631</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>b8d917ff-d52f-461b-9dac-b93d845ec257</t>
+        </is>
+      </c>
+      <c r="B645" t="n">
+        <v>95</v>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F645" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="G645" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H645" s="2" t="n">
+        <v>46094.59608746633</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>6c80f053-815c-4aca-9f83-31f1b2d0e592</t>
+        </is>
+      </c>
+      <c r="B646" t="n">
+        <v>95</v>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F646" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="G646" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H646" s="2" t="n">
+        <v>46082.59608746944</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>8a8b9b44-f54f-4413-8c50-8ceb0ea9abdc</t>
+        </is>
+      </c>
+      <c r="B647" t="n">
+        <v>95</v>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F647" t="n">
+        <v>297.06</v>
+      </c>
+      <c r="G647" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="H647" s="2" t="n">
+        <v>46086.59608747246</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>bdf75d57-ba5d-4d13-914a-bc8398b6de57</t>
+        </is>
+      </c>
+      <c r="B648" t="n">
+        <v>95</v>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F648" t="n">
+        <v>109.47</v>
+      </c>
+      <c r="G648" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H648" s="2" t="n">
+        <v>46091.59608747566</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>e306753e-620e-4d67-a040-73c65dca1210</t>
+        </is>
+      </c>
+      <c r="B649" t="n">
+        <v>95</v>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F649" t="n">
+        <v>64.97</v>
+      </c>
+      <c r="G649" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H649" s="2" t="n">
+        <v>46080.59608747887</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>0a5e8503-5cd4-4982-86ef-ecd8f50fcd98</t>
+        </is>
+      </c>
+      <c r="B650" t="n">
+        <v>95</v>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F650" t="n">
+        <v>454.46</v>
+      </c>
+      <c r="G650" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="H650" s="2" t="n">
+        <v>46081.59608748208</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>c0829025-9725-4f56-ba50-d752ed12d42b</t>
+        </is>
+      </c>
+      <c r="B651" t="n">
+        <v>95</v>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F651" t="n">
+        <v>162.02</v>
+      </c>
+      <c r="G651" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H651" s="2" t="n">
+        <v>46068.59608748528</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H651"/>
+  <dimension ref="A1:H701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20905,7 +20905,7 @@
         <v>4.45</v>
       </c>
       <c r="H602" s="2" t="n">
-        <v>46072.59608732769</v>
+        <v>46072.59608732639</v>
       </c>
     </row>
     <row r="603">
@@ -20939,7 +20939,7 @@
         <v>3.78</v>
       </c>
       <c r="H603" s="2" t="n">
-        <v>46085.5960873319</v>
+        <v>46085.59608732639</v>
       </c>
     </row>
     <row r="604">
@@ -20973,7 +20973,7 @@
         <v>1.18</v>
       </c>
       <c r="H604" s="2" t="n">
-        <v>46087.5960873353</v>
+        <v>46087.59608733797</v>
       </c>
     </row>
     <row r="605">
@@ -21007,7 +21007,7 @@
         <v>1.37</v>
       </c>
       <c r="H605" s="2" t="n">
-        <v>46069.59608733867</v>
+        <v>46069.59608733797</v>
       </c>
     </row>
     <row r="606">
@@ -21041,7 +21041,7 @@
         <v>1.9</v>
       </c>
       <c r="H606" s="2" t="n">
-        <v>46091.59608734177</v>
+        <v>46091.59608733797</v>
       </c>
     </row>
     <row r="607">
@@ -21075,7 +21075,7 @@
         <v>2.33</v>
       </c>
       <c r="H607" s="2" t="n">
-        <v>46068.5960873451</v>
+        <v>46068.59608734954</v>
       </c>
     </row>
     <row r="608">
@@ -21109,7 +21109,7 @@
         <v>0.93</v>
       </c>
       <c r="H608" s="2" t="n">
-        <v>46078.59608734838</v>
+        <v>46078.59608734954</v>
       </c>
     </row>
     <row r="609">
@@ -21143,7 +21143,7 @@
         <v>4.44</v>
       </c>
       <c r="H609" s="2" t="n">
-        <v>46087.59608735154</v>
+        <v>46087.59608734954</v>
       </c>
     </row>
     <row r="610">
@@ -21177,7 +21177,7 @@
         <v>3.4</v>
       </c>
       <c r="H610" s="2" t="n">
-        <v>46066.59608735476</v>
+        <v>46066.59608734954</v>
       </c>
     </row>
     <row r="611">
@@ -21211,7 +21211,7 @@
         <v>1.24</v>
       </c>
       <c r="H611" s="2" t="n">
-        <v>46073.59608735793</v>
+        <v>46073.59608736111</v>
       </c>
     </row>
     <row r="612">
@@ -21245,7 +21245,7 @@
         <v>4.25</v>
       </c>
       <c r="H612" s="2" t="n">
-        <v>46092.59608736123</v>
+        <v>46092.59608736111</v>
       </c>
     </row>
     <row r="613">
@@ -21279,7 +21279,7 @@
         <v>3.79</v>
       </c>
       <c r="H613" s="2" t="n">
-        <v>46083.59608736446</v>
+        <v>46083.59608736111</v>
       </c>
     </row>
     <row r="614">
@@ -21313,7 +21313,7 @@
         <v>0.15</v>
       </c>
       <c r="H614" s="2" t="n">
-        <v>46076.59608736759</v>
+        <v>46076.59608737269</v>
       </c>
     </row>
     <row r="615">
@@ -21347,7 +21347,7 @@
         <v>1.38</v>
       </c>
       <c r="H615" s="2" t="n">
-        <v>46066.59608737077</v>
+        <v>46066.59608737269</v>
       </c>
     </row>
     <row r="616">
@@ -21381,7 +21381,7 @@
         <v>2.39</v>
       </c>
       <c r="H616" s="2" t="n">
-        <v>46094.59608737432</v>
+        <v>46094.59608737269</v>
       </c>
     </row>
     <row r="617">
@@ -21415,7 +21415,7 @@
         <v>0.22</v>
       </c>
       <c r="H617" s="2" t="n">
-        <v>46074.59608737735</v>
+        <v>46074.59608737269</v>
       </c>
     </row>
     <row r="618">
@@ -21449,7 +21449,7 @@
         <v>3.03</v>
       </c>
       <c r="H618" s="2" t="n">
-        <v>46091.59608738041</v>
+        <v>46091.59608738426</v>
       </c>
     </row>
     <row r="619">
@@ -21483,7 +21483,7 @@
         <v>1.01</v>
       </c>
       <c r="H619" s="2" t="n">
-        <v>46081.59608738368</v>
+        <v>46081.59608738426</v>
       </c>
     </row>
     <row r="620">
@@ -21517,7 +21517,7 @@
         <v>4.89</v>
       </c>
       <c r="H620" s="2" t="n">
-        <v>46072.59608738678</v>
+        <v>46072.59608738426</v>
       </c>
     </row>
     <row r="621">
@@ -21551,7 +21551,7 @@
         <v>1.26</v>
       </c>
       <c r="H621" s="2" t="n">
-        <v>46073.59608738997</v>
+        <v>46073.59608738426</v>
       </c>
     </row>
     <row r="622">
@@ -21585,7 +21585,7 @@
         <v>0.27</v>
       </c>
       <c r="H622" s="2" t="n">
-        <v>46090.59608739295</v>
+        <v>46090.59608739583</v>
       </c>
     </row>
     <row r="623">
@@ -21619,7 +21619,7 @@
         <v>2.38</v>
       </c>
       <c r="H623" s="2" t="n">
-        <v>46093.59608739618</v>
+        <v>46093.59608739583</v>
       </c>
     </row>
     <row r="624">
@@ -21653,7 +21653,7 @@
         <v>3.43</v>
       </c>
       <c r="H624" s="2" t="n">
-        <v>46066.59608739933</v>
+        <v>46066.59608739583</v>
       </c>
     </row>
     <row r="625">
@@ -21687,7 +21687,7 @@
         <v>3.84</v>
       </c>
       <c r="H625" s="2" t="n">
-        <v>46091.59608740231</v>
+        <v>46091.59608740741</v>
       </c>
     </row>
     <row r="626">
@@ -21721,7 +21721,7 @@
         <v>3.56</v>
       </c>
       <c r="H626" s="2" t="n">
-        <v>46078.59608740543</v>
+        <v>46078.59608740741</v>
       </c>
     </row>
     <row r="627">
@@ -21755,7 +21755,7 @@
         <v>0.05</v>
       </c>
       <c r="H627" s="2" t="n">
-        <v>46084.5960874088</v>
+        <v>46084.59608740741</v>
       </c>
     </row>
     <row r="628">
@@ -21789,7 +21789,7 @@
         <v>2.03</v>
       </c>
       <c r="H628" s="2" t="n">
-        <v>46075.59608741204</v>
+        <v>46075.59608740741</v>
       </c>
     </row>
     <row r="629">
@@ -21823,7 +21823,7 @@
         <v>4.02</v>
       </c>
       <c r="H629" s="2" t="n">
-        <v>46072.59608741507</v>
+        <v>46072.59608741898</v>
       </c>
     </row>
     <row r="630">
@@ -21857,7 +21857,7 @@
         <v>4.16</v>
       </c>
       <c r="H630" s="2" t="n">
-        <v>46087.59608741837</v>
+        <v>46087.59608741898</v>
       </c>
     </row>
     <row r="631">
@@ -21891,7 +21891,7 @@
         <v>4.36</v>
       </c>
       <c r="H631" s="2" t="n">
-        <v>46068.59608742173</v>
+        <v>46068.59608741898</v>
       </c>
     </row>
     <row r="632">
@@ -21925,7 +21925,7 @@
         <v>0.77</v>
       </c>
       <c r="H632" s="2" t="n">
-        <v>46072.59608742501</v>
+        <v>46072.59608743055</v>
       </c>
     </row>
     <row r="633">
@@ -21959,7 +21959,7 @@
         <v>4.45</v>
       </c>
       <c r="H633" s="2" t="n">
-        <v>46089.59608742806</v>
+        <v>46089.59608743055</v>
       </c>
     </row>
     <row r="634">
@@ -21993,7 +21993,7 @@
         <v>3.22</v>
       </c>
       <c r="H634" s="2" t="n">
-        <v>46071.59608743135</v>
+        <v>46071.59608743055</v>
       </c>
     </row>
     <row r="635">
@@ -22027,7 +22027,7 @@
         <v>1.65</v>
       </c>
       <c r="H635" s="2" t="n">
-        <v>46080.59608743447</v>
+        <v>46080.59608743055</v>
       </c>
     </row>
     <row r="636">
@@ -22061,7 +22061,7 @@
         <v>0.7</v>
       </c>
       <c r="H636" s="2" t="n">
-        <v>46090.5960874376</v>
+        <v>46090.59608744213</v>
       </c>
     </row>
     <row r="637">
@@ -22095,7 +22095,7 @@
         <v>1.48</v>
       </c>
       <c r="H637" s="2" t="n">
-        <v>46086.59608744081</v>
+        <v>46086.59608744213</v>
       </c>
     </row>
     <row r="638">
@@ -22129,7 +22129,7 @@
         <v>3.88</v>
       </c>
       <c r="H638" s="2" t="n">
-        <v>46085.59608744404</v>
+        <v>46085.59608744213</v>
       </c>
     </row>
     <row r="639">
@@ -22163,7 +22163,7 @@
         <v>1.83</v>
       </c>
       <c r="H639" s="2" t="n">
-        <v>46080.5960874472</v>
+        <v>46080.59608744213</v>
       </c>
     </row>
     <row r="640">
@@ -22197,7 +22197,7 @@
         <v>0.88</v>
       </c>
       <c r="H640" s="2" t="n">
-        <v>46091.59608745036</v>
+        <v>46091.5960874537</v>
       </c>
     </row>
     <row r="641">
@@ -22231,7 +22231,7 @@
         <v>4.73</v>
       </c>
       <c r="H641" s="2" t="n">
-        <v>46066.59608745373</v>
+        <v>46066.5960874537</v>
       </c>
     </row>
     <row r="642">
@@ -22265,7 +22265,7 @@
         <v>1.17</v>
       </c>
       <c r="H642" s="2" t="n">
-        <v>46074.59608745688</v>
+        <v>46074.5960874537</v>
       </c>
     </row>
     <row r="643">
@@ -22299,7 +22299,7 @@
         <v>2.11</v>
       </c>
       <c r="H643" s="2" t="n">
-        <v>46065.59608745999</v>
+        <v>46065.59608746528</v>
       </c>
     </row>
     <row r="644">
@@ -22333,7 +22333,7 @@
         <v>4.16</v>
       </c>
       <c r="H644" s="2" t="n">
-        <v>46070.5960874631</v>
+        <v>46070.59608746528</v>
       </c>
     </row>
     <row r="645">
@@ -22367,7 +22367,7 @@
         <v>0.84</v>
       </c>
       <c r="H645" s="2" t="n">
-        <v>46094.59608746633</v>
+        <v>46094.59608746528</v>
       </c>
     </row>
     <row r="646">
@@ -22401,7 +22401,7 @@
         <v>0.05</v>
       </c>
       <c r="H646" s="2" t="n">
-        <v>46082.59608746944</v>
+        <v>46082.59608746528</v>
       </c>
     </row>
     <row r="647">
@@ -22435,7 +22435,7 @@
         <v>2.97</v>
       </c>
       <c r="H647" s="2" t="n">
-        <v>46086.59608747246</v>
+        <v>46086.59608747685</v>
       </c>
     </row>
     <row r="648">
@@ -22469,7 +22469,7 @@
         <v>1.09</v>
       </c>
       <c r="H648" s="2" t="n">
-        <v>46091.59608747566</v>
+        <v>46091.59608747685</v>
       </c>
     </row>
     <row r="649">
@@ -22503,7 +22503,7 @@
         <v>0.65</v>
       </c>
       <c r="H649" s="2" t="n">
-        <v>46080.59608747887</v>
+        <v>46080.59608747685</v>
       </c>
     </row>
     <row r="650">
@@ -22537,7 +22537,7 @@
         <v>4.54</v>
       </c>
       <c r="H650" s="2" t="n">
-        <v>46081.59608748208</v>
+        <v>46081.59608747685</v>
       </c>
     </row>
     <row r="651">
@@ -22571,7 +22571,1707 @@
         <v>1.62</v>
       </c>
       <c r="H651" s="2" t="n">
-        <v>46068.59608748528</v>
+        <v>46068.59608748843</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>50b7255d-476e-4238-9d70-2c720e2eaeef</t>
+        </is>
+      </c>
+      <c r="B652" t="n">
+        <v>95</v>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F652" t="n">
+        <v>419.01</v>
+      </c>
+      <c r="G652" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="H652" s="2" t="n">
+        <v>46081.61179396173</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>d016f671-bfe6-44da-9864-f40b52009548</t>
+        </is>
+      </c>
+      <c r="B653" t="n">
+        <v>95</v>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F653" t="n">
+        <v>320.78</v>
+      </c>
+      <c r="G653" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="H653" s="2" t="n">
+        <v>46079.61179396624</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>d0493c70-feee-44b3-904a-c2d49a899a65</t>
+        </is>
+      </c>
+      <c r="B654" t="n">
+        <v>95</v>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F654" t="n">
+        <v>264.05</v>
+      </c>
+      <c r="G654" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H654" s="2" t="n">
+        <v>46069.61179396943</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>58eaca07-7f6e-469e-82ee-ef26f1d55147</t>
+        </is>
+      </c>
+      <c r="B655" t="n">
+        <v>95</v>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F655" t="n">
+        <v>323.45</v>
+      </c>
+      <c r="G655" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="H655" s="2" t="n">
+        <v>46075.61179397273</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>64cb6a25-ce39-44de-b7dd-1aea65360e0a</t>
+        </is>
+      </c>
+      <c r="B656" t="n">
+        <v>95</v>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F656" t="n">
+        <v>16.97</v>
+      </c>
+      <c r="G656" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H656" s="2" t="n">
+        <v>46066.61179397591</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>7b45770b-97a7-4f27-acd7-b0a83f233805</t>
+        </is>
+      </c>
+      <c r="B657" t="n">
+        <v>95</v>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F657" t="n">
+        <v>383.85</v>
+      </c>
+      <c r="G657" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="H657" s="2" t="n">
+        <v>46075.61179397925</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>ae8d9832-1820-4576-88fb-7c759e1304a6</t>
+        </is>
+      </c>
+      <c r="B658" t="n">
+        <v>95</v>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F658" t="n">
+        <v>238.14</v>
+      </c>
+      <c r="G658" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H658" s="2" t="n">
+        <v>46065.61179398235</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>837840d4-088d-4771-8ed8-80e491829998</t>
+        </is>
+      </c>
+      <c r="B659" t="n">
+        <v>95</v>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F659" t="n">
+        <v>288.97</v>
+      </c>
+      <c r="G659" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="H659" s="2" t="n">
+        <v>46071.61179398542</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>53658452-c234-44ab-96c8-521fb8f20a1f</t>
+        </is>
+      </c>
+      <c r="B660" t="n">
+        <v>95</v>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F660" t="n">
+        <v>40.91</v>
+      </c>
+      <c r="G660" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H660" s="2" t="n">
+        <v>46071.61179398852</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>e82d9af5-b28e-4046-b142-278d1dedb31b</t>
+        </is>
+      </c>
+      <c r="B661" t="n">
+        <v>95</v>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F661" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="G661" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H661" s="2" t="n">
+        <v>46072.61179399218</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>7faad09f-5b0e-4eb1-9823-f094399c0bdd</t>
+        </is>
+      </c>
+      <c r="B662" t="n">
+        <v>95</v>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F662" t="n">
+        <v>71.84</v>
+      </c>
+      <c r="G662" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H662" s="2" t="n">
+        <v>46069.61179399538</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>55a27469-0140-4719-935f-d997cea4de36</t>
+        </is>
+      </c>
+      <c r="B663" t="n">
+        <v>95</v>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F663" t="n">
+        <v>424.74</v>
+      </c>
+      <c r="G663" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="H663" s="2" t="n">
+        <v>46074.61179399846</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>e452e18f-55b0-4a77-b265-679a6f1068b9</t>
+        </is>
+      </c>
+      <c r="B664" t="n">
+        <v>95</v>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F664" t="n">
+        <v>189.43</v>
+      </c>
+      <c r="G664" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H664" s="2" t="n">
+        <v>46079.61179400211</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>89f8d0ff-245a-4035-ac17-001d9714ef1f</t>
+        </is>
+      </c>
+      <c r="B665" t="n">
+        <v>95</v>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F665" t="n">
+        <v>426.96</v>
+      </c>
+      <c r="G665" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="H665" s="2" t="n">
+        <v>46066.61179400529</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>4285c4d1-fdac-4a52-ae33-79cb4da4b3c2</t>
+        </is>
+      </c>
+      <c r="B666" t="n">
+        <v>95</v>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F666" t="n">
+        <v>371.61</v>
+      </c>
+      <c r="G666" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="H666" s="2" t="n">
+        <v>46083.61179400842</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>37a7dcb1-7521-4007-a711-357c1f1adb77</t>
+        </is>
+      </c>
+      <c r="B667" t="n">
+        <v>95</v>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F667" t="n">
+        <v>452</v>
+      </c>
+      <c r="G667" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="H667" s="2" t="n">
+        <v>46085.61179401147</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>6f81e737-1bd6-4d70-95e2-2e2f7a796e33</t>
+        </is>
+      </c>
+      <c r="B668" t="n">
+        <v>95</v>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F668" t="n">
+        <v>102.44</v>
+      </c>
+      <c r="G668" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H668" s="2" t="n">
+        <v>46065.61179401483</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>b6676b5d-9e7e-4dad-a651-a4c11c1ee04a</t>
+        </is>
+      </c>
+      <c r="B669" t="n">
+        <v>95</v>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F669" t="n">
+        <v>356.42</v>
+      </c>
+      <c r="G669" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="H669" s="2" t="n">
+        <v>46069.61179401798</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>7eed7d97-ca1c-4408-90d9-a0e0d45a8cea</t>
+        </is>
+      </c>
+      <c r="B670" t="n">
+        <v>95</v>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F670" t="n">
+        <v>455.68</v>
+      </c>
+      <c r="G670" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="H670" s="2" t="n">
+        <v>46088.61179402109</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>31f9bf89-f3bb-468e-b22c-d99c6352888f</t>
+        </is>
+      </c>
+      <c r="B671" t="n">
+        <v>95</v>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F671" t="n">
+        <v>161.42</v>
+      </c>
+      <c r="G671" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H671" s="2" t="n">
+        <v>46094.61179402428</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>3d31031a-5fce-42ad-a7f6-0b8f60b8368a</t>
+        </is>
+      </c>
+      <c r="B672" t="n">
+        <v>95</v>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F672" t="n">
+        <v>25.19</v>
+      </c>
+      <c r="G672" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H672" s="2" t="n">
+        <v>46081.61179402744</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>ffe2d4d6-7edc-442f-a591-2adb63399103</t>
+        </is>
+      </c>
+      <c r="B673" t="n">
+        <v>95</v>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F673" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="G673" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H673" s="2" t="n">
+        <v>46092.61179403054</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>7b11a2c9-c127-430c-aba9-874b0d7d60a1</t>
+        </is>
+      </c>
+      <c r="B674" t="n">
+        <v>95</v>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F674" t="n">
+        <v>98.33</v>
+      </c>
+      <c r="G674" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H674" s="2" t="n">
+        <v>46076.61179403355</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>d8af2d27-ffd6-400f-9909-8bca54261334</t>
+        </is>
+      </c>
+      <c r="B675" t="n">
+        <v>95</v>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F675" t="n">
+        <v>210.21</v>
+      </c>
+      <c r="G675" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H675" s="2" t="n">
+        <v>46086.61179403673</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>a5f4bb36-2e0b-40ee-9979-2836680e6bf3</t>
+        </is>
+      </c>
+      <c r="B676" t="n">
+        <v>95</v>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F676" t="n">
+        <v>211.96</v>
+      </c>
+      <c r="G676" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H676" s="2" t="n">
+        <v>46085.61179403979</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>d3445bbe-07e6-4b31-afa2-f316de4e88bd</t>
+        </is>
+      </c>
+      <c r="B677" t="n">
+        <v>95</v>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F677" t="n">
+        <v>349.03</v>
+      </c>
+      <c r="G677" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="H677" s="2" t="n">
+        <v>46087.61179404286</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>a786efb3-2d5e-4338-bb26-aa2c6b07e303</t>
+        </is>
+      </c>
+      <c r="B678" t="n">
+        <v>95</v>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F678" t="n">
+        <v>433.43</v>
+      </c>
+      <c r="G678" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="H678" s="2" t="n">
+        <v>46070.61179404601</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>ab35d860-c8ba-42ff-b36e-8c5b4712c812</t>
+        </is>
+      </c>
+      <c r="B679" t="n">
+        <v>95</v>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F679" t="n">
+        <v>308.15</v>
+      </c>
+      <c r="G679" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="H679" s="2" t="n">
+        <v>46073.6117940496</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>24c1f530-8b3a-4895-a21f-f1baacf639d1</t>
+        </is>
+      </c>
+      <c r="B680" t="n">
+        <v>95</v>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F680" t="n">
+        <v>354.08</v>
+      </c>
+      <c r="G680" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="H680" s="2" t="n">
+        <v>46089.61179405285</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>caee9bdb-f0ed-41bc-b363-1679b4bf92b4</t>
+        </is>
+      </c>
+      <c r="B681" t="n">
+        <v>95</v>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F681" t="n">
+        <v>168.46</v>
+      </c>
+      <c r="G681" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H681" s="2" t="n">
+        <v>46090.61179405617</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>3fc6c417-6242-4987-a29f-f0816aac8cdb</t>
+        </is>
+      </c>
+      <c r="B682" t="n">
+        <v>95</v>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F682" t="n">
+        <v>136.9</v>
+      </c>
+      <c r="G682" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H682" s="2" t="n">
+        <v>46073.61179405943</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>722acc51-a7ad-4e31-a890-834bf2b52348</t>
+        </is>
+      </c>
+      <c r="B683" t="n">
+        <v>95</v>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F683" t="n">
+        <v>446.56</v>
+      </c>
+      <c r="G683" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="H683" s="2" t="n">
+        <v>46091.61179406247</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>dc4c3c5a-6a72-4c80-b014-1db0d28b8ab3</t>
+        </is>
+      </c>
+      <c r="B684" t="n">
+        <v>95</v>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F684" t="n">
+        <v>290.07</v>
+      </c>
+      <c r="G684" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H684" s="2" t="n">
+        <v>46089.61179406563</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>d6e1ae04-ef81-4183-9c0c-0410a911b306</t>
+        </is>
+      </c>
+      <c r="B685" t="n">
+        <v>95</v>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F685" t="n">
+        <v>464.89</v>
+      </c>
+      <c r="G685" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="H685" s="2" t="n">
+        <v>46079.61179406888</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>50a27a7b-9ff6-4da6-8ade-41375578fa90</t>
+        </is>
+      </c>
+      <c r="B686" t="n">
+        <v>95</v>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F686" t="n">
+        <v>73.86</v>
+      </c>
+      <c r="G686" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H686" s="2" t="n">
+        <v>46087.61179407204</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>4f058fa4-0986-4766-a63e-5854c724ce2e</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>95</v>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F687" t="n">
+        <v>276.6</v>
+      </c>
+      <c r="G687" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="H687" s="2" t="n">
+        <v>46082.61179407528</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>b5abcdaa-8f1d-405e-bc26-e8539c96a86f</t>
+        </is>
+      </c>
+      <c r="B688" t="n">
+        <v>95</v>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F688" t="n">
+        <v>132.84</v>
+      </c>
+      <c r="G688" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H688" s="2" t="n">
+        <v>46089.61179407842</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>095b74d7-13d1-432f-ae1f-1210cc566b7d</t>
+        </is>
+      </c>
+      <c r="B689" t="n">
+        <v>95</v>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F689" t="n">
+        <v>58.07</v>
+      </c>
+      <c r="G689" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H689" s="2" t="n">
+        <v>46093.61179408162</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>c2811e74-9dd6-4c43-8775-2445557a6d14</t>
+        </is>
+      </c>
+      <c r="B690" t="n">
+        <v>95</v>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F690" t="n">
+        <v>102.72</v>
+      </c>
+      <c r="G690" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H690" s="2" t="n">
+        <v>46066.61179408475</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>7639bc2c-b8d2-4908-a6e3-4e43360c06b9</t>
+        </is>
+      </c>
+      <c r="B691" t="n">
+        <v>95</v>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F691" t="n">
+        <v>456.08</v>
+      </c>
+      <c r="G691" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="H691" s="2" t="n">
+        <v>46082.61179408788</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>adf08da6-1507-48f4-985b-6428905f5d80</t>
+        </is>
+      </c>
+      <c r="B692" t="n">
+        <v>95</v>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F692" t="n">
+        <v>430.29</v>
+      </c>
+      <c r="G692" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H692" s="2" t="n">
+        <v>46083.61179409098</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>3a24274c-68c3-4368-a7d4-f93885bfc531</t>
+        </is>
+      </c>
+      <c r="B693" t="n">
+        <v>95</v>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F693" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="G693" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H693" s="2" t="n">
+        <v>46076.61179409466</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>af50c5b4-88d4-472d-8dfc-c2c700b7ca8a</t>
+        </is>
+      </c>
+      <c r="B694" t="n">
+        <v>95</v>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F694" t="n">
+        <v>249.64</v>
+      </c>
+      <c r="G694" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H694" s="2" t="n">
+        <v>46065.61179409815</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>165e8d0a-3ac1-45d7-a734-af1eed6bfd95</t>
+        </is>
+      </c>
+      <c r="B695" t="n">
+        <v>95</v>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F695" t="n">
+        <v>461.54</v>
+      </c>
+      <c r="G695" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="H695" s="2" t="n">
+        <v>46076.61179410118</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>3cc9a3a8-c5dd-49f9-8dbb-dd3fed0c405e</t>
+        </is>
+      </c>
+      <c r="B696" t="n">
+        <v>95</v>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F696" t="n">
+        <v>234.57</v>
+      </c>
+      <c r="G696" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="H696" s="2" t="n">
+        <v>46068.61179410419</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>c90d96ca-e9ab-40ff-b2af-ed3144a590a5</t>
+        </is>
+      </c>
+      <c r="B697" t="n">
+        <v>95</v>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F697" t="n">
+        <v>419.5</v>
+      </c>
+      <c r="G697" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H697" s="2" t="n">
+        <v>46088.61179410746</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>da65f702-8f71-46a3-9eb8-c03e65c831ee</t>
+        </is>
+      </c>
+      <c r="B698" t="n">
+        <v>95</v>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F698" t="n">
+        <v>311.78</v>
+      </c>
+      <c r="G698" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="H698" s="2" t="n">
+        <v>46079.61179411066</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>042d8ec2-dfe2-4a2a-a566-e46a10688be8</t>
+        </is>
+      </c>
+      <c r="B699" t="n">
+        <v>95</v>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F699" t="n">
+        <v>392.42</v>
+      </c>
+      <c r="G699" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H699" s="2" t="n">
+        <v>46075.61179411387</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>e3bf582c-17ef-4b04-8385-194b5152b866</t>
+        </is>
+      </c>
+      <c r="B700" t="n">
+        <v>95</v>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F700" t="n">
+        <v>108.64</v>
+      </c>
+      <c r="G700" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H700" s="2" t="n">
+        <v>46078.61179411702</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>0e84fbd8-daa6-46f4-b937-24dc76d64f61</t>
+        </is>
+      </c>
+      <c r="B701" t="n">
+        <v>95</v>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F701" t="n">
+        <v>237.39</v>
+      </c>
+      <c r="G701" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="H701" s="2" t="n">
+        <v>46082.6117941203</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H701"/>
+  <dimension ref="A1:H751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22605,7 +22605,7 @@
         <v>4.19</v>
       </c>
       <c r="H652" s="2" t="n">
-        <v>46081.61179396173</v>
+        <v>46081.61179395833</v>
       </c>
     </row>
     <row r="653">
@@ -22639,7 +22639,7 @@
         <v>3.21</v>
       </c>
       <c r="H653" s="2" t="n">
-        <v>46079.61179396624</v>
+        <v>46079.61179396991</v>
       </c>
     </row>
     <row r="654">
@@ -22673,7 +22673,7 @@
         <v>2.64</v>
       </c>
       <c r="H654" s="2" t="n">
-        <v>46069.61179396943</v>
+        <v>46069.61179396991</v>
       </c>
     </row>
     <row r="655">
@@ -22707,7 +22707,7 @@
         <v>3.23</v>
       </c>
       <c r="H655" s="2" t="n">
-        <v>46075.61179397273</v>
+        <v>46075.61179396991</v>
       </c>
     </row>
     <row r="656">
@@ -22741,7 +22741,7 @@
         <v>0.17</v>
       </c>
       <c r="H656" s="2" t="n">
-        <v>46066.61179397591</v>
+        <v>46066.61179398148</v>
       </c>
     </row>
     <row r="657">
@@ -22775,7 +22775,7 @@
         <v>3.84</v>
       </c>
       <c r="H657" s="2" t="n">
-        <v>46075.61179397925</v>
+        <v>46075.61179398148</v>
       </c>
     </row>
     <row r="658">
@@ -22809,7 +22809,7 @@
         <v>2.38</v>
       </c>
       <c r="H658" s="2" t="n">
-        <v>46065.61179398235</v>
+        <v>46065.61179398148</v>
       </c>
     </row>
     <row r="659">
@@ -22843,7 +22843,7 @@
         <v>2.89</v>
       </c>
       <c r="H659" s="2" t="n">
-        <v>46071.61179398542</v>
+        <v>46071.61179398148</v>
       </c>
     </row>
     <row r="660">
@@ -22877,7 +22877,7 @@
         <v>0.41</v>
       </c>
       <c r="H660" s="2" t="n">
-        <v>46071.61179398852</v>
+        <v>46071.61179399306</v>
       </c>
     </row>
     <row r="661">
@@ -22911,7 +22911,7 @@
         <v>0.44</v>
       </c>
       <c r="H661" s="2" t="n">
-        <v>46072.61179399218</v>
+        <v>46072.61179399306</v>
       </c>
     </row>
     <row r="662">
@@ -22945,7 +22945,7 @@
         <v>0.72</v>
       </c>
       <c r="H662" s="2" t="n">
-        <v>46069.61179399538</v>
+        <v>46069.61179399306</v>
       </c>
     </row>
     <row r="663">
@@ -22979,7 +22979,7 @@
         <v>4.25</v>
       </c>
       <c r="H663" s="2" t="n">
-        <v>46074.61179399846</v>
+        <v>46074.61179399306</v>
       </c>
     </row>
     <row r="664">
@@ -23013,7 +23013,7 @@
         <v>1.89</v>
       </c>
       <c r="H664" s="2" t="n">
-        <v>46079.61179400211</v>
+        <v>46079.61179400463</v>
       </c>
     </row>
     <row r="665">
@@ -23047,7 +23047,7 @@
         <v>4.27</v>
       </c>
       <c r="H665" s="2" t="n">
-        <v>46066.61179400529</v>
+        <v>46066.61179400463</v>
       </c>
     </row>
     <row r="666">
@@ -23081,7 +23081,7 @@
         <v>3.72</v>
       </c>
       <c r="H666" s="2" t="n">
-        <v>46083.61179400842</v>
+        <v>46083.61179400463</v>
       </c>
     </row>
     <row r="667">
@@ -23115,7 +23115,7 @@
         <v>4.52</v>
       </c>
       <c r="H667" s="2" t="n">
-        <v>46085.61179401147</v>
+        <v>46085.6117940162</v>
       </c>
     </row>
     <row r="668">
@@ -23149,7 +23149,7 @@
         <v>1.02</v>
       </c>
       <c r="H668" s="2" t="n">
-        <v>46065.61179401483</v>
+        <v>46065.6117940162</v>
       </c>
     </row>
     <row r="669">
@@ -23183,7 +23183,7 @@
         <v>3.56</v>
       </c>
       <c r="H669" s="2" t="n">
-        <v>46069.61179401798</v>
+        <v>46069.6117940162</v>
       </c>
     </row>
     <row r="670">
@@ -23217,7 +23217,7 @@
         <v>4.56</v>
       </c>
       <c r="H670" s="2" t="n">
-        <v>46088.61179402109</v>
+        <v>46088.6117940162</v>
       </c>
     </row>
     <row r="671">
@@ -23251,7 +23251,7 @@
         <v>1.61</v>
       </c>
       <c r="H671" s="2" t="n">
-        <v>46094.61179402428</v>
+        <v>46094.61179402778</v>
       </c>
     </row>
     <row r="672">
@@ -23285,7 +23285,7 @@
         <v>0.25</v>
       </c>
       <c r="H672" s="2" t="n">
-        <v>46081.61179402744</v>
+        <v>46081.61179402778</v>
       </c>
     </row>
     <row r="673">
@@ -23319,7 +23319,7 @@
         <v>0.36</v>
       </c>
       <c r="H673" s="2" t="n">
-        <v>46092.61179403054</v>
+        <v>46092.61179402778</v>
       </c>
     </row>
     <row r="674">
@@ -23353,7 +23353,7 @@
         <v>0.98</v>
       </c>
       <c r="H674" s="2" t="n">
-        <v>46076.61179403355</v>
+        <v>46076.61179402778</v>
       </c>
     </row>
     <row r="675">
@@ -23387,7 +23387,7 @@
         <v>2.1</v>
       </c>
       <c r="H675" s="2" t="n">
-        <v>46086.61179403673</v>
+        <v>46086.61179403935</v>
       </c>
     </row>
     <row r="676">
@@ -23421,7 +23421,7 @@
         <v>2.12</v>
       </c>
       <c r="H676" s="2" t="n">
-        <v>46085.61179403979</v>
+        <v>46085.61179403935</v>
       </c>
     </row>
     <row r="677">
@@ -23455,7 +23455,7 @@
         <v>3.49</v>
       </c>
       <c r="H677" s="2" t="n">
-        <v>46087.61179404286</v>
+        <v>46087.61179403935</v>
       </c>
     </row>
     <row r="678">
@@ -23489,7 +23489,7 @@
         <v>4.33</v>
       </c>
       <c r="H678" s="2" t="n">
-        <v>46070.61179404601</v>
+        <v>46070.61179405093</v>
       </c>
     </row>
     <row r="679">
@@ -23523,7 +23523,7 @@
         <v>3.08</v>
       </c>
       <c r="H679" s="2" t="n">
-        <v>46073.6117940496</v>
+        <v>46073.61179405093</v>
       </c>
     </row>
     <row r="680">
@@ -23557,7 +23557,7 @@
         <v>3.54</v>
       </c>
       <c r="H680" s="2" t="n">
-        <v>46089.61179405285</v>
+        <v>46089.61179405093</v>
       </c>
     </row>
     <row r="681">
@@ -23591,7 +23591,7 @@
         <v>1.68</v>
       </c>
       <c r="H681" s="2" t="n">
-        <v>46090.61179405617</v>
+        <v>46090.61179405093</v>
       </c>
     </row>
     <row r="682">
@@ -23625,7 +23625,7 @@
         <v>1.37</v>
       </c>
       <c r="H682" s="2" t="n">
-        <v>46073.61179405943</v>
+        <v>46073.6117940625</v>
       </c>
     </row>
     <row r="683">
@@ -23659,7 +23659,7 @@
         <v>4.47</v>
       </c>
       <c r="H683" s="2" t="n">
-        <v>46091.61179406247</v>
+        <v>46091.6117940625</v>
       </c>
     </row>
     <row r="684">
@@ -23693,7 +23693,7 @@
         <v>2.9</v>
       </c>
       <c r="H684" s="2" t="n">
-        <v>46089.61179406563</v>
+        <v>46089.6117940625</v>
       </c>
     </row>
     <row r="685">
@@ -23727,7 +23727,7 @@
         <v>4.65</v>
       </c>
       <c r="H685" s="2" t="n">
-        <v>46079.61179406888</v>
+        <v>46079.61179407407</v>
       </c>
     </row>
     <row r="686">
@@ -23761,7 +23761,7 @@
         <v>0.74</v>
       </c>
       <c r="H686" s="2" t="n">
-        <v>46087.61179407204</v>
+        <v>46087.61179407407</v>
       </c>
     </row>
     <row r="687">
@@ -23795,7 +23795,7 @@
         <v>2.77</v>
       </c>
       <c r="H687" s="2" t="n">
-        <v>46082.61179407528</v>
+        <v>46082.61179407407</v>
       </c>
     </row>
     <row r="688">
@@ -23829,7 +23829,7 @@
         <v>1.33</v>
       </c>
       <c r="H688" s="2" t="n">
-        <v>46089.61179407842</v>
+        <v>46089.61179407407</v>
       </c>
     </row>
     <row r="689">
@@ -23863,7 +23863,7 @@
         <v>0.58</v>
       </c>
       <c r="H689" s="2" t="n">
-        <v>46093.61179408162</v>
+        <v>46093.61179408565</v>
       </c>
     </row>
     <row r="690">
@@ -23897,7 +23897,7 @@
         <v>1.03</v>
       </c>
       <c r="H690" s="2" t="n">
-        <v>46066.61179408475</v>
+        <v>46066.61179408565</v>
       </c>
     </row>
     <row r="691">
@@ -23931,7 +23931,7 @@
         <v>4.56</v>
       </c>
       <c r="H691" s="2" t="n">
-        <v>46082.61179408788</v>
+        <v>46082.61179408565</v>
       </c>
     </row>
     <row r="692">
@@ -23965,7 +23965,7 @@
         <v>4.3</v>
       </c>
       <c r="H692" s="2" t="n">
-        <v>46083.61179409098</v>
+        <v>46083.61179408565</v>
       </c>
     </row>
     <row r="693">
@@ -23999,7 +23999,7 @@
         <v>0.34</v>
       </c>
       <c r="H693" s="2" t="n">
-        <v>46076.61179409466</v>
+        <v>46076.61179409723</v>
       </c>
     </row>
     <row r="694">
@@ -24033,7 +24033,7 @@
         <v>2.5</v>
       </c>
       <c r="H694" s="2" t="n">
-        <v>46065.61179409815</v>
+        <v>46065.61179409723</v>
       </c>
     </row>
     <row r="695">
@@ -24067,7 +24067,7 @@
         <v>4.62</v>
       </c>
       <c r="H695" s="2" t="n">
-        <v>46076.61179410118</v>
+        <v>46076.61179409723</v>
       </c>
     </row>
     <row r="696">
@@ -24101,7 +24101,7 @@
         <v>2.35</v>
       </c>
       <c r="H696" s="2" t="n">
-        <v>46068.61179410419</v>
+        <v>46068.61179410879</v>
       </c>
     </row>
     <row r="697">
@@ -24135,7 +24135,7 @@
         <v>4.2</v>
       </c>
       <c r="H697" s="2" t="n">
-        <v>46088.61179410746</v>
+        <v>46088.61179410879</v>
       </c>
     </row>
     <row r="698">
@@ -24169,7 +24169,7 @@
         <v>3.12</v>
       </c>
       <c r="H698" s="2" t="n">
-        <v>46079.61179411066</v>
+        <v>46079.61179410879</v>
       </c>
     </row>
     <row r="699">
@@ -24203,7 +24203,7 @@
         <v>3.92</v>
       </c>
       <c r="H699" s="2" t="n">
-        <v>46075.61179411387</v>
+        <v>46075.61179410879</v>
       </c>
     </row>
     <row r="700">
@@ -24237,7 +24237,7 @@
         <v>1.09</v>
       </c>
       <c r="H700" s="2" t="n">
-        <v>46078.61179411702</v>
+        <v>46078.61179412037</v>
       </c>
     </row>
     <row r="701">
@@ -24271,7 +24271,1707 @@
         <v>2.37</v>
       </c>
       <c r="H701" s="2" t="n">
-        <v>46082.6117941203</v>
+        <v>46082.61179412037</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>35aa2688-4610-4dac-8329-49519fb81a39</t>
+        </is>
+      </c>
+      <c r="B702" t="n">
+        <v>95</v>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F702" t="n">
+        <v>112.71</v>
+      </c>
+      <c r="G702" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H702" s="2" t="n">
+        <v>46082.63651467322</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>5b89f551-babc-4982-8875-556751dc288e</t>
+        </is>
+      </c>
+      <c r="B703" t="n">
+        <v>95</v>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F703" t="n">
+        <v>143.15</v>
+      </c>
+      <c r="G703" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H703" s="2" t="n">
+        <v>46089.63651467743</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>5786831b-8a66-44f2-aa16-e7492c82926b</t>
+        </is>
+      </c>
+      <c r="B704" t="n">
+        <v>95</v>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F704" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="G704" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H704" s="2" t="n">
+        <v>46093.63651468074</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>8fdb9fdb-afef-437f-a2cd-08565e8a0480</t>
+        </is>
+      </c>
+      <c r="B705" t="n">
+        <v>95</v>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F705" t="n">
+        <v>239.57</v>
+      </c>
+      <c r="G705" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H705" s="2" t="n">
+        <v>46075.63651468396</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>b35949de-3dfb-4ba6-821e-ea840ebe883a</t>
+        </is>
+      </c>
+      <c r="B706" t="n">
+        <v>95</v>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F706" t="n">
+        <v>152.99</v>
+      </c>
+      <c r="G706" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H706" s="2" t="n">
+        <v>46092.6365146868</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>f7c6ebe6-e509-497f-9cbe-7b705b7272b5</t>
+        </is>
+      </c>
+      <c r="B707" t="n">
+        <v>95</v>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F707" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="G707" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H707" s="2" t="n">
+        <v>46083.63651468976</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>f79ad350-2ad4-495a-9723-309aa26a9a56</t>
+        </is>
+      </c>
+      <c r="B708" t="n">
+        <v>95</v>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F708" t="n">
+        <v>53.08</v>
+      </c>
+      <c r="G708" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H708" s="2" t="n">
+        <v>46087.63651469274</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>6cfc439b-196e-4a2d-a26f-27d348483dd3</t>
+        </is>
+      </c>
+      <c r="B709" t="n">
+        <v>95</v>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F709" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="G709" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H709" s="2" t="n">
+        <v>46068.6365146957</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>ade4dfbf-d42b-40f7-99a5-a1d5b733f301</t>
+        </is>
+      </c>
+      <c r="B710" t="n">
+        <v>95</v>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F710" t="n">
+        <v>234.08</v>
+      </c>
+      <c r="G710" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H710" s="2" t="n">
+        <v>46067.63651469882</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>7eb34511-5578-4724-b6fa-49fb9727f7f8</t>
+        </is>
+      </c>
+      <c r="B711" t="n">
+        <v>95</v>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F711" t="n">
+        <v>142.47</v>
+      </c>
+      <c r="G711" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H711" s="2" t="n">
+        <v>46075.63651470173</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>e8d84f66-4034-44c4-8d21-6de99927041d</t>
+        </is>
+      </c>
+      <c r="B712" t="n">
+        <v>95</v>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F712" t="n">
+        <v>193.06</v>
+      </c>
+      <c r="G712" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H712" s="2" t="n">
+        <v>46075.63651470489</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2a1bc2c5-77cd-4203-9045-38933e5efd81</t>
+        </is>
+      </c>
+      <c r="B713" t="n">
+        <v>95</v>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F713" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="G713" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H713" s="2" t="n">
+        <v>46066.63651470779</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>01677c6b-8d51-43d1-863d-0619175f13fa</t>
+        </is>
+      </c>
+      <c r="B714" t="n">
+        <v>95</v>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F714" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="G714" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H714" s="2" t="n">
+        <v>46072.63651471069</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>628714d0-ef00-4a6b-a2d0-30c82040a3e4</t>
+        </is>
+      </c>
+      <c r="B715" t="n">
+        <v>95</v>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F715" t="n">
+        <v>166.18</v>
+      </c>
+      <c r="G715" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H715" s="2" t="n">
+        <v>46067.6365147136</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>f7a5e412-964d-47c8-b1bd-9d705a0018c6</t>
+        </is>
+      </c>
+      <c r="B716" t="n">
+        <v>95</v>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F716" t="n">
+        <v>77.44</v>
+      </c>
+      <c r="G716" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="H716" s="2" t="n">
+        <v>46090.63651471637</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>a5baf645-5c6a-47dd-be45-4b96104ee25b</t>
+        </is>
+      </c>
+      <c r="B717" t="n">
+        <v>95</v>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F717" t="n">
+        <v>496.92</v>
+      </c>
+      <c r="G717" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="H717" s="2" t="n">
+        <v>46074.6365147192</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>d9ba2d5c-e81d-4dda-959f-8da6cf67c3e2</t>
+        </is>
+      </c>
+      <c r="B718" t="n">
+        <v>95</v>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F718" t="n">
+        <v>346.29</v>
+      </c>
+      <c r="G718" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="H718" s="2" t="n">
+        <v>46094.63651472214</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>ad575945-0ffb-4bcc-8d2b-98ee38a0753e</t>
+        </is>
+      </c>
+      <c r="B719" t="n">
+        <v>95</v>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F719" t="n">
+        <v>275.34</v>
+      </c>
+      <c r="G719" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H719" s="2" t="n">
+        <v>46069.63651472513</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>6eb031f5-7aad-44b8-8e09-3111ccad9cd5</t>
+        </is>
+      </c>
+      <c r="B720" t="n">
+        <v>95</v>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F720" t="n">
+        <v>286.29</v>
+      </c>
+      <c r="G720" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H720" s="2" t="n">
+        <v>46085.63651472817</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>52f04c7f-62b1-4b1f-bcb1-6cdfd5196825</t>
+        </is>
+      </c>
+      <c r="B721" t="n">
+        <v>95</v>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F721" t="n">
+        <v>285.88</v>
+      </c>
+      <c r="G721" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H721" s="2" t="n">
+        <v>46083.63651473104</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>20cf546d-c0cd-4544-bc1f-5141b26749ef</t>
+        </is>
+      </c>
+      <c r="B722" t="n">
+        <v>95</v>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F722" t="n">
+        <v>476.54</v>
+      </c>
+      <c r="G722" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="H722" s="2" t="n">
+        <v>46081.63651473385</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>3332f984-c78d-43c4-a9f6-d8ccd68f975b</t>
+        </is>
+      </c>
+      <c r="B723" t="n">
+        <v>95</v>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F723" t="n">
+        <v>315.18</v>
+      </c>
+      <c r="G723" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H723" s="2" t="n">
+        <v>46084.63651473675</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>c75a6c59-e493-4467-b660-dad12e3401ac</t>
+        </is>
+      </c>
+      <c r="B724" t="n">
+        <v>95</v>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F724" t="n">
+        <v>263.87</v>
+      </c>
+      <c r="G724" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H724" s="2" t="n">
+        <v>46086.63651473955</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>e940d1e4-0acf-4d9e-b5e1-d8b10596b24a</t>
+        </is>
+      </c>
+      <c r="B725" t="n">
+        <v>95</v>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F725" t="n">
+        <v>213.52</v>
+      </c>
+      <c r="G725" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H725" s="2" t="n">
+        <v>46088.63651474248</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>c9028daa-5f41-4c46-b87b-9cc5609f5b31</t>
+        </is>
+      </c>
+      <c r="B726" t="n">
+        <v>95</v>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F726" t="n">
+        <v>349.72</v>
+      </c>
+      <c r="G726" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H726" s="2" t="n">
+        <v>46079.63651474538</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>079105b9-cef6-453e-88f8-2bf4491273ce</t>
+        </is>
+      </c>
+      <c r="B727" t="n">
+        <v>95</v>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F727" t="n">
+        <v>199.8</v>
+      </c>
+      <c r="G727" t="n">
+        <v>2</v>
+      </c>
+      <c r="H727" s="2" t="n">
+        <v>46065.63651474838</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>facfe198-cdd9-4503-829e-39fa06644086</t>
+        </is>
+      </c>
+      <c r="B728" t="n">
+        <v>95</v>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F728" t="n">
+        <v>198.22</v>
+      </c>
+      <c r="G728" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H728" s="2" t="n">
+        <v>46086.6365147514</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>8760a690-8a67-4ee4-bcbd-52aa87117a45</t>
+        </is>
+      </c>
+      <c r="B729" t="n">
+        <v>95</v>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F729" t="n">
+        <v>201.55</v>
+      </c>
+      <c r="G729" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H729" s="2" t="n">
+        <v>46087.63651475419</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>f574277e-a113-41ef-9013-10321d51cf7c</t>
+        </is>
+      </c>
+      <c r="B730" t="n">
+        <v>95</v>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F730" t="n">
+        <v>277.58</v>
+      </c>
+      <c r="G730" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="H730" s="2" t="n">
+        <v>46070.63651475698</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>c537c210-f6ad-4224-bdd3-4a8f57e1f605</t>
+        </is>
+      </c>
+      <c r="B731" t="n">
+        <v>95</v>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F731" t="n">
+        <v>158.43</v>
+      </c>
+      <c r="G731" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H731" s="2" t="n">
+        <v>46092.63651476</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>ad5afe57-d10d-4e1d-9073-4b427096c69e</t>
+        </is>
+      </c>
+      <c r="B732" t="n">
+        <v>95</v>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F732" t="n">
+        <v>217.58</v>
+      </c>
+      <c r="G732" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H732" s="2" t="n">
+        <v>46086.63651476288</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>298f2a77-ae3d-4bd9-a39f-1fa781eb3261</t>
+        </is>
+      </c>
+      <c r="B733" t="n">
+        <v>95</v>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F733" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="G733" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H733" s="2" t="n">
+        <v>46083.63651476572</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>eb60a40c-d999-428e-b81a-3c9737a07930</t>
+        </is>
+      </c>
+      <c r="B734" t="n">
+        <v>95</v>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F734" t="n">
+        <v>186.15</v>
+      </c>
+      <c r="G734" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H734" s="2" t="n">
+        <v>46081.63651476859</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>fe2f7ddf-c47f-4b59-85d9-cc1be9488a26</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>95</v>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F735" t="n">
+        <v>382.75</v>
+      </c>
+      <c r="G735" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="H735" s="2" t="n">
+        <v>46083.63651477166</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>81e9aba8-d0af-4dbc-af74-e25b3e84817e</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>95</v>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F736" t="n">
+        <v>490.74</v>
+      </c>
+      <c r="G736" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="H736" s="2" t="n">
+        <v>46093.63651477442</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>ece9f276-5821-4901-b49d-2f942b3471f8</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>95</v>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F737" t="n">
+        <v>54.53</v>
+      </c>
+      <c r="G737" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H737" s="2" t="n">
+        <v>46083.63651477727</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>5d7787cb-7f5f-45f1-942d-a99b6564d550</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>95</v>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F738" t="n">
+        <v>150.6</v>
+      </c>
+      <c r="G738" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="H738" s="2" t="n">
+        <v>46087.63651478009</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>fec6a825-caf6-44df-bfce-d992e57deaf6</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>95</v>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F739" t="n">
+        <v>412.49</v>
+      </c>
+      <c r="G739" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="H739" s="2" t="n">
+        <v>46076.63651478312</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>dde62b51-867f-4cae-b258-d99052e21b62</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>95</v>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F740" t="n">
+        <v>333.61</v>
+      </c>
+      <c r="G740" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="H740" s="2" t="n">
+        <v>46088.63651478589</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>06d2f2d5-9c46-49eb-819c-6fa3c6cac829</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>95</v>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F741" t="n">
+        <v>55.77</v>
+      </c>
+      <c r="G741" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H741" s="2" t="n">
+        <v>46073.63651478873</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>cf047088-b027-4b5e-ba75-59a492210609</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>95</v>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F742" t="n">
+        <v>288.55</v>
+      </c>
+      <c r="G742" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="H742" s="2" t="n">
+        <v>46083.63651479153</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>0a09acdd-3439-413f-9023-581788539b59</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>95</v>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F743" t="n">
+        <v>81.51000000000001</v>
+      </c>
+      <c r="G743" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H743" s="2" t="n">
+        <v>46078.63651479437</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>41d345fe-73b0-4957-979b-7e6d1892a6dc</t>
+        </is>
+      </c>
+      <c r="B744" t="n">
+        <v>95</v>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F744" t="n">
+        <v>257.42</v>
+      </c>
+      <c r="G744" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="H744" s="2" t="n">
+        <v>46091.6365147976</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>71b3478f-44d1-4729-aef1-4795e2514d29</t>
+        </is>
+      </c>
+      <c r="B745" t="n">
+        <v>95</v>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F745" t="n">
+        <v>84.76000000000001</v>
+      </c>
+      <c r="G745" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H745" s="2" t="n">
+        <v>46065.6365148004</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>c3679b77-77d2-45f1-8375-d8741acce97a</t>
+        </is>
+      </c>
+      <c r="B746" t="n">
+        <v>95</v>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F746" t="n">
+        <v>255.16</v>
+      </c>
+      <c r="G746" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H746" s="2" t="n">
+        <v>46090.63651480322</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>e1ad3d75-e7fa-4904-823d-a69a086b704e</t>
+        </is>
+      </c>
+      <c r="B747" t="n">
+        <v>95</v>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F747" t="n">
+        <v>476.93</v>
+      </c>
+      <c r="G747" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="H747" s="2" t="n">
+        <v>46069.63651480608</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>bbf6d2c2-5c02-474e-acce-1fa06ac68ada</t>
+        </is>
+      </c>
+      <c r="B748" t="n">
+        <v>95</v>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F748" t="n">
+        <v>147.81</v>
+      </c>
+      <c r="G748" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H748" s="2" t="n">
+        <v>46077.636514809</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>e1efef48-47b6-4a2e-9fad-571b4cab21ea</t>
+        </is>
+      </c>
+      <c r="B749" t="n">
+        <v>95</v>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F749" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="G749" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H749" s="2" t="n">
+        <v>46077.63651481193</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>1f18f7f9-09ea-4e33-835d-5889fb7739f4</t>
+        </is>
+      </c>
+      <c r="B750" t="n">
+        <v>95</v>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F750" t="n">
+        <v>307.45</v>
+      </c>
+      <c r="G750" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="H750" s="2" t="n">
+        <v>46077.6365148147</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>c571bdcd-200b-4cda-8f28-8c1f4e4ec856</t>
+        </is>
+      </c>
+      <c r="B751" t="n">
+        <v>95</v>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F751" t="n">
+        <v>396.57</v>
+      </c>
+      <c r="G751" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="H751" s="2" t="n">
+        <v>46077.63651481755</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H751"/>
+  <dimension ref="A1:H801"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24305,7 +24305,7 @@
         <v>1.13</v>
       </c>
       <c r="H702" s="2" t="n">
-        <v>46082.63651467322</v>
+        <v>46082.63651467593</v>
       </c>
     </row>
     <row r="703">
@@ -24339,7 +24339,7 @@
         <v>1.43</v>
       </c>
       <c r="H703" s="2" t="n">
-        <v>46089.63651467743</v>
+        <v>46089.63651467593</v>
       </c>
     </row>
     <row r="704">
@@ -24373,7 +24373,7 @@
         <v>0.48</v>
       </c>
       <c r="H704" s="2" t="n">
-        <v>46093.63651468074</v>
+        <v>46093.63651467593</v>
       </c>
     </row>
     <row r="705">
@@ -24407,7 +24407,7 @@
         <v>2.4</v>
       </c>
       <c r="H705" s="2" t="n">
-        <v>46075.63651468396</v>
+        <v>46075.6365146875</v>
       </c>
     </row>
     <row r="706">
@@ -24441,7 +24441,7 @@
         <v>1.53</v>
       </c>
       <c r="H706" s="2" t="n">
-        <v>46092.6365146868</v>
+        <v>46092.6365146875</v>
       </c>
     </row>
     <row r="707">
@@ -24475,7 +24475,7 @@
         <v>0.25</v>
       </c>
       <c r="H707" s="2" t="n">
-        <v>46083.63651468976</v>
+        <v>46083.6365146875</v>
       </c>
     </row>
     <row r="708">
@@ -24509,7 +24509,7 @@
         <v>0.53</v>
       </c>
       <c r="H708" s="2" t="n">
-        <v>46087.63651469274</v>
+        <v>46087.6365146875</v>
       </c>
     </row>
     <row r="709">
@@ -24543,7 +24543,7 @@
         <v>0.18</v>
       </c>
       <c r="H709" s="2" t="n">
-        <v>46068.6365146957</v>
+        <v>46068.63651469907</v>
       </c>
     </row>
     <row r="710">
@@ -24577,7 +24577,7 @@
         <v>2.34</v>
       </c>
       <c r="H710" s="2" t="n">
-        <v>46067.63651469882</v>
+        <v>46067.63651469907</v>
       </c>
     </row>
     <row r="711">
@@ -24611,7 +24611,7 @@
         <v>1.42</v>
       </c>
       <c r="H711" s="2" t="n">
-        <v>46075.63651470173</v>
+        <v>46075.63651469907</v>
       </c>
     </row>
     <row r="712">
@@ -24645,7 +24645,7 @@
         <v>1.93</v>
       </c>
       <c r="H712" s="2" t="n">
-        <v>46075.63651470489</v>
+        <v>46075.63651471065</v>
       </c>
     </row>
     <row r="713">
@@ -24679,7 +24679,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="H713" s="2" t="n">
-        <v>46066.63651470779</v>
+        <v>46066.63651471065</v>
       </c>
     </row>
     <row r="714">
@@ -24713,7 +24713,7 @@
         <v>0.15</v>
       </c>
       <c r="H714" s="2" t="n">
-        <v>46072.63651471069</v>
+        <v>46072.63651471065</v>
       </c>
     </row>
     <row r="715">
@@ -24747,7 +24747,7 @@
         <v>1.66</v>
       </c>
       <c r="H715" s="2" t="n">
-        <v>46067.6365147136</v>
+        <v>46067.63651471065</v>
       </c>
     </row>
     <row r="716">
@@ -24781,7 +24781,7 @@
         <v>0.77</v>
       </c>
       <c r="H716" s="2" t="n">
-        <v>46090.63651471637</v>
+        <v>46090.63651471065</v>
       </c>
     </row>
     <row r="717">
@@ -24815,7 +24815,7 @@
         <v>4.97</v>
       </c>
       <c r="H717" s="2" t="n">
-        <v>46074.6365147192</v>
+        <v>46074.63651472222</v>
       </c>
     </row>
     <row r="718">
@@ -24849,7 +24849,7 @@
         <v>3.46</v>
       </c>
       <c r="H718" s="2" t="n">
-        <v>46094.63651472214</v>
+        <v>46094.63651472222</v>
       </c>
     </row>
     <row r="719">
@@ -24883,7 +24883,7 @@
         <v>2.75</v>
       </c>
       <c r="H719" s="2" t="n">
-        <v>46069.63651472513</v>
+        <v>46069.63651472222</v>
       </c>
     </row>
     <row r="720">
@@ -24917,7 +24917,7 @@
         <v>2.86</v>
       </c>
       <c r="H720" s="2" t="n">
-        <v>46085.63651472817</v>
+        <v>46085.63651473379</v>
       </c>
     </row>
     <row r="721">
@@ -24951,7 +24951,7 @@
         <v>2.86</v>
       </c>
       <c r="H721" s="2" t="n">
-        <v>46083.63651473104</v>
+        <v>46083.63651473379</v>
       </c>
     </row>
     <row r="722">
@@ -24985,7 +24985,7 @@
         <v>4.77</v>
       </c>
       <c r="H722" s="2" t="n">
-        <v>46081.63651473385</v>
+        <v>46081.63651473379</v>
       </c>
     </row>
     <row r="723">
@@ -25019,7 +25019,7 @@
         <v>3.15</v>
       </c>
       <c r="H723" s="2" t="n">
-        <v>46084.63651473675</v>
+        <v>46084.63651473379</v>
       </c>
     </row>
     <row r="724">
@@ -25053,7 +25053,7 @@
         <v>2.64</v>
       </c>
       <c r="H724" s="2" t="n">
-        <v>46086.63651473955</v>
+        <v>46086.63651473379</v>
       </c>
     </row>
     <row r="725">
@@ -25087,7 +25087,7 @@
         <v>2.14</v>
       </c>
       <c r="H725" s="2" t="n">
-        <v>46088.63651474248</v>
+        <v>46088.63651474537</v>
       </c>
     </row>
     <row r="726">
@@ -25121,7 +25121,7 @@
         <v>3.5</v>
       </c>
       <c r="H726" s="2" t="n">
-        <v>46079.63651474538</v>
+        <v>46079.63651474537</v>
       </c>
     </row>
     <row r="727">
@@ -25155,7 +25155,7 @@
         <v>2</v>
       </c>
       <c r="H727" s="2" t="n">
-        <v>46065.63651474838</v>
+        <v>46065.63651474537</v>
       </c>
     </row>
     <row r="728">
@@ -25189,7 +25189,7 @@
         <v>1.98</v>
       </c>
       <c r="H728" s="2" t="n">
-        <v>46086.6365147514</v>
+        <v>46086.63651475694</v>
       </c>
     </row>
     <row r="729">
@@ -25223,7 +25223,7 @@
         <v>2.02</v>
       </c>
       <c r="H729" s="2" t="n">
-        <v>46087.63651475419</v>
+        <v>46087.63651475694</v>
       </c>
     </row>
     <row r="730">
@@ -25257,7 +25257,7 @@
         <v>2.78</v>
       </c>
       <c r="H730" s="2" t="n">
-        <v>46070.63651475698</v>
+        <v>46070.63651475694</v>
       </c>
     </row>
     <row r="731">
@@ -25291,7 +25291,7 @@
         <v>1.58</v>
       </c>
       <c r="H731" s="2" t="n">
-        <v>46092.63651476</v>
+        <v>46092.63651475694</v>
       </c>
     </row>
     <row r="732">
@@ -25325,7 +25325,7 @@
         <v>2.18</v>
       </c>
       <c r="H732" s="2" t="n">
-        <v>46086.63651476288</v>
+        <v>46086.63651476852</v>
       </c>
     </row>
     <row r="733">
@@ -25359,7 +25359,7 @@
         <v>0.02</v>
       </c>
       <c r="H733" s="2" t="n">
-        <v>46083.63651476572</v>
+        <v>46083.63651476852</v>
       </c>
     </row>
     <row r="734">
@@ -25393,7 +25393,7 @@
         <v>1.86</v>
       </c>
       <c r="H734" s="2" t="n">
-        <v>46081.63651476859</v>
+        <v>46081.63651476852</v>
       </c>
     </row>
     <row r="735">
@@ -25427,7 +25427,7 @@
         <v>3.83</v>
       </c>
       <c r="H735" s="2" t="n">
-        <v>46083.63651477166</v>
+        <v>46083.63651476852</v>
       </c>
     </row>
     <row r="736">
@@ -25461,7 +25461,7 @@
         <v>4.91</v>
       </c>
       <c r="H736" s="2" t="n">
-        <v>46093.63651477442</v>
+        <v>46093.63651478009</v>
       </c>
     </row>
     <row r="737">
@@ -25495,7 +25495,7 @@
         <v>0.55</v>
       </c>
       <c r="H737" s="2" t="n">
-        <v>46083.63651477727</v>
+        <v>46083.63651478009</v>
       </c>
     </row>
     <row r="738">
@@ -25563,7 +25563,7 @@
         <v>4.12</v>
       </c>
       <c r="H739" s="2" t="n">
-        <v>46076.63651478312</v>
+        <v>46076.63651478009</v>
       </c>
     </row>
     <row r="740">
@@ -25597,7 +25597,7 @@
         <v>3.34</v>
       </c>
       <c r="H740" s="2" t="n">
-        <v>46088.63651478589</v>
+        <v>46088.63651479167</v>
       </c>
     </row>
     <row r="741">
@@ -25631,7 +25631,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="H741" s="2" t="n">
-        <v>46073.63651478873</v>
+        <v>46073.63651479167</v>
       </c>
     </row>
     <row r="742">
@@ -25665,7 +25665,7 @@
         <v>2.89</v>
       </c>
       <c r="H742" s="2" t="n">
-        <v>46083.63651479153</v>
+        <v>46083.63651479167</v>
       </c>
     </row>
     <row r="743">
@@ -25699,7 +25699,7 @@
         <v>0.82</v>
       </c>
       <c r="H743" s="2" t="n">
-        <v>46078.63651479437</v>
+        <v>46078.63651479167</v>
       </c>
     </row>
     <row r="744">
@@ -25733,7 +25733,7 @@
         <v>2.57</v>
       </c>
       <c r="H744" s="2" t="n">
-        <v>46091.6365147976</v>
+        <v>46091.63651480324</v>
       </c>
     </row>
     <row r="745">
@@ -25767,7 +25767,7 @@
         <v>0.85</v>
       </c>
       <c r="H745" s="2" t="n">
-        <v>46065.6365148004</v>
+        <v>46065.63651480324</v>
       </c>
     </row>
     <row r="746">
@@ -25801,7 +25801,7 @@
         <v>2.55</v>
       </c>
       <c r="H746" s="2" t="n">
-        <v>46090.63651480322</v>
+        <v>46090.63651480324</v>
       </c>
     </row>
     <row r="747">
@@ -25835,7 +25835,7 @@
         <v>4.77</v>
       </c>
       <c r="H747" s="2" t="n">
-        <v>46069.63651480608</v>
+        <v>46069.63651480324</v>
       </c>
     </row>
     <row r="748">
@@ -25869,7 +25869,7 @@
         <v>1.48</v>
       </c>
       <c r="H748" s="2" t="n">
-        <v>46077.636514809</v>
+        <v>46077.63651480324</v>
       </c>
     </row>
     <row r="749">
@@ -25903,7 +25903,7 @@
         <v>0.32</v>
       </c>
       <c r="H749" s="2" t="n">
-        <v>46077.63651481193</v>
+        <v>46077.63651481482</v>
       </c>
     </row>
     <row r="750">
@@ -25937,7 +25937,7 @@
         <v>3.07</v>
       </c>
       <c r="H750" s="2" t="n">
-        <v>46077.6365148147</v>
+        <v>46077.63651481482</v>
       </c>
     </row>
     <row r="751">
@@ -25971,7 +25971,1707 @@
         <v>3.97</v>
       </c>
       <c r="H751" s="2" t="n">
-        <v>46077.63651481755</v>
+        <v>46077.63651481482</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>def882b6-def6-42c6-938c-1495d06a3c3c</t>
+        </is>
+      </c>
+      <c r="B752" t="n">
+        <v>95</v>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F752" t="n">
+        <v>362.12</v>
+      </c>
+      <c r="G752" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="H752" s="2" t="n">
+        <v>46074.67981566994</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>c92629df-3759-41d5-9132-d27d52263f12</t>
+        </is>
+      </c>
+      <c r="B753" t="n">
+        <v>95</v>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F753" t="n">
+        <v>55.97</v>
+      </c>
+      <c r="G753" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H753" s="2" t="n">
+        <v>46089.67981567408</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>948c1d3d-efdb-40fc-bf6e-f4b39a551456</t>
+        </is>
+      </c>
+      <c r="B754" t="n">
+        <v>95</v>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F754" t="n">
+        <v>413.87</v>
+      </c>
+      <c r="G754" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H754" s="2" t="n">
+        <v>46073.67981567739</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>061a9842-e334-492e-9e57-10f6a9533380</t>
+        </is>
+      </c>
+      <c r="B755" t="n">
+        <v>95</v>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F755" t="n">
+        <v>445.02</v>
+      </c>
+      <c r="G755" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="H755" s="2" t="n">
+        <v>46067.67981568087</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>e39f1e89-dc85-4722-a75c-334d615ebb78</t>
+        </is>
+      </c>
+      <c r="B756" t="n">
+        <v>95</v>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F756" t="n">
+        <v>41.65</v>
+      </c>
+      <c r="G756" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H756" s="2" t="n">
+        <v>46069.67981568407</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>17229131-e051-4a61-b82a-9f83bc45863e</t>
+        </is>
+      </c>
+      <c r="B757" t="n">
+        <v>95</v>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F757" t="n">
+        <v>100.56</v>
+      </c>
+      <c r="G757" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="H757" s="2" t="n">
+        <v>46074.67981568717</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>da2964a6-47c4-40ed-8ab2-5d7da5806f08</t>
+        </is>
+      </c>
+      <c r="B758" t="n">
+        <v>95</v>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F758" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="G758" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H758" s="2" t="n">
+        <v>46066.67981569034</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>dd9508fa-da1a-4b66-b2f7-dfb81cc98eaf</t>
+        </is>
+      </c>
+      <c r="B759" t="n">
+        <v>95</v>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F759" t="n">
+        <v>129.95</v>
+      </c>
+      <c r="G759" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H759" s="2" t="n">
+        <v>46074.67981569363</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>d24cf199-935a-44d4-ada6-a3a992c8c71c</t>
+        </is>
+      </c>
+      <c r="B760" t="n">
+        <v>95</v>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F760" t="n">
+        <v>451.04</v>
+      </c>
+      <c r="G760" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="H760" s="2" t="n">
+        <v>46088.67981569669</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>1d1ef314-52f0-4082-9862-13108c87437b</t>
+        </is>
+      </c>
+      <c r="B761" t="n">
+        <v>95</v>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F761" t="n">
+        <v>262.37</v>
+      </c>
+      <c r="G761" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H761" s="2" t="n">
+        <v>46082.67981569986</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>4ae48d55-eb7f-4c10-a390-9dd89386963c</t>
+        </is>
+      </c>
+      <c r="B762" t="n">
+        <v>95</v>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F762" t="n">
+        <v>257.68</v>
+      </c>
+      <c r="G762" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H762" s="2" t="n">
+        <v>46068.67981570315</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>b9fcfad8-fdeb-457a-a843-8df49df72a02</t>
+        </is>
+      </c>
+      <c r="B763" t="n">
+        <v>95</v>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F763" t="n">
+        <v>206.98</v>
+      </c>
+      <c r="G763" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="H763" s="2" t="n">
+        <v>46074.67981570633</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>bcd1dd37-a81a-4eb5-80a3-554f841982a2</t>
+        </is>
+      </c>
+      <c r="B764" t="n">
+        <v>95</v>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F764" t="n">
+        <v>499.99</v>
+      </c>
+      <c r="G764" t="n">
+        <v>5</v>
+      </c>
+      <c r="H764" s="2" t="n">
+        <v>46083.67981570937</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>53ff8292-39e0-42be-b2cd-674b6c8237c0</t>
+        </is>
+      </c>
+      <c r="B765" t="n">
+        <v>95</v>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F765" t="n">
+        <v>414.84</v>
+      </c>
+      <c r="G765" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="H765" s="2" t="n">
+        <v>46078.67981571238</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>ee5bd2f6-4903-4311-bb1d-bfc80a97cc86</t>
+        </is>
+      </c>
+      <c r="B766" t="n">
+        <v>95</v>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F766" t="n">
+        <v>299.5</v>
+      </c>
+      <c r="G766" t="n">
+        <v>3</v>
+      </c>
+      <c r="H766" s="2" t="n">
+        <v>46091.67981571573</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>e683cdb2-169d-427f-9988-a1882ec49376</t>
+        </is>
+      </c>
+      <c r="B767" t="n">
+        <v>95</v>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F767" t="n">
+        <v>442.71</v>
+      </c>
+      <c r="G767" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="H767" s="2" t="n">
+        <v>46088.67981571893</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>ee252fdb-4dab-44ae-a49d-a9f0ecfeafa0</t>
+        </is>
+      </c>
+      <c r="B768" t="n">
+        <v>95</v>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F768" t="n">
+        <v>166.32</v>
+      </c>
+      <c r="G768" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H768" s="2" t="n">
+        <v>46091.67981572195</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>48f1e553-b8bf-4462-833e-a9143dd2553c</t>
+        </is>
+      </c>
+      <c r="B769" t="n">
+        <v>95</v>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F769" t="n">
+        <v>278.08</v>
+      </c>
+      <c r="G769" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="H769" s="2" t="n">
+        <v>46078.67981572494</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>a5121bc6-b739-4ca2-8f6f-35d6f2615db4</t>
+        </is>
+      </c>
+      <c r="B770" t="n">
+        <v>95</v>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F770" t="n">
+        <v>38.98</v>
+      </c>
+      <c r="G770" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H770" s="2" t="n">
+        <v>46069.67981572814</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>eb1f00ff-1fe1-4943-9f2f-d5743c621a19</t>
+        </is>
+      </c>
+      <c r="B771" t="n">
+        <v>95</v>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F771" t="n">
+        <v>230.09</v>
+      </c>
+      <c r="G771" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H771" s="2" t="n">
+        <v>46071.67981573135</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>ec102bf8-b99f-42c4-a6ab-1216097b7d19</t>
+        </is>
+      </c>
+      <c r="B772" t="n">
+        <v>95</v>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F772" t="n">
+        <v>422.57</v>
+      </c>
+      <c r="G772" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="H772" s="2" t="n">
+        <v>46068.67981573454</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>0173642e-3ca4-45f9-b7b3-e7a8252f38cd</t>
+        </is>
+      </c>
+      <c r="B773" t="n">
+        <v>95</v>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F773" t="n">
+        <v>240.54</v>
+      </c>
+      <c r="G773" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="H773" s="2" t="n">
+        <v>46070.67981573772</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>8183ea22-9000-4f57-b3da-a02cebc5b2ea</t>
+        </is>
+      </c>
+      <c r="B774" t="n">
+        <v>95</v>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F774" t="n">
+        <v>444.18</v>
+      </c>
+      <c r="G774" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="H774" s="2" t="n">
+        <v>46077.6798157408</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>639a7382-e74b-47f4-b1f7-d3f037edde05</t>
+        </is>
+      </c>
+      <c r="B775" t="n">
+        <v>95</v>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F775" t="n">
+        <v>74.44</v>
+      </c>
+      <c r="G775" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H775" s="2" t="n">
+        <v>46073.67981574377</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>d8006394-103b-4106-9a7c-fce11b677073</t>
+        </is>
+      </c>
+      <c r="B776" t="n">
+        <v>95</v>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F776" t="n">
+        <v>487.74</v>
+      </c>
+      <c r="G776" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="H776" s="2" t="n">
+        <v>46085.67981574679</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>88f6f350-56b4-4456-b412-2b48c8714cf3</t>
+        </is>
+      </c>
+      <c r="B777" t="n">
+        <v>95</v>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F777" t="n">
+        <v>495.84</v>
+      </c>
+      <c r="G777" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="H777" s="2" t="n">
+        <v>46072.6798157502</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>e4889755-bad3-44fd-a814-2ba395fff6ef</t>
+        </is>
+      </c>
+      <c r="B778" t="n">
+        <v>95</v>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F778" t="n">
+        <v>274.53</v>
+      </c>
+      <c r="G778" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H778" s="2" t="n">
+        <v>46086.6798157534</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>429319d8-196b-4125-af5c-a90afd03818d</t>
+        </is>
+      </c>
+      <c r="B779" t="n">
+        <v>95</v>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F779" t="n">
+        <v>207.37</v>
+      </c>
+      <c r="G779" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="H779" s="2" t="n">
+        <v>46080.67981575647</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>aeaef3db-23e4-4af5-9d22-85653f916edb</t>
+        </is>
+      </c>
+      <c r="B780" t="n">
+        <v>95</v>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F780" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="G780" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H780" s="2" t="n">
+        <v>46066.67981575961</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>67483aeb-f661-433a-8026-dc1a19d04a40</t>
+        </is>
+      </c>
+      <c r="B781" t="n">
+        <v>95</v>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F781" t="n">
+        <v>408.01</v>
+      </c>
+      <c r="G781" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="H781" s="2" t="n">
+        <v>46090.67981576294</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>95d456b7-4823-4913-970a-8967073748d1</t>
+        </is>
+      </c>
+      <c r="B782" t="n">
+        <v>95</v>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F782" t="n">
+        <v>475.61</v>
+      </c>
+      <c r="G782" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="H782" s="2" t="n">
+        <v>46090.6798157663</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>0418ae8f-6703-4a6c-b83e-b0fe9fd037e4</t>
+        </is>
+      </c>
+      <c r="B783" t="n">
+        <v>95</v>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F783" t="n">
+        <v>265.15</v>
+      </c>
+      <c r="G783" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="H783" s="2" t="n">
+        <v>46074.67981576944</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>5b41e7cc-006e-4c63-8a1d-85dfff1cc10e</t>
+        </is>
+      </c>
+      <c r="B784" t="n">
+        <v>95</v>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F784" t="n">
+        <v>118</v>
+      </c>
+      <c r="G784" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H784" s="2" t="n">
+        <v>46089.67981577278</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>04395110-3b3d-4b75-8f8b-6502f948c986</t>
+        </is>
+      </c>
+      <c r="B785" t="n">
+        <v>95</v>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F785" t="n">
+        <v>53.98</v>
+      </c>
+      <c r="G785" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H785" s="2" t="n">
+        <v>46083.67981577582</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>784d086b-aa3b-4aa0-8ad9-4d8f0e1c4d5a</t>
+        </is>
+      </c>
+      <c r="B786" t="n">
+        <v>95</v>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F786" t="n">
+        <v>186.89</v>
+      </c>
+      <c r="G786" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H786" s="2" t="n">
+        <v>46067.67981577884</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>9d772244-7f72-4a63-93d9-b46f6536dfbd</t>
+        </is>
+      </c>
+      <c r="B787" t="n">
+        <v>95</v>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F787" t="n">
+        <v>93.45999999999999</v>
+      </c>
+      <c r="G787" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H787" s="2" t="n">
+        <v>46081.67981578207</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>1752cca5-ce66-48aa-8ad0-b583c45e3cf4</t>
+        </is>
+      </c>
+      <c r="B788" t="n">
+        <v>95</v>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F788" t="n">
+        <v>218.9</v>
+      </c>
+      <c r="G788" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="H788" s="2" t="n">
+        <v>46070.67981578535</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>92a43823-016b-4402-9f11-123ef62af4f9</t>
+        </is>
+      </c>
+      <c r="B789" t="n">
+        <v>95</v>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F789" t="n">
+        <v>286.13</v>
+      </c>
+      <c r="G789" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H789" s="2" t="n">
+        <v>46080.67981578839</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>d03a8487-3061-4bc7-b510-eff9d3910d1d</t>
+        </is>
+      </c>
+      <c r="B790" t="n">
+        <v>95</v>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F790" t="n">
+        <v>432.22</v>
+      </c>
+      <c r="G790" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="H790" s="2" t="n">
+        <v>46088.6798157914</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>a06ded3f-56ec-457e-aa98-750bbd584cf7</t>
+        </is>
+      </c>
+      <c r="B791" t="n">
+        <v>95</v>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F791" t="n">
+        <v>357.62</v>
+      </c>
+      <c r="G791" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="H791" s="2" t="n">
+        <v>46077.67981579489</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>fa8bc42b-413a-444f-953c-1e8e954d680c</t>
+        </is>
+      </c>
+      <c r="B792" t="n">
+        <v>95</v>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F792" t="n">
+        <v>259.9</v>
+      </c>
+      <c r="G792" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H792" s="2" t="n">
+        <v>46085.67981579797</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2a30d9c7-fe48-47a5-b02c-62036ea6212a</t>
+        </is>
+      </c>
+      <c r="B793" t="n">
+        <v>95</v>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F793" t="n">
+        <v>240.7</v>
+      </c>
+      <c r="G793" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="H793" s="2" t="n">
+        <v>46091.679815801</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>dc2dcf9c-646c-4875-800f-75faf2c477af</t>
+        </is>
+      </c>
+      <c r="B794" t="n">
+        <v>95</v>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F794" t="n">
+        <v>245.89</v>
+      </c>
+      <c r="G794" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H794" s="2" t="n">
+        <v>46092.67981580406</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>3a17ede1-b206-455b-9cf9-2c400522dcb6</t>
+        </is>
+      </c>
+      <c r="B795" t="n">
+        <v>95</v>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F795" t="n">
+        <v>323.31</v>
+      </c>
+      <c r="G795" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="H795" s="2" t="n">
+        <v>46082.67981580735</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>21b19f56-3bea-46b9-af6a-58e810292df8</t>
+        </is>
+      </c>
+      <c r="B796" t="n">
+        <v>95</v>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F796" t="n">
+        <v>495.05</v>
+      </c>
+      <c r="G796" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="H796" s="2" t="n">
+        <v>46066.67981581039</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>98621bb2-d51c-4362-83d6-8fb319ee80da</t>
+        </is>
+      </c>
+      <c r="B797" t="n">
+        <v>95</v>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F797" t="n">
+        <v>411.03</v>
+      </c>
+      <c r="G797" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="H797" s="2" t="n">
+        <v>46094.67981581359</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>7b041b20-4548-4d01-9dea-f30c710ef3da</t>
+        </is>
+      </c>
+      <c r="B798" t="n">
+        <v>95</v>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F798" t="n">
+        <v>421.5</v>
+      </c>
+      <c r="G798" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="H798" s="2" t="n">
+        <v>46090.67981581675</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>559699cf-6ee3-4045-a124-0f566ce5a841</t>
+        </is>
+      </c>
+      <c r="B799" t="n">
+        <v>95</v>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F799" t="n">
+        <v>114.27</v>
+      </c>
+      <c r="G799" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H799" s="2" t="n">
+        <v>46071.67981582</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>b84a2a61-3d0c-4680-b66b-e827f4dd39de</t>
+        </is>
+      </c>
+      <c r="B800" t="n">
+        <v>95</v>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F800" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="G800" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H800" s="2" t="n">
+        <v>46074.67981582315</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>ca46c94f-9fa0-4bb3-b7dc-a9726f10abce</t>
+        </is>
+      </c>
+      <c r="B801" t="n">
+        <v>95</v>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F801" t="n">
+        <v>65.81</v>
+      </c>
+      <c r="G801" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H801" s="2" t="n">
+        <v>46089.67981582624</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H801"/>
+  <dimension ref="A1:H851"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26005,7 +26005,7 @@
         <v>3.62</v>
       </c>
       <c r="H752" s="2" t="n">
-        <v>46074.67981566994</v>
+        <v>46074.6798156713</v>
       </c>
     </row>
     <row r="753">
@@ -26039,7 +26039,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="H753" s="2" t="n">
-        <v>46089.67981567408</v>
+        <v>46089.6798156713</v>
       </c>
     </row>
     <row r="754">
@@ -26073,7 +26073,7 @@
         <v>4.14</v>
       </c>
       <c r="H754" s="2" t="n">
-        <v>46073.67981567739</v>
+        <v>46073.67981568287</v>
       </c>
     </row>
     <row r="755">
@@ -26107,7 +26107,7 @@
         <v>4.45</v>
       </c>
       <c r="H755" s="2" t="n">
-        <v>46067.67981568087</v>
+        <v>46067.67981568287</v>
       </c>
     </row>
     <row r="756">
@@ -26141,7 +26141,7 @@
         <v>0.42</v>
       </c>
       <c r="H756" s="2" t="n">
-        <v>46069.67981568407</v>
+        <v>46069.67981568287</v>
       </c>
     </row>
     <row r="757">
@@ -26175,7 +26175,7 @@
         <v>1.01</v>
       </c>
       <c r="H757" s="2" t="n">
-        <v>46074.67981568717</v>
+        <v>46074.67981568287</v>
       </c>
     </row>
     <row r="758">
@@ -26209,7 +26209,7 @@
         <v>0.05</v>
       </c>
       <c r="H758" s="2" t="n">
-        <v>46066.67981569034</v>
+        <v>46066.67981569444</v>
       </c>
     </row>
     <row r="759">
@@ -26243,7 +26243,7 @@
         <v>1.3</v>
       </c>
       <c r="H759" s="2" t="n">
-        <v>46074.67981569363</v>
+        <v>46074.67981569444</v>
       </c>
     </row>
     <row r="760">
@@ -26277,7 +26277,7 @@
         <v>4.51</v>
       </c>
       <c r="H760" s="2" t="n">
-        <v>46088.67981569669</v>
+        <v>46088.67981569444</v>
       </c>
     </row>
     <row r="761">
@@ -26311,7 +26311,7 @@
         <v>2.62</v>
       </c>
       <c r="H761" s="2" t="n">
-        <v>46082.67981569986</v>
+        <v>46082.67981569444</v>
       </c>
     </row>
     <row r="762">
@@ -26345,7 +26345,7 @@
         <v>2.58</v>
       </c>
       <c r="H762" s="2" t="n">
-        <v>46068.67981570315</v>
+        <v>46068.67981570602</v>
       </c>
     </row>
     <row r="763">
@@ -26379,7 +26379,7 @@
         <v>2.07</v>
       </c>
       <c r="H763" s="2" t="n">
-        <v>46074.67981570633</v>
+        <v>46074.67981570602</v>
       </c>
     </row>
     <row r="764">
@@ -26413,7 +26413,7 @@
         <v>5</v>
       </c>
       <c r="H764" s="2" t="n">
-        <v>46083.67981570937</v>
+        <v>46083.67981570602</v>
       </c>
     </row>
     <row r="765">
@@ -26447,7 +26447,7 @@
         <v>4.15</v>
       </c>
       <c r="H765" s="2" t="n">
-        <v>46078.67981571238</v>
+        <v>46078.67981571759</v>
       </c>
     </row>
     <row r="766">
@@ -26481,7 +26481,7 @@
         <v>3</v>
       </c>
       <c r="H766" s="2" t="n">
-        <v>46091.67981571573</v>
+        <v>46091.67981571759</v>
       </c>
     </row>
     <row r="767">
@@ -26515,7 +26515,7 @@
         <v>4.43</v>
       </c>
       <c r="H767" s="2" t="n">
-        <v>46088.67981571893</v>
+        <v>46088.67981571759</v>
       </c>
     </row>
     <row r="768">
@@ -26549,7 +26549,7 @@
         <v>1.66</v>
       </c>
       <c r="H768" s="2" t="n">
-        <v>46091.67981572195</v>
+        <v>46091.67981571759</v>
       </c>
     </row>
     <row r="769">
@@ -26583,7 +26583,7 @@
         <v>2.78</v>
       </c>
       <c r="H769" s="2" t="n">
-        <v>46078.67981572494</v>
+        <v>46078.67981572916</v>
       </c>
     </row>
     <row r="770">
@@ -26617,7 +26617,7 @@
         <v>0.39</v>
       </c>
       <c r="H770" s="2" t="n">
-        <v>46069.67981572814</v>
+        <v>46069.67981572916</v>
       </c>
     </row>
     <row r="771">
@@ -26651,7 +26651,7 @@
         <v>2.3</v>
       </c>
       <c r="H771" s="2" t="n">
-        <v>46071.67981573135</v>
+        <v>46071.67981572916</v>
       </c>
     </row>
     <row r="772">
@@ -26685,7 +26685,7 @@
         <v>4.23</v>
       </c>
       <c r="H772" s="2" t="n">
-        <v>46068.67981573454</v>
+        <v>46068.67981572916</v>
       </c>
     </row>
     <row r="773">
@@ -26719,7 +26719,7 @@
         <v>2.41</v>
       </c>
       <c r="H773" s="2" t="n">
-        <v>46070.67981573772</v>
+        <v>46070.67981574074</v>
       </c>
     </row>
     <row r="774">
@@ -26753,7 +26753,7 @@
         <v>4.44</v>
       </c>
       <c r="H774" s="2" t="n">
-        <v>46077.6798157408</v>
+        <v>46077.67981574074</v>
       </c>
     </row>
     <row r="775">
@@ -26787,7 +26787,7 @@
         <v>0.74</v>
       </c>
       <c r="H775" s="2" t="n">
-        <v>46073.67981574377</v>
+        <v>46073.67981574074</v>
       </c>
     </row>
     <row r="776">
@@ -26821,7 +26821,7 @@
         <v>4.88</v>
       </c>
       <c r="H776" s="2" t="n">
-        <v>46085.67981574679</v>
+        <v>46085.67981575232</v>
       </c>
     </row>
     <row r="777">
@@ -26855,7 +26855,7 @@
         <v>4.96</v>
       </c>
       <c r="H777" s="2" t="n">
-        <v>46072.6798157502</v>
+        <v>46072.67981575232</v>
       </c>
     </row>
     <row r="778">
@@ -26889,7 +26889,7 @@
         <v>2.75</v>
       </c>
       <c r="H778" s="2" t="n">
-        <v>46086.6798157534</v>
+        <v>46086.67981575232</v>
       </c>
     </row>
     <row r="779">
@@ -26923,7 +26923,7 @@
         <v>2.07</v>
       </c>
       <c r="H779" s="2" t="n">
-        <v>46080.67981575647</v>
+        <v>46080.67981575232</v>
       </c>
     </row>
     <row r="780">
@@ -26957,7 +26957,7 @@
         <v>0.19</v>
       </c>
       <c r="H780" s="2" t="n">
-        <v>46066.67981575961</v>
+        <v>46066.67981576389</v>
       </c>
     </row>
     <row r="781">
@@ -26991,7 +26991,7 @@
         <v>4.08</v>
       </c>
       <c r="H781" s="2" t="n">
-        <v>46090.67981576294</v>
+        <v>46090.67981576389</v>
       </c>
     </row>
     <row r="782">
@@ -27025,7 +27025,7 @@
         <v>4.76</v>
       </c>
       <c r="H782" s="2" t="n">
-        <v>46090.6798157663</v>
+        <v>46090.67981576389</v>
       </c>
     </row>
     <row r="783">
@@ -27059,7 +27059,7 @@
         <v>2.65</v>
       </c>
       <c r="H783" s="2" t="n">
-        <v>46074.67981576944</v>
+        <v>46074.67981576389</v>
       </c>
     </row>
     <row r="784">
@@ -27093,7 +27093,7 @@
         <v>1.18</v>
       </c>
       <c r="H784" s="2" t="n">
-        <v>46089.67981577278</v>
+        <v>46089.67981577546</v>
       </c>
     </row>
     <row r="785">
@@ -27127,7 +27127,7 @@
         <v>0.54</v>
       </c>
       <c r="H785" s="2" t="n">
-        <v>46083.67981577582</v>
+        <v>46083.67981577546</v>
       </c>
     </row>
     <row r="786">
@@ -27161,7 +27161,7 @@
         <v>1.87</v>
       </c>
       <c r="H786" s="2" t="n">
-        <v>46067.67981577884</v>
+        <v>46067.67981577546</v>
       </c>
     </row>
     <row r="787">
@@ -27195,7 +27195,7 @@
         <v>0.93</v>
       </c>
       <c r="H787" s="2" t="n">
-        <v>46081.67981578207</v>
+        <v>46081.67981578704</v>
       </c>
     </row>
     <row r="788">
@@ -27229,7 +27229,7 @@
         <v>2.19</v>
       </c>
       <c r="H788" s="2" t="n">
-        <v>46070.67981578535</v>
+        <v>46070.67981578704</v>
       </c>
     </row>
     <row r="789">
@@ -27263,7 +27263,7 @@
         <v>2.86</v>
       </c>
       <c r="H789" s="2" t="n">
-        <v>46080.67981578839</v>
+        <v>46080.67981578704</v>
       </c>
     </row>
     <row r="790">
@@ -27297,7 +27297,7 @@
         <v>4.32</v>
       </c>
       <c r="H790" s="2" t="n">
-        <v>46088.6798157914</v>
+        <v>46088.67981578704</v>
       </c>
     </row>
     <row r="791">
@@ -27331,7 +27331,7 @@
         <v>3.58</v>
       </c>
       <c r="H791" s="2" t="n">
-        <v>46077.67981579489</v>
+        <v>46077.67981579861</v>
       </c>
     </row>
     <row r="792">
@@ -27365,7 +27365,7 @@
         <v>2.6</v>
       </c>
       <c r="H792" s="2" t="n">
-        <v>46085.67981579797</v>
+        <v>46085.67981579861</v>
       </c>
     </row>
     <row r="793">
@@ -27399,7 +27399,7 @@
         <v>2.41</v>
       </c>
       <c r="H793" s="2" t="n">
-        <v>46091.679815801</v>
+        <v>46091.67981579861</v>
       </c>
     </row>
     <row r="794">
@@ -27433,7 +27433,7 @@
         <v>2.46</v>
       </c>
       <c r="H794" s="2" t="n">
-        <v>46092.67981580406</v>
+        <v>46092.67981579861</v>
       </c>
     </row>
     <row r="795">
@@ -27467,7 +27467,7 @@
         <v>3.23</v>
       </c>
       <c r="H795" s="2" t="n">
-        <v>46082.67981580735</v>
+        <v>46082.67981581019</v>
       </c>
     </row>
     <row r="796">
@@ -27501,7 +27501,7 @@
         <v>4.95</v>
       </c>
       <c r="H796" s="2" t="n">
-        <v>46066.67981581039</v>
+        <v>46066.67981581019</v>
       </c>
     </row>
     <row r="797">
@@ -27535,7 +27535,7 @@
         <v>4.11</v>
       </c>
       <c r="H797" s="2" t="n">
-        <v>46094.67981581359</v>
+        <v>46094.67981581019</v>
       </c>
     </row>
     <row r="798">
@@ -27569,7 +27569,7 @@
         <v>4.21</v>
       </c>
       <c r="H798" s="2" t="n">
-        <v>46090.67981581675</v>
+        <v>46090.67981582176</v>
       </c>
     </row>
     <row r="799">
@@ -27603,7 +27603,7 @@
         <v>1.14</v>
       </c>
       <c r="H799" s="2" t="n">
-        <v>46071.67981582</v>
+        <v>46071.67981582176</v>
       </c>
     </row>
     <row r="800">
@@ -27637,7 +27637,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="H800" s="2" t="n">
-        <v>46074.67981582315</v>
+        <v>46074.67981582176</v>
       </c>
     </row>
     <row r="801">
@@ -27671,7 +27671,1707 @@
         <v>0.66</v>
       </c>
       <c r="H801" s="2" t="n">
-        <v>46089.67981582624</v>
+        <v>46089.67981582176</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>b1280636-e3ce-4fd4-83fb-2003c154a453</t>
+        </is>
+      </c>
+      <c r="B802" t="n">
+        <v>95</v>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F802" t="n">
+        <v>411.69</v>
+      </c>
+      <c r="G802" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="H802" s="2" t="n">
+        <v>46067.72017556887</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>c6a4dbc1-f752-41da-8749-21a410731bfa</t>
+        </is>
+      </c>
+      <c r="B803" t="n">
+        <v>95</v>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F803" t="n">
+        <v>294.37</v>
+      </c>
+      <c r="G803" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H803" s="2" t="n">
+        <v>46085.72017557322</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>6b719db8-d872-4401-b8b7-cff1f1a8cbdc</t>
+        </is>
+      </c>
+      <c r="B804" t="n">
+        <v>95</v>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F804" t="n">
+        <v>225.5</v>
+      </c>
+      <c r="G804" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H804" s="2" t="n">
+        <v>46090.7201755766</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>37cdf58e-e19b-43f7-a2e2-b68fa6a4e9f3</t>
+        </is>
+      </c>
+      <c r="B805" t="n">
+        <v>95</v>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F805" t="n">
+        <v>221.52</v>
+      </c>
+      <c r="G805" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H805" s="2" t="n">
+        <v>46088.72017557982</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>7934b399-37d5-45b6-a6b9-88ab62284696</t>
+        </is>
+      </c>
+      <c r="B806" t="n">
+        <v>95</v>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F806" t="n">
+        <v>270.9</v>
+      </c>
+      <c r="G806" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="H806" s="2" t="n">
+        <v>46088.72017558294</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>215dac92-3b8a-4048-9492-afcbb38b6741</t>
+        </is>
+      </c>
+      <c r="B807" t="n">
+        <v>95</v>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F807" t="n">
+        <v>157.82</v>
+      </c>
+      <c r="G807" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H807" s="2" t="n">
+        <v>46083.72017558666</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>03185e8e-1460-4bf0-94e5-ac5bef028002</t>
+        </is>
+      </c>
+      <c r="B808" t="n">
+        <v>95</v>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F808" t="n">
+        <v>114.89</v>
+      </c>
+      <c r="G808" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H808" s="2" t="n">
+        <v>46078.72017558973</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>09a00b98-2a99-482d-bf63-db20b449c231</t>
+        </is>
+      </c>
+      <c r="B809" t="n">
+        <v>95</v>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F809" t="n">
+        <v>297.32</v>
+      </c>
+      <c r="G809" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="H809" s="2" t="n">
+        <v>46078.72017559287</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>db0bb19c-1b2b-466e-a2e7-fb1fcbdfa089</t>
+        </is>
+      </c>
+      <c r="B810" t="n">
+        <v>95</v>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F810" t="n">
+        <v>344.45</v>
+      </c>
+      <c r="G810" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="H810" s="2" t="n">
+        <v>46068.72017559685</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>0a62276d-a1a8-477a-9b9e-4e36075570d4</t>
+        </is>
+      </c>
+      <c r="B811" t="n">
+        <v>95</v>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F811" t="n">
+        <v>160.13</v>
+      </c>
+      <c r="G811" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H811" s="2" t="n">
+        <v>46069.72017560013</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>bece8b1d-7d8e-4589-a5e7-66a1213fa737</t>
+        </is>
+      </c>
+      <c r="B812" t="n">
+        <v>95</v>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F812" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="G812" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H812" s="2" t="n">
+        <v>46072.72017560348</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>79dffc75-b06a-49a7-938f-65f7da965b17</t>
+        </is>
+      </c>
+      <c r="B813" t="n">
+        <v>95</v>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F813" t="n">
+        <v>394.31</v>
+      </c>
+      <c r="G813" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="H813" s="2" t="n">
+        <v>46088.72017560693</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>da953338-d740-4e2e-9aec-31ca59b1f3b1</t>
+        </is>
+      </c>
+      <c r="B814" t="n">
+        <v>95</v>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F814" t="n">
+        <v>213.43</v>
+      </c>
+      <c r="G814" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="H814" s="2" t="n">
+        <v>46082.72017561011</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2e0fb77e-5499-421b-996d-2aea1fe4ae10</t>
+        </is>
+      </c>
+      <c r="B815" t="n">
+        <v>95</v>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F815" t="n">
+        <v>239.34</v>
+      </c>
+      <c r="G815" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H815" s="2" t="n">
+        <v>46076.72017561316</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>40a698cc-ad4b-48a2-8242-35f0dea4083c</t>
+        </is>
+      </c>
+      <c r="B816" t="n">
+        <v>95</v>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F816" t="n">
+        <v>298.54</v>
+      </c>
+      <c r="G816" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H816" s="2" t="n">
+        <v>46072.72017561622</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>de3df5c4-c47e-4a7c-8c62-10124aba11bb</t>
+        </is>
+      </c>
+      <c r="B817" t="n">
+        <v>95</v>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F817" t="n">
+        <v>106.58</v>
+      </c>
+      <c r="G817" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H817" s="2" t="n">
+        <v>46081.72017561949</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>c5ea309c-4537-438f-8cd8-cdbc21cd9ddd</t>
+        </is>
+      </c>
+      <c r="B818" t="n">
+        <v>95</v>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F818" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="G818" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H818" s="2" t="n">
+        <v>46093.72017562253</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>0f0fd362-0345-4d85-9d1a-8b0c18e939e0</t>
+        </is>
+      </c>
+      <c r="B819" t="n">
+        <v>95</v>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F819" t="n">
+        <v>316.61</v>
+      </c>
+      <c r="G819" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="H819" s="2" t="n">
+        <v>46078.72017562575</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>b49bcc59-b5e9-4a3e-ba45-2e6e8c077cc0</t>
+        </is>
+      </c>
+      <c r="B820" t="n">
+        <v>95</v>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F820" t="n">
+        <v>60.12</v>
+      </c>
+      <c r="G820" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H820" s="2" t="n">
+        <v>46078.72017562882</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>4dfd08ec-de9e-4737-86af-8fbda7edc363</t>
+        </is>
+      </c>
+      <c r="B821" t="n">
+        <v>95</v>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F821" t="n">
+        <v>420.67</v>
+      </c>
+      <c r="G821" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="H821" s="2" t="n">
+        <v>46088.72017563219</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>bd09e1c4-7972-47bd-ad09-d707e6358385</t>
+        </is>
+      </c>
+      <c r="B822" t="n">
+        <v>95</v>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F822" t="n">
+        <v>97.97</v>
+      </c>
+      <c r="G822" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H822" s="2" t="n">
+        <v>46076.72017563524</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>deea15e2-8f12-4453-b6d1-8de07a91dd81</t>
+        </is>
+      </c>
+      <c r="B823" t="n">
+        <v>95</v>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F823" t="n">
+        <v>40.47</v>
+      </c>
+      <c r="G823" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H823" s="2" t="n">
+        <v>46083.72017563834</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>1a9d9071-6d5b-4907-b755-30980f2aa9ea</t>
+        </is>
+      </c>
+      <c r="B824" t="n">
+        <v>95</v>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F824" t="n">
+        <v>23.89</v>
+      </c>
+      <c r="G824" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H824" s="2" t="n">
+        <v>46080.72017564187</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>7918a951-f712-43d8-82da-29c50f53b2d4</t>
+        </is>
+      </c>
+      <c r="B825" t="n">
+        <v>95</v>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F825" t="n">
+        <v>330.68</v>
+      </c>
+      <c r="G825" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="H825" s="2" t="n">
+        <v>46073.72017564498</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>aa0d1ca4-0bdd-40e3-916d-4c8ccd6263da</t>
+        </is>
+      </c>
+      <c r="B826" t="n">
+        <v>95</v>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F826" t="n">
+        <v>73.31</v>
+      </c>
+      <c r="G826" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H826" s="2" t="n">
+        <v>46088.72017564815</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>04b4622d-0934-4bde-ad68-378e5cba3bee</t>
+        </is>
+      </c>
+      <c r="B827" t="n">
+        <v>95</v>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F827" t="n">
+        <v>256.94</v>
+      </c>
+      <c r="G827" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="H827" s="2" t="n">
+        <v>46069.72017565139</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>7d55820e-b500-4be6-aba6-6e1b54e699f2</t>
+        </is>
+      </c>
+      <c r="B828" t="n">
+        <v>95</v>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F828" t="n">
+        <v>102.79</v>
+      </c>
+      <c r="G828" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H828" s="2" t="n">
+        <v>46071.7201756546</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>6cc32273-1b7f-462c-8b65-057dbdda68f0</t>
+        </is>
+      </c>
+      <c r="B829" t="n">
+        <v>95</v>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F829" t="n">
+        <v>409.35</v>
+      </c>
+      <c r="G829" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="H829" s="2" t="n">
+        <v>46089.72017565771</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>acf20933-63e8-438e-835c-c9ca7c2630b2</t>
+        </is>
+      </c>
+      <c r="B830" t="n">
+        <v>95</v>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F830" t="n">
+        <v>434.84</v>
+      </c>
+      <c r="G830" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="H830" s="2" t="n">
+        <v>46090.72017566072</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>60f472af-3772-4903-a82f-dbd7aa94ff17</t>
+        </is>
+      </c>
+      <c r="B831" t="n">
+        <v>95</v>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F831" t="n">
+        <v>232.41</v>
+      </c>
+      <c r="G831" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H831" s="2" t="n">
+        <v>46082.72017566382</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>40af0366-d9ad-4dd8-b8c6-929bdea9de0e</t>
+        </is>
+      </c>
+      <c r="B832" t="n">
+        <v>95</v>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F832" t="n">
+        <v>393.71</v>
+      </c>
+      <c r="G832" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="H832" s="2" t="n">
+        <v>46094.72017566721</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>a67911c6-8945-43ce-90b8-254bb38e13d8</t>
+        </is>
+      </c>
+      <c r="B833" t="n">
+        <v>95</v>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F833" t="n">
+        <v>212.38</v>
+      </c>
+      <c r="G833" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H833" s="2" t="n">
+        <v>46092.72017567028</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>d93f8dd0-5fd0-4035-b2ec-18e9a72a6db4</t>
+        </is>
+      </c>
+      <c r="B834" t="n">
+        <v>95</v>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F834" t="n">
+        <v>67.98999999999999</v>
+      </c>
+      <c r="G834" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H834" s="2" t="n">
+        <v>46085.72017567351</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>410d510e-bd75-4122-9725-f0f4f426d478</t>
+        </is>
+      </c>
+      <c r="B835" t="n">
+        <v>95</v>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F835" t="n">
+        <v>420.69</v>
+      </c>
+      <c r="G835" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="H835" s="2" t="n">
+        <v>46090.72017567686</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>fcc520fd-a135-41ba-a89b-ef711524ac6b</t>
+        </is>
+      </c>
+      <c r="B836" t="n">
+        <v>95</v>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F836" t="n">
+        <v>220.22</v>
+      </c>
+      <c r="G836" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H836" s="2" t="n">
+        <v>46087.72017567982</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>4e9d9df4-65ac-4cbc-97e5-d95bce1106a2</t>
+        </is>
+      </c>
+      <c r="B837" t="n">
+        <v>95</v>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F837" t="n">
+        <v>362.28</v>
+      </c>
+      <c r="G837" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="H837" s="2" t="n">
+        <v>46090.72017568293</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>7e764c48-99d5-4fe8-bb41-74f0455719ff</t>
+        </is>
+      </c>
+      <c r="B838" t="n">
+        <v>95</v>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F838" t="n">
+        <v>106.91</v>
+      </c>
+      <c r="G838" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H838" s="2" t="n">
+        <v>46081.72017568597</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>3dfb7c84-20de-41bd-a508-c1ec5f108d6a</t>
+        </is>
+      </c>
+      <c r="B839" t="n">
+        <v>95</v>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F839" t="n">
+        <v>120.42</v>
+      </c>
+      <c r="G839" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H839" s="2" t="n">
+        <v>46073.7201756896</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>83db7dae-edd6-46b6-9a59-ea31a80cec6c</t>
+        </is>
+      </c>
+      <c r="B840" t="n">
+        <v>95</v>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F840" t="n">
+        <v>336.24</v>
+      </c>
+      <c r="G840" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="H840" s="2" t="n">
+        <v>46074.72017569275</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>50409910-90a5-40ef-8968-8132feff19ac</t>
+        </is>
+      </c>
+      <c r="B841" t="n">
+        <v>95</v>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F841" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G841" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H841" s="2" t="n">
+        <v>46074.72017569585</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>8a589903-e137-4a60-82d7-fc0b1da76393</t>
+        </is>
+      </c>
+      <c r="B842" t="n">
+        <v>95</v>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F842" t="n">
+        <v>381.34</v>
+      </c>
+      <c r="G842" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="H842" s="2" t="n">
+        <v>46090.720175699</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>94c8fcd4-f6cc-403f-b81d-2c34859f3312</t>
+        </is>
+      </c>
+      <c r="B843" t="n">
+        <v>95</v>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F843" t="n">
+        <v>403.06</v>
+      </c>
+      <c r="G843" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H843" s="2" t="n">
+        <v>46068.72017570234</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>fb82b25e-5718-4a9f-bb2c-8e97185fec6f</t>
+        </is>
+      </c>
+      <c r="B844" t="n">
+        <v>95</v>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F844" t="n">
+        <v>210.36</v>
+      </c>
+      <c r="G844" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H844" s="2" t="n">
+        <v>46072.72017570541</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>e21d4a4a-d2fb-4d97-a357-22cae8ddf31f</t>
+        </is>
+      </c>
+      <c r="B845" t="n">
+        <v>95</v>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F845" t="n">
+        <v>429.09</v>
+      </c>
+      <c r="G845" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="H845" s="2" t="n">
+        <v>46075.72017570846</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>59c74d3e-af1c-4cc5-be6a-be9b340d2fc5</t>
+        </is>
+      </c>
+      <c r="B846" t="n">
+        <v>95</v>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F846" t="n">
+        <v>299.1</v>
+      </c>
+      <c r="G846" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H846" s="2" t="n">
+        <v>46087.72017571172</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>c3d88499-ee91-486f-8905-9ab7d20ac1aa</t>
+        </is>
+      </c>
+      <c r="B847" t="n">
+        <v>95</v>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F847" t="n">
+        <v>238.52</v>
+      </c>
+      <c r="G847" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H847" s="2" t="n">
+        <v>46088.72017571703</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>85601bfa-b688-4964-8b0b-a7f8115652ef</t>
+        </is>
+      </c>
+      <c r="B848" t="n">
+        <v>95</v>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F848" t="n">
+        <v>330.06</v>
+      </c>
+      <c r="G848" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H848" s="2" t="n">
+        <v>46074.72017572085</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>bce2ac2a-7daa-446e-9388-63b75860ecac</t>
+        </is>
+      </c>
+      <c r="B849" t="n">
+        <v>95</v>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F849" t="n">
+        <v>243.59</v>
+      </c>
+      <c r="G849" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H849" s="2" t="n">
+        <v>46071.72017572461</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>68169296-4328-41f4-a64a-1665ecca8a70</t>
+        </is>
+      </c>
+      <c r="B850" t="n">
+        <v>95</v>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F850" t="n">
+        <v>351.15</v>
+      </c>
+      <c r="G850" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="H850" s="2" t="n">
+        <v>46090.72017572765</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>3ab75ca7-e7fd-418d-9e7b-80f4bbc48ce4</t>
+        </is>
+      </c>
+      <c r="B851" t="n">
+        <v>95</v>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F851" t="n">
+        <v>211.73</v>
+      </c>
+      <c r="G851" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H851" s="2" t="n">
+        <v>46080.7201757307</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H851"/>
+  <dimension ref="A1:H901"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27705,7 +27705,7 @@
         <v>4.12</v>
       </c>
       <c r="H802" s="2" t="n">
-        <v>46067.72017556887</v>
+        <v>46067.72017556713</v>
       </c>
     </row>
     <row r="803">
@@ -27739,7 +27739,7 @@
         <v>2.94</v>
       </c>
       <c r="H803" s="2" t="n">
-        <v>46085.72017557322</v>
+        <v>46085.7201755787</v>
       </c>
     </row>
     <row r="804">
@@ -27773,7 +27773,7 @@
         <v>2.25</v>
       </c>
       <c r="H804" s="2" t="n">
-        <v>46090.7201755766</v>
+        <v>46090.7201755787</v>
       </c>
     </row>
     <row r="805">
@@ -27807,7 +27807,7 @@
         <v>2.22</v>
       </c>
       <c r="H805" s="2" t="n">
-        <v>46088.72017557982</v>
+        <v>46088.7201755787</v>
       </c>
     </row>
     <row r="806">
@@ -27841,7 +27841,7 @@
         <v>2.71</v>
       </c>
       <c r="H806" s="2" t="n">
-        <v>46088.72017558294</v>
+        <v>46088.7201755787</v>
       </c>
     </row>
     <row r="807">
@@ -27875,7 +27875,7 @@
         <v>1.58</v>
       </c>
       <c r="H807" s="2" t="n">
-        <v>46083.72017558666</v>
+        <v>46083.72017559028</v>
       </c>
     </row>
     <row r="808">
@@ -27909,7 +27909,7 @@
         <v>1.15</v>
       </c>
       <c r="H808" s="2" t="n">
-        <v>46078.72017558973</v>
+        <v>46078.72017559028</v>
       </c>
     </row>
     <row r="809">
@@ -27943,7 +27943,7 @@
         <v>2.97</v>
       </c>
       <c r="H809" s="2" t="n">
-        <v>46078.72017559287</v>
+        <v>46078.72017559028</v>
       </c>
     </row>
     <row r="810">
@@ -27977,7 +27977,7 @@
         <v>3.44</v>
       </c>
       <c r="H810" s="2" t="n">
-        <v>46068.72017559685</v>
+        <v>46068.72017560185</v>
       </c>
     </row>
     <row r="811">
@@ -28011,7 +28011,7 @@
         <v>1.6</v>
       </c>
       <c r="H811" s="2" t="n">
-        <v>46069.72017560013</v>
+        <v>46069.72017560185</v>
       </c>
     </row>
     <row r="812">
@@ -28045,7 +28045,7 @@
         <v>0.12</v>
       </c>
       <c r="H812" s="2" t="n">
-        <v>46072.72017560348</v>
+        <v>46072.72017560185</v>
       </c>
     </row>
     <row r="813">
@@ -28079,7 +28079,7 @@
         <v>3.94</v>
       </c>
       <c r="H813" s="2" t="n">
-        <v>46088.72017560693</v>
+        <v>46088.72017560185</v>
       </c>
     </row>
     <row r="814">
@@ -28113,7 +28113,7 @@
         <v>2.13</v>
       </c>
       <c r="H814" s="2" t="n">
-        <v>46082.72017561011</v>
+        <v>46082.72017561342</v>
       </c>
     </row>
     <row r="815">
@@ -28147,7 +28147,7 @@
         <v>2.39</v>
       </c>
       <c r="H815" s="2" t="n">
-        <v>46076.72017561316</v>
+        <v>46076.72017561342</v>
       </c>
     </row>
     <row r="816">
@@ -28181,7 +28181,7 @@
         <v>2.99</v>
       </c>
       <c r="H816" s="2" t="n">
-        <v>46072.72017561622</v>
+        <v>46072.72017561342</v>
       </c>
     </row>
     <row r="817">
@@ -28215,7 +28215,7 @@
         <v>1.07</v>
       </c>
       <c r="H817" s="2" t="n">
-        <v>46081.72017561949</v>
+        <v>46081.720175625</v>
       </c>
     </row>
     <row r="818">
@@ -28249,7 +28249,7 @@
         <v>0.82</v>
       </c>
       <c r="H818" s="2" t="n">
-        <v>46093.72017562253</v>
+        <v>46093.720175625</v>
       </c>
     </row>
     <row r="819">
@@ -28283,7 +28283,7 @@
         <v>3.17</v>
       </c>
       <c r="H819" s="2" t="n">
-        <v>46078.72017562575</v>
+        <v>46078.720175625</v>
       </c>
     </row>
     <row r="820">
@@ -28317,7 +28317,7 @@
         <v>0.6</v>
       </c>
       <c r="H820" s="2" t="n">
-        <v>46078.72017562882</v>
+        <v>46078.720175625</v>
       </c>
     </row>
     <row r="821">
@@ -28351,7 +28351,7 @@
         <v>4.21</v>
       </c>
       <c r="H821" s="2" t="n">
-        <v>46088.72017563219</v>
+        <v>46088.72017563658</v>
       </c>
     </row>
     <row r="822">
@@ -28385,7 +28385,7 @@
         <v>0.98</v>
       </c>
       <c r="H822" s="2" t="n">
-        <v>46076.72017563524</v>
+        <v>46076.72017563658</v>
       </c>
     </row>
     <row r="823">
@@ -28419,7 +28419,7 @@
         <v>0.4</v>
       </c>
       <c r="H823" s="2" t="n">
-        <v>46083.72017563834</v>
+        <v>46083.72017563658</v>
       </c>
     </row>
     <row r="824">
@@ -28453,7 +28453,7 @@
         <v>0.24</v>
       </c>
       <c r="H824" s="2" t="n">
-        <v>46080.72017564187</v>
+        <v>46080.72017563658</v>
       </c>
     </row>
     <row r="825">
@@ -28487,7 +28487,7 @@
         <v>3.31</v>
       </c>
       <c r="H825" s="2" t="n">
-        <v>46073.72017564498</v>
+        <v>46073.72017564815</v>
       </c>
     </row>
     <row r="826">
@@ -28555,7 +28555,7 @@
         <v>2.57</v>
       </c>
       <c r="H827" s="2" t="n">
-        <v>46069.72017565139</v>
+        <v>46069.72017564815</v>
       </c>
     </row>
     <row r="828">
@@ -28589,7 +28589,7 @@
         <v>1.03</v>
       </c>
       <c r="H828" s="2" t="n">
-        <v>46071.7201756546</v>
+        <v>46071.72017565972</v>
       </c>
     </row>
     <row r="829">
@@ -28623,7 +28623,7 @@
         <v>4.09</v>
       </c>
       <c r="H829" s="2" t="n">
-        <v>46089.72017565771</v>
+        <v>46089.72017565972</v>
       </c>
     </row>
     <row r="830">
@@ -28657,7 +28657,7 @@
         <v>4.35</v>
       </c>
       <c r="H830" s="2" t="n">
-        <v>46090.72017566072</v>
+        <v>46090.72017565972</v>
       </c>
     </row>
     <row r="831">
@@ -28691,7 +28691,7 @@
         <v>2.32</v>
       </c>
       <c r="H831" s="2" t="n">
-        <v>46082.72017566382</v>
+        <v>46082.72017565972</v>
       </c>
     </row>
     <row r="832">
@@ -28725,7 +28725,7 @@
         <v>3.94</v>
       </c>
       <c r="H832" s="2" t="n">
-        <v>46094.72017566721</v>
+        <v>46094.7201756713</v>
       </c>
     </row>
     <row r="833">
@@ -28759,7 +28759,7 @@
         <v>2.12</v>
       </c>
       <c r="H833" s="2" t="n">
-        <v>46092.72017567028</v>
+        <v>46092.7201756713</v>
       </c>
     </row>
     <row r="834">
@@ -28793,7 +28793,7 @@
         <v>0.68</v>
       </c>
       <c r="H834" s="2" t="n">
-        <v>46085.72017567351</v>
+        <v>46085.7201756713</v>
       </c>
     </row>
     <row r="835">
@@ -28827,7 +28827,7 @@
         <v>4.21</v>
       </c>
       <c r="H835" s="2" t="n">
-        <v>46090.72017567686</v>
+        <v>46090.7201756713</v>
       </c>
     </row>
     <row r="836">
@@ -28861,7 +28861,7 @@
         <v>2.2</v>
       </c>
       <c r="H836" s="2" t="n">
-        <v>46087.72017567982</v>
+        <v>46087.72017568287</v>
       </c>
     </row>
     <row r="837">
@@ -28895,7 +28895,7 @@
         <v>3.62</v>
       </c>
       <c r="H837" s="2" t="n">
-        <v>46090.72017568293</v>
+        <v>46090.72017568287</v>
       </c>
     </row>
     <row r="838">
@@ -28929,7 +28929,7 @@
         <v>1.07</v>
       </c>
       <c r="H838" s="2" t="n">
-        <v>46081.72017568597</v>
+        <v>46081.72017568287</v>
       </c>
     </row>
     <row r="839">
@@ -28963,7 +28963,7 @@
         <v>1.2</v>
       </c>
       <c r="H839" s="2" t="n">
-        <v>46073.7201756896</v>
+        <v>46073.72017569444</v>
       </c>
     </row>
     <row r="840">
@@ -28997,7 +28997,7 @@
         <v>3.36</v>
       </c>
       <c r="H840" s="2" t="n">
-        <v>46074.72017569275</v>
+        <v>46074.72017569444</v>
       </c>
     </row>
     <row r="841">
@@ -29031,7 +29031,7 @@
         <v>0.01</v>
       </c>
       <c r="H841" s="2" t="n">
-        <v>46074.72017569585</v>
+        <v>46074.72017569444</v>
       </c>
     </row>
     <row r="842">
@@ -29065,7 +29065,7 @@
         <v>3.81</v>
       </c>
       <c r="H842" s="2" t="n">
-        <v>46090.720175699</v>
+        <v>46090.72017569444</v>
       </c>
     </row>
     <row r="843">
@@ -29099,7 +29099,7 @@
         <v>4.03</v>
       </c>
       <c r="H843" s="2" t="n">
-        <v>46068.72017570234</v>
+        <v>46068.72017570602</v>
       </c>
     </row>
     <row r="844">
@@ -29133,7 +29133,7 @@
         <v>2.1</v>
       </c>
       <c r="H844" s="2" t="n">
-        <v>46072.72017570541</v>
+        <v>46072.72017570602</v>
       </c>
     </row>
     <row r="845">
@@ -29167,7 +29167,7 @@
         <v>4.29</v>
       </c>
       <c r="H845" s="2" t="n">
-        <v>46075.72017570846</v>
+        <v>46075.72017570602</v>
       </c>
     </row>
     <row r="846">
@@ -29201,7 +29201,7 @@
         <v>2.99</v>
       </c>
       <c r="H846" s="2" t="n">
-        <v>46087.72017571172</v>
+        <v>46087.72017570602</v>
       </c>
     </row>
     <row r="847">
@@ -29235,7 +29235,7 @@
         <v>2.39</v>
       </c>
       <c r="H847" s="2" t="n">
-        <v>46088.72017571703</v>
+        <v>46088.72017571759</v>
       </c>
     </row>
     <row r="848">
@@ -29269,7 +29269,7 @@
         <v>3.3</v>
       </c>
       <c r="H848" s="2" t="n">
-        <v>46074.72017572085</v>
+        <v>46074.72017571759</v>
       </c>
     </row>
     <row r="849">
@@ -29303,7 +29303,7 @@
         <v>2.44</v>
       </c>
       <c r="H849" s="2" t="n">
-        <v>46071.72017572461</v>
+        <v>46071.72017572917</v>
       </c>
     </row>
     <row r="850">
@@ -29337,7 +29337,7 @@
         <v>3.51</v>
       </c>
       <c r="H850" s="2" t="n">
-        <v>46090.72017572765</v>
+        <v>46090.72017572917</v>
       </c>
     </row>
     <row r="851">
@@ -29371,7 +29371,1707 @@
         <v>2.12</v>
       </c>
       <c r="H851" s="2" t="n">
-        <v>46080.7201757307</v>
+        <v>46080.72017572917</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>93668fa5-91f9-4fbd-945f-71f23ce3b2ca</t>
+        </is>
+      </c>
+      <c r="B852" t="n">
+        <v>95</v>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F852" t="n">
+        <v>94.11</v>
+      </c>
+      <c r="G852" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H852" s="2" t="n">
+        <v>46078.76571767292</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>4d8b9348-02ef-4ca3-b880-fd5c9170d4b1</t>
+        </is>
+      </c>
+      <c r="B853" t="n">
+        <v>95</v>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F853" t="n">
+        <v>327.72</v>
+      </c>
+      <c r="G853" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="H853" s="2" t="n">
+        <v>46091.76571767736</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>8c51aa49-b13d-4c72-8707-9d7877b32082</t>
+        </is>
+      </c>
+      <c r="B854" t="n">
+        <v>95</v>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F854" t="n">
+        <v>404.21</v>
+      </c>
+      <c r="G854" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="H854" s="2" t="n">
+        <v>46080.76571768057</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>22e49c19-5e98-4b93-985c-aaac85522b33</t>
+        </is>
+      </c>
+      <c r="B855" t="n">
+        <v>95</v>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F855" t="n">
+        <v>272.31</v>
+      </c>
+      <c r="G855" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H855" s="2" t="n">
+        <v>46092.76571768389</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>bb47010d-05d2-41f9-96f0-bb1398fcd8a6</t>
+        </is>
+      </c>
+      <c r="B856" t="n">
+        <v>95</v>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F856" t="n">
+        <v>389.49</v>
+      </c>
+      <c r="G856" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="H856" s="2" t="n">
+        <v>46086.76571768698</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>bac3db48-92c3-4b37-8bdf-18c85c77f64d</t>
+        </is>
+      </c>
+      <c r="B857" t="n">
+        <v>95</v>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F857" t="n">
+        <v>397.32</v>
+      </c>
+      <c r="G857" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="H857" s="2" t="n">
+        <v>46068.76571769036</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>70e4f9f8-888d-4677-a074-e4ec5cbd24de</t>
+        </is>
+      </c>
+      <c r="B858" t="n">
+        <v>95</v>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F858" t="n">
+        <v>352.09</v>
+      </c>
+      <c r="G858" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="H858" s="2" t="n">
+        <v>46087.76571769344</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>2f9f8ba5-ea34-44f1-bf03-9f9610a4a3a3</t>
+        </is>
+      </c>
+      <c r="B859" t="n">
+        <v>95</v>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F859" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="G859" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H859" s="2" t="n">
+        <v>46068.76571769665</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>adf072be-aa9c-4b75-b361-a2deb1c68e3a</t>
+        </is>
+      </c>
+      <c r="B860" t="n">
+        <v>95</v>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F860" t="n">
+        <v>321.76</v>
+      </c>
+      <c r="G860" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="H860" s="2" t="n">
+        <v>46080.7657177001</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>2822993d-b582-4212-9052-61dcba6a5fd7</t>
+        </is>
+      </c>
+      <c r="B861" t="n">
+        <v>95</v>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F861" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="G861" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H861" s="2" t="n">
+        <v>46071.76571770341</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>8d5c1327-c2bf-448f-9715-c6af231009a9</t>
+        </is>
+      </c>
+      <c r="B862" t="n">
+        <v>95</v>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F862" t="n">
+        <v>412.49</v>
+      </c>
+      <c r="G862" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="H862" s="2" t="n">
+        <v>46088.76571770653</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>4ee5deb4-c40a-4db2-9037-d166971fc2f5</t>
+        </is>
+      </c>
+      <c r="B863" t="n">
+        <v>95</v>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F863" t="n">
+        <v>78.94</v>
+      </c>
+      <c r="G863" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H863" s="2" t="n">
+        <v>46069.76571770968</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>0e5b1f8e-4c02-43d8-87de-7ccf21a6fd01</t>
+        </is>
+      </c>
+      <c r="B864" t="n">
+        <v>95</v>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F864" t="n">
+        <v>334.75</v>
+      </c>
+      <c r="G864" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H864" s="2" t="n">
+        <v>46065.76571771291</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>c8d8740b-92fd-4cc8-bf7c-fbc94e8b1aed</t>
+        </is>
+      </c>
+      <c r="B865" t="n">
+        <v>95</v>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F865" t="n">
+        <v>453.33</v>
+      </c>
+      <c r="G865" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="H865" s="2" t="n">
+        <v>46076.76571771603</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>1f76e152-f8dd-41e8-9cbe-b641309c7665</t>
+        </is>
+      </c>
+      <c r="B866" t="n">
+        <v>95</v>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F866" t="n">
+        <v>328.87</v>
+      </c>
+      <c r="G866" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="H866" s="2" t="n">
+        <v>46070.7657177192</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>d5ca044a-b92a-40ab-8be4-b5550db9ef3d</t>
+        </is>
+      </c>
+      <c r="B867" t="n">
+        <v>95</v>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F867" t="n">
+        <v>227.41</v>
+      </c>
+      <c r="G867" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="H867" s="2" t="n">
+        <v>46087.7657177223</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>d15ab7b6-a885-42ef-b999-58cf8bcd720f</t>
+        </is>
+      </c>
+      <c r="B868" t="n">
+        <v>95</v>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F868" t="n">
+        <v>143.38</v>
+      </c>
+      <c r="G868" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H868" s="2" t="n">
+        <v>46082.76571772561</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>859bccbb-3738-499d-a559-c907174e29f2</t>
+        </is>
+      </c>
+      <c r="B869" t="n">
+        <v>95</v>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F869" t="n">
+        <v>248.8</v>
+      </c>
+      <c r="G869" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H869" s="2" t="n">
+        <v>46077.76571772878</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>fa383ea1-aa85-4241-8259-e6c5ec39316f</t>
+        </is>
+      </c>
+      <c r="B870" t="n">
+        <v>95</v>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F870" t="n">
+        <v>74.84</v>
+      </c>
+      <c r="G870" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H870" s="2" t="n">
+        <v>46094.76571773209</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>15f2fe6f-23b3-4aa7-8317-29a90be625ca</t>
+        </is>
+      </c>
+      <c r="B871" t="n">
+        <v>95</v>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F871" t="n">
+        <v>29.56</v>
+      </c>
+      <c r="G871" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H871" s="2" t="n">
+        <v>46082.76571773543</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>7d01bdb8-2b6f-4993-acd1-d2fe9c427d29</t>
+        </is>
+      </c>
+      <c r="B872" t="n">
+        <v>95</v>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F872" t="n">
+        <v>298.89</v>
+      </c>
+      <c r="G872" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H872" s="2" t="n">
+        <v>46079.7657177385</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>3ce0ea1a-7bc7-4a29-8446-49643ce3befd</t>
+        </is>
+      </c>
+      <c r="B873" t="n">
+        <v>95</v>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F873" t="n">
+        <v>373.59</v>
+      </c>
+      <c r="G873" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H873" s="2" t="n">
+        <v>46083.76571774167</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>9c640618-38e5-4498-a62b-476e6cc2baf4</t>
+        </is>
+      </c>
+      <c r="B874" t="n">
+        <v>95</v>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F874" t="n">
+        <v>232.51</v>
+      </c>
+      <c r="G874" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="H874" s="2" t="n">
+        <v>46080.76571774475</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>1396f573-b493-4000-8639-0639db89579b</t>
+        </is>
+      </c>
+      <c r="B875" t="n">
+        <v>95</v>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F875" t="n">
+        <v>376.19</v>
+      </c>
+      <c r="G875" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="H875" s="2" t="n">
+        <v>46088.76571774812</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>dde0639a-19e2-4378-96a4-878adfb5231d</t>
+        </is>
+      </c>
+      <c r="B876" t="n">
+        <v>95</v>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F876" t="n">
+        <v>163.54</v>
+      </c>
+      <c r="G876" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H876" s="2" t="n">
+        <v>46068.76571775116</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>8bfd4ec0-fa09-4d9f-bfc4-f1d35a9b754c</t>
+        </is>
+      </c>
+      <c r="B877" t="n">
+        <v>95</v>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F877" t="n">
+        <v>466.96</v>
+      </c>
+      <c r="G877" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="H877" s="2" t="n">
+        <v>46091.76571775427</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>28c2f6c1-244a-4737-95c3-cbdab592de14</t>
+        </is>
+      </c>
+      <c r="B878" t="n">
+        <v>95</v>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F878" t="n">
+        <v>214.97</v>
+      </c>
+      <c r="G878" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="H878" s="2" t="n">
+        <v>46093.76571775743</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>6efcc097-1e3e-4397-82bc-75515e7c1806</t>
+        </is>
+      </c>
+      <c r="B879" t="n">
+        <v>95</v>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F879" t="n">
+        <v>104.48</v>
+      </c>
+      <c r="G879" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H879" s="2" t="n">
+        <v>46085.7657177607</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>f3e7d1ad-2cb8-448d-90af-3006b02cf41f</t>
+        </is>
+      </c>
+      <c r="B880" t="n">
+        <v>95</v>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F880" t="n">
+        <v>123.44</v>
+      </c>
+      <c r="G880" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="H880" s="2" t="n">
+        <v>46083.76571776376</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>b33a2863-e166-4891-b579-c2023352f1ee</t>
+        </is>
+      </c>
+      <c r="B881" t="n">
+        <v>95</v>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F881" t="n">
+        <v>197.56</v>
+      </c>
+      <c r="G881" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H881" s="2" t="n">
+        <v>46066.76571776681</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>191fe4b7-5573-4747-b498-4e2581d7e30c</t>
+        </is>
+      </c>
+      <c r="B882" t="n">
+        <v>95</v>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F882" t="n">
+        <v>378.39</v>
+      </c>
+      <c r="G882" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="H882" s="2" t="n">
+        <v>46081.76571777018</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>2fdfeff1-05b7-4bbb-8824-96d8e84187a7</t>
+        </is>
+      </c>
+      <c r="B883" t="n">
+        <v>95</v>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F883" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="G883" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H883" s="2" t="n">
+        <v>46068.76571777336</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>068ae17a-d416-4013-b953-9e16fc556ee5</t>
+        </is>
+      </c>
+      <c r="B884" t="n">
+        <v>95</v>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F884" t="n">
+        <v>153.23</v>
+      </c>
+      <c r="G884" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H884" s="2" t="n">
+        <v>46085.76571777655</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>bfa5aa0e-1a5d-4bc6-82e0-ce9bbdf6061e</t>
+        </is>
+      </c>
+      <c r="B885" t="n">
+        <v>95</v>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F885" t="n">
+        <v>166.18</v>
+      </c>
+      <c r="G885" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H885" s="2" t="n">
+        <v>46075.76571778015</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>2beed69d-35c1-4546-a31f-4229ddecc147</t>
+        </is>
+      </c>
+      <c r="B886" t="n">
+        <v>95</v>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F886" t="n">
+        <v>201.54</v>
+      </c>
+      <c r="G886" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H886" s="2" t="n">
+        <v>46081.76571778338</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>aa6a2c46-ed3a-4048-a634-311b21bf6e9e</t>
+        </is>
+      </c>
+      <c r="B887" t="n">
+        <v>95</v>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F887" t="n">
+        <v>319.7</v>
+      </c>
+      <c r="G887" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H887" s="2" t="n">
+        <v>46091.7657177864</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>6d72c8f9-867a-4322-8ef0-68fe741a411c</t>
+        </is>
+      </c>
+      <c r="B888" t="n">
+        <v>95</v>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F888" t="n">
+        <v>400.1</v>
+      </c>
+      <c r="G888" t="n">
+        <v>4</v>
+      </c>
+      <c r="H888" s="2" t="n">
+        <v>46087.76571778941</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>8c87d06b-52c1-463d-9147-99e2638a174c</t>
+        </is>
+      </c>
+      <c r="B889" t="n">
+        <v>95</v>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F889" t="n">
+        <v>316.81</v>
+      </c>
+      <c r="G889" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="H889" s="2" t="n">
+        <v>46090.76571779263</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>c8e6f612-589f-4d79-897e-c57d4d81506c</t>
+        </is>
+      </c>
+      <c r="B890" t="n">
+        <v>95</v>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F890" t="n">
+        <v>119.22</v>
+      </c>
+      <c r="G890" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H890" s="2" t="n">
+        <v>46078.76571779569</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>c7cd60f3-2608-4c7a-bf34-0245032684a9</t>
+        </is>
+      </c>
+      <c r="B891" t="n">
+        <v>95</v>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F891" t="n">
+        <v>165.22</v>
+      </c>
+      <c r="G891" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H891" s="2" t="n">
+        <v>46093.76571779873</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>c01171f0-ce05-4ae4-88db-2392f58aecac</t>
+        </is>
+      </c>
+      <c r="B892" t="n">
+        <v>95</v>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F892" t="n">
+        <v>322.53</v>
+      </c>
+      <c r="G892" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="H892" s="2" t="n">
+        <v>46070.76571780185</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>b6d8c20c-91c8-4b1f-afaa-83e5ddb8900f</t>
+        </is>
+      </c>
+      <c r="B893" t="n">
+        <v>95</v>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F893" t="n">
+        <v>298.71</v>
+      </c>
+      <c r="G893" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H893" s="2" t="n">
+        <v>46081.7657178052</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>80dcd774-783e-4909-b51f-571d70f7b635</t>
+        </is>
+      </c>
+      <c r="B894" t="n">
+        <v>95</v>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F894" t="n">
+        <v>271.66</v>
+      </c>
+      <c r="G894" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H894" s="2" t="n">
+        <v>46082.76571780822</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>42792fb1-b396-404e-95a9-db12a2e833f6</t>
+        </is>
+      </c>
+      <c r="B895" t="n">
+        <v>95</v>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F895" t="n">
+        <v>388.46</v>
+      </c>
+      <c r="G895" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="H895" s="2" t="n">
+        <v>46069.76571781141</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>5e355f22-61bc-4fca-a051-894897e522fd</t>
+        </is>
+      </c>
+      <c r="B896" t="n">
+        <v>95</v>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F896" t="n">
+        <v>85.37</v>
+      </c>
+      <c r="G896" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H896" s="2" t="n">
+        <v>46079.7657178146</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>aed45ccf-bfdb-42db-9d6b-0a21456cfd21</t>
+        </is>
+      </c>
+      <c r="B897" t="n">
+        <v>95</v>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F897" t="n">
+        <v>230</v>
+      </c>
+      <c r="G897" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H897" s="2" t="n">
+        <v>46073.76571781791</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>c485f3c2-4b42-4bfa-98ed-a7d9e16f8e75</t>
+        </is>
+      </c>
+      <c r="B898" t="n">
+        <v>95</v>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F898" t="n">
+        <v>150.46</v>
+      </c>
+      <c r="G898" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H898" s="2" t="n">
+        <v>46070.76571782095</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>e0fef902-3f0a-4795-a65b-90575ccd6f3c</t>
+        </is>
+      </c>
+      <c r="B899" t="n">
+        <v>95</v>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F899" t="n">
+        <v>54.48</v>
+      </c>
+      <c r="G899" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H899" s="2" t="n">
+        <v>46068.76571782405</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>40b123b9-bfba-47d6-a6b0-cf70b4c9e259</t>
+        </is>
+      </c>
+      <c r="B900" t="n">
+        <v>95</v>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F900" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="G900" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H900" s="2" t="n">
+        <v>46086.76571782719</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>ad841e60-97c5-40a6-8bc3-d950b61f54f6</t>
+        </is>
+      </c>
+      <c r="B901" t="n">
+        <v>95</v>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F901" t="n">
+        <v>225.48</v>
+      </c>
+      <c r="G901" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H901" s="2" t="n">
+        <v>46091.76571783039</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H901"/>
+  <dimension ref="A1:H951"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29405,7 +29405,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="H852" s="2" t="n">
-        <v>46078.76571767292</v>
+        <v>46078.76571767361</v>
       </c>
     </row>
     <row r="853">
@@ -29439,7 +29439,7 @@
         <v>3.28</v>
       </c>
       <c r="H853" s="2" t="n">
-        <v>46091.76571767736</v>
+        <v>46091.76571767361</v>
       </c>
     </row>
     <row r="854">
@@ -29473,7 +29473,7 @@
         <v>4.04</v>
       </c>
       <c r="H854" s="2" t="n">
-        <v>46080.76571768057</v>
+        <v>46080.76571768519</v>
       </c>
     </row>
     <row r="855">
@@ -29507,7 +29507,7 @@
         <v>2.72</v>
       </c>
       <c r="H855" s="2" t="n">
-        <v>46092.76571768389</v>
+        <v>46092.76571768519</v>
       </c>
     </row>
     <row r="856">
@@ -29541,7 +29541,7 @@
         <v>3.89</v>
       </c>
       <c r="H856" s="2" t="n">
-        <v>46086.76571768698</v>
+        <v>46086.76571768519</v>
       </c>
     </row>
     <row r="857">
@@ -29575,7 +29575,7 @@
         <v>3.97</v>
       </c>
       <c r="H857" s="2" t="n">
-        <v>46068.76571769036</v>
+        <v>46068.76571768519</v>
       </c>
     </row>
     <row r="858">
@@ -29609,7 +29609,7 @@
         <v>3.52</v>
       </c>
       <c r="H858" s="2" t="n">
-        <v>46087.76571769344</v>
+        <v>46087.76571769676</v>
       </c>
     </row>
     <row r="859">
@@ -29643,7 +29643,7 @@
         <v>0.96</v>
       </c>
       <c r="H859" s="2" t="n">
-        <v>46068.76571769665</v>
+        <v>46068.76571769676</v>
       </c>
     </row>
     <row r="860">
@@ -29677,7 +29677,7 @@
         <v>3.22</v>
       </c>
       <c r="H860" s="2" t="n">
-        <v>46080.7657177001</v>
+        <v>46080.76571769676</v>
       </c>
     </row>
     <row r="861">
@@ -29711,7 +29711,7 @@
         <v>0.25</v>
       </c>
       <c r="H861" s="2" t="n">
-        <v>46071.76571770341</v>
+        <v>46071.76571770833</v>
       </c>
     </row>
     <row r="862">
@@ -29745,7 +29745,7 @@
         <v>4.12</v>
       </c>
       <c r="H862" s="2" t="n">
-        <v>46088.76571770653</v>
+        <v>46088.76571770833</v>
       </c>
     </row>
     <row r="863">
@@ -29779,7 +29779,7 @@
         <v>0.79</v>
       </c>
       <c r="H863" s="2" t="n">
-        <v>46069.76571770968</v>
+        <v>46069.76571770833</v>
       </c>
     </row>
     <row r="864">
@@ -29813,7 +29813,7 @@
         <v>3.35</v>
       </c>
       <c r="H864" s="2" t="n">
-        <v>46065.76571771291</v>
+        <v>46065.76571770833</v>
       </c>
     </row>
     <row r="865">
@@ -29847,7 +29847,7 @@
         <v>4.53</v>
       </c>
       <c r="H865" s="2" t="n">
-        <v>46076.76571771603</v>
+        <v>46076.76571771991</v>
       </c>
     </row>
     <row r="866">
@@ -29881,7 +29881,7 @@
         <v>3.29</v>
       </c>
       <c r="H866" s="2" t="n">
-        <v>46070.7657177192</v>
+        <v>46070.76571771991</v>
       </c>
     </row>
     <row r="867">
@@ -29915,7 +29915,7 @@
         <v>2.27</v>
       </c>
       <c r="H867" s="2" t="n">
-        <v>46087.7657177223</v>
+        <v>46087.76571771991</v>
       </c>
     </row>
     <row r="868">
@@ -29949,7 +29949,7 @@
         <v>1.43</v>
       </c>
       <c r="H868" s="2" t="n">
-        <v>46082.76571772561</v>
+        <v>46082.76571771991</v>
       </c>
     </row>
     <row r="869">
@@ -29983,7 +29983,7 @@
         <v>2.49</v>
       </c>
       <c r="H869" s="2" t="n">
-        <v>46077.76571772878</v>
+        <v>46077.76571773148</v>
       </c>
     </row>
     <row r="870">
@@ -30017,7 +30017,7 @@
         <v>0.75</v>
       </c>
       <c r="H870" s="2" t="n">
-        <v>46094.76571773209</v>
+        <v>46094.76571773148</v>
       </c>
     </row>
     <row r="871">
@@ -30051,7 +30051,7 @@
         <v>0.3</v>
       </c>
       <c r="H871" s="2" t="n">
-        <v>46082.76571773543</v>
+        <v>46082.76571773148</v>
       </c>
     </row>
     <row r="872">
@@ -30085,7 +30085,7 @@
         <v>2.99</v>
       </c>
       <c r="H872" s="2" t="n">
-        <v>46079.7657177385</v>
+        <v>46079.76571774305</v>
       </c>
     </row>
     <row r="873">
@@ -30119,7 +30119,7 @@
         <v>3.74</v>
       </c>
       <c r="H873" s="2" t="n">
-        <v>46083.76571774167</v>
+        <v>46083.76571774305</v>
       </c>
     </row>
     <row r="874">
@@ -30153,7 +30153,7 @@
         <v>2.33</v>
       </c>
       <c r="H874" s="2" t="n">
-        <v>46080.76571774475</v>
+        <v>46080.76571774305</v>
       </c>
     </row>
     <row r="875">
@@ -30187,7 +30187,7 @@
         <v>3.76</v>
       </c>
       <c r="H875" s="2" t="n">
-        <v>46088.76571774812</v>
+        <v>46088.76571774305</v>
       </c>
     </row>
     <row r="876">
@@ -30221,7 +30221,7 @@
         <v>1.64</v>
       </c>
       <c r="H876" s="2" t="n">
-        <v>46068.76571775116</v>
+        <v>46068.76571775463</v>
       </c>
     </row>
     <row r="877">
@@ -30255,7 +30255,7 @@
         <v>4.67</v>
       </c>
       <c r="H877" s="2" t="n">
-        <v>46091.76571775427</v>
+        <v>46091.76571775463</v>
       </c>
     </row>
     <row r="878">
@@ -30289,7 +30289,7 @@
         <v>2.15</v>
       </c>
       <c r="H878" s="2" t="n">
-        <v>46093.76571775743</v>
+        <v>46093.76571775463</v>
       </c>
     </row>
     <row r="879">
@@ -30323,7 +30323,7 @@
         <v>1.04</v>
       </c>
       <c r="H879" s="2" t="n">
-        <v>46085.7657177607</v>
+        <v>46085.7657177662</v>
       </c>
     </row>
     <row r="880">
@@ -30357,7 +30357,7 @@
         <v>1.23</v>
       </c>
       <c r="H880" s="2" t="n">
-        <v>46083.76571776376</v>
+        <v>46083.7657177662</v>
       </c>
     </row>
     <row r="881">
@@ -30391,7 +30391,7 @@
         <v>1.98</v>
       </c>
       <c r="H881" s="2" t="n">
-        <v>46066.76571776681</v>
+        <v>46066.7657177662</v>
       </c>
     </row>
     <row r="882">
@@ -30425,7 +30425,7 @@
         <v>3.78</v>
       </c>
       <c r="H882" s="2" t="n">
-        <v>46081.76571777018</v>
+        <v>46081.7657177662</v>
       </c>
     </row>
     <row r="883">
@@ -30459,7 +30459,7 @@
         <v>0.03</v>
       </c>
       <c r="H883" s="2" t="n">
-        <v>46068.76571777336</v>
+        <v>46068.76571777778</v>
       </c>
     </row>
     <row r="884">
@@ -30493,7 +30493,7 @@
         <v>1.53</v>
       </c>
       <c r="H884" s="2" t="n">
-        <v>46085.76571777655</v>
+        <v>46085.76571777778</v>
       </c>
     </row>
     <row r="885">
@@ -30527,7 +30527,7 @@
         <v>1.66</v>
       </c>
       <c r="H885" s="2" t="n">
-        <v>46075.76571778015</v>
+        <v>46075.76571777778</v>
       </c>
     </row>
     <row r="886">
@@ -30561,7 +30561,7 @@
         <v>2.02</v>
       </c>
       <c r="H886" s="2" t="n">
-        <v>46081.76571778338</v>
+        <v>46081.76571777778</v>
       </c>
     </row>
     <row r="887">
@@ -30595,7 +30595,7 @@
         <v>3.2</v>
       </c>
       <c r="H887" s="2" t="n">
-        <v>46091.7657177864</v>
+        <v>46091.76571778935</v>
       </c>
     </row>
     <row r="888">
@@ -30629,7 +30629,7 @@
         <v>4</v>
       </c>
       <c r="H888" s="2" t="n">
-        <v>46087.76571778941</v>
+        <v>46087.76571778935</v>
       </c>
     </row>
     <row r="889">
@@ -30663,7 +30663,7 @@
         <v>3.17</v>
       </c>
       <c r="H889" s="2" t="n">
-        <v>46090.76571779263</v>
+        <v>46090.76571778935</v>
       </c>
     </row>
     <row r="890">
@@ -30697,7 +30697,7 @@
         <v>1.19</v>
       </c>
       <c r="H890" s="2" t="n">
-        <v>46078.76571779569</v>
+        <v>46078.76571780092</v>
       </c>
     </row>
     <row r="891">
@@ -30731,7 +30731,7 @@
         <v>1.65</v>
       </c>
       <c r="H891" s="2" t="n">
-        <v>46093.76571779873</v>
+        <v>46093.76571780092</v>
       </c>
     </row>
     <row r="892">
@@ -30765,7 +30765,7 @@
         <v>3.23</v>
       </c>
       <c r="H892" s="2" t="n">
-        <v>46070.76571780185</v>
+        <v>46070.76571780092</v>
       </c>
     </row>
     <row r="893">
@@ -30799,7 +30799,7 @@
         <v>2.99</v>
       </c>
       <c r="H893" s="2" t="n">
-        <v>46081.7657178052</v>
+        <v>46081.76571780092</v>
       </c>
     </row>
     <row r="894">
@@ -30833,7 +30833,7 @@
         <v>2.72</v>
       </c>
       <c r="H894" s="2" t="n">
-        <v>46082.76571780822</v>
+        <v>46082.7657178125</v>
       </c>
     </row>
     <row r="895">
@@ -30867,7 +30867,7 @@
         <v>3.88</v>
       </c>
       <c r="H895" s="2" t="n">
-        <v>46069.76571781141</v>
+        <v>46069.7657178125</v>
       </c>
     </row>
     <row r="896">
@@ -30901,7 +30901,7 @@
         <v>0.85</v>
       </c>
       <c r="H896" s="2" t="n">
-        <v>46079.7657178146</v>
+        <v>46079.7657178125</v>
       </c>
     </row>
     <row r="897">
@@ -30935,7 +30935,7 @@
         <v>2.3</v>
       </c>
       <c r="H897" s="2" t="n">
-        <v>46073.76571781791</v>
+        <v>46073.7657178125</v>
       </c>
     </row>
     <row r="898">
@@ -30969,7 +30969,7 @@
         <v>1.5</v>
       </c>
       <c r="H898" s="2" t="n">
-        <v>46070.76571782095</v>
+        <v>46070.76571782408</v>
       </c>
     </row>
     <row r="899">
@@ -31003,7 +31003,7 @@
         <v>0.54</v>
       </c>
       <c r="H899" s="2" t="n">
-        <v>46068.76571782405</v>
+        <v>46068.76571782408</v>
       </c>
     </row>
     <row r="900">
@@ -31037,7 +31037,7 @@
         <v>1.83</v>
       </c>
       <c r="H900" s="2" t="n">
-        <v>46086.76571782719</v>
+        <v>46086.76571782408</v>
       </c>
     </row>
     <row r="901">
@@ -31071,7 +31071,1707 @@
         <v>2.25</v>
       </c>
       <c r="H901" s="2" t="n">
-        <v>46091.76571783039</v>
+        <v>46091.76571783565</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>faee317d-6923-4612-8d8a-988b09c13bef</t>
+        </is>
+      </c>
+      <c r="B902" t="n">
+        <v>95</v>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F902" t="n">
+        <v>103.98</v>
+      </c>
+      <c r="G902" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H902" s="2" t="n">
+        <v>46092.80440636374</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>66a1fa9b-36e4-4c86-9863-e5ee6997ca94</t>
+        </is>
+      </c>
+      <c r="B903" t="n">
+        <v>95</v>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F903" t="n">
+        <v>406.49</v>
+      </c>
+      <c r="G903" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="H903" s="2" t="n">
+        <v>46080.80440636795</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>f36f0b64-f83e-4f26-95d6-b2fedc4e3b6c</t>
+        </is>
+      </c>
+      <c r="B904" t="n">
+        <v>95</v>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F904" t="n">
+        <v>346.45</v>
+      </c>
+      <c r="G904" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="H904" s="2" t="n">
+        <v>46065.80440637137</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>b8c15e58-e7ec-49af-a166-4cea197fd8b6</t>
+        </is>
+      </c>
+      <c r="B905" t="n">
+        <v>95</v>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F905" t="n">
+        <v>372.43</v>
+      </c>
+      <c r="G905" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="H905" s="2" t="n">
+        <v>46070.8044063749</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>7652c18e-722d-4640-8301-6948d24fb23d</t>
+        </is>
+      </c>
+      <c r="B906" t="n">
+        <v>95</v>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F906" t="n">
+        <v>145.4</v>
+      </c>
+      <c r="G906" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H906" s="2" t="n">
+        <v>46087.80440637823</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>79ca0b75-f950-4059-9c37-eb170fc83240</t>
+        </is>
+      </c>
+      <c r="B907" t="n">
+        <v>95</v>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F907" t="n">
+        <v>306.23</v>
+      </c>
+      <c r="G907" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="H907" s="2" t="n">
+        <v>46066.8044063816</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>96547d68-e41b-47d2-9756-7d0769b43924</t>
+        </is>
+      </c>
+      <c r="B908" t="n">
+        <v>95</v>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F908" t="n">
+        <v>355.06</v>
+      </c>
+      <c r="G908" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H908" s="2" t="n">
+        <v>46069.80440638468</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>a53df51c-a547-4ebe-9807-1555247cc5f1</t>
+        </is>
+      </c>
+      <c r="B909" t="n">
+        <v>95</v>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F909" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="G909" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H909" s="2" t="n">
+        <v>46094.80440638823</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>3c8fb256-6a9d-49ea-8646-32ce0d81e579</t>
+        </is>
+      </c>
+      <c r="B910" t="n">
+        <v>95</v>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F910" t="n">
+        <v>305.2</v>
+      </c>
+      <c r="G910" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H910" s="2" t="n">
+        <v>46081.80440639157</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>22df145d-4831-4d54-88a5-e8b583c14286</t>
+        </is>
+      </c>
+      <c r="B911" t="n">
+        <v>95</v>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F911" t="n">
+        <v>320.63</v>
+      </c>
+      <c r="G911" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="H911" s="2" t="n">
+        <v>46089.80440639487</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>902bcfe6-d7f2-4e96-9655-4cc9010bcb4f</t>
+        </is>
+      </c>
+      <c r="B912" t="n">
+        <v>95</v>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F912" t="n">
+        <v>439.18</v>
+      </c>
+      <c r="G912" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="H912" s="2" t="n">
+        <v>46091.80440639866</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>8c871962-2965-4819-9753-2ba6ff553a98</t>
+        </is>
+      </c>
+      <c r="B913" t="n">
+        <v>95</v>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F913" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="G913" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H913" s="2" t="n">
+        <v>46075.80440640193</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>227c6139-b6a5-437f-ad06-7f41241e2965</t>
+        </is>
+      </c>
+      <c r="B914" t="n">
+        <v>95</v>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F914" t="n">
+        <v>313.93</v>
+      </c>
+      <c r="G914" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H914" s="2" t="n">
+        <v>46078.80440640528</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>a114eb37-6b79-4a3d-9482-37b9402bd77e</t>
+        </is>
+      </c>
+      <c r="B915" t="n">
+        <v>95</v>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F915" t="n">
+        <v>354.54</v>
+      </c>
+      <c r="G915" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H915" s="2" t="n">
+        <v>46070.80440640861</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>c9da8397-2620-4d0b-b0b1-74e91520491c</t>
+        </is>
+      </c>
+      <c r="B916" t="n">
+        <v>95</v>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F916" t="n">
+        <v>479.59</v>
+      </c>
+      <c r="G916" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H916" s="2" t="n">
+        <v>46066.80440641173</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>327fe8d7-1088-40e5-8cdb-c3d45b511ec7</t>
+        </is>
+      </c>
+      <c r="B917" t="n">
+        <v>95</v>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F917" t="n">
+        <v>427.12</v>
+      </c>
+      <c r="G917" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="H917" s="2" t="n">
+        <v>46093.80440641504</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>b8d6314f-b5bc-4647-8d3d-86fbdf91f497</t>
+        </is>
+      </c>
+      <c r="B918" t="n">
+        <v>95</v>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F918" t="n">
+        <v>199.75</v>
+      </c>
+      <c r="G918" t="n">
+        <v>2</v>
+      </c>
+      <c r="H918" s="2" t="n">
+        <v>46091.8044064183</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>784b7953-0cb8-4573-b0dc-f0092bfb94b7</t>
+        </is>
+      </c>
+      <c r="B919" t="n">
+        <v>95</v>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F919" t="n">
+        <v>71.03</v>
+      </c>
+      <c r="G919" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H919" s="2" t="n">
+        <v>46072.80440642161</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>205343d9-57cb-43b7-b9d3-bb5bba7f02d3</t>
+        </is>
+      </c>
+      <c r="B920" t="n">
+        <v>95</v>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F920" t="n">
+        <v>192.15</v>
+      </c>
+      <c r="G920" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H920" s="2" t="n">
+        <v>46081.80440642474</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>cf32270a-6acc-4a50-8afc-9a8bbaaf5776</t>
+        </is>
+      </c>
+      <c r="B921" t="n">
+        <v>95</v>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F921" t="n">
+        <v>403.19</v>
+      </c>
+      <c r="G921" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H921" s="2" t="n">
+        <v>46078.80440642796</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>278420f9-a71d-4ff9-bf8e-36c42d011f66</t>
+        </is>
+      </c>
+      <c r="B922" t="n">
+        <v>95</v>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F922" t="n">
+        <v>317.66</v>
+      </c>
+      <c r="G922" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H922" s="2" t="n">
+        <v>46076.80440643107</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>1996a631-8c6c-47a2-bf95-71a3790c1ba9</t>
+        </is>
+      </c>
+      <c r="B923" t="n">
+        <v>95</v>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F923" t="n">
+        <v>320.52</v>
+      </c>
+      <c r="G923" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="H923" s="2" t="n">
+        <v>46072.80440643505</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>79ae80d8-a741-408a-b426-1045dd5f901f</t>
+        </is>
+      </c>
+      <c r="B924" t="n">
+        <v>95</v>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F924" t="n">
+        <v>84.45999999999999</v>
+      </c>
+      <c r="G924" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H924" s="2" t="n">
+        <v>46071.80440643826</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>cc6cb5f9-497e-4ae2-8243-025efb78c913</t>
+        </is>
+      </c>
+      <c r="B925" t="n">
+        <v>95</v>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F925" t="n">
+        <v>316.31</v>
+      </c>
+      <c r="G925" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="H925" s="2" t="n">
+        <v>46065.80440644147</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>a244c00d-80aa-4979-a99e-de973e1f385d</t>
+        </is>
+      </c>
+      <c r="B926" t="n">
+        <v>95</v>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F926" t="n">
+        <v>242.83</v>
+      </c>
+      <c r="G926" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="H926" s="2" t="n">
+        <v>46094.80440644494</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>6404c7eb-8486-484f-9cd3-f6c05f20ab1e</t>
+        </is>
+      </c>
+      <c r="B927" t="n">
+        <v>95</v>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F927" t="n">
+        <v>388.14</v>
+      </c>
+      <c r="G927" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="H927" s="2" t="n">
+        <v>46075.80440644809</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>c101efbf-9d21-440d-acee-14718f324e41</t>
+        </is>
+      </c>
+      <c r="B928" t="n">
+        <v>95</v>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F928" t="n">
+        <v>73.11</v>
+      </c>
+      <c r="G928" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H928" s="2" t="n">
+        <v>46073.80440645119</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>d813f0b1-a2bc-4704-a01a-dcfac48ecdc8</t>
+        </is>
+      </c>
+      <c r="B929" t="n">
+        <v>95</v>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F929" t="n">
+        <v>169.74</v>
+      </c>
+      <c r="G929" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H929" s="2" t="n">
+        <v>46082.80440645434</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>4b5dcbfe-17f1-4847-bcf4-683026e1371d</t>
+        </is>
+      </c>
+      <c r="B930" t="n">
+        <v>95</v>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F930" t="n">
+        <v>214.24</v>
+      </c>
+      <c r="G930" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H930" s="2" t="n">
+        <v>46087.80440645762</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>9272b8f7-149d-47b4-b746-9551e91eca22</t>
+        </is>
+      </c>
+      <c r="B931" t="n">
+        <v>95</v>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F931" t="n">
+        <v>118.85</v>
+      </c>
+      <c r="G931" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H931" s="2" t="n">
+        <v>46093.80440646079</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>122ed255-e344-4d28-bfc5-f984cdd5896d</t>
+        </is>
+      </c>
+      <c r="B932" t="n">
+        <v>95</v>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F932" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="G932" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H932" s="2" t="n">
+        <v>46074.80440646412</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>4fe6469b-0aed-486c-a504-ad08459d70a6</t>
+        </is>
+      </c>
+      <c r="B933" t="n">
+        <v>95</v>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F933" t="n">
+        <v>497.65</v>
+      </c>
+      <c r="G933" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="H933" s="2" t="n">
+        <v>46085.80440646742</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>fee0bceb-82a6-4201-94e4-42d1aa3dc818</t>
+        </is>
+      </c>
+      <c r="B934" t="n">
+        <v>95</v>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F934" t="n">
+        <v>248.81</v>
+      </c>
+      <c r="G934" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H934" s="2" t="n">
+        <v>46094.80440647055</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>6768216a-3cea-4658-9583-8910e44fd9d8</t>
+        </is>
+      </c>
+      <c r="B935" t="n">
+        <v>95</v>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F935" t="n">
+        <v>16.93</v>
+      </c>
+      <c r="G935" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H935" s="2" t="n">
+        <v>46068.80440647375</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>e976e11c-07e0-468a-bfe0-393a35101eb6</t>
+        </is>
+      </c>
+      <c r="B936" t="n">
+        <v>95</v>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F936" t="n">
+        <v>328.83</v>
+      </c>
+      <c r="G936" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="H936" s="2" t="n">
+        <v>46089.80440647683</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>823c63ea-d079-4cc1-b547-51c3bc93dcac</t>
+        </is>
+      </c>
+      <c r="B937" t="n">
+        <v>95</v>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F937" t="n">
+        <v>414.85</v>
+      </c>
+      <c r="G937" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="H937" s="2" t="n">
+        <v>46083.80440648029</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>26083769-e9c1-45a4-9c19-a02cec237d0a</t>
+        </is>
+      </c>
+      <c r="B938" t="n">
+        <v>95</v>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F938" t="n">
+        <v>373.21</v>
+      </c>
+      <c r="G938" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="H938" s="2" t="n">
+        <v>46066.80440648388</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>21718b80-07fc-441e-883b-38f0ffc958a8</t>
+        </is>
+      </c>
+      <c r="B939" t="n">
+        <v>95</v>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F939" t="n">
+        <v>32.59</v>
+      </c>
+      <c r="G939" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H939" s="2" t="n">
+        <v>46069.80440648715</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>98e8ecd1-d581-41c6-b608-802dab97fc82</t>
+        </is>
+      </c>
+      <c r="B940" t="n">
+        <v>95</v>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F940" t="n">
+        <v>255.77</v>
+      </c>
+      <c r="G940" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H940" s="2" t="n">
+        <v>46080.80440649046</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>3a5f7e93-03e2-4ffd-b905-f58e1a57fc99</t>
+        </is>
+      </c>
+      <c r="B941" t="n">
+        <v>95</v>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F941" t="n">
+        <v>213.15</v>
+      </c>
+      <c r="G941" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="H941" s="2" t="n">
+        <v>46070.80440649367</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>391956ce-a1c5-4e36-844e-9a756b23c3d7</t>
+        </is>
+      </c>
+      <c r="B942" t="n">
+        <v>95</v>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F942" t="n">
+        <v>301.58</v>
+      </c>
+      <c r="G942" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="H942" s="2" t="n">
+        <v>46066.80440649675</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>2a4dadd3-7f75-4936-abe0-e52ee0bd42b2</t>
+        </is>
+      </c>
+      <c r="B943" t="n">
+        <v>95</v>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F943" t="n">
+        <v>494.46</v>
+      </c>
+      <c r="G943" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="H943" s="2" t="n">
+        <v>46083.80440650001</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>2d01e1ee-28b0-4ef1-bda4-21d336441ccd</t>
+        </is>
+      </c>
+      <c r="B944" t="n">
+        <v>95</v>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F944" t="n">
+        <v>280.55</v>
+      </c>
+      <c r="G944" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="H944" s="2" t="n">
+        <v>46070.80440650333</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>d837b880-4ea0-42da-97b5-0c3a078fdd43</t>
+        </is>
+      </c>
+      <c r="B945" t="n">
+        <v>95</v>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F945" t="n">
+        <v>438.5</v>
+      </c>
+      <c r="G945" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="H945" s="2" t="n">
+        <v>46090.80440650639</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>c6f7006f-f43a-461c-ad47-e41b19c1f14d</t>
+        </is>
+      </c>
+      <c r="B946" t="n">
+        <v>95</v>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F946" t="n">
+        <v>392.44</v>
+      </c>
+      <c r="G946" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H946" s="2" t="n">
+        <v>46067.80440650963</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>760239e4-e7af-4e92-86c9-53c238f76eef</t>
+        </is>
+      </c>
+      <c r="B947" t="n">
+        <v>95</v>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F947" t="n">
+        <v>95.73999999999999</v>
+      </c>
+      <c r="G947" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H947" s="2" t="n">
+        <v>46086.80440651299</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>2eca3f95-9c63-498f-8b10-3506a12aa77b</t>
+        </is>
+      </c>
+      <c r="B948" t="n">
+        <v>95</v>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F948" t="n">
+        <v>477.92</v>
+      </c>
+      <c r="G948" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H948" s="2" t="n">
+        <v>46090.80440651625</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>827ec653-76d9-4241-89e5-3a14d915a1cf</t>
+        </is>
+      </c>
+      <c r="B949" t="n">
+        <v>95</v>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F949" t="n">
+        <v>247.58</v>
+      </c>
+      <c r="G949" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H949" s="2" t="n">
+        <v>46092.8044065195</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>b08d9958-573f-49f6-85f9-807f938ba9ca</t>
+        </is>
+      </c>
+      <c r="B950" t="n">
+        <v>95</v>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F950" t="n">
+        <v>60.43</v>
+      </c>
+      <c r="G950" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H950" s="2" t="n">
+        <v>46082.80440652255</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>c0cfba62-af52-4eec-89d9-a6b32cbc6829</t>
+        </is>
+      </c>
+      <c r="B951" t="n">
+        <v>95</v>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F951" t="n">
+        <v>238.1</v>
+      </c>
+      <c r="G951" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H951" s="2" t="n">
+        <v>46075.80440652594</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H951"/>
+  <dimension ref="A1:H1001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31105,7 +31105,7 @@
         <v>1.04</v>
       </c>
       <c r="H902" s="2" t="n">
-        <v>46092.80440636374</v>
+        <v>46092.80440636574</v>
       </c>
     </row>
     <row r="903">
@@ -31139,7 +31139,7 @@
         <v>4.06</v>
       </c>
       <c r="H903" s="2" t="n">
-        <v>46080.80440636795</v>
+        <v>46080.80440636574</v>
       </c>
     </row>
     <row r="904">
@@ -31173,7 +31173,7 @@
         <v>3.46</v>
       </c>
       <c r="H904" s="2" t="n">
-        <v>46065.80440637137</v>
+        <v>46065.80440636574</v>
       </c>
     </row>
     <row r="905">
@@ -31207,7 +31207,7 @@
         <v>3.72</v>
       </c>
       <c r="H905" s="2" t="n">
-        <v>46070.8044063749</v>
+        <v>46070.80440637731</v>
       </c>
     </row>
     <row r="906">
@@ -31241,7 +31241,7 @@
         <v>1.45</v>
       </c>
       <c r="H906" s="2" t="n">
-        <v>46087.80440637823</v>
+        <v>46087.80440637731</v>
       </c>
     </row>
     <row r="907">
@@ -31275,7 +31275,7 @@
         <v>3.06</v>
       </c>
       <c r="H907" s="2" t="n">
-        <v>46066.8044063816</v>
+        <v>46066.80440637731</v>
       </c>
     </row>
     <row r="908">
@@ -31309,7 +31309,7 @@
         <v>3.55</v>
       </c>
       <c r="H908" s="2" t="n">
-        <v>46069.80440638468</v>
+        <v>46069.80440638889</v>
       </c>
     </row>
     <row r="909">
@@ -31343,7 +31343,7 @@
         <v>0.11</v>
       </c>
       <c r="H909" s="2" t="n">
-        <v>46094.80440638823</v>
+        <v>46094.80440638889</v>
       </c>
     </row>
     <row r="910">
@@ -31377,7 +31377,7 @@
         <v>3.05</v>
       </c>
       <c r="H910" s="2" t="n">
-        <v>46081.80440639157</v>
+        <v>46081.80440638889</v>
       </c>
     </row>
     <row r="911">
@@ -31411,7 +31411,7 @@
         <v>3.21</v>
       </c>
       <c r="H911" s="2" t="n">
-        <v>46089.80440639487</v>
+        <v>46089.80440640046</v>
       </c>
     </row>
     <row r="912">
@@ -31445,7 +31445,7 @@
         <v>4.39</v>
       </c>
       <c r="H912" s="2" t="n">
-        <v>46091.80440639866</v>
+        <v>46091.80440640046</v>
       </c>
     </row>
     <row r="913">
@@ -31479,7 +31479,7 @@
         <v>0.13</v>
       </c>
       <c r="H913" s="2" t="n">
-        <v>46075.80440640193</v>
+        <v>46075.80440640046</v>
       </c>
     </row>
     <row r="914">
@@ -31513,7 +31513,7 @@
         <v>3.14</v>
       </c>
       <c r="H914" s="2" t="n">
-        <v>46078.80440640528</v>
+        <v>46078.80440640046</v>
       </c>
     </row>
     <row r="915">
@@ -31547,7 +31547,7 @@
         <v>3.55</v>
       </c>
       <c r="H915" s="2" t="n">
-        <v>46070.80440640861</v>
+        <v>46070.80440641204</v>
       </c>
     </row>
     <row r="916">
@@ -31581,7 +31581,7 @@
         <v>4.8</v>
       </c>
       <c r="H916" s="2" t="n">
-        <v>46066.80440641173</v>
+        <v>46066.80440641204</v>
       </c>
     </row>
     <row r="917">
@@ -31615,7 +31615,7 @@
         <v>4.27</v>
       </c>
       <c r="H917" s="2" t="n">
-        <v>46093.80440641504</v>
+        <v>46093.80440641204</v>
       </c>
     </row>
     <row r="918">
@@ -31649,7 +31649,7 @@
         <v>2</v>
       </c>
       <c r="H918" s="2" t="n">
-        <v>46091.8044064183</v>
+        <v>46091.80440642361</v>
       </c>
     </row>
     <row r="919">
@@ -31683,7 +31683,7 @@
         <v>0.71</v>
       </c>
       <c r="H919" s="2" t="n">
-        <v>46072.80440642161</v>
+        <v>46072.80440642361</v>
       </c>
     </row>
     <row r="920">
@@ -31717,7 +31717,7 @@
         <v>1.92</v>
       </c>
       <c r="H920" s="2" t="n">
-        <v>46081.80440642474</v>
+        <v>46081.80440642361</v>
       </c>
     </row>
     <row r="921">
@@ -31751,7 +31751,7 @@
         <v>4.03</v>
       </c>
       <c r="H921" s="2" t="n">
-        <v>46078.80440642796</v>
+        <v>46078.80440642361</v>
       </c>
     </row>
     <row r="922">
@@ -31785,7 +31785,7 @@
         <v>3.18</v>
       </c>
       <c r="H922" s="2" t="n">
-        <v>46076.80440643107</v>
+        <v>46076.80440643519</v>
       </c>
     </row>
     <row r="923">
@@ -31819,7 +31819,7 @@
         <v>3.21</v>
       </c>
       <c r="H923" s="2" t="n">
-        <v>46072.80440643505</v>
+        <v>46072.80440643519</v>
       </c>
     </row>
     <row r="924">
@@ -31853,7 +31853,7 @@
         <v>0.84</v>
       </c>
       <c r="H924" s="2" t="n">
-        <v>46071.80440643826</v>
+        <v>46071.80440643519</v>
       </c>
     </row>
     <row r="925">
@@ -31887,7 +31887,7 @@
         <v>3.16</v>
       </c>
       <c r="H925" s="2" t="n">
-        <v>46065.80440644147</v>
+        <v>46065.80440644676</v>
       </c>
     </row>
     <row r="926">
@@ -31921,7 +31921,7 @@
         <v>2.43</v>
       </c>
       <c r="H926" s="2" t="n">
-        <v>46094.80440644494</v>
+        <v>46094.80440644676</v>
       </c>
     </row>
     <row r="927">
@@ -31955,7 +31955,7 @@
         <v>3.88</v>
       </c>
       <c r="H927" s="2" t="n">
-        <v>46075.80440644809</v>
+        <v>46075.80440644676</v>
       </c>
     </row>
     <row r="928">
@@ -31989,7 +31989,7 @@
         <v>0.73</v>
       </c>
       <c r="H928" s="2" t="n">
-        <v>46073.80440645119</v>
+        <v>46073.80440644676</v>
       </c>
     </row>
     <row r="929">
@@ -32023,7 +32023,7 @@
         <v>1.7</v>
       </c>
       <c r="H929" s="2" t="n">
-        <v>46082.80440645434</v>
+        <v>46082.80440645833</v>
       </c>
     </row>
     <row r="930">
@@ -32057,7 +32057,7 @@
         <v>2.14</v>
       </c>
       <c r="H930" s="2" t="n">
-        <v>46087.80440645762</v>
+        <v>46087.80440645833</v>
       </c>
     </row>
     <row r="931">
@@ -32091,7 +32091,7 @@
         <v>1.19</v>
       </c>
       <c r="H931" s="2" t="n">
-        <v>46093.80440646079</v>
+        <v>46093.80440645833</v>
       </c>
     </row>
     <row r="932">
@@ -32125,7 +32125,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="H932" s="2" t="n">
-        <v>46074.80440646412</v>
+        <v>46074.80440646991</v>
       </c>
     </row>
     <row r="933">
@@ -32159,7 +32159,7 @@
         <v>4.98</v>
       </c>
       <c r="H933" s="2" t="n">
-        <v>46085.80440646742</v>
+        <v>46085.80440646991</v>
       </c>
     </row>
     <row r="934">
@@ -32193,7 +32193,7 @@
         <v>2.49</v>
       </c>
       <c r="H934" s="2" t="n">
-        <v>46094.80440647055</v>
+        <v>46094.80440646991</v>
       </c>
     </row>
     <row r="935">
@@ -32227,7 +32227,7 @@
         <v>0.17</v>
       </c>
       <c r="H935" s="2" t="n">
-        <v>46068.80440647375</v>
+        <v>46068.80440646991</v>
       </c>
     </row>
     <row r="936">
@@ -32261,7 +32261,7 @@
         <v>3.29</v>
       </c>
       <c r="H936" s="2" t="n">
-        <v>46089.80440647683</v>
+        <v>46089.80440648148</v>
       </c>
     </row>
     <row r="937">
@@ -32295,7 +32295,7 @@
         <v>4.15</v>
       </c>
       <c r="H937" s="2" t="n">
-        <v>46083.80440648029</v>
+        <v>46083.80440648148</v>
       </c>
     </row>
     <row r="938">
@@ -32329,7 +32329,7 @@
         <v>3.73</v>
       </c>
       <c r="H938" s="2" t="n">
-        <v>46066.80440648388</v>
+        <v>46066.80440648148</v>
       </c>
     </row>
     <row r="939">
@@ -32363,7 +32363,7 @@
         <v>0.33</v>
       </c>
       <c r="H939" s="2" t="n">
-        <v>46069.80440648715</v>
+        <v>46069.80440648148</v>
       </c>
     </row>
     <row r="940">
@@ -32397,7 +32397,7 @@
         <v>2.56</v>
       </c>
       <c r="H940" s="2" t="n">
-        <v>46080.80440649046</v>
+        <v>46080.80440649306</v>
       </c>
     </row>
     <row r="941">
@@ -32431,7 +32431,7 @@
         <v>2.13</v>
       </c>
       <c r="H941" s="2" t="n">
-        <v>46070.80440649367</v>
+        <v>46070.80440649306</v>
       </c>
     </row>
     <row r="942">
@@ -32465,7 +32465,7 @@
         <v>3.02</v>
       </c>
       <c r="H942" s="2" t="n">
-        <v>46066.80440649675</v>
+        <v>46066.80440649306</v>
       </c>
     </row>
     <row r="943">
@@ -32499,7 +32499,7 @@
         <v>4.94</v>
       </c>
       <c r="H943" s="2" t="n">
-        <v>46083.80440650001</v>
+        <v>46083.80440650463</v>
       </c>
     </row>
     <row r="944">
@@ -32533,7 +32533,7 @@
         <v>2.81</v>
       </c>
       <c r="H944" s="2" t="n">
-        <v>46070.80440650333</v>
+        <v>46070.80440650463</v>
       </c>
     </row>
     <row r="945">
@@ -32567,7 +32567,7 @@
         <v>4.38</v>
       </c>
       <c r="H945" s="2" t="n">
-        <v>46090.80440650639</v>
+        <v>46090.80440650463</v>
       </c>
     </row>
     <row r="946">
@@ -32601,7 +32601,7 @@
         <v>3.92</v>
       </c>
       <c r="H946" s="2" t="n">
-        <v>46067.80440650963</v>
+        <v>46067.80440650463</v>
       </c>
     </row>
     <row r="947">
@@ -32635,7 +32635,7 @@
         <v>0.96</v>
       </c>
       <c r="H947" s="2" t="n">
-        <v>46086.80440651299</v>
+        <v>46086.8044065162</v>
       </c>
     </row>
     <row r="948">
@@ -32669,7 +32669,7 @@
         <v>4.78</v>
       </c>
       <c r="H948" s="2" t="n">
-        <v>46090.80440651625</v>
+        <v>46090.8044065162</v>
       </c>
     </row>
     <row r="949">
@@ -32703,7 +32703,7 @@
         <v>2.48</v>
       </c>
       <c r="H949" s="2" t="n">
-        <v>46092.8044065195</v>
+        <v>46092.8044065162</v>
       </c>
     </row>
     <row r="950">
@@ -32737,7 +32737,7 @@
         <v>0.6</v>
       </c>
       <c r="H950" s="2" t="n">
-        <v>46082.80440652255</v>
+        <v>46082.80440652778</v>
       </c>
     </row>
     <row r="951">
@@ -32771,7 +32771,1707 @@
         <v>2.38</v>
       </c>
       <c r="H951" s="2" t="n">
-        <v>46075.80440652594</v>
+        <v>46075.80440652778</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>a02685a3-06d6-44f7-8ea3-dc4588f6c547</t>
+        </is>
+      </c>
+      <c r="B952" t="n">
+        <v>95</v>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F952" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="G952" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H952" s="2" t="n">
+        <v>46069.8449306226</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>304cf696-fdda-4cff-b693-bd08f6a45d2d</t>
+        </is>
+      </c>
+      <c r="B953" t="n">
+        <v>95</v>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F953" t="n">
+        <v>342.73</v>
+      </c>
+      <c r="G953" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="H953" s="2" t="n">
+        <v>46093.844930627</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>b7399f78-afe6-4d4c-8b73-131fc07e692b</t>
+        </is>
+      </c>
+      <c r="B954" t="n">
+        <v>95</v>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F954" t="n">
+        <v>144.89</v>
+      </c>
+      <c r="G954" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H954" s="2" t="n">
+        <v>46087.84493063045</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>47b425cf-bf57-45e4-8111-32e7b3face78</t>
+        </is>
+      </c>
+      <c r="B955" t="n">
+        <v>95</v>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F955" t="n">
+        <v>285.85</v>
+      </c>
+      <c r="G955" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H955" s="2" t="n">
+        <v>46067.8449306342</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>965ec4c0-6e8d-48c7-a87c-f39796e78c12</t>
+        </is>
+      </c>
+      <c r="B956" t="n">
+        <v>95</v>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F956" t="n">
+        <v>208.88</v>
+      </c>
+      <c r="G956" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="H956" s="2" t="n">
+        <v>46082.84493063729</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>b5295492-2520-4373-bb3e-a3fb01f98a8f</t>
+        </is>
+      </c>
+      <c r="B957" t="n">
+        <v>95</v>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F957" t="n">
+        <v>455.69</v>
+      </c>
+      <c r="G957" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="H957" s="2" t="n">
+        <v>46066.84493064057</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>a8e216dc-a773-4d4d-b0c8-c4c52e979300</t>
+        </is>
+      </c>
+      <c r="B958" t="n">
+        <v>95</v>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F958" t="n">
+        <v>175.68</v>
+      </c>
+      <c r="G958" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H958" s="2" t="n">
+        <v>46094.84493064421</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>c4ad7838-72b7-4b00-83eb-abe6019300d0</t>
+        </is>
+      </c>
+      <c r="B959" t="n">
+        <v>95</v>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F959" t="n">
+        <v>234.57</v>
+      </c>
+      <c r="G959" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="H959" s="2" t="n">
+        <v>46078.84493064745</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>1b2493fe-1e16-4136-a930-639e79debe08</t>
+        </is>
+      </c>
+      <c r="B960" t="n">
+        <v>95</v>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F960" t="n">
+        <v>438.78</v>
+      </c>
+      <c r="G960" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="H960" s="2" t="n">
+        <v>46073.8449306506</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>11a96b3b-ba33-4765-8c3d-2c27efc88d75</t>
+        </is>
+      </c>
+      <c r="B961" t="n">
+        <v>95</v>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F961" t="n">
+        <v>376.53</v>
+      </c>
+      <c r="G961" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="H961" s="2" t="n">
+        <v>46068.84493065396</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>790b43a1-147d-4da1-9c99-dfd6e10961ac</t>
+        </is>
+      </c>
+      <c r="B962" t="n">
+        <v>95</v>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F962" t="n">
+        <v>498.5</v>
+      </c>
+      <c r="G962" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="H962" s="2" t="n">
+        <v>46087.84493065743</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>f0d987e5-7cf8-4d53-acc8-8586c7471d51</t>
+        </is>
+      </c>
+      <c r="B963" t="n">
+        <v>95</v>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F963" t="n">
+        <v>292.8</v>
+      </c>
+      <c r="G963" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="H963" s="2" t="n">
+        <v>46080.84493066058</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>f33e0e7b-3c18-4892-95d1-1b9df8c2e7a7</t>
+        </is>
+      </c>
+      <c r="B964" t="n">
+        <v>95</v>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F964" t="n">
+        <v>409.59</v>
+      </c>
+      <c r="G964" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H964" s="2" t="n">
+        <v>46084.84493066376</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>e0e16ca1-3de2-4638-b0a2-10a853767c26</t>
+        </is>
+      </c>
+      <c r="B965" t="n">
+        <v>95</v>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F965" t="n">
+        <v>414.61</v>
+      </c>
+      <c r="G965" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="H965" s="2" t="n">
+        <v>46070.84493066757</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>392bf59a-f913-4032-a826-4679f6282e07</t>
+        </is>
+      </c>
+      <c r="B966" t="n">
+        <v>95</v>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F966" t="n">
+        <v>257.53</v>
+      </c>
+      <c r="G966" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H966" s="2" t="n">
+        <v>46077.84493067072</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>c0d2b5f6-cbcb-4d70-8f49-9fddb9bbf7ae</t>
+        </is>
+      </c>
+      <c r="B967" t="n">
+        <v>95</v>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F967" t="n">
+        <v>169.91</v>
+      </c>
+      <c r="G967" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H967" s="2" t="n">
+        <v>46080.8449306738</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>0c1f8b65-9504-405d-a705-2d026fa3c8bc</t>
+        </is>
+      </c>
+      <c r="B968" t="n">
+        <v>95</v>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F968" t="n">
+        <v>326.24</v>
+      </c>
+      <c r="G968" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="H968" s="2" t="n">
+        <v>46083.8449306769</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>ead207e9-1408-4986-bd6e-0e94afe16d3d</t>
+        </is>
+      </c>
+      <c r="B969" t="n">
+        <v>95</v>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F969" t="n">
+        <v>490.72</v>
+      </c>
+      <c r="G969" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="H969" s="2" t="n">
+        <v>46091.8449306804</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>338c6d71-a408-4308-869a-3436a0c91e83</t>
+        </is>
+      </c>
+      <c r="B970" t="n">
+        <v>95</v>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F970" t="n">
+        <v>305.76</v>
+      </c>
+      <c r="G970" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="H970" s="2" t="n">
+        <v>46072.84493068359</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>0a10f249-13da-4371-a199-75c2ad82d491</t>
+        </is>
+      </c>
+      <c r="B971" t="n">
+        <v>95</v>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F971" t="n">
+        <v>461.53</v>
+      </c>
+      <c r="G971" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="H971" s="2" t="n">
+        <v>46081.84493068662</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>1fa7119d-faf3-4ffb-8b83-393a06318af2</t>
+        </is>
+      </c>
+      <c r="B972" t="n">
+        <v>95</v>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F972" t="n">
+        <v>224.69</v>
+      </c>
+      <c r="G972" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H972" s="2" t="n">
+        <v>46085.84493069004</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>2a21b7cc-3384-4997-8661-e6758f68394f</t>
+        </is>
+      </c>
+      <c r="B973" t="n">
+        <v>95</v>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F973" t="n">
+        <v>105.43</v>
+      </c>
+      <c r="G973" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H973" s="2" t="n">
+        <v>46079.84493069317</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>a99acec5-6416-4490-a246-eb2ec8d719d7</t>
+        </is>
+      </c>
+      <c r="B974" t="n">
+        <v>95</v>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F974" t="n">
+        <v>26.31</v>
+      </c>
+      <c r="G974" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H974" s="2" t="n">
+        <v>46079.84493069621</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>0f25cd74-4a8a-4231-805b-c3c7663cc5b1</t>
+        </is>
+      </c>
+      <c r="B975" t="n">
+        <v>95</v>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F975" t="n">
+        <v>478.7</v>
+      </c>
+      <c r="G975" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="H975" s="2" t="n">
+        <v>46094.84493069941</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>5efd4503-96f5-4fb2-824f-e667ac52c10b</t>
+        </is>
+      </c>
+      <c r="B976" t="n">
+        <v>95</v>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F976" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="G976" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H976" s="2" t="n">
+        <v>46090.84493070267</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>9af21df8-cd51-4502-94ce-f3553d0928a4</t>
+        </is>
+      </c>
+      <c r="B977" t="n">
+        <v>95</v>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F977" t="n">
+        <v>192.42</v>
+      </c>
+      <c r="G977" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H977" s="2" t="n">
+        <v>46073.84493070588</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>8319d142-4654-4038-ae44-51c3cb160448</t>
+        </is>
+      </c>
+      <c r="B978" t="n">
+        <v>95</v>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F978" t="n">
+        <v>427.73</v>
+      </c>
+      <c r="G978" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="H978" s="2" t="n">
+        <v>46088.84493070896</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>135adb38-7f11-4675-965f-d978a472b278</t>
+        </is>
+      </c>
+      <c r="B979" t="n">
+        <v>95</v>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F979" t="n">
+        <v>354.61</v>
+      </c>
+      <c r="G979" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H979" s="2" t="n">
+        <v>46093.84493071212</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>5f288a9f-0801-4d04-bc47-937e6ebfa0a3</t>
+        </is>
+      </c>
+      <c r="B980" t="n">
+        <v>95</v>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F980" t="n">
+        <v>254.03</v>
+      </c>
+      <c r="G980" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H980" s="2" t="n">
+        <v>46070.84493071572</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>079795f7-bd4d-4e1b-ae9c-d39e2ef2904b</t>
+        </is>
+      </c>
+      <c r="B981" t="n">
+        <v>95</v>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F981" t="n">
+        <v>468.95</v>
+      </c>
+      <c r="G981" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="H981" s="2" t="n">
+        <v>46082.84493071904</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>3b70566f-9d15-4d01-9994-1ccffe8e9f0e</t>
+        </is>
+      </c>
+      <c r="B982" t="n">
+        <v>95</v>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F982" t="n">
+        <v>182.54</v>
+      </c>
+      <c r="G982" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H982" s="2" t="n">
+        <v>46068.84493072213</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>b2cd0119-099a-4406-89ca-34cbb74ffaf4</t>
+        </is>
+      </c>
+      <c r="B983" t="n">
+        <v>95</v>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F983" t="n">
+        <v>91.25</v>
+      </c>
+      <c r="G983" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H983" s="2" t="n">
+        <v>46092.8449307255</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>1b415b2a-42ab-4c43-a205-2a2e67a566e4</t>
+        </is>
+      </c>
+      <c r="B984" t="n">
+        <v>95</v>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F984" t="n">
+        <v>191.41</v>
+      </c>
+      <c r="G984" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H984" s="2" t="n">
+        <v>46092.8449307287</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>15589b64-caec-4170-8f0e-27ef9bcdcd14</t>
+        </is>
+      </c>
+      <c r="B985" t="n">
+        <v>95</v>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F985" t="n">
+        <v>327.3</v>
+      </c>
+      <c r="G985" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="H985" s="2" t="n">
+        <v>46090.84493073195</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>af9ee15b-eb37-401b-a7df-624a933df8f8</t>
+        </is>
+      </c>
+      <c r="B986" t="n">
+        <v>95</v>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F986" t="n">
+        <v>261.85</v>
+      </c>
+      <c r="G986" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H986" s="2" t="n">
+        <v>46076.84493073495</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>041865dc-2220-400d-ac7e-c94b308542a3</t>
+        </is>
+      </c>
+      <c r="B987" t="n">
+        <v>95</v>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F987" t="n">
+        <v>158.94</v>
+      </c>
+      <c r="G987" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H987" s="2" t="n">
+        <v>46079.84493073834</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>5bfe573b-451d-477f-bbe1-8fbe1e39daf8</t>
+        </is>
+      </c>
+      <c r="B988" t="n">
+        <v>95</v>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F988" t="n">
+        <v>496.99</v>
+      </c>
+      <c r="G988" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="H988" s="2" t="n">
+        <v>46088.84493074143</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>53ef4842-e00b-4f4b-8768-707b0a2a6370</t>
+        </is>
+      </c>
+      <c r="B989" t="n">
+        <v>95</v>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F989" t="n">
+        <v>52.63</v>
+      </c>
+      <c r="G989" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H989" s="2" t="n">
+        <v>46072.84493074451</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>4ac33e31-b837-4db2-a3fb-818d4181dbb4</t>
+        </is>
+      </c>
+      <c r="B990" t="n">
+        <v>95</v>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F990" t="n">
+        <v>258.79</v>
+      </c>
+      <c r="G990" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="H990" s="2" t="n">
+        <v>46069.84493074784</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>96a62cd2-1fbb-42e7-a6c6-80117f8b68e6</t>
+        </is>
+      </c>
+      <c r="B991" t="n">
+        <v>95</v>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F991" t="n">
+        <v>83.47</v>
+      </c>
+      <c r="G991" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H991" s="2" t="n">
+        <v>46072.84493075091</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>3d31088d-2f2a-4efd-9a69-b795777050d9</t>
+        </is>
+      </c>
+      <c r="B992" t="n">
+        <v>95</v>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F992" t="n">
+        <v>304.29</v>
+      </c>
+      <c r="G992" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="H992" s="2" t="n">
+        <v>46089.84493075535</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>7634b231-a06c-4835-a6d1-12120884b16a</t>
+        </is>
+      </c>
+      <c r="B993" t="n">
+        <v>95</v>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F993" t="n">
+        <v>431.96</v>
+      </c>
+      <c r="G993" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="H993" s="2" t="n">
+        <v>46091.84493075847</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>83471ce2-d99b-4d0a-8ca8-78d4573296b6</t>
+        </is>
+      </c>
+      <c r="B994" t="n">
+        <v>95</v>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F994" t="n">
+        <v>216.94</v>
+      </c>
+      <c r="G994" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="H994" s="2" t="n">
+        <v>46068.84493076205</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>4f6ded20-4a22-40ac-9cfd-0e734d4892f3</t>
+        </is>
+      </c>
+      <c r="B995" t="n">
+        <v>95</v>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F995" t="n">
+        <v>148.07</v>
+      </c>
+      <c r="G995" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H995" s="2" t="n">
+        <v>46078.84493076512</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>be961253-cc99-42aa-8fca-b11a974c87ba</t>
+        </is>
+      </c>
+      <c r="B996" t="n">
+        <v>95</v>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F996" t="n">
+        <v>33.13</v>
+      </c>
+      <c r="G996" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H996" s="2" t="n">
+        <v>46077.84493076826</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>1fb8479e-4e53-4969-900d-0172a0a877a1</t>
+        </is>
+      </c>
+      <c r="B997" t="n">
+        <v>95</v>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F997" t="n">
+        <v>291.59</v>
+      </c>
+      <c r="G997" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H997" s="2" t="n">
+        <v>46083.84493077166</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>1fc1e725-31ae-4d22-b93a-45c1aa8f6f42</t>
+        </is>
+      </c>
+      <c r="B998" t="n">
+        <v>95</v>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F998" t="n">
+        <v>204.33</v>
+      </c>
+      <c r="G998" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H998" s="2" t="n">
+        <v>46087.84493077474</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>809465fc-383a-4da2-81e1-852e4f415c41</t>
+        </is>
+      </c>
+      <c r="B999" t="n">
+        <v>95</v>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F999" t="n">
+        <v>428.75</v>
+      </c>
+      <c r="G999" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="H999" s="2" t="n">
+        <v>46067.84493077818</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>1b3b5cd2-a1c7-4e9d-97f1-950018875e4e</t>
+        </is>
+      </c>
+      <c r="B1000" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1000" t="n">
+        <v>314.43</v>
+      </c>
+      <c r="G1000" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H1000" s="2" t="n">
+        <v>46071.84493078132</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>d316f029-e54a-4b26-bbdc-9f2b631a56a2</t>
+        </is>
+      </c>
+      <c r="B1001" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1001" t="n">
+        <v>261.05</v>
+      </c>
+      <c r="G1001" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="H1001" s="2" t="n">
+        <v>46081.84493078457</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1001"/>
+  <dimension ref="A1:H1051"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32805,7 +32805,7 @@
         <v>1.16</v>
       </c>
       <c r="H952" s="2" t="n">
-        <v>46069.8449306226</v>
+        <v>46069.844930625</v>
       </c>
     </row>
     <row r="953">
@@ -32839,7 +32839,7 @@
         <v>3.43</v>
       </c>
       <c r="H953" s="2" t="n">
-        <v>46093.844930627</v>
+        <v>46093.844930625</v>
       </c>
     </row>
     <row r="954">
@@ -32873,7 +32873,7 @@
         <v>1.45</v>
       </c>
       <c r="H954" s="2" t="n">
-        <v>46087.84493063045</v>
+        <v>46087.844930625</v>
       </c>
     </row>
     <row r="955">
@@ -32907,7 +32907,7 @@
         <v>2.86</v>
       </c>
       <c r="H955" s="2" t="n">
-        <v>46067.8449306342</v>
+        <v>46067.84493063657</v>
       </c>
     </row>
     <row r="956">
@@ -32941,7 +32941,7 @@
         <v>2.09</v>
       </c>
       <c r="H956" s="2" t="n">
-        <v>46082.84493063729</v>
+        <v>46082.84493063657</v>
       </c>
     </row>
     <row r="957">
@@ -32975,7 +32975,7 @@
         <v>4.56</v>
       </c>
       <c r="H957" s="2" t="n">
-        <v>46066.84493064057</v>
+        <v>46066.84493063657</v>
       </c>
     </row>
     <row r="958">
@@ -33009,7 +33009,7 @@
         <v>1.76</v>
       </c>
       <c r="H958" s="2" t="n">
-        <v>46094.84493064421</v>
+        <v>46094.84493064815</v>
       </c>
     </row>
     <row r="959">
@@ -33043,7 +33043,7 @@
         <v>2.35</v>
       </c>
       <c r="H959" s="2" t="n">
-        <v>46078.84493064745</v>
+        <v>46078.84493064815</v>
       </c>
     </row>
     <row r="960">
@@ -33077,7 +33077,7 @@
         <v>4.39</v>
       </c>
       <c r="H960" s="2" t="n">
-        <v>46073.8449306506</v>
+        <v>46073.84493064815</v>
       </c>
     </row>
     <row r="961">
@@ -33111,7 +33111,7 @@
         <v>3.77</v>
       </c>
       <c r="H961" s="2" t="n">
-        <v>46068.84493065396</v>
+        <v>46068.84493065972</v>
       </c>
     </row>
     <row r="962">
@@ -33145,7 +33145,7 @@
         <v>4.98</v>
       </c>
       <c r="H962" s="2" t="n">
-        <v>46087.84493065743</v>
+        <v>46087.84493065972</v>
       </c>
     </row>
     <row r="963">
@@ -33179,7 +33179,7 @@
         <v>2.93</v>
       </c>
       <c r="H963" s="2" t="n">
-        <v>46080.84493066058</v>
+        <v>46080.84493065972</v>
       </c>
     </row>
     <row r="964">
@@ -33213,7 +33213,7 @@
         <v>4.1</v>
       </c>
       <c r="H964" s="2" t="n">
-        <v>46084.84493066376</v>
+        <v>46084.84493065972</v>
       </c>
     </row>
     <row r="965">
@@ -33247,7 +33247,7 @@
         <v>4.15</v>
       </c>
       <c r="H965" s="2" t="n">
-        <v>46070.84493066757</v>
+        <v>46070.84493067129</v>
       </c>
     </row>
     <row r="966">
@@ -33281,7 +33281,7 @@
         <v>2.58</v>
       </c>
       <c r="H966" s="2" t="n">
-        <v>46077.84493067072</v>
+        <v>46077.84493067129</v>
       </c>
     </row>
     <row r="967">
@@ -33315,7 +33315,7 @@
         <v>1.7</v>
       </c>
       <c r="H967" s="2" t="n">
-        <v>46080.8449306738</v>
+        <v>46080.84493067129</v>
       </c>
     </row>
     <row r="968">
@@ -33349,7 +33349,7 @@
         <v>3.26</v>
       </c>
       <c r="H968" s="2" t="n">
-        <v>46083.8449306769</v>
+        <v>46083.84493067129</v>
       </c>
     </row>
     <row r="969">
@@ -33383,7 +33383,7 @@
         <v>4.91</v>
       </c>
       <c r="H969" s="2" t="n">
-        <v>46091.8449306804</v>
+        <v>46091.84493068287</v>
       </c>
     </row>
     <row r="970">
@@ -33417,7 +33417,7 @@
         <v>3.06</v>
       </c>
       <c r="H970" s="2" t="n">
-        <v>46072.84493068359</v>
+        <v>46072.84493068287</v>
       </c>
     </row>
     <row r="971">
@@ -33451,7 +33451,7 @@
         <v>4.62</v>
       </c>
       <c r="H971" s="2" t="n">
-        <v>46081.84493068662</v>
+        <v>46081.84493068287</v>
       </c>
     </row>
     <row r="972">
@@ -33485,7 +33485,7 @@
         <v>2.25</v>
       </c>
       <c r="H972" s="2" t="n">
-        <v>46085.84493069004</v>
+        <v>46085.84493069445</v>
       </c>
     </row>
     <row r="973">
@@ -33519,7 +33519,7 @@
         <v>1.05</v>
       </c>
       <c r="H973" s="2" t="n">
-        <v>46079.84493069317</v>
+        <v>46079.84493069445</v>
       </c>
     </row>
     <row r="974">
@@ -33553,7 +33553,7 @@
         <v>0.26</v>
       </c>
       <c r="H974" s="2" t="n">
-        <v>46079.84493069621</v>
+        <v>46079.84493069445</v>
       </c>
     </row>
     <row r="975">
@@ -33587,7 +33587,7 @@
         <v>4.79</v>
       </c>
       <c r="H975" s="2" t="n">
-        <v>46094.84493069941</v>
+        <v>46094.84493069445</v>
       </c>
     </row>
     <row r="976">
@@ -33621,7 +33621,7 @@
         <v>0.05</v>
       </c>
       <c r="H976" s="2" t="n">
-        <v>46090.84493070267</v>
+        <v>46090.84493070602</v>
       </c>
     </row>
     <row r="977">
@@ -33655,7 +33655,7 @@
         <v>1.92</v>
       </c>
       <c r="H977" s="2" t="n">
-        <v>46073.84493070588</v>
+        <v>46073.84493070602</v>
       </c>
     </row>
     <row r="978">
@@ -33689,7 +33689,7 @@
         <v>4.28</v>
       </c>
       <c r="H978" s="2" t="n">
-        <v>46088.84493070896</v>
+        <v>46088.84493070602</v>
       </c>
     </row>
     <row r="979">
@@ -33723,7 +33723,7 @@
         <v>3.55</v>
       </c>
       <c r="H979" s="2" t="n">
-        <v>46093.84493071212</v>
+        <v>46093.84493071759</v>
       </c>
     </row>
     <row r="980">
@@ -33757,7 +33757,7 @@
         <v>2.54</v>
       </c>
       <c r="H980" s="2" t="n">
-        <v>46070.84493071572</v>
+        <v>46070.84493071759</v>
       </c>
     </row>
     <row r="981">
@@ -33791,7 +33791,7 @@
         <v>4.69</v>
       </c>
       <c r="H981" s="2" t="n">
-        <v>46082.84493071904</v>
+        <v>46082.84493071759</v>
       </c>
     </row>
     <row r="982">
@@ -33825,7 +33825,7 @@
         <v>1.83</v>
       </c>
       <c r="H982" s="2" t="n">
-        <v>46068.84493072213</v>
+        <v>46068.84493071759</v>
       </c>
     </row>
     <row r="983">
@@ -33859,7 +33859,7 @@
         <v>0.91</v>
       </c>
       <c r="H983" s="2" t="n">
-        <v>46092.8449307255</v>
+        <v>46092.84493072917</v>
       </c>
     </row>
     <row r="984">
@@ -33893,7 +33893,7 @@
         <v>1.91</v>
       </c>
       <c r="H984" s="2" t="n">
-        <v>46092.8449307287</v>
+        <v>46092.84493072917</v>
       </c>
     </row>
     <row r="985">
@@ -33927,7 +33927,7 @@
         <v>3.27</v>
       </c>
       <c r="H985" s="2" t="n">
-        <v>46090.84493073195</v>
+        <v>46090.84493072917</v>
       </c>
     </row>
     <row r="986">
@@ -33961,7 +33961,7 @@
         <v>2.62</v>
       </c>
       <c r="H986" s="2" t="n">
-        <v>46076.84493073495</v>
+        <v>46076.84493072917</v>
       </c>
     </row>
     <row r="987">
@@ -33995,7 +33995,7 @@
         <v>1.59</v>
       </c>
       <c r="H987" s="2" t="n">
-        <v>46079.84493073834</v>
+        <v>46079.84493074074</v>
       </c>
     </row>
     <row r="988">
@@ -34029,7 +34029,7 @@
         <v>4.97</v>
       </c>
       <c r="H988" s="2" t="n">
-        <v>46088.84493074143</v>
+        <v>46088.84493074074</v>
       </c>
     </row>
     <row r="989">
@@ -34063,7 +34063,7 @@
         <v>0.53</v>
       </c>
       <c r="H989" s="2" t="n">
-        <v>46072.84493074451</v>
+        <v>46072.84493074074</v>
       </c>
     </row>
     <row r="990">
@@ -34097,7 +34097,7 @@
         <v>2.59</v>
       </c>
       <c r="H990" s="2" t="n">
-        <v>46069.84493074784</v>
+        <v>46069.84493075231</v>
       </c>
     </row>
     <row r="991">
@@ -34131,7 +34131,7 @@
         <v>0.83</v>
       </c>
       <c r="H991" s="2" t="n">
-        <v>46072.84493075091</v>
+        <v>46072.84493075231</v>
       </c>
     </row>
     <row r="992">
@@ -34165,7 +34165,7 @@
         <v>3.04</v>
       </c>
       <c r="H992" s="2" t="n">
-        <v>46089.84493075535</v>
+        <v>46089.84493075231</v>
       </c>
     </row>
     <row r="993">
@@ -34199,7 +34199,7 @@
         <v>4.32</v>
       </c>
       <c r="H993" s="2" t="n">
-        <v>46091.84493075847</v>
+        <v>46091.84493076389</v>
       </c>
     </row>
     <row r="994">
@@ -34233,7 +34233,7 @@
         <v>2.17</v>
       </c>
       <c r="H994" s="2" t="n">
-        <v>46068.84493076205</v>
+        <v>46068.84493076389</v>
       </c>
     </row>
     <row r="995">
@@ -34267,7 +34267,7 @@
         <v>1.48</v>
       </c>
       <c r="H995" s="2" t="n">
-        <v>46078.84493076512</v>
+        <v>46078.84493076389</v>
       </c>
     </row>
     <row r="996">
@@ -34301,7 +34301,7 @@
         <v>0.33</v>
       </c>
       <c r="H996" s="2" t="n">
-        <v>46077.84493076826</v>
+        <v>46077.84493076389</v>
       </c>
     </row>
     <row r="997">
@@ -34335,7 +34335,7 @@
         <v>2.92</v>
       </c>
       <c r="H997" s="2" t="n">
-        <v>46083.84493077166</v>
+        <v>46083.84493077546</v>
       </c>
     </row>
     <row r="998">
@@ -34369,7 +34369,7 @@
         <v>2.04</v>
       </c>
       <c r="H998" s="2" t="n">
-        <v>46087.84493077474</v>
+        <v>46087.84493077546</v>
       </c>
     </row>
     <row r="999">
@@ -34403,7 +34403,7 @@
         <v>4.29</v>
       </c>
       <c r="H999" s="2" t="n">
-        <v>46067.84493077818</v>
+        <v>46067.84493077546</v>
       </c>
     </row>
     <row r="1000">
@@ -34437,7 +34437,7 @@
         <v>3.14</v>
       </c>
       <c r="H1000" s="2" t="n">
-        <v>46071.84493078132</v>
+        <v>46071.84493078704</v>
       </c>
     </row>
     <row r="1001">
@@ -34471,7 +34471,1707 @@
         <v>2.61</v>
       </c>
       <c r="H1001" s="2" t="n">
-        <v>46081.84493078457</v>
+        <v>46081.84493078704</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>875050a1-b0ef-4e94-86df-99e81c6c7ac8</t>
+        </is>
+      </c>
+      <c r="B1002" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1002" t="n">
+        <v>102.27</v>
+      </c>
+      <c r="G1002" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H1002" s="2" t="n">
+        <v>46070.88617045216</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>f3362f22-aeca-4338-ba01-0fd14eab7ebc</t>
+        </is>
+      </c>
+      <c r="B1003" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1003" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="G1003" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H1003" s="2" t="n">
+        <v>46065.88617045641</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>d17de870-ea0d-4ca1-981f-7a372f1cc3ed</t>
+        </is>
+      </c>
+      <c r="B1004" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1004" t="n">
+        <v>434.86</v>
+      </c>
+      <c r="G1004" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="H1004" s="2" t="n">
+        <v>46088.88617045945</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>085d94d0-bba5-4ede-8990-ac9d7715c717</t>
+        </is>
+      </c>
+      <c r="B1005" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1005" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="G1005" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H1005" s="2" t="n">
+        <v>46068.88617046311</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>dfc41205-7812-4be0-b610-292704959829</t>
+        </is>
+      </c>
+      <c r="B1006" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1006" t="n">
+        <v>483.04</v>
+      </c>
+      <c r="G1006" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="H1006" s="2" t="n">
+        <v>46078.88617046604</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>34e52add-1e4c-4f41-9352-cb81d8e52b35</t>
+        </is>
+      </c>
+      <c r="B1007" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1007" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="G1007" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H1007" s="2" t="n">
+        <v>46083.88617046904</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>03be5c79-3899-4ed0-8795-ce3f154a3fc3</t>
+        </is>
+      </c>
+      <c r="B1008" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1008" t="n">
+        <v>360.87</v>
+      </c>
+      <c r="G1008" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="H1008" s="2" t="n">
+        <v>46081.88617047207</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>cd51a6aa-170b-4a6e-957b-c1a47c6b694e</t>
+        </is>
+      </c>
+      <c r="B1009" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1009" t="n">
+        <v>240.33</v>
+      </c>
+      <c r="G1009" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H1009" s="2" t="n">
+        <v>46086.88617047514</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>55eae441-a279-4cc0-85e1-b065a1b05edb</t>
+        </is>
+      </c>
+      <c r="B1010" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1010" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1010" t="n">
+        <v>200.1</v>
+      </c>
+      <c r="G1010" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1010" s="2" t="n">
+        <v>46074.88617047802</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>f4a7d138-c478-4311-a08b-20a94c868aec</t>
+        </is>
+      </c>
+      <c r="B1011" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1011" t="n">
+        <v>418.07</v>
+      </c>
+      <c r="G1011" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="H1011" s="2" t="n">
+        <v>46076.88617048087</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>74257408-7a9f-4c95-978a-026cadefec3e</t>
+        </is>
+      </c>
+      <c r="B1012" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1012" t="n">
+        <v>132.6</v>
+      </c>
+      <c r="G1012" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H1012" s="2" t="n">
+        <v>46073.88617048383</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>f2bc2587-8dfc-4747-8f1b-4f93a4a4b188</t>
+        </is>
+      </c>
+      <c r="B1013" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1013" t="n">
+        <v>336.29</v>
+      </c>
+      <c r="G1013" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="H1013" s="2" t="n">
+        <v>46072.88617048682</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>45c2bb71-eb62-4e4a-9282-2cafa0d9d95a</t>
+        </is>
+      </c>
+      <c r="B1014" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1014" t="n">
+        <v>231.6</v>
+      </c>
+      <c r="G1014" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H1014" s="2" t="n">
+        <v>46093.88617048982</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>5c13ff06-e031-42b0-9395-8136eb255c62</t>
+        </is>
+      </c>
+      <c r="B1015" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1015" t="n">
+        <v>294.02</v>
+      </c>
+      <c r="G1015" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H1015" s="2" t="n">
+        <v>46066.88617049275</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>32f54874-ada2-4f62-8679-58e497aa4a82</t>
+        </is>
+      </c>
+      <c r="B1016" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1016" t="n">
+        <v>247.27</v>
+      </c>
+      <c r="G1016" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="H1016" s="2" t="n">
+        <v>46078.88617049567</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>54588a3b-e495-4748-a156-7f1eefb878ad</t>
+        </is>
+      </c>
+      <c r="B1017" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1017" t="n">
+        <v>151.84</v>
+      </c>
+      <c r="G1017" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="H1017" s="2" t="n">
+        <v>46070.88617049868</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>e4ee32e5-7e60-45eb-a213-c679be87c8bf</t>
+        </is>
+      </c>
+      <c r="B1018" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1018" t="n">
+        <v>335</v>
+      </c>
+      <c r="G1018" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H1018" s="2" t="n">
+        <v>46083.88617050152</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>3c7f8b0c-0c18-4be1-9f2a-2025c68e1257</t>
+        </is>
+      </c>
+      <c r="B1019" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1019" t="n">
+        <v>462.69</v>
+      </c>
+      <c r="G1019" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="H1019" s="2" t="n">
+        <v>46093.88617050457</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>81deb3c4-c0a5-4a5f-b5c4-3576d080737e</t>
+        </is>
+      </c>
+      <c r="B1020" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1020" t="n">
+        <v>33.96</v>
+      </c>
+      <c r="G1020" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H1020" s="2" t="n">
+        <v>46066.88617050766</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>e6d9ae79-3ecf-4735-bd91-f7bb2e52b5a3</t>
+        </is>
+      </c>
+      <c r="B1021" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1021" t="n">
+        <v>373.94</v>
+      </c>
+      <c r="G1021" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H1021" s="2" t="n">
+        <v>46083.88617051047</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>480b6348-d27b-421f-a0f2-08e1c021db70</t>
+        </is>
+      </c>
+      <c r="B1022" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1022" t="n">
+        <v>423.24</v>
+      </c>
+      <c r="G1022" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="H1022" s="2" t="n">
+        <v>46080.8861705133</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>415db6e1-e911-403d-848a-949773067834</t>
+        </is>
+      </c>
+      <c r="B1023" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1023" t="n">
+        <v>461.51</v>
+      </c>
+      <c r="G1023" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="H1023" s="2" t="n">
+        <v>46075.88617051615</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>ab24f9d3-e916-4b00-8d41-19126de3f241</t>
+        </is>
+      </c>
+      <c r="B1024" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1024" t="n">
+        <v>365.18</v>
+      </c>
+      <c r="G1024" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H1024" s="2" t="n">
+        <v>46065.88617051918</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>a3d3aadc-5143-4b43-ac28-e76e9f4d6e06</t>
+        </is>
+      </c>
+      <c r="B1025" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1025" t="n">
+        <v>36.55</v>
+      </c>
+      <c r="G1025" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H1025" s="2" t="n">
+        <v>46085.88617052201</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>2fbdead1-9d5c-499f-af78-1bf7785c6052</t>
+        </is>
+      </c>
+      <c r="B1026" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1026" t="n">
+        <v>193.93</v>
+      </c>
+      <c r="G1026" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H1026" s="2" t="n">
+        <v>46076.88617052481</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>7ba5b19f-ee0e-4d03-b8fd-c9107a28308e</t>
+        </is>
+      </c>
+      <c r="B1027" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1027" t="n">
+        <v>275.1</v>
+      </c>
+      <c r="G1027" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H1027" s="2" t="n">
+        <v>46072.8861705278</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>871552f8-cbb3-463f-9db0-e3aba46857ec</t>
+        </is>
+      </c>
+      <c r="B1028" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1028" t="n">
+        <v>140.99</v>
+      </c>
+      <c r="G1028" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H1028" s="2" t="n">
+        <v>46072.88617053084</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>32624650-aba6-436c-86dd-200e54a8f336</t>
+        </is>
+      </c>
+      <c r="B1029" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1029" t="n">
+        <v>446.88</v>
+      </c>
+      <c r="G1029" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="H1029" s="2" t="n">
+        <v>46085.88617053386</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>ceb9a8fb-089a-4db7-9ecf-e7ff7bd42b95</t>
+        </is>
+      </c>
+      <c r="B1030" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1030" t="n">
+        <v>497.92</v>
+      </c>
+      <c r="G1030" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="H1030" s="2" t="n">
+        <v>46077.88617053667</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>85529bde-7020-4411-afb1-c1de2aee00a2</t>
+        </is>
+      </c>
+      <c r="B1031" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1031" t="n">
+        <v>453.11</v>
+      </c>
+      <c r="G1031" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="H1031" s="2" t="n">
+        <v>46080.88617053944</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>04993d78-9dd2-4545-b5af-6d94a67541d9</t>
+        </is>
+      </c>
+      <c r="B1032" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1032" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="G1032" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H1032" s="2" t="n">
+        <v>46082.8861705426</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>43d41146-64a8-4730-84e5-1f233298a0f2</t>
+        </is>
+      </c>
+      <c r="B1033" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1033" t="n">
+        <v>442.57</v>
+      </c>
+      <c r="G1033" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="H1033" s="2" t="n">
+        <v>46065.8861705454</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>da4fcc85-22ac-481b-addf-21e4047018ac</t>
+        </is>
+      </c>
+      <c r="B1034" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1034" t="n">
+        <v>225.08</v>
+      </c>
+      <c r="G1034" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H1034" s="2" t="n">
+        <v>46083.88617054823</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>8c099825-0e00-42ab-aed1-9bcc3ce88c9c</t>
+        </is>
+      </c>
+      <c r="B1035" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1035" t="n">
+        <v>429.42</v>
+      </c>
+      <c r="G1035" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="H1035" s="2" t="n">
+        <v>46093.88617055114</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>0fa0c178-3331-4262-b3b0-2cecb4f0129f</t>
+        </is>
+      </c>
+      <c r="B1036" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1036" t="n">
+        <v>81.48999999999999</v>
+      </c>
+      <c r="G1036" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H1036" s="2" t="n">
+        <v>46070.88617055416</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>e6b70cec-a923-431b-9ae6-3bd1d9a5012a</t>
+        </is>
+      </c>
+      <c r="B1037" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1037" t="n">
+        <v>404.9</v>
+      </c>
+      <c r="G1037" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="H1037" s="2" t="n">
+        <v>46093.88617055702</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>73fc9a67-9098-4274-86cf-310aa345714e</t>
+        </is>
+      </c>
+      <c r="B1038" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1038" t="n">
+        <v>132.99</v>
+      </c>
+      <c r="G1038" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H1038" s="2" t="n">
+        <v>46082.88617055984</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>bcc971a8-905a-4f4b-b4aa-d274c37721f4</t>
+        </is>
+      </c>
+      <c r="B1039" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1039" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="G1039" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H1039" s="2" t="n">
+        <v>46080.88617056284</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>b9d3e107-be28-4d4d-a16d-f3c09866bdb8</t>
+        </is>
+      </c>
+      <c r="B1040" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1040" t="n">
+        <v>118.23</v>
+      </c>
+      <c r="G1040" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H1040" s="2" t="n">
+        <v>46072.88617056587</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>c206dd25-25cb-48f8-8fb2-f2e135c6db25</t>
+        </is>
+      </c>
+      <c r="B1041" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1041" t="n">
+        <v>78.17</v>
+      </c>
+      <c r="G1041" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H1041" s="2" t="n">
+        <v>46086.88617056867</v>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>61cbdc40-c5de-482d-ab85-16f77a521bae</t>
+        </is>
+      </c>
+      <c r="B1042" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1042" t="n">
+        <v>263.17</v>
+      </c>
+      <c r="G1042" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="H1042" s="2" t="n">
+        <v>46082.88617057173</v>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>90ff5adf-5551-458a-b72f-334fa6cdb1ea</t>
+        </is>
+      </c>
+      <c r="B1043" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1043" t="n">
+        <v>213.67</v>
+      </c>
+      <c r="G1043" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H1043" s="2" t="n">
+        <v>46074.88617057456</v>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>45ec2436-9667-4e3c-abbd-8aee014e4f70</t>
+        </is>
+      </c>
+      <c r="B1044" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1044" t="n">
+        <v>497.19</v>
+      </c>
+      <c r="G1044" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="H1044" s="2" t="n">
+        <v>46066.88617057751</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>cd540633-7ba7-4907-9339-c0c06ee5d9af</t>
+        </is>
+      </c>
+      <c r="B1045" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1045" t="n">
+        <v>348.02</v>
+      </c>
+      <c r="G1045" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="H1045" s="2" t="n">
+        <v>46076.88617058032</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>1ce6cef6-2824-4c10-9906-cda4277265e1</t>
+        </is>
+      </c>
+      <c r="B1046" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1046" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1046" t="n">
+        <v>464.89</v>
+      </c>
+      <c r="G1046" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="H1046" s="2" t="n">
+        <v>46065.88617058318</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>ea18cdc6-44ec-4839-8a92-88e7dea25555</t>
+        </is>
+      </c>
+      <c r="B1047" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1047" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="G1047" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H1047" s="2" t="n">
+        <v>46069.88617058604</v>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>e3705764-7a95-4cca-9546-4cc768c99e09</t>
+        </is>
+      </c>
+      <c r="B1048" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1048" t="n">
+        <v>457.08</v>
+      </c>
+      <c r="G1048" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="H1048" s="2" t="n">
+        <v>46077.88617058911</v>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>514839d7-a1bd-43bf-938e-012c877db275</t>
+        </is>
+      </c>
+      <c r="B1049" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1049" t="n">
+        <v>465.82</v>
+      </c>
+      <c r="G1049" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="H1049" s="2" t="n">
+        <v>46082.88617059199</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>033f7bb8-f6c4-4624-ac08-cac683c3d702</t>
+        </is>
+      </c>
+      <c r="B1050" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1050" t="n">
+        <v>396.79</v>
+      </c>
+      <c r="G1050" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="H1050" s="2" t="n">
+        <v>46078.88617059489</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>b391d8c4-66f0-4f6a-b27d-48a27a466082</t>
+        </is>
+      </c>
+      <c r="B1051" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1051" t="n">
+        <v>150.12</v>
+      </c>
+      <c r="G1051" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H1051" s="2" t="n">
+        <v>46088.88617059783</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1051"/>
+  <dimension ref="A1:H1101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34505,7 +34505,7 @@
         <v>1.02</v>
       </c>
       <c r="H1002" s="2" t="n">
-        <v>46070.88617045216</v>
+        <v>46070.88617045139</v>
       </c>
     </row>
     <row r="1003">
@@ -34539,7 +34539,7 @@
         <v>0.08</v>
       </c>
       <c r="H1003" s="2" t="n">
-        <v>46065.88617045641</v>
+        <v>46065.88617045139</v>
       </c>
     </row>
     <row r="1004">
@@ -34573,7 +34573,7 @@
         <v>4.35</v>
       </c>
       <c r="H1004" s="2" t="n">
-        <v>46088.88617045945</v>
+        <v>46088.88617046296</v>
       </c>
     </row>
     <row r="1005">
@@ -34607,7 +34607,7 @@
         <v>0.06</v>
       </c>
       <c r="H1005" s="2" t="n">
-        <v>46068.88617046311</v>
+        <v>46068.88617046296</v>
       </c>
     </row>
     <row r="1006">
@@ -34641,7 +34641,7 @@
         <v>4.83</v>
       </c>
       <c r="H1006" s="2" t="n">
-        <v>46078.88617046604</v>
+        <v>46078.88617046296</v>
       </c>
     </row>
     <row r="1007">
@@ -34675,7 +34675,7 @@
         <v>0.23</v>
       </c>
       <c r="H1007" s="2" t="n">
-        <v>46083.88617046904</v>
+        <v>46083.88617047454</v>
       </c>
     </row>
     <row r="1008">
@@ -34709,7 +34709,7 @@
         <v>3.61</v>
       </c>
       <c r="H1008" s="2" t="n">
-        <v>46081.88617047207</v>
+        <v>46081.88617047454</v>
       </c>
     </row>
     <row r="1009">
@@ -34743,7 +34743,7 @@
         <v>2.4</v>
       </c>
       <c r="H1009" s="2" t="n">
-        <v>46086.88617047514</v>
+        <v>46086.88617047454</v>
       </c>
     </row>
     <row r="1010">
@@ -34777,7 +34777,7 @@
         <v>2</v>
       </c>
       <c r="H1010" s="2" t="n">
-        <v>46074.88617047802</v>
+        <v>46074.88617047454</v>
       </c>
     </row>
     <row r="1011">
@@ -34811,7 +34811,7 @@
         <v>4.18</v>
       </c>
       <c r="H1011" s="2" t="n">
-        <v>46076.88617048087</v>
+        <v>46076.88617048611</v>
       </c>
     </row>
     <row r="1012">
@@ -34845,7 +34845,7 @@
         <v>1.33</v>
       </c>
       <c r="H1012" s="2" t="n">
-        <v>46073.88617048383</v>
+        <v>46073.88617048611</v>
       </c>
     </row>
     <row r="1013">
@@ -34879,7 +34879,7 @@
         <v>3.36</v>
       </c>
       <c r="H1013" s="2" t="n">
-        <v>46072.88617048682</v>
+        <v>46072.88617048611</v>
       </c>
     </row>
     <row r="1014">
@@ -34913,7 +34913,7 @@
         <v>2.32</v>
       </c>
       <c r="H1014" s="2" t="n">
-        <v>46093.88617048982</v>
+        <v>46093.88617048611</v>
       </c>
     </row>
     <row r="1015">
@@ -34947,7 +34947,7 @@
         <v>2.94</v>
       </c>
       <c r="H1015" s="2" t="n">
-        <v>46066.88617049275</v>
+        <v>46066.88617049769</v>
       </c>
     </row>
     <row r="1016">
@@ -34981,7 +34981,7 @@
         <v>2.47</v>
       </c>
       <c r="H1016" s="2" t="n">
-        <v>46078.88617049567</v>
+        <v>46078.88617049769</v>
       </c>
     </row>
     <row r="1017">
@@ -35015,7 +35015,7 @@
         <v>1.52</v>
       </c>
       <c r="H1017" s="2" t="n">
-        <v>46070.88617049868</v>
+        <v>46070.88617049769</v>
       </c>
     </row>
     <row r="1018">
@@ -35049,7 +35049,7 @@
         <v>3.35</v>
       </c>
       <c r="H1018" s="2" t="n">
-        <v>46083.88617050152</v>
+        <v>46083.88617049769</v>
       </c>
     </row>
     <row r="1019">
@@ -35083,7 +35083,7 @@
         <v>4.63</v>
       </c>
       <c r="H1019" s="2" t="n">
-        <v>46093.88617050457</v>
+        <v>46093.88617050926</v>
       </c>
     </row>
     <row r="1020">
@@ -35117,7 +35117,7 @@
         <v>0.34</v>
       </c>
       <c r="H1020" s="2" t="n">
-        <v>46066.88617050766</v>
+        <v>46066.88617050926</v>
       </c>
     </row>
     <row r="1021">
@@ -35151,7 +35151,7 @@
         <v>3.74</v>
       </c>
       <c r="H1021" s="2" t="n">
-        <v>46083.88617051047</v>
+        <v>46083.88617050926</v>
       </c>
     </row>
     <row r="1022">
@@ -35185,7 +35185,7 @@
         <v>4.23</v>
       </c>
       <c r="H1022" s="2" t="n">
-        <v>46080.8861705133</v>
+        <v>46080.88617050926</v>
       </c>
     </row>
     <row r="1023">
@@ -35219,7 +35219,7 @@
         <v>4.62</v>
       </c>
       <c r="H1023" s="2" t="n">
-        <v>46075.88617051615</v>
+        <v>46075.88617052083</v>
       </c>
     </row>
     <row r="1024">
@@ -35253,7 +35253,7 @@
         <v>3.65</v>
       </c>
       <c r="H1024" s="2" t="n">
-        <v>46065.88617051918</v>
+        <v>46065.88617052083</v>
       </c>
     </row>
     <row r="1025">
@@ -35287,7 +35287,7 @@
         <v>0.37</v>
       </c>
       <c r="H1025" s="2" t="n">
-        <v>46085.88617052201</v>
+        <v>46085.88617052083</v>
       </c>
     </row>
     <row r="1026">
@@ -35321,7 +35321,7 @@
         <v>1.94</v>
       </c>
       <c r="H1026" s="2" t="n">
-        <v>46076.88617052481</v>
+        <v>46076.88617052083</v>
       </c>
     </row>
     <row r="1027">
@@ -35355,7 +35355,7 @@
         <v>2.75</v>
       </c>
       <c r="H1027" s="2" t="n">
-        <v>46072.8861705278</v>
+        <v>46072.88617053241</v>
       </c>
     </row>
     <row r="1028">
@@ -35389,7 +35389,7 @@
         <v>1.41</v>
       </c>
       <c r="H1028" s="2" t="n">
-        <v>46072.88617053084</v>
+        <v>46072.88617053241</v>
       </c>
     </row>
     <row r="1029">
@@ -35423,7 +35423,7 @@
         <v>4.47</v>
       </c>
       <c r="H1029" s="2" t="n">
-        <v>46085.88617053386</v>
+        <v>46085.88617053241</v>
       </c>
     </row>
     <row r="1030">
@@ -35457,7 +35457,7 @@
         <v>4.98</v>
       </c>
       <c r="H1030" s="2" t="n">
-        <v>46077.88617053667</v>
+        <v>46077.88617053241</v>
       </c>
     </row>
     <row r="1031">
@@ -35491,7 +35491,7 @@
         <v>4.53</v>
       </c>
       <c r="H1031" s="2" t="n">
-        <v>46080.88617053944</v>
+        <v>46080.88617054398</v>
       </c>
     </row>
     <row r="1032">
@@ -35525,7 +35525,7 @@
         <v>0.08</v>
       </c>
       <c r="H1032" s="2" t="n">
-        <v>46082.8861705426</v>
+        <v>46082.88617054398</v>
       </c>
     </row>
     <row r="1033">
@@ -35559,7 +35559,7 @@
         <v>4.43</v>
       </c>
       <c r="H1033" s="2" t="n">
-        <v>46065.8861705454</v>
+        <v>46065.88617054398</v>
       </c>
     </row>
     <row r="1034">
@@ -35593,7 +35593,7 @@
         <v>2.25</v>
       </c>
       <c r="H1034" s="2" t="n">
-        <v>46083.88617054823</v>
+        <v>46083.88617054398</v>
       </c>
     </row>
     <row r="1035">
@@ -35627,7 +35627,7 @@
         <v>4.29</v>
       </c>
       <c r="H1035" s="2" t="n">
-        <v>46093.88617055114</v>
+        <v>46093.88617055555</v>
       </c>
     </row>
     <row r="1036">
@@ -35661,7 +35661,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H1036" s="2" t="n">
-        <v>46070.88617055416</v>
+        <v>46070.88617055555</v>
       </c>
     </row>
     <row r="1037">
@@ -35695,7 +35695,7 @@
         <v>4.05</v>
       </c>
       <c r="H1037" s="2" t="n">
-        <v>46093.88617055702</v>
+        <v>46093.88617055555</v>
       </c>
     </row>
     <row r="1038">
@@ -35729,7 +35729,7 @@
         <v>1.33</v>
       </c>
       <c r="H1038" s="2" t="n">
-        <v>46082.88617055984</v>
+        <v>46082.88617055555</v>
       </c>
     </row>
     <row r="1039">
@@ -35763,7 +35763,7 @@
         <v>0.13</v>
       </c>
       <c r="H1039" s="2" t="n">
-        <v>46080.88617056284</v>
+        <v>46080.88617056713</v>
       </c>
     </row>
     <row r="1040">
@@ -35797,7 +35797,7 @@
         <v>1.18</v>
       </c>
       <c r="H1040" s="2" t="n">
-        <v>46072.88617056587</v>
+        <v>46072.88617056713</v>
       </c>
     </row>
     <row r="1041">
@@ -35831,7 +35831,7 @@
         <v>0.78</v>
       </c>
       <c r="H1041" s="2" t="n">
-        <v>46086.88617056867</v>
+        <v>46086.88617056713</v>
       </c>
     </row>
     <row r="1042">
@@ -35865,7 +35865,7 @@
         <v>2.63</v>
       </c>
       <c r="H1042" s="2" t="n">
-        <v>46082.88617057173</v>
+        <v>46082.88617056713</v>
       </c>
     </row>
     <row r="1043">
@@ -35899,7 +35899,7 @@
         <v>2.14</v>
       </c>
       <c r="H1043" s="2" t="n">
-        <v>46074.88617057456</v>
+        <v>46074.88617057871</v>
       </c>
     </row>
     <row r="1044">
@@ -35933,7 +35933,7 @@
         <v>4.97</v>
       </c>
       <c r="H1044" s="2" t="n">
-        <v>46066.88617057751</v>
+        <v>46066.88617057871</v>
       </c>
     </row>
     <row r="1045">
@@ -35967,7 +35967,7 @@
         <v>3.48</v>
       </c>
       <c r="H1045" s="2" t="n">
-        <v>46076.88617058032</v>
+        <v>46076.88617057871</v>
       </c>
     </row>
     <row r="1046">
@@ -36001,7 +36001,7 @@
         <v>4.65</v>
       </c>
       <c r="H1046" s="2" t="n">
-        <v>46065.88617058318</v>
+        <v>46065.88617057871</v>
       </c>
     </row>
     <row r="1047">
@@ -36035,7 +36035,7 @@
         <v>0.17</v>
       </c>
       <c r="H1047" s="2" t="n">
-        <v>46069.88617058604</v>
+        <v>46069.88617059027</v>
       </c>
     </row>
     <row r="1048">
@@ -36069,7 +36069,7 @@
         <v>4.57</v>
       </c>
       <c r="H1048" s="2" t="n">
-        <v>46077.88617058911</v>
+        <v>46077.88617059027</v>
       </c>
     </row>
     <row r="1049">
@@ -36103,7 +36103,7 @@
         <v>4.66</v>
       </c>
       <c r="H1049" s="2" t="n">
-        <v>46082.88617059199</v>
+        <v>46082.88617059027</v>
       </c>
     </row>
     <row r="1050">
@@ -36137,7 +36137,7 @@
         <v>3.97</v>
       </c>
       <c r="H1050" s="2" t="n">
-        <v>46078.88617059489</v>
+        <v>46078.88617059027</v>
       </c>
     </row>
     <row r="1051">
@@ -36171,7 +36171,1707 @@
         <v>1.5</v>
       </c>
       <c r="H1051" s="2" t="n">
-        <v>46088.88617059783</v>
+        <v>46088.88617060185</v>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>e16dabbd-1d2f-4339-b1cc-80a62f94afdf</t>
+        </is>
+      </c>
+      <c r="B1052" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1052" t="n">
+        <v>186.23</v>
+      </c>
+      <c r="G1052" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H1052" s="2" t="n">
+        <v>46093.92765186141</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>8f839f88-f48b-488a-a964-44395f0703cf</t>
+        </is>
+      </c>
+      <c r="B1053" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1053" t="n">
+        <v>409.64</v>
+      </c>
+      <c r="G1053" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H1053" s="2" t="n">
+        <v>46081.92765186596</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>75590bbb-a494-4465-808f-fb6b375fdadc</t>
+        </is>
+      </c>
+      <c r="B1054" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1054" t="n">
+        <v>436.51</v>
+      </c>
+      <c r="G1054" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="H1054" s="2" t="n">
+        <v>46070.92765186915</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>c05580c4-7618-4be4-bd64-e4761cfbd829</t>
+        </is>
+      </c>
+      <c r="B1055" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1055" t="n">
+        <v>143.56</v>
+      </c>
+      <c r="G1055" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H1055" s="2" t="n">
+        <v>46084.92765187251</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>5c262d93-398c-47a2-aaec-f5b18e59b71c</t>
+        </is>
+      </c>
+      <c r="B1056" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1056" t="n">
+        <v>373.43</v>
+      </c>
+      <c r="G1056" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="H1056" s="2" t="n">
+        <v>46079.92765187576</v>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>3a1e969f-61d3-4dfb-af1d-5f71b64e4e69</t>
+        </is>
+      </c>
+      <c r="B1057" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1057" t="n">
+        <v>95.05</v>
+      </c>
+      <c r="G1057" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H1057" s="2" t="n">
+        <v>46069.92765187928</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>4c69d7c4-4f6b-494a-a86f-5c2db622892c</t>
+        </is>
+      </c>
+      <c r="B1058" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1058" t="n">
+        <v>79.51000000000001</v>
+      </c>
+      <c r="G1058" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H1058" s="2" t="n">
+        <v>46067.9276518825</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>a1a0e509-e7f5-4cfa-ac65-796dee233ff3</t>
+        </is>
+      </c>
+      <c r="B1059" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1059" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="G1059" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H1059" s="2" t="n">
+        <v>46071.9276518856</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>7e5f596b-c489-4bd7-bfc2-a71c88138893</t>
+        </is>
+      </c>
+      <c r="B1060" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1060" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1060" t="n">
+        <v>456.27</v>
+      </c>
+      <c r="G1060" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="H1060" s="2" t="n">
+        <v>46074.92765188897</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>a5f22db9-f22c-48bf-8821-f090f0715fdc</t>
+        </is>
+      </c>
+      <c r="B1061" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1061" t="n">
+        <v>403.47</v>
+      </c>
+      <c r="G1061" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H1061" s="2" t="n">
+        <v>46069.92765189202</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>a0fc3a9a-6d1d-4ceb-a400-06e51faa868d</t>
+        </is>
+      </c>
+      <c r="B1062" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1062" t="n">
+        <v>326.95</v>
+      </c>
+      <c r="G1062" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="H1062" s="2" t="n">
+        <v>46078.92765189547</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>94a7a421-2c32-4eba-b98f-00028e8790ec</t>
+        </is>
+      </c>
+      <c r="B1063" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1063" t="n">
+        <v>47.06</v>
+      </c>
+      <c r="G1063" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H1063" s="2" t="n">
+        <v>46075.9276518987</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>e2bf5eb7-0b52-4bfb-bd7c-6f9307596561</t>
+        </is>
+      </c>
+      <c r="B1064" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1064" t="n">
+        <v>320.29</v>
+      </c>
+      <c r="G1064" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H1064" s="2" t="n">
+        <v>46084.92765190226</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>2462299b-6b78-4a77-a0c9-eb548d12cbd8</t>
+        </is>
+      </c>
+      <c r="B1065" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1065" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1065" t="n">
+        <v>349.75</v>
+      </c>
+      <c r="G1065" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H1065" s="2" t="n">
+        <v>46090.92765190562</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>2a80a252-8f36-4a58-b2a7-12b46645d3dc</t>
+        </is>
+      </c>
+      <c r="B1066" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1066" t="n">
+        <v>206.63</v>
+      </c>
+      <c r="G1066" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="H1066" s="2" t="n">
+        <v>46068.92765190881</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>93cdd32c-822a-41a4-9bca-2ca6611ee24e</t>
+        </is>
+      </c>
+      <c r="B1067" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1067" t="n">
+        <v>413.56</v>
+      </c>
+      <c r="G1067" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H1067" s="2" t="n">
+        <v>46075.92765191213</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>50bfdb89-c1b3-496e-9e23-7255dffdd35c</t>
+        </is>
+      </c>
+      <c r="B1068" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1068" t="n">
+        <v>310.67</v>
+      </c>
+      <c r="G1068" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="H1068" s="2" t="n">
+        <v>46066.92765191532</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>2a4f75df-ddc8-4388-a4a0-3580f3b3bc3e</t>
+        </is>
+      </c>
+      <c r="B1069" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1069" t="n">
+        <v>465.03</v>
+      </c>
+      <c r="G1069" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="H1069" s="2" t="n">
+        <v>46082.92765191841</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>fa54045f-c307-44c2-9cb2-4da9b00ace67</t>
+        </is>
+      </c>
+      <c r="B1070" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1070" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1070" t="n">
+        <v>409.28</v>
+      </c>
+      <c r="G1070" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="H1070" s="2" t="n">
+        <v>46082.92765192151</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>d95cb3e8-2d42-4707-bf30-ba372af93d33</t>
+        </is>
+      </c>
+      <c r="B1071" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1071" t="n">
+        <v>369.63</v>
+      </c>
+      <c r="G1071" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H1071" s="2" t="n">
+        <v>46070.92765192471</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>fd7e06d8-23a0-49fa-85f5-bf223431a177</t>
+        </is>
+      </c>
+      <c r="B1072" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1072" t="n">
+        <v>189.06</v>
+      </c>
+      <c r="G1072" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H1072" s="2" t="n">
+        <v>46085.92765192778</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>8bf7ce47-f41d-4170-aab9-3483db575959</t>
+        </is>
+      </c>
+      <c r="B1073" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1073" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1073" t="n">
+        <v>107.93</v>
+      </c>
+      <c r="G1073" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="H1073" s="2" t="n">
+        <v>46077.92765193082</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>d75a70de-9895-4467-9f7a-1bdbe489d936</t>
+        </is>
+      </c>
+      <c r="B1074" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1074" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1074" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="G1074" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H1074" s="2" t="n">
+        <v>46087.92765193393</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>1d50234b-0f7f-410c-8b0e-74ac6adae46b</t>
+        </is>
+      </c>
+      <c r="B1075" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1075" t="n">
+        <v>480.07</v>
+      </c>
+      <c r="G1075" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H1075" s="2" t="n">
+        <v>46084.92765193714</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>93c7e2e9-e4c5-45dd-8616-427bf268accb</t>
+        </is>
+      </c>
+      <c r="B1076" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1076" t="n">
+        <v>68.78</v>
+      </c>
+      <c r="G1076" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H1076" s="2" t="n">
+        <v>46088.92765194014</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>3d654124-fe83-462a-b82d-21e7a83e7995</t>
+        </is>
+      </c>
+      <c r="B1077" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1077" t="n">
+        <v>56.87</v>
+      </c>
+      <c r="G1077" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H1077" s="2" t="n">
+        <v>46087.92765194343</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>b2374eb8-5dca-4d23-86d0-74ec5777924d</t>
+        </is>
+      </c>
+      <c r="B1078" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1078" t="n">
+        <v>473.88</v>
+      </c>
+      <c r="G1078" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="H1078" s="2" t="n">
+        <v>46086.92765194691</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>0ea8d3dc-64a0-4309-ac80-8bc1f52c869e</t>
+        </is>
+      </c>
+      <c r="B1079" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1079" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1079" t="n">
+        <v>364.01</v>
+      </c>
+      <c r="G1079" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="H1079" s="2" t="n">
+        <v>46069.92765195003</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>c7bbcccf-4817-4cce-a4d4-edb90dedd086</t>
+        </is>
+      </c>
+      <c r="B1080" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1080" t="n">
+        <v>164.5</v>
+      </c>
+      <c r="G1080" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H1080" s="2" t="n">
+        <v>46067.92765195309</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>1ef489b9-c0a7-4c55-802a-cf1b486c0db6</t>
+        </is>
+      </c>
+      <c r="B1081" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1081" t="n">
+        <v>407.08</v>
+      </c>
+      <c r="G1081" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="H1081" s="2" t="n">
+        <v>46079.92765195615</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>84d4c225-14b3-4210-a713-ce6c3e0fadee</t>
+        </is>
+      </c>
+      <c r="B1082" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1082" t="n">
+        <v>216.17</v>
+      </c>
+      <c r="G1082" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H1082" s="2" t="n">
+        <v>46085.92765195961</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>63a26f9a-9e9b-4368-9f9b-bd08332ec7a8</t>
+        </is>
+      </c>
+      <c r="B1083" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1083" t="n">
+        <v>419.83</v>
+      </c>
+      <c r="G1083" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H1083" s="2" t="n">
+        <v>46079.92765196475</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>60b90ee6-b3ae-40ef-bdab-ec0bdd121f56</t>
+        </is>
+      </c>
+      <c r="B1084" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1084" t="n">
+        <v>105.33</v>
+      </c>
+      <c r="G1084" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H1084" s="2" t="n">
+        <v>46077.9276519681</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>43687e84-6d98-4596-94cb-826f028b3542</t>
+        </is>
+      </c>
+      <c r="B1085" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1085" t="n">
+        <v>354.89</v>
+      </c>
+      <c r="G1085" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H1085" s="2" t="n">
+        <v>46094.9276519718</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>55b1e94d-9df6-4841-b5ee-5b412113e0bf</t>
+        </is>
+      </c>
+      <c r="B1086" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1086" t="n">
+        <v>385.46</v>
+      </c>
+      <c r="G1086" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H1086" s="2" t="n">
+        <v>46075.92765197485</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>28d1062a-61f9-4818-8c75-4d8bee485c68</t>
+        </is>
+      </c>
+      <c r="B1087" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1087" t="n">
+        <v>123.2</v>
+      </c>
+      <c r="G1087" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="H1087" s="2" t="n">
+        <v>46076.92765197808</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>1f8b29aa-a9bd-4f76-b8d7-833c35008aaa</t>
+        </is>
+      </c>
+      <c r="B1088" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1088" t="n">
+        <v>64.45999999999999</v>
+      </c>
+      <c r="G1088" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H1088" s="2" t="n">
+        <v>46080.92765198134</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>eb796adf-6fff-4250-9bce-7f3a9570c6de</t>
+        </is>
+      </c>
+      <c r="B1089" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1089" t="n">
+        <v>455.59</v>
+      </c>
+      <c r="G1089" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="H1089" s="2" t="n">
+        <v>46066.92765198461</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>1a87ac9c-baa7-406b-9aff-83ff08e44c5c</t>
+        </is>
+      </c>
+      <c r="B1090" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1090" t="n">
+        <v>81.98</v>
+      </c>
+      <c r="G1090" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H1090" s="2" t="n">
+        <v>46074.9276519878</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>a3f4c2da-40ae-41fd-9ffe-4936e50fb01f</t>
+        </is>
+      </c>
+      <c r="B1091" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1091" t="n">
+        <v>405.13</v>
+      </c>
+      <c r="G1091" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="H1091" s="2" t="n">
+        <v>46076.92765199098</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>3a903d55-0e13-45e3-8d8d-e28bbe73d6b6</t>
+        </is>
+      </c>
+      <c r="B1092" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1092" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="G1092" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H1092" s="2" t="n">
+        <v>46087.92765199434</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>b2c3c351-caf6-4ce5-9fc6-2d9a8d2e6d46</t>
+        </is>
+      </c>
+      <c r="B1093" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1093" t="n">
+        <v>227.79</v>
+      </c>
+      <c r="G1093" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H1093" s="2" t="n">
+        <v>46087.92765199759</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>93b274b8-690e-4871-a1c3-36862a74250c</t>
+        </is>
+      </c>
+      <c r="B1094" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1094" t="n">
+        <v>325.82</v>
+      </c>
+      <c r="G1094" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="H1094" s="2" t="n">
+        <v>46067.92765200089</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>355c8edc-4a3f-47a4-91ba-28bdbe68d261</t>
+        </is>
+      </c>
+      <c r="B1095" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1095" t="n">
+        <v>223.91</v>
+      </c>
+      <c r="G1095" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H1095" s="2" t="n">
+        <v>46065.92765200423</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>ef4e1cc5-1f3e-4126-bc4f-0c0a79bf15c4</t>
+        </is>
+      </c>
+      <c r="B1096" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1096" t="n">
+        <v>159.37</v>
+      </c>
+      <c r="G1096" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H1096" s="2" t="n">
+        <v>46067.92765200746</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>71e58d7e-5dad-4317-a9ee-e67e85c09a63</t>
+        </is>
+      </c>
+      <c r="B1097" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1097" t="n">
+        <v>293.74</v>
+      </c>
+      <c r="G1097" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H1097" s="2" t="n">
+        <v>46082.92765201065</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>c0dae086-5d8b-49e4-a166-551828cb440d</t>
+        </is>
+      </c>
+      <c r="B1098" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1098" t="n">
+        <v>251.64</v>
+      </c>
+      <c r="G1098" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H1098" s="2" t="n">
+        <v>46065.92765201374</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>6a5abde0-66d5-4855-bdcf-adfda2dd7fa9</t>
+        </is>
+      </c>
+      <c r="B1099" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1099" t="n">
+        <v>344.76</v>
+      </c>
+      <c r="G1099" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H1099" s="2" t="n">
+        <v>46073.9276520173</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>6a356440-8ea9-4a73-90c3-1051799f93dd</t>
+        </is>
+      </c>
+      <c r="B1100" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1100" t="n">
+        <v>471.12</v>
+      </c>
+      <c r="G1100" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="H1100" s="2" t="n">
+        <v>46069.92765202047</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>f514f02e-5ac1-4e8f-b47b-3a1cf2c2a90c</t>
+        </is>
+      </c>
+      <c r="B1101" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1101" t="n">
+        <v>476.31</v>
+      </c>
+      <c r="G1101" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="H1101" s="2" t="n">
+        <v>46081.92765202355</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1101"/>
+  <dimension ref="A1:H1151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36205,7 +36205,7 @@
         <v>1.86</v>
       </c>
       <c r="H1052" s="2" t="n">
-        <v>46093.92765186141</v>
+        <v>46093.92765186343</v>
       </c>
     </row>
     <row r="1053">
@@ -36239,7 +36239,7 @@
         <v>4.1</v>
       </c>
       <c r="H1053" s="2" t="n">
-        <v>46081.92765186596</v>
+        <v>46081.92765186343</v>
       </c>
     </row>
     <row r="1054">
@@ -36273,7 +36273,7 @@
         <v>4.37</v>
       </c>
       <c r="H1054" s="2" t="n">
-        <v>46070.92765186915</v>
+        <v>46070.92765186343</v>
       </c>
     </row>
     <row r="1055">
@@ -36307,7 +36307,7 @@
         <v>1.44</v>
       </c>
       <c r="H1055" s="2" t="n">
-        <v>46084.92765187251</v>
+        <v>46084.927651875</v>
       </c>
     </row>
     <row r="1056">
@@ -36341,7 +36341,7 @@
         <v>3.73</v>
       </c>
       <c r="H1056" s="2" t="n">
-        <v>46079.92765187576</v>
+        <v>46079.927651875</v>
       </c>
     </row>
     <row r="1057">
@@ -36375,7 +36375,7 @@
         <v>0.95</v>
       </c>
       <c r="H1057" s="2" t="n">
-        <v>46069.92765187928</v>
+        <v>46069.927651875</v>
       </c>
     </row>
     <row r="1058">
@@ -36409,7 +36409,7 @@
         <v>0.8</v>
       </c>
       <c r="H1058" s="2" t="n">
-        <v>46067.9276518825</v>
+        <v>46067.92765188657</v>
       </c>
     </row>
     <row r="1059">
@@ -36443,7 +36443,7 @@
         <v>0.25</v>
       </c>
       <c r="H1059" s="2" t="n">
-        <v>46071.9276518856</v>
+        <v>46071.92765188657</v>
       </c>
     </row>
     <row r="1060">
@@ -36477,7 +36477,7 @@
         <v>4.56</v>
       </c>
       <c r="H1060" s="2" t="n">
-        <v>46074.92765188897</v>
+        <v>46074.92765188657</v>
       </c>
     </row>
     <row r="1061">
@@ -36511,7 +36511,7 @@
         <v>4.03</v>
       </c>
       <c r="H1061" s="2" t="n">
-        <v>46069.92765189202</v>
+        <v>46069.92765188657</v>
       </c>
     </row>
     <row r="1062">
@@ -36545,7 +36545,7 @@
         <v>3.27</v>
       </c>
       <c r="H1062" s="2" t="n">
-        <v>46078.92765189547</v>
+        <v>46078.92765189815</v>
       </c>
     </row>
     <row r="1063">
@@ -36579,7 +36579,7 @@
         <v>0.47</v>
       </c>
       <c r="H1063" s="2" t="n">
-        <v>46075.9276518987</v>
+        <v>46075.92765189815</v>
       </c>
     </row>
     <row r="1064">
@@ -36613,7 +36613,7 @@
         <v>3.2</v>
       </c>
       <c r="H1064" s="2" t="n">
-        <v>46084.92765190226</v>
+        <v>46084.92765189815</v>
       </c>
     </row>
     <row r="1065">
@@ -36647,7 +36647,7 @@
         <v>3.5</v>
       </c>
       <c r="H1065" s="2" t="n">
-        <v>46090.92765190562</v>
+        <v>46090.92765190973</v>
       </c>
     </row>
     <row r="1066">
@@ -36681,7 +36681,7 @@
         <v>2.07</v>
       </c>
       <c r="H1066" s="2" t="n">
-        <v>46068.92765190881</v>
+        <v>46068.92765190973</v>
       </c>
     </row>
     <row r="1067">
@@ -36715,7 +36715,7 @@
         <v>4.14</v>
       </c>
       <c r="H1067" s="2" t="n">
-        <v>46075.92765191213</v>
+        <v>46075.92765190973</v>
       </c>
     </row>
     <row r="1068">
@@ -36749,7 +36749,7 @@
         <v>3.11</v>
       </c>
       <c r="H1068" s="2" t="n">
-        <v>46066.92765191532</v>
+        <v>46066.92765190973</v>
       </c>
     </row>
     <row r="1069">
@@ -36783,7 +36783,7 @@
         <v>4.65</v>
       </c>
       <c r="H1069" s="2" t="n">
-        <v>46082.92765191841</v>
+        <v>46082.92765192129</v>
       </c>
     </row>
     <row r="1070">
@@ -36817,7 +36817,7 @@
         <v>4.09</v>
       </c>
       <c r="H1070" s="2" t="n">
-        <v>46082.92765192151</v>
+        <v>46082.92765192129</v>
       </c>
     </row>
     <row r="1071">
@@ -36851,7 +36851,7 @@
         <v>3.7</v>
       </c>
       <c r="H1071" s="2" t="n">
-        <v>46070.92765192471</v>
+        <v>46070.92765192129</v>
       </c>
     </row>
     <row r="1072">
@@ -36885,7 +36885,7 @@
         <v>1.89</v>
       </c>
       <c r="H1072" s="2" t="n">
-        <v>46085.92765192778</v>
+        <v>46085.92765193287</v>
       </c>
     </row>
     <row r="1073">
@@ -36919,7 +36919,7 @@
         <v>1.08</v>
       </c>
       <c r="H1073" s="2" t="n">
-        <v>46077.92765193082</v>
+        <v>46077.92765193287</v>
       </c>
     </row>
     <row r="1074">
@@ -36953,7 +36953,7 @@
         <v>0.01</v>
       </c>
       <c r="H1074" s="2" t="n">
-        <v>46087.92765193393</v>
+        <v>46087.92765193287</v>
       </c>
     </row>
     <row r="1075">
@@ -36987,7 +36987,7 @@
         <v>4.8</v>
       </c>
       <c r="H1075" s="2" t="n">
-        <v>46084.92765193714</v>
+        <v>46084.92765193287</v>
       </c>
     </row>
     <row r="1076">
@@ -37021,7 +37021,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="H1076" s="2" t="n">
-        <v>46088.92765194014</v>
+        <v>46088.92765194445</v>
       </c>
     </row>
     <row r="1077">
@@ -37055,7 +37055,7 @@
         <v>0.57</v>
       </c>
       <c r="H1077" s="2" t="n">
-        <v>46087.92765194343</v>
+        <v>46087.92765194445</v>
       </c>
     </row>
     <row r="1078">
@@ -37089,7 +37089,7 @@
         <v>4.74</v>
       </c>
       <c r="H1078" s="2" t="n">
-        <v>46086.92765194691</v>
+        <v>46086.92765194445</v>
       </c>
     </row>
     <row r="1079">
@@ -37123,7 +37123,7 @@
         <v>3.64</v>
       </c>
       <c r="H1079" s="2" t="n">
-        <v>46069.92765195003</v>
+        <v>46069.92765194445</v>
       </c>
     </row>
     <row r="1080">
@@ -37157,7 +37157,7 @@
         <v>1.65</v>
       </c>
       <c r="H1080" s="2" t="n">
-        <v>46067.92765195309</v>
+        <v>46067.92765195602</v>
       </c>
     </row>
     <row r="1081">
@@ -37191,7 +37191,7 @@
         <v>4.07</v>
       </c>
       <c r="H1081" s="2" t="n">
-        <v>46079.92765195615</v>
+        <v>46079.92765195602</v>
       </c>
     </row>
     <row r="1082">
@@ -37225,7 +37225,7 @@
         <v>2.16</v>
       </c>
       <c r="H1082" s="2" t="n">
-        <v>46085.92765195961</v>
+        <v>46085.92765195602</v>
       </c>
     </row>
     <row r="1083">
@@ -37259,7 +37259,7 @@
         <v>4.2</v>
       </c>
       <c r="H1083" s="2" t="n">
-        <v>46079.92765196475</v>
+        <v>46079.92765196759</v>
       </c>
     </row>
     <row r="1084">
@@ -37293,7 +37293,7 @@
         <v>1.05</v>
       </c>
       <c r="H1084" s="2" t="n">
-        <v>46077.9276519681</v>
+        <v>46077.92765196759</v>
       </c>
     </row>
     <row r="1085">
@@ -37327,7 +37327,7 @@
         <v>3.55</v>
       </c>
       <c r="H1085" s="2" t="n">
-        <v>46094.9276519718</v>
+        <v>46094.92765196759</v>
       </c>
     </row>
     <row r="1086">
@@ -37361,7 +37361,7 @@
         <v>3.85</v>
       </c>
       <c r="H1086" s="2" t="n">
-        <v>46075.92765197485</v>
+        <v>46075.92765197917</v>
       </c>
     </row>
     <row r="1087">
@@ -37395,7 +37395,7 @@
         <v>1.23</v>
       </c>
       <c r="H1087" s="2" t="n">
-        <v>46076.92765197808</v>
+        <v>46076.92765197917</v>
       </c>
     </row>
     <row r="1088">
@@ -37429,7 +37429,7 @@
         <v>0.64</v>
       </c>
       <c r="H1088" s="2" t="n">
-        <v>46080.92765198134</v>
+        <v>46080.92765197917</v>
       </c>
     </row>
     <row r="1089">
@@ -37463,7 +37463,7 @@
         <v>4.56</v>
       </c>
       <c r="H1089" s="2" t="n">
-        <v>46066.92765198461</v>
+        <v>46066.92765197917</v>
       </c>
     </row>
     <row r="1090">
@@ -37497,7 +37497,7 @@
         <v>0.82</v>
       </c>
       <c r="H1090" s="2" t="n">
-        <v>46074.9276519878</v>
+        <v>46074.92765199074</v>
       </c>
     </row>
     <row r="1091">
@@ -37531,7 +37531,7 @@
         <v>4.05</v>
       </c>
       <c r="H1091" s="2" t="n">
-        <v>46076.92765199098</v>
+        <v>46076.92765199074</v>
       </c>
     </row>
     <row r="1092">
@@ -37565,7 +37565,7 @@
         <v>0.08</v>
       </c>
       <c r="H1092" s="2" t="n">
-        <v>46087.92765199434</v>
+        <v>46087.92765199074</v>
       </c>
     </row>
     <row r="1093">
@@ -37599,7 +37599,7 @@
         <v>2.28</v>
       </c>
       <c r="H1093" s="2" t="n">
-        <v>46087.92765199759</v>
+        <v>46087.92765200231</v>
       </c>
     </row>
     <row r="1094">
@@ -37633,7 +37633,7 @@
         <v>3.26</v>
       </c>
       <c r="H1094" s="2" t="n">
-        <v>46067.92765200089</v>
+        <v>46067.92765200231</v>
       </c>
     </row>
     <row r="1095">
@@ -37667,7 +37667,7 @@
         <v>2.24</v>
       </c>
       <c r="H1095" s="2" t="n">
-        <v>46065.92765200423</v>
+        <v>46065.92765200231</v>
       </c>
     </row>
     <row r="1096">
@@ -37701,7 +37701,7 @@
         <v>1.59</v>
       </c>
       <c r="H1096" s="2" t="n">
-        <v>46067.92765200746</v>
+        <v>46067.92765200231</v>
       </c>
     </row>
     <row r="1097">
@@ -37735,7 +37735,7 @@
         <v>2.94</v>
       </c>
       <c r="H1097" s="2" t="n">
-        <v>46082.92765201065</v>
+        <v>46082.92765201389</v>
       </c>
     </row>
     <row r="1098">
@@ -37769,7 +37769,7 @@
         <v>2.52</v>
       </c>
       <c r="H1098" s="2" t="n">
-        <v>46065.92765201374</v>
+        <v>46065.92765201389</v>
       </c>
     </row>
     <row r="1099">
@@ -37803,7 +37803,7 @@
         <v>3.45</v>
       </c>
       <c r="H1099" s="2" t="n">
-        <v>46073.9276520173</v>
+        <v>46073.92765201389</v>
       </c>
     </row>
     <row r="1100">
@@ -37837,7 +37837,7 @@
         <v>4.71</v>
       </c>
       <c r="H1100" s="2" t="n">
-        <v>46069.92765202047</v>
+        <v>46069.92765202546</v>
       </c>
     </row>
     <row r="1101">
@@ -37871,7 +37871,1707 @@
         <v>4.76</v>
       </c>
       <c r="H1101" s="2" t="n">
-        <v>46081.92765202355</v>
+        <v>46081.92765202546</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>d2ccf7f0-9de1-443e-b26f-285a4a5c9f4e</t>
+        </is>
+      </c>
+      <c r="B1102" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1102" t="n">
+        <v>19.02</v>
+      </c>
+      <c r="G1102" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H1102" s="2" t="n">
+        <v>46077.96951588426</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>625f52a0-1520-4bd3-97b6-b0c003143539</t>
+        </is>
+      </c>
+      <c r="B1103" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1103" t="n">
+        <v>353.08</v>
+      </c>
+      <c r="G1103" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="H1103" s="2" t="n">
+        <v>46068.96951588847</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>791d9521-49ea-412f-94ec-3f834affd71a</t>
+        </is>
+      </c>
+      <c r="B1104" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1104" t="n">
+        <v>460.45</v>
+      </c>
+      <c r="G1104" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H1104" s="2" t="n">
+        <v>46072.96951589212</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>07b46a48-c32d-491a-9210-a12786071a4a</t>
+        </is>
+      </c>
+      <c r="B1105" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1105" t="n">
+        <v>453.77</v>
+      </c>
+      <c r="G1105" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="H1105" s="2" t="n">
+        <v>46080.96951589531</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>21597957-c0db-41d6-bb3f-ac139cb59066</t>
+        </is>
+      </c>
+      <c r="B1106" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1106" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="G1106" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H1106" s="2" t="n">
+        <v>46068.96951589861</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>5b0af28d-a0bc-4436-bd85-97ebd102ca81</t>
+        </is>
+      </c>
+      <c r="B1107" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1107" t="n">
+        <v>81.39</v>
+      </c>
+      <c r="G1107" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H1107" s="2" t="n">
+        <v>46073.96951590214</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>8ed4a7ac-c2b0-4df3-8f21-fd1cd62b1d69</t>
+        </is>
+      </c>
+      <c r="B1108" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1108" t="n">
+        <v>242.85</v>
+      </c>
+      <c r="G1108" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="H1108" s="2" t="n">
+        <v>46073.96951590518</v>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>1fc9a28b-19ff-4118-a7c0-cd9d3c1d62be</t>
+        </is>
+      </c>
+      <c r="B1109" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1109" t="n">
+        <v>407.05</v>
+      </c>
+      <c r="G1109" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="H1109" s="2" t="n">
+        <v>46088.96951590843</v>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>97b54d8b-aa2b-4bef-bc40-1356eeb269a8</t>
+        </is>
+      </c>
+      <c r="B1110" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1110" t="n">
+        <v>197.5</v>
+      </c>
+      <c r="G1110" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H1110" s="2" t="n">
+        <v>46093.96951591153</v>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>c21bb342-4ef3-496e-8d68-0524a60aff18</t>
+        </is>
+      </c>
+      <c r="B1111" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1111" t="n">
+        <v>166.25</v>
+      </c>
+      <c r="G1111" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H1111" s="2" t="n">
+        <v>46087.96951591499</v>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>b458fe90-081c-4487-9d3c-18c13a5ba00c</t>
+        </is>
+      </c>
+      <c r="B1112" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1112" t="n">
+        <v>256.9</v>
+      </c>
+      <c r="G1112" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="H1112" s="2" t="n">
+        <v>46068.96951591835</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>5ddc5d20-f011-4602-96f7-97fea21579ca</t>
+        </is>
+      </c>
+      <c r="B1113" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1113" t="n">
+        <v>121.58</v>
+      </c>
+      <c r="G1113" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H1113" s="2" t="n">
+        <v>46077.96951592155</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>7247395f-ae70-4d17-869d-ba90f4071ca3</t>
+        </is>
+      </c>
+      <c r="B1114" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1114" t="n">
+        <v>489.94</v>
+      </c>
+      <c r="G1114" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H1114" s="2" t="n">
+        <v>46071.96951592538</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>8e5661d9-114a-41c9-aefd-06f82e213f68</t>
+        </is>
+      </c>
+      <c r="B1115" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1115" t="n">
+        <v>33.73</v>
+      </c>
+      <c r="G1115" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H1115" s="2" t="n">
+        <v>46089.96951592866</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>cf206d23-9f64-404c-993c-d06f37941bf4</t>
+        </is>
+      </c>
+      <c r="B1116" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1116" t="n">
+        <v>179.02</v>
+      </c>
+      <c r="G1116" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="H1116" s="2" t="n">
+        <v>46071.96951593187</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>4120ab62-081e-46e2-841a-b1c488ff23a1</t>
+        </is>
+      </c>
+      <c r="B1117" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1117" t="n">
+        <v>476.7</v>
+      </c>
+      <c r="G1117" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="H1117" s="2" t="n">
+        <v>46091.96951593523</v>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>5b982147-9f97-4af5-a031-6330dd1e6fa3</t>
+        </is>
+      </c>
+      <c r="B1118" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1118" t="n">
+        <v>195.58</v>
+      </c>
+      <c r="G1118" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H1118" s="2" t="n">
+        <v>46077.96951593849</v>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>2a7e856a-a4d4-4689-9fb8-5b8ba31b3756</t>
+        </is>
+      </c>
+      <c r="B1119" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1119" t="n">
+        <v>83.45999999999999</v>
+      </c>
+      <c r="G1119" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H1119" s="2" t="n">
+        <v>46082.96951594149</v>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>a1229b92-505f-4ab9-b33d-c478f6308440</t>
+        </is>
+      </c>
+      <c r="B1120" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1120" t="n">
+        <v>107.34</v>
+      </c>
+      <c r="G1120" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H1120" s="2" t="n">
+        <v>46088.96951594476</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>e14b5a01-a9d3-494e-8a27-25ba8b85ee8e</t>
+        </is>
+      </c>
+      <c r="B1121" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1121" t="n">
+        <v>237.23</v>
+      </c>
+      <c r="G1121" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="H1121" s="2" t="n">
+        <v>46083.96951594825</v>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>2e65af93-0eae-451b-9fb3-7912b544f47d</t>
+        </is>
+      </c>
+      <c r="B1122" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1122" t="n">
+        <v>404.13</v>
+      </c>
+      <c r="G1122" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="H1122" s="2" t="n">
+        <v>46078.96951595152</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>1947735c-99fb-4591-8515-4199ab7ae856</t>
+        </is>
+      </c>
+      <c r="B1123" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1123" t="n">
+        <v>280.15</v>
+      </c>
+      <c r="G1123" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H1123" s="2" t="n">
+        <v>46075.96951595478</v>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>05cb4225-a92a-4b1c-ad0e-e6b4530089e8</t>
+        </is>
+      </c>
+      <c r="B1124" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1124" t="n">
+        <v>464.06</v>
+      </c>
+      <c r="G1124" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="H1124" s="2" t="n">
+        <v>46089.96951595787</v>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>b4ddff6e-c535-4e12-85ba-f6b94c9ddddc</t>
+        </is>
+      </c>
+      <c r="B1125" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1125" t="n">
+        <v>172.54</v>
+      </c>
+      <c r="G1125" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H1125" s="2" t="n">
+        <v>46086.9695159614</v>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>ab22b40c-6d45-4e73-a538-89c7cf7d755b</t>
+        </is>
+      </c>
+      <c r="B1126" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1126" t="n">
+        <v>245.87</v>
+      </c>
+      <c r="G1126" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H1126" s="2" t="n">
+        <v>46091.96951596445</v>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>6dc962e0-af41-4d57-8529-0ebf8d4b407f</t>
+        </is>
+      </c>
+      <c r="B1127" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1127" t="n">
+        <v>48.53</v>
+      </c>
+      <c r="G1127" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H1127" s="2" t="n">
+        <v>46066.9695159677</v>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>0fcdccd1-01f3-4b93-a474-c9848e91901d</t>
+        </is>
+      </c>
+      <c r="B1128" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1128" t="n">
+        <v>200.39</v>
+      </c>
+      <c r="G1128" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1128" s="2" t="n">
+        <v>46066.96951597147</v>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>443d6df9-8566-47a9-824d-5d34e62427cb</t>
+        </is>
+      </c>
+      <c r="B1129" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1129" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="G1129" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H1129" s="2" t="n">
+        <v>46076.96951597472</v>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>c62bf95e-c6c8-439b-b4cb-6e309c8411e4</t>
+        </is>
+      </c>
+      <c r="B1130" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1130" t="n">
+        <v>103.11</v>
+      </c>
+      <c r="G1130" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H1130" s="2" t="n">
+        <v>46078.96951597797</v>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>83a0780e-a8b1-466f-97ca-bb74c956ea67</t>
+        </is>
+      </c>
+      <c r="B1131" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1131" t="n">
+        <v>455.12</v>
+      </c>
+      <c r="G1131" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="H1131" s="2" t="n">
+        <v>46083.96951598113</v>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>72575689-3a34-4a48-99e6-dc1d5ae8ef7d</t>
+        </is>
+      </c>
+      <c r="B1132" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1132" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="G1132" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H1132" s="2" t="n">
+        <v>46086.96951598463</v>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>9b20e40b-700b-4b39-a46b-ab9c2b223a71</t>
+        </is>
+      </c>
+      <c r="B1133" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1133" t="n">
+        <v>241.8</v>
+      </c>
+      <c r="G1133" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H1133" s="2" t="n">
+        <v>46080.96951598772</v>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>129b97e9-ebb1-4bf0-b2f4-0eb5ccb772b6</t>
+        </is>
+      </c>
+      <c r="B1134" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1134" t="n">
+        <v>487.78</v>
+      </c>
+      <c r="G1134" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="H1134" s="2" t="n">
+        <v>46067.96951599094</v>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>57d32540-b995-4982-b7e5-1a21fcfeda45</t>
+        </is>
+      </c>
+      <c r="B1135" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1135" t="n">
+        <v>134.05</v>
+      </c>
+      <c r="G1135" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="H1135" s="2" t="n">
+        <v>46072.96951599439</v>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>6c145f29-0bab-49d8-9a4b-334f4c9d20b3</t>
+        </is>
+      </c>
+      <c r="B1136" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1136" t="n">
+        <v>457.55</v>
+      </c>
+      <c r="G1136" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="H1136" s="2" t="n">
+        <v>46067.96951599737</v>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>ba3e8f8c-a625-4c79-9af0-ade85a184a53</t>
+        </is>
+      </c>
+      <c r="B1137" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1137" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="G1137" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H1137" s="2" t="n">
+        <v>46071.96951600048</v>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>7b860a4a-3b9d-44d3-8d59-89a0019578da</t>
+        </is>
+      </c>
+      <c r="B1138" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1138" t="n">
+        <v>118.13</v>
+      </c>
+      <c r="G1138" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H1138" s="2" t="n">
+        <v>46089.96951600353</v>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>e31a35e5-4a85-45f3-9102-4681e89d57f7</t>
+        </is>
+      </c>
+      <c r="B1139" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1139" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="G1139" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H1139" s="2" t="n">
+        <v>46076.96951600706</v>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>2d4f2c47-efb3-405c-961e-8222f25fe1f9</t>
+        </is>
+      </c>
+      <c r="B1140" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1140" t="n">
+        <v>202.7</v>
+      </c>
+      <c r="G1140" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="H1140" s="2" t="n">
+        <v>46070.96951601026</v>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>e0a0e00e-d2cd-4ef6-8f55-04489fbd210b</t>
+        </is>
+      </c>
+      <c r="B1141" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1141" t="n">
+        <v>266.7</v>
+      </c>
+      <c r="G1141" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="H1141" s="2" t="n">
+        <v>46070.96951601349</v>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>4f9bd536-2a22-48f1-b5f7-81168938ffa5</t>
+        </is>
+      </c>
+      <c r="B1142" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1142" t="n">
+        <v>491.14</v>
+      </c>
+      <c r="G1142" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="H1142" s="2" t="n">
+        <v>46068.96951601723</v>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>982e3ed0-02c7-4a05-a41e-bc7c5473beba</t>
+        </is>
+      </c>
+      <c r="B1143" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1143" t="n">
+        <v>108.27</v>
+      </c>
+      <c r="G1143" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="H1143" s="2" t="n">
+        <v>46078.96951602052</v>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>acf8f7b3-e498-4c4e-b99f-6f2aae17caf3</t>
+        </is>
+      </c>
+      <c r="B1144" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1144" t="n">
+        <v>325.35</v>
+      </c>
+      <c r="G1144" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H1144" s="2" t="n">
+        <v>46088.96951602366</v>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>2202438b-1dff-42c1-9b7b-7c61b98889fc</t>
+        </is>
+      </c>
+      <c r="B1145" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1145" t="n">
+        <v>289.08</v>
+      </c>
+      <c r="G1145" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="H1145" s="2" t="n">
+        <v>46072.96951602664</v>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>89576101-332f-4f69-939f-096d83372f1e</t>
+        </is>
+      </c>
+      <c r="B1146" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1146" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="G1146" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H1146" s="2" t="n">
+        <v>46065.96951603019</v>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>b73e16af-cad5-4701-aca0-c9ffb38a9fee</t>
+        </is>
+      </c>
+      <c r="B1147" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1147" t="n">
+        <v>123.71</v>
+      </c>
+      <c r="G1147" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="H1147" s="2" t="n">
+        <v>46076.96951603334</v>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>3b59f533-a9a2-4c4e-b5a8-0da877858b8d</t>
+        </is>
+      </c>
+      <c r="B1148" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1148" t="n">
+        <v>138.62</v>
+      </c>
+      <c r="G1148" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H1148" s="2" t="n">
+        <v>46073.96951603642</v>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>f1c14c1a-2da4-4d81-aae1-924627ac801c</t>
+        </is>
+      </c>
+      <c r="B1149" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1149" t="n">
+        <v>281.11</v>
+      </c>
+      <c r="G1149" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="H1149" s="2" t="n">
+        <v>46072.9695160398</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>2672a97f-59d8-4e78-bf25-a674091cded1</t>
+        </is>
+      </c>
+      <c r="B1150" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1150" t="n">
+        <v>321.86</v>
+      </c>
+      <c r="G1150" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="H1150" s="2" t="n">
+        <v>46089.96951604296</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>d26d6c86-f71f-43f1-9755-3fdfea12200a</t>
+        </is>
+      </c>
+      <c r="B1151" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1151" t="n">
+        <v>78.92</v>
+      </c>
+      <c r="G1151" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H1151" s="2" t="n">
+        <v>46071.969516046</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1151"/>
+  <dimension ref="A1:H1201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37905,7 +37905,7 @@
         <v>0.19</v>
       </c>
       <c r="H1102" s="2" t="n">
-        <v>46077.96951588426</v>
+        <v>46077.96951587963</v>
       </c>
     </row>
     <row r="1103">
@@ -37939,7 +37939,7 @@
         <v>3.53</v>
       </c>
       <c r="H1103" s="2" t="n">
-        <v>46068.96951588847</v>
+        <v>46068.96951589121</v>
       </c>
     </row>
     <row r="1104">
@@ -37973,7 +37973,7 @@
         <v>4.6</v>
       </c>
       <c r="H1104" s="2" t="n">
-        <v>46072.96951589212</v>
+        <v>46072.96951589121</v>
       </c>
     </row>
     <row r="1105">
@@ -38007,7 +38007,7 @@
         <v>4.54</v>
       </c>
       <c r="H1105" s="2" t="n">
-        <v>46080.96951589531</v>
+        <v>46080.96951589121</v>
       </c>
     </row>
     <row r="1106">
@@ -38041,7 +38041,7 @@
         <v>0.83</v>
       </c>
       <c r="H1106" s="2" t="n">
-        <v>46068.96951589861</v>
+        <v>46068.96951590278</v>
       </c>
     </row>
     <row r="1107">
@@ -38075,7 +38075,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H1107" s="2" t="n">
-        <v>46073.96951590214</v>
+        <v>46073.96951590278</v>
       </c>
     </row>
     <row r="1108">
@@ -38109,7 +38109,7 @@
         <v>2.43</v>
       </c>
       <c r="H1108" s="2" t="n">
-        <v>46073.96951590518</v>
+        <v>46073.96951590278</v>
       </c>
     </row>
     <row r="1109">
@@ -38143,7 +38143,7 @@
         <v>4.07</v>
       </c>
       <c r="H1109" s="2" t="n">
-        <v>46088.96951590843</v>
+        <v>46088.96951590278</v>
       </c>
     </row>
     <row r="1110">
@@ -38177,7 +38177,7 @@
         <v>1.98</v>
       </c>
       <c r="H1110" s="2" t="n">
-        <v>46093.96951591153</v>
+        <v>46093.96951591435</v>
       </c>
     </row>
     <row r="1111">
@@ -38211,7 +38211,7 @@
         <v>1.66</v>
       </c>
       <c r="H1111" s="2" t="n">
-        <v>46087.96951591499</v>
+        <v>46087.96951591435</v>
       </c>
     </row>
     <row r="1112">
@@ -38245,7 +38245,7 @@
         <v>2.57</v>
       </c>
       <c r="H1112" s="2" t="n">
-        <v>46068.96951591835</v>
+        <v>46068.96951591435</v>
       </c>
     </row>
     <row r="1113">
@@ -38279,7 +38279,7 @@
         <v>1.22</v>
       </c>
       <c r="H1113" s="2" t="n">
-        <v>46077.96951592155</v>
+        <v>46077.96951592593</v>
       </c>
     </row>
     <row r="1114">
@@ -38313,7 +38313,7 @@
         <v>4.9</v>
       </c>
       <c r="H1114" s="2" t="n">
-        <v>46071.96951592538</v>
+        <v>46071.96951592593</v>
       </c>
     </row>
     <row r="1115">
@@ -38347,7 +38347,7 @@
         <v>0.34</v>
       </c>
       <c r="H1115" s="2" t="n">
-        <v>46089.96951592866</v>
+        <v>46089.96951592593</v>
       </c>
     </row>
     <row r="1116">
@@ -38381,7 +38381,7 @@
         <v>1.79</v>
       </c>
       <c r="H1116" s="2" t="n">
-        <v>46071.96951593187</v>
+        <v>46071.9695159375</v>
       </c>
     </row>
     <row r="1117">
@@ -38415,7 +38415,7 @@
         <v>4.77</v>
       </c>
       <c r="H1117" s="2" t="n">
-        <v>46091.96951593523</v>
+        <v>46091.9695159375</v>
       </c>
     </row>
     <row r="1118">
@@ -38449,7 +38449,7 @@
         <v>1.96</v>
       </c>
       <c r="H1118" s="2" t="n">
-        <v>46077.96951593849</v>
+        <v>46077.9695159375</v>
       </c>
     </row>
     <row r="1119">
@@ -38483,7 +38483,7 @@
         <v>0.83</v>
       </c>
       <c r="H1119" s="2" t="n">
-        <v>46082.96951594149</v>
+        <v>46082.9695159375</v>
       </c>
     </row>
     <row r="1120">
@@ -38517,7 +38517,7 @@
         <v>1.07</v>
       </c>
       <c r="H1120" s="2" t="n">
-        <v>46088.96951594476</v>
+        <v>46088.96951594907</v>
       </c>
     </row>
     <row r="1121">
@@ -38551,7 +38551,7 @@
         <v>2.37</v>
       </c>
       <c r="H1121" s="2" t="n">
-        <v>46083.96951594825</v>
+        <v>46083.96951594907</v>
       </c>
     </row>
     <row r="1122">
@@ -38585,7 +38585,7 @@
         <v>4.04</v>
       </c>
       <c r="H1122" s="2" t="n">
-        <v>46078.96951595152</v>
+        <v>46078.96951594907</v>
       </c>
     </row>
     <row r="1123">
@@ -38619,7 +38619,7 @@
         <v>2.8</v>
       </c>
       <c r="H1123" s="2" t="n">
-        <v>46075.96951595478</v>
+        <v>46075.96951594907</v>
       </c>
     </row>
     <row r="1124">
@@ -38653,7 +38653,7 @@
         <v>4.64</v>
       </c>
       <c r="H1124" s="2" t="n">
-        <v>46089.96951595787</v>
+        <v>46089.96951596065</v>
       </c>
     </row>
     <row r="1125">
@@ -38687,7 +38687,7 @@
         <v>1.73</v>
       </c>
       <c r="H1125" s="2" t="n">
-        <v>46086.9695159614</v>
+        <v>46086.96951596065</v>
       </c>
     </row>
     <row r="1126">
@@ -38721,7 +38721,7 @@
         <v>2.46</v>
       </c>
       <c r="H1126" s="2" t="n">
-        <v>46091.96951596445</v>
+        <v>46091.96951596065</v>
       </c>
     </row>
     <row r="1127">
@@ -38755,7 +38755,7 @@
         <v>0.49</v>
       </c>
       <c r="H1127" s="2" t="n">
-        <v>46066.9695159677</v>
+        <v>46066.96951597223</v>
       </c>
     </row>
     <row r="1128">
@@ -38789,7 +38789,7 @@
         <v>2</v>
       </c>
       <c r="H1128" s="2" t="n">
-        <v>46066.96951597147</v>
+        <v>46066.96951597223</v>
       </c>
     </row>
     <row r="1129">
@@ -38823,7 +38823,7 @@
         <v>0.89</v>
       </c>
       <c r="H1129" s="2" t="n">
-        <v>46076.96951597472</v>
+        <v>46076.96951597223</v>
       </c>
     </row>
     <row r="1130">
@@ -38857,7 +38857,7 @@
         <v>1.03</v>
       </c>
       <c r="H1130" s="2" t="n">
-        <v>46078.96951597797</v>
+        <v>46078.96951597223</v>
       </c>
     </row>
     <row r="1131">
@@ -38891,7 +38891,7 @@
         <v>4.55</v>
       </c>
       <c r="H1131" s="2" t="n">
-        <v>46083.96951598113</v>
+        <v>46083.96951598379</v>
       </c>
     </row>
     <row r="1132">
@@ -38925,7 +38925,7 @@
         <v>0.1</v>
       </c>
       <c r="H1132" s="2" t="n">
-        <v>46086.96951598463</v>
+        <v>46086.96951598379</v>
       </c>
     </row>
     <row r="1133">
@@ -38959,7 +38959,7 @@
         <v>2.42</v>
       </c>
       <c r="H1133" s="2" t="n">
-        <v>46080.96951598772</v>
+        <v>46080.96951598379</v>
       </c>
     </row>
     <row r="1134">
@@ -38993,7 +38993,7 @@
         <v>4.88</v>
       </c>
       <c r="H1134" s="2" t="n">
-        <v>46067.96951599094</v>
+        <v>46067.96951599537</v>
       </c>
     </row>
     <row r="1135">
@@ -39027,7 +39027,7 @@
         <v>1.34</v>
       </c>
       <c r="H1135" s="2" t="n">
-        <v>46072.96951599439</v>
+        <v>46072.96951599537</v>
       </c>
     </row>
     <row r="1136">
@@ -39061,7 +39061,7 @@
         <v>4.58</v>
       </c>
       <c r="H1136" s="2" t="n">
-        <v>46067.96951599737</v>
+        <v>46067.96951599537</v>
       </c>
     </row>
     <row r="1137">
@@ -39095,7 +39095,7 @@
         <v>0.19</v>
       </c>
       <c r="H1137" s="2" t="n">
-        <v>46071.96951600048</v>
+        <v>46071.96951599537</v>
       </c>
     </row>
     <row r="1138">
@@ -39129,7 +39129,7 @@
         <v>1.18</v>
       </c>
       <c r="H1138" s="2" t="n">
-        <v>46089.96951600353</v>
+        <v>46089.96951600695</v>
       </c>
     </row>
     <row r="1139">
@@ -39163,7 +39163,7 @@
         <v>0.19</v>
       </c>
       <c r="H1139" s="2" t="n">
-        <v>46076.96951600706</v>
+        <v>46076.96951600695</v>
       </c>
     </row>
     <row r="1140">
@@ -39197,7 +39197,7 @@
         <v>2.03</v>
       </c>
       <c r="H1140" s="2" t="n">
-        <v>46070.96951601026</v>
+        <v>46070.96951600695</v>
       </c>
     </row>
     <row r="1141">
@@ -39231,7 +39231,7 @@
         <v>2.67</v>
       </c>
       <c r="H1141" s="2" t="n">
-        <v>46070.96951601349</v>
+        <v>46070.96951601852</v>
       </c>
     </row>
     <row r="1142">
@@ -39265,7 +39265,7 @@
         <v>4.91</v>
       </c>
       <c r="H1142" s="2" t="n">
-        <v>46068.96951601723</v>
+        <v>46068.96951601852</v>
       </c>
     </row>
     <row r="1143">
@@ -39299,7 +39299,7 @@
         <v>1.08</v>
       </c>
       <c r="H1143" s="2" t="n">
-        <v>46078.96951602052</v>
+        <v>46078.96951601852</v>
       </c>
     </row>
     <row r="1144">
@@ -39333,7 +39333,7 @@
         <v>3.25</v>
       </c>
       <c r="H1144" s="2" t="n">
-        <v>46088.96951602366</v>
+        <v>46088.96951601852</v>
       </c>
     </row>
     <row r="1145">
@@ -39367,7 +39367,7 @@
         <v>2.89</v>
       </c>
       <c r="H1145" s="2" t="n">
-        <v>46072.96951602664</v>
+        <v>46072.96951603009</v>
       </c>
     </row>
     <row r="1146">
@@ -39401,7 +39401,7 @@
         <v>1.03</v>
       </c>
       <c r="H1146" s="2" t="n">
-        <v>46065.96951603019</v>
+        <v>46065.96951603009</v>
       </c>
     </row>
     <row r="1147">
@@ -39435,7 +39435,7 @@
         <v>1.24</v>
       </c>
       <c r="H1147" s="2" t="n">
-        <v>46076.96951603334</v>
+        <v>46076.96951603009</v>
       </c>
     </row>
     <row r="1148">
@@ -39469,7 +39469,7 @@
         <v>1.39</v>
       </c>
       <c r="H1148" s="2" t="n">
-        <v>46073.96951603642</v>
+        <v>46073.96951604167</v>
       </c>
     </row>
     <row r="1149">
@@ -39503,7 +39503,7 @@
         <v>2.81</v>
       </c>
       <c r="H1149" s="2" t="n">
-        <v>46072.9695160398</v>
+        <v>46072.96951604167</v>
       </c>
     </row>
     <row r="1150">
@@ -39537,7 +39537,7 @@
         <v>3.22</v>
       </c>
       <c r="H1150" s="2" t="n">
-        <v>46089.96951604296</v>
+        <v>46089.96951604167</v>
       </c>
     </row>
     <row r="1151">
@@ -39571,7 +39571,1707 @@
         <v>0.79</v>
       </c>
       <c r="H1151" s="2" t="n">
-        <v>46071.969516046</v>
+        <v>46071.96951604167</v>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>bdf4b332-0b8b-4345-8efc-5da99cba448f</t>
+        </is>
+      </c>
+      <c r="B1152" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1152" t="n">
+        <v>156.97</v>
+      </c>
+      <c r="G1152" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H1152" s="2" t="n">
+        <v>46066.05567037185</v>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>19c89a45-aa5b-42a7-a4c4-f37c45aabfa6</t>
+        </is>
+      </c>
+      <c r="B1153" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1153" t="n">
+        <v>141.26</v>
+      </c>
+      <c r="G1153" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H1153" s="2" t="n">
+        <v>46088.05567037634</v>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>c836f447-2e61-4e2d-93e6-40c39cb154f4</t>
+        </is>
+      </c>
+      <c r="B1154" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1154" t="n">
+        <v>61.67</v>
+      </c>
+      <c r="G1154" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H1154" s="2" t="n">
+        <v>46075.05567037963</v>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>62f560a5-91f1-4f66-b3cb-9d58b6eab438</t>
+        </is>
+      </c>
+      <c r="B1155" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1155" t="n">
+        <v>375.11</v>
+      </c>
+      <c r="G1155" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H1155" s="2" t="n">
+        <v>46088.05567038291</v>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>bb4bd56d-5a84-4a0c-a431-099e02ae72d8</t>
+        </is>
+      </c>
+      <c r="B1156" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1156" t="n">
+        <v>187.22</v>
+      </c>
+      <c r="G1156" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H1156" s="2" t="n">
+        <v>46067.05567038616</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>44faa6cf-9b22-4d69-b9a2-4345a45d3352</t>
+        </is>
+      </c>
+      <c r="B1157" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1157" t="n">
+        <v>274.75</v>
+      </c>
+      <c r="G1157" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H1157" s="2" t="n">
+        <v>46074.05567038919</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>b49d50bb-b452-432a-b4d6-91832883d3bc</t>
+        </is>
+      </c>
+      <c r="B1158" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1158" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="G1158" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H1158" s="2" t="n">
+        <v>46079.05567039228</v>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>71f378d4-e4cd-43fc-a31f-bef166595fa4</t>
+        </is>
+      </c>
+      <c r="B1159" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1159" t="n">
+        <v>274.16</v>
+      </c>
+      <c r="G1159" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H1159" s="2" t="n">
+        <v>46085.05567039533</v>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>fcae4882-87eb-4fab-9351-03c7d2848d20</t>
+        </is>
+      </c>
+      <c r="B1160" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1160" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G1160" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H1160" s="2" t="n">
+        <v>46088.05567039894</v>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>e9168ebc-7ecf-4cbe-8a98-f938355e9523</t>
+        </is>
+      </c>
+      <c r="B1161" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1161" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="G1161" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H1161" s="2" t="n">
+        <v>46069.05567040199</v>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>6b39cd39-e27a-4b64-aeca-4e007d2af4e1</t>
+        </is>
+      </c>
+      <c r="B1162" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1162" t="n">
+        <v>388.31</v>
+      </c>
+      <c r="G1162" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="H1162" s="2" t="n">
+        <v>46086.05567040522</v>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>61a1cfe8-947b-48ce-9efd-5de0790e0464</t>
+        </is>
+      </c>
+      <c r="B1163" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1163" t="n">
+        <v>194.05</v>
+      </c>
+      <c r="G1163" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H1163" s="2" t="n">
+        <v>46083.0556704085</v>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>781ed867-0298-4e17-b8b2-acff8967a7bf</t>
+        </is>
+      </c>
+      <c r="B1164" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1164" t="n">
+        <v>458.29</v>
+      </c>
+      <c r="G1164" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="H1164" s="2" t="n">
+        <v>46079.05567041152</v>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>63ddbf74-1643-45a2-9ec6-d121cb1b59a1</t>
+        </is>
+      </c>
+      <c r="B1165" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1165" t="n">
+        <v>376.7</v>
+      </c>
+      <c r="G1165" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="H1165" s="2" t="n">
+        <v>46088.05567041459</v>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>b4477b36-8d6b-4bfa-8342-f947487f970d</t>
+        </is>
+      </c>
+      <c r="B1166" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1166" t="n">
+        <v>202.78</v>
+      </c>
+      <c r="G1166" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="H1166" s="2" t="n">
+        <v>46094.05567041774</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>4a9cb2bb-1014-48da-9937-60401e10b680</t>
+        </is>
+      </c>
+      <c r="B1167" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1167" t="n">
+        <v>76.78</v>
+      </c>
+      <c r="G1167" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="H1167" s="2" t="n">
+        <v>46074.0556704211</v>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>726735f7-3ea1-47ab-8022-fd30fa0f6c7f</t>
+        </is>
+      </c>
+      <c r="B1168" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1168" t="n">
+        <v>447.78</v>
+      </c>
+      <c r="G1168" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="H1168" s="2" t="n">
+        <v>46081.0556704245</v>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>2fe930f4-2ee6-4474-a7b3-a7eff48c5025</t>
+        </is>
+      </c>
+      <c r="B1169" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1169" t="n">
+        <v>266.77</v>
+      </c>
+      <c r="G1169" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="H1169" s="2" t="n">
+        <v>46087.05567042749</v>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>e8d5f8dc-538a-47b8-aa19-c6efbbb15162</t>
+        </is>
+      </c>
+      <c r="B1170" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1170" t="n">
+        <v>272.11</v>
+      </c>
+      <c r="G1170" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H1170" s="2" t="n">
+        <v>46072.05567043069</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>0d6bfacf-0d3c-4e53-8b7d-c70341d3949a</t>
+        </is>
+      </c>
+      <c r="B1171" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1171" t="n">
+        <v>146.45</v>
+      </c>
+      <c r="G1171" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="H1171" s="2" t="n">
+        <v>46095.05567043377</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>6298f79d-8fc6-4201-b04c-9e078adfbca5</t>
+        </is>
+      </c>
+      <c r="B1172" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1172" t="n">
+        <v>232.02</v>
+      </c>
+      <c r="G1172" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H1172" s="2" t="n">
+        <v>46082.0556704369</v>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>771e2c3f-e781-4e76-af89-0c99cd1ff86c</t>
+        </is>
+      </c>
+      <c r="B1173" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1173" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="G1173" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H1173" s="2" t="n">
+        <v>46084.05567043996</v>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>6c399d03-88ad-4a26-9e67-715a2d62bf92</t>
+        </is>
+      </c>
+      <c r="B1174" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1174" t="n">
+        <v>313.85</v>
+      </c>
+      <c r="G1174" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H1174" s="2" t="n">
+        <v>46075.05567044353</v>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>046b44a0-97a7-4dff-adbd-96108301e013</t>
+        </is>
+      </c>
+      <c r="B1175" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1175" t="n">
+        <v>240.63</v>
+      </c>
+      <c r="G1175" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="H1175" s="2" t="n">
+        <v>46076.05567044654</v>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>62e0c69d-24d8-460c-a781-bb7ffe39cb94</t>
+        </is>
+      </c>
+      <c r="B1176" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1176" t="n">
+        <v>118.55</v>
+      </c>
+      <c r="G1176" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H1176" s="2" t="n">
+        <v>46072.05567044957</v>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>f06f517b-cbfb-4184-a8ef-2a5dcb5b7a5d</t>
+        </is>
+      </c>
+      <c r="B1177" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1177" t="n">
+        <v>144.31</v>
+      </c>
+      <c r="G1177" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H1177" s="2" t="n">
+        <v>46067.05567045262</v>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>c5ace0d9-ce34-4d25-94c8-c819aef3c171</t>
+        </is>
+      </c>
+      <c r="B1178" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1178" t="n">
+        <v>176.68</v>
+      </c>
+      <c r="G1178" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H1178" s="2" t="n">
+        <v>46070.05567045596</v>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>288d828c-0f2f-407f-abb4-2c8a67d328bd</t>
+        </is>
+      </c>
+      <c r="B1179" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1179" t="n">
+        <v>118.62</v>
+      </c>
+      <c r="G1179" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H1179" s="2" t="n">
+        <v>46084.05567045918</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>c0568aea-d541-4170-ba5b-38da5ce5ae4f</t>
+        </is>
+      </c>
+      <c r="B1180" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1180" t="n">
+        <v>318.52</v>
+      </c>
+      <c r="G1180" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="H1180" s="2" t="n">
+        <v>46075.05567046218</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>3f1b1d8a-1e2c-4b9d-8dd8-936c29080361</t>
+        </is>
+      </c>
+      <c r="B1181" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1181" t="n">
+        <v>436.62</v>
+      </c>
+      <c r="G1181" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="H1181" s="2" t="n">
+        <v>46076.05567046547</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>b8c0a864-7562-46c7-894c-47370b646b8c</t>
+        </is>
+      </c>
+      <c r="B1182" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1182" t="n">
+        <v>326.68</v>
+      </c>
+      <c r="G1182" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="H1182" s="2" t="n">
+        <v>46080.05567046876</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>7f883c33-d214-4625-b546-6d594d62c7ac</t>
+        </is>
+      </c>
+      <c r="B1183" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1183" t="n">
+        <v>89.72</v>
+      </c>
+      <c r="G1183" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H1183" s="2" t="n">
+        <v>46069.05567047193</v>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>1e0f76eb-e3fa-4a67-b771-555dcb1987a0</t>
+        </is>
+      </c>
+      <c r="B1184" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1184" t="n">
+        <v>48.68</v>
+      </c>
+      <c r="G1184" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H1184" s="2" t="n">
+        <v>46094.05567047513</v>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>5cae1cf4-f2db-4493-aa63-af54df75d896</t>
+        </is>
+      </c>
+      <c r="B1185" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1185" t="n">
+        <v>31.36</v>
+      </c>
+      <c r="G1185" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H1185" s="2" t="n">
+        <v>46076.0556704785</v>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>0bb142ac-6ba7-4e2e-acae-c5ac023342df</t>
+        </is>
+      </c>
+      <c r="B1186" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1186" t="n">
+        <v>316.23</v>
+      </c>
+      <c r="G1186" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="H1186" s="2" t="n">
+        <v>46089.05567048164</v>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>e3e4474e-6e98-48c2-9344-3af5ba3909e5</t>
+        </is>
+      </c>
+      <c r="B1187" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1187" t="n">
+        <v>253.19</v>
+      </c>
+      <c r="G1187" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="H1187" s="2" t="n">
+        <v>46092.05567048479</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>f712fc12-f343-4248-8ce4-8649ce06a500</t>
+        </is>
+      </c>
+      <c r="B1188" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1188" t="n">
+        <v>96.13</v>
+      </c>
+      <c r="G1188" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H1188" s="2" t="n">
+        <v>46084.05567048779</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>26b04a3b-76b1-4ffa-ba1a-982a51f09914</t>
+        </is>
+      </c>
+      <c r="B1189" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1189" t="n">
+        <v>56.39</v>
+      </c>
+      <c r="G1189" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H1189" s="2" t="n">
+        <v>46071.05567049114</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>ed5dc14e-dbda-4b9a-8919-cda379a62979</t>
+        </is>
+      </c>
+      <c r="B1190" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1190" t="n">
+        <v>324.26</v>
+      </c>
+      <c r="G1190" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="H1190" s="2" t="n">
+        <v>46088.05567049429</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>ed88fb44-c86b-4715-a767-834c2848c74e</t>
+        </is>
+      </c>
+      <c r="B1191" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1191" t="n">
+        <v>448.59</v>
+      </c>
+      <c r="G1191" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="H1191" s="2" t="n">
+        <v>46095.05567049731</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>3f17a970-39db-4117-85be-a95d593c2536</t>
+        </is>
+      </c>
+      <c r="B1192" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1192" t="n">
+        <v>108.72</v>
+      </c>
+      <c r="G1192" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H1192" s="2" t="n">
+        <v>46081.0556705006</v>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>8acd125c-97ca-40ee-a7fe-fb2143675c19</t>
+        </is>
+      </c>
+      <c r="B1193" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1193" t="n">
+        <v>444.97</v>
+      </c>
+      <c r="G1193" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="H1193" s="2" t="n">
+        <v>46088.05567050374</v>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>e7728085-bf72-47c0-a8cf-b4110c3548aa</t>
+        </is>
+      </c>
+      <c r="B1194" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1194" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="G1194" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H1194" s="2" t="n">
+        <v>46070.05567050678</v>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>843a114b-443f-4556-b73b-2876fcff2f82</t>
+        </is>
+      </c>
+      <c r="B1195" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1195" t="n">
+        <v>114.4</v>
+      </c>
+      <c r="G1195" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H1195" s="2" t="n">
+        <v>46067.05567050973</v>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>b5b095cb-ccec-4024-95c6-af22afb6b6f5</t>
+        </is>
+      </c>
+      <c r="B1196" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1196" t="n">
+        <v>192.3</v>
+      </c>
+      <c r="G1196" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H1196" s="2" t="n">
+        <v>46069.0556705131</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>e55383eb-f12d-4688-ad53-c70b1cbcae49</t>
+        </is>
+      </c>
+      <c r="B1197" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1197" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="G1197" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H1197" s="2" t="n">
+        <v>46074.05567051612</v>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>57c46f50-a180-4588-9da7-adac5f8b862e</t>
+        </is>
+      </c>
+      <c r="B1198" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1198" t="n">
+        <v>494.11</v>
+      </c>
+      <c r="G1198" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="H1198" s="2" t="n">
+        <v>46075.05567051921</v>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>a54b3498-017c-4e06-977a-b50cc555b9b6</t>
+        </is>
+      </c>
+      <c r="B1199" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1199" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="G1199" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H1199" s="2" t="n">
+        <v>46085.05567052276</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>9c6e2f28-7db4-4bd1-8fce-f4b1fb405422</t>
+        </is>
+      </c>
+      <c r="B1200" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1200" t="n">
+        <v>283.88</v>
+      </c>
+      <c r="G1200" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="H1200" s="2" t="n">
+        <v>46081.05567052597</v>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>c86a7f02-5792-4c0d-8afb-4325fd0b98fe</t>
+        </is>
+      </c>
+      <c r="B1201" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1201" t="n">
+        <v>449.74</v>
+      </c>
+      <c r="G1201" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H1201" s="2" t="n">
+        <v>46068.05567052915</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1201"/>
+  <dimension ref="A1:H1251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39605,7 +39605,7 @@
         <v>1.57</v>
       </c>
       <c r="H1152" s="2" t="n">
-        <v>46066.05567037185</v>
+        <v>46066.05567037037</v>
       </c>
     </row>
     <row r="1153">
@@ -39639,7 +39639,7 @@
         <v>1.41</v>
       </c>
       <c r="H1153" s="2" t="n">
-        <v>46088.05567037634</v>
+        <v>46088.05567038195</v>
       </c>
     </row>
     <row r="1154">
@@ -39673,7 +39673,7 @@
         <v>0.62</v>
       </c>
       <c r="H1154" s="2" t="n">
-        <v>46075.05567037963</v>
+        <v>46075.05567038195</v>
       </c>
     </row>
     <row r="1155">
@@ -39707,7 +39707,7 @@
         <v>3.75</v>
       </c>
       <c r="H1155" s="2" t="n">
-        <v>46088.05567038291</v>
+        <v>46088.05567038195</v>
       </c>
     </row>
     <row r="1156">
@@ -39741,7 +39741,7 @@
         <v>1.87</v>
       </c>
       <c r="H1156" s="2" t="n">
-        <v>46067.05567038616</v>
+        <v>46067.05567038195</v>
       </c>
     </row>
     <row r="1157">
@@ -39775,7 +39775,7 @@
         <v>2.75</v>
       </c>
       <c r="H1157" s="2" t="n">
-        <v>46074.05567038919</v>
+        <v>46074.05567039352</v>
       </c>
     </row>
     <row r="1158">
@@ -39809,7 +39809,7 @@
         <v>0.06</v>
       </c>
       <c r="H1158" s="2" t="n">
-        <v>46079.05567039228</v>
+        <v>46079.05567039352</v>
       </c>
     </row>
     <row r="1159">
@@ -39843,7 +39843,7 @@
         <v>2.74</v>
       </c>
       <c r="H1159" s="2" t="n">
-        <v>46085.05567039533</v>
+        <v>46085.05567039352</v>
       </c>
     </row>
     <row r="1160">
@@ -39877,7 +39877,7 @@
         <v>0.25</v>
       </c>
       <c r="H1160" s="2" t="n">
-        <v>46088.05567039894</v>
+        <v>46088.05567039352</v>
       </c>
     </row>
     <row r="1161">
@@ -39911,7 +39911,7 @@
         <v>1.66</v>
       </c>
       <c r="H1161" s="2" t="n">
-        <v>46069.05567040199</v>
+        <v>46069.05567040509</v>
       </c>
     </row>
     <row r="1162">
@@ -39945,7 +39945,7 @@
         <v>3.88</v>
       </c>
       <c r="H1162" s="2" t="n">
-        <v>46086.05567040522</v>
+        <v>46086.05567040509</v>
       </c>
     </row>
     <row r="1163">
@@ -39979,7 +39979,7 @@
         <v>1.94</v>
       </c>
       <c r="H1163" s="2" t="n">
-        <v>46083.0556704085</v>
+        <v>46083.05567040509</v>
       </c>
     </row>
     <row r="1164">
@@ -40013,7 +40013,7 @@
         <v>4.58</v>
       </c>
       <c r="H1164" s="2" t="n">
-        <v>46079.05567041152</v>
+        <v>46079.05567041667</v>
       </c>
     </row>
     <row r="1165">
@@ -40047,7 +40047,7 @@
         <v>3.77</v>
       </c>
       <c r="H1165" s="2" t="n">
-        <v>46088.05567041459</v>
+        <v>46088.05567041667</v>
       </c>
     </row>
     <row r="1166">
@@ -40081,7 +40081,7 @@
         <v>2.03</v>
       </c>
       <c r="H1166" s="2" t="n">
-        <v>46094.05567041774</v>
+        <v>46094.05567041667</v>
       </c>
     </row>
     <row r="1167">
@@ -40115,7 +40115,7 @@
         <v>0.77</v>
       </c>
       <c r="H1167" s="2" t="n">
-        <v>46074.0556704211</v>
+        <v>46074.05567041667</v>
       </c>
     </row>
     <row r="1168">
@@ -40149,7 +40149,7 @@
         <v>4.48</v>
       </c>
       <c r="H1168" s="2" t="n">
-        <v>46081.0556704245</v>
+        <v>46081.05567042824</v>
       </c>
     </row>
     <row r="1169">
@@ -40183,7 +40183,7 @@
         <v>2.67</v>
       </c>
       <c r="H1169" s="2" t="n">
-        <v>46087.05567042749</v>
+        <v>46087.05567042824</v>
       </c>
     </row>
     <row r="1170">
@@ -40217,7 +40217,7 @@
         <v>2.72</v>
       </c>
       <c r="H1170" s="2" t="n">
-        <v>46072.05567043069</v>
+        <v>46072.05567042824</v>
       </c>
     </row>
     <row r="1171">
@@ -40251,7 +40251,7 @@
         <v>1.46</v>
       </c>
       <c r="H1171" s="2" t="n">
-        <v>46095.05567043377</v>
+        <v>46095.05567042824</v>
       </c>
     </row>
     <row r="1172">
@@ -40285,7 +40285,7 @@
         <v>2.32</v>
       </c>
       <c r="H1172" s="2" t="n">
-        <v>46082.0556704369</v>
+        <v>46082.05567043981</v>
       </c>
     </row>
     <row r="1173">
@@ -40319,7 +40319,7 @@
         <v>0.39</v>
       </c>
       <c r="H1173" s="2" t="n">
-        <v>46084.05567043996</v>
+        <v>46084.05567043981</v>
       </c>
     </row>
     <row r="1174">
@@ -40353,7 +40353,7 @@
         <v>3.14</v>
       </c>
       <c r="H1174" s="2" t="n">
-        <v>46075.05567044353</v>
+        <v>46075.05567043981</v>
       </c>
     </row>
     <row r="1175">
@@ -40387,7 +40387,7 @@
         <v>2.41</v>
       </c>
       <c r="H1175" s="2" t="n">
-        <v>46076.05567044654</v>
+        <v>46076.05567045139</v>
       </c>
     </row>
     <row r="1176">
@@ -40421,7 +40421,7 @@
         <v>1.19</v>
       </c>
       <c r="H1176" s="2" t="n">
-        <v>46072.05567044957</v>
+        <v>46072.05567045139</v>
       </c>
     </row>
     <row r="1177">
@@ -40455,7 +40455,7 @@
         <v>1.44</v>
       </c>
       <c r="H1177" s="2" t="n">
-        <v>46067.05567045262</v>
+        <v>46067.05567045139</v>
       </c>
     </row>
     <row r="1178">
@@ -40489,7 +40489,7 @@
         <v>1.77</v>
       </c>
       <c r="H1178" s="2" t="n">
-        <v>46070.05567045596</v>
+        <v>46070.05567045139</v>
       </c>
     </row>
     <row r="1179">
@@ -40523,7 +40523,7 @@
         <v>1.19</v>
       </c>
       <c r="H1179" s="2" t="n">
-        <v>46084.05567045918</v>
+        <v>46084.05567046296</v>
       </c>
     </row>
     <row r="1180">
@@ -40557,7 +40557,7 @@
         <v>3.19</v>
       </c>
       <c r="H1180" s="2" t="n">
-        <v>46075.05567046218</v>
+        <v>46075.05567046296</v>
       </c>
     </row>
     <row r="1181">
@@ -40591,7 +40591,7 @@
         <v>4.37</v>
       </c>
       <c r="H1181" s="2" t="n">
-        <v>46076.05567046547</v>
+        <v>46076.05567046296</v>
       </c>
     </row>
     <row r="1182">
@@ -40625,7 +40625,7 @@
         <v>3.27</v>
       </c>
       <c r="H1182" s="2" t="n">
-        <v>46080.05567046876</v>
+        <v>46080.05567047454</v>
       </c>
     </row>
     <row r="1183">
@@ -40659,7 +40659,7 @@
         <v>0.9</v>
       </c>
       <c r="H1183" s="2" t="n">
-        <v>46069.05567047193</v>
+        <v>46069.05567047454</v>
       </c>
     </row>
     <row r="1184">
@@ -40693,7 +40693,7 @@
         <v>0.49</v>
       </c>
       <c r="H1184" s="2" t="n">
-        <v>46094.05567047513</v>
+        <v>46094.05567047454</v>
       </c>
     </row>
     <row r="1185">
@@ -40727,7 +40727,7 @@
         <v>0.31</v>
       </c>
       <c r="H1185" s="2" t="n">
-        <v>46076.0556704785</v>
+        <v>46076.05567047454</v>
       </c>
     </row>
     <row r="1186">
@@ -40761,7 +40761,7 @@
         <v>3.16</v>
       </c>
       <c r="H1186" s="2" t="n">
-        <v>46089.05567048164</v>
+        <v>46089.05567048611</v>
       </c>
     </row>
     <row r="1187">
@@ -40795,7 +40795,7 @@
         <v>2.53</v>
       </c>
       <c r="H1187" s="2" t="n">
-        <v>46092.05567048479</v>
+        <v>46092.05567048611</v>
       </c>
     </row>
     <row r="1188">
@@ -40829,7 +40829,7 @@
         <v>0.96</v>
       </c>
       <c r="H1188" s="2" t="n">
-        <v>46084.05567048779</v>
+        <v>46084.05567048611</v>
       </c>
     </row>
     <row r="1189">
@@ -40863,7 +40863,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="H1189" s="2" t="n">
-        <v>46071.05567049114</v>
+        <v>46071.05567048611</v>
       </c>
     </row>
     <row r="1190">
@@ -40897,7 +40897,7 @@
         <v>3.24</v>
       </c>
       <c r="H1190" s="2" t="n">
-        <v>46088.05567049429</v>
+        <v>46088.05567049768</v>
       </c>
     </row>
     <row r="1191">
@@ -40931,7 +40931,7 @@
         <v>4.49</v>
       </c>
       <c r="H1191" s="2" t="n">
-        <v>46095.05567049731</v>
+        <v>46095.05567049768</v>
       </c>
     </row>
     <row r="1192">
@@ -40965,7 +40965,7 @@
         <v>1.09</v>
       </c>
       <c r="H1192" s="2" t="n">
-        <v>46081.0556705006</v>
+        <v>46081.05567049768</v>
       </c>
     </row>
     <row r="1193">
@@ -40999,7 +40999,7 @@
         <v>4.45</v>
       </c>
       <c r="H1193" s="2" t="n">
-        <v>46088.05567050374</v>
+        <v>46088.05567050926</v>
       </c>
     </row>
     <row r="1194">
@@ -41033,7 +41033,7 @@
         <v>0.11</v>
       </c>
       <c r="H1194" s="2" t="n">
-        <v>46070.05567050678</v>
+        <v>46070.05567050926</v>
       </c>
     </row>
     <row r="1195">
@@ -41067,7 +41067,7 @@
         <v>1.14</v>
       </c>
       <c r="H1195" s="2" t="n">
-        <v>46067.05567050973</v>
+        <v>46067.05567050926</v>
       </c>
     </row>
     <row r="1196">
@@ -41101,7 +41101,7 @@
         <v>1.92</v>
       </c>
       <c r="H1196" s="2" t="n">
-        <v>46069.0556705131</v>
+        <v>46069.05567050926</v>
       </c>
     </row>
     <row r="1197">
@@ -41135,7 +41135,7 @@
         <v>0.11</v>
       </c>
       <c r="H1197" s="2" t="n">
-        <v>46074.05567051612</v>
+        <v>46074.05567052084</v>
       </c>
     </row>
     <row r="1198">
@@ -41169,7 +41169,7 @@
         <v>4.94</v>
       </c>
       <c r="H1198" s="2" t="n">
-        <v>46075.05567051921</v>
+        <v>46075.05567052084</v>
       </c>
     </row>
     <row r="1199">
@@ -41203,7 +41203,7 @@
         <v>0.18</v>
       </c>
       <c r="H1199" s="2" t="n">
-        <v>46085.05567052276</v>
+        <v>46085.05567052084</v>
       </c>
     </row>
     <row r="1200">
@@ -41237,7 +41237,7 @@
         <v>2.84</v>
       </c>
       <c r="H1200" s="2" t="n">
-        <v>46081.05567052597</v>
+        <v>46081.05567052084</v>
       </c>
     </row>
     <row r="1201">
@@ -41271,7 +41271,1707 @@
         <v>4.5</v>
       </c>
       <c r="H1201" s="2" t="n">
-        <v>46068.05567052915</v>
+        <v>46068.05567053241</v>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>9a8ff805-6da3-4da3-b1ef-f58c00603732</t>
+        </is>
+      </c>
+      <c r="B1202" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1202" t="n">
+        <v>208.45</v>
+      </c>
+      <c r="G1202" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H1202" s="2" t="n">
+        <v>46077.17316444519</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>6eb81ee1-6e66-41bc-9aed-38095788779f</t>
+        </is>
+      </c>
+      <c r="B1203" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1203" t="n">
+        <v>252.91</v>
+      </c>
+      <c r="G1203" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="H1203" s="2" t="n">
+        <v>46066.17316444956</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>7cfc8e0c-02a5-4518-9d5a-7113557c184e</t>
+        </is>
+      </c>
+      <c r="B1204" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1204" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="G1204" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H1204" s="2" t="n">
+        <v>46076.17316445275</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>596693ff-c197-470c-83c5-ff193f42a5ed</t>
+        </is>
+      </c>
+      <c r="B1205" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1205" t="n">
+        <v>450.09</v>
+      </c>
+      <c r="G1205" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H1205" s="2" t="n">
+        <v>46090.17316445591</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>2dde8c4e-2466-4cf3-accf-9d2acd738fbb</t>
+        </is>
+      </c>
+      <c r="B1206" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1206" t="n">
+        <v>267.3</v>
+      </c>
+      <c r="G1206" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="H1206" s="2" t="n">
+        <v>46086.17316445887</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>f021a564-f38d-4a0a-b157-17e169e61a38</t>
+        </is>
+      </c>
+      <c r="B1207" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1207" t="n">
+        <v>315.81</v>
+      </c>
+      <c r="G1207" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="H1207" s="2" t="n">
+        <v>46066.17316446183</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>3a1d1b14-3923-45b1-b286-e485dd10740c</t>
+        </is>
+      </c>
+      <c r="B1208" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1208" t="n">
+        <v>208.75</v>
+      </c>
+      <c r="G1208" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="H1208" s="2" t="n">
+        <v>46074.17316446478</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>2071a1ba-aae1-400f-aad6-a03e2c96d338</t>
+        </is>
+      </c>
+      <c r="B1209" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1209" t="n">
+        <v>168.97</v>
+      </c>
+      <c r="G1209" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H1209" s="2" t="n">
+        <v>46073.17316446762</v>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>9ad3e4dc-e4d4-45a3-bd81-430fdbcf5f65</t>
+        </is>
+      </c>
+      <c r="B1210" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1210" t="n">
+        <v>309.53</v>
+      </c>
+      <c r="G1210" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H1210" s="2" t="n">
+        <v>46095.17316447046</v>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>e58e06c0-083a-4911-88db-58130f90716c</t>
+        </is>
+      </c>
+      <c r="B1211" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1211" t="n">
+        <v>198.05</v>
+      </c>
+      <c r="G1211" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H1211" s="2" t="n">
+        <v>46085.17316447342</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>ac1cc16c-c20a-4c98-827a-b36c83d66644</t>
+        </is>
+      </c>
+      <c r="B1212" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1212" t="n">
+        <v>353.65</v>
+      </c>
+      <c r="G1212" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="H1212" s="2" t="n">
+        <v>46093.17316447636</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>61ef864d-5038-4613-983f-45fc3d206e2b</t>
+        </is>
+      </c>
+      <c r="B1213" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1213" t="n">
+        <v>124.92</v>
+      </c>
+      <c r="G1213" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H1213" s="2" t="n">
+        <v>46090.17316447932</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>dfeb839d-8703-433f-8bdd-56112e282277</t>
+        </is>
+      </c>
+      <c r="B1214" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1214" t="n">
+        <v>236.04</v>
+      </c>
+      <c r="G1214" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H1214" s="2" t="n">
+        <v>46073.17316448212</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>91b0138d-aecb-43cc-b23d-5d29a1db951f</t>
+        </is>
+      </c>
+      <c r="B1215" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1215" t="n">
+        <v>198.55</v>
+      </c>
+      <c r="G1215" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H1215" s="2" t="n">
+        <v>46079.17316448507</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>9c8e2496-1f1e-405e-9fa0-985b00fda461</t>
+        </is>
+      </c>
+      <c r="B1216" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1216" t="n">
+        <v>259.58</v>
+      </c>
+      <c r="G1216" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H1216" s="2" t="n">
+        <v>46070.17316448804</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>55a1d6a0-fffd-4488-b317-a266765d87a0</t>
+        </is>
+      </c>
+      <c r="B1217" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1217" t="n">
+        <v>344.73</v>
+      </c>
+      <c r="G1217" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H1217" s="2" t="n">
+        <v>46083.17316449086</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>177bf079-0211-4389-8503-686b1f1a1a6d</t>
+        </is>
+      </c>
+      <c r="B1218" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1218" t="n">
+        <v>339.19</v>
+      </c>
+      <c r="G1218" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="H1218" s="2" t="n">
+        <v>46082.17316449368</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>9e93126b-69c6-4ad5-86c8-2bd587aa43ed</t>
+        </is>
+      </c>
+      <c r="B1219" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1219" t="n">
+        <v>303.69</v>
+      </c>
+      <c r="G1219" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="H1219" s="2" t="n">
+        <v>46078.17316449668</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>c30dcdeb-1eb3-4e45-bd5c-88e93fb3840e</t>
+        </is>
+      </c>
+      <c r="B1220" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1220" t="n">
+        <v>499.23</v>
+      </c>
+      <c r="G1220" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="H1220" s="2" t="n">
+        <v>46079.17316449956</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>be96c13b-a08f-47f8-9b98-91042f4d0095</t>
+        </is>
+      </c>
+      <c r="B1221" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1221" t="n">
+        <v>292.46</v>
+      </c>
+      <c r="G1221" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H1221" s="2" t="n">
+        <v>46081.1731645024</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>e9cc9899-a89d-4165-9b89-8dcdbb2e5949</t>
+        </is>
+      </c>
+      <c r="B1222" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1222" t="n">
+        <v>456.82</v>
+      </c>
+      <c r="G1222" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="H1222" s="2" t="n">
+        <v>46082.17316450524</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>bfc165f5-879e-485f-a379-7a153e0cb1f7</t>
+        </is>
+      </c>
+      <c r="B1223" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1223" t="n">
+        <v>348.47</v>
+      </c>
+      <c r="G1223" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="H1223" s="2" t="n">
+        <v>46086.17316450816</v>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>c49fa654-d4bc-423d-9713-72190c1a1eb5</t>
+        </is>
+      </c>
+      <c r="B1224" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1224" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="G1224" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H1224" s="2" t="n">
+        <v>46072.17316451106</v>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>0c3b1af1-6e10-4338-b047-6ad57d99f9e2</t>
+        </is>
+      </c>
+      <c r="B1225" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1225" t="n">
+        <v>201.71</v>
+      </c>
+      <c r="G1225" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H1225" s="2" t="n">
+        <v>46068.17316451402</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>d17e70c4-6cfb-4fcb-ab96-cf70cb5d3c51</t>
+        </is>
+      </c>
+      <c r="B1226" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1226" t="n">
+        <v>148.53</v>
+      </c>
+      <c r="G1226" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H1226" s="2" t="n">
+        <v>46086.1731645168</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>a05239ce-9766-4939-8328-c688ce099f98</t>
+        </is>
+      </c>
+      <c r="B1227" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1227" t="n">
+        <v>485.47</v>
+      </c>
+      <c r="G1227" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="H1227" s="2" t="n">
+        <v>46080.17316451982</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>fb91054a-0ddc-449f-9813-17f721d8ed71</t>
+        </is>
+      </c>
+      <c r="B1228" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1228" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1228" t="n">
+        <v>189.84</v>
+      </c>
+      <c r="G1228" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H1228" s="2" t="n">
+        <v>46086.17316452265</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>438e6c33-561f-40e8-8db1-dfdca7b3e896</t>
+        </is>
+      </c>
+      <c r="B1229" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1229" t="n">
+        <v>149.46</v>
+      </c>
+      <c r="G1229" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H1229" s="2" t="n">
+        <v>46067.17316452546</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>eb675ef2-a6e8-408c-aaae-53eafb439578</t>
+        </is>
+      </c>
+      <c r="B1230" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1230" t="n">
+        <v>103.09</v>
+      </c>
+      <c r="G1230" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H1230" s="2" t="n">
+        <v>46086.17316452834</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>9a31b5aa-4f68-4fbe-873a-0448c3f59d19</t>
+        </is>
+      </c>
+      <c r="B1231" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1231" t="n">
+        <v>354.65</v>
+      </c>
+      <c r="G1231" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H1231" s="2" t="n">
+        <v>46067.1731645313</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>08ef3b3a-3584-40e2-ae2d-db4b7260616c</t>
+        </is>
+      </c>
+      <c r="B1232" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1232" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1232" t="n">
+        <v>160.25</v>
+      </c>
+      <c r="G1232" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H1232" s="2" t="n">
+        <v>46085.17316453414</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>87536869-7fa6-422f-825f-36f07177e404</t>
+        </is>
+      </c>
+      <c r="B1233" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1233" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1233" t="n">
+        <v>91.34999999999999</v>
+      </c>
+      <c r="G1233" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H1233" s="2" t="n">
+        <v>46086.17316453707</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>7e5f2b36-466e-48ab-912b-15351ead53c6</t>
+        </is>
+      </c>
+      <c r="B1234" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1234" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1234" t="n">
+        <v>348.58</v>
+      </c>
+      <c r="G1234" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="H1234" s="2" t="n">
+        <v>46093.17316453999</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>a0a624e9-5a4e-4e4e-8f0e-f5c33e9065b1</t>
+        </is>
+      </c>
+      <c r="B1235" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1235" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1235" t="n">
+        <v>195.44</v>
+      </c>
+      <c r="G1235" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H1235" s="2" t="n">
+        <v>46078.17316454306</v>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>7da06451-7637-4e8e-a945-bbd0f9c4c823</t>
+        </is>
+      </c>
+      <c r="B1236" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1236" t="n">
+        <v>120.89</v>
+      </c>
+      <c r="G1236" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="H1236" s="2" t="n">
+        <v>46075.17316454583</v>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>70e017c0-d36d-4bb3-80dd-50cef40c261c</t>
+        </is>
+      </c>
+      <c r="B1237" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1237" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1237" t="n">
+        <v>354.73</v>
+      </c>
+      <c r="G1237" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H1237" s="2" t="n">
+        <v>46089.17316454877</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>6748ac31-4d13-4f4f-a60e-1fdff1edf4dd</t>
+        </is>
+      </c>
+      <c r="B1238" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1238" t="n">
+        <v>67.34</v>
+      </c>
+      <c r="G1238" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H1238" s="2" t="n">
+        <v>46067.17316455154</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>32ae9cc1-19eb-44e4-8424-4ff932fc20ce</t>
+        </is>
+      </c>
+      <c r="B1239" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1239" t="n">
+        <v>76.91</v>
+      </c>
+      <c r="G1239" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="H1239" s="2" t="n">
+        <v>46094.17316455442</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>3e2da127-51fa-4e4b-a534-c680530aac0f</t>
+        </is>
+      </c>
+      <c r="B1240" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1240" t="n">
+        <v>135.6</v>
+      </c>
+      <c r="G1240" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H1240" s="2" t="n">
+        <v>46069.17316455724</v>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>03edb0d7-86ad-4298-85bb-d8383182d0e5</t>
+        </is>
+      </c>
+      <c r="B1241" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1241" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1241" t="n">
+        <v>421.79</v>
+      </c>
+      <c r="G1241" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="H1241" s="2" t="n">
+        <v>46075.17316456001</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>4c573721-54ef-44ec-b407-144c237e2596</t>
+        </is>
+      </c>
+      <c r="B1242" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1242" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1242" t="n">
+        <v>373.11</v>
+      </c>
+      <c r="G1242" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="H1242" s="2" t="n">
+        <v>46067.17316456295</v>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>02f6b388-0396-44af-af45-818bf41cecee</t>
+        </is>
+      </c>
+      <c r="B1243" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1243" t="n">
+        <v>90.06999999999999</v>
+      </c>
+      <c r="G1243" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H1243" s="2" t="n">
+        <v>46074.17316456592</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>e5566647-dbd8-4d00-9f9f-bf4e8f44350f</t>
+        </is>
+      </c>
+      <c r="B1244" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1244" t="n">
+        <v>51.77</v>
+      </c>
+      <c r="G1244" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H1244" s="2" t="n">
+        <v>46077.17316456875</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>53d03aa6-8b91-4402-afc5-18e0a2422c7d</t>
+        </is>
+      </c>
+      <c r="B1245" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1245" t="n">
+        <v>401.55</v>
+      </c>
+      <c r="G1245" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="H1245" s="2" t="n">
+        <v>46075.1731645716</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>b3525334-3cb2-461b-855b-ba39faa00e6e</t>
+        </is>
+      </c>
+      <c r="B1246" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1246" t="n">
+        <v>419.84</v>
+      </c>
+      <c r="G1246" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H1246" s="2" t="n">
+        <v>46073.17316457452</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>be6fbd69-e5c9-47ac-94c5-a6eddb3ee14c</t>
+        </is>
+      </c>
+      <c r="B1247" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1247" t="n">
+        <v>403.47</v>
+      </c>
+      <c r="G1247" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H1247" s="2" t="n">
+        <v>46088.17316457738</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>0bdb2e56-1f52-4ed9-a45a-a0069354e994</t>
+        </is>
+      </c>
+      <c r="B1248" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1248" t="n">
+        <v>142.91</v>
+      </c>
+      <c r="G1248" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H1248" s="2" t="n">
+        <v>46072.17316458028</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>18b55cba-6b9c-4e06-9977-e93909a1f08e</t>
+        </is>
+      </c>
+      <c r="B1249" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1249" t="n">
+        <v>223.16</v>
+      </c>
+      <c r="G1249" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H1249" s="2" t="n">
+        <v>46067.17316458326</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>c559c979-3a78-4837-9383-c508d34515c8</t>
+        </is>
+      </c>
+      <c r="B1250" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1250" t="n">
+        <v>356.34</v>
+      </c>
+      <c r="G1250" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="H1250" s="2" t="n">
+        <v>46069.17316458606</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>db3046ee-b42d-4d8f-86d3-2f3c746bcd21</t>
+        </is>
+      </c>
+      <c r="B1251" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1251" t="n">
+        <v>358.66</v>
+      </c>
+      <c r="G1251" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="H1251" s="2" t="n">
+        <v>46078.17316458908</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1251"/>
+  <dimension ref="A1:H1301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41305,7 +41305,7 @@
         <v>2.08</v>
       </c>
       <c r="H1202" s="2" t="n">
-        <v>46077.17316444519</v>
+        <v>46077.17316444444</v>
       </c>
     </row>
     <row r="1203">
@@ -41339,7 +41339,7 @@
         <v>2.53</v>
       </c>
       <c r="H1203" s="2" t="n">
-        <v>46066.17316444956</v>
+        <v>46066.17316444444</v>
       </c>
     </row>
     <row r="1204">
@@ -41373,7 +41373,7 @@
         <v>0.54</v>
       </c>
       <c r="H1204" s="2" t="n">
-        <v>46076.17316445275</v>
+        <v>46076.17316445602</v>
       </c>
     </row>
     <row r="1205">
@@ -41407,7 +41407,7 @@
         <v>4.5</v>
       </c>
       <c r="H1205" s="2" t="n">
-        <v>46090.17316445591</v>
+        <v>46090.17316445602</v>
       </c>
     </row>
     <row r="1206">
@@ -41441,7 +41441,7 @@
         <v>2.67</v>
       </c>
       <c r="H1206" s="2" t="n">
-        <v>46086.17316445887</v>
+        <v>46086.17316445602</v>
       </c>
     </row>
     <row r="1207">
@@ -41475,7 +41475,7 @@
         <v>3.16</v>
       </c>
       <c r="H1207" s="2" t="n">
-        <v>46066.17316446183</v>
+        <v>46066.17316446759</v>
       </c>
     </row>
     <row r="1208">
@@ -41509,7 +41509,7 @@
         <v>2.09</v>
       </c>
       <c r="H1208" s="2" t="n">
-        <v>46074.17316446478</v>
+        <v>46074.17316446759</v>
       </c>
     </row>
     <row r="1209">
@@ -41543,7 +41543,7 @@
         <v>1.69</v>
       </c>
       <c r="H1209" s="2" t="n">
-        <v>46073.17316446762</v>
+        <v>46073.17316446759</v>
       </c>
     </row>
     <row r="1210">
@@ -41577,7 +41577,7 @@
         <v>3.1</v>
       </c>
       <c r="H1210" s="2" t="n">
-        <v>46095.17316447046</v>
+        <v>46095.17316446759</v>
       </c>
     </row>
     <row r="1211">
@@ -41611,7 +41611,7 @@
         <v>1.98</v>
       </c>
       <c r="H1211" s="2" t="n">
-        <v>46085.17316447342</v>
+        <v>46085.17316447917</v>
       </c>
     </row>
     <row r="1212">
@@ -41645,7 +41645,7 @@
         <v>3.54</v>
       </c>
       <c r="H1212" s="2" t="n">
-        <v>46093.17316447636</v>
+        <v>46093.17316447917</v>
       </c>
     </row>
     <row r="1213">
@@ -41679,7 +41679,7 @@
         <v>1.25</v>
       </c>
       <c r="H1213" s="2" t="n">
-        <v>46090.17316447932</v>
+        <v>46090.17316447917</v>
       </c>
     </row>
     <row r="1214">
@@ -41713,7 +41713,7 @@
         <v>2.36</v>
       </c>
       <c r="H1214" s="2" t="n">
-        <v>46073.17316448212</v>
+        <v>46073.17316447917</v>
       </c>
     </row>
     <row r="1215">
@@ -41747,7 +41747,7 @@
         <v>1.99</v>
       </c>
       <c r="H1215" s="2" t="n">
-        <v>46079.17316448507</v>
+        <v>46079.17316449074</v>
       </c>
     </row>
     <row r="1216">
@@ -41781,7 +41781,7 @@
         <v>2.6</v>
       </c>
       <c r="H1216" s="2" t="n">
-        <v>46070.17316448804</v>
+        <v>46070.17316449074</v>
       </c>
     </row>
     <row r="1217">
@@ -41815,7 +41815,7 @@
         <v>3.45</v>
       </c>
       <c r="H1217" s="2" t="n">
-        <v>46083.17316449086</v>
+        <v>46083.17316449074</v>
       </c>
     </row>
     <row r="1218">
@@ -41849,7 +41849,7 @@
         <v>3.39</v>
       </c>
       <c r="H1218" s="2" t="n">
-        <v>46082.17316449368</v>
+        <v>46082.17316449074</v>
       </c>
     </row>
     <row r="1219">
@@ -41883,7 +41883,7 @@
         <v>3.04</v>
       </c>
       <c r="H1219" s="2" t="n">
-        <v>46078.17316449668</v>
+        <v>46078.17316450232</v>
       </c>
     </row>
     <row r="1220">
@@ -41917,7 +41917,7 @@
         <v>4.99</v>
       </c>
       <c r="H1220" s="2" t="n">
-        <v>46079.17316449956</v>
+        <v>46079.17316450232</v>
       </c>
     </row>
     <row r="1221">
@@ -41951,7 +41951,7 @@
         <v>2.92</v>
       </c>
       <c r="H1221" s="2" t="n">
-        <v>46081.1731645024</v>
+        <v>46081.17316450232</v>
       </c>
     </row>
     <row r="1222">
@@ -41985,7 +41985,7 @@
         <v>4.57</v>
       </c>
       <c r="H1222" s="2" t="n">
-        <v>46082.17316450524</v>
+        <v>46082.17316450232</v>
       </c>
     </row>
     <row r="1223">
@@ -42019,7 +42019,7 @@
         <v>3.48</v>
       </c>
       <c r="H1223" s="2" t="n">
-        <v>46086.17316450816</v>
+        <v>46086.17316451389</v>
       </c>
     </row>
     <row r="1224">
@@ -42053,7 +42053,7 @@
         <v>0.21</v>
       </c>
       <c r="H1224" s="2" t="n">
-        <v>46072.17316451106</v>
+        <v>46072.17316451389</v>
       </c>
     </row>
     <row r="1225">
@@ -42087,7 +42087,7 @@
         <v>2.02</v>
       </c>
       <c r="H1225" s="2" t="n">
-        <v>46068.17316451402</v>
+        <v>46068.17316451389</v>
       </c>
     </row>
     <row r="1226">
@@ -42121,7 +42121,7 @@
         <v>1.49</v>
       </c>
       <c r="H1226" s="2" t="n">
-        <v>46086.1731645168</v>
+        <v>46086.17316451389</v>
       </c>
     </row>
     <row r="1227">
@@ -42155,7 +42155,7 @@
         <v>4.85</v>
       </c>
       <c r="H1227" s="2" t="n">
-        <v>46080.17316451982</v>
+        <v>46080.17316452546</v>
       </c>
     </row>
     <row r="1228">
@@ -42189,7 +42189,7 @@
         <v>1.9</v>
       </c>
       <c r="H1228" s="2" t="n">
-        <v>46086.17316452265</v>
+        <v>46086.17316452546</v>
       </c>
     </row>
     <row r="1229">
@@ -42257,7 +42257,7 @@
         <v>1.03</v>
       </c>
       <c r="H1230" s="2" t="n">
-        <v>46086.17316452834</v>
+        <v>46086.17316452546</v>
       </c>
     </row>
     <row r="1231">
@@ -42291,7 +42291,7 @@
         <v>3.55</v>
       </c>
       <c r="H1231" s="2" t="n">
-        <v>46067.1731645313</v>
+        <v>46067.17316453704</v>
       </c>
     </row>
     <row r="1232">
@@ -42325,7 +42325,7 @@
         <v>1.6</v>
       </c>
       <c r="H1232" s="2" t="n">
-        <v>46085.17316453414</v>
+        <v>46085.17316453704</v>
       </c>
     </row>
     <row r="1233">
@@ -42359,7 +42359,7 @@
         <v>0.91</v>
       </c>
       <c r="H1233" s="2" t="n">
-        <v>46086.17316453707</v>
+        <v>46086.17316453704</v>
       </c>
     </row>
     <row r="1234">
@@ -42393,7 +42393,7 @@
         <v>3.49</v>
       </c>
       <c r="H1234" s="2" t="n">
-        <v>46093.17316453999</v>
+        <v>46093.17316453704</v>
       </c>
     </row>
     <row r="1235">
@@ -42427,7 +42427,7 @@
         <v>1.95</v>
       </c>
       <c r="H1235" s="2" t="n">
-        <v>46078.17316454306</v>
+        <v>46078.17316454861</v>
       </c>
     </row>
     <row r="1236">
@@ -42461,7 +42461,7 @@
         <v>1.21</v>
       </c>
       <c r="H1236" s="2" t="n">
-        <v>46075.17316454583</v>
+        <v>46075.17316454861</v>
       </c>
     </row>
     <row r="1237">
@@ -42495,7 +42495,7 @@
         <v>3.55</v>
       </c>
       <c r="H1237" s="2" t="n">
-        <v>46089.17316454877</v>
+        <v>46089.17316454861</v>
       </c>
     </row>
     <row r="1238">
@@ -42529,7 +42529,7 @@
         <v>0.67</v>
       </c>
       <c r="H1238" s="2" t="n">
-        <v>46067.17316455154</v>
+        <v>46067.17316454861</v>
       </c>
     </row>
     <row r="1239">
@@ -42563,7 +42563,7 @@
         <v>0.77</v>
       </c>
       <c r="H1239" s="2" t="n">
-        <v>46094.17316455442</v>
+        <v>46094.17316456018</v>
       </c>
     </row>
     <row r="1240">
@@ -42597,7 +42597,7 @@
         <v>1.36</v>
       </c>
       <c r="H1240" s="2" t="n">
-        <v>46069.17316455724</v>
+        <v>46069.17316456018</v>
       </c>
     </row>
     <row r="1241">
@@ -42631,7 +42631,7 @@
         <v>4.22</v>
       </c>
       <c r="H1241" s="2" t="n">
-        <v>46075.17316456001</v>
+        <v>46075.17316456018</v>
       </c>
     </row>
     <row r="1242">
@@ -42665,7 +42665,7 @@
         <v>3.73</v>
       </c>
       <c r="H1242" s="2" t="n">
-        <v>46067.17316456295</v>
+        <v>46067.17316456018</v>
       </c>
     </row>
     <row r="1243">
@@ -42699,7 +42699,7 @@
         <v>0.9</v>
       </c>
       <c r="H1243" s="2" t="n">
-        <v>46074.17316456592</v>
+        <v>46074.17316456018</v>
       </c>
     </row>
     <row r="1244">
@@ -42733,7 +42733,7 @@
         <v>0.52</v>
       </c>
       <c r="H1244" s="2" t="n">
-        <v>46077.17316456875</v>
+        <v>46077.17316457176</v>
       </c>
     </row>
     <row r="1245">
@@ -42767,7 +42767,7 @@
         <v>4.02</v>
       </c>
       <c r="H1245" s="2" t="n">
-        <v>46075.1731645716</v>
+        <v>46075.17316457176</v>
       </c>
     </row>
     <row r="1246">
@@ -42801,7 +42801,7 @@
         <v>4.2</v>
       </c>
       <c r="H1246" s="2" t="n">
-        <v>46073.17316457452</v>
+        <v>46073.17316457176</v>
       </c>
     </row>
     <row r="1247">
@@ -42835,7 +42835,7 @@
         <v>4.03</v>
       </c>
       <c r="H1247" s="2" t="n">
-        <v>46088.17316457738</v>
+        <v>46088.17316457176</v>
       </c>
     </row>
     <row r="1248">
@@ -42869,7 +42869,7 @@
         <v>1.43</v>
       </c>
       <c r="H1248" s="2" t="n">
-        <v>46072.17316458028</v>
+        <v>46072.17316458334</v>
       </c>
     </row>
     <row r="1249">
@@ -42903,7 +42903,7 @@
         <v>2.23</v>
       </c>
       <c r="H1249" s="2" t="n">
-        <v>46067.17316458326</v>
+        <v>46067.17316458334</v>
       </c>
     </row>
     <row r="1250">
@@ -42937,7 +42937,7 @@
         <v>3.56</v>
       </c>
       <c r="H1250" s="2" t="n">
-        <v>46069.17316458606</v>
+        <v>46069.17316458334</v>
       </c>
     </row>
     <row r="1251">
@@ -42971,7 +42971,1707 @@
         <v>3.59</v>
       </c>
       <c r="H1251" s="2" t="n">
-        <v>46078.17316458908</v>
+        <v>46078.17316458334</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>c1afc87a-643f-4914-a4a9-ffc8466f3eb3</t>
+        </is>
+      </c>
+      <c r="B1252" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1252" t="n">
+        <v>415.49</v>
+      </c>
+      <c r="G1252" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="H1252" s="2" t="n">
+        <v>46091.24482821159</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>c6ea2614-3a4d-4eaa-9873-dbcbbfdb9431</t>
+        </is>
+      </c>
+      <c r="B1253" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1253" t="n">
+        <v>250.86</v>
+      </c>
+      <c r="G1253" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="H1253" s="2" t="n">
+        <v>46071.244828216</v>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>e82fe2e6-0b60-4807-bd8a-793a9b2f49fe</t>
+        </is>
+      </c>
+      <c r="B1254" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1254" t="n">
+        <v>374.37</v>
+      </c>
+      <c r="G1254" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H1254" s="2" t="n">
+        <v>46082.24482821939</v>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>13273bba-d933-4a91-938a-a7f7b28e8890</t>
+        </is>
+      </c>
+      <c r="B1255" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1255" t="n">
+        <v>56.59</v>
+      </c>
+      <c r="G1255" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H1255" s="2" t="n">
+        <v>46087.24482822263</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>234d1e42-9650-4cdf-8589-89c7e325b347</t>
+        </is>
+      </c>
+      <c r="B1256" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1256" t="n">
+        <v>252.1</v>
+      </c>
+      <c r="G1256" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H1256" s="2" t="n">
+        <v>46082.24482822619</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>36ac80a6-9ebf-4acf-962f-0b280dabc221</t>
+        </is>
+      </c>
+      <c r="B1257" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1257" t="n">
+        <v>181.26</v>
+      </c>
+      <c r="G1257" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H1257" s="2" t="n">
+        <v>46085.2448282293</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>d335773b-eda9-4318-9c55-8638aa61138c</t>
+        </is>
+      </c>
+      <c r="B1258" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1258" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1258" t="n">
+        <v>391.36</v>
+      </c>
+      <c r="G1258" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="H1258" s="2" t="n">
+        <v>46087.2448282324</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>09a0a469-10fd-41c9-b065-4effe35e04bb</t>
+        </is>
+      </c>
+      <c r="B1259" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1259" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1259" t="n">
+        <v>170.47</v>
+      </c>
+      <c r="G1259" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H1259" s="2" t="n">
+        <v>46090.24482823582</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>41781fb9-cd8a-47b8-9969-51c7327ca9b0</t>
+        </is>
+      </c>
+      <c r="B1260" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1260" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1260" t="n">
+        <v>368.76</v>
+      </c>
+      <c r="G1260" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="H1260" s="2" t="n">
+        <v>46076.24482823911</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>2e77154a-a2df-42fc-bd9b-331b1db91f45</t>
+        </is>
+      </c>
+      <c r="B1261" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1261" t="n">
+        <v>218.42</v>
+      </c>
+      <c r="G1261" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H1261" s="2" t="n">
+        <v>46089.24482824239</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>8508e6e9-6400-4104-bda2-c827580f5781</t>
+        </is>
+      </c>
+      <c r="B1262" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1262" t="n">
+        <v>163.21</v>
+      </c>
+      <c r="G1262" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H1262" s="2" t="n">
+        <v>46078.24482824582</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>cbde95c0-da37-4281-9c1a-418c872be54f</t>
+        </is>
+      </c>
+      <c r="B1263" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1263" t="n">
+        <v>260.09</v>
+      </c>
+      <c r="G1263" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H1263" s="2" t="n">
+        <v>46079.24482824931</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>329535c1-3bfe-4010-8fb3-a463cc2c53c8</t>
+        </is>
+      </c>
+      <c r="B1264" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1264" t="n">
+        <v>318.73</v>
+      </c>
+      <c r="G1264" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="H1264" s="2" t="n">
+        <v>46069.24482825241</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>a1c8ebe8-e479-481d-9f8d-bab0fbefd54e</t>
+        </is>
+      </c>
+      <c r="B1265" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1265" t="n">
+        <v>300.88</v>
+      </c>
+      <c r="G1265" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="H1265" s="2" t="n">
+        <v>46086.24482825548</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>db49429e-66c0-4409-bca7-8b57d328aaf4</t>
+        </is>
+      </c>
+      <c r="B1266" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1266" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="G1266" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H1266" s="2" t="n">
+        <v>46081.24482825883</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>7f543c70-cc08-4b4c-a892-e33637504543</t>
+        </is>
+      </c>
+      <c r="B1267" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1267" t="n">
+        <v>248.19</v>
+      </c>
+      <c r="G1267" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H1267" s="2" t="n">
+        <v>46069.24482826194</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>3e3e5545-d4d8-4bfa-bbfd-cd13ac788188</t>
+        </is>
+      </c>
+      <c r="B1268" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1268" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1268" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="G1268" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="H1268" s="2" t="n">
+        <v>46091.24482826502</v>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>045557d5-41d0-419b-ac29-8031371c7565</t>
+        </is>
+      </c>
+      <c r="B1269" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1269" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1269" t="n">
+        <v>368.66</v>
+      </c>
+      <c r="G1269" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="H1269" s="2" t="n">
+        <v>46074.24482826816</v>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>da24ee09-852a-43f6-bee2-dc6fa932d14a</t>
+        </is>
+      </c>
+      <c r="B1270" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1270" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1270" t="n">
+        <v>452.63</v>
+      </c>
+      <c r="G1270" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="H1270" s="2" t="n">
+        <v>46091.24482827157</v>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>10924f7b-09ee-4478-bc3b-610693f8af29</t>
+        </is>
+      </c>
+      <c r="B1271" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1271" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1271" t="n">
+        <v>154.15</v>
+      </c>
+      <c r="G1271" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="H1271" s="2" t="n">
+        <v>46066.24482827468</v>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>817f4449-3843-4f1f-9e20-196f05093068</t>
+        </is>
+      </c>
+      <c r="B1272" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1272" t="n">
+        <v>37.33</v>
+      </c>
+      <c r="G1272" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H1272" s="2" t="n">
+        <v>46091.24482827791</v>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>e02efd50-472d-423a-9220-99fcc0ff11e3</t>
+        </is>
+      </c>
+      <c r="B1273" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1273" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1273" t="n">
+        <v>261.91</v>
+      </c>
+      <c r="G1273" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H1273" s="2" t="n">
+        <v>46085.24482828128</v>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>bf19db49-3742-4d79-b413-c77141a69904</t>
+        </is>
+      </c>
+      <c r="B1274" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1274" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1274" t="n">
+        <v>315.31</v>
+      </c>
+      <c r="G1274" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H1274" s="2" t="n">
+        <v>46094.24482828451</v>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>8245ad66-a0ae-432a-b17a-b8ef166c9c1b</t>
+        </is>
+      </c>
+      <c r="B1275" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1275" t="n">
+        <v>326.88</v>
+      </c>
+      <c r="G1275" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="H1275" s="2" t="n">
+        <v>46094.24482828761</v>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>eeeb64f8-db7b-4d17-a698-800ecee7442e</t>
+        </is>
+      </c>
+      <c r="B1276" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1276" t="n">
+        <v>274.62</v>
+      </c>
+      <c r="G1276" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H1276" s="2" t="n">
+        <v>46071.24482829065</v>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>4a9d71b7-ec13-4219-bfef-da5f684e346d</t>
+        </is>
+      </c>
+      <c r="B1277" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1277" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1277" t="n">
+        <v>86.75</v>
+      </c>
+      <c r="G1277" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H1277" s="2" t="n">
+        <v>46082.24482829394</v>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>7363adaa-9a64-4f4b-912e-34a85500526c</t>
+        </is>
+      </c>
+      <c r="B1278" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1278" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1278" t="n">
+        <v>447.81</v>
+      </c>
+      <c r="G1278" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="H1278" s="2" t="n">
+        <v>46084.24482829705</v>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>245c0e15-5690-4550-9892-abbd6587468f</t>
+        </is>
+      </c>
+      <c r="B1279" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1279" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1279" t="n">
+        <v>299.96</v>
+      </c>
+      <c r="G1279" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1279" s="2" t="n">
+        <v>46073.24482830023</v>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>ef291911-db07-4742-9d82-5e60fd3904de</t>
+        </is>
+      </c>
+      <c r="B1280" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1280" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1280" t="n">
+        <v>423.7</v>
+      </c>
+      <c r="G1280" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="H1280" s="2" t="n">
+        <v>46093.24482830329</v>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>d8244b87-6537-433a-955c-1acb09861283</t>
+        </is>
+      </c>
+      <c r="B1281" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1281" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="G1281" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H1281" s="2" t="n">
+        <v>46068.24482830654</v>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>570f9ac6-f58d-4d2f-8e67-ef269695365e</t>
+        </is>
+      </c>
+      <c r="B1282" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1282" t="n">
+        <v>168.39</v>
+      </c>
+      <c r="G1282" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H1282" s="2" t="n">
+        <v>46073.24482830997</v>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>e4b8ea04-4e72-4fcf-9a43-a9fba34f0fa8</t>
+        </is>
+      </c>
+      <c r="B1283" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1283" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1283" t="n">
+        <v>383.32</v>
+      </c>
+      <c r="G1283" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="H1283" s="2" t="n">
+        <v>46092.24482831318</v>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>f76d1f94-d08f-4521-a9ea-ced64a27e7ac</t>
+        </is>
+      </c>
+      <c r="B1284" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1284" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1284" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="G1284" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H1284" s="2" t="n">
+        <v>46074.24482831665</v>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>2b26ed8c-4969-4498-8154-2f577b42efb8</t>
+        </is>
+      </c>
+      <c r="B1285" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1285" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1285" t="n">
+        <v>73.15000000000001</v>
+      </c>
+      <c r="G1285" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H1285" s="2" t="n">
+        <v>46084.24482831996</v>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>13fdc35e-5136-46d5-adac-c7cb4199e051</t>
+        </is>
+      </c>
+      <c r="B1286" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1286" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1286" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="G1286" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H1286" s="2" t="n">
+        <v>46091.24482832298</v>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>298736fc-77fe-447f-8feb-d01ab1a656bd</t>
+        </is>
+      </c>
+      <c r="B1287" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1287" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1287" t="n">
+        <v>132.56</v>
+      </c>
+      <c r="G1287" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H1287" s="2" t="n">
+        <v>46074.24482832605</v>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>c3cfbebe-94a1-4102-9d49-ccc86f61d85a</t>
+        </is>
+      </c>
+      <c r="B1288" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1288" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="G1288" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H1288" s="2" t="n">
+        <v>46069.24482832933</v>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>7ebc5a2d-c96b-47bb-8e15-ebe133d899da</t>
+        </is>
+      </c>
+      <c r="B1289" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1289" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1289" t="n">
+        <v>148.59</v>
+      </c>
+      <c r="G1289" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H1289" s="2" t="n">
+        <v>46089.24482833244</v>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>69a36108-4301-40fb-89af-82d0fd82c575</t>
+        </is>
+      </c>
+      <c r="B1290" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1290" t="n">
+        <v>477.78</v>
+      </c>
+      <c r="G1290" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H1290" s="2" t="n">
+        <v>46079.2448283356</v>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>73d3ee13-8936-43d6-bee6-e28a6201e3ab</t>
+        </is>
+      </c>
+      <c r="B1291" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1291" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1291" t="n">
+        <v>52.92</v>
+      </c>
+      <c r="G1291" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H1291" s="2" t="n">
+        <v>46080.24482833887</v>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>6d8619e4-69a3-4338-9b21-791a88a2b35c</t>
+        </is>
+      </c>
+      <c r="B1292" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1292" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1292" t="n">
+        <v>100.01</v>
+      </c>
+      <c r="G1292" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1292" s="2" t="n">
+        <v>46075.24482834214</v>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>7bbfdca7-3ad4-46b4-9297-7f13ac39e5c8</t>
+        </is>
+      </c>
+      <c r="B1293" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1293" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1293" t="n">
+        <v>281.36</v>
+      </c>
+      <c r="G1293" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="H1293" s="2" t="n">
+        <v>46073.24482834578</v>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>f8b4359f-457f-4743-9450-3f697c0915f0</t>
+        </is>
+      </c>
+      <c r="B1294" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1294" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1294" t="n">
+        <v>83.86</v>
+      </c>
+      <c r="G1294" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H1294" s="2" t="n">
+        <v>46086.24482834889</v>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>eb01cbf2-e9f5-459c-b243-8768aa44172f</t>
+        </is>
+      </c>
+      <c r="B1295" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1295" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1295" t="n">
+        <v>103.47</v>
+      </c>
+      <c r="G1295" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H1295" s="2" t="n">
+        <v>46070.24482835206</v>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>45f7d833-ad78-4bd0-aa46-0722228363ae</t>
+        </is>
+      </c>
+      <c r="B1296" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1296" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1296" t="n">
+        <v>189.96</v>
+      </c>
+      <c r="G1296" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H1296" s="2" t="n">
+        <v>46092.24482835516</v>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>ef79e2a1-f6c9-476b-952f-969c4cb4b643</t>
+        </is>
+      </c>
+      <c r="B1297" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1297" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1297" t="n">
+        <v>392.98</v>
+      </c>
+      <c r="G1297" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="H1297" s="2" t="n">
+        <v>46078.24482835824</v>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>2f568f3c-79b6-4786-a007-6b430fe5b2bd</t>
+        </is>
+      </c>
+      <c r="B1298" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1298" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1298" t="n">
+        <v>103.79</v>
+      </c>
+      <c r="G1298" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H1298" s="2" t="n">
+        <v>46087.24482836139</v>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>4f6598ee-d976-4fb2-a81d-9da12b17b329</t>
+        </is>
+      </c>
+      <c r="B1299" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1299" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1299" t="n">
+        <v>250.24</v>
+      </c>
+      <c r="G1299" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H1299" s="2" t="n">
+        <v>46066.24482836478</v>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>a5a0bc4a-ab0e-46d3-8297-2e0a6058aee8</t>
+        </is>
+      </c>
+      <c r="B1300" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1300" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1300" t="n">
+        <v>286.72</v>
+      </c>
+      <c r="G1300" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="H1300" s="2" t="n">
+        <v>46086.24482836779</v>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>6d2125d6-4fa7-4dfb-ad1a-6f00ed30bbfe</t>
+        </is>
+      </c>
+      <c r="B1301" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1301" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1301" t="n">
+        <v>95.08</v>
+      </c>
+      <c r="G1301" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H1301" s="2" t="n">
+        <v>46080.24482837086</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1301"/>
+  <dimension ref="A1:H1351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43005,7 +43005,7 @@
         <v>4.15</v>
       </c>
       <c r="H1252" s="2" t="n">
-        <v>46091.24482821159</v>
+        <v>46091.24482820602</v>
       </c>
     </row>
     <row r="1253">
@@ -43039,7 +43039,7 @@
         <v>2.51</v>
       </c>
       <c r="H1253" s="2" t="n">
-        <v>46071.244828216</v>
+        <v>46071.24482821759</v>
       </c>
     </row>
     <row r="1254">
@@ -43073,7 +43073,7 @@
         <v>3.74</v>
       </c>
       <c r="H1254" s="2" t="n">
-        <v>46082.24482821939</v>
+        <v>46082.24482821759</v>
       </c>
     </row>
     <row r="1255">
@@ -43107,7 +43107,7 @@
         <v>0.57</v>
       </c>
       <c r="H1255" s="2" t="n">
-        <v>46087.24482822263</v>
+        <v>46087.24482821759</v>
       </c>
     </row>
     <row r="1256">
@@ -43141,7 +43141,7 @@
         <v>2.52</v>
       </c>
       <c r="H1256" s="2" t="n">
-        <v>46082.24482822619</v>
+        <v>46082.24482822917</v>
       </c>
     </row>
     <row r="1257">
@@ -43175,7 +43175,7 @@
         <v>1.81</v>
       </c>
       <c r="H1257" s="2" t="n">
-        <v>46085.2448282293</v>
+        <v>46085.24482822917</v>
       </c>
     </row>
     <row r="1258">
@@ -43209,7 +43209,7 @@
         <v>3.91</v>
       </c>
       <c r="H1258" s="2" t="n">
-        <v>46087.2448282324</v>
+        <v>46087.24482822917</v>
       </c>
     </row>
     <row r="1259">
@@ -43243,7 +43243,7 @@
         <v>1.7</v>
       </c>
       <c r="H1259" s="2" t="n">
-        <v>46090.24482823582</v>
+        <v>46090.24482824074</v>
       </c>
     </row>
     <row r="1260">
@@ -43277,7 +43277,7 @@
         <v>3.69</v>
       </c>
       <c r="H1260" s="2" t="n">
-        <v>46076.24482823911</v>
+        <v>46076.24482824074</v>
       </c>
     </row>
     <row r="1261">
@@ -43311,7 +43311,7 @@
         <v>2.18</v>
       </c>
       <c r="H1261" s="2" t="n">
-        <v>46089.24482824239</v>
+        <v>46089.24482824074</v>
       </c>
     </row>
     <row r="1262">
@@ -43345,7 +43345,7 @@
         <v>1.63</v>
       </c>
       <c r="H1262" s="2" t="n">
-        <v>46078.24482824582</v>
+        <v>46078.24482824074</v>
       </c>
     </row>
     <row r="1263">
@@ -43379,7 +43379,7 @@
         <v>2.6</v>
       </c>
       <c r="H1263" s="2" t="n">
-        <v>46079.24482824931</v>
+        <v>46079.24482825232</v>
       </c>
     </row>
     <row r="1264">
@@ -43413,7 +43413,7 @@
         <v>3.19</v>
       </c>
       <c r="H1264" s="2" t="n">
-        <v>46069.24482825241</v>
+        <v>46069.24482825232</v>
       </c>
     </row>
     <row r="1265">
@@ -43447,7 +43447,7 @@
         <v>3.01</v>
       </c>
       <c r="H1265" s="2" t="n">
-        <v>46086.24482825548</v>
+        <v>46086.24482825232</v>
       </c>
     </row>
     <row r="1266">
@@ -43481,7 +43481,7 @@
         <v>0.9</v>
       </c>
       <c r="H1266" s="2" t="n">
-        <v>46081.24482825883</v>
+        <v>46081.24482826389</v>
       </c>
     </row>
     <row r="1267">
@@ -43515,7 +43515,7 @@
         <v>2.48</v>
       </c>
       <c r="H1267" s="2" t="n">
-        <v>46069.24482826194</v>
+        <v>46069.24482826389</v>
       </c>
     </row>
     <row r="1268">
@@ -43549,7 +43549,7 @@
         <v>0.99</v>
       </c>
       <c r="H1268" s="2" t="n">
-        <v>46091.24482826502</v>
+        <v>46091.24482826389</v>
       </c>
     </row>
     <row r="1269">
@@ -43583,7 +43583,7 @@
         <v>3.69</v>
       </c>
       <c r="H1269" s="2" t="n">
-        <v>46074.24482826816</v>
+        <v>46074.24482826389</v>
       </c>
     </row>
     <row r="1270">
@@ -43617,7 +43617,7 @@
         <v>4.53</v>
       </c>
       <c r="H1270" s="2" t="n">
-        <v>46091.24482827157</v>
+        <v>46091.24482827546</v>
       </c>
     </row>
     <row r="1271">
@@ -43651,7 +43651,7 @@
         <v>1.54</v>
       </c>
       <c r="H1271" s="2" t="n">
-        <v>46066.24482827468</v>
+        <v>46066.24482827546</v>
       </c>
     </row>
     <row r="1272">
@@ -43685,7 +43685,7 @@
         <v>0.37</v>
       </c>
       <c r="H1272" s="2" t="n">
-        <v>46091.24482827791</v>
+        <v>46091.24482827546</v>
       </c>
     </row>
     <row r="1273">
@@ -43719,7 +43719,7 @@
         <v>2.62</v>
       </c>
       <c r="H1273" s="2" t="n">
-        <v>46085.24482828128</v>
+        <v>46085.24482828704</v>
       </c>
     </row>
     <row r="1274">
@@ -43753,7 +43753,7 @@
         <v>3.15</v>
       </c>
       <c r="H1274" s="2" t="n">
-        <v>46094.24482828451</v>
+        <v>46094.24482828704</v>
       </c>
     </row>
     <row r="1275">
@@ -43787,7 +43787,7 @@
         <v>3.27</v>
       </c>
       <c r="H1275" s="2" t="n">
-        <v>46094.24482828761</v>
+        <v>46094.24482828704</v>
       </c>
     </row>
     <row r="1276">
@@ -43821,7 +43821,7 @@
         <v>2.75</v>
       </c>
       <c r="H1276" s="2" t="n">
-        <v>46071.24482829065</v>
+        <v>46071.24482828704</v>
       </c>
     </row>
     <row r="1277">
@@ -43855,7 +43855,7 @@
         <v>0.87</v>
       </c>
       <c r="H1277" s="2" t="n">
-        <v>46082.24482829394</v>
+        <v>46082.24482829861</v>
       </c>
     </row>
     <row r="1278">
@@ -43889,7 +43889,7 @@
         <v>4.48</v>
       </c>
       <c r="H1278" s="2" t="n">
-        <v>46084.24482829705</v>
+        <v>46084.24482829861</v>
       </c>
     </row>
     <row r="1279">
@@ -43923,7 +43923,7 @@
         <v>3</v>
       </c>
       <c r="H1279" s="2" t="n">
-        <v>46073.24482830023</v>
+        <v>46073.24482829861</v>
       </c>
     </row>
     <row r="1280">
@@ -43957,7 +43957,7 @@
         <v>4.24</v>
       </c>
       <c r="H1280" s="2" t="n">
-        <v>46093.24482830329</v>
+        <v>46093.24482829861</v>
       </c>
     </row>
     <row r="1281">
@@ -43991,7 +43991,7 @@
         <v>0.06</v>
       </c>
       <c r="H1281" s="2" t="n">
-        <v>46068.24482830654</v>
+        <v>46068.24482831018</v>
       </c>
     </row>
     <row r="1282">
@@ -44025,7 +44025,7 @@
         <v>1.68</v>
       </c>
       <c r="H1282" s="2" t="n">
-        <v>46073.24482830997</v>
+        <v>46073.24482831018</v>
       </c>
     </row>
     <row r="1283">
@@ -44059,7 +44059,7 @@
         <v>3.83</v>
       </c>
       <c r="H1283" s="2" t="n">
-        <v>46092.24482831318</v>
+        <v>46092.24482831018</v>
       </c>
     </row>
     <row r="1284">
@@ -44093,7 +44093,7 @@
         <v>0.04</v>
       </c>
       <c r="H1284" s="2" t="n">
-        <v>46074.24482831665</v>
+        <v>46074.24482832176</v>
       </c>
     </row>
     <row r="1285">
@@ -44127,7 +44127,7 @@
         <v>0.73</v>
       </c>
       <c r="H1285" s="2" t="n">
-        <v>46084.24482831996</v>
+        <v>46084.24482832176</v>
       </c>
     </row>
     <row r="1286">
@@ -44161,7 +44161,7 @@
         <v>0.05</v>
       </c>
       <c r="H1286" s="2" t="n">
-        <v>46091.24482832298</v>
+        <v>46091.24482832176</v>
       </c>
     </row>
     <row r="1287">
@@ -44195,7 +44195,7 @@
         <v>1.33</v>
       </c>
       <c r="H1287" s="2" t="n">
-        <v>46074.24482832605</v>
+        <v>46074.24482832176</v>
       </c>
     </row>
     <row r="1288">
@@ -44229,7 +44229,7 @@
         <v>0.2</v>
       </c>
       <c r="H1288" s="2" t="n">
-        <v>46069.24482832933</v>
+        <v>46069.24482833334</v>
       </c>
     </row>
     <row r="1289">
@@ -44263,7 +44263,7 @@
         <v>1.49</v>
       </c>
       <c r="H1289" s="2" t="n">
-        <v>46089.24482833244</v>
+        <v>46089.24482833334</v>
       </c>
     </row>
     <row r="1290">
@@ -44297,7 +44297,7 @@
         <v>4.78</v>
       </c>
       <c r="H1290" s="2" t="n">
-        <v>46079.2448283356</v>
+        <v>46079.24482833334</v>
       </c>
     </row>
     <row r="1291">
@@ -44331,7 +44331,7 @@
         <v>0.53</v>
       </c>
       <c r="H1291" s="2" t="n">
-        <v>46080.24482833887</v>
+        <v>46080.24482833334</v>
       </c>
     </row>
     <row r="1292">
@@ -44365,7 +44365,7 @@
         <v>1</v>
       </c>
       <c r="H1292" s="2" t="n">
-        <v>46075.24482834214</v>
+        <v>46075.2448283449</v>
       </c>
     </row>
     <row r="1293">
@@ -44399,7 +44399,7 @@
         <v>2.81</v>
       </c>
       <c r="H1293" s="2" t="n">
-        <v>46073.24482834578</v>
+        <v>46073.2448283449</v>
       </c>
     </row>
     <row r="1294">
@@ -44433,7 +44433,7 @@
         <v>0.84</v>
       </c>
       <c r="H1294" s="2" t="n">
-        <v>46086.24482834889</v>
+        <v>46086.2448283449</v>
       </c>
     </row>
     <row r="1295">
@@ -44467,7 +44467,7 @@
         <v>1.03</v>
       </c>
       <c r="H1295" s="2" t="n">
-        <v>46070.24482835206</v>
+        <v>46070.24482835648</v>
       </c>
     </row>
     <row r="1296">
@@ -44501,7 +44501,7 @@
         <v>1.9</v>
       </c>
       <c r="H1296" s="2" t="n">
-        <v>46092.24482835516</v>
+        <v>46092.24482835648</v>
       </c>
     </row>
     <row r="1297">
@@ -44535,7 +44535,7 @@
         <v>3.93</v>
       </c>
       <c r="H1297" s="2" t="n">
-        <v>46078.24482835824</v>
+        <v>46078.24482835648</v>
       </c>
     </row>
     <row r="1298">
@@ -44569,7 +44569,7 @@
         <v>1.04</v>
       </c>
       <c r="H1298" s="2" t="n">
-        <v>46087.24482836139</v>
+        <v>46087.24482835648</v>
       </c>
     </row>
     <row r="1299">
@@ -44603,7 +44603,7 @@
         <v>2.5</v>
       </c>
       <c r="H1299" s="2" t="n">
-        <v>46066.24482836478</v>
+        <v>46066.24482836806</v>
       </c>
     </row>
     <row r="1300">
@@ -44637,7 +44637,7 @@
         <v>2.87</v>
       </c>
       <c r="H1300" s="2" t="n">
-        <v>46086.24482836779</v>
+        <v>46086.24482836806</v>
       </c>
     </row>
     <row r="1301">
@@ -44671,7 +44671,1707 @@
         <v>0.95</v>
       </c>
       <c r="H1301" s="2" t="n">
-        <v>46080.24482837086</v>
+        <v>46080.24482836806</v>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>803c794c-abad-44c9-af7c-ca5cc9e6da48</t>
+        </is>
+      </c>
+      <c r="B1302" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1302" t="n">
+        <v>328.98</v>
+      </c>
+      <c r="G1302" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="H1302" s="2" t="n">
+        <v>46066.28641161769</v>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>9b2fe321-2c99-4766-bf76-030845ae0a1d</t>
+        </is>
+      </c>
+      <c r="B1303" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1303" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1303" t="n">
+        <v>266.33</v>
+      </c>
+      <c r="G1303" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H1303" s="2" t="n">
+        <v>46068.28641162244</v>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>19acb1fc-9efc-4a37-a12c-049ffbbea276</t>
+        </is>
+      </c>
+      <c r="B1304" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1304" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1304" t="n">
+        <v>191.32</v>
+      </c>
+      <c r="G1304" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H1304" s="2" t="n">
+        <v>46085.28641162608</v>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>1fc39a69-26aa-4602-a7d0-3a2763eaa2b9</t>
+        </is>
+      </c>
+      <c r="B1305" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1305" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1305" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="G1305" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H1305" s="2" t="n">
+        <v>46076.2864116292</v>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>9d84f1d3-9ade-4269-b2ae-7c452cf014fd</t>
+        </is>
+      </c>
+      <c r="B1306" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1306" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1306" t="n">
+        <v>78.62</v>
+      </c>
+      <c r="G1306" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H1306" s="2" t="n">
+        <v>46095.28641163242</v>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>7c4e7a82-1f01-46ad-96d0-56f9ef7ae577</t>
+        </is>
+      </c>
+      <c r="B1307" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1307" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1307" t="n">
+        <v>170.3</v>
+      </c>
+      <c r="G1307" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H1307" s="2" t="n">
+        <v>46068.28641163577</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>3f4421ff-1261-427e-944e-2671b034212e</t>
+        </is>
+      </c>
+      <c r="B1308" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1308" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1308" t="n">
+        <v>304.74</v>
+      </c>
+      <c r="G1308" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H1308" s="2" t="n">
+        <v>46077.28641163898</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>4af20b6a-3945-44ce-903a-613eca25acdb</t>
+        </is>
+      </c>
+      <c r="B1309" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1309" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1309" t="n">
+        <v>166.37</v>
+      </c>
+      <c r="G1309" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H1309" s="2" t="n">
+        <v>46076.28641164256</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>b0dac955-6769-4d1f-b623-491b7e33dcb0</t>
+        </is>
+      </c>
+      <c r="B1310" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1310" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1310" t="n">
+        <v>157.15</v>
+      </c>
+      <c r="G1310" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H1310" s="2" t="n">
+        <v>46066.28641164579</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>014902fb-6dee-40fe-87c8-882e3172cf74</t>
+        </is>
+      </c>
+      <c r="B1311" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1311" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1311" t="n">
+        <v>439.58</v>
+      </c>
+      <c r="G1311" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H1311" s="2" t="n">
+        <v>46087.28641164896</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>dc4e4b8b-f4f6-4d98-bd2e-3b5c404b0764</t>
+        </is>
+      </c>
+      <c r="B1312" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1312" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1312" t="n">
+        <v>178.22</v>
+      </c>
+      <c r="G1312" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H1312" s="2" t="n">
+        <v>46080.28641165234</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>20b2a01d-fbea-4e99-b06f-9f0225766fc9</t>
+        </is>
+      </c>
+      <c r="B1313" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1313" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1313" t="n">
+        <v>158.68</v>
+      </c>
+      <c r="G1313" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H1313" s="2" t="n">
+        <v>46080.28641165568</v>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>14af815e-0b83-4a49-8a3b-497794c1e6ed</t>
+        </is>
+      </c>
+      <c r="B1314" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1314" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1314" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="G1314" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H1314" s="2" t="n">
+        <v>46077.28641165879</v>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>0458c646-6470-4be2-b304-40de35f43fdb</t>
+        </is>
+      </c>
+      <c r="B1315" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1315" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1315" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="G1315" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H1315" s="2" t="n">
+        <v>46083.28641166181</v>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>86418913-14b6-44cb-a8af-87109b9e0d46</t>
+        </is>
+      </c>
+      <c r="B1316" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1316" t="n">
+        <v>36.13</v>
+      </c>
+      <c r="G1316" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H1316" s="2" t="n">
+        <v>46095.28641166523</v>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>9311be89-f97f-4b07-86e3-ca6f88abf3c1</t>
+        </is>
+      </c>
+      <c r="B1317" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1317" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1317" t="n">
+        <v>191.48</v>
+      </c>
+      <c r="G1317" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H1317" s="2" t="n">
+        <v>46072.28641166844</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>ab708a6c-697e-4ca9-b36f-95faf07403a8</t>
+        </is>
+      </c>
+      <c r="B1318" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1318" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1318" t="n">
+        <v>371.3</v>
+      </c>
+      <c r="G1318" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="H1318" s="2" t="n">
+        <v>46095.28641167151</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>91302732-2aa5-486d-bb0e-69526d06c573</t>
+        </is>
+      </c>
+      <c r="B1319" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1319" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1319" t="n">
+        <v>239.4</v>
+      </c>
+      <c r="G1319" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H1319" s="2" t="n">
+        <v>46091.28641167469</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>32761a91-cda4-4b00-87f6-2607f212de2e</t>
+        </is>
+      </c>
+      <c r="B1320" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1320" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1320" t="n">
+        <v>408.46</v>
+      </c>
+      <c r="G1320" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="H1320" s="2" t="n">
+        <v>46077.28641167788</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>5d569967-0717-4da5-a164-dd10978bcd76</t>
+        </is>
+      </c>
+      <c r="B1321" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1321" t="n">
+        <v>219.87</v>
+      </c>
+      <c r="G1321" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H1321" s="2" t="n">
+        <v>46080.28641168105</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>ea9c5664-f75b-4a88-bd7e-2f74275746ba</t>
+        </is>
+      </c>
+      <c r="B1322" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1322" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1322" t="n">
+        <v>175.51</v>
+      </c>
+      <c r="G1322" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H1322" s="2" t="n">
+        <v>46069.28641168415</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>b2bb4ac7-06a7-42db-b132-a871e334a877</t>
+        </is>
+      </c>
+      <c r="B1323" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1323" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1323" t="n">
+        <v>421.88</v>
+      </c>
+      <c r="G1323" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="H1323" s="2" t="n">
+        <v>46073.28641168836</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>ae2124e8-b55d-4db4-bdf5-8a53283b062b</t>
+        </is>
+      </c>
+      <c r="B1324" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1324" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1324" t="n">
+        <v>36.48</v>
+      </c>
+      <c r="G1324" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H1324" s="2" t="n">
+        <v>46091.28641169161</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>c6e0c488-1d90-4d67-aa47-6af90217e633</t>
+        </is>
+      </c>
+      <c r="B1325" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1325" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1325" t="n">
+        <v>123.28</v>
+      </c>
+      <c r="G1325" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="H1325" s="2" t="n">
+        <v>46086.28641169467</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>6c69b523-65b3-46c3-a792-c6ac665b3114</t>
+        </is>
+      </c>
+      <c r="B1326" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1326" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1326" t="n">
+        <v>37.31</v>
+      </c>
+      <c r="G1326" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H1326" s="2" t="n">
+        <v>46079.28641169773</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>49f28af4-1cb9-47b6-9c10-b4ac3cc1fece</t>
+        </is>
+      </c>
+      <c r="B1327" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1327" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1327" t="n">
+        <v>157.08</v>
+      </c>
+      <c r="G1327" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H1327" s="2" t="n">
+        <v>46093.28641170112</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>00dfaaad-0ab4-4d0a-93f1-61ce2b4b0f84</t>
+        </is>
+      </c>
+      <c r="B1328" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1328" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1328" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="G1328" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H1328" s="2" t="n">
+        <v>46075.28641170433</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>3e30eee4-0eaa-4b65-a121-1ba9d2501417</t>
+        </is>
+      </c>
+      <c r="B1329" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1329" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1329" t="n">
+        <v>401.18</v>
+      </c>
+      <c r="G1329" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="H1329" s="2" t="n">
+        <v>46069.28641170741</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>0682c165-3967-4c80-854d-3d7e4e158fbe</t>
+        </is>
+      </c>
+      <c r="B1330" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1330" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1330" t="n">
+        <v>489.42</v>
+      </c>
+      <c r="G1330" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="H1330" s="2" t="n">
+        <v>46067.28641171058</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>15f2ec6e-3f14-41f8-9570-7155c28f11e1</t>
+        </is>
+      </c>
+      <c r="B1331" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1331" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1331" t="n">
+        <v>168.13</v>
+      </c>
+      <c r="G1331" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H1331" s="2" t="n">
+        <v>46086.28641171393</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>472cded4-4ab1-46fe-a32d-dff5d0472b1b</t>
+        </is>
+      </c>
+      <c r="B1332" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1332" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1332" t="n">
+        <v>202.92</v>
+      </c>
+      <c r="G1332" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="H1332" s="2" t="n">
+        <v>46089.28641171727</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>1bd9a9d6-6554-4986-ba99-c3c3f1e77fbf</t>
+        </is>
+      </c>
+      <c r="B1333" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1333" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1333" t="n">
+        <v>430.59</v>
+      </c>
+      <c r="G1333" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="H1333" s="2" t="n">
+        <v>46080.2864117203</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>eecb0e7d-3672-4af6-9b8a-836dfc7b4222</t>
+        </is>
+      </c>
+      <c r="B1334" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1334" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1334" t="n">
+        <v>307.5</v>
+      </c>
+      <c r="G1334" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="H1334" s="2" t="n">
+        <v>46071.28641172357</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>159082a5-2306-483a-b4e9-74f021151a87</t>
+        </is>
+      </c>
+      <c r="B1335" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1335" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1335" t="n">
+        <v>446.23</v>
+      </c>
+      <c r="G1335" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="H1335" s="2" t="n">
+        <v>46091.28641172659</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>cc9693d7-3843-4f40-b387-625ace8642ec</t>
+        </is>
+      </c>
+      <c r="B1336" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1336" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1336" t="n">
+        <v>155.87</v>
+      </c>
+      <c r="G1336" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H1336" s="2" t="n">
+        <v>46080.28641172958</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>f75fa40f-8655-45c6-b5b8-c5357845776b</t>
+        </is>
+      </c>
+      <c r="B1337" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1337" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1337" t="n">
+        <v>154.79</v>
+      </c>
+      <c r="G1337" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H1337" s="2" t="n">
+        <v>46075.2864117327</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>4ee705b5-1b9e-4056-8963-991087f303a8</t>
+        </is>
+      </c>
+      <c r="B1338" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1338" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1338" t="n">
+        <v>337.27</v>
+      </c>
+      <c r="G1338" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="H1338" s="2" t="n">
+        <v>46070.28641173617</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>46b96833-2ac3-4f5b-9f92-afbf42061e0d</t>
+        </is>
+      </c>
+      <c r="B1339" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1339" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1339" t="n">
+        <v>123.22</v>
+      </c>
+      <c r="G1339" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="H1339" s="2" t="n">
+        <v>46090.28641173925</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>ebe49ddf-36a6-40d6-9d18-5fe71107e8f2</t>
+        </is>
+      </c>
+      <c r="B1340" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1340" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1340" t="n">
+        <v>119.51</v>
+      </c>
+      <c r="G1340" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H1340" s="2" t="n">
+        <v>46076.28641174226</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>e2daa030-a550-4b12-aadb-ddc1a4c36032</t>
+        </is>
+      </c>
+      <c r="B1341" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1341" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1341" t="n">
+        <v>153.01</v>
+      </c>
+      <c r="G1341" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H1341" s="2" t="n">
+        <v>46074.28641174528</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>8239e330-26a6-4cfe-b592-0f782f98a731</t>
+        </is>
+      </c>
+      <c r="B1342" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1342" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1342" t="n">
+        <v>311.13</v>
+      </c>
+      <c r="G1342" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="H1342" s="2" t="n">
+        <v>46072.28641174863</v>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>bcd812ef-db00-4a21-b1af-76d28a7cf8cf</t>
+        </is>
+      </c>
+      <c r="B1343" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1343" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1343" t="n">
+        <v>235.15</v>
+      </c>
+      <c r="G1343" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="H1343" s="2" t="n">
+        <v>46090.28641175186</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>e9f4f7bb-f29c-479c-8729-dd71ab1729b7</t>
+        </is>
+      </c>
+      <c r="B1344" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1344" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1344" t="n">
+        <v>301.58</v>
+      </c>
+      <c r="G1344" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="H1344" s="2" t="n">
+        <v>46090.28641175497</v>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>1987d7dd-e960-4872-babc-c54f3e81ba88</t>
+        </is>
+      </c>
+      <c r="B1345" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1345" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1345" t="n">
+        <v>479.5</v>
+      </c>
+      <c r="G1345" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="H1345" s="2" t="n">
+        <v>46073.28641175831</v>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>2a840d95-cabe-49f5-ab28-4c51ea88fdcc</t>
+        </is>
+      </c>
+      <c r="B1346" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1346" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1346" t="n">
+        <v>367.26</v>
+      </c>
+      <c r="G1346" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="H1346" s="2" t="n">
+        <v>46080.2864117615</v>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>b8b8a080-ebee-4b4e-987c-611dfb3353a1</t>
+        </is>
+      </c>
+      <c r="B1347" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1347" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1347" t="n">
+        <v>463.65</v>
+      </c>
+      <c r="G1347" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="H1347" s="2" t="n">
+        <v>46093.28641176457</v>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>c36cf6ac-c8e5-4282-b820-2757f763f03c</t>
+        </is>
+      </c>
+      <c r="B1348" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1348" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1348" t="n">
+        <v>75.83</v>
+      </c>
+      <c r="G1348" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H1348" s="2" t="n">
+        <v>46095.28641176772</v>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>ab43e0bd-22ed-4136-a721-ea7d489fccbe</t>
+        </is>
+      </c>
+      <c r="B1349" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1349" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1349" t="n">
+        <v>421.26</v>
+      </c>
+      <c r="G1349" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="H1349" s="2" t="n">
+        <v>46087.28641177102</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>c59a1917-59f1-4042-b2ea-18e6965a90fa</t>
+        </is>
+      </c>
+      <c r="B1350" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1350" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1350" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="G1350" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H1350" s="2" t="n">
+        <v>46067.28641177412</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>0f5dca8e-067c-425d-b7bc-42ae7a8e4374</t>
+        </is>
+      </c>
+      <c r="B1351" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1351" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1351" t="n">
+        <v>54.46</v>
+      </c>
+      <c r="G1351" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H1351" s="2" t="n">
+        <v>46088.28641177717</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1351"/>
+  <dimension ref="A1:H1401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44705,7 +44705,7 @@
         <v>3.29</v>
       </c>
       <c r="H1302" s="2" t="n">
-        <v>46066.28641161769</v>
+        <v>46066.28641162037</v>
       </c>
     </row>
     <row r="1303">
@@ -44739,7 +44739,7 @@
         <v>2.66</v>
       </c>
       <c r="H1303" s="2" t="n">
-        <v>46068.28641162244</v>
+        <v>46068.28641162037</v>
       </c>
     </row>
     <row r="1304">
@@ -44773,7 +44773,7 @@
         <v>1.91</v>
       </c>
       <c r="H1304" s="2" t="n">
-        <v>46085.28641162608</v>
+        <v>46085.28641162037</v>
       </c>
     </row>
     <row r="1305">
@@ -44807,7 +44807,7 @@
         <v>0.2</v>
       </c>
       <c r="H1305" s="2" t="n">
-        <v>46076.2864116292</v>
+        <v>46076.28641163195</v>
       </c>
     </row>
     <row r="1306">
@@ -44841,7 +44841,7 @@
         <v>0.79</v>
       </c>
       <c r="H1306" s="2" t="n">
-        <v>46095.28641163242</v>
+        <v>46095.28641163195</v>
       </c>
     </row>
     <row r="1307">
@@ -44875,7 +44875,7 @@
         <v>1.7</v>
       </c>
       <c r="H1307" s="2" t="n">
-        <v>46068.28641163577</v>
+        <v>46068.28641163195</v>
       </c>
     </row>
     <row r="1308">
@@ -44909,7 +44909,7 @@
         <v>3.05</v>
       </c>
       <c r="H1308" s="2" t="n">
-        <v>46077.28641163898</v>
+        <v>46077.28641164352</v>
       </c>
     </row>
     <row r="1309">
@@ -44943,7 +44943,7 @@
         <v>1.66</v>
       </c>
       <c r="H1309" s="2" t="n">
-        <v>46076.28641164256</v>
+        <v>46076.28641164352</v>
       </c>
     </row>
     <row r="1310">
@@ -44977,7 +44977,7 @@
         <v>1.57</v>
       </c>
       <c r="H1310" s="2" t="n">
-        <v>46066.28641164579</v>
+        <v>46066.28641164352</v>
       </c>
     </row>
     <row r="1311">
@@ -45011,7 +45011,7 @@
         <v>4.4</v>
       </c>
       <c r="H1311" s="2" t="n">
-        <v>46087.28641164896</v>
+        <v>46087.28641164352</v>
       </c>
     </row>
     <row r="1312">
@@ -45045,7 +45045,7 @@
         <v>1.78</v>
       </c>
       <c r="H1312" s="2" t="n">
-        <v>46080.28641165234</v>
+        <v>46080.28641165509</v>
       </c>
     </row>
     <row r="1313">
@@ -45079,7 +45079,7 @@
         <v>1.59</v>
       </c>
       <c r="H1313" s="2" t="n">
-        <v>46080.28641165568</v>
+        <v>46080.28641165509</v>
       </c>
     </row>
     <row r="1314">
@@ -45113,7 +45113,7 @@
         <v>0.16</v>
       </c>
       <c r="H1314" s="2" t="n">
-        <v>46077.28641165879</v>
+        <v>46077.28641165509</v>
       </c>
     </row>
     <row r="1315">
@@ -45147,7 +45147,7 @@
         <v>0.22</v>
       </c>
       <c r="H1315" s="2" t="n">
-        <v>46083.28641166181</v>
+        <v>46083.28641166667</v>
       </c>
     </row>
     <row r="1316">
@@ -45181,7 +45181,7 @@
         <v>0.36</v>
       </c>
       <c r="H1316" s="2" t="n">
-        <v>46095.28641166523</v>
+        <v>46095.28641166667</v>
       </c>
     </row>
     <row r="1317">
@@ -45215,7 +45215,7 @@
         <v>1.91</v>
       </c>
       <c r="H1317" s="2" t="n">
-        <v>46072.28641166844</v>
+        <v>46072.28641166667</v>
       </c>
     </row>
     <row r="1318">
@@ -45249,7 +45249,7 @@
         <v>3.71</v>
       </c>
       <c r="H1318" s="2" t="n">
-        <v>46095.28641167151</v>
+        <v>46095.28641166667</v>
       </c>
     </row>
     <row r="1319">
@@ -45283,7 +45283,7 @@
         <v>2.39</v>
       </c>
       <c r="H1319" s="2" t="n">
-        <v>46091.28641167469</v>
+        <v>46091.28641167824</v>
       </c>
     </row>
     <row r="1320">
@@ -45317,7 +45317,7 @@
         <v>4.08</v>
       </c>
       <c r="H1320" s="2" t="n">
-        <v>46077.28641167788</v>
+        <v>46077.28641167824</v>
       </c>
     </row>
     <row r="1321">
@@ -45351,7 +45351,7 @@
         <v>2.2</v>
       </c>
       <c r="H1321" s="2" t="n">
-        <v>46080.28641168105</v>
+        <v>46080.28641167824</v>
       </c>
     </row>
     <row r="1322">
@@ -45385,7 +45385,7 @@
         <v>1.76</v>
       </c>
       <c r="H1322" s="2" t="n">
-        <v>46069.28641168415</v>
+        <v>46069.28641168981</v>
       </c>
     </row>
     <row r="1323">
@@ -45419,7 +45419,7 @@
         <v>4.22</v>
       </c>
       <c r="H1323" s="2" t="n">
-        <v>46073.28641168836</v>
+        <v>46073.28641168981</v>
       </c>
     </row>
     <row r="1324">
@@ -45453,7 +45453,7 @@
         <v>0.36</v>
       </c>
       <c r="H1324" s="2" t="n">
-        <v>46091.28641169161</v>
+        <v>46091.28641168981</v>
       </c>
     </row>
     <row r="1325">
@@ -45487,7 +45487,7 @@
         <v>1.23</v>
       </c>
       <c r="H1325" s="2" t="n">
-        <v>46086.28641169467</v>
+        <v>46086.28641168981</v>
       </c>
     </row>
     <row r="1326">
@@ -45521,7 +45521,7 @@
         <v>0.37</v>
       </c>
       <c r="H1326" s="2" t="n">
-        <v>46079.28641169773</v>
+        <v>46079.28641170139</v>
       </c>
     </row>
     <row r="1327">
@@ -45555,7 +45555,7 @@
         <v>1.57</v>
       </c>
       <c r="H1327" s="2" t="n">
-        <v>46093.28641170112</v>
+        <v>46093.28641170139</v>
       </c>
     </row>
     <row r="1328">
@@ -45589,7 +45589,7 @@
         <v>0.05</v>
       </c>
       <c r="H1328" s="2" t="n">
-        <v>46075.28641170433</v>
+        <v>46075.28641170139</v>
       </c>
     </row>
     <row r="1329">
@@ -45623,7 +45623,7 @@
         <v>4.01</v>
       </c>
       <c r="H1329" s="2" t="n">
-        <v>46069.28641170741</v>
+        <v>46069.28641171296</v>
       </c>
     </row>
     <row r="1330">
@@ -45657,7 +45657,7 @@
         <v>4.89</v>
       </c>
       <c r="H1330" s="2" t="n">
-        <v>46067.28641171058</v>
+        <v>46067.28641171296</v>
       </c>
     </row>
     <row r="1331">
@@ -45691,7 +45691,7 @@
         <v>1.68</v>
       </c>
       <c r="H1331" s="2" t="n">
-        <v>46086.28641171393</v>
+        <v>46086.28641171296</v>
       </c>
     </row>
     <row r="1332">
@@ -45725,7 +45725,7 @@
         <v>2.03</v>
       </c>
       <c r="H1332" s="2" t="n">
-        <v>46089.28641171727</v>
+        <v>46089.28641171296</v>
       </c>
     </row>
     <row r="1333">
@@ -45759,7 +45759,7 @@
         <v>4.31</v>
       </c>
       <c r="H1333" s="2" t="n">
-        <v>46080.2864117203</v>
+        <v>46080.28641172453</v>
       </c>
     </row>
     <row r="1334">
@@ -45793,7 +45793,7 @@
         <v>3.08</v>
       </c>
       <c r="H1334" s="2" t="n">
-        <v>46071.28641172357</v>
+        <v>46071.28641172453</v>
       </c>
     </row>
     <row r="1335">
@@ -45827,7 +45827,7 @@
         <v>4.46</v>
       </c>
       <c r="H1335" s="2" t="n">
-        <v>46091.28641172659</v>
+        <v>46091.28641172453</v>
       </c>
     </row>
     <row r="1336">
@@ -45861,7 +45861,7 @@
         <v>1.56</v>
       </c>
       <c r="H1336" s="2" t="n">
-        <v>46080.28641172958</v>
+        <v>46080.28641172453</v>
       </c>
     </row>
     <row r="1337">
@@ -45895,7 +45895,7 @@
         <v>1.55</v>
       </c>
       <c r="H1337" s="2" t="n">
-        <v>46075.2864117327</v>
+        <v>46075.28641173611</v>
       </c>
     </row>
     <row r="1338">
@@ -45929,7 +45929,7 @@
         <v>3.37</v>
       </c>
       <c r="H1338" s="2" t="n">
-        <v>46070.28641173617</v>
+        <v>46070.28641173611</v>
       </c>
     </row>
     <row r="1339">
@@ -45963,7 +45963,7 @@
         <v>1.23</v>
       </c>
       <c r="H1339" s="2" t="n">
-        <v>46090.28641173925</v>
+        <v>46090.28641173611</v>
       </c>
     </row>
     <row r="1340">
@@ -45997,7 +45997,7 @@
         <v>1.2</v>
       </c>
       <c r="H1340" s="2" t="n">
-        <v>46076.28641174226</v>
+        <v>46076.28641174769</v>
       </c>
     </row>
     <row r="1341">
@@ -46031,7 +46031,7 @@
         <v>1.53</v>
       </c>
       <c r="H1341" s="2" t="n">
-        <v>46074.28641174528</v>
+        <v>46074.28641174769</v>
       </c>
     </row>
     <row r="1342">
@@ -46065,7 +46065,7 @@
         <v>3.11</v>
       </c>
       <c r="H1342" s="2" t="n">
-        <v>46072.28641174863</v>
+        <v>46072.28641174769</v>
       </c>
     </row>
     <row r="1343">
@@ -46099,7 +46099,7 @@
         <v>2.35</v>
       </c>
       <c r="H1343" s="2" t="n">
-        <v>46090.28641175186</v>
+        <v>46090.28641174769</v>
       </c>
     </row>
     <row r="1344">
@@ -46133,7 +46133,7 @@
         <v>3.02</v>
       </c>
       <c r="H1344" s="2" t="n">
-        <v>46090.28641175497</v>
+        <v>46090.28641175926</v>
       </c>
     </row>
     <row r="1345">
@@ -46167,7 +46167,7 @@
         <v>4.79</v>
       </c>
       <c r="H1345" s="2" t="n">
-        <v>46073.28641175831</v>
+        <v>46073.28641175926</v>
       </c>
     </row>
     <row r="1346">
@@ -46201,7 +46201,7 @@
         <v>3.67</v>
       </c>
       <c r="H1346" s="2" t="n">
-        <v>46080.2864117615</v>
+        <v>46080.28641175926</v>
       </c>
     </row>
     <row r="1347">
@@ -46235,7 +46235,7 @@
         <v>4.64</v>
       </c>
       <c r="H1347" s="2" t="n">
-        <v>46093.28641176457</v>
+        <v>46093.28641175926</v>
       </c>
     </row>
     <row r="1348">
@@ -46269,7 +46269,7 @@
         <v>0.76</v>
       </c>
       <c r="H1348" s="2" t="n">
-        <v>46095.28641176772</v>
+        <v>46095.28641177083</v>
       </c>
     </row>
     <row r="1349">
@@ -46303,7 +46303,7 @@
         <v>4.21</v>
       </c>
       <c r="H1349" s="2" t="n">
-        <v>46087.28641177102</v>
+        <v>46087.28641177083</v>
       </c>
     </row>
     <row r="1350">
@@ -46337,7 +46337,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="H1350" s="2" t="n">
-        <v>46067.28641177412</v>
+        <v>46067.28641177083</v>
       </c>
     </row>
     <row r="1351">
@@ -46371,7 +46371,1707 @@
         <v>0.54</v>
       </c>
       <c r="H1351" s="2" t="n">
-        <v>46088.28641177717</v>
+        <v>46088.28641178241</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>042c0172-287c-41a9-aa2b-35d24bed17cb</t>
+        </is>
+      </c>
+      <c r="B1352" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1352" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1352" t="n">
+        <v>310.57</v>
+      </c>
+      <c r="G1352" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="H1352" s="2" t="n">
+        <v>46084.32285992507</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>d89801b1-f7ce-452a-9967-c9e0646f5f20</t>
+        </is>
+      </c>
+      <c r="B1353" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1353" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1353" t="n">
+        <v>426.26</v>
+      </c>
+      <c r="G1353" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="H1353" s="2" t="n">
+        <v>46066.32285992941</v>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>07f0b4c3-3055-4059-bfc8-e5982f74dd40</t>
+        </is>
+      </c>
+      <c r="B1354" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1354" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1354" t="n">
+        <v>283.28</v>
+      </c>
+      <c r="G1354" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="H1354" s="2" t="n">
+        <v>46083.32285993282</v>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>6226717f-afae-405c-b543-aaaca372a881</t>
+        </is>
+      </c>
+      <c r="B1355" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1355" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1355" t="n">
+        <v>396.72</v>
+      </c>
+      <c r="G1355" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="H1355" s="2" t="n">
+        <v>46086.32285993652</v>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>2bd5f778-63a7-41fe-b7ed-e7c08ef1a386</t>
+        </is>
+      </c>
+      <c r="B1356" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1356" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1356" t="n">
+        <v>45.88</v>
+      </c>
+      <c r="G1356" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H1356" s="2" t="n">
+        <v>46083.32285993961</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>bcaa84f3-497f-494a-87bc-ab1188aae3fc</t>
+        </is>
+      </c>
+      <c r="B1357" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1357" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1357" t="n">
+        <v>441.76</v>
+      </c>
+      <c r="G1357" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="H1357" s="2" t="n">
+        <v>46079.32285994302</v>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>61e49900-8e22-41cd-81d6-a8881bf76446</t>
+        </is>
+      </c>
+      <c r="B1358" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1358" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1358" t="n">
+        <v>20.28</v>
+      </c>
+      <c r="G1358" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H1358" s="2" t="n">
+        <v>46091.3228599463</v>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>61189384-2783-44be-8198-bc01b2ee5878</t>
+        </is>
+      </c>
+      <c r="B1359" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1359" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1359" t="n">
+        <v>482.38</v>
+      </c>
+      <c r="G1359" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="H1359" s="2" t="n">
+        <v>46081.32285994949</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>53ffd795-6564-453d-b63b-0a499fbb0ad1</t>
+        </is>
+      </c>
+      <c r="B1360" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1360" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1360" t="n">
+        <v>164.41</v>
+      </c>
+      <c r="G1360" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H1360" s="2" t="n">
+        <v>46092.3228599526</v>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>9681db5e-f4df-44ee-8c27-d53df6f5df80</t>
+        </is>
+      </c>
+      <c r="B1361" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1361" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1361" t="n">
+        <v>208.7</v>
+      </c>
+      <c r="G1361" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="H1361" s="2" t="n">
+        <v>46078.32285995584</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>eeba8993-98e2-4388-b4b6-e59f9469684b</t>
+        </is>
+      </c>
+      <c r="B1362" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1362" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1362" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="G1362" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H1362" s="2" t="n">
+        <v>46095.32285995917</v>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>d413c626-7ec8-4ad4-9674-c399a597c62c</t>
+        </is>
+      </c>
+      <c r="B1363" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1363" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1363" t="n">
+        <v>347.36</v>
+      </c>
+      <c r="G1363" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="H1363" s="2" t="n">
+        <v>46086.3228599624</v>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>86cc4417-25d9-4744-9627-df6a177b79ac</t>
+        </is>
+      </c>
+      <c r="B1364" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1364" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1364" t="n">
+        <v>452.46</v>
+      </c>
+      <c r="G1364" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="H1364" s="2" t="n">
+        <v>46081.32285996567</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>6ccfe209-ab8a-4ce9-987f-9783fe5e957c</t>
+        </is>
+      </c>
+      <c r="B1365" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1365" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1365" t="n">
+        <v>163.74</v>
+      </c>
+      <c r="G1365" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H1365" s="2" t="n">
+        <v>46071.32285996973</v>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>7cf7806f-dce3-429d-97a8-e0b9bd41b8ed</t>
+        </is>
+      </c>
+      <c r="B1366" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1366" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1366" t="n">
+        <v>338.92</v>
+      </c>
+      <c r="G1366" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="H1366" s="2" t="n">
+        <v>46068.32285997286</v>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>87e9a731-54a2-4375-a2e9-1e437e5c7b11</t>
+        </is>
+      </c>
+      <c r="B1367" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1367" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1367" t="n">
+        <v>101.71</v>
+      </c>
+      <c r="G1367" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H1367" s="2" t="n">
+        <v>46073.32285997614</v>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>f1264bd0-b226-4918-b8cd-33df7c1d66c6</t>
+        </is>
+      </c>
+      <c r="B1368" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1368" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1368" t="n">
+        <v>358.37</v>
+      </c>
+      <c r="G1368" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="H1368" s="2" t="n">
+        <v>46071.32285997931</v>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>a9c1bb20-6bb7-4b54-9b8e-2c47eb726682</t>
+        </is>
+      </c>
+      <c r="B1369" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1369" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1369" t="n">
+        <v>455.99</v>
+      </c>
+      <c r="G1369" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="H1369" s="2" t="n">
+        <v>46091.32285998268</v>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>b659833e-9aaf-46f8-9a4a-8f61f6e12efa</t>
+        </is>
+      </c>
+      <c r="B1370" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1370" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1370" t="n">
+        <v>496.74</v>
+      </c>
+      <c r="G1370" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="H1370" s="2" t="n">
+        <v>46087.32285998595</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>e7923e10-72de-4366-acae-0293dac6674e</t>
+        </is>
+      </c>
+      <c r="B1371" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1371" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1371" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1371" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="G1371" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H1371" s="2" t="n">
+        <v>46066.32285998904</v>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>371953eb-61c5-415a-ba30-92c60efc9059</t>
+        </is>
+      </c>
+      <c r="B1372" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1372" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1372" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1372" t="n">
+        <v>453.82</v>
+      </c>
+      <c r="G1372" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="H1372" s="2" t="n">
+        <v>46088.3228599925</v>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>96a1a977-9b51-417f-99ed-aae66d9a89d9</t>
+        </is>
+      </c>
+      <c r="B1373" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1373" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1373" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1373" t="n">
+        <v>180.07</v>
+      </c>
+      <c r="G1373" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H1373" s="2" t="n">
+        <v>46075.32285999559</v>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>799033ac-761f-48e0-8324-c5f6b3d92ec5</t>
+        </is>
+      </c>
+      <c r="B1374" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1374" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1374" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1374" t="n">
+        <v>280.54</v>
+      </c>
+      <c r="G1374" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="H1374" s="2" t="n">
+        <v>46072.32285999883</v>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>09c88e58-ca09-454c-8de9-9820434f10e1</t>
+        </is>
+      </c>
+      <c r="B1375" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1375" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1375" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1375" t="n">
+        <v>459.77</v>
+      </c>
+      <c r="G1375" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H1375" s="2" t="n">
+        <v>46066.32286000184</v>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>b2b466d4-7975-4ff3-99ce-87742466c525</t>
+        </is>
+      </c>
+      <c r="B1376" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1376" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1376" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1376" t="n">
+        <v>376.43</v>
+      </c>
+      <c r="G1376" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="H1376" s="2" t="n">
+        <v>46078.32286000525</v>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>531462a2-3085-4d1f-9780-eaebcdaaf18b</t>
+        </is>
+      </c>
+      <c r="B1377" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1377" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1377" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1377" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="G1377" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H1377" s="2" t="n">
+        <v>46083.32286000862</v>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>2b4799c4-3670-4808-8778-eae82aeb1763</t>
+        </is>
+      </c>
+      <c r="B1378" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1378" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1378" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1378" t="n">
+        <v>205.11</v>
+      </c>
+      <c r="G1378" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H1378" s="2" t="n">
+        <v>46070.32286001185</v>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>b6779d9f-5466-47a5-a68d-ad3a1ad73103</t>
+        </is>
+      </c>
+      <c r="B1379" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1379" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1379" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1379" t="n">
+        <v>73.94</v>
+      </c>
+      <c r="G1379" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H1379" s="2" t="n">
+        <v>46086.32286001596</v>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>5dc3c061-fc4c-478e-b42e-7fc97d9c1057</t>
+        </is>
+      </c>
+      <c r="B1380" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1380" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1380" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1380" t="n">
+        <v>71.16</v>
+      </c>
+      <c r="G1380" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H1380" s="2" t="n">
+        <v>46066.32286001905</v>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>11057573-f394-479c-a800-c397fa82254b</t>
+        </is>
+      </c>
+      <c r="B1381" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1381" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1381" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1381" t="n">
+        <v>461.2</v>
+      </c>
+      <c r="G1381" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="H1381" s="2" t="n">
+        <v>46091.32286002226</v>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>e33248c9-dd6a-4a57-adfb-42e950332c81</t>
+        </is>
+      </c>
+      <c r="B1382" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1382" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1382" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1382" t="n">
+        <v>318.85</v>
+      </c>
+      <c r="G1382" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="H1382" s="2" t="n">
+        <v>46078.32286002535</v>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>b202a867-d31d-487b-8ec5-5ca805a2f47b</t>
+        </is>
+      </c>
+      <c r="B1383" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1383" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1383" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1383" t="n">
+        <v>40.24</v>
+      </c>
+      <c r="G1383" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H1383" s="2" t="n">
+        <v>46093.32286002857</v>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>a9ca00f1-bf17-46b7-8242-b5544f40e24e</t>
+        </is>
+      </c>
+      <c r="B1384" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1384" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1384" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1384" t="n">
+        <v>402.09</v>
+      </c>
+      <c r="G1384" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="H1384" s="2" t="n">
+        <v>46095.3228600318</v>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>a14edb41-93ce-4614-a48e-79d6f7af4eb2</t>
+        </is>
+      </c>
+      <c r="B1385" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1385" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1385" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1385" t="n">
+        <v>240.23</v>
+      </c>
+      <c r="G1385" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H1385" s="2" t="n">
+        <v>46085.32286003488</v>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>f5f9551a-34e9-4e7e-aac2-e00976b9d675</t>
+        </is>
+      </c>
+      <c r="B1386" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1386" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1386" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1386" t="n">
+        <v>262.84</v>
+      </c>
+      <c r="G1386" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="H1386" s="2" t="n">
+        <v>46092.32286003864</v>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>09129bc0-e031-451a-ba2c-557552e4613a</t>
+        </is>
+      </c>
+      <c r="B1387" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1387" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1387" t="n">
+        <v>431.67</v>
+      </c>
+      <c r="G1387" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="H1387" s="2" t="n">
+        <v>46084.32286004175</v>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>d55e95ca-f146-4db6-bd4a-cd8a295f0757</t>
+        </is>
+      </c>
+      <c r="B1388" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1388" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1388" t="n">
+        <v>422.54</v>
+      </c>
+      <c r="G1388" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="H1388" s="2" t="n">
+        <v>46084.32286004492</v>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>dbebf4b9-63ac-4758-b20c-73da260347ee</t>
+        </is>
+      </c>
+      <c r="B1389" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1389" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1389" t="n">
+        <v>476.95</v>
+      </c>
+      <c r="G1389" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="H1389" s="2" t="n">
+        <v>46081.32286004804</v>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>f97556a6-39e3-4c1c-99f9-89869070319b</t>
+        </is>
+      </c>
+      <c r="B1390" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1390" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1390" t="n">
+        <v>206.03</v>
+      </c>
+      <c r="G1390" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H1390" s="2" t="n">
+        <v>46082.32286005131</v>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>79e97a7c-b334-4834-b507-a7fffdc05c30</t>
+        </is>
+      </c>
+      <c r="B1391" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1391" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1391" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="G1391" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H1391" s="2" t="n">
+        <v>46083.32286005449</v>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>f8516c87-be83-4455-8d74-15fbca730b80</t>
+        </is>
+      </c>
+      <c r="B1392" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1392" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1392" t="n">
+        <v>410.16</v>
+      </c>
+      <c r="G1392" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H1392" s="2" t="n">
+        <v>46094.32286005755</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>ea5c9ae0-192e-4bad-8096-51f2b9a8ebc3</t>
+        </is>
+      </c>
+      <c r="B1393" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1393" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1393" t="n">
+        <v>420.12</v>
+      </c>
+      <c r="G1393" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H1393" s="2" t="n">
+        <v>46076.3228600606</v>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>784fa69c-0ef3-4ef4-977b-2be19f7ba08d</t>
+        </is>
+      </c>
+      <c r="B1394" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1394" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1394" t="n">
+        <v>395.51</v>
+      </c>
+      <c r="G1394" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="H1394" s="2" t="n">
+        <v>46069.32286006435</v>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>6195dead-f130-41dd-a558-02f38456b2cc</t>
+        </is>
+      </c>
+      <c r="B1395" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1395" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1395" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1395" t="n">
+        <v>205.66</v>
+      </c>
+      <c r="G1395" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H1395" s="2" t="n">
+        <v>46075.32286006756</v>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>95cf1499-f773-433f-aa0f-c1e1d7a809af</t>
+        </is>
+      </c>
+      <c r="B1396" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1396" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1396" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1396" t="n">
+        <v>453.22</v>
+      </c>
+      <c r="G1396" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="H1396" s="2" t="n">
+        <v>46085.32286007085</v>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>9c6e90b1-dff2-4b78-ae67-cf32817d5df4</t>
+        </is>
+      </c>
+      <c r="B1397" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1397" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1397" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1397" t="n">
+        <v>242.97</v>
+      </c>
+      <c r="G1397" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="H1397" s="2" t="n">
+        <v>46079.3228600743</v>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>6c608919-9b21-4924-8ffa-05693147aed7</t>
+        </is>
+      </c>
+      <c r="B1398" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1398" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1398" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1398" t="n">
+        <v>83.98</v>
+      </c>
+      <c r="G1398" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H1398" s="2" t="n">
+        <v>46093.32286007755</v>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>45ac5b49-4ae9-40ba-816a-20f768a2d408</t>
+        </is>
+      </c>
+      <c r="B1399" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1399" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1399" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1399" t="n">
+        <v>66.48</v>
+      </c>
+      <c r="G1399" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H1399" s="2" t="n">
+        <v>46095.32286008081</v>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>d66a44be-271b-4e19-b4fa-fb2b86a67062</t>
+        </is>
+      </c>
+      <c r="B1400" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1400" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1400" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1400" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1400" t="n">
+        <v>355.01</v>
+      </c>
+      <c r="G1400" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H1400" s="2" t="n">
+        <v>46074.32286008428</v>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>3e97200b-aff4-476f-9ae6-ad2ce4d611a1</t>
+        </is>
+      </c>
+      <c r="B1401" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1401" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1401" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1401" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="G1401" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H1401" s="2" t="n">
+        <v>46070.32286008786</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1401"/>
+  <dimension ref="A1:H1451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46405,7 +46405,7 @@
         <v>3.11</v>
       </c>
       <c r="H1352" s="2" t="n">
-        <v>46084.32285992507</v>
+        <v>46084.32285993056</v>
       </c>
     </row>
     <row r="1353">
@@ -46439,7 +46439,7 @@
         <v>4.26</v>
       </c>
       <c r="H1353" s="2" t="n">
-        <v>46066.32285992941</v>
+        <v>46066.32285993056</v>
       </c>
     </row>
     <row r="1354">
@@ -46473,7 +46473,7 @@
         <v>2.83</v>
       </c>
       <c r="H1354" s="2" t="n">
-        <v>46083.32285993282</v>
+        <v>46083.32285993056</v>
       </c>
     </row>
     <row r="1355">
@@ -46507,7 +46507,7 @@
         <v>3.97</v>
       </c>
       <c r="H1355" s="2" t="n">
-        <v>46086.32285993652</v>
+        <v>46086.32285994213</v>
       </c>
     </row>
     <row r="1356">
@@ -46541,7 +46541,7 @@
         <v>0.46</v>
       </c>
       <c r="H1356" s="2" t="n">
-        <v>46083.32285993961</v>
+        <v>46083.32285994213</v>
       </c>
     </row>
     <row r="1357">
@@ -46575,7 +46575,7 @@
         <v>4.42</v>
       </c>
       <c r="H1357" s="2" t="n">
-        <v>46079.32285994302</v>
+        <v>46079.32285994213</v>
       </c>
     </row>
     <row r="1358">
@@ -46609,7 +46609,7 @@
         <v>0.2</v>
       </c>
       <c r="H1358" s="2" t="n">
-        <v>46091.3228599463</v>
+        <v>46091.32285994213</v>
       </c>
     </row>
     <row r="1359">
@@ -46643,7 +46643,7 @@
         <v>4.82</v>
       </c>
       <c r="H1359" s="2" t="n">
-        <v>46081.32285994949</v>
+        <v>46081.3228599537</v>
       </c>
     </row>
     <row r="1360">
@@ -46677,7 +46677,7 @@
         <v>1.64</v>
       </c>
       <c r="H1360" s="2" t="n">
-        <v>46092.3228599526</v>
+        <v>46092.3228599537</v>
       </c>
     </row>
     <row r="1361">
@@ -46711,7 +46711,7 @@
         <v>2.09</v>
       </c>
       <c r="H1361" s="2" t="n">
-        <v>46078.32285995584</v>
+        <v>46078.3228599537</v>
       </c>
     </row>
     <row r="1362">
@@ -46745,7 +46745,7 @@
         <v>0.03</v>
       </c>
       <c r="H1362" s="2" t="n">
-        <v>46095.32285995917</v>
+        <v>46095.3228599537</v>
       </c>
     </row>
     <row r="1363">
@@ -46779,7 +46779,7 @@
         <v>3.47</v>
       </c>
       <c r="H1363" s="2" t="n">
-        <v>46086.3228599624</v>
+        <v>46086.32285996528</v>
       </c>
     </row>
     <row r="1364">
@@ -46813,7 +46813,7 @@
         <v>4.52</v>
       </c>
       <c r="H1364" s="2" t="n">
-        <v>46081.32285996567</v>
+        <v>46081.32285996528</v>
       </c>
     </row>
     <row r="1365">
@@ -46847,7 +46847,7 @@
         <v>1.64</v>
       </c>
       <c r="H1365" s="2" t="n">
-        <v>46071.32285996973</v>
+        <v>46071.32285996528</v>
       </c>
     </row>
     <row r="1366">
@@ -46881,7 +46881,7 @@
         <v>3.39</v>
       </c>
       <c r="H1366" s="2" t="n">
-        <v>46068.32285997286</v>
+        <v>46068.32285997686</v>
       </c>
     </row>
     <row r="1367">
@@ -46915,7 +46915,7 @@
         <v>1.02</v>
       </c>
       <c r="H1367" s="2" t="n">
-        <v>46073.32285997614</v>
+        <v>46073.32285997686</v>
       </c>
     </row>
     <row r="1368">
@@ -46949,7 +46949,7 @@
         <v>3.58</v>
       </c>
       <c r="H1368" s="2" t="n">
-        <v>46071.32285997931</v>
+        <v>46071.32285997686</v>
       </c>
     </row>
     <row r="1369">
@@ -46983,7 +46983,7 @@
         <v>4.56</v>
       </c>
       <c r="H1369" s="2" t="n">
-        <v>46091.32285998268</v>
+        <v>46091.32285998842</v>
       </c>
     </row>
     <row r="1370">
@@ -47017,7 +47017,7 @@
         <v>4.97</v>
       </c>
       <c r="H1370" s="2" t="n">
-        <v>46087.32285998595</v>
+        <v>46087.32285998842</v>
       </c>
     </row>
     <row r="1371">
@@ -47051,7 +47051,7 @@
         <v>0.22</v>
       </c>
       <c r="H1371" s="2" t="n">
-        <v>46066.32285998904</v>
+        <v>46066.32285998842</v>
       </c>
     </row>
     <row r="1372">
@@ -47085,7 +47085,7 @@
         <v>4.54</v>
       </c>
       <c r="H1372" s="2" t="n">
-        <v>46088.3228599925</v>
+        <v>46088.32285998842</v>
       </c>
     </row>
     <row r="1373">
@@ -47119,7 +47119,7 @@
         <v>1.8</v>
       </c>
       <c r="H1373" s="2" t="n">
-        <v>46075.32285999559</v>
+        <v>46075.32286</v>
       </c>
     </row>
     <row r="1374">
@@ -47153,7 +47153,7 @@
         <v>2.81</v>
       </c>
       <c r="H1374" s="2" t="n">
-        <v>46072.32285999883</v>
+        <v>46072.32286</v>
       </c>
     </row>
     <row r="1375">
@@ -47187,7 +47187,7 @@
         <v>4.6</v>
       </c>
       <c r="H1375" s="2" t="n">
-        <v>46066.32286000184</v>
+        <v>46066.32286</v>
       </c>
     </row>
     <row r="1376">
@@ -47221,7 +47221,7 @@
         <v>3.76</v>
       </c>
       <c r="H1376" s="2" t="n">
-        <v>46078.32286000525</v>
+        <v>46078.32286</v>
       </c>
     </row>
     <row r="1377">
@@ -47255,7 +47255,7 @@
         <v>1.3</v>
       </c>
       <c r="H1377" s="2" t="n">
-        <v>46083.32286000862</v>
+        <v>46083.32286001158</v>
       </c>
     </row>
     <row r="1378">
@@ -47289,7 +47289,7 @@
         <v>2.05</v>
       </c>
       <c r="H1378" s="2" t="n">
-        <v>46070.32286001185</v>
+        <v>46070.32286001158</v>
       </c>
     </row>
     <row r="1379">
@@ -47323,7 +47323,7 @@
         <v>0.74</v>
       </c>
       <c r="H1379" s="2" t="n">
-        <v>46086.32286001596</v>
+        <v>46086.32286001158</v>
       </c>
     </row>
     <row r="1380">
@@ -47357,7 +47357,7 @@
         <v>0.71</v>
       </c>
       <c r="H1380" s="2" t="n">
-        <v>46066.32286001905</v>
+        <v>46066.32286002315</v>
       </c>
     </row>
     <row r="1381">
@@ -47391,7 +47391,7 @@
         <v>4.61</v>
       </c>
       <c r="H1381" s="2" t="n">
-        <v>46091.32286002226</v>
+        <v>46091.32286002315</v>
       </c>
     </row>
     <row r="1382">
@@ -47425,7 +47425,7 @@
         <v>3.19</v>
       </c>
       <c r="H1382" s="2" t="n">
-        <v>46078.32286002535</v>
+        <v>46078.32286002315</v>
       </c>
     </row>
     <row r="1383">
@@ -47459,7 +47459,7 @@
         <v>0.4</v>
       </c>
       <c r="H1383" s="2" t="n">
-        <v>46093.32286002857</v>
+        <v>46093.32286002315</v>
       </c>
     </row>
     <row r="1384">
@@ -47493,7 +47493,7 @@
         <v>4.02</v>
       </c>
       <c r="H1384" s="2" t="n">
-        <v>46095.3228600318</v>
+        <v>46095.32286003472</v>
       </c>
     </row>
     <row r="1385">
@@ -47527,7 +47527,7 @@
         <v>2.4</v>
       </c>
       <c r="H1385" s="2" t="n">
-        <v>46085.32286003488</v>
+        <v>46085.32286003472</v>
       </c>
     </row>
     <row r="1386">
@@ -47561,7 +47561,7 @@
         <v>2.63</v>
       </c>
       <c r="H1386" s="2" t="n">
-        <v>46092.32286003864</v>
+        <v>46092.32286003472</v>
       </c>
     </row>
     <row r="1387">
@@ -47595,7 +47595,7 @@
         <v>4.32</v>
       </c>
       <c r="H1387" s="2" t="n">
-        <v>46084.32286004175</v>
+        <v>46084.3228600463</v>
       </c>
     </row>
     <row r="1388">
@@ -47629,7 +47629,7 @@
         <v>4.23</v>
       </c>
       <c r="H1388" s="2" t="n">
-        <v>46084.32286004492</v>
+        <v>46084.3228600463</v>
       </c>
     </row>
     <row r="1389">
@@ -47663,7 +47663,7 @@
         <v>4.77</v>
       </c>
       <c r="H1389" s="2" t="n">
-        <v>46081.32286004804</v>
+        <v>46081.3228600463</v>
       </c>
     </row>
     <row r="1390">
@@ -47697,7 +47697,7 @@
         <v>2.06</v>
       </c>
       <c r="H1390" s="2" t="n">
-        <v>46082.32286005131</v>
+        <v>46082.3228600463</v>
       </c>
     </row>
     <row r="1391">
@@ -47731,7 +47731,7 @@
         <v>0.17</v>
       </c>
       <c r="H1391" s="2" t="n">
-        <v>46083.32286005449</v>
+        <v>46083.32286005787</v>
       </c>
     </row>
     <row r="1392">
@@ -47765,7 +47765,7 @@
         <v>4.1</v>
       </c>
       <c r="H1392" s="2" t="n">
-        <v>46094.32286005755</v>
+        <v>46094.32286005787</v>
       </c>
     </row>
     <row r="1393">
@@ -47799,7 +47799,7 @@
         <v>4.2</v>
       </c>
       <c r="H1393" s="2" t="n">
-        <v>46076.3228600606</v>
+        <v>46076.32286005787</v>
       </c>
     </row>
     <row r="1394">
@@ -47833,7 +47833,7 @@
         <v>3.96</v>
       </c>
       <c r="H1394" s="2" t="n">
-        <v>46069.32286006435</v>
+        <v>46069.32286006944</v>
       </c>
     </row>
     <row r="1395">
@@ -47867,7 +47867,7 @@
         <v>2.06</v>
       </c>
       <c r="H1395" s="2" t="n">
-        <v>46075.32286006756</v>
+        <v>46075.32286006944</v>
       </c>
     </row>
     <row r="1396">
@@ -47901,7 +47901,7 @@
         <v>4.53</v>
       </c>
       <c r="H1396" s="2" t="n">
-        <v>46085.32286007085</v>
+        <v>46085.32286006944</v>
       </c>
     </row>
     <row r="1397">
@@ -47935,7 +47935,7 @@
         <v>2.43</v>
       </c>
       <c r="H1397" s="2" t="n">
-        <v>46079.3228600743</v>
+        <v>46079.32286006944</v>
       </c>
     </row>
     <row r="1398">
@@ -47969,7 +47969,7 @@
         <v>0.84</v>
       </c>
       <c r="H1398" s="2" t="n">
-        <v>46093.32286007755</v>
+        <v>46093.32286008102</v>
       </c>
     </row>
     <row r="1399">
@@ -48003,7 +48003,7 @@
         <v>0.66</v>
       </c>
       <c r="H1399" s="2" t="n">
-        <v>46095.32286008081</v>
+        <v>46095.32286008102</v>
       </c>
     </row>
     <row r="1400">
@@ -48037,7 +48037,7 @@
         <v>3.55</v>
       </c>
       <c r="H1400" s="2" t="n">
-        <v>46074.32286008428</v>
+        <v>46074.32286008102</v>
       </c>
     </row>
     <row r="1401">
@@ -48071,7 +48071,1707 @@
         <v>0.2</v>
       </c>
       <c r="H1401" s="2" t="n">
-        <v>46070.32286008786</v>
+        <v>46070.32286009259</v>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>315233ab-de09-4dae-98c5-60b6571801ec</t>
+        </is>
+      </c>
+      <c r="B1402" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1402" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1402" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1402" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1402" t="n">
+        <v>197.25</v>
+      </c>
+      <c r="G1402" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H1402" s="2" t="n">
+        <v>46082.35787033964</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>eab062a8-1ce4-4835-8e45-830bbc1b4f20</t>
+        </is>
+      </c>
+      <c r="B1403" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1403" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1403" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1403" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1403" t="n">
+        <v>493.46</v>
+      </c>
+      <c r="G1403" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="H1403" s="2" t="n">
+        <v>46079.35787034393</v>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>c8cddf37-cf9c-4eb8-938d-5a84537c9fb2</t>
+        </is>
+      </c>
+      <c r="B1404" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1404" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1404" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1404" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1404" t="n">
+        <v>490.57</v>
+      </c>
+      <c r="G1404" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="H1404" s="2" t="n">
+        <v>46092.35787034714</v>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>9fe9a17c-a3b0-4753-9222-2375b34f844d</t>
+        </is>
+      </c>
+      <c r="B1405" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1405" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1405" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1405" t="n">
+        <v>129.19</v>
+      </c>
+      <c r="G1405" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H1405" s="2" t="n">
+        <v>46092.35787035071</v>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>bc5b5ab3-fd7b-4b80-b7dd-26a1b1b369f5</t>
+        </is>
+      </c>
+      <c r="B1406" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1406" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1406" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1406" t="n">
+        <v>101.21</v>
+      </c>
+      <c r="G1406" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="H1406" s="2" t="n">
+        <v>46079.35787035383</v>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>380dc11e-72e7-4f87-a035-6fc7e73fcf74</t>
+        </is>
+      </c>
+      <c r="B1407" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1407" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1407" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1407" t="n">
+        <v>272.58</v>
+      </c>
+      <c r="G1407" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H1407" s="2" t="n">
+        <v>46095.35787035698</v>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>7d49ce68-5ef4-4986-a6af-96d91692b951</t>
+        </is>
+      </c>
+      <c r="B1408" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1408" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1408" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1408" t="n">
+        <v>325.33</v>
+      </c>
+      <c r="G1408" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H1408" s="2" t="n">
+        <v>46094.35787036037</v>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>c15ff324-436b-4f2d-8f6b-5f3f9986a0e7</t>
+        </is>
+      </c>
+      <c r="B1409" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1409" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1409" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1409" t="n">
+        <v>450.9</v>
+      </c>
+      <c r="G1409" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="H1409" s="2" t="n">
+        <v>46079.35787036354</v>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>f49e7147-f99e-41ec-b4fb-f831915d9808</t>
+        </is>
+      </c>
+      <c r="B1410" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1410" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1410" t="n">
+        <v>354.16</v>
+      </c>
+      <c r="G1410" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="H1410" s="2" t="n">
+        <v>46079.35787036682</v>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>92ca576c-ffe6-4381-b759-c6121480811f</t>
+        </is>
+      </c>
+      <c r="B1411" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1411" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1411" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1411" t="n">
+        <v>133.6</v>
+      </c>
+      <c r="G1411" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="H1411" s="2" t="n">
+        <v>46093.35787036993</v>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>1fd0156d-2bea-4bbc-808c-1182cb60a55a</t>
+        </is>
+      </c>
+      <c r="B1412" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1412" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1412" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1412" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="G1412" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H1412" s="2" t="n">
+        <v>46081.35787037356</v>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>c632a8d6-3b22-4dce-b0b5-7306627f5148</t>
+        </is>
+      </c>
+      <c r="B1413" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1413" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1413" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1413" t="n">
+        <v>413.08</v>
+      </c>
+      <c r="G1413" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="H1413" s="2" t="n">
+        <v>46089.3578703767</v>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>c0dd2dfd-3ea2-4b9a-9783-bf0889f8bff1</t>
+        </is>
+      </c>
+      <c r="B1414" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1414" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1414" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1414" t="n">
+        <v>208.75</v>
+      </c>
+      <c r="G1414" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="H1414" s="2" t="n">
+        <v>46079.35787037977</v>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>b03112af-9a3b-459f-b875-2ecc7d9fba8c</t>
+        </is>
+      </c>
+      <c r="B1415" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1415" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1415" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1415" t="n">
+        <v>496.12</v>
+      </c>
+      <c r="G1415" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="H1415" s="2" t="n">
+        <v>46091.35787038316</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>8dcd002e-a0e7-4018-b0de-e4c4fd212841</t>
+        </is>
+      </c>
+      <c r="B1416" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1416" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1416" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1416" t="n">
+        <v>318.33</v>
+      </c>
+      <c r="G1416" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H1416" s="2" t="n">
+        <v>46080.35787038643</v>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>bffd4a96-12ad-4f6b-8b6a-0ca105fed16a</t>
+        </is>
+      </c>
+      <c r="B1417" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1417" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1417" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1417" t="n">
+        <v>50.82</v>
+      </c>
+      <c r="G1417" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H1417" s="2" t="n">
+        <v>46074.35787038977</v>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>3af35cbb-553a-4847-b55a-cd2904c63077</t>
+        </is>
+      </c>
+      <c r="B1418" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1418" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1418" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1418" t="n">
+        <v>197.85</v>
+      </c>
+      <c r="G1418" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H1418" s="2" t="n">
+        <v>46089.35787039284</v>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>15022968-461a-44bb-b54b-c299deaf6bfc</t>
+        </is>
+      </c>
+      <c r="B1419" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1419" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1419" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1419" t="n">
+        <v>439.62</v>
+      </c>
+      <c r="G1419" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H1419" s="2" t="n">
+        <v>46066.35787039605</v>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>09bedb2b-2ea0-4eb3-af78-bbc3c28ade61</t>
+        </is>
+      </c>
+      <c r="B1420" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1420" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1420" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1420" t="n">
+        <v>394.23</v>
+      </c>
+      <c r="G1420" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="H1420" s="2" t="n">
+        <v>46073.35787039919</v>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>11dffe95-811d-4e2e-9fd8-be9946cb68f8</t>
+        </is>
+      </c>
+      <c r="B1421" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1421" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1421" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1421" t="n">
+        <v>178.23</v>
+      </c>
+      <c r="G1421" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H1421" s="2" t="n">
+        <v>46069.35787040242</v>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>234b7614-2114-4453-9ace-dbc32b4cb825</t>
+        </is>
+      </c>
+      <c r="B1422" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1422" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1422" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1422" t="n">
+        <v>142.75</v>
+      </c>
+      <c r="G1422" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H1422" s="2" t="n">
+        <v>46077.35787040542</v>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>fdb0626c-e24c-4cf5-bdc1-a8d380425e08</t>
+        </is>
+      </c>
+      <c r="B1423" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1423" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1423" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1423" t="n">
+        <v>428.95</v>
+      </c>
+      <c r="G1423" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="H1423" s="2" t="n">
+        <v>46079.35787040873</v>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>f2ed00f5-36cb-478f-99be-63cead244709</t>
+        </is>
+      </c>
+      <c r="B1424" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1424" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1424" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1424" t="n">
+        <v>303.31</v>
+      </c>
+      <c r="G1424" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="H1424" s="2" t="n">
+        <v>46069.35787041192</v>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>d78dba12-9afe-48e4-9c3f-55269b2dc908</t>
+        </is>
+      </c>
+      <c r="B1425" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1425" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1425" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1425" t="n">
+        <v>149.21</v>
+      </c>
+      <c r="G1425" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H1425" s="2" t="n">
+        <v>46079.35787041514</v>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>edc89045-64eb-47e4-b5e3-41dbe705b88d</t>
+        </is>
+      </c>
+      <c r="B1426" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1426" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1426" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1426" t="n">
+        <v>239.02</v>
+      </c>
+      <c r="G1426" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H1426" s="2" t="n">
+        <v>46086.35787041856</v>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>13614c8b-a55f-44db-9bdb-f1ff61e76013</t>
+        </is>
+      </c>
+      <c r="B1427" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1427" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1427" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1427" t="n">
+        <v>16.93</v>
+      </c>
+      <c r="G1427" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H1427" s="2" t="n">
+        <v>46085.35787042179</v>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>b882e698-7840-4ca0-b55d-395ac2b45bf6</t>
+        </is>
+      </c>
+      <c r="B1428" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1428" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1428" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1428" t="n">
+        <v>252.34</v>
+      </c>
+      <c r="G1428" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H1428" s="2" t="n">
+        <v>46080.35787042485</v>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>7d9c9c31-fd3c-479d-8024-cc236370d0e0</t>
+        </is>
+      </c>
+      <c r="B1429" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1429" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1429" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1429" t="n">
+        <v>118.64</v>
+      </c>
+      <c r="G1429" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H1429" s="2" t="n">
+        <v>46090.35787042801</v>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>e8e78f87-cb95-4c3e-bab2-72eee3f5b485</t>
+        </is>
+      </c>
+      <c r="B1430" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1430" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1430" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1430" t="n">
+        <v>67.09</v>
+      </c>
+      <c r="G1430" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H1430" s="2" t="n">
+        <v>46078.35787043128</v>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>0e415e56-3c59-4ba8-8785-cdedc6768dd6</t>
+        </is>
+      </c>
+      <c r="B1431" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1431" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1431" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1431" t="n">
+        <v>230.26</v>
+      </c>
+      <c r="G1431" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H1431" s="2" t="n">
+        <v>46082.35787043439</v>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>51882319-ae87-45eb-8db4-e713ebbee69d</t>
+        </is>
+      </c>
+      <c r="B1432" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1432" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1432" t="n">
+        <v>437.65</v>
+      </c>
+      <c r="G1432" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="H1432" s="2" t="n">
+        <v>46089.3578704375</v>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>a227ebea-f21b-4d04-a2b7-4ab954d1d161</t>
+        </is>
+      </c>
+      <c r="B1433" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1433" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1433" t="n">
+        <v>74.61</v>
+      </c>
+      <c r="G1433" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H1433" s="2" t="n">
+        <v>46068.35787044065</v>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>2ea7a0ee-0b88-45b1-8f6e-10bf837d4d01</t>
+        </is>
+      </c>
+      <c r="B1434" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1434" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1434" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1434" t="n">
+        <v>491.07</v>
+      </c>
+      <c r="G1434" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="H1434" s="2" t="n">
+        <v>46079.35787044399</v>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>47dacfa0-4728-457b-990a-d2ef6b408eff</t>
+        </is>
+      </c>
+      <c r="B1435" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1435" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1435" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1435" t="n">
+        <v>390.98</v>
+      </c>
+      <c r="G1435" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="H1435" s="2" t="n">
+        <v>46091.35787044729</v>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>f53b4355-9e88-4cfb-a4ab-73c5cfadee2a</t>
+        </is>
+      </c>
+      <c r="B1436" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1436" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1436" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1436" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1436" t="n">
+        <v>274.98</v>
+      </c>
+      <c r="G1436" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H1436" s="2" t="n">
+        <v>46088.35787045035</v>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>cfcc4d79-0855-42f9-a818-e9e9b139df07</t>
+        </is>
+      </c>
+      <c r="B1437" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1437" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1437" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1437" t="n">
+        <v>244.48</v>
+      </c>
+      <c r="G1437" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H1437" s="2" t="n">
+        <v>46067.3578704536</v>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>83c896ed-1bc6-43fc-953b-c2ed8653c403</t>
+        </is>
+      </c>
+      <c r="B1438" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1438" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1438" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1438" t="n">
+        <v>143.4</v>
+      </c>
+      <c r="G1438" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H1438" s="2" t="n">
+        <v>46088.35787045665</v>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>fe6eaa60-4df6-4912-8deb-c8d13c6186d7</t>
+        </is>
+      </c>
+      <c r="B1439" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1439" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1439" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1439" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="G1439" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="H1439" s="2" t="n">
+        <v>46080.35787045973</v>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>99751164-e488-40f3-9872-54ccdf062bef</t>
+        </is>
+      </c>
+      <c r="B1440" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1440" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1440" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1440" t="n">
+        <v>458.84</v>
+      </c>
+      <c r="G1440" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="H1440" s="2" t="n">
+        <v>46074.35787046278</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>a9103f53-c513-45e3-a226-ab4e3265da6d</t>
+        </is>
+      </c>
+      <c r="B1441" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1441" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1441" t="n">
+        <v>77.39</v>
+      </c>
+      <c r="G1441" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="H1441" s="2" t="n">
+        <v>46088.35787046605</v>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>41fab8da-6513-4c74-8f8b-d27c5ef456d5</t>
+        </is>
+      </c>
+      <c r="B1442" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1442" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1442" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1442" t="n">
+        <v>93</v>
+      </c>
+      <c r="G1442" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H1442" s="2" t="n">
+        <v>46074.3578704692</v>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>de57da4b-992c-4fb2-a357-ba21928762a4</t>
+        </is>
+      </c>
+      <c r="B1443" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1443" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1443" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1443" t="n">
+        <v>29.04</v>
+      </c>
+      <c r="G1443" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H1443" s="2" t="n">
+        <v>46084.35787047241</v>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>cdf7124e-bcf9-4481-818e-c51d0ee94887</t>
+        </is>
+      </c>
+      <c r="B1444" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1444" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1444" t="n">
+        <v>384.38</v>
+      </c>
+      <c r="G1444" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="H1444" s="2" t="n">
+        <v>46086.35787047545</v>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>ffa5af68-410a-4ab4-8502-d401c1df3fee</t>
+        </is>
+      </c>
+      <c r="B1445" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1445" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1445" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1445" t="n">
+        <v>77.55</v>
+      </c>
+      <c r="G1445" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H1445" s="2" t="n">
+        <v>46087.35787047885</v>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>30f111ce-8dff-4556-b7b9-13a8769da80b</t>
+        </is>
+      </c>
+      <c r="B1446" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1446" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1446" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1446" t="n">
+        <v>21.83</v>
+      </c>
+      <c r="G1446" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H1446" s="2" t="n">
+        <v>46068.35787048196</v>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>acb5eb49-7b5e-4cae-a741-c64cc062efb1</t>
+        </is>
+      </c>
+      <c r="B1447" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1447" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1447" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1447" t="n">
+        <v>135.4</v>
+      </c>
+      <c r="G1447" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H1447" s="2" t="n">
+        <v>46092.35787048502</v>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>e2d13110-c4bb-41fb-bcac-078759600775</t>
+        </is>
+      </c>
+      <c r="B1448" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1448" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1448" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1448" t="n">
+        <v>333.04</v>
+      </c>
+      <c r="G1448" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="H1448" s="2" t="n">
+        <v>46072.35787048821</v>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>0ce82719-aaeb-49e8-89b3-dc1e39078a56</t>
+        </is>
+      </c>
+      <c r="B1449" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1449" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1449" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1449" t="n">
+        <v>344.77</v>
+      </c>
+      <c r="G1449" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H1449" s="2" t="n">
+        <v>46089.35787049133</v>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>1976c0dc-3963-4c80-9ae1-f1e0f5f188c8</t>
+        </is>
+      </c>
+      <c r="B1450" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1450" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1450" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1450" t="n">
+        <v>104.84</v>
+      </c>
+      <c r="G1450" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H1450" s="2" t="n">
+        <v>46068.35787049436</v>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>ba12dd4b-3f38-404f-9d51-6febaa1de92f</t>
+        </is>
+      </c>
+      <c r="B1451" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1451" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1451" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1451" t="n">
+        <v>163.15</v>
+      </c>
+      <c r="G1451" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H1451" s="2" t="n">
+        <v>46074.3578704974</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1451"/>
+  <dimension ref="A1:H1501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48105,7 +48105,7 @@
         <v>1.97</v>
       </c>
       <c r="H1402" s="2" t="n">
-        <v>46082.35787033964</v>
+        <v>46082.35787033565</v>
       </c>
     </row>
     <row r="1403">
@@ -48139,7 +48139,7 @@
         <v>4.93</v>
       </c>
       <c r="H1403" s="2" t="n">
-        <v>46079.35787034393</v>
+        <v>46079.35787034722</v>
       </c>
     </row>
     <row r="1404">
@@ -48173,7 +48173,7 @@
         <v>4.91</v>
       </c>
       <c r="H1404" s="2" t="n">
-        <v>46092.35787034714</v>
+        <v>46092.35787034722</v>
       </c>
     </row>
     <row r="1405">
@@ -48207,7 +48207,7 @@
         <v>1.29</v>
       </c>
       <c r="H1405" s="2" t="n">
-        <v>46092.35787035071</v>
+        <v>46092.35787034722</v>
       </c>
     </row>
     <row r="1406">
@@ -48241,7 +48241,7 @@
         <v>1.01</v>
       </c>
       <c r="H1406" s="2" t="n">
-        <v>46079.35787035383</v>
+        <v>46079.3578703588</v>
       </c>
     </row>
     <row r="1407">
@@ -48275,7 +48275,7 @@
         <v>2.73</v>
       </c>
       <c r="H1407" s="2" t="n">
-        <v>46095.35787035698</v>
+        <v>46095.3578703588</v>
       </c>
     </row>
     <row r="1408">
@@ -48309,7 +48309,7 @@
         <v>3.25</v>
       </c>
       <c r="H1408" s="2" t="n">
-        <v>46094.35787036037</v>
+        <v>46094.3578703588</v>
       </c>
     </row>
     <row r="1409">
@@ -48343,7 +48343,7 @@
         <v>4.51</v>
       </c>
       <c r="H1409" s="2" t="n">
-        <v>46079.35787036354</v>
+        <v>46079.3578703588</v>
       </c>
     </row>
     <row r="1410">
@@ -48377,7 +48377,7 @@
         <v>3.54</v>
       </c>
       <c r="H1410" s="2" t="n">
-        <v>46079.35787036682</v>
+        <v>46079.35787037037</v>
       </c>
     </row>
     <row r="1411">
@@ -48411,7 +48411,7 @@
         <v>1.34</v>
       </c>
       <c r="H1411" s="2" t="n">
-        <v>46093.35787036993</v>
+        <v>46093.35787037037</v>
       </c>
     </row>
     <row r="1412">
@@ -48445,7 +48445,7 @@
         <v>0.08</v>
       </c>
       <c r="H1412" s="2" t="n">
-        <v>46081.35787037356</v>
+        <v>46081.35787037037</v>
       </c>
     </row>
     <row r="1413">
@@ -48479,7 +48479,7 @@
         <v>4.13</v>
       </c>
       <c r="H1413" s="2" t="n">
-        <v>46089.3578703767</v>
+        <v>46089.35787038194</v>
       </c>
     </row>
     <row r="1414">
@@ -48513,7 +48513,7 @@
         <v>2.09</v>
       </c>
       <c r="H1414" s="2" t="n">
-        <v>46079.35787037977</v>
+        <v>46079.35787038194</v>
       </c>
     </row>
     <row r="1415">
@@ -48547,7 +48547,7 @@
         <v>4.96</v>
       </c>
       <c r="H1415" s="2" t="n">
-        <v>46091.35787038316</v>
+        <v>46091.35787038194</v>
       </c>
     </row>
     <row r="1416">
@@ -48581,7 +48581,7 @@
         <v>3.18</v>
       </c>
       <c r="H1416" s="2" t="n">
-        <v>46080.35787038643</v>
+        <v>46080.35787038194</v>
       </c>
     </row>
     <row r="1417">
@@ -48615,7 +48615,7 @@
         <v>0.51</v>
       </c>
       <c r="H1417" s="2" t="n">
-        <v>46074.35787038977</v>
+        <v>46074.35787039352</v>
       </c>
     </row>
     <row r="1418">
@@ -48649,7 +48649,7 @@
         <v>1.98</v>
       </c>
       <c r="H1418" s="2" t="n">
-        <v>46089.35787039284</v>
+        <v>46089.35787039352</v>
       </c>
     </row>
     <row r="1419">
@@ -48683,7 +48683,7 @@
         <v>4.4</v>
       </c>
       <c r="H1419" s="2" t="n">
-        <v>46066.35787039605</v>
+        <v>46066.35787039352</v>
       </c>
     </row>
     <row r="1420">
@@ -48717,7 +48717,7 @@
         <v>3.94</v>
       </c>
       <c r="H1420" s="2" t="n">
-        <v>46073.35787039919</v>
+        <v>46073.35787039352</v>
       </c>
     </row>
     <row r="1421">
@@ -48751,7 +48751,7 @@
         <v>1.78</v>
       </c>
       <c r="H1421" s="2" t="n">
-        <v>46069.35787040242</v>
+        <v>46069.3578704051</v>
       </c>
     </row>
     <row r="1422">
@@ -48785,7 +48785,7 @@
         <v>1.43</v>
       </c>
       <c r="H1422" s="2" t="n">
-        <v>46077.35787040542</v>
+        <v>46077.3578704051</v>
       </c>
     </row>
     <row r="1423">
@@ -48819,7 +48819,7 @@
         <v>4.29</v>
       </c>
       <c r="H1423" s="2" t="n">
-        <v>46079.35787040873</v>
+        <v>46079.3578704051</v>
       </c>
     </row>
     <row r="1424">
@@ -48853,7 +48853,7 @@
         <v>3.03</v>
       </c>
       <c r="H1424" s="2" t="n">
-        <v>46069.35787041192</v>
+        <v>46069.35787041666</v>
       </c>
     </row>
     <row r="1425">
@@ -48887,7 +48887,7 @@
         <v>1.49</v>
       </c>
       <c r="H1425" s="2" t="n">
-        <v>46079.35787041514</v>
+        <v>46079.35787041666</v>
       </c>
     </row>
     <row r="1426">
@@ -48921,7 +48921,7 @@
         <v>2.39</v>
       </c>
       <c r="H1426" s="2" t="n">
-        <v>46086.35787041856</v>
+        <v>46086.35787041666</v>
       </c>
     </row>
     <row r="1427">
@@ -48955,7 +48955,7 @@
         <v>0.17</v>
       </c>
       <c r="H1427" s="2" t="n">
-        <v>46085.35787042179</v>
+        <v>46085.35787041666</v>
       </c>
     </row>
     <row r="1428">
@@ -48989,7 +48989,7 @@
         <v>2.52</v>
       </c>
       <c r="H1428" s="2" t="n">
-        <v>46080.35787042485</v>
+        <v>46080.35787042824</v>
       </c>
     </row>
     <row r="1429">
@@ -49023,7 +49023,7 @@
         <v>1.19</v>
       </c>
       <c r="H1429" s="2" t="n">
-        <v>46090.35787042801</v>
+        <v>46090.35787042824</v>
       </c>
     </row>
     <row r="1430">
@@ -49057,7 +49057,7 @@
         <v>0.67</v>
       </c>
       <c r="H1430" s="2" t="n">
-        <v>46078.35787043128</v>
+        <v>46078.35787042824</v>
       </c>
     </row>
     <row r="1431">
@@ -49091,7 +49091,7 @@
         <v>2.3</v>
       </c>
       <c r="H1431" s="2" t="n">
-        <v>46082.35787043439</v>
+        <v>46082.35787043982</v>
       </c>
     </row>
     <row r="1432">
@@ -49125,7 +49125,7 @@
         <v>4.38</v>
       </c>
       <c r="H1432" s="2" t="n">
-        <v>46089.3578704375</v>
+        <v>46089.35787043982</v>
       </c>
     </row>
     <row r="1433">
@@ -49159,7 +49159,7 @@
         <v>0.75</v>
       </c>
       <c r="H1433" s="2" t="n">
-        <v>46068.35787044065</v>
+        <v>46068.35787043982</v>
       </c>
     </row>
     <row r="1434">
@@ -49193,7 +49193,7 @@
         <v>4.91</v>
       </c>
       <c r="H1434" s="2" t="n">
-        <v>46079.35787044399</v>
+        <v>46079.35787043982</v>
       </c>
     </row>
     <row r="1435">
@@ -49227,7 +49227,7 @@
         <v>3.91</v>
       </c>
       <c r="H1435" s="2" t="n">
-        <v>46091.35787044729</v>
+        <v>46091.35787045139</v>
       </c>
     </row>
     <row r="1436">
@@ -49261,7 +49261,7 @@
         <v>2.75</v>
       </c>
       <c r="H1436" s="2" t="n">
-        <v>46088.35787045035</v>
+        <v>46088.35787045139</v>
       </c>
     </row>
     <row r="1437">
@@ -49295,7 +49295,7 @@
         <v>2.44</v>
       </c>
       <c r="H1437" s="2" t="n">
-        <v>46067.3578704536</v>
+        <v>46067.35787045139</v>
       </c>
     </row>
     <row r="1438">
@@ -49329,7 +49329,7 @@
         <v>1.43</v>
       </c>
       <c r="H1438" s="2" t="n">
-        <v>46088.35787045665</v>
+        <v>46088.35787045139</v>
       </c>
     </row>
     <row r="1439">
@@ -49363,7 +49363,7 @@
         <v>0.77</v>
       </c>
       <c r="H1439" s="2" t="n">
-        <v>46080.35787045973</v>
+        <v>46080.35787046296</v>
       </c>
     </row>
     <row r="1440">
@@ -49397,7 +49397,7 @@
         <v>4.59</v>
       </c>
       <c r="H1440" s="2" t="n">
-        <v>46074.35787046278</v>
+        <v>46074.35787046296</v>
       </c>
     </row>
     <row r="1441">
@@ -49431,7 +49431,7 @@
         <v>0.77</v>
       </c>
       <c r="H1441" s="2" t="n">
-        <v>46088.35787046605</v>
+        <v>46088.35787046296</v>
       </c>
     </row>
     <row r="1442">
@@ -49465,7 +49465,7 @@
         <v>0.93</v>
       </c>
       <c r="H1442" s="2" t="n">
-        <v>46074.3578704692</v>
+        <v>46074.35787047454</v>
       </c>
     </row>
     <row r="1443">
@@ -49499,7 +49499,7 @@
         <v>0.29</v>
       </c>
       <c r="H1443" s="2" t="n">
-        <v>46084.35787047241</v>
+        <v>46084.35787047454</v>
       </c>
     </row>
     <row r="1444">
@@ -49533,7 +49533,7 @@
         <v>3.84</v>
       </c>
       <c r="H1444" s="2" t="n">
-        <v>46086.35787047545</v>
+        <v>46086.35787047454</v>
       </c>
     </row>
     <row r="1445">
@@ -49567,7 +49567,7 @@
         <v>0.78</v>
       </c>
       <c r="H1445" s="2" t="n">
-        <v>46087.35787047885</v>
+        <v>46087.35787047454</v>
       </c>
     </row>
     <row r="1446">
@@ -49601,7 +49601,7 @@
         <v>0.22</v>
       </c>
       <c r="H1446" s="2" t="n">
-        <v>46068.35787048196</v>
+        <v>46068.35787048611</v>
       </c>
     </row>
     <row r="1447">
@@ -49635,7 +49635,7 @@
         <v>1.35</v>
       </c>
       <c r="H1447" s="2" t="n">
-        <v>46092.35787048502</v>
+        <v>46092.35787048611</v>
       </c>
     </row>
     <row r="1448">
@@ -49669,7 +49669,7 @@
         <v>3.33</v>
       </c>
       <c r="H1448" s="2" t="n">
-        <v>46072.35787048821</v>
+        <v>46072.35787048611</v>
       </c>
     </row>
     <row r="1449">
@@ -49703,7 +49703,7 @@
         <v>3.45</v>
       </c>
       <c r="H1449" s="2" t="n">
-        <v>46089.35787049133</v>
+        <v>46089.35787048611</v>
       </c>
     </row>
     <row r="1450">
@@ -49737,7 +49737,7 @@
         <v>1.05</v>
       </c>
       <c r="H1450" s="2" t="n">
-        <v>46068.35787049436</v>
+        <v>46068.35787049768</v>
       </c>
     </row>
     <row r="1451">
@@ -49771,7 +49771,1707 @@
         <v>1.63</v>
       </c>
       <c r="H1451" s="2" t="n">
-        <v>46074.3578704974</v>
+        <v>46074.35787049768</v>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>93a7dd36-c161-4c0b-899e-925c6aa3978d</t>
+        </is>
+      </c>
+      <c r="B1452" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1452" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1452" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1452" t="n">
+        <v>73.56999999999999</v>
+      </c>
+      <c r="G1452" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H1452" s="2" t="n">
+        <v>46085.40331800383</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>6cef5e0a-eebb-4fc2-8f07-8993e3eaf566</t>
+        </is>
+      </c>
+      <c r="B1453" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1453" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1453" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1453" t="n">
+        <v>197.57</v>
+      </c>
+      <c r="G1453" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H1453" s="2" t="n">
+        <v>46095.40331800817</v>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>d0c08cf7-ce3d-4c80-ae6d-6e53d1efd26f</t>
+        </is>
+      </c>
+      <c r="B1454" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1454" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1454" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1454" t="n">
+        <v>381.56</v>
+      </c>
+      <c r="G1454" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="H1454" s="2" t="n">
+        <v>46088.40331801179</v>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>b7c770b6-07e3-4d03-8d78-48942e9e9f7a</t>
+        </is>
+      </c>
+      <c r="B1455" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1455" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1455" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1455" t="n">
+        <v>158.22</v>
+      </c>
+      <c r="G1455" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H1455" s="2" t="n">
+        <v>46078.40331801493</v>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>14e8f1c9-2069-4a38-970e-9d19d34d0c4e</t>
+        </is>
+      </c>
+      <c r="B1456" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1456" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1456" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1456" t="n">
+        <v>331.76</v>
+      </c>
+      <c r="G1456" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="H1456" s="2" t="n">
+        <v>46091.40331801808</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>1d99a719-8e52-4c22-a377-cd029face776</t>
+        </is>
+      </c>
+      <c r="B1457" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1457" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1457" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1457" t="n">
+        <v>436.79</v>
+      </c>
+      <c r="G1457" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="H1457" s="2" t="n">
+        <v>46092.40331802178</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>51777f26-2035-4552-8cb1-630a4c2c0abc</t>
+        </is>
+      </c>
+      <c r="B1458" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1458" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1458" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1458" t="n">
+        <v>397.67</v>
+      </c>
+      <c r="G1458" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="H1458" s="2" t="n">
+        <v>46087.40331802499</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>707d7704-d0a9-44c7-9be2-ded67341a1fb</t>
+        </is>
+      </c>
+      <c r="B1459" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1459" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1459" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1459" t="n">
+        <v>217.43</v>
+      </c>
+      <c r="G1459" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="H1459" s="2" t="n">
+        <v>46076.40331802811</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>b5722f70-9126-4a23-8dea-e47e792fc988</t>
+        </is>
+      </c>
+      <c r="B1460" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1460" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1460" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1460" t="n">
+        <v>83.65000000000001</v>
+      </c>
+      <c r="G1460" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H1460" s="2" t="n">
+        <v>46088.40331803136</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>8e81bcf0-c5a6-4abf-b964-dd993289e4f2</t>
+        </is>
+      </c>
+      <c r="B1461" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1461" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1461" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1461" t="n">
+        <v>286.21</v>
+      </c>
+      <c r="G1461" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H1461" s="2" t="n">
+        <v>46074.40331803489</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>b9721a7d-4ea7-4c5c-9064-41104bc17d22</t>
+        </is>
+      </c>
+      <c r="B1462" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1462" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1462" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1462" t="n">
+        <v>127.55</v>
+      </c>
+      <c r="G1462" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="H1462" s="2" t="n">
+        <v>46075.40331803829</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>4a84da00-71f7-46a1-9351-d2352b101a51</t>
+        </is>
+      </c>
+      <c r="B1463" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1463" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1463" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1463" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="G1463" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H1463" s="2" t="n">
+        <v>46072.40331804139</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>06e26132-7517-437f-bbbf-d5ea907afb83</t>
+        </is>
+      </c>
+      <c r="B1464" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1464" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1464" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1464" t="n">
+        <v>51.85</v>
+      </c>
+      <c r="G1464" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H1464" s="2" t="n">
+        <v>46078.40331804464</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>25abd816-b2a4-40a1-b8ae-c93b921d1530</t>
+        </is>
+      </c>
+      <c r="B1465" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1465" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1465" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1465" t="n">
+        <v>229.08</v>
+      </c>
+      <c r="G1465" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H1465" s="2" t="n">
+        <v>46080.40331804768</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>2c0cb1c6-f81a-4ab9-9e5d-e51688ca0855</t>
+        </is>
+      </c>
+      <c r="B1466" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1466" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1466" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1466" t="n">
+        <v>442.48</v>
+      </c>
+      <c r="G1466" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="H1466" s="2" t="n">
+        <v>46081.40331805076</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>a04b9c4f-2345-48ba-8ef9-e301a6e4c5d4</t>
+        </is>
+      </c>
+      <c r="B1467" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1467" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1467" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1467" t="n">
+        <v>274.74</v>
+      </c>
+      <c r="G1467" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H1467" s="2" t="n">
+        <v>46079.40331805387</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>35c28588-998e-470a-b667-a3b5d40b79bc</t>
+        </is>
+      </c>
+      <c r="B1468" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1468" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1468" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1468" t="n">
+        <v>18.31</v>
+      </c>
+      <c r="G1468" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H1468" s="2" t="n">
+        <v>46080.40331805713</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>7bc7f9f4-dd81-49da-8f21-edafc1e67248</t>
+        </is>
+      </c>
+      <c r="B1469" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1469" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1469" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1469" t="n">
+        <v>233.77</v>
+      </c>
+      <c r="G1469" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H1469" s="2" t="n">
+        <v>46092.40331806014</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>3bcb3e2b-3fcf-475e-b9a3-7abe86678f59</t>
+        </is>
+      </c>
+      <c r="B1470" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1470" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1470" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1470" t="n">
+        <v>498.45</v>
+      </c>
+      <c r="G1470" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="H1470" s="2" t="n">
+        <v>46066.40331806317</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>eeff5a70-0003-4a71-8fc1-ddeee2675712</t>
+        </is>
+      </c>
+      <c r="B1471" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1471" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1471" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1471" t="n">
+        <v>482.65</v>
+      </c>
+      <c r="G1471" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="H1471" s="2" t="n">
+        <v>46088.40331806643</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>e2f063a2-b65d-4b41-b0c7-fc6f17fce8d5</t>
+        </is>
+      </c>
+      <c r="B1472" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1472" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1472" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1472" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G1472" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1472" s="2" t="n">
+        <v>46068.40331806963</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>64563d3d-0a1d-4eb5-8a3e-36f31c8da6cb</t>
+        </is>
+      </c>
+      <c r="B1473" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1473" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1473" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1473" t="n">
+        <v>200.59</v>
+      </c>
+      <c r="G1473" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="H1473" s="2" t="n">
+        <v>46081.40331807279</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>870d4b67-fe2d-45d5-8b63-450adbeb9182</t>
+        </is>
+      </c>
+      <c r="B1474" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1474" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1474" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1474" t="n">
+        <v>274.13</v>
+      </c>
+      <c r="G1474" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H1474" s="2" t="n">
+        <v>46083.40331807599</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>bbd79780-2130-4f69-8370-2f02731f8084</t>
+        </is>
+      </c>
+      <c r="B1475" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1475" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1475" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1475" t="n">
+        <v>430.99</v>
+      </c>
+      <c r="G1475" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="H1475" s="2" t="n">
+        <v>46086.4033180804</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>b0f04673-935e-4e30-99ec-1b107bc70620</t>
+        </is>
+      </c>
+      <c r="B1476" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1476" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1476" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1476" t="n">
+        <v>17.84</v>
+      </c>
+      <c r="G1476" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H1476" s="2" t="n">
+        <v>46092.40331808354</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>ec14a453-5157-4578-9df0-17e1bbc0429b</t>
+        </is>
+      </c>
+      <c r="B1477" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1477" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1477" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1477" t="n">
+        <v>266</v>
+      </c>
+      <c r="G1477" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H1477" s="2" t="n">
+        <v>46081.40331808675</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>c0b1ec6d-0ec7-481f-930d-b337447f3943</t>
+        </is>
+      </c>
+      <c r="B1478" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1478" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1478" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1478" t="n">
+        <v>412.36</v>
+      </c>
+      <c r="G1478" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="H1478" s="2" t="n">
+        <v>46072.40331808994</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>ef74ad1b-a9ef-4bb5-8aea-3aa573751659</t>
+        </is>
+      </c>
+      <c r="B1479" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1479" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1479" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1479" t="n">
+        <v>479.49</v>
+      </c>
+      <c r="G1479" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="H1479" s="2" t="n">
+        <v>46072.40331809341</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>561d427b-61e5-4002-9905-ffb75c1988b9</t>
+        </is>
+      </c>
+      <c r="B1480" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1480" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1480" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1480" t="n">
+        <v>345.01</v>
+      </c>
+      <c r="G1480" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H1480" s="2" t="n">
+        <v>46067.40331809647</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>bac436f0-1e04-4674-a401-1935af996487</t>
+        </is>
+      </c>
+      <c r="B1481" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1481" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1481" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1481" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="G1481" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H1481" s="2" t="n">
+        <v>46078.40331809957</v>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>b7574b04-197e-4a71-9339-47ba35108319</t>
+        </is>
+      </c>
+      <c r="B1482" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1482" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1482" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1482" t="n">
+        <v>187.89</v>
+      </c>
+      <c r="G1482" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H1482" s="2" t="n">
+        <v>46068.40331810274</v>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>f44ed429-f41f-4e20-b349-351fad8f9293</t>
+        </is>
+      </c>
+      <c r="B1483" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1483" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1483" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1483" t="n">
+        <v>211.51</v>
+      </c>
+      <c r="G1483" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H1483" s="2" t="n">
+        <v>46084.40331810607</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>73b57c8d-e51b-413f-881c-71a7dffb4179</t>
+        </is>
+      </c>
+      <c r="B1484" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1484" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1484" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1484" t="n">
+        <v>172.79</v>
+      </c>
+      <c r="G1484" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H1484" s="2" t="n">
+        <v>46077.40331810926</v>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>3c99ba9e-f5a7-4ad8-b7c2-b317cdb9dd5f</t>
+        </is>
+      </c>
+      <c r="B1485" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1485" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1485" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1485" t="n">
+        <v>462.15</v>
+      </c>
+      <c r="G1485" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="H1485" s="2" t="n">
+        <v>46078.40331811263</v>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>05f239c7-29e5-41b4-9e85-192ea8b904d2</t>
+        </is>
+      </c>
+      <c r="B1486" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1486" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1486" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1486" t="n">
+        <v>196.29</v>
+      </c>
+      <c r="G1486" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H1486" s="2" t="n">
+        <v>46085.40331811584</v>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>29df2464-ee11-4264-a02a-add31b6b7684</t>
+        </is>
+      </c>
+      <c r="B1487" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1487" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1487" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1487" t="n">
+        <v>221.69</v>
+      </c>
+      <c r="G1487" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H1487" s="2" t="n">
+        <v>46075.403318119</v>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>cde54da0-c63c-4291-a137-0de6b67688c5</t>
+        </is>
+      </c>
+      <c r="B1488" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1488" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1488" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1488" t="n">
+        <v>437.03</v>
+      </c>
+      <c r="G1488" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="H1488" s="2" t="n">
+        <v>46072.40331812219</v>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>5d71e634-193c-47be-b8b6-1c7e03146d0b</t>
+        </is>
+      </c>
+      <c r="B1489" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1489" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1489" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1489" t="n">
+        <v>399.94</v>
+      </c>
+      <c r="G1489" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1489" s="2" t="n">
+        <v>46092.40331812551</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>e7463096-b291-459a-bfa4-d8cea719ea12</t>
+        </is>
+      </c>
+      <c r="B1490" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1490" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1490" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1490" t="n">
+        <v>163.59</v>
+      </c>
+      <c r="G1490" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H1490" s="2" t="n">
+        <v>46080.40331812856</v>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>30a4ff7d-c883-42fe-bb8d-5b5e5da4cff2</t>
+        </is>
+      </c>
+      <c r="B1491" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1491" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1491" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1491" t="n">
+        <v>98.27</v>
+      </c>
+      <c r="G1491" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H1491" s="2" t="n">
+        <v>46082.40331813162</v>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>7ac6eeca-058f-46a6-b1ec-40ef22dc16de</t>
+        </is>
+      </c>
+      <c r="B1492" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1492" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1492" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1492" t="n">
+        <v>69.31</v>
+      </c>
+      <c r="G1492" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H1492" s="2" t="n">
+        <v>46075.40331813478</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>c10197a7-2631-4208-ad01-fa12f8608570</t>
+        </is>
+      </c>
+      <c r="B1493" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1493" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1493" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1493" t="n">
+        <v>339.46</v>
+      </c>
+      <c r="G1493" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="H1493" s="2" t="n">
+        <v>46082.40331813797</v>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>1d646589-8be6-4f5e-b24b-34b5f60ae183</t>
+        </is>
+      </c>
+      <c r="B1494" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1494" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1494" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1494" t="n">
+        <v>348.72</v>
+      </c>
+      <c r="G1494" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="H1494" s="2" t="n">
+        <v>46078.4033181411</v>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>1c8d9e5b-ab8a-4920-9338-cbc14d94ff67</t>
+        </is>
+      </c>
+      <c r="B1495" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1495" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1495" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1495" t="n">
+        <v>359.23</v>
+      </c>
+      <c r="G1495" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="H1495" s="2" t="n">
+        <v>46077.40331814413</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>7ae4f17e-f70a-498d-b970-245323816177</t>
+        </is>
+      </c>
+      <c r="B1496" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1496" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1496" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1496" t="n">
+        <v>371.35</v>
+      </c>
+      <c r="G1496" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="H1496" s="2" t="n">
+        <v>46082.40331814719</v>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>88001572-2e2d-46e2-a534-c64b08db74b8</t>
+        </is>
+      </c>
+      <c r="B1497" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1497" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1497" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1497" t="n">
+        <v>163.5</v>
+      </c>
+      <c r="G1497" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H1497" s="2" t="n">
+        <v>46076.40331815042</v>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>b24f18ce-35bb-43b9-85ba-a05efcb082c3</t>
+        </is>
+      </c>
+      <c r="B1498" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1498" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1498" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1498" t="n">
+        <v>259.8</v>
+      </c>
+      <c r="G1498" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H1498" s="2" t="n">
+        <v>46074.40331815345</v>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>e0b1e092-25dc-4f82-aae2-20c94e21a487</t>
+        </is>
+      </c>
+      <c r="B1499" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1499" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1499" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1499" t="n">
+        <v>249.86</v>
+      </c>
+      <c r="G1499" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H1499" s="2" t="n">
+        <v>46088.40331815654</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>41541b51-5d3a-441e-80c4-7bc5f6f2c5fc</t>
+        </is>
+      </c>
+      <c r="B1500" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1500" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1500" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1500" t="n">
+        <v>53.92</v>
+      </c>
+      <c r="G1500" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H1500" s="2" t="n">
+        <v>46084.40331815952</v>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>f7db0db1-6ccb-4f9e-a82a-35354c6aac21</t>
+        </is>
+      </c>
+      <c r="B1501" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1501" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1501" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1501" t="n">
+        <v>445.57</v>
+      </c>
+      <c r="G1501" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="H1501" s="2" t="n">
+        <v>46075.40331816285</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1501"/>
+  <dimension ref="A1:H1551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49805,7 +49805,7 @@
         <v>0.74</v>
       </c>
       <c r="H1452" s="2" t="n">
-        <v>46085.40331800383</v>
+        <v>46085.40331800926</v>
       </c>
     </row>
     <row r="1453">
@@ -49839,7 +49839,7 @@
         <v>1.98</v>
       </c>
       <c r="H1453" s="2" t="n">
-        <v>46095.40331800817</v>
+        <v>46095.40331800926</v>
       </c>
     </row>
     <row r="1454">
@@ -49873,7 +49873,7 @@
         <v>3.82</v>
       </c>
       <c r="H1454" s="2" t="n">
-        <v>46088.40331801179</v>
+        <v>46088.40331800926</v>
       </c>
     </row>
     <row r="1455">
@@ -49907,7 +49907,7 @@
         <v>1.58</v>
       </c>
       <c r="H1455" s="2" t="n">
-        <v>46078.40331801493</v>
+        <v>46078.40331800926</v>
       </c>
     </row>
     <row r="1456">
@@ -49941,7 +49941,7 @@
         <v>3.32</v>
       </c>
       <c r="H1456" s="2" t="n">
-        <v>46091.40331801808</v>
+        <v>46091.40331802084</v>
       </c>
     </row>
     <row r="1457">
@@ -49975,7 +49975,7 @@
         <v>4.37</v>
       </c>
       <c r="H1457" s="2" t="n">
-        <v>46092.40331802178</v>
+        <v>46092.40331802084</v>
       </c>
     </row>
     <row r="1458">
@@ -50009,7 +50009,7 @@
         <v>3.98</v>
       </c>
       <c r="H1458" s="2" t="n">
-        <v>46087.40331802499</v>
+        <v>46087.40331802084</v>
       </c>
     </row>
     <row r="1459">
@@ -50043,7 +50043,7 @@
         <v>2.17</v>
       </c>
       <c r="H1459" s="2" t="n">
-        <v>46076.40331802811</v>
+        <v>46076.4033180324</v>
       </c>
     </row>
     <row r="1460">
@@ -50077,7 +50077,7 @@
         <v>0.84</v>
       </c>
       <c r="H1460" s="2" t="n">
-        <v>46088.40331803136</v>
+        <v>46088.4033180324</v>
       </c>
     </row>
     <row r="1461">
@@ -50111,7 +50111,7 @@
         <v>2.86</v>
       </c>
       <c r="H1461" s="2" t="n">
-        <v>46074.40331803489</v>
+        <v>46074.4033180324</v>
       </c>
     </row>
     <row r="1462">
@@ -50145,7 +50145,7 @@
         <v>1.28</v>
       </c>
       <c r="H1462" s="2" t="n">
-        <v>46075.40331803829</v>
+        <v>46075.40331804398</v>
       </c>
     </row>
     <row r="1463">
@@ -50179,7 +50179,7 @@
         <v>0.6</v>
       </c>
       <c r="H1463" s="2" t="n">
-        <v>46072.40331804139</v>
+        <v>46072.40331804398</v>
       </c>
     </row>
     <row r="1464">
@@ -50213,7 +50213,7 @@
         <v>0.52</v>
       </c>
       <c r="H1464" s="2" t="n">
-        <v>46078.40331804464</v>
+        <v>46078.40331804398</v>
       </c>
     </row>
     <row r="1465">
@@ -50247,7 +50247,7 @@
         <v>2.29</v>
       </c>
       <c r="H1465" s="2" t="n">
-        <v>46080.40331804768</v>
+        <v>46080.40331804398</v>
       </c>
     </row>
     <row r="1466">
@@ -50281,7 +50281,7 @@
         <v>4.42</v>
       </c>
       <c r="H1466" s="2" t="n">
-        <v>46081.40331805076</v>
+        <v>46081.40331805556</v>
       </c>
     </row>
     <row r="1467">
@@ -50315,7 +50315,7 @@
         <v>2.75</v>
       </c>
       <c r="H1467" s="2" t="n">
-        <v>46079.40331805387</v>
+        <v>46079.40331805556</v>
       </c>
     </row>
     <row r="1468">
@@ -50349,7 +50349,7 @@
         <v>0.18</v>
       </c>
       <c r="H1468" s="2" t="n">
-        <v>46080.40331805713</v>
+        <v>46080.40331805556</v>
       </c>
     </row>
     <row r="1469">
@@ -50383,7 +50383,7 @@
         <v>2.34</v>
       </c>
       <c r="H1469" s="2" t="n">
-        <v>46092.40331806014</v>
+        <v>46092.40331805556</v>
       </c>
     </row>
     <row r="1470">
@@ -50417,7 +50417,7 @@
         <v>4.98</v>
       </c>
       <c r="H1470" s="2" t="n">
-        <v>46066.40331806317</v>
+        <v>46066.40331806713</v>
       </c>
     </row>
     <row r="1471">
@@ -50451,7 +50451,7 @@
         <v>4.83</v>
       </c>
       <c r="H1471" s="2" t="n">
-        <v>46088.40331806643</v>
+        <v>46088.40331806713</v>
       </c>
     </row>
     <row r="1472">
@@ -50485,7 +50485,7 @@
         <v>0</v>
       </c>
       <c r="H1472" s="2" t="n">
-        <v>46068.40331806963</v>
+        <v>46068.40331806713</v>
       </c>
     </row>
     <row r="1473">
@@ -50519,7 +50519,7 @@
         <v>2.01</v>
       </c>
       <c r="H1473" s="2" t="n">
-        <v>46081.40331807279</v>
+        <v>46081.40331806713</v>
       </c>
     </row>
     <row r="1474">
@@ -50553,7 +50553,7 @@
         <v>2.74</v>
       </c>
       <c r="H1474" s="2" t="n">
-        <v>46083.40331807599</v>
+        <v>46083.4033180787</v>
       </c>
     </row>
     <row r="1475">
@@ -50587,7 +50587,7 @@
         <v>4.31</v>
       </c>
       <c r="H1475" s="2" t="n">
-        <v>46086.4033180804</v>
+        <v>46086.4033180787</v>
       </c>
     </row>
     <row r="1476">
@@ -50621,7 +50621,7 @@
         <v>0.18</v>
       </c>
       <c r="H1476" s="2" t="n">
-        <v>46092.40331808354</v>
+        <v>46092.4033180787</v>
       </c>
     </row>
     <row r="1477">
@@ -50655,7 +50655,7 @@
         <v>2.66</v>
       </c>
       <c r="H1477" s="2" t="n">
-        <v>46081.40331808675</v>
+        <v>46081.40331809028</v>
       </c>
     </row>
     <row r="1478">
@@ -50689,7 +50689,7 @@
         <v>4.12</v>
       </c>
       <c r="H1478" s="2" t="n">
-        <v>46072.40331808994</v>
+        <v>46072.40331809028</v>
       </c>
     </row>
     <row r="1479">
@@ -50723,7 +50723,7 @@
         <v>4.79</v>
       </c>
       <c r="H1479" s="2" t="n">
-        <v>46072.40331809341</v>
+        <v>46072.40331809028</v>
       </c>
     </row>
     <row r="1480">
@@ -50757,7 +50757,7 @@
         <v>3.45</v>
       </c>
       <c r="H1480" s="2" t="n">
-        <v>46067.40331809647</v>
+        <v>46067.40331810185</v>
       </c>
     </row>
     <row r="1481">
@@ -50791,7 +50791,7 @@
         <v>0.21</v>
       </c>
       <c r="H1481" s="2" t="n">
-        <v>46078.40331809957</v>
+        <v>46078.40331810185</v>
       </c>
     </row>
     <row r="1482">
@@ -50825,7 +50825,7 @@
         <v>1.88</v>
       </c>
       <c r="H1482" s="2" t="n">
-        <v>46068.40331810274</v>
+        <v>46068.40331810185</v>
       </c>
     </row>
     <row r="1483">
@@ -50859,7 +50859,7 @@
         <v>2.12</v>
       </c>
       <c r="H1483" s="2" t="n">
-        <v>46084.40331810607</v>
+        <v>46084.40331810185</v>
       </c>
     </row>
     <row r="1484">
@@ -50893,7 +50893,7 @@
         <v>1.73</v>
       </c>
       <c r="H1484" s="2" t="n">
-        <v>46077.40331810926</v>
+        <v>46077.40331811343</v>
       </c>
     </row>
     <row r="1485">
@@ -50927,7 +50927,7 @@
         <v>4.62</v>
       </c>
       <c r="H1485" s="2" t="n">
-        <v>46078.40331811263</v>
+        <v>46078.40331811343</v>
       </c>
     </row>
     <row r="1486">
@@ -50961,7 +50961,7 @@
         <v>1.96</v>
       </c>
       <c r="H1486" s="2" t="n">
-        <v>46085.40331811584</v>
+        <v>46085.40331811343</v>
       </c>
     </row>
     <row r="1487">
@@ -50995,7 +50995,7 @@
         <v>2.22</v>
       </c>
       <c r="H1487" s="2" t="n">
-        <v>46075.403318119</v>
+        <v>46075.40331811343</v>
       </c>
     </row>
     <row r="1488">
@@ -51029,7 +51029,7 @@
         <v>4.37</v>
       </c>
       <c r="H1488" s="2" t="n">
-        <v>46072.40331812219</v>
+        <v>46072.403318125</v>
       </c>
     </row>
     <row r="1489">
@@ -51063,7 +51063,7 @@
         <v>4</v>
       </c>
       <c r="H1489" s="2" t="n">
-        <v>46092.40331812551</v>
+        <v>46092.403318125</v>
       </c>
     </row>
     <row r="1490">
@@ -51097,7 +51097,7 @@
         <v>1.64</v>
       </c>
       <c r="H1490" s="2" t="n">
-        <v>46080.40331812856</v>
+        <v>46080.403318125</v>
       </c>
     </row>
     <row r="1491">
@@ -51131,7 +51131,7 @@
         <v>0.98</v>
       </c>
       <c r="H1491" s="2" t="n">
-        <v>46082.40331813162</v>
+        <v>46082.40331813657</v>
       </c>
     </row>
     <row r="1492">
@@ -51165,7 +51165,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="H1492" s="2" t="n">
-        <v>46075.40331813478</v>
+        <v>46075.40331813657</v>
       </c>
     </row>
     <row r="1493">
@@ -51199,7 +51199,7 @@
         <v>3.39</v>
       </c>
       <c r="H1493" s="2" t="n">
-        <v>46082.40331813797</v>
+        <v>46082.40331813657</v>
       </c>
     </row>
     <row r="1494">
@@ -51233,7 +51233,7 @@
         <v>3.49</v>
       </c>
       <c r="H1494" s="2" t="n">
-        <v>46078.4033181411</v>
+        <v>46078.40331813657</v>
       </c>
     </row>
     <row r="1495">
@@ -51267,7 +51267,7 @@
         <v>3.59</v>
       </c>
       <c r="H1495" s="2" t="n">
-        <v>46077.40331814413</v>
+        <v>46077.40331814815</v>
       </c>
     </row>
     <row r="1496">
@@ -51301,7 +51301,7 @@
         <v>3.71</v>
       </c>
       <c r="H1496" s="2" t="n">
-        <v>46082.40331814719</v>
+        <v>46082.40331814815</v>
       </c>
     </row>
     <row r="1497">
@@ -51335,7 +51335,7 @@
         <v>1.64</v>
       </c>
       <c r="H1497" s="2" t="n">
-        <v>46076.40331815042</v>
+        <v>46076.40331814815</v>
       </c>
     </row>
     <row r="1498">
@@ -51369,7 +51369,7 @@
         <v>2.6</v>
       </c>
       <c r="H1498" s="2" t="n">
-        <v>46074.40331815345</v>
+        <v>46074.40331814815</v>
       </c>
     </row>
     <row r="1499">
@@ -51403,7 +51403,7 @@
         <v>2.5</v>
       </c>
       <c r="H1499" s="2" t="n">
-        <v>46088.40331815654</v>
+        <v>46088.40331815972</v>
       </c>
     </row>
     <row r="1500">
@@ -51437,7 +51437,7 @@
         <v>0.54</v>
       </c>
       <c r="H1500" s="2" t="n">
-        <v>46084.40331815952</v>
+        <v>46084.40331815972</v>
       </c>
     </row>
     <row r="1501">
@@ -51471,7 +51471,1707 @@
         <v>4.46</v>
       </c>
       <c r="H1501" s="2" t="n">
-        <v>46075.40331816285</v>
+        <v>46075.40331815972</v>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>43ead498-870f-416c-b396-890889c57ea0</t>
+        </is>
+      </c>
+      <c r="B1502" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1502" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1502" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1502" t="n">
+        <v>36.73</v>
+      </c>
+      <c r="G1502" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H1502" s="2" t="n">
+        <v>46077.44312581167</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>7c5ebdec-d583-4838-8213-68859d666c6c</t>
+        </is>
+      </c>
+      <c r="B1503" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1503" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1503" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1503" t="n">
+        <v>446.61</v>
+      </c>
+      <c r="G1503" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="H1503" s="2" t="n">
+        <v>46095.44312581584</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>ac67a1e0-8f9d-4da3-ac13-3938417523d7</t>
+        </is>
+      </c>
+      <c r="B1504" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1504" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1504" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1504" t="n">
+        <v>337.56</v>
+      </c>
+      <c r="G1504" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="H1504" s="2" t="n">
+        <v>46083.44312581902</v>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>e97d69e4-2c88-46e7-8cde-8199f582f5b9</t>
+        </is>
+      </c>
+      <c r="B1505" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1505" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1505" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1505" t="n">
+        <v>65.65000000000001</v>
+      </c>
+      <c r="G1505" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H1505" s="2" t="n">
+        <v>46090.44312582257</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>460ae794-5de5-43a2-9fb7-a5ddadf804a0</t>
+        </is>
+      </c>
+      <c r="B1506" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1506" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1506" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1506" t="n">
+        <v>472.31</v>
+      </c>
+      <c r="G1506" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="H1506" s="2" t="n">
+        <v>46077.44312582564</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>0d577491-be37-4c49-9002-72d0fefc6b2d</t>
+        </is>
+      </c>
+      <c r="B1507" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1507" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1507" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1507" t="n">
+        <v>442.29</v>
+      </c>
+      <c r="G1507" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="H1507" s="2" t="n">
+        <v>46070.44312582895</v>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>1b17354c-f320-46b2-923c-5a3e7a807718</t>
+        </is>
+      </c>
+      <c r="B1508" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1508" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1508" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1508" t="n">
+        <v>436.06</v>
+      </c>
+      <c r="G1508" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="H1508" s="2" t="n">
+        <v>46082.4431258322</v>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>404f2c56-b24b-4538-86d7-660edac1076e</t>
+        </is>
+      </c>
+      <c r="B1509" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1509" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1509" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1509" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="G1509" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H1509" s="2" t="n">
+        <v>46088.4431258353</v>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>fbca9172-dda7-4fe7-a1e9-f0da0239e89c</t>
+        </is>
+      </c>
+      <c r="B1510" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1510" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1510" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1510" t="n">
+        <v>276.82</v>
+      </c>
+      <c r="G1510" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="H1510" s="2" t="n">
+        <v>46079.44312583853</v>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>d4379e26-250b-46f3-918b-e3e66820d055</t>
+        </is>
+      </c>
+      <c r="B1511" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1511" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1511" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1511" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="G1511" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H1511" s="2" t="n">
+        <v>46079.44312584171</v>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>af909e78-6d84-4e73-95c6-7816f8f19772</t>
+        </is>
+      </c>
+      <c r="B1512" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1512" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1512" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1512" t="n">
+        <v>280.41</v>
+      </c>
+      <c r="G1512" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H1512" s="2" t="n">
+        <v>46084.44312584502</v>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>f81f159b-951d-4ade-bc7d-817395085946</t>
+        </is>
+      </c>
+      <c r="B1513" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1513" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1513" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1513" t="n">
+        <v>52.98</v>
+      </c>
+      <c r="G1513" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H1513" s="2" t="n">
+        <v>46071.44312584821</v>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t>fa8dd032-10c7-420f-bc7e-cad5db014adb</t>
+        </is>
+      </c>
+      <c r="B1514" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1514" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1514" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1514" t="n">
+        <v>466.78</v>
+      </c>
+      <c r="G1514" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="H1514" s="2" t="n">
+        <v>46086.44312585129</v>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>be79ec6f-f616-41ae-9692-49ebc3f17f3d</t>
+        </is>
+      </c>
+      <c r="B1515" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1515" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1515" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1515" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1515" t="n">
+        <v>279.35</v>
+      </c>
+      <c r="G1515" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="H1515" s="2" t="n">
+        <v>46066.44312585449</v>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t>fe69e734-7888-4b9e-9932-8190010df45e</t>
+        </is>
+      </c>
+      <c r="B1516" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1516" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1516" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1516" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1516" t="n">
+        <v>13.52</v>
+      </c>
+      <c r="G1516" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H1516" s="2" t="n">
+        <v>46094.44312585783</v>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>c22d9f4b-48e5-4569-9e5e-15f419b34d78</t>
+        </is>
+      </c>
+      <c r="B1517" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1517" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1517" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1517" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1517" t="n">
+        <v>156.38</v>
+      </c>
+      <c r="G1517" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H1517" s="2" t="n">
+        <v>46070.44312586108</v>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>b2b53b75-d7e6-44bb-9c62-02c3b74eb452</t>
+        </is>
+      </c>
+      <c r="B1518" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1518" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1518" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1518" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1518" t="n">
+        <v>293.82</v>
+      </c>
+      <c r="G1518" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H1518" s="2" t="n">
+        <v>46073.44312586416</v>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>967cd44a-5048-4e88-9d54-8ef465483dcb</t>
+        </is>
+      </c>
+      <c r="B1519" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1519" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1519" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1519" t="n">
+        <v>376.63</v>
+      </c>
+      <c r="G1519" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="H1519" s="2" t="n">
+        <v>46073.44312586734</v>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>6530f826-58e2-490e-95fe-e9a2fb8b4d5a</t>
+        </is>
+      </c>
+      <c r="B1520" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1520" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1520" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1520" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1520" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="G1520" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H1520" s="2" t="n">
+        <v>46070.44312587047</v>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>69a3f584-36f2-43b2-89e0-4bf3e2c00ba9</t>
+        </is>
+      </c>
+      <c r="B1521" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1521" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1521" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1521" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1521" t="n">
+        <v>254.35</v>
+      </c>
+      <c r="G1521" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H1521" s="2" t="n">
+        <v>46072.44312587352</v>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>1836e4ae-19a2-40ff-a833-e4ae189b10b7</t>
+        </is>
+      </c>
+      <c r="B1522" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1522" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1522" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1522" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1522" t="n">
+        <v>233.34</v>
+      </c>
+      <c r="G1522" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="H1522" s="2" t="n">
+        <v>46095.44312587656</v>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>2a60688e-379f-4b5c-915a-54da616893c8</t>
+        </is>
+      </c>
+      <c r="B1523" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1523" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1523" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1523" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1523" t="n">
+        <v>122.7</v>
+      </c>
+      <c r="G1523" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="H1523" s="2" t="n">
+        <v>46082.44312587981</v>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>65c4a910-295a-4f61-9265-7d4137adabdf</t>
+        </is>
+      </c>
+      <c r="B1524" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1524" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1524" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1524" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1524" t="n">
+        <v>442.07</v>
+      </c>
+      <c r="G1524" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="H1524" s="2" t="n">
+        <v>46077.44312588294</v>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>f95a8bcf-3bf1-4449-bcef-894d85f72918</t>
+        </is>
+      </c>
+      <c r="B1525" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1525" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1525" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1525" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1525" t="n">
+        <v>283.07</v>
+      </c>
+      <c r="G1525" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="H1525" s="2" t="n">
+        <v>46074.44312588588</v>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>903e0975-c5bb-4cbc-bd34-5958da4c5476</t>
+        </is>
+      </c>
+      <c r="B1526" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1526" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1526" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1526" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1526" t="n">
+        <v>248.96</v>
+      </c>
+      <c r="G1526" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H1526" s="2" t="n">
+        <v>46078.44312588905</v>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>ad80ecb9-1bf4-4c82-8ed6-b1f9e101e211</t>
+        </is>
+      </c>
+      <c r="B1527" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1527" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1527" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1527" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1527" t="n">
+        <v>115.28</v>
+      </c>
+      <c r="G1527" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H1527" s="2" t="n">
+        <v>46067.44312589245</v>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>f0239146-558d-4c14-9514-6d11280b4e2a</t>
+        </is>
+      </c>
+      <c r="B1528" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1528" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1528" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1528" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1528" t="n">
+        <v>361.37</v>
+      </c>
+      <c r="G1528" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="H1528" s="2" t="n">
+        <v>46085.4431258955</v>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>2ad03e7e-04c9-486c-9845-fe18c3002cf8</t>
+        </is>
+      </c>
+      <c r="B1529" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1529" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1529" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1529" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1529" t="n">
+        <v>200.05</v>
+      </c>
+      <c r="G1529" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1529" s="2" t="n">
+        <v>46092.44312589856</v>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>64e76db7-cbdb-4080-9529-edd682f22665</t>
+        </is>
+      </c>
+      <c r="B1530" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1530" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1530" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1530" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1530" t="n">
+        <v>441.93</v>
+      </c>
+      <c r="G1530" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="H1530" s="2" t="n">
+        <v>46067.44312590175</v>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>5cbec4d9-11b0-49c3-85bd-78c356084d53</t>
+        </is>
+      </c>
+      <c r="B1531" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1531" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1531" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1531" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1531" t="n">
+        <v>275.84</v>
+      </c>
+      <c r="G1531" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H1531" s="2" t="n">
+        <v>46086.44312590487</v>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>075238b2-a36b-474f-9705-e6766faac0d5</t>
+        </is>
+      </c>
+      <c r="B1532" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1532" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1532" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1532" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1532" t="n">
+        <v>328.54</v>
+      </c>
+      <c r="G1532" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="H1532" s="2" t="n">
+        <v>46087.44312590811</v>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>a9ea206b-caea-48a4-a271-b220636b24cb</t>
+        </is>
+      </c>
+      <c r="B1533" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1533" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1533" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1533" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1533" t="n">
+        <v>423.05</v>
+      </c>
+      <c r="G1533" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="H1533" s="2" t="n">
+        <v>46071.44312591136</v>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>4805c05d-46f5-458b-b23a-e6b6f52ecf89</t>
+        </is>
+      </c>
+      <c r="B1534" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1534" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1534" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1534" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1534" t="n">
+        <v>498.09</v>
+      </c>
+      <c r="G1534" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="H1534" s="2" t="n">
+        <v>46088.44312591463</v>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>9ea13220-e54c-4951-8e76-d130654c4c37</t>
+        </is>
+      </c>
+      <c r="B1535" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1535" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1535" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1535" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1535" t="n">
+        <v>28.83</v>
+      </c>
+      <c r="G1535" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H1535" s="2" t="n">
+        <v>46088.4431259177</v>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="inlineStr">
+        <is>
+          <t>c1886a20-3adb-4dcd-b1cd-11a253aefda1</t>
+        </is>
+      </c>
+      <c r="B1536" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1536" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1536" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1536" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1536" t="n">
+        <v>294.78</v>
+      </c>
+      <c r="G1536" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="H1536" s="2" t="n">
+        <v>46078.44312592084</v>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="inlineStr">
+        <is>
+          <t>def9ea47-d57e-4c3f-b8f9-38acb7611352</t>
+        </is>
+      </c>
+      <c r="B1537" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1537" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1537" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1537" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1537" t="n">
+        <v>247.88</v>
+      </c>
+      <c r="G1537" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H1537" s="2" t="n">
+        <v>46075.44312592409</v>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t>f6751b24-dd46-4249-bae6-abcf2526741a</t>
+        </is>
+      </c>
+      <c r="B1538" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1538" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1538" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1538" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1538" t="n">
+        <v>339.04</v>
+      </c>
+      <c r="G1538" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="H1538" s="2" t="n">
+        <v>46088.44312592728</v>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t>d24bc756-3716-44b0-aa85-b07557b579c5</t>
+        </is>
+      </c>
+      <c r="B1539" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1539" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1539" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1539" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1539" t="n">
+        <v>47.29</v>
+      </c>
+      <c r="G1539" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H1539" s="2" t="n">
+        <v>46094.44312593054</v>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="inlineStr">
+        <is>
+          <t>28612b0a-bc11-4198-aec4-ad60e16c15cd</t>
+        </is>
+      </c>
+      <c r="B1540" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1540" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1540" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1540" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1540" t="n">
+        <v>310.18</v>
+      </c>
+      <c r="G1540" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H1540" s="2" t="n">
+        <v>46077.44312593353</v>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>1d8d0756-c8d6-4287-82e8-ff4bb3ed804b</t>
+        </is>
+      </c>
+      <c r="B1541" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1541" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1541" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1541" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1541" t="n">
+        <v>136.32</v>
+      </c>
+      <c r="G1541" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H1541" s="2" t="n">
+        <v>46093.44312593693</v>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="inlineStr">
+        <is>
+          <t>388562b1-f2ec-45d3-9a5c-4d989d6a1681</t>
+        </is>
+      </c>
+      <c r="B1542" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1542" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1542" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1542" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1542" t="n">
+        <v>64.43000000000001</v>
+      </c>
+      <c r="G1542" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H1542" s="2" t="n">
+        <v>46077.44312593998</v>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="inlineStr">
+        <is>
+          <t>cb529afb-515f-4ace-b3de-bb143aed65c5</t>
+        </is>
+      </c>
+      <c r="B1543" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1543" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1543" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1543" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1543" t="n">
+        <v>127.96</v>
+      </c>
+      <c r="G1543" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="H1543" s="2" t="n">
+        <v>46086.44312594321</v>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>6708345b-4eaf-4bc0-852d-27808640263e</t>
+        </is>
+      </c>
+      <c r="B1544" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1544" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1544" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1544" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1544" t="n">
+        <v>415.92</v>
+      </c>
+      <c r="G1544" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="H1544" s="2" t="n">
+        <v>46071.44312594632</v>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t>a4a799ab-ceab-44ed-88f2-61159292cede</t>
+        </is>
+      </c>
+      <c r="B1545" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1545" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1545" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1545" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1545" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="G1545" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H1545" s="2" t="n">
+        <v>46076.44312594966</v>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t>789a2e54-11f1-40ab-88d9-5de9af64a414</t>
+        </is>
+      </c>
+      <c r="B1546" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1546" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1546" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1546" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1546" t="n">
+        <v>268.14</v>
+      </c>
+      <c r="G1546" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H1546" s="2" t="n">
+        <v>46082.44312595276</v>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t>0ad01bbe-0572-45f3-8f5e-9bc5640777b7</t>
+        </is>
+      </c>
+      <c r="B1547" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1547" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1547" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1547" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1547" t="n">
+        <v>189.58</v>
+      </c>
+      <c r="G1547" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H1547" s="2" t="n">
+        <v>46073.44312595594</v>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>8c3dd099-3828-4305-96c3-3bbc3f06b2c0</t>
+        </is>
+      </c>
+      <c r="B1548" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1548" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1548" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1548" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1548" t="n">
+        <v>288.75</v>
+      </c>
+      <c r="G1548" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="H1548" s="2" t="n">
+        <v>46095.44312595913</v>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t>e21b025c-9608-45b0-8548-3fd14ae75f2a</t>
+        </is>
+      </c>
+      <c r="B1549" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1549" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1549" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1549" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1549" t="n">
+        <v>157.55</v>
+      </c>
+      <c r="G1549" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H1549" s="2" t="n">
+        <v>46080.44312596234</v>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="inlineStr">
+        <is>
+          <t>043e59f6-65ab-4ca4-bf1a-cfa6f53d27e5</t>
+        </is>
+      </c>
+      <c r="B1550" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1550" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1550" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1550" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1550" t="n">
+        <v>466.39</v>
+      </c>
+      <c r="G1550" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="H1550" s="2" t="n">
+        <v>46092.44312596553</v>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="inlineStr">
+        <is>
+          <t>3522ebf8-6440-454d-85cc-59c762d79052</t>
+        </is>
+      </c>
+      <c r="B1551" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1551" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1551" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1551" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1551" t="n">
+        <v>450.96</v>
+      </c>
+      <c r="G1551" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="H1551" s="2" t="n">
+        <v>46082.44312596863</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1551"/>
+  <dimension ref="A1:H1601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51505,7 +51505,7 @@
         <v>0.37</v>
       </c>
       <c r="H1502" s="2" t="n">
-        <v>46077.44312581167</v>
+        <v>46077.44312581018</v>
       </c>
     </row>
     <row r="1503">
@@ -51539,7 +51539,7 @@
         <v>4.47</v>
       </c>
       <c r="H1503" s="2" t="n">
-        <v>46095.44312581584</v>
+        <v>46095.44312581018</v>
       </c>
     </row>
     <row r="1504">
@@ -51573,7 +51573,7 @@
         <v>3.38</v>
       </c>
       <c r="H1504" s="2" t="n">
-        <v>46083.44312581902</v>
+        <v>46083.44312582176</v>
       </c>
     </row>
     <row r="1505">
@@ -51607,7 +51607,7 @@
         <v>0.66</v>
       </c>
       <c r="H1505" s="2" t="n">
-        <v>46090.44312582257</v>
+        <v>46090.44312582176</v>
       </c>
     </row>
     <row r="1506">
@@ -51641,7 +51641,7 @@
         <v>4.72</v>
       </c>
       <c r="H1506" s="2" t="n">
-        <v>46077.44312582564</v>
+        <v>46077.44312582176</v>
       </c>
     </row>
     <row r="1507">
@@ -51675,7 +51675,7 @@
         <v>4.42</v>
       </c>
       <c r="H1507" s="2" t="n">
-        <v>46070.44312582895</v>
+        <v>46070.44312583334</v>
       </c>
     </row>
     <row r="1508">
@@ -51709,7 +51709,7 @@
         <v>4.36</v>
       </c>
       <c r="H1508" s="2" t="n">
-        <v>46082.4431258322</v>
+        <v>46082.44312583334</v>
       </c>
     </row>
     <row r="1509">
@@ -51743,7 +51743,7 @@
         <v>0.03</v>
       </c>
       <c r="H1509" s="2" t="n">
-        <v>46088.4431258353</v>
+        <v>46088.44312583334</v>
       </c>
     </row>
     <row r="1510">
@@ -51777,7 +51777,7 @@
         <v>2.77</v>
       </c>
       <c r="H1510" s="2" t="n">
-        <v>46079.44312583853</v>
+        <v>46079.44312583334</v>
       </c>
     </row>
     <row r="1511">
@@ -51811,7 +51811,7 @@
         <v>0.05</v>
       </c>
       <c r="H1511" s="2" t="n">
-        <v>46079.44312584171</v>
+        <v>46079.4431258449</v>
       </c>
     </row>
     <row r="1512">
@@ -51845,7 +51845,7 @@
         <v>2.8</v>
       </c>
       <c r="H1512" s="2" t="n">
-        <v>46084.44312584502</v>
+        <v>46084.4431258449</v>
       </c>
     </row>
     <row r="1513">
@@ -51879,7 +51879,7 @@
         <v>0.53</v>
       </c>
       <c r="H1513" s="2" t="n">
-        <v>46071.44312584821</v>
+        <v>46071.4431258449</v>
       </c>
     </row>
     <row r="1514">
@@ -51913,7 +51913,7 @@
         <v>4.67</v>
       </c>
       <c r="H1514" s="2" t="n">
-        <v>46086.44312585129</v>
+        <v>46086.44312585648</v>
       </c>
     </row>
     <row r="1515">
@@ -51947,7 +51947,7 @@
         <v>2.79</v>
       </c>
       <c r="H1515" s="2" t="n">
-        <v>46066.44312585449</v>
+        <v>46066.44312585648</v>
       </c>
     </row>
     <row r="1516">
@@ -51981,7 +51981,7 @@
         <v>0.14</v>
       </c>
       <c r="H1516" s="2" t="n">
-        <v>46094.44312585783</v>
+        <v>46094.44312585648</v>
       </c>
     </row>
     <row r="1517">
@@ -52015,7 +52015,7 @@
         <v>1.56</v>
       </c>
       <c r="H1517" s="2" t="n">
-        <v>46070.44312586108</v>
+        <v>46070.44312585648</v>
       </c>
     </row>
     <row r="1518">
@@ -52049,7 +52049,7 @@
         <v>2.94</v>
       </c>
       <c r="H1518" s="2" t="n">
-        <v>46073.44312586416</v>
+        <v>46073.44312586806</v>
       </c>
     </row>
     <row r="1519">
@@ -52083,7 +52083,7 @@
         <v>3.77</v>
       </c>
       <c r="H1519" s="2" t="n">
-        <v>46073.44312586734</v>
+        <v>46073.44312586806</v>
       </c>
     </row>
     <row r="1520">
@@ -52117,7 +52117,7 @@
         <v>0.57</v>
       </c>
       <c r="H1520" s="2" t="n">
-        <v>46070.44312587047</v>
+        <v>46070.44312586806</v>
       </c>
     </row>
     <row r="1521">
@@ -52151,7 +52151,7 @@
         <v>2.54</v>
       </c>
       <c r="H1521" s="2" t="n">
-        <v>46072.44312587352</v>
+        <v>46072.44312586806</v>
       </c>
     </row>
     <row r="1522">
@@ -52185,7 +52185,7 @@
         <v>2.33</v>
       </c>
       <c r="H1522" s="2" t="n">
-        <v>46095.44312587656</v>
+        <v>46095.44312587963</v>
       </c>
     </row>
     <row r="1523">
@@ -52219,7 +52219,7 @@
         <v>1.23</v>
       </c>
       <c r="H1523" s="2" t="n">
-        <v>46082.44312587981</v>
+        <v>46082.44312587963</v>
       </c>
     </row>
     <row r="1524">
@@ -52253,7 +52253,7 @@
         <v>4.42</v>
       </c>
       <c r="H1524" s="2" t="n">
-        <v>46077.44312588294</v>
+        <v>46077.44312587963</v>
       </c>
     </row>
     <row r="1525">
@@ -52287,7 +52287,7 @@
         <v>2.83</v>
       </c>
       <c r="H1525" s="2" t="n">
-        <v>46074.44312588588</v>
+        <v>46074.4431258912</v>
       </c>
     </row>
     <row r="1526">
@@ -52321,7 +52321,7 @@
         <v>2.49</v>
       </c>
       <c r="H1526" s="2" t="n">
-        <v>46078.44312588905</v>
+        <v>46078.4431258912</v>
       </c>
     </row>
     <row r="1527">
@@ -52355,7 +52355,7 @@
         <v>1.15</v>
       </c>
       <c r="H1527" s="2" t="n">
-        <v>46067.44312589245</v>
+        <v>46067.4431258912</v>
       </c>
     </row>
     <row r="1528">
@@ -52389,7 +52389,7 @@
         <v>3.61</v>
       </c>
       <c r="H1528" s="2" t="n">
-        <v>46085.4431258955</v>
+        <v>46085.4431258912</v>
       </c>
     </row>
     <row r="1529">
@@ -52423,7 +52423,7 @@
         <v>2</v>
       </c>
       <c r="H1529" s="2" t="n">
-        <v>46092.44312589856</v>
+        <v>46092.44312590278</v>
       </c>
     </row>
     <row r="1530">
@@ -52457,7 +52457,7 @@
         <v>4.42</v>
       </c>
       <c r="H1530" s="2" t="n">
-        <v>46067.44312590175</v>
+        <v>46067.44312590278</v>
       </c>
     </row>
     <row r="1531">
@@ -52491,7 +52491,7 @@
         <v>2.76</v>
       </c>
       <c r="H1531" s="2" t="n">
-        <v>46086.44312590487</v>
+        <v>46086.44312590278</v>
       </c>
     </row>
     <row r="1532">
@@ -52525,7 +52525,7 @@
         <v>3.29</v>
       </c>
       <c r="H1532" s="2" t="n">
-        <v>46087.44312590811</v>
+        <v>46087.44312590278</v>
       </c>
     </row>
     <row r="1533">
@@ -52559,7 +52559,7 @@
         <v>4.23</v>
       </c>
       <c r="H1533" s="2" t="n">
-        <v>46071.44312591136</v>
+        <v>46071.44312591435</v>
       </c>
     </row>
     <row r="1534">
@@ -52593,7 +52593,7 @@
         <v>4.98</v>
       </c>
       <c r="H1534" s="2" t="n">
-        <v>46088.44312591463</v>
+        <v>46088.44312591435</v>
       </c>
     </row>
     <row r="1535">
@@ -52627,7 +52627,7 @@
         <v>0.29</v>
       </c>
       <c r="H1535" s="2" t="n">
-        <v>46088.4431259177</v>
+        <v>46088.44312591435</v>
       </c>
     </row>
     <row r="1536">
@@ -52661,7 +52661,7 @@
         <v>2.95</v>
       </c>
       <c r="H1536" s="2" t="n">
-        <v>46078.44312592084</v>
+        <v>46078.44312592593</v>
       </c>
     </row>
     <row r="1537">
@@ -52695,7 +52695,7 @@
         <v>2.48</v>
       </c>
       <c r="H1537" s="2" t="n">
-        <v>46075.44312592409</v>
+        <v>46075.44312592593</v>
       </c>
     </row>
     <row r="1538">
@@ -52729,7 +52729,7 @@
         <v>3.39</v>
       </c>
       <c r="H1538" s="2" t="n">
-        <v>46088.44312592728</v>
+        <v>46088.44312592593</v>
       </c>
     </row>
     <row r="1539">
@@ -52763,7 +52763,7 @@
         <v>0.47</v>
       </c>
       <c r="H1539" s="2" t="n">
-        <v>46094.44312593054</v>
+        <v>46094.44312592593</v>
       </c>
     </row>
     <row r="1540">
@@ -52797,7 +52797,7 @@
         <v>3.1</v>
       </c>
       <c r="H1540" s="2" t="n">
-        <v>46077.44312593353</v>
+        <v>46077.4431259375</v>
       </c>
     </row>
     <row r="1541">
@@ -52831,7 +52831,7 @@
         <v>1.36</v>
       </c>
       <c r="H1541" s="2" t="n">
-        <v>46093.44312593693</v>
+        <v>46093.4431259375</v>
       </c>
     </row>
     <row r="1542">
@@ -52865,7 +52865,7 @@
         <v>0.64</v>
       </c>
       <c r="H1542" s="2" t="n">
-        <v>46077.44312593998</v>
+        <v>46077.4431259375</v>
       </c>
     </row>
     <row r="1543">
@@ -52899,7 +52899,7 @@
         <v>1.28</v>
       </c>
       <c r="H1543" s="2" t="n">
-        <v>46086.44312594321</v>
+        <v>46086.4431259375</v>
       </c>
     </row>
     <row r="1544">
@@ -52933,7 +52933,7 @@
         <v>4.16</v>
       </c>
       <c r="H1544" s="2" t="n">
-        <v>46071.44312594632</v>
+        <v>46071.44312594907</v>
       </c>
     </row>
     <row r="1545">
@@ -52967,7 +52967,7 @@
         <v>0.22</v>
       </c>
       <c r="H1545" s="2" t="n">
-        <v>46076.44312594966</v>
+        <v>46076.44312594907</v>
       </c>
     </row>
     <row r="1546">
@@ -53001,7 +53001,7 @@
         <v>2.68</v>
       </c>
       <c r="H1546" s="2" t="n">
-        <v>46082.44312595276</v>
+        <v>46082.44312594907</v>
       </c>
     </row>
     <row r="1547">
@@ -53035,7 +53035,7 @@
         <v>1.9</v>
       </c>
       <c r="H1547" s="2" t="n">
-        <v>46073.44312595594</v>
+        <v>46073.44312596065</v>
       </c>
     </row>
     <row r="1548">
@@ -53069,7 +53069,7 @@
         <v>2.89</v>
       </c>
       <c r="H1548" s="2" t="n">
-        <v>46095.44312595913</v>
+        <v>46095.44312596065</v>
       </c>
     </row>
     <row r="1549">
@@ -53103,7 +53103,7 @@
         <v>1.58</v>
       </c>
       <c r="H1549" s="2" t="n">
-        <v>46080.44312596234</v>
+        <v>46080.44312596065</v>
       </c>
     </row>
     <row r="1550">
@@ -53137,7 +53137,7 @@
         <v>4.66</v>
       </c>
       <c r="H1550" s="2" t="n">
-        <v>46092.44312596553</v>
+        <v>46092.44312596065</v>
       </c>
     </row>
     <row r="1551">
@@ -53171,7 +53171,1707 @@
         <v>4.51</v>
       </c>
       <c r="H1551" s="2" t="n">
-        <v>46082.44312596863</v>
+        <v>46082.44312597222</v>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="inlineStr">
+        <is>
+          <t>82a04c67-3eb9-4673-88bf-14fe0b9482d0</t>
+        </is>
+      </c>
+      <c r="B1552" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1552" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1552" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1552" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1552" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="G1552" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H1552" s="2" t="n">
+        <v>46069.47898272161</v>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t>bc321edc-229c-4a48-8a7a-7ccdfa5dae42</t>
+        </is>
+      </c>
+      <c r="B1553" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1553" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1553" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1553" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1553" t="n">
+        <v>203.78</v>
+      </c>
+      <c r="G1553" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H1553" s="2" t="n">
+        <v>46078.47898272613</v>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>74242ec0-3458-4f01-b43e-6361481a7820</t>
+        </is>
+      </c>
+      <c r="B1554" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1554" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1554" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1554" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1554" t="n">
+        <v>165.33</v>
+      </c>
+      <c r="G1554" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H1554" s="2" t="n">
+        <v>46078.47898272962</v>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>6a15ed7f-1488-43dc-9bcd-f89dc4094bb7</t>
+        </is>
+      </c>
+      <c r="B1555" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1555" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1555" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1555" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1555" t="n">
+        <v>395.66</v>
+      </c>
+      <c r="G1555" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="H1555" s="2" t="n">
+        <v>46083.47898273277</v>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>dd7074f7-f55f-499a-9a38-baebcd56a308</t>
+        </is>
+      </c>
+      <c r="B1556" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1556" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1556" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1556" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1556" t="n">
+        <v>359.46</v>
+      </c>
+      <c r="G1556" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="H1556" s="2" t="n">
+        <v>46088.47898273618</v>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t>719684b9-50eb-4921-8d7d-df59fbf67eb1</t>
+        </is>
+      </c>
+      <c r="B1557" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1557" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1557" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1557" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1557" t="n">
+        <v>443.86</v>
+      </c>
+      <c r="G1557" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="H1557" s="2" t="n">
+        <v>46075.47898273928</v>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="inlineStr">
+        <is>
+          <t>61bc4fe3-444b-4de9-8927-f46d060dd889</t>
+        </is>
+      </c>
+      <c r="B1558" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1558" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1558" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1558" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1558" t="n">
+        <v>223.31</v>
+      </c>
+      <c r="G1558" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H1558" s="2" t="n">
+        <v>46095.47898274247</v>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t>2edebf3a-a0bc-471d-a3d7-6cc9e69b978a</t>
+        </is>
+      </c>
+      <c r="B1559" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1559" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1559" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1559" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1559" t="n">
+        <v>43.68</v>
+      </c>
+      <c r="G1559" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H1559" s="2" t="n">
+        <v>46087.47898274573</v>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t>fcf166d5-2662-4fa3-afee-125d1ccc8631</t>
+        </is>
+      </c>
+      <c r="B1560" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1560" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1560" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1560" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1560" t="n">
+        <v>485.89</v>
+      </c>
+      <c r="G1560" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="H1560" s="2" t="n">
+        <v>46069.47898274883</v>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="inlineStr">
+        <is>
+          <t>e86d0ec7-ac06-486c-82e6-690e23bef1ea</t>
+        </is>
+      </c>
+      <c r="B1561" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1561" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1561" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1561" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1561" t="n">
+        <v>405.61</v>
+      </c>
+      <c r="G1561" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="H1561" s="2" t="n">
+        <v>46081.47898275188</v>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="inlineStr">
+        <is>
+          <t>0764d7a0-740e-4595-b8f4-a312b615c481</t>
+        </is>
+      </c>
+      <c r="B1562" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1562" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1562" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1562" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1562" t="n">
+        <v>297.67</v>
+      </c>
+      <c r="G1562" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H1562" s="2" t="n">
+        <v>46075.47898275507</v>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="inlineStr">
+        <is>
+          <t>cf4be5de-aebb-446f-8587-59dd8f0af58f</t>
+        </is>
+      </c>
+      <c r="B1563" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1563" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1563" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1563" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1563" t="n">
+        <v>142.83</v>
+      </c>
+      <c r="G1563" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H1563" s="2" t="n">
+        <v>46084.4789827586</v>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="inlineStr">
+        <is>
+          <t>3947e43a-1719-4984-8e3b-590345bee770</t>
+        </is>
+      </c>
+      <c r="B1564" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1564" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1564" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1564" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1564" t="n">
+        <v>297.96</v>
+      </c>
+      <c r="G1564" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H1564" s="2" t="n">
+        <v>46084.4789827617</v>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="inlineStr">
+        <is>
+          <t>a31213b1-2755-4cf7-941b-a941ea08f7eb</t>
+        </is>
+      </c>
+      <c r="B1565" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1565" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1565" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1565" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1565" t="n">
+        <v>412.39</v>
+      </c>
+      <c r="G1565" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="H1565" s="2" t="n">
+        <v>46075.47898276475</v>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="inlineStr">
+        <is>
+          <t>193650e0-91a8-4f3c-be49-a665fdab8769</t>
+        </is>
+      </c>
+      <c r="B1566" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1566" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1566" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1566" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1566" t="n">
+        <v>91.29000000000001</v>
+      </c>
+      <c r="G1566" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H1566" s="2" t="n">
+        <v>46068.47898276781</v>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="inlineStr">
+        <is>
+          <t>720bc1c3-dad2-4482-9965-ca1e6c36cea1</t>
+        </is>
+      </c>
+      <c r="B1567" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1567" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1567" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1567" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1567" t="n">
+        <v>380.35</v>
+      </c>
+      <c r="G1567" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H1567" s="2" t="n">
+        <v>46080.47898277108</v>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="inlineStr">
+        <is>
+          <t>4d458f3a-1eb5-4cd7-9a97-e5c9c55b53b3</t>
+        </is>
+      </c>
+      <c r="B1568" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1568" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1568" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1568" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1568" t="n">
+        <v>448.97</v>
+      </c>
+      <c r="G1568" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="H1568" s="2" t="n">
+        <v>46077.47898277417</v>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="inlineStr">
+        <is>
+          <t>082aafa9-f9b3-4446-ab72-679767d04d66</t>
+        </is>
+      </c>
+      <c r="B1569" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1569" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1569" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1569" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1569" t="n">
+        <v>428.74</v>
+      </c>
+      <c r="G1569" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="H1569" s="2" t="n">
+        <v>46088.47898277719</v>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="inlineStr">
+        <is>
+          <t>1c7f08a8-3072-425e-b5bf-5ff9fd546ad6</t>
+        </is>
+      </c>
+      <c r="B1570" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1570" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1570" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1570" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1570" t="n">
+        <v>475.84</v>
+      </c>
+      <c r="G1570" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="H1570" s="2" t="n">
+        <v>46071.4789827807</v>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="inlineStr">
+        <is>
+          <t>7d5d970d-04cd-46e0-9ff8-4d554d8dd0ad</t>
+        </is>
+      </c>
+      <c r="B1571" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1571" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1571" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1571" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1571" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="G1571" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H1571" s="2" t="n">
+        <v>46074.47898278375</v>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="inlineStr">
+        <is>
+          <t>f93b9637-5fe6-44bd-b6a6-6e35bb967566</t>
+        </is>
+      </c>
+      <c r="B1572" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1572" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1572" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1572" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1572" t="n">
+        <v>299.19</v>
+      </c>
+      <c r="G1572" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H1572" s="2" t="n">
+        <v>46072.47898278677</v>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="inlineStr">
+        <is>
+          <t>2283e264-2c0c-4706-84bf-a0f47e6d5822</t>
+        </is>
+      </c>
+      <c r="B1573" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1573" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1573" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1573" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1573" t="n">
+        <v>492.46</v>
+      </c>
+      <c r="G1573" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="H1573" s="2" t="n">
+        <v>46074.47898278983</v>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="inlineStr">
+        <is>
+          <t>16d47716-e177-4925-85d6-3e3b3b47f9e5</t>
+        </is>
+      </c>
+      <c r="B1574" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1574" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1574" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1574" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1574" t="n">
+        <v>35.08</v>
+      </c>
+      <c r="G1574" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H1574" s="2" t="n">
+        <v>46083.47898279308</v>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="inlineStr">
+        <is>
+          <t>502664f9-7266-48cd-90d2-f3367666cbc8</t>
+        </is>
+      </c>
+      <c r="B1575" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1575" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1575" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1575" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1575" t="n">
+        <v>100.73</v>
+      </c>
+      <c r="G1575" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="H1575" s="2" t="n">
+        <v>46078.47898279614</v>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="inlineStr">
+        <is>
+          <t>8332fc06-6930-41a0-8cd7-e905465ad935</t>
+        </is>
+      </c>
+      <c r="B1576" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1576" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1576" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1576" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1576" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="G1576" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H1576" s="2" t="n">
+        <v>46075.47898279929</v>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="inlineStr">
+        <is>
+          <t>3d27dd1a-a56c-44c2-93ed-e25c132aba62</t>
+        </is>
+      </c>
+      <c r="B1577" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1577" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1577" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1577" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1577" t="n">
+        <v>63.65</v>
+      </c>
+      <c r="G1577" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H1577" s="2" t="n">
+        <v>46088.47898280239</v>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="inlineStr">
+        <is>
+          <t>eeb6d8a2-aca3-457c-b5a4-c9dc228e6bcb</t>
+        </is>
+      </c>
+      <c r="B1578" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1578" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1578" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1578" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1578" t="n">
+        <v>217.03</v>
+      </c>
+      <c r="G1578" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="H1578" s="2" t="n">
+        <v>46076.47898280567</v>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr">
+        <is>
+          <t>e9d3dd75-88ee-4c15-98bf-2aa2dfcdd8a9</t>
+        </is>
+      </c>
+      <c r="B1579" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1579" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1579" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1579" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1579" t="n">
+        <v>178.22</v>
+      </c>
+      <c r="G1579" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H1579" s="2" t="n">
+        <v>46095.47898280869</v>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr">
+        <is>
+          <t>738cf86d-19ef-474a-81f0-90e94185d453</t>
+        </is>
+      </c>
+      <c r="B1580" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1580" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1580" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1580" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1580" t="n">
+        <v>205.74</v>
+      </c>
+      <c r="G1580" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H1580" s="2" t="n">
+        <v>46095.47898281184</v>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="inlineStr">
+        <is>
+          <t>5290939c-4ef1-4dec-b2fd-79ecd4a0c8f4</t>
+        </is>
+      </c>
+      <c r="B1581" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1581" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1581" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1581" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1581" t="n">
+        <v>170.9</v>
+      </c>
+      <c r="G1581" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H1581" s="2" t="n">
+        <v>46072.47898281505</v>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="inlineStr">
+        <is>
+          <t>84793907-d425-4b5f-84e1-58f5fec4d756</t>
+        </is>
+      </c>
+      <c r="B1582" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1582" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1582" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1582" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1582" t="n">
+        <v>381.19</v>
+      </c>
+      <c r="G1582" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="H1582" s="2" t="n">
+        <v>46081.47898281834</v>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="inlineStr">
+        <is>
+          <t>c9e2e540-1006-48f0-936a-c96df820744d</t>
+        </is>
+      </c>
+      <c r="B1583" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1583" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1583" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1583" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1583" t="n">
+        <v>346.93</v>
+      </c>
+      <c r="G1583" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="H1583" s="2" t="n">
+        <v>46086.47898282131</v>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="inlineStr">
+        <is>
+          <t>b91551f5-2bd3-4247-9bfc-33cd1149855d</t>
+        </is>
+      </c>
+      <c r="B1584" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1584" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1584" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1584" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1584" t="n">
+        <v>255.07</v>
+      </c>
+      <c r="G1584" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H1584" s="2" t="n">
+        <v>46076.47898282449</v>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="inlineStr">
+        <is>
+          <t>8b635b57-5a39-4409-85a4-930bcbe379bc</t>
+        </is>
+      </c>
+      <c r="B1585" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1585" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1585" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1585" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1585" t="n">
+        <v>342.69</v>
+      </c>
+      <c r="G1585" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="H1585" s="2" t="n">
+        <v>46086.47898282779</v>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="inlineStr">
+        <is>
+          <t>96139e9b-077f-40a8-85ae-3e5a5b8a6d9e</t>
+        </is>
+      </c>
+      <c r="B1586" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1586" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1586" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1586" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1586" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="G1586" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H1586" s="2" t="n">
+        <v>46088.47898283097</v>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="inlineStr">
+        <is>
+          <t>28baa84b-0ac2-4aea-aa21-2e15271c2448</t>
+        </is>
+      </c>
+      <c r="B1587" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1587" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1587" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1587" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1587" t="n">
+        <v>101.77</v>
+      </c>
+      <c r="G1587" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H1587" s="2" t="n">
+        <v>46073.47898283407</v>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="inlineStr">
+        <is>
+          <t>b32bc3c0-6835-47dd-aaac-ba5a8e64d1b6</t>
+        </is>
+      </c>
+      <c r="B1588" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1588" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1588" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1588" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1588" t="n">
+        <v>441.65</v>
+      </c>
+      <c r="G1588" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="H1588" s="2" t="n">
+        <v>46088.47898283718</v>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="inlineStr">
+        <is>
+          <t>ec72b444-4f6f-4213-ba14-fae0813369f7</t>
+        </is>
+      </c>
+      <c r="B1589" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1589" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1589" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1589" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1589" t="n">
+        <v>389.58</v>
+      </c>
+      <c r="G1589" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H1589" s="2" t="n">
+        <v>46070.47898284043</v>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="inlineStr">
+        <is>
+          <t>a96c54e6-05b1-41e9-b2a2-af1197dfb230</t>
+        </is>
+      </c>
+      <c r="B1590" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1590" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1590" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1590" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1590" t="n">
+        <v>178.14</v>
+      </c>
+      <c r="G1590" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H1590" s="2" t="n">
+        <v>46076.47898284357</v>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="inlineStr">
+        <is>
+          <t>0891ead1-2926-4a13-b395-b43c4eb0f483</t>
+        </is>
+      </c>
+      <c r="B1591" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1591" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1591" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1591" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1591" t="n">
+        <v>303.73</v>
+      </c>
+      <c r="G1591" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="H1591" s="2" t="n">
+        <v>46077.47898284667</v>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="inlineStr">
+        <is>
+          <t>95a0cdad-0d8e-455e-aba0-20fb0e569294</t>
+        </is>
+      </c>
+      <c r="B1592" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1592" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1592" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1592" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1592" t="n">
+        <v>487.16</v>
+      </c>
+      <c r="G1592" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="H1592" s="2" t="n">
+        <v>46081.4789828499</v>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="inlineStr">
+        <is>
+          <t>87009d6e-a488-4d92-8aec-f096f0c3402c</t>
+        </is>
+      </c>
+      <c r="B1593" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1593" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1593" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1593" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1593" t="n">
+        <v>153.99</v>
+      </c>
+      <c r="G1593" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="H1593" s="2" t="n">
+        <v>46086.47898285292</v>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="inlineStr">
+        <is>
+          <t>8dff7b50-f382-49bc-8f61-18e5bb86a257</t>
+        </is>
+      </c>
+      <c r="B1594" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1594" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1594" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1594" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1594" t="n">
+        <v>190.48</v>
+      </c>
+      <c r="G1594" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H1594" s="2" t="n">
+        <v>46073.4789828561</v>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="inlineStr">
+        <is>
+          <t>1797cd90-3237-4bf7-9f2d-930a28ce0af5</t>
+        </is>
+      </c>
+      <c r="B1595" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1595" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1595" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1595" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1595" t="n">
+        <v>82.29000000000001</v>
+      </c>
+      <c r="G1595" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H1595" s="2" t="n">
+        <v>46092.47898285909</v>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="inlineStr">
+        <is>
+          <t>53c97ff1-4f0f-4243-aee9-b8db6686cbc9</t>
+        </is>
+      </c>
+      <c r="B1596" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1596" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1596" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1596" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1596" t="n">
+        <v>128.87</v>
+      </c>
+      <c r="G1596" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H1596" s="2" t="n">
+        <v>46082.47898286287</v>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="inlineStr">
+        <is>
+          <t>13f88061-a8b6-4caf-b9e3-fe48dc8e0eeb</t>
+        </is>
+      </c>
+      <c r="B1597" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1597" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1597" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1597" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1597" t="n">
+        <v>363.72</v>
+      </c>
+      <c r="G1597" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="H1597" s="2" t="n">
+        <v>46084.47898286609</v>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="inlineStr">
+        <is>
+          <t>7fde1eef-84f6-412e-8763-a6e019dc7398</t>
+        </is>
+      </c>
+      <c r="B1598" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1598" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1598" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1598" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1598" t="n">
+        <v>483.17</v>
+      </c>
+      <c r="G1598" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="H1598" s="2" t="n">
+        <v>46094.47898286908</v>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="inlineStr">
+        <is>
+          <t>b022749b-faf7-43aa-ac2d-48ecdd214338</t>
+        </is>
+      </c>
+      <c r="B1599" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1599" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1599" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1599" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1599" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="G1599" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H1599" s="2" t="n">
+        <v>46082.47898287233</v>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="inlineStr">
+        <is>
+          <t>009aab46-bbae-408d-898f-aff157ab4e90</t>
+        </is>
+      </c>
+      <c r="B1600" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1600" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1600" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1600" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1600" t="n">
+        <v>485.78</v>
+      </c>
+      <c r="G1600" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="H1600" s="2" t="n">
+        <v>46081.47898287535</v>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="inlineStr">
+        <is>
+          <t>ac3cb701-ca53-445f-8bb9-7f7ceb1d846d</t>
+        </is>
+      </c>
+      <c r="B1601" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1601" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1601" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1601" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1601" t="n">
+        <v>186.35</v>
+      </c>
+      <c r="G1601" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H1601" s="2" t="n">
+        <v>46089.47898287953</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1601"/>
+  <dimension ref="A1:H1651"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53205,7 +53205,7 @@
         <v>0.18</v>
       </c>
       <c r="H1552" s="2" t="n">
-        <v>46069.47898272161</v>
+        <v>46069.47898271991</v>
       </c>
     </row>
     <row r="1553">
@@ -53239,7 +53239,7 @@
         <v>2.04</v>
       </c>
       <c r="H1553" s="2" t="n">
-        <v>46078.47898272613</v>
+        <v>46078.47898273148</v>
       </c>
     </row>
     <row r="1554">
@@ -53273,7 +53273,7 @@
         <v>1.65</v>
       </c>
       <c r="H1554" s="2" t="n">
-        <v>46078.47898272962</v>
+        <v>46078.47898273148</v>
       </c>
     </row>
     <row r="1555">
@@ -53307,7 +53307,7 @@
         <v>3.96</v>
       </c>
       <c r="H1555" s="2" t="n">
-        <v>46083.47898273277</v>
+        <v>46083.47898273148</v>
       </c>
     </row>
     <row r="1556">
@@ -53341,7 +53341,7 @@
         <v>3.59</v>
       </c>
       <c r="H1556" s="2" t="n">
-        <v>46088.47898273618</v>
+        <v>46088.47898273148</v>
       </c>
     </row>
     <row r="1557">
@@ -53375,7 +53375,7 @@
         <v>4.44</v>
       </c>
       <c r="H1557" s="2" t="n">
-        <v>46075.47898273928</v>
+        <v>46075.47898274306</v>
       </c>
     </row>
     <row r="1558">
@@ -53409,7 +53409,7 @@
         <v>2.23</v>
       </c>
       <c r="H1558" s="2" t="n">
-        <v>46095.47898274247</v>
+        <v>46095.47898274306</v>
       </c>
     </row>
     <row r="1559">
@@ -53443,7 +53443,7 @@
         <v>0.44</v>
       </c>
       <c r="H1559" s="2" t="n">
-        <v>46087.47898274573</v>
+        <v>46087.47898274306</v>
       </c>
     </row>
     <row r="1560">
@@ -53477,7 +53477,7 @@
         <v>4.86</v>
       </c>
       <c r="H1560" s="2" t="n">
-        <v>46069.47898274883</v>
+        <v>46069.47898274306</v>
       </c>
     </row>
     <row r="1561">
@@ -53511,7 +53511,7 @@
         <v>4.06</v>
       </c>
       <c r="H1561" s="2" t="n">
-        <v>46081.47898275188</v>
+        <v>46081.47898275463</v>
       </c>
     </row>
     <row r="1562">
@@ -53545,7 +53545,7 @@
         <v>2.98</v>
       </c>
       <c r="H1562" s="2" t="n">
-        <v>46075.47898275507</v>
+        <v>46075.47898275463</v>
       </c>
     </row>
     <row r="1563">
@@ -53579,7 +53579,7 @@
         <v>1.43</v>
       </c>
       <c r="H1563" s="2" t="n">
-        <v>46084.4789827586</v>
+        <v>46084.47898275463</v>
       </c>
     </row>
     <row r="1564">
@@ -53613,7 +53613,7 @@
         <v>2.98</v>
       </c>
       <c r="H1564" s="2" t="n">
-        <v>46084.4789827617</v>
+        <v>46084.4789827662</v>
       </c>
     </row>
     <row r="1565">
@@ -53647,7 +53647,7 @@
         <v>4.12</v>
       </c>
       <c r="H1565" s="2" t="n">
-        <v>46075.47898276475</v>
+        <v>46075.4789827662</v>
       </c>
     </row>
     <row r="1566">
@@ -53681,7 +53681,7 @@
         <v>0.91</v>
       </c>
       <c r="H1566" s="2" t="n">
-        <v>46068.47898276781</v>
+        <v>46068.4789827662</v>
       </c>
     </row>
     <row r="1567">
@@ -53715,7 +53715,7 @@
         <v>3.8</v>
       </c>
       <c r="H1567" s="2" t="n">
-        <v>46080.47898277108</v>
+        <v>46080.4789827662</v>
       </c>
     </row>
     <row r="1568">
@@ -53749,7 +53749,7 @@
         <v>4.49</v>
       </c>
       <c r="H1568" s="2" t="n">
-        <v>46077.47898277417</v>
+        <v>46077.47898277778</v>
       </c>
     </row>
     <row r="1569">
@@ -53783,7 +53783,7 @@
         <v>4.29</v>
       </c>
       <c r="H1569" s="2" t="n">
-        <v>46088.47898277719</v>
+        <v>46088.47898277778</v>
       </c>
     </row>
     <row r="1570">
@@ -53817,7 +53817,7 @@
         <v>4.76</v>
       </c>
       <c r="H1570" s="2" t="n">
-        <v>46071.4789827807</v>
+        <v>46071.47898277778</v>
       </c>
     </row>
     <row r="1571">
@@ -53851,7 +53851,7 @@
         <v>0.25</v>
       </c>
       <c r="H1571" s="2" t="n">
-        <v>46074.47898278375</v>
+        <v>46074.47898278935</v>
       </c>
     </row>
     <row r="1572">
@@ -53885,7 +53885,7 @@
         <v>2.99</v>
       </c>
       <c r="H1572" s="2" t="n">
-        <v>46072.47898278677</v>
+        <v>46072.47898278935</v>
       </c>
     </row>
     <row r="1573">
@@ -53919,7 +53919,7 @@
         <v>4.92</v>
       </c>
       <c r="H1573" s="2" t="n">
-        <v>46074.47898278983</v>
+        <v>46074.47898278935</v>
       </c>
     </row>
     <row r="1574">
@@ -53953,7 +53953,7 @@
         <v>0.35</v>
       </c>
       <c r="H1574" s="2" t="n">
-        <v>46083.47898279308</v>
+        <v>46083.47898278935</v>
       </c>
     </row>
     <row r="1575">
@@ -53987,7 +53987,7 @@
         <v>1.01</v>
       </c>
       <c r="H1575" s="2" t="n">
-        <v>46078.47898279614</v>
+        <v>46078.47898280092</v>
       </c>
     </row>
     <row r="1576">
@@ -54021,7 +54021,7 @@
         <v>0.28</v>
       </c>
       <c r="H1576" s="2" t="n">
-        <v>46075.47898279929</v>
+        <v>46075.47898280092</v>
       </c>
     </row>
     <row r="1577">
@@ -54055,7 +54055,7 @@
         <v>0.64</v>
       </c>
       <c r="H1577" s="2" t="n">
-        <v>46088.47898280239</v>
+        <v>46088.47898280092</v>
       </c>
     </row>
     <row r="1578">
@@ -54089,7 +54089,7 @@
         <v>2.17</v>
       </c>
       <c r="H1578" s="2" t="n">
-        <v>46076.47898280567</v>
+        <v>46076.47898280092</v>
       </c>
     </row>
     <row r="1579">
@@ -54123,7 +54123,7 @@
         <v>1.78</v>
       </c>
       <c r="H1579" s="2" t="n">
-        <v>46095.47898280869</v>
+        <v>46095.4789828125</v>
       </c>
     </row>
     <row r="1580">
@@ -54157,7 +54157,7 @@
         <v>2.06</v>
       </c>
       <c r="H1580" s="2" t="n">
-        <v>46095.47898281184</v>
+        <v>46095.4789828125</v>
       </c>
     </row>
     <row r="1581">
@@ -54191,7 +54191,7 @@
         <v>1.71</v>
       </c>
       <c r="H1581" s="2" t="n">
-        <v>46072.47898281505</v>
+        <v>46072.4789828125</v>
       </c>
     </row>
     <row r="1582">
@@ -54225,7 +54225,7 @@
         <v>3.81</v>
       </c>
       <c r="H1582" s="2" t="n">
-        <v>46081.47898281834</v>
+        <v>46081.47898282408</v>
       </c>
     </row>
     <row r="1583">
@@ -54259,7 +54259,7 @@
         <v>3.47</v>
       </c>
       <c r="H1583" s="2" t="n">
-        <v>46086.47898282131</v>
+        <v>46086.47898282408</v>
       </c>
     </row>
     <row r="1584">
@@ -54293,7 +54293,7 @@
         <v>2.55</v>
       </c>
       <c r="H1584" s="2" t="n">
-        <v>46076.47898282449</v>
+        <v>46076.47898282408</v>
       </c>
     </row>
     <row r="1585">
@@ -54327,7 +54327,7 @@
         <v>3.43</v>
       </c>
       <c r="H1585" s="2" t="n">
-        <v>46086.47898282779</v>
+        <v>46086.47898282408</v>
       </c>
     </row>
     <row r="1586">
@@ -54361,7 +54361,7 @@
         <v>0.78</v>
       </c>
       <c r="H1586" s="2" t="n">
-        <v>46088.47898283097</v>
+        <v>46088.47898283565</v>
       </c>
     </row>
     <row r="1587">
@@ -54395,7 +54395,7 @@
         <v>1.02</v>
       </c>
       <c r="H1587" s="2" t="n">
-        <v>46073.47898283407</v>
+        <v>46073.47898283565</v>
       </c>
     </row>
     <row r="1588">
@@ -54429,7 +54429,7 @@
         <v>4.42</v>
       </c>
       <c r="H1588" s="2" t="n">
-        <v>46088.47898283718</v>
+        <v>46088.47898283565</v>
       </c>
     </row>
     <row r="1589">
@@ -54463,7 +54463,7 @@
         <v>3.9</v>
       </c>
       <c r="H1589" s="2" t="n">
-        <v>46070.47898284043</v>
+        <v>46070.47898283565</v>
       </c>
     </row>
     <row r="1590">
@@ -54497,7 +54497,7 @@
         <v>1.78</v>
       </c>
       <c r="H1590" s="2" t="n">
-        <v>46076.47898284357</v>
+        <v>46076.47898284722</v>
       </c>
     </row>
     <row r="1591">
@@ -54531,7 +54531,7 @@
         <v>3.04</v>
       </c>
       <c r="H1591" s="2" t="n">
-        <v>46077.47898284667</v>
+        <v>46077.47898284722</v>
       </c>
     </row>
     <row r="1592">
@@ -54565,7 +54565,7 @@
         <v>4.87</v>
       </c>
       <c r="H1592" s="2" t="n">
-        <v>46081.4789828499</v>
+        <v>46081.47898284722</v>
       </c>
     </row>
     <row r="1593">
@@ -54599,7 +54599,7 @@
         <v>1.54</v>
       </c>
       <c r="H1593" s="2" t="n">
-        <v>46086.47898285292</v>
+        <v>46086.47898284722</v>
       </c>
     </row>
     <row r="1594">
@@ -54633,7 +54633,7 @@
         <v>1.9</v>
       </c>
       <c r="H1594" s="2" t="n">
-        <v>46073.4789828561</v>
+        <v>46073.4789828588</v>
       </c>
     </row>
     <row r="1595">
@@ -54667,7 +54667,7 @@
         <v>0.82</v>
       </c>
       <c r="H1595" s="2" t="n">
-        <v>46092.47898285909</v>
+        <v>46092.4789828588</v>
       </c>
     </row>
     <row r="1596">
@@ -54701,7 +54701,7 @@
         <v>1.29</v>
       </c>
       <c r="H1596" s="2" t="n">
-        <v>46082.47898286287</v>
+        <v>46082.4789828588</v>
       </c>
     </row>
     <row r="1597">
@@ -54735,7 +54735,7 @@
         <v>3.64</v>
       </c>
       <c r="H1597" s="2" t="n">
-        <v>46084.47898286609</v>
+        <v>46084.47898287037</v>
       </c>
     </row>
     <row r="1598">
@@ -54769,7 +54769,7 @@
         <v>4.83</v>
       </c>
       <c r="H1598" s="2" t="n">
-        <v>46094.47898286908</v>
+        <v>46094.47898287037</v>
       </c>
     </row>
     <row r="1599">
@@ -54803,7 +54803,7 @@
         <v>0.45</v>
       </c>
       <c r="H1599" s="2" t="n">
-        <v>46082.47898287233</v>
+        <v>46082.47898287037</v>
       </c>
     </row>
     <row r="1600">
@@ -54837,7 +54837,7 @@
         <v>4.86</v>
       </c>
       <c r="H1600" s="2" t="n">
-        <v>46081.47898287535</v>
+        <v>46081.47898287037</v>
       </c>
     </row>
     <row r="1601">
@@ -54871,7 +54871,1707 @@
         <v>1.86</v>
       </c>
       <c r="H1601" s="2" t="n">
-        <v>46089.47898287953</v>
+        <v>46089.47898288194</v>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="inlineStr">
+        <is>
+          <t>ea1ade11-e0de-457b-bd14-dba10e5b8df1</t>
+        </is>
+      </c>
+      <c r="B1602" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1602" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1602" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1602" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1602" t="n">
+        <v>93.53</v>
+      </c>
+      <c r="G1602" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H1602" s="2" t="n">
+        <v>46067.52871142534</v>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="inlineStr">
+        <is>
+          <t>2f64b978-cdb5-4011-805c-affa8505dcc3</t>
+        </is>
+      </c>
+      <c r="B1603" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1603" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1603" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1603" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1603" t="n">
+        <v>146.89</v>
+      </c>
+      <c r="G1603" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H1603" s="2" t="n">
+        <v>46094.52871142949</v>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="inlineStr">
+        <is>
+          <t>f8ebd807-a83d-48ef-922f-350303dc643c</t>
+        </is>
+      </c>
+      <c r="B1604" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1604" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1604" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1604" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1604" t="n">
+        <v>252.67</v>
+      </c>
+      <c r="G1604" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="H1604" s="2" t="n">
+        <v>46087.52871143267</v>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="inlineStr">
+        <is>
+          <t>d2644b10-1e36-4b4c-baea-73611e153056</t>
+        </is>
+      </c>
+      <c r="B1605" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1605" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1605" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1605" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1605" t="n">
+        <v>190.76</v>
+      </c>
+      <c r="G1605" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H1605" s="2" t="n">
+        <v>46088.52871143596</v>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="inlineStr">
+        <is>
+          <t>165c2050-dd0b-4d08-bac7-cd9b837c7876</t>
+        </is>
+      </c>
+      <c r="B1606" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1606" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1606" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1606" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1606" t="n">
+        <v>92.43000000000001</v>
+      </c>
+      <c r="G1606" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H1606" s="2" t="n">
+        <v>46074.52871143886</v>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="inlineStr">
+        <is>
+          <t>2397a646-3569-4429-9221-ca160cf56935</t>
+        </is>
+      </c>
+      <c r="B1607" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1607" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1607" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1607" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1607" t="n">
+        <v>362.22</v>
+      </c>
+      <c r="G1607" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="H1607" s="2" t="n">
+        <v>46079.52871144184</v>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="inlineStr">
+        <is>
+          <t>4ccf7ba1-aab8-4a4f-8072-14e2df78904b</t>
+        </is>
+      </c>
+      <c r="B1608" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1608" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1608" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1608" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1608" t="n">
+        <v>293.88</v>
+      </c>
+      <c r="G1608" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H1608" s="2" t="n">
+        <v>46092.52871144508</v>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="inlineStr">
+        <is>
+          <t>aac7b5b9-d2a6-44af-a9ce-62e197ef6ba1</t>
+        </is>
+      </c>
+      <c r="B1609" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1609" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1609" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1609" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1609" t="n">
+        <v>183.3</v>
+      </c>
+      <c r="G1609" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H1609" s="2" t="n">
+        <v>46090.52871144808</v>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="inlineStr">
+        <is>
+          <t>4a8b5bcc-e2e2-4ae4-b750-f12a8a0403e3</t>
+        </is>
+      </c>
+      <c r="B1610" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1610" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1610" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1610" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1610" t="n">
+        <v>384.84</v>
+      </c>
+      <c r="G1610" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H1610" s="2" t="n">
+        <v>46085.52871145105</v>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="inlineStr">
+        <is>
+          <t>4f444683-952d-4d16-9cbf-471e4f5ea548</t>
+        </is>
+      </c>
+      <c r="B1611" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1611" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1611" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1611" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1611" t="n">
+        <v>96.08</v>
+      </c>
+      <c r="G1611" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H1611" s="2" t="n">
+        <v>46087.52871145396</v>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="inlineStr">
+        <is>
+          <t>c6ef6f80-7d7a-4c78-82ad-cdb3b898be49</t>
+        </is>
+      </c>
+      <c r="B1612" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1612" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1612" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1612" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1612" t="n">
+        <v>495.03</v>
+      </c>
+      <c r="G1612" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="H1612" s="2" t="n">
+        <v>46089.52871145712</v>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="inlineStr">
+        <is>
+          <t>324a63d0-6a77-4c68-b7fc-b0ed62bdf894</t>
+        </is>
+      </c>
+      <c r="B1613" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1613" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1613" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1613" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1613" t="n">
+        <v>292.46</v>
+      </c>
+      <c r="G1613" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H1613" s="2" t="n">
+        <v>46087.52871145992</v>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="inlineStr">
+        <is>
+          <t>b231d7f9-304a-49b2-aa3f-26c8dc5ca713</t>
+        </is>
+      </c>
+      <c r="B1614" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1614" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1614" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1614" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1614" t="n">
+        <v>491.66</v>
+      </c>
+      <c r="G1614" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="H1614" s="2" t="n">
+        <v>46074.52871146292</v>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="inlineStr">
+        <is>
+          <t>51b23182-54fe-408e-b79d-d8a6767491c5</t>
+        </is>
+      </c>
+      <c r="B1615" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1615" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1615" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1615" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1615" t="n">
+        <v>130.06</v>
+      </c>
+      <c r="G1615" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H1615" s="2" t="n">
+        <v>46088.52871146572</v>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="inlineStr">
+        <is>
+          <t>68d2577e-a351-4963-9504-73eed23780b8</t>
+        </is>
+      </c>
+      <c r="B1616" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1616" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1616" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1616" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1616" t="n">
+        <v>171.45</v>
+      </c>
+      <c r="G1616" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H1616" s="2" t="n">
+        <v>46078.5287114687</v>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="inlineStr">
+        <is>
+          <t>5397d209-ec33-4d75-9188-edb617d2a6bd</t>
+        </is>
+      </c>
+      <c r="B1617" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1617" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1617" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1617" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1617" t="n">
+        <v>402.81</v>
+      </c>
+      <c r="G1617" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H1617" s="2" t="n">
+        <v>46074.52871147158</v>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="inlineStr">
+        <is>
+          <t>00a450c1-b452-49f8-8ffd-44980fbab741</t>
+        </is>
+      </c>
+      <c r="B1618" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1618" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1618" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1618" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1618" t="n">
+        <v>67.83</v>
+      </c>
+      <c r="G1618" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H1618" s="2" t="n">
+        <v>46079.52871147444</v>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="inlineStr">
+        <is>
+          <t>e5953e7c-def1-4859-9914-497d9e45a546</t>
+        </is>
+      </c>
+      <c r="B1619" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1619" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1619" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1619" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1619" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G1619" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H1619" s="2" t="n">
+        <v>46070.52871147732</v>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="inlineStr">
+        <is>
+          <t>c8c49300-bf43-48b5-9dd4-c026dffbd8fa</t>
+        </is>
+      </c>
+      <c r="B1620" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1620" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1620" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1620" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1620" t="n">
+        <v>411.6</v>
+      </c>
+      <c r="G1620" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="H1620" s="2" t="n">
+        <v>46081.52871148023</v>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="inlineStr">
+        <is>
+          <t>8d48a831-a3b9-4c65-a364-03f34843c89b</t>
+        </is>
+      </c>
+      <c r="B1621" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1621" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1621" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1621" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1621" t="n">
+        <v>261.39</v>
+      </c>
+      <c r="G1621" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="H1621" s="2" t="n">
+        <v>46071.52871148302</v>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="inlineStr">
+        <is>
+          <t>062773b1-56d2-49db-b88f-9f97350a2fee</t>
+        </is>
+      </c>
+      <c r="B1622" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1622" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1622" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1622" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1622" t="n">
+        <v>428.47</v>
+      </c>
+      <c r="G1622" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="H1622" s="2" t="n">
+        <v>46069.5287114858</v>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="inlineStr">
+        <is>
+          <t>cbac912c-7bac-4388-b743-45016096e1ab</t>
+        </is>
+      </c>
+      <c r="B1623" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1623" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1623" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1623" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1623" t="n">
+        <v>418.77</v>
+      </c>
+      <c r="G1623" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="H1623" s="2" t="n">
+        <v>46093.52871148861</v>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="inlineStr">
+        <is>
+          <t>d021f5b2-c8e6-46cc-b11f-b4a767296329</t>
+        </is>
+      </c>
+      <c r="B1624" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1624" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1624" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1624" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1624" t="n">
+        <v>80.18000000000001</v>
+      </c>
+      <c r="G1624" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H1624" s="2" t="n">
+        <v>46072.52871149177</v>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="inlineStr">
+        <is>
+          <t>749840f1-b431-4b26-9350-71270d4e85be</t>
+        </is>
+      </c>
+      <c r="B1625" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1625" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1625" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1625" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1625" t="n">
+        <v>123.66</v>
+      </c>
+      <c r="G1625" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="H1625" s="2" t="n">
+        <v>46071.52871149458</v>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="inlineStr">
+        <is>
+          <t>235b0eee-0e97-4f9a-8430-ff35d8f66e2a</t>
+        </is>
+      </c>
+      <c r="B1626" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1626" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1626" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1626" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1626" t="n">
+        <v>54.58</v>
+      </c>
+      <c r="G1626" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H1626" s="2" t="n">
+        <v>46072.5287114974</v>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="inlineStr">
+        <is>
+          <t>1c55a946-2bc9-4634-8b87-664eb8bf4a22</t>
+        </is>
+      </c>
+      <c r="B1627" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1627" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1627" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1627" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1627" t="n">
+        <v>40.23</v>
+      </c>
+      <c r="G1627" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H1627" s="2" t="n">
+        <v>46092.52871150037</v>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="inlineStr">
+        <is>
+          <t>c4b2e4f1-5221-44c1-8fe7-fad95537e24c</t>
+        </is>
+      </c>
+      <c r="B1628" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1628" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1628" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1628" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1628" t="n">
+        <v>292.27</v>
+      </c>
+      <c r="G1628" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H1628" s="2" t="n">
+        <v>46080.5287115035</v>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="inlineStr">
+        <is>
+          <t>15d3c483-b65b-46bd-9541-fcf711d1c507</t>
+        </is>
+      </c>
+      <c r="B1629" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1629" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1629" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1629" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1629" t="n">
+        <v>308.11</v>
+      </c>
+      <c r="G1629" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="H1629" s="2" t="n">
+        <v>46093.52871150631</v>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="inlineStr">
+        <is>
+          <t>bfaed988-53d0-48bb-8972-f6cd027f8079</t>
+        </is>
+      </c>
+      <c r="B1630" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1630" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1630" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1630" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1630" t="n">
+        <v>311.25</v>
+      </c>
+      <c r="G1630" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="H1630" s="2" t="n">
+        <v>46083.52871150919</v>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="inlineStr">
+        <is>
+          <t>2938f337-2cc1-4b8b-9a68-34337776f600</t>
+        </is>
+      </c>
+      <c r="B1631" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1631" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1631" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1631" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1631" t="n">
+        <v>243.56</v>
+      </c>
+      <c r="G1631" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H1631" s="2" t="n">
+        <v>46079.52871151223</v>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="inlineStr">
+        <is>
+          <t>9ef9153b-2e51-40d7-b1d4-a64e45d92077</t>
+        </is>
+      </c>
+      <c r="B1632" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1632" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1632" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1632" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1632" t="n">
+        <v>271.6</v>
+      </c>
+      <c r="G1632" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H1632" s="2" t="n">
+        <v>46079.52871151535</v>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="inlineStr">
+        <is>
+          <t>594bc6c5-c9d8-40cd-9c24-17d7a0085ab8</t>
+        </is>
+      </c>
+      <c r="B1633" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1633" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1633" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1633" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1633" t="n">
+        <v>123.72</v>
+      </c>
+      <c r="G1633" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="H1633" s="2" t="n">
+        <v>46094.52871151811</v>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="inlineStr">
+        <is>
+          <t>7977ee2c-bae1-4870-8b16-eef3e094461e</t>
+        </is>
+      </c>
+      <c r="B1634" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1634" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1634" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1634" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1634" t="n">
+        <v>84.42</v>
+      </c>
+      <c r="G1634" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H1634" s="2" t="n">
+        <v>46079.52871152103</v>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="inlineStr">
+        <is>
+          <t>e2e2de27-e4b9-43d0-9ddd-802346c4d403</t>
+        </is>
+      </c>
+      <c r="B1635" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1635" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1635" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1635" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1635" t="n">
+        <v>185.53</v>
+      </c>
+      <c r="G1635" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H1635" s="2" t="n">
+        <v>46075.52871152383</v>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="inlineStr">
+        <is>
+          <t>5e3e0231-2d14-411e-9b47-bca184c4aa5d</t>
+        </is>
+      </c>
+      <c r="B1636" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1636" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1636" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1636" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1636" t="n">
+        <v>465.76</v>
+      </c>
+      <c r="G1636" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="H1636" s="2" t="n">
+        <v>46086.52871152671</v>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="inlineStr">
+        <is>
+          <t>27d2ecc2-69db-4819-b606-b41d0bf486d8</t>
+        </is>
+      </c>
+      <c r="B1637" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1637" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1637" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1637" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1637" t="n">
+        <v>291.97</v>
+      </c>
+      <c r="G1637" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H1637" s="2" t="n">
+        <v>46067.52871152961</v>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="inlineStr">
+        <is>
+          <t>91b3022c-da7f-4b4e-a964-ba8a9a2a95ef</t>
+        </is>
+      </c>
+      <c r="B1638" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1638" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1638" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1638" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1638" t="n">
+        <v>22.24</v>
+      </c>
+      <c r="G1638" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H1638" s="2" t="n">
+        <v>46070.52871153236</v>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="inlineStr">
+        <is>
+          <t>af96b77e-68de-48a0-82dc-fc97c9fe0e3b</t>
+        </is>
+      </c>
+      <c r="B1639" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1639" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1639" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1639" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1639" t="n">
+        <v>79.15000000000001</v>
+      </c>
+      <c r="G1639" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H1639" s="2" t="n">
+        <v>46090.52871153516</v>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="inlineStr">
+        <is>
+          <t>da937882-1298-4b84-b4fc-4964515d2ee7</t>
+        </is>
+      </c>
+      <c r="B1640" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1640" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1640" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1640" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1640" t="n">
+        <v>283.31</v>
+      </c>
+      <c r="G1640" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="H1640" s="2" t="n">
+        <v>46073.52871153837</v>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="inlineStr">
+        <is>
+          <t>ff95a6ca-c245-4299-af48-ed8c1e7d27b0</t>
+        </is>
+      </c>
+      <c r="B1641" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1641" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1641" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1641" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1641" t="n">
+        <v>469.63</v>
+      </c>
+      <c r="G1641" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H1641" s="2" t="n">
+        <v>46079.52871154116</v>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="inlineStr">
+        <is>
+          <t>df7f5860-c639-4c07-aa2a-1ea062c086d4</t>
+        </is>
+      </c>
+      <c r="B1642" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1642" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1642" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1642" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1642" t="n">
+        <v>250.05</v>
+      </c>
+      <c r="G1642" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H1642" s="2" t="n">
+        <v>46074.52871154391</v>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="inlineStr">
+        <is>
+          <t>9c88d087-aae5-4e0b-a32a-c2e7825f72ac</t>
+        </is>
+      </c>
+      <c r="B1643" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1643" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1643" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1643" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1643" t="n">
+        <v>374.13</v>
+      </c>
+      <c r="G1643" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H1643" s="2" t="n">
+        <v>46071.52871154668</v>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="inlineStr">
+        <is>
+          <t>e985b288-8447-478e-9c29-dee339fc3912</t>
+        </is>
+      </c>
+      <c r="B1644" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1644" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1644" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1644" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1644" t="n">
+        <v>93.45999999999999</v>
+      </c>
+      <c r="G1644" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H1644" s="2" t="n">
+        <v>46087.52871154983</v>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="inlineStr">
+        <is>
+          <t>aec046df-5801-45ed-9d71-b6210c999eeb</t>
+        </is>
+      </c>
+      <c r="B1645" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1645" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1645" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1645" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1645" t="n">
+        <v>302.13</v>
+      </c>
+      <c r="G1645" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="H1645" s="2" t="n">
+        <v>46077.52871155273</v>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr">
+        <is>
+          <t>518bf301-5c1c-48a3-b60c-60db3add2b43</t>
+        </is>
+      </c>
+      <c r="B1646" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1646" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1646" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1646" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1646" t="n">
+        <v>143.49</v>
+      </c>
+      <c r="G1646" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H1646" s="2" t="n">
+        <v>46075.52871155555</v>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr">
+        <is>
+          <t>30f5a114-3f55-43c7-8c20-7b493195a827</t>
+        </is>
+      </c>
+      <c r="B1647" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1647" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1647" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1647" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1647" t="n">
+        <v>346.39</v>
+      </c>
+      <c r="G1647" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="H1647" s="2" t="n">
+        <v>46071.52871155843</v>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr">
+        <is>
+          <t>859f9a02-9e1c-40da-b029-149d2e1b2c24</t>
+        </is>
+      </c>
+      <c r="B1648" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1648" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1648" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1648" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1648" t="n">
+        <v>353.09</v>
+      </c>
+      <c r="G1648" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="H1648" s="2" t="n">
+        <v>46092.52871156127</v>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr">
+        <is>
+          <t>8c7dcd58-00b9-44fe-b999-e3a10c1a0d40</t>
+        </is>
+      </c>
+      <c r="B1649" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1649" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1649" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1649" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1649" t="n">
+        <v>305.23</v>
+      </c>
+      <c r="G1649" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H1649" s="2" t="n">
+        <v>46081.52871156417</v>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="inlineStr">
+        <is>
+          <t>6c1a0323-a6f9-4d7a-8282-fee59517b9fc</t>
+        </is>
+      </c>
+      <c r="B1650" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1650" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1650" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1650" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1650" t="n">
+        <v>329.45</v>
+      </c>
+      <c r="G1650" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="H1650" s="2" t="n">
+        <v>46089.52871156701</v>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="inlineStr">
+        <is>
+          <t>3db46911-742e-4c93-b385-83fa04a7b668</t>
+        </is>
+      </c>
+      <c r="B1651" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1651" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1651" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1651" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1651" t="n">
+        <v>119.58</v>
+      </c>
+      <c r="G1651" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H1651" s="2" t="n">
+        <v>46067.5287115698</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1651"/>
+  <dimension ref="A1:H1701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54905,7 +54905,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="H1602" s="2" t="n">
-        <v>46067.52871142534</v>
+        <v>46067.52871142361</v>
       </c>
     </row>
     <row r="1603">
@@ -54939,7 +54939,7 @@
         <v>1.47</v>
       </c>
       <c r="H1603" s="2" t="n">
-        <v>46094.52871142949</v>
+        <v>46094.52871143519</v>
       </c>
     </row>
     <row r="1604">
@@ -54973,7 +54973,7 @@
         <v>2.53</v>
       </c>
       <c r="H1604" s="2" t="n">
-        <v>46087.52871143267</v>
+        <v>46087.52871143519</v>
       </c>
     </row>
     <row r="1605">
@@ -55007,7 +55007,7 @@
         <v>1.91</v>
       </c>
       <c r="H1605" s="2" t="n">
-        <v>46088.52871143596</v>
+        <v>46088.52871143519</v>
       </c>
     </row>
     <row r="1606">
@@ -55041,7 +55041,7 @@
         <v>0.92</v>
       </c>
       <c r="H1606" s="2" t="n">
-        <v>46074.52871143886</v>
+        <v>46074.52871143519</v>
       </c>
     </row>
     <row r="1607">
@@ -55075,7 +55075,7 @@
         <v>3.62</v>
       </c>
       <c r="H1607" s="2" t="n">
-        <v>46079.52871144184</v>
+        <v>46079.52871144676</v>
       </c>
     </row>
     <row r="1608">
@@ -55109,7 +55109,7 @@
         <v>2.94</v>
       </c>
       <c r="H1608" s="2" t="n">
-        <v>46092.52871144508</v>
+        <v>46092.52871144676</v>
       </c>
     </row>
     <row r="1609">
@@ -55143,7 +55143,7 @@
         <v>1.83</v>
       </c>
       <c r="H1609" s="2" t="n">
-        <v>46090.52871144808</v>
+        <v>46090.52871144676</v>
       </c>
     </row>
     <row r="1610">
@@ -55177,7 +55177,7 @@
         <v>3.85</v>
       </c>
       <c r="H1610" s="2" t="n">
-        <v>46085.52871145105</v>
+        <v>46085.52871144676</v>
       </c>
     </row>
     <row r="1611">
@@ -55211,7 +55211,7 @@
         <v>0.96</v>
       </c>
       <c r="H1611" s="2" t="n">
-        <v>46087.52871145396</v>
+        <v>46087.52871145833</v>
       </c>
     </row>
     <row r="1612">
@@ -55245,7 +55245,7 @@
         <v>4.95</v>
       </c>
       <c r="H1612" s="2" t="n">
-        <v>46089.52871145712</v>
+        <v>46089.52871145833</v>
       </c>
     </row>
     <row r="1613">
@@ -55279,7 +55279,7 @@
         <v>2.92</v>
       </c>
       <c r="H1613" s="2" t="n">
-        <v>46087.52871145992</v>
+        <v>46087.52871145833</v>
       </c>
     </row>
     <row r="1614">
@@ -55313,7 +55313,7 @@
         <v>4.92</v>
       </c>
       <c r="H1614" s="2" t="n">
-        <v>46074.52871146292</v>
+        <v>46074.52871145833</v>
       </c>
     </row>
     <row r="1615">
@@ -55347,7 +55347,7 @@
         <v>1.3</v>
       </c>
       <c r="H1615" s="2" t="n">
-        <v>46088.52871146572</v>
+        <v>46088.52871146991</v>
       </c>
     </row>
     <row r="1616">
@@ -55381,7 +55381,7 @@
         <v>1.71</v>
       </c>
       <c r="H1616" s="2" t="n">
-        <v>46078.5287114687</v>
+        <v>46078.52871146991</v>
       </c>
     </row>
     <row r="1617">
@@ -55415,7 +55415,7 @@
         <v>4.03</v>
       </c>
       <c r="H1617" s="2" t="n">
-        <v>46074.52871147158</v>
+        <v>46074.52871146991</v>
       </c>
     </row>
     <row r="1618">
@@ -55449,7 +55449,7 @@
         <v>0.68</v>
       </c>
       <c r="H1618" s="2" t="n">
-        <v>46079.52871147444</v>
+        <v>46079.52871146991</v>
       </c>
     </row>
     <row r="1619">
@@ -55483,7 +55483,7 @@
         <v>0.02</v>
       </c>
       <c r="H1619" s="2" t="n">
-        <v>46070.52871147732</v>
+        <v>46070.52871148148</v>
       </c>
     </row>
     <row r="1620">
@@ -55517,7 +55517,7 @@
         <v>4.12</v>
       </c>
       <c r="H1620" s="2" t="n">
-        <v>46081.52871148023</v>
+        <v>46081.52871148148</v>
       </c>
     </row>
     <row r="1621">
@@ -55551,7 +55551,7 @@
         <v>2.61</v>
       </c>
       <c r="H1621" s="2" t="n">
-        <v>46071.52871148302</v>
+        <v>46071.52871148148</v>
       </c>
     </row>
     <row r="1622">
@@ -55585,7 +55585,7 @@
         <v>4.28</v>
       </c>
       <c r="H1622" s="2" t="n">
-        <v>46069.5287114858</v>
+        <v>46069.52871148148</v>
       </c>
     </row>
     <row r="1623">
@@ -55619,7 +55619,7 @@
         <v>4.19</v>
       </c>
       <c r="H1623" s="2" t="n">
-        <v>46093.52871148861</v>
+        <v>46093.52871149305</v>
       </c>
     </row>
     <row r="1624">
@@ -55653,7 +55653,7 @@
         <v>0.8</v>
       </c>
       <c r="H1624" s="2" t="n">
-        <v>46072.52871149177</v>
+        <v>46072.52871149305</v>
       </c>
     </row>
     <row r="1625">
@@ -55687,7 +55687,7 @@
         <v>1.24</v>
       </c>
       <c r="H1625" s="2" t="n">
-        <v>46071.52871149458</v>
+        <v>46071.52871149305</v>
       </c>
     </row>
     <row r="1626">
@@ -55721,7 +55721,7 @@
         <v>0.55</v>
       </c>
       <c r="H1626" s="2" t="n">
-        <v>46072.5287114974</v>
+        <v>46072.52871149305</v>
       </c>
     </row>
     <row r="1627">
@@ -55755,7 +55755,7 @@
         <v>0.4</v>
       </c>
       <c r="H1627" s="2" t="n">
-        <v>46092.52871150037</v>
+        <v>46092.52871150463</v>
       </c>
     </row>
     <row r="1628">
@@ -55789,7 +55789,7 @@
         <v>2.92</v>
       </c>
       <c r="H1628" s="2" t="n">
-        <v>46080.5287115035</v>
+        <v>46080.52871150463</v>
       </c>
     </row>
     <row r="1629">
@@ -55823,7 +55823,7 @@
         <v>3.08</v>
       </c>
       <c r="H1629" s="2" t="n">
-        <v>46093.52871150631</v>
+        <v>46093.52871150463</v>
       </c>
     </row>
     <row r="1630">
@@ -55857,7 +55857,7 @@
         <v>3.11</v>
       </c>
       <c r="H1630" s="2" t="n">
-        <v>46083.52871150919</v>
+        <v>46083.52871150463</v>
       </c>
     </row>
     <row r="1631">
@@ -55891,7 +55891,7 @@
         <v>2.44</v>
       </c>
       <c r="H1631" s="2" t="n">
-        <v>46079.52871151223</v>
+        <v>46079.52871151621</v>
       </c>
     </row>
     <row r="1632">
@@ -55925,7 +55925,7 @@
         <v>2.72</v>
       </c>
       <c r="H1632" s="2" t="n">
-        <v>46079.52871151535</v>
+        <v>46079.52871151621</v>
       </c>
     </row>
     <row r="1633">
@@ -55959,7 +55959,7 @@
         <v>1.24</v>
       </c>
       <c r="H1633" s="2" t="n">
-        <v>46094.52871151811</v>
+        <v>46094.52871151621</v>
       </c>
     </row>
     <row r="1634">
@@ -55993,7 +55993,7 @@
         <v>0.84</v>
       </c>
       <c r="H1634" s="2" t="n">
-        <v>46079.52871152103</v>
+        <v>46079.52871151621</v>
       </c>
     </row>
     <row r="1635">
@@ -56027,7 +56027,7 @@
         <v>1.86</v>
       </c>
       <c r="H1635" s="2" t="n">
-        <v>46075.52871152383</v>
+        <v>46075.52871152778</v>
       </c>
     </row>
     <row r="1636">
@@ -56061,7 +56061,7 @@
         <v>4.66</v>
       </c>
       <c r="H1636" s="2" t="n">
-        <v>46086.52871152671</v>
+        <v>46086.52871152778</v>
       </c>
     </row>
     <row r="1637">
@@ -56095,7 +56095,7 @@
         <v>2.92</v>
       </c>
       <c r="H1637" s="2" t="n">
-        <v>46067.52871152961</v>
+        <v>46067.52871152778</v>
       </c>
     </row>
     <row r="1638">
@@ -56129,7 +56129,7 @@
         <v>0.22</v>
       </c>
       <c r="H1638" s="2" t="n">
-        <v>46070.52871153236</v>
+        <v>46070.52871152778</v>
       </c>
     </row>
     <row r="1639">
@@ -56163,7 +56163,7 @@
         <v>0.79</v>
       </c>
       <c r="H1639" s="2" t="n">
-        <v>46090.52871153516</v>
+        <v>46090.52871153935</v>
       </c>
     </row>
     <row r="1640">
@@ -56197,7 +56197,7 @@
         <v>2.83</v>
       </c>
       <c r="H1640" s="2" t="n">
-        <v>46073.52871153837</v>
+        <v>46073.52871153935</v>
       </c>
     </row>
     <row r="1641">
@@ -56231,7 +56231,7 @@
         <v>4.7</v>
       </c>
       <c r="H1641" s="2" t="n">
-        <v>46079.52871154116</v>
+        <v>46079.52871153935</v>
       </c>
     </row>
     <row r="1642">
@@ -56265,7 +56265,7 @@
         <v>2.5</v>
       </c>
       <c r="H1642" s="2" t="n">
-        <v>46074.52871154391</v>
+        <v>46074.52871153935</v>
       </c>
     </row>
     <row r="1643">
@@ -56299,7 +56299,7 @@
         <v>3.74</v>
       </c>
       <c r="H1643" s="2" t="n">
-        <v>46071.52871154668</v>
+        <v>46071.52871155093</v>
       </c>
     </row>
     <row r="1644">
@@ -56333,7 +56333,7 @@
         <v>0.93</v>
       </c>
       <c r="H1644" s="2" t="n">
-        <v>46087.52871154983</v>
+        <v>46087.52871155093</v>
       </c>
     </row>
     <row r="1645">
@@ -56367,7 +56367,7 @@
         <v>3.02</v>
       </c>
       <c r="H1645" s="2" t="n">
-        <v>46077.52871155273</v>
+        <v>46077.52871155093</v>
       </c>
     </row>
     <row r="1646">
@@ -56401,7 +56401,7 @@
         <v>1.43</v>
       </c>
       <c r="H1646" s="2" t="n">
-        <v>46075.52871155555</v>
+        <v>46075.52871155093</v>
       </c>
     </row>
     <row r="1647">
@@ -56435,7 +56435,7 @@
         <v>3.46</v>
       </c>
       <c r="H1647" s="2" t="n">
-        <v>46071.52871155843</v>
+        <v>46071.5287115625</v>
       </c>
     </row>
     <row r="1648">
@@ -56469,7 +56469,7 @@
         <v>3.53</v>
       </c>
       <c r="H1648" s="2" t="n">
-        <v>46092.52871156127</v>
+        <v>46092.5287115625</v>
       </c>
     </row>
     <row r="1649">
@@ -56503,7 +56503,7 @@
         <v>3.05</v>
       </c>
       <c r="H1649" s="2" t="n">
-        <v>46081.52871156417</v>
+        <v>46081.5287115625</v>
       </c>
     </row>
     <row r="1650">
@@ -56537,7 +56537,7 @@
         <v>3.29</v>
       </c>
       <c r="H1650" s="2" t="n">
-        <v>46089.52871156701</v>
+        <v>46089.5287115625</v>
       </c>
     </row>
     <row r="1651">
@@ -56571,7 +56571,1707 @@
         <v>1.2</v>
       </c>
       <c r="H1651" s="2" t="n">
-        <v>46067.5287115698</v>
+        <v>46067.52871157407</v>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="inlineStr">
+        <is>
+          <t>57ab6d74-f2aa-4832-9eb1-6ff9d5bf8e3e</t>
+        </is>
+      </c>
+      <c r="B1652" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1652" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1652" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1652" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1652" t="n">
+        <v>223.74</v>
+      </c>
+      <c r="G1652" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H1652" s="2" t="n">
+        <v>46084.6785767574</v>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr">
+        <is>
+          <t>7923be07-ca5a-46e1-b54f-99074ef66e2c</t>
+        </is>
+      </c>
+      <c r="B1653" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1653" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1653" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1653" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1653" t="n">
+        <v>157.54</v>
+      </c>
+      <c r="G1653" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H1653" s="2" t="n">
+        <v>46079.67857676251</v>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr">
+        <is>
+          <t>4d898aa9-1c65-4b1e-a54b-38b41cea9839</t>
+        </is>
+      </c>
+      <c r="B1654" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1654" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1654" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1654" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1654" t="n">
+        <v>259.26</v>
+      </c>
+      <c r="G1654" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="H1654" s="2" t="n">
+        <v>46087.67857676662</v>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="inlineStr">
+        <is>
+          <t>06e330e3-42c6-473e-8b0c-5609d9c4fd34</t>
+        </is>
+      </c>
+      <c r="B1655" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1655" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1655" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1655" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1655" t="n">
+        <v>111.82</v>
+      </c>
+      <c r="G1655" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H1655" s="2" t="n">
+        <v>46092.67857677013</v>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="inlineStr">
+        <is>
+          <t>5dc314db-1ec4-4fca-a591-3f46528f9e14</t>
+        </is>
+      </c>
+      <c r="B1656" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1656" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1656" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1656" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1656" t="n">
+        <v>190.69</v>
+      </c>
+      <c r="G1656" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H1656" s="2" t="n">
+        <v>46076.67857677327</v>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="inlineStr">
+        <is>
+          <t>12e7c0d0-038c-4ca1-9dd4-1a58f374423f</t>
+        </is>
+      </c>
+      <c r="B1657" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1657" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1657" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1657" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1657" t="n">
+        <v>54.74</v>
+      </c>
+      <c r="G1657" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H1657" s="2" t="n">
+        <v>46088.67857677677</v>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="inlineStr">
+        <is>
+          <t>3320910b-fe0c-40dc-a6fa-b2621760955a</t>
+        </is>
+      </c>
+      <c r="B1658" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1658" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1658" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1658" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1658" t="n">
+        <v>170.71</v>
+      </c>
+      <c r="G1658" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H1658" s="2" t="n">
+        <v>46083.67857677994</v>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="inlineStr">
+        <is>
+          <t>b85720b9-16f7-4d68-9800-f5099246c862</t>
+        </is>
+      </c>
+      <c r="B1659" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1659" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1659" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1659" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1659" t="n">
+        <v>492.41</v>
+      </c>
+      <c r="G1659" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="H1659" s="2" t="n">
+        <v>46093.67857678317</v>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="inlineStr">
+        <is>
+          <t>2562bd8c-c4ae-4098-af74-634b0c20a9bb</t>
+        </is>
+      </c>
+      <c r="B1660" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1660" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1660" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1660" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1660" t="n">
+        <v>79.27</v>
+      </c>
+      <c r="G1660" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H1660" s="2" t="n">
+        <v>46073.67857678673</v>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="inlineStr">
+        <is>
+          <t>b2043ac9-51b6-4436-9009-2b9441ec57c6</t>
+        </is>
+      </c>
+      <c r="B1661" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1661" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1661" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1661" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1661" t="n">
+        <v>227.62</v>
+      </c>
+      <c r="G1661" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H1661" s="2" t="n">
+        <v>46066.67857678999</v>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr">
+        <is>
+          <t>b76145ac-2cca-45d8-8027-848e5228b265</t>
+        </is>
+      </c>
+      <c r="B1662" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1662" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1662" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1662" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1662" t="n">
+        <v>203.3</v>
+      </c>
+      <c r="G1662" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="H1662" s="2" t="n">
+        <v>46088.67857679319</v>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr">
+        <is>
+          <t>579b495e-6d4e-4dbb-83fa-211bcaafc3ed</t>
+        </is>
+      </c>
+      <c r="B1663" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1663" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1663" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1663" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1663" t="n">
+        <v>415.08</v>
+      </c>
+      <c r="G1663" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="H1663" s="2" t="n">
+        <v>46066.67857679647</v>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="inlineStr">
+        <is>
+          <t>12f1af42-93ef-485d-9778-a762bc02b4ae</t>
+        </is>
+      </c>
+      <c r="B1664" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1664" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1664" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1664" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1664" t="n">
+        <v>179.64</v>
+      </c>
+      <c r="G1664" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H1664" s="2" t="n">
+        <v>46084.67857679991</v>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="inlineStr">
+        <is>
+          <t>9b060e97-5aeb-4ba9-9b1a-a0e6e69da063</t>
+        </is>
+      </c>
+      <c r="B1665" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1665" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1665" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1665" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1665" t="n">
+        <v>442.89</v>
+      </c>
+      <c r="G1665" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="H1665" s="2" t="n">
+        <v>46077.67857680303</v>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
+        <is>
+          <t>dfe14294-5675-4662-af29-698700b69859</t>
+        </is>
+      </c>
+      <c r="B1666" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1666" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1666" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1666" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1666" t="n">
+        <v>187.75</v>
+      </c>
+      <c r="G1666" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H1666" s="2" t="n">
+        <v>46080.67857680612</v>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="inlineStr">
+        <is>
+          <t>69e7348b-c265-405c-b2f6-2dc28a3eec80</t>
+        </is>
+      </c>
+      <c r="B1667" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1667" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1667" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1667" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1667" t="n">
+        <v>34.27</v>
+      </c>
+      <c r="G1667" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H1667" s="2" t="n">
+        <v>46087.67857680971</v>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>21084d39-cd0e-4b0a-8312-fe2471e2ad13</t>
+        </is>
+      </c>
+      <c r="B1668" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1668" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1668" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1668" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1668" t="n">
+        <v>293.04</v>
+      </c>
+      <c r="G1668" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="H1668" s="2" t="n">
+        <v>46076.67857681295</v>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>58878448-5c52-42eb-a195-866fa8bf7e52</t>
+        </is>
+      </c>
+      <c r="B1669" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1669" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1669" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1669" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1669" t="n">
+        <v>185.17</v>
+      </c>
+      <c r="G1669" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H1669" s="2" t="n">
+        <v>46068.67857681617</v>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>5c60f1ac-e406-4d09-8556-1b3ee905ebf8</t>
+        </is>
+      </c>
+      <c r="B1670" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1670" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1670" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1670" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1670" t="n">
+        <v>388.62</v>
+      </c>
+      <c r="G1670" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="H1670" s="2" t="n">
+        <v>46076.67857681933</v>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>ef6a45c5-4825-49f2-876f-92cb78724d7c</t>
+        </is>
+      </c>
+      <c r="B1671" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1671" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1671" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1671" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1671" t="n">
+        <v>450.37</v>
+      </c>
+      <c r="G1671" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H1671" s="2" t="n">
+        <v>46087.67857682281</v>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>3ead2d53-4ccb-429b-a2a5-e7a68cee8e8a</t>
+        </is>
+      </c>
+      <c r="B1672" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1672" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1672" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1672" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1672" t="n">
+        <v>202.92</v>
+      </c>
+      <c r="G1672" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="H1672" s="2" t="n">
+        <v>46076.67857682597</v>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr">
+        <is>
+          <t>0c5f752e-b73b-4645-bf37-c3bbfd9cb7d8</t>
+        </is>
+      </c>
+      <c r="B1673" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1673" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1673" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1673" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1673" t="n">
+        <v>282.84</v>
+      </c>
+      <c r="G1673" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="H1673" s="2" t="n">
+        <v>46071.67857682914</v>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>2449b7e5-78fc-40d4-b51c-7a641035fd87</t>
+        </is>
+      </c>
+      <c r="B1674" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1674" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1674" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1674" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1674" t="n">
+        <v>371.51</v>
+      </c>
+      <c r="G1674" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="H1674" s="2" t="n">
+        <v>46094.67857683254</v>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>8fd0e957-b0e0-48c7-b5cb-937a005f8741</t>
+        </is>
+      </c>
+      <c r="B1675" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1675" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1675" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1675" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1675" t="n">
+        <v>150.78</v>
+      </c>
+      <c r="G1675" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="H1675" s="2" t="n">
+        <v>46077.67857683581</v>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr">
+        <is>
+          <t>c08bef1a-097c-4d6d-97ce-ace3a2036c13</t>
+        </is>
+      </c>
+      <c r="B1676" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1676" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1676" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1676" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1676" t="n">
+        <v>60.41</v>
+      </c>
+      <c r="G1676" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H1676" s="2" t="n">
+        <v>46066.67857683908</v>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr">
+        <is>
+          <t>70dfe2fc-eeb1-43d9-929d-de1432f0debe</t>
+        </is>
+      </c>
+      <c r="B1677" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1677" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1677" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1677" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1677" t="n">
+        <v>495.19</v>
+      </c>
+      <c r="G1677" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="H1677" s="2" t="n">
+        <v>46067.67857684216</v>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>d8df92f9-4a92-476f-b577-7ed831caf15b</t>
+        </is>
+      </c>
+      <c r="B1678" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1678" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1678" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1678" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1678" t="n">
+        <v>48.78</v>
+      </c>
+      <c r="G1678" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H1678" s="2" t="n">
+        <v>46083.67857684576</v>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
+        <is>
+          <t>5e4c6806-f63b-48b6-bcb1-715e65bc82fe</t>
+        </is>
+      </c>
+      <c r="B1679" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1679" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1679" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1679" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1679" t="n">
+        <v>348.12</v>
+      </c>
+      <c r="G1679" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="H1679" s="2" t="n">
+        <v>46078.67857684886</v>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr">
+        <is>
+          <t>6b6a2616-8905-478f-a523-6cc7cc7e9975</t>
+        </is>
+      </c>
+      <c r="B1680" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1680" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1680" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1680" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1680" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="G1680" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H1680" s="2" t="n">
+        <v>46085.67857685211</v>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr">
+        <is>
+          <t>92459525-16a6-4d67-805f-6fdf96fcf29d</t>
+        </is>
+      </c>
+      <c r="B1681" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1681" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1681" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1681" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1681" t="n">
+        <v>291.44</v>
+      </c>
+      <c r="G1681" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="H1681" s="2" t="n">
+        <v>46076.67857685585</v>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr">
+        <is>
+          <t>b063787e-7684-48c6-9c66-b68552a50c2a</t>
+        </is>
+      </c>
+      <c r="B1682" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1682" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1682" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1682" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1682" t="n">
+        <v>155.35</v>
+      </c>
+      <c r="G1682" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H1682" s="2" t="n">
+        <v>46082.67857685918</v>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>ef2bb356-22ba-4a69-b6bd-474dbcd2bfda</t>
+        </is>
+      </c>
+      <c r="B1683" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1683" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1683" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1683" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1683" t="n">
+        <v>25.39</v>
+      </c>
+      <c r="G1683" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H1683" s="2" t="n">
+        <v>46085.67857686226</v>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>c7dd6d71-5a7a-4f0d-a69b-881815587ddf</t>
+        </is>
+      </c>
+      <c r="B1684" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1684" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1684" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1684" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1684" t="n">
+        <v>141.19</v>
+      </c>
+      <c r="G1684" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H1684" s="2" t="n">
+        <v>46088.67857686542</v>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>1b9426e0-dc1d-49ec-bb71-5dc56c29d85d</t>
+        </is>
+      </c>
+      <c r="B1685" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1685" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1685" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1685" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1685" t="n">
+        <v>467.27</v>
+      </c>
+      <c r="G1685" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="H1685" s="2" t="n">
+        <v>46082.67857686911</v>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr">
+        <is>
+          <t>260bc29a-d52a-43f3-ab31-c7a7ef019d16</t>
+        </is>
+      </c>
+      <c r="B1686" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1686" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1686" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1686" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1686" t="n">
+        <v>417.01</v>
+      </c>
+      <c r="G1686" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="H1686" s="2" t="n">
+        <v>46093.67857687221</v>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr">
+        <is>
+          <t>06bab144-a675-4a7d-bd87-79014aedc371</t>
+        </is>
+      </c>
+      <c r="B1687" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1687" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1687" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1687" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1687" t="n">
+        <v>306.11</v>
+      </c>
+      <c r="G1687" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="H1687" s="2" t="n">
+        <v>46084.67857687533</v>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="inlineStr">
+        <is>
+          <t>4a697c78-2548-4eec-be93-c019ec24998b</t>
+        </is>
+      </c>
+      <c r="B1688" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1688" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1688" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1688" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1688" t="n">
+        <v>206.49</v>
+      </c>
+      <c r="G1688" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H1688" s="2" t="n">
+        <v>46075.67857687834</v>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="inlineStr">
+        <is>
+          <t>794b3f5d-2b87-45f8-9f5d-540c3ccbb0c9</t>
+        </is>
+      </c>
+      <c r="B1689" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1689" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1689" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1689" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1689" t="n">
+        <v>73.23</v>
+      </c>
+      <c r="G1689" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H1689" s="2" t="n">
+        <v>46082.67857688169</v>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="inlineStr">
+        <is>
+          <t>dd2423ec-5c50-4b40-8941-591a214a1726</t>
+        </is>
+      </c>
+      <c r="B1690" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1690" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1690" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1690" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1690" t="n">
+        <v>316.66</v>
+      </c>
+      <c r="G1690" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="H1690" s="2" t="n">
+        <v>46085.67857688489</v>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="inlineStr">
+        <is>
+          <t>99b9ea5f-acab-42d1-a108-88ca690492f9</t>
+        </is>
+      </c>
+      <c r="B1691" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1691" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1691" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1691" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1691" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="G1691" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H1691" s="2" t="n">
+        <v>46086.67857688816</v>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="inlineStr">
+        <is>
+          <t>4a4bd5ff-b415-4f34-ac73-d84b8e657757</t>
+        </is>
+      </c>
+      <c r="B1692" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1692" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1692" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1692" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1692" t="n">
+        <v>79.67</v>
+      </c>
+      <c r="G1692" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H1692" s="2" t="n">
+        <v>46094.67857689153</v>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="inlineStr">
+        <is>
+          <t>0f9bc35e-a2cd-4f1d-8d76-3e1d23bf416b</t>
+        </is>
+      </c>
+      <c r="B1693" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1693" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1693" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1693" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1693" t="n">
+        <v>161.73</v>
+      </c>
+      <c r="G1693" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H1693" s="2" t="n">
+        <v>46076.67857689474</v>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="inlineStr">
+        <is>
+          <t>1d279b40-4d75-4083-8567-f2de1634e430</t>
+        </is>
+      </c>
+      <c r="B1694" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1694" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1694" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1694" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1694" t="n">
+        <v>445.38</v>
+      </c>
+      <c r="G1694" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="H1694" s="2" t="n">
+        <v>46093.67857689804</v>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="inlineStr">
+        <is>
+          <t>2fb1608f-059c-42f9-8705-575d4c58a877</t>
+        </is>
+      </c>
+      <c r="B1695" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1695" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1695" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1695" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1695" t="n">
+        <v>352.97</v>
+      </c>
+      <c r="G1695" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="H1695" s="2" t="n">
+        <v>46081.67857690123</v>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="inlineStr">
+        <is>
+          <t>c1eef5b2-75f6-43b0-b8e6-461d99ac512b</t>
+        </is>
+      </c>
+      <c r="B1696" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1696" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1696" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1696" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1696" t="n">
+        <v>304.61</v>
+      </c>
+      <c r="G1696" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H1696" s="2" t="n">
+        <v>46071.67857690503</v>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr">
+        <is>
+          <t>949ebc06-2a8a-4987-a932-6fd616a8aa81</t>
+        </is>
+      </c>
+      <c r="B1697" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1697" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1697" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1697" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1697" t="n">
+        <v>465.54</v>
+      </c>
+      <c r="G1697" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="H1697" s="2" t="n">
+        <v>46073.67857690811</v>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr">
+        <is>
+          <t>6a1a7d08-fada-4ce2-a11f-5245489f4c6f</t>
+        </is>
+      </c>
+      <c r="B1698" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1698" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1698" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1698" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1698" t="n">
+        <v>387.99</v>
+      </c>
+      <c r="G1698" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="H1698" s="2" t="n">
+        <v>46089.6785769113</v>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr">
+        <is>
+          <t>944c66d7-f53a-4cd6-9511-159698cd4419</t>
+        </is>
+      </c>
+      <c r="B1699" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1699" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1699" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1699" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1699" t="n">
+        <v>77.88</v>
+      </c>
+      <c r="G1699" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H1699" s="2" t="n">
+        <v>46093.67857691492</v>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="inlineStr">
+        <is>
+          <t>41a4f48d-0e68-4c42-9660-515a903adaa2</t>
+        </is>
+      </c>
+      <c r="B1700" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1700" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1700" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1700" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1700" t="n">
+        <v>483.17</v>
+      </c>
+      <c r="G1700" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="H1700" s="2" t="n">
+        <v>46090.6785769181</v>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr">
+        <is>
+          <t>973218a7-b805-4dfb-8a1b-df529cffde50</t>
+        </is>
+      </c>
+      <c r="B1701" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1701" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1701" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1701" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1701" t="n">
+        <v>282.72</v>
+      </c>
+      <c r="G1701" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="H1701" s="2" t="n">
+        <v>46086.67857692132</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1701"/>
+  <dimension ref="A1:H1751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56605,7 +56605,7 @@
         <v>2.24</v>
       </c>
       <c r="H1652" s="2" t="n">
-        <v>46084.6785767574</v>
+        <v>46084.67857675926</v>
       </c>
     </row>
     <row r="1653">
@@ -56639,7 +56639,7 @@
         <v>1.58</v>
       </c>
       <c r="H1653" s="2" t="n">
-        <v>46079.67857676251</v>
+        <v>46079.67857675926</v>
       </c>
     </row>
     <row r="1654">
@@ -56673,7 +56673,7 @@
         <v>2.59</v>
       </c>
       <c r="H1654" s="2" t="n">
-        <v>46087.67857676662</v>
+        <v>46087.67857677084</v>
       </c>
     </row>
     <row r="1655">
@@ -56707,7 +56707,7 @@
         <v>1.12</v>
       </c>
       <c r="H1655" s="2" t="n">
-        <v>46092.67857677013</v>
+        <v>46092.67857677084</v>
       </c>
     </row>
     <row r="1656">
@@ -56741,7 +56741,7 @@
         <v>1.91</v>
       </c>
       <c r="H1656" s="2" t="n">
-        <v>46076.67857677327</v>
+        <v>46076.67857677084</v>
       </c>
     </row>
     <row r="1657">
@@ -56775,7 +56775,7 @@
         <v>0.55</v>
       </c>
       <c r="H1657" s="2" t="n">
-        <v>46088.67857677677</v>
+        <v>46088.6785767824</v>
       </c>
     </row>
     <row r="1658">
@@ -56809,7 +56809,7 @@
         <v>1.71</v>
       </c>
       <c r="H1658" s="2" t="n">
-        <v>46083.67857677994</v>
+        <v>46083.6785767824</v>
       </c>
     </row>
     <row r="1659">
@@ -56843,7 +56843,7 @@
         <v>4.92</v>
       </c>
       <c r="H1659" s="2" t="n">
-        <v>46093.67857678317</v>
+        <v>46093.6785767824</v>
       </c>
     </row>
     <row r="1660">
@@ -56877,7 +56877,7 @@
         <v>0.79</v>
       </c>
       <c r="H1660" s="2" t="n">
-        <v>46073.67857678673</v>
+        <v>46073.6785767824</v>
       </c>
     </row>
     <row r="1661">
@@ -56911,7 +56911,7 @@
         <v>2.28</v>
       </c>
       <c r="H1661" s="2" t="n">
-        <v>46066.67857678999</v>
+        <v>46066.67857679398</v>
       </c>
     </row>
     <row r="1662">
@@ -56945,7 +56945,7 @@
         <v>2.03</v>
       </c>
       <c r="H1662" s="2" t="n">
-        <v>46088.67857679319</v>
+        <v>46088.67857679398</v>
       </c>
     </row>
     <row r="1663">
@@ -56979,7 +56979,7 @@
         <v>4.15</v>
       </c>
       <c r="H1663" s="2" t="n">
-        <v>46066.67857679647</v>
+        <v>46066.67857679398</v>
       </c>
     </row>
     <row r="1664">
@@ -57013,7 +57013,7 @@
         <v>1.8</v>
       </c>
       <c r="H1664" s="2" t="n">
-        <v>46084.67857679991</v>
+        <v>46084.67857680556</v>
       </c>
     </row>
     <row r="1665">
@@ -57047,7 +57047,7 @@
         <v>4.43</v>
       </c>
       <c r="H1665" s="2" t="n">
-        <v>46077.67857680303</v>
+        <v>46077.67857680556</v>
       </c>
     </row>
     <row r="1666">
@@ -57081,7 +57081,7 @@
         <v>1.88</v>
       </c>
       <c r="H1666" s="2" t="n">
-        <v>46080.67857680612</v>
+        <v>46080.67857680556</v>
       </c>
     </row>
     <row r="1667">
@@ -57115,7 +57115,7 @@
         <v>0.34</v>
       </c>
       <c r="H1667" s="2" t="n">
-        <v>46087.67857680971</v>
+        <v>46087.67857680556</v>
       </c>
     </row>
     <row r="1668">
@@ -57149,7 +57149,7 @@
         <v>2.93</v>
       </c>
       <c r="H1668" s="2" t="n">
-        <v>46076.67857681295</v>
+        <v>46076.67857681713</v>
       </c>
     </row>
     <row r="1669">
@@ -57183,7 +57183,7 @@
         <v>1.85</v>
       </c>
       <c r="H1669" s="2" t="n">
-        <v>46068.67857681617</v>
+        <v>46068.67857681713</v>
       </c>
     </row>
     <row r="1670">
@@ -57217,7 +57217,7 @@
         <v>3.89</v>
       </c>
       <c r="H1670" s="2" t="n">
-        <v>46076.67857681933</v>
+        <v>46076.67857681713</v>
       </c>
     </row>
     <row r="1671">
@@ -57251,7 +57251,7 @@
         <v>4.5</v>
       </c>
       <c r="H1671" s="2" t="n">
-        <v>46087.67857682281</v>
+        <v>46087.67857681713</v>
       </c>
     </row>
     <row r="1672">
@@ -57285,7 +57285,7 @@
         <v>2.03</v>
       </c>
       <c r="H1672" s="2" t="n">
-        <v>46076.67857682597</v>
+        <v>46076.6785768287</v>
       </c>
     </row>
     <row r="1673">
@@ -57319,7 +57319,7 @@
         <v>2.83</v>
       </c>
       <c r="H1673" s="2" t="n">
-        <v>46071.67857682914</v>
+        <v>46071.6785768287</v>
       </c>
     </row>
     <row r="1674">
@@ -57353,7 +57353,7 @@
         <v>3.72</v>
       </c>
       <c r="H1674" s="2" t="n">
-        <v>46094.67857683254</v>
+        <v>46094.6785768287</v>
       </c>
     </row>
     <row r="1675">
@@ -57387,7 +57387,7 @@
         <v>1.51</v>
       </c>
       <c r="H1675" s="2" t="n">
-        <v>46077.67857683581</v>
+        <v>46077.67857684028</v>
       </c>
     </row>
     <row r="1676">
@@ -57421,7 +57421,7 @@
         <v>0.6</v>
       </c>
       <c r="H1676" s="2" t="n">
-        <v>46066.67857683908</v>
+        <v>46066.67857684028</v>
       </c>
     </row>
     <row r="1677">
@@ -57455,7 +57455,7 @@
         <v>4.95</v>
       </c>
       <c r="H1677" s="2" t="n">
-        <v>46067.67857684216</v>
+        <v>46067.67857684028</v>
       </c>
     </row>
     <row r="1678">
@@ -57489,7 +57489,7 @@
         <v>0.49</v>
       </c>
       <c r="H1678" s="2" t="n">
-        <v>46083.67857684576</v>
+        <v>46083.67857684028</v>
       </c>
     </row>
     <row r="1679">
@@ -57523,7 +57523,7 @@
         <v>3.48</v>
       </c>
       <c r="H1679" s="2" t="n">
-        <v>46078.67857684886</v>
+        <v>46078.67857685185</v>
       </c>
     </row>
     <row r="1680">
@@ -57557,7 +57557,7 @@
         <v>0.06</v>
       </c>
       <c r="H1680" s="2" t="n">
-        <v>46085.67857685211</v>
+        <v>46085.67857685185</v>
       </c>
     </row>
     <row r="1681">
@@ -57591,7 +57591,7 @@
         <v>2.91</v>
       </c>
       <c r="H1681" s="2" t="n">
-        <v>46076.67857685585</v>
+        <v>46076.67857685185</v>
       </c>
     </row>
     <row r="1682">
@@ -57625,7 +57625,7 @@
         <v>1.55</v>
       </c>
       <c r="H1682" s="2" t="n">
-        <v>46082.67857685918</v>
+        <v>46082.67857686343</v>
       </c>
     </row>
     <row r="1683">
@@ -57659,7 +57659,7 @@
         <v>0.25</v>
       </c>
       <c r="H1683" s="2" t="n">
-        <v>46085.67857686226</v>
+        <v>46085.67857686343</v>
       </c>
     </row>
     <row r="1684">
@@ -57693,7 +57693,7 @@
         <v>1.41</v>
       </c>
       <c r="H1684" s="2" t="n">
-        <v>46088.67857686542</v>
+        <v>46088.67857686343</v>
       </c>
     </row>
     <row r="1685">
@@ -57727,7 +57727,7 @@
         <v>4.67</v>
       </c>
       <c r="H1685" s="2" t="n">
-        <v>46082.67857686911</v>
+        <v>46082.67857686343</v>
       </c>
     </row>
     <row r="1686">
@@ -57761,7 +57761,7 @@
         <v>4.17</v>
       </c>
       <c r="H1686" s="2" t="n">
-        <v>46093.67857687221</v>
+        <v>46093.678576875</v>
       </c>
     </row>
     <row r="1687">
@@ -57795,7 +57795,7 @@
         <v>3.06</v>
       </c>
       <c r="H1687" s="2" t="n">
-        <v>46084.67857687533</v>
+        <v>46084.678576875</v>
       </c>
     </row>
     <row r="1688">
@@ -57829,7 +57829,7 @@
         <v>2.06</v>
       </c>
       <c r="H1688" s="2" t="n">
-        <v>46075.67857687834</v>
+        <v>46075.678576875</v>
       </c>
     </row>
     <row r="1689">
@@ -57863,7 +57863,7 @@
         <v>0.73</v>
       </c>
       <c r="H1689" s="2" t="n">
-        <v>46082.67857688169</v>
+        <v>46082.67857688657</v>
       </c>
     </row>
     <row r="1690">
@@ -57897,7 +57897,7 @@
         <v>3.17</v>
       </c>
       <c r="H1690" s="2" t="n">
-        <v>46085.67857688489</v>
+        <v>46085.67857688657</v>
       </c>
     </row>
     <row r="1691">
@@ -57931,7 +57931,7 @@
         <v>0.62</v>
       </c>
       <c r="H1691" s="2" t="n">
-        <v>46086.67857688816</v>
+        <v>46086.67857688657</v>
       </c>
     </row>
     <row r="1692">
@@ -57965,7 +57965,7 @@
         <v>0.8</v>
       </c>
       <c r="H1692" s="2" t="n">
-        <v>46094.67857689153</v>
+        <v>46094.67857688657</v>
       </c>
     </row>
     <row r="1693">
@@ -57999,7 +57999,7 @@
         <v>1.62</v>
       </c>
       <c r="H1693" s="2" t="n">
-        <v>46076.67857689474</v>
+        <v>46076.67857689815</v>
       </c>
     </row>
     <row r="1694">
@@ -58033,7 +58033,7 @@
         <v>4.45</v>
       </c>
       <c r="H1694" s="2" t="n">
-        <v>46093.67857689804</v>
+        <v>46093.67857689815</v>
       </c>
     </row>
     <row r="1695">
@@ -58067,7 +58067,7 @@
         <v>3.53</v>
       </c>
       <c r="H1695" s="2" t="n">
-        <v>46081.67857690123</v>
+        <v>46081.67857689815</v>
       </c>
     </row>
     <row r="1696">
@@ -58101,7 +58101,7 @@
         <v>3.05</v>
       </c>
       <c r="H1696" s="2" t="n">
-        <v>46071.67857690503</v>
+        <v>46071.67857690972</v>
       </c>
     </row>
     <row r="1697">
@@ -58135,7 +58135,7 @@
         <v>4.66</v>
       </c>
       <c r="H1697" s="2" t="n">
-        <v>46073.67857690811</v>
+        <v>46073.67857690972</v>
       </c>
     </row>
     <row r="1698">
@@ -58169,7 +58169,7 @@
         <v>3.88</v>
       </c>
       <c r="H1698" s="2" t="n">
-        <v>46089.6785769113</v>
+        <v>46089.67857690972</v>
       </c>
     </row>
     <row r="1699">
@@ -58203,7 +58203,7 @@
         <v>0.78</v>
       </c>
       <c r="H1699" s="2" t="n">
-        <v>46093.67857691492</v>
+        <v>46093.67857690972</v>
       </c>
     </row>
     <row r="1700">
@@ -58237,7 +58237,7 @@
         <v>4.83</v>
       </c>
       <c r="H1700" s="2" t="n">
-        <v>46090.6785769181</v>
+        <v>46090.67857692129</v>
       </c>
     </row>
     <row r="1701">
@@ -58271,7 +58271,1707 @@
         <v>2.83</v>
       </c>
       <c r="H1701" s="2" t="n">
-        <v>46086.67857692132</v>
+        <v>46086.67857692129</v>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="inlineStr">
+        <is>
+          <t>f4ddca0a-8d6e-44d0-9ee1-7a810dfa9b0e</t>
+        </is>
+      </c>
+      <c r="B1702" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1702" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1702" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1702" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1702" t="n">
+        <v>199.09</v>
+      </c>
+      <c r="G1702" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H1702" s="2" t="n">
+        <v>46078.18522146757</v>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="inlineStr">
+        <is>
+          <t>2c3bb197-67e5-435f-8433-3556cab58193</t>
+        </is>
+      </c>
+      <c r="B1703" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1703" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1703" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1703" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1703" t="n">
+        <v>134.93</v>
+      </c>
+      <c r="G1703" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H1703" s="2" t="n">
+        <v>46071.18522147178</v>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="inlineStr">
+        <is>
+          <t>ff87bae6-6f31-494d-8205-180932ca4233</t>
+        </is>
+      </c>
+      <c r="B1704" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1704" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1704" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1704" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1704" t="n">
+        <v>464.25</v>
+      </c>
+      <c r="G1704" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="H1704" s="2" t="n">
+        <v>46070.18522147501</v>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="inlineStr">
+        <is>
+          <t>bf74494f-051e-4574-9a1a-aec3f3e9208d</t>
+        </is>
+      </c>
+      <c r="B1705" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1705" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1705" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1705" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1705" t="n">
+        <v>357.27</v>
+      </c>
+      <c r="G1705" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="H1705" s="2" t="n">
+        <v>46081.18522147834</v>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="inlineStr">
+        <is>
+          <t>0c8c97e3-5295-47c9-8cb1-972dd8fff04b</t>
+        </is>
+      </c>
+      <c r="B1706" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1706" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1706" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1706" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1706" t="n">
+        <v>279.21</v>
+      </c>
+      <c r="G1706" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="H1706" s="2" t="n">
+        <v>46080.18522148159</v>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="inlineStr">
+        <is>
+          <t>b4ee5f9c-67a0-47e6-aa1c-a0b4bebecbbd</t>
+        </is>
+      </c>
+      <c r="B1707" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1707" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1707" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1707" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1707" t="n">
+        <v>387.26</v>
+      </c>
+      <c r="G1707" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="H1707" s="2" t="n">
+        <v>46071.18522148477</v>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="inlineStr">
+        <is>
+          <t>c4453e34-7115-41a3-ac3d-cd5577a50d82</t>
+        </is>
+      </c>
+      <c r="B1708" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1708" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1708" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1708" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1708" t="n">
+        <v>240.89</v>
+      </c>
+      <c r="G1708" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="H1708" s="2" t="n">
+        <v>46073.18522148816</v>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="inlineStr">
+        <is>
+          <t>b604085a-7388-40c9-ac7c-8740ca2c8fd0</t>
+        </is>
+      </c>
+      <c r="B1709" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1709" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1709" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1709" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1709" t="n">
+        <v>232.66</v>
+      </c>
+      <c r="G1709" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="H1709" s="2" t="n">
+        <v>46067.18522149131</v>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="inlineStr">
+        <is>
+          <t>a1ed0d99-f814-4a34-b2aa-19694f92df1d</t>
+        </is>
+      </c>
+      <c r="B1710" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1710" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1710" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1710" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1710" t="n">
+        <v>129.34</v>
+      </c>
+      <c r="G1710" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H1710" s="2" t="n">
+        <v>46093.18522149436</v>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="inlineStr">
+        <is>
+          <t>503b913b-7f84-4634-bbee-f0de199efaf1</t>
+        </is>
+      </c>
+      <c r="B1711" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1711" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1711" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1711" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1711" t="n">
+        <v>27.79</v>
+      </c>
+      <c r="G1711" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H1711" s="2" t="n">
+        <v>46084.18522149795</v>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="inlineStr">
+        <is>
+          <t>1f0c4806-5f83-4757-843b-3ce783d94ed1</t>
+        </is>
+      </c>
+      <c r="B1712" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1712" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1712" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1712" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1712" t="n">
+        <v>265.22</v>
+      </c>
+      <c r="G1712" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="H1712" s="2" t="n">
+        <v>46093.1852215017</v>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="inlineStr">
+        <is>
+          <t>90931d55-9c18-42d6-b45f-545f8c04a3c5</t>
+        </is>
+      </c>
+      <c r="B1713" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1713" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1713" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1713" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1713" t="n">
+        <v>68.06999999999999</v>
+      </c>
+      <c r="G1713" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H1713" s="2" t="n">
+        <v>46081.18522150483</v>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="inlineStr">
+        <is>
+          <t>9171a899-96a3-4b86-8007-fdf3642d883c</t>
+        </is>
+      </c>
+      <c r="B1714" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1714" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1714" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1714" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1714" t="n">
+        <v>489.99</v>
+      </c>
+      <c r="G1714" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H1714" s="2" t="n">
+        <v>46086.18522150807</v>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="inlineStr">
+        <is>
+          <t>d39a7d81-f7e2-487f-80c8-05ceb05bf1b1</t>
+        </is>
+      </c>
+      <c r="B1715" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1715" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1715" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1715" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1715" t="n">
+        <v>106.22</v>
+      </c>
+      <c r="G1715" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="H1715" s="2" t="n">
+        <v>46091.18522151131</v>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="inlineStr">
+        <is>
+          <t>3283ce6f-36b6-48cd-9e89-574e38696d87</t>
+        </is>
+      </c>
+      <c r="B1716" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1716" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1716" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1716" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1716" t="n">
+        <v>102.89</v>
+      </c>
+      <c r="G1716" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H1716" s="2" t="n">
+        <v>46093.18522151439</v>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" t="inlineStr">
+        <is>
+          <t>3ce1a7c4-66ee-47ae-999e-98568c0308fd</t>
+        </is>
+      </c>
+      <c r="B1717" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1717" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1717" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1717" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1717" t="n">
+        <v>44.41</v>
+      </c>
+      <c r="G1717" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H1717" s="2" t="n">
+        <v>46085.18522151747</v>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="inlineStr">
+        <is>
+          <t>504a65b7-c3d6-4166-b758-bb902bd19b72</t>
+        </is>
+      </c>
+      <c r="B1718" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1718" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1718" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1718" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1718" t="n">
+        <v>332.02</v>
+      </c>
+      <c r="G1718" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="H1718" s="2" t="n">
+        <v>46073.18522152056</v>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="inlineStr">
+        <is>
+          <t>d16cd225-39dc-4a14-9a3b-090e0b8e587c</t>
+        </is>
+      </c>
+      <c r="B1719" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1719" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1719" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1719" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1719" t="n">
+        <v>36.33</v>
+      </c>
+      <c r="G1719" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H1719" s="2" t="n">
+        <v>46083.18522152376</v>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="inlineStr">
+        <is>
+          <t>0d3e9a26-5073-422c-9963-0de08047c88e</t>
+        </is>
+      </c>
+      <c r="B1720" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1720" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1720" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1720" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1720" t="n">
+        <v>459.58</v>
+      </c>
+      <c r="G1720" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H1720" s="2" t="n">
+        <v>46081.18522152698</v>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="inlineStr">
+        <is>
+          <t>d1459ffa-93b9-4965-96f5-46458a9e59ef</t>
+        </is>
+      </c>
+      <c r="B1721" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1721" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1721" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1721" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1721" t="n">
+        <v>145.86</v>
+      </c>
+      <c r="G1721" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="H1721" s="2" t="n">
+        <v>46094.18522153005</v>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="inlineStr">
+        <is>
+          <t>e54b6ca7-1b45-4ac2-990d-37c8a27bdd17</t>
+        </is>
+      </c>
+      <c r="B1722" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1722" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1722" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1722" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1722" t="n">
+        <v>411.47</v>
+      </c>
+      <c r="G1722" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="H1722" s="2" t="n">
+        <v>46078.1852215332</v>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="inlineStr">
+        <is>
+          <t>6e126c78-b907-4ad5-b820-2dd132493ce1</t>
+        </is>
+      </c>
+      <c r="B1723" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1723" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1723" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1723" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1723" t="n">
+        <v>95.94</v>
+      </c>
+      <c r="G1723" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H1723" s="2" t="n">
+        <v>46091.18522153661</v>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" t="inlineStr">
+        <is>
+          <t>fa4b4209-549a-4b18-891c-a5d7517af47d</t>
+        </is>
+      </c>
+      <c r="B1724" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1724" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1724" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1724" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1724" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="G1724" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H1724" s="2" t="n">
+        <v>46080.1852215397</v>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" t="inlineStr">
+        <is>
+          <t>4c0de839-9120-4329-8d07-e4d34a2ceed2</t>
+        </is>
+      </c>
+      <c r="B1725" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1725" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1725" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1725" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1725" t="n">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="G1725" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H1725" s="2" t="n">
+        <v>46084.1852215427</v>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" t="inlineStr">
+        <is>
+          <t>4f22234f-0d19-418f-898e-57f2e157b85b</t>
+        </is>
+      </c>
+      <c r="B1726" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1726" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1726" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1726" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1726" t="n">
+        <v>390.06</v>
+      </c>
+      <c r="G1726" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H1726" s="2" t="n">
+        <v>46072.1852215459</v>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" t="inlineStr">
+        <is>
+          <t>8f46e708-fb90-4fb9-b75a-2331ddbd7ab4</t>
+        </is>
+      </c>
+      <c r="B1727" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1727" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1727" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1727" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1727" t="n">
+        <v>300.26</v>
+      </c>
+      <c r="G1727" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1727" s="2" t="n">
+        <v>46069.18522154899</v>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" t="inlineStr">
+        <is>
+          <t>b86e336f-cf03-4875-90ac-bc8c94d1abb2</t>
+        </is>
+      </c>
+      <c r="B1728" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1728" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1728" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1728" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1728" t="n">
+        <v>430.58</v>
+      </c>
+      <c r="G1728" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="H1728" s="2" t="n">
+        <v>46067.18522155219</v>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" t="inlineStr">
+        <is>
+          <t>f2784152-1332-4324-8269-cd162b8bba8c</t>
+        </is>
+      </c>
+      <c r="B1729" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1729" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1729" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1729" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1729" t="n">
+        <v>375.25</v>
+      </c>
+      <c r="G1729" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H1729" s="2" t="n">
+        <v>46070.1852215554</v>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="inlineStr">
+        <is>
+          <t>796c11a2-9a25-43e0-8ff9-47fa9911a9e4</t>
+        </is>
+      </c>
+      <c r="B1730" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1730" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1730" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1730" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1730" t="n">
+        <v>302.44</v>
+      </c>
+      <c r="G1730" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="H1730" s="2" t="n">
+        <v>46081.18522155871</v>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" t="inlineStr">
+        <is>
+          <t>8a4462d1-a0ce-4637-931e-963e3e2c0fdc</t>
+        </is>
+      </c>
+      <c r="B1731" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1731" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1731" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1731" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1731" t="n">
+        <v>421.62</v>
+      </c>
+      <c r="G1731" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="H1731" s="2" t="n">
+        <v>46087.18522156178</v>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" t="inlineStr">
+        <is>
+          <t>c7a05a34-fb92-492e-8386-6542e879adc1</t>
+        </is>
+      </c>
+      <c r="B1732" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1732" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1732" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1732" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1732" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="G1732" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H1732" s="2" t="n">
+        <v>46071.18522156496</v>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" t="inlineStr">
+        <is>
+          <t>154b43ad-64df-44ef-a48d-60762d0059ef</t>
+        </is>
+      </c>
+      <c r="B1733" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1733" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1733" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1733" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1733" t="n">
+        <v>496.5</v>
+      </c>
+      <c r="G1733" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="H1733" s="2" t="n">
+        <v>46070.18522156811</v>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" t="inlineStr">
+        <is>
+          <t>717acdea-bcd0-45e9-ab95-b3ecd58e34b0</t>
+        </is>
+      </c>
+      <c r="B1734" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1734" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1734" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1734" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1734" t="n">
+        <v>393.57</v>
+      </c>
+      <c r="G1734" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="H1734" s="2" t="n">
+        <v>46095.18522157139</v>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" t="inlineStr">
+        <is>
+          <t>25076df8-400f-4109-8e22-1bc52e8eccac</t>
+        </is>
+      </c>
+      <c r="B1735" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1735" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1735" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1735" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1735" t="n">
+        <v>475.37</v>
+      </c>
+      <c r="G1735" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="H1735" s="2" t="n">
+        <v>46074.18522157448</v>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" t="inlineStr">
+        <is>
+          <t>f8dc4389-8a70-4a31-86b9-1910ce5e56d0</t>
+        </is>
+      </c>
+      <c r="B1736" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1736" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1736" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1736" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1736" t="n">
+        <v>317.81</v>
+      </c>
+      <c r="G1736" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H1736" s="2" t="n">
+        <v>46084.18522157765</v>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" t="inlineStr">
+        <is>
+          <t>dd112ac8-d264-499c-a23d-e018926e1a43</t>
+        </is>
+      </c>
+      <c r="B1737" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1737" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1737" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1737" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1737" t="n">
+        <v>152.33</v>
+      </c>
+      <c r="G1737" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="H1737" s="2" t="n">
+        <v>46093.18522158083</v>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="inlineStr">
+        <is>
+          <t>fc16ce42-9e10-41b8-b0d4-7e990c8eff82</t>
+        </is>
+      </c>
+      <c r="B1738" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1738" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1738" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1738" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1738" t="n">
+        <v>179.8</v>
+      </c>
+      <c r="G1738" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H1738" s="2" t="n">
+        <v>46082.18522158402</v>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" t="inlineStr">
+        <is>
+          <t>1da8ac8a-e486-4869-9749-a9c6c9832700</t>
+        </is>
+      </c>
+      <c r="B1739" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1739" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1739" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1739" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1739" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="G1739" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H1739" s="2" t="n">
+        <v>46084.18522158715</v>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="inlineStr">
+        <is>
+          <t>f357bd3e-4aa3-4c35-8fa1-900d8c277bf9</t>
+        </is>
+      </c>
+      <c r="B1740" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1740" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1740" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1740" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1740" t="n">
+        <v>445.51</v>
+      </c>
+      <c r="G1740" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="H1740" s="2" t="n">
+        <v>46081.18522159017</v>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="inlineStr">
+        <is>
+          <t>2a0e9d17-703d-4c3b-864c-4fc6327956e5</t>
+        </is>
+      </c>
+      <c r="B1741" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1741" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1741" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1741" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1741" t="n">
+        <v>451.27</v>
+      </c>
+      <c r="G1741" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="H1741" s="2" t="n">
+        <v>46092.18522159343</v>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="inlineStr">
+        <is>
+          <t>edb13e45-57ef-4ea6-897b-b07e2be59ae8</t>
+        </is>
+      </c>
+      <c r="B1742" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1742" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1742" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1742" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1742" t="n">
+        <v>338.75</v>
+      </c>
+      <c r="G1742" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="H1742" s="2" t="n">
+        <v>46091.18522159647</v>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="inlineStr">
+        <is>
+          <t>dc90146d-128d-49b1-b4ca-57d26dce2bb3</t>
+        </is>
+      </c>
+      <c r="B1743" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1743" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1743" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1743" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1743" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="G1743" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H1743" s="2" t="n">
+        <v>46089.18522159955</v>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="inlineStr">
+        <is>
+          <t>169ee050-8624-4623-93a3-395d634a3855</t>
+        </is>
+      </c>
+      <c r="B1744" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1744" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1744" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1744" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1744" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="G1744" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H1744" s="2" t="n">
+        <v>46076.18522160258</v>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="inlineStr">
+        <is>
+          <t>a4c828a0-3afd-45ea-a4d2-c6e4a4cb86d8</t>
+        </is>
+      </c>
+      <c r="B1745" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1745" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1745" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1745" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1745" t="n">
+        <v>94.54000000000001</v>
+      </c>
+      <c r="G1745" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H1745" s="2" t="n">
+        <v>46089.18522160593</v>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="inlineStr">
+        <is>
+          <t>7d00b664-fcfe-4efe-b6af-e8841b875413</t>
+        </is>
+      </c>
+      <c r="B1746" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1746" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1746" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1746" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1746" t="n">
+        <v>66.34</v>
+      </c>
+      <c r="G1746" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H1746" s="2" t="n">
+        <v>46074.18522160903</v>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="inlineStr">
+        <is>
+          <t>7a52e499-ed14-4bf4-b071-35aac2c3164f</t>
+        </is>
+      </c>
+      <c r="B1747" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1747" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1747" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1747" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1747" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="G1747" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H1747" s="2" t="n">
+        <v>46083.18522161206</v>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="inlineStr">
+        <is>
+          <t>b4cb8dd2-62be-478d-b2f2-24fda97dfd4d</t>
+        </is>
+      </c>
+      <c r="B1748" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1748" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1748" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1748" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1748" t="n">
+        <v>396.12</v>
+      </c>
+      <c r="G1748" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="H1748" s="2" t="n">
+        <v>46067.1852216153</v>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" t="inlineStr">
+        <is>
+          <t>d4e4d4e9-26c4-4407-9b5d-ebd2f6e8174c</t>
+        </is>
+      </c>
+      <c r="B1749" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1749" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1749" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1749" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1749" t="n">
+        <v>295.12</v>
+      </c>
+      <c r="G1749" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="H1749" s="2" t="n">
+        <v>46072.18522161854</v>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" t="inlineStr">
+        <is>
+          <t>6a86c908-e562-4056-b138-1eedc260241b</t>
+        </is>
+      </c>
+      <c r="B1750" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1750" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1750" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1750" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1750" t="n">
+        <v>175.85</v>
+      </c>
+      <c r="G1750" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H1750" s="2" t="n">
+        <v>46072.18522162154</v>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" t="inlineStr">
+        <is>
+          <t>0f4a82f0-8519-481c-9026-86692b20a125</t>
+        </is>
+      </c>
+      <c r="B1751" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1751" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1751" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1751" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1751" t="n">
+        <v>28.18</v>
+      </c>
+      <c r="G1751" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H1751" s="2" t="n">
+        <v>46092.1852216246</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1751"/>
+  <dimension ref="A1:H1801"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58305,7 +58305,7 @@
         <v>1.99</v>
       </c>
       <c r="H1702" s="2" t="n">
-        <v>46078.18522146757</v>
+        <v>46078.18522146991</v>
       </c>
     </row>
     <row r="1703">
@@ -58339,7 +58339,7 @@
         <v>1.35</v>
       </c>
       <c r="H1703" s="2" t="n">
-        <v>46071.18522147178</v>
+        <v>46071.18522146991</v>
       </c>
     </row>
     <row r="1704">
@@ -58373,7 +58373,7 @@
         <v>4.64</v>
       </c>
       <c r="H1704" s="2" t="n">
-        <v>46070.18522147501</v>
+        <v>46070.18522146991</v>
       </c>
     </row>
     <row r="1705">
@@ -58407,7 +58407,7 @@
         <v>3.57</v>
       </c>
       <c r="H1705" s="2" t="n">
-        <v>46081.18522147834</v>
+        <v>46081.18522148148</v>
       </c>
     </row>
     <row r="1706">
@@ -58441,7 +58441,7 @@
         <v>2.79</v>
       </c>
       <c r="H1706" s="2" t="n">
-        <v>46080.18522148159</v>
+        <v>46080.18522148148</v>
       </c>
     </row>
     <row r="1707">
@@ -58475,7 +58475,7 @@
         <v>3.87</v>
       </c>
       <c r="H1707" s="2" t="n">
-        <v>46071.18522148477</v>
+        <v>46071.18522148148</v>
       </c>
     </row>
     <row r="1708">
@@ -58509,7 +58509,7 @@
         <v>2.41</v>
       </c>
       <c r="H1708" s="2" t="n">
-        <v>46073.18522148816</v>
+        <v>46073.18522149305</v>
       </c>
     </row>
     <row r="1709">
@@ -58543,7 +58543,7 @@
         <v>2.33</v>
       </c>
       <c r="H1709" s="2" t="n">
-        <v>46067.18522149131</v>
+        <v>46067.18522149305</v>
       </c>
     </row>
     <row r="1710">
@@ -58577,7 +58577,7 @@
         <v>1.29</v>
       </c>
       <c r="H1710" s="2" t="n">
-        <v>46093.18522149436</v>
+        <v>46093.18522149305</v>
       </c>
     </row>
     <row r="1711">
@@ -58611,7 +58611,7 @@
         <v>0.28</v>
       </c>
       <c r="H1711" s="2" t="n">
-        <v>46084.18522149795</v>
+        <v>46084.18522149305</v>
       </c>
     </row>
     <row r="1712">
@@ -58645,7 +58645,7 @@
         <v>2.65</v>
       </c>
       <c r="H1712" s="2" t="n">
-        <v>46093.1852215017</v>
+        <v>46093.18522150463</v>
       </c>
     </row>
     <row r="1713">
@@ -58679,7 +58679,7 @@
         <v>0.68</v>
       </c>
       <c r="H1713" s="2" t="n">
-        <v>46081.18522150483</v>
+        <v>46081.18522150463</v>
       </c>
     </row>
     <row r="1714">
@@ -58713,7 +58713,7 @@
         <v>4.9</v>
       </c>
       <c r="H1714" s="2" t="n">
-        <v>46086.18522150807</v>
+        <v>46086.18522150463</v>
       </c>
     </row>
     <row r="1715">
@@ -58747,7 +58747,7 @@
         <v>1.06</v>
       </c>
       <c r="H1715" s="2" t="n">
-        <v>46091.18522151131</v>
+        <v>46091.18522151621</v>
       </c>
     </row>
     <row r="1716">
@@ -58781,7 +58781,7 @@
         <v>1.03</v>
       </c>
       <c r="H1716" s="2" t="n">
-        <v>46093.18522151439</v>
+        <v>46093.18522151621</v>
       </c>
     </row>
     <row r="1717">
@@ -58815,7 +58815,7 @@
         <v>0.44</v>
       </c>
       <c r="H1717" s="2" t="n">
-        <v>46085.18522151747</v>
+        <v>46085.18522151621</v>
       </c>
     </row>
     <row r="1718">
@@ -58849,7 +58849,7 @@
         <v>3.32</v>
       </c>
       <c r="H1718" s="2" t="n">
-        <v>46073.18522152056</v>
+        <v>46073.18522151621</v>
       </c>
     </row>
     <row r="1719">
@@ -58883,7 +58883,7 @@
         <v>0.36</v>
       </c>
       <c r="H1719" s="2" t="n">
-        <v>46083.18522152376</v>
+        <v>46083.18522152778</v>
       </c>
     </row>
     <row r="1720">
@@ -58917,7 +58917,7 @@
         <v>4.6</v>
       </c>
       <c r="H1720" s="2" t="n">
-        <v>46081.18522152698</v>
+        <v>46081.18522152778</v>
       </c>
     </row>
     <row r="1721">
@@ -58951,7 +58951,7 @@
         <v>1.46</v>
       </c>
       <c r="H1721" s="2" t="n">
-        <v>46094.18522153005</v>
+        <v>46094.18522152778</v>
       </c>
     </row>
     <row r="1722">
@@ -58985,7 +58985,7 @@
         <v>4.11</v>
       </c>
       <c r="H1722" s="2" t="n">
-        <v>46078.1852215332</v>
+        <v>46078.18522152778</v>
       </c>
     </row>
     <row r="1723">
@@ -59019,7 +59019,7 @@
         <v>0.96</v>
       </c>
       <c r="H1723" s="2" t="n">
-        <v>46091.18522153661</v>
+        <v>46091.18522153935</v>
       </c>
     </row>
     <row r="1724">
@@ -59053,7 +59053,7 @@
         <v>0.27</v>
       </c>
       <c r="H1724" s="2" t="n">
-        <v>46080.1852215397</v>
+        <v>46080.18522153935</v>
       </c>
     </row>
     <row r="1725">
@@ -59087,7 +59087,7 @@
         <v>0.87</v>
       </c>
       <c r="H1725" s="2" t="n">
-        <v>46084.1852215427</v>
+        <v>46084.18522153935</v>
       </c>
     </row>
     <row r="1726">
@@ -59121,7 +59121,7 @@
         <v>3.9</v>
       </c>
       <c r="H1726" s="2" t="n">
-        <v>46072.1852215459</v>
+        <v>46072.18522155093</v>
       </c>
     </row>
     <row r="1727">
@@ -59155,7 +59155,7 @@
         <v>3</v>
       </c>
       <c r="H1727" s="2" t="n">
-        <v>46069.18522154899</v>
+        <v>46069.18522155093</v>
       </c>
     </row>
     <row r="1728">
@@ -59189,7 +59189,7 @@
         <v>4.31</v>
       </c>
       <c r="H1728" s="2" t="n">
-        <v>46067.18522155219</v>
+        <v>46067.18522155093</v>
       </c>
     </row>
     <row r="1729">
@@ -59223,7 +59223,7 @@
         <v>3.75</v>
       </c>
       <c r="H1729" s="2" t="n">
-        <v>46070.1852215554</v>
+        <v>46070.18522155093</v>
       </c>
     </row>
     <row r="1730">
@@ -59257,7 +59257,7 @@
         <v>3.02</v>
       </c>
       <c r="H1730" s="2" t="n">
-        <v>46081.18522155871</v>
+        <v>46081.1852215625</v>
       </c>
     </row>
     <row r="1731">
@@ -59291,7 +59291,7 @@
         <v>4.22</v>
       </c>
       <c r="H1731" s="2" t="n">
-        <v>46087.18522156178</v>
+        <v>46087.1852215625</v>
       </c>
     </row>
     <row r="1732">
@@ -59325,7 +59325,7 @@
         <v>0.05</v>
       </c>
       <c r="H1732" s="2" t="n">
-        <v>46071.18522156496</v>
+        <v>46071.1852215625</v>
       </c>
     </row>
     <row r="1733">
@@ -59359,7 +59359,7 @@
         <v>4.96</v>
       </c>
       <c r="H1733" s="2" t="n">
-        <v>46070.18522156811</v>
+        <v>46070.1852215625</v>
       </c>
     </row>
     <row r="1734">
@@ -59393,7 +59393,7 @@
         <v>3.94</v>
       </c>
       <c r="H1734" s="2" t="n">
-        <v>46095.18522157139</v>
+        <v>46095.18522157407</v>
       </c>
     </row>
     <row r="1735">
@@ -59427,7 +59427,7 @@
         <v>4.75</v>
       </c>
       <c r="H1735" s="2" t="n">
-        <v>46074.18522157448</v>
+        <v>46074.18522157407</v>
       </c>
     </row>
     <row r="1736">
@@ -59461,7 +59461,7 @@
         <v>3.18</v>
       </c>
       <c r="H1736" s="2" t="n">
-        <v>46084.18522157765</v>
+        <v>46084.18522157407</v>
       </c>
     </row>
     <row r="1737">
@@ -59495,7 +59495,7 @@
         <v>1.52</v>
       </c>
       <c r="H1737" s="2" t="n">
-        <v>46093.18522158083</v>
+        <v>46093.18522158565</v>
       </c>
     </row>
     <row r="1738">
@@ -59529,7 +59529,7 @@
         <v>1.8</v>
       </c>
       <c r="H1738" s="2" t="n">
-        <v>46082.18522158402</v>
+        <v>46082.18522158565</v>
       </c>
     </row>
     <row r="1739">
@@ -59563,7 +59563,7 @@
         <v>0.28</v>
       </c>
       <c r="H1739" s="2" t="n">
-        <v>46084.18522158715</v>
+        <v>46084.18522158565</v>
       </c>
     </row>
     <row r="1740">
@@ -59597,7 +59597,7 @@
         <v>4.46</v>
       </c>
       <c r="H1740" s="2" t="n">
-        <v>46081.18522159017</v>
+        <v>46081.18522158565</v>
       </c>
     </row>
     <row r="1741">
@@ -59631,7 +59631,7 @@
         <v>4.51</v>
       </c>
       <c r="H1741" s="2" t="n">
-        <v>46092.18522159343</v>
+        <v>46092.18522159722</v>
       </c>
     </row>
     <row r="1742">
@@ -59665,7 +59665,7 @@
         <v>3.39</v>
       </c>
       <c r="H1742" s="2" t="n">
-        <v>46091.18522159647</v>
+        <v>46091.18522159722</v>
       </c>
     </row>
     <row r="1743">
@@ -59699,7 +59699,7 @@
         <v>0.15</v>
       </c>
       <c r="H1743" s="2" t="n">
-        <v>46089.18522159955</v>
+        <v>46089.18522159722</v>
       </c>
     </row>
     <row r="1744">
@@ -59733,7 +59733,7 @@
         <v>0.41</v>
       </c>
       <c r="H1744" s="2" t="n">
-        <v>46076.18522160258</v>
+        <v>46076.18522159722</v>
       </c>
     </row>
     <row r="1745">
@@ -59767,7 +59767,7 @@
         <v>0.95</v>
       </c>
       <c r="H1745" s="2" t="n">
-        <v>46089.18522160593</v>
+        <v>46089.18522160879</v>
       </c>
     </row>
     <row r="1746">
@@ -59801,7 +59801,7 @@
         <v>0.66</v>
       </c>
       <c r="H1746" s="2" t="n">
-        <v>46074.18522160903</v>
+        <v>46074.18522160879</v>
       </c>
     </row>
     <row r="1747">
@@ -59835,7 +59835,7 @@
         <v>0.2</v>
       </c>
       <c r="H1747" s="2" t="n">
-        <v>46083.18522161206</v>
+        <v>46083.18522160879</v>
       </c>
     </row>
     <row r="1748">
@@ -59869,7 +59869,7 @@
         <v>3.96</v>
       </c>
       <c r="H1748" s="2" t="n">
-        <v>46067.1852216153</v>
+        <v>46067.18522162037</v>
       </c>
     </row>
     <row r="1749">
@@ -59903,7 +59903,7 @@
         <v>2.95</v>
       </c>
       <c r="H1749" s="2" t="n">
-        <v>46072.18522161854</v>
+        <v>46072.18522162037</v>
       </c>
     </row>
     <row r="1750">
@@ -59937,7 +59937,7 @@
         <v>1.76</v>
       </c>
       <c r="H1750" s="2" t="n">
-        <v>46072.18522162154</v>
+        <v>46072.18522162037</v>
       </c>
     </row>
     <row r="1751">
@@ -59971,7 +59971,1707 @@
         <v>0.28</v>
       </c>
       <c r="H1751" s="2" t="n">
-        <v>46092.1852216246</v>
+        <v>46092.18522162037</v>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" t="inlineStr">
+        <is>
+          <t>9170c1a3-49ac-4096-8f62-8b2343897fc3</t>
+        </is>
+      </c>
+      <c r="B1752" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1752" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1752" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1752" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1752" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="G1752" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H1752" s="2" t="n">
+        <v>46088.23563889218</v>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" t="inlineStr">
+        <is>
+          <t>e296c0d2-7e2d-4794-acf1-d5e4421841d5</t>
+        </is>
+      </c>
+      <c r="B1753" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1753" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1753" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1753" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1753" t="n">
+        <v>420.79</v>
+      </c>
+      <c r="G1753" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="H1753" s="2" t="n">
+        <v>46090.23563889649</v>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" t="inlineStr">
+        <is>
+          <t>74afb41f-0b93-40ff-a9fd-99c168e556e8</t>
+        </is>
+      </c>
+      <c r="B1754" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1754" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1754" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1754" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1754" t="n">
+        <v>332.33</v>
+      </c>
+      <c r="G1754" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="H1754" s="2" t="n">
+        <v>46070.23563889977</v>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" t="inlineStr">
+        <is>
+          <t>309975ad-3945-4359-ac5a-1c4708531910</t>
+        </is>
+      </c>
+      <c r="B1755" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1755" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1755" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1755" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1755" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="G1755" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H1755" s="2" t="n">
+        <v>46069.23563890303</v>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" t="inlineStr">
+        <is>
+          <t>3e705212-95fa-4880-9718-7c822acdfc81</t>
+        </is>
+      </c>
+      <c r="B1756" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1756" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1756" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1756" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1756" t="n">
+        <v>158.03</v>
+      </c>
+      <c r="G1756" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H1756" s="2" t="n">
+        <v>46092.2356389063</v>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" t="inlineStr">
+        <is>
+          <t>93c4aec4-4b3a-4f6a-bc3e-37905c7c39fc</t>
+        </is>
+      </c>
+      <c r="B1757" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1757" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1757" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1757" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1757" t="n">
+        <v>398.14</v>
+      </c>
+      <c r="G1757" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="H1757" s="2" t="n">
+        <v>46093.2356389095</v>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" t="inlineStr">
+        <is>
+          <t>c0cfd944-c7cd-4ca1-9deb-08176c2352d6</t>
+        </is>
+      </c>
+      <c r="B1758" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1758" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1758" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1758" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1758" t="n">
+        <v>282.08</v>
+      </c>
+      <c r="G1758" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H1758" s="2" t="n">
+        <v>46079.23563891259</v>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" t="inlineStr">
+        <is>
+          <t>bae82fd6-0baf-466c-8e7c-3ea79860b08e</t>
+        </is>
+      </c>
+      <c r="B1759" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1759" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1759" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1759" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1759" t="n">
+        <v>344.91</v>
+      </c>
+      <c r="G1759" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H1759" s="2" t="n">
+        <v>46084.23563891614</v>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" t="inlineStr">
+        <is>
+          <t>25c0c2b8-392c-4765-a339-cb3086ab747b</t>
+        </is>
+      </c>
+      <c r="B1760" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1760" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1760" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1760" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1760" t="n">
+        <v>272.21</v>
+      </c>
+      <c r="G1760" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H1760" s="2" t="n">
+        <v>46085.23563891928</v>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" t="inlineStr">
+        <is>
+          <t>dce08e91-42b2-4729-a4e0-5c1d7c860654</t>
+        </is>
+      </c>
+      <c r="B1761" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1761" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1761" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1761" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1761" t="n">
+        <v>413.81</v>
+      </c>
+      <c r="G1761" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H1761" s="2" t="n">
+        <v>46094.23563892239</v>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" t="inlineStr">
+        <is>
+          <t>12c64a62-689d-4657-9b7d-84f5ffde97c6</t>
+        </is>
+      </c>
+      <c r="B1762" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1762" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1762" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1762" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1762" t="n">
+        <v>47.78</v>
+      </c>
+      <c r="G1762" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H1762" s="2" t="n">
+        <v>46074.23563892567</v>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" t="inlineStr">
+        <is>
+          <t>f9d666aa-c4de-43a8-9fa3-7865d5fccc56</t>
+        </is>
+      </c>
+      <c r="B1763" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1763" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1763" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1763" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1763" t="n">
+        <v>166.7</v>
+      </c>
+      <c r="G1763" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H1763" s="2" t="n">
+        <v>46095.23563892905</v>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" t="inlineStr">
+        <is>
+          <t>27fe8019-fd17-4109-b75a-128ed57b18fa</t>
+        </is>
+      </c>
+      <c r="B1764" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1764" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1764" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1764" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1764" t="n">
+        <v>436.34</v>
+      </c>
+      <c r="G1764" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="H1764" s="2" t="n">
+        <v>46096.23563893232</v>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" t="inlineStr">
+        <is>
+          <t>17ee1e1e-5681-422b-89e0-b3484743d9fc</t>
+        </is>
+      </c>
+      <c r="B1765" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1765" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1765" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1765" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1765" t="n">
+        <v>176.14</v>
+      </c>
+      <c r="G1765" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H1765" s="2" t="n">
+        <v>46093.23563893538</v>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" t="inlineStr">
+        <is>
+          <t>2634c01f-3652-4f11-9402-abde766bbb0f</t>
+        </is>
+      </c>
+      <c r="B1766" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1766" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1766" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1766" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1766" t="n">
+        <v>221.57</v>
+      </c>
+      <c r="G1766" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H1766" s="2" t="n">
+        <v>46092.23563893846</v>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" t="inlineStr">
+        <is>
+          <t>d4f38b3c-241b-46aa-8d95-9f7aedd15fe4</t>
+        </is>
+      </c>
+      <c r="B1767" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1767" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1767" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1767" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1767" t="n">
+        <v>219.94</v>
+      </c>
+      <c r="G1767" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H1767" s="2" t="n">
+        <v>46075.2356389419</v>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" t="inlineStr">
+        <is>
+          <t>11c08e16-1dce-482f-ad40-d8be8b67cdbf</t>
+        </is>
+      </c>
+      <c r="B1768" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1768" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1768" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1768" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1768" t="n">
+        <v>459.51</v>
+      </c>
+      <c r="G1768" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H1768" s="2" t="n">
+        <v>46083.23563894499</v>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" t="inlineStr">
+        <is>
+          <t>2d02b18a-3ade-402f-bf3b-9e23c29e5d3e</t>
+        </is>
+      </c>
+      <c r="B1769" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1769" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1769" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1769" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1769" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="G1769" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H1769" s="2" t="n">
+        <v>46094.23563894818</v>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="A1770" t="inlineStr">
+        <is>
+          <t>bd660620-205f-4836-9c1e-2ed6c5f3abc5</t>
+        </is>
+      </c>
+      <c r="B1770" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1770" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1770" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1770" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1770" t="n">
+        <v>396.19</v>
+      </c>
+      <c r="G1770" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="H1770" s="2" t="n">
+        <v>46074.23563895162</v>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" t="inlineStr">
+        <is>
+          <t>b110d69b-4f13-47ee-8847-fa4568bba672</t>
+        </is>
+      </c>
+      <c r="B1771" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1771" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1771" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1771" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1771" t="n">
+        <v>159</v>
+      </c>
+      <c r="G1771" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H1771" s="2" t="n">
+        <v>46085.2356389547</v>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" t="inlineStr">
+        <is>
+          <t>c6e116af-5ee1-4d4a-a1b3-1118a5b9a178</t>
+        </is>
+      </c>
+      <c r="B1772" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1772" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1772" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1772" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1772" t="n">
+        <v>198.67</v>
+      </c>
+      <c r="G1772" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H1772" s="2" t="n">
+        <v>46072.23563895777</v>
+      </c>
+    </row>
+    <row r="1773">
+      <c r="A1773" t="inlineStr">
+        <is>
+          <t>7ee40d22-1f4f-4583-9500-9dcb76fe803b</t>
+        </is>
+      </c>
+      <c r="B1773" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1773" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1773" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1773" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1773" t="n">
+        <v>434.71</v>
+      </c>
+      <c r="G1773" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="H1773" s="2" t="n">
+        <v>46080.23563896103</v>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" t="inlineStr">
+        <is>
+          <t>11be0600-7eb2-41dc-883c-5d6090a9087c</t>
+        </is>
+      </c>
+      <c r="B1774" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1774" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1774" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1774" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1774" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="G1774" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H1774" s="2" t="n">
+        <v>46072.23563896459</v>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" t="inlineStr">
+        <is>
+          <t>7e3b4db0-f84f-4eb6-9510-e8aac1dddf25</t>
+        </is>
+      </c>
+      <c r="B1775" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1775" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1775" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1775" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1775" t="n">
+        <v>384.89</v>
+      </c>
+      <c r="G1775" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H1775" s="2" t="n">
+        <v>46069.23563896763</v>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" t="inlineStr">
+        <is>
+          <t>4f9aea4b-0c8d-405c-8433-600df2917004</t>
+        </is>
+      </c>
+      <c r="B1776" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1776" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1776" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1776" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1776" t="n">
+        <v>116.56</v>
+      </c>
+      <c r="G1776" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H1776" s="2" t="n">
+        <v>46069.23563897067</v>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" t="inlineStr">
+        <is>
+          <t>401392e4-960b-49f7-bfdd-07258dfd613e</t>
+        </is>
+      </c>
+      <c r="B1777" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1777" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1777" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1777" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1777" t="n">
+        <v>483.77</v>
+      </c>
+      <c r="G1777" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="H1777" s="2" t="n">
+        <v>46070.23563897398</v>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" t="inlineStr">
+        <is>
+          <t>5d5483b9-ee6e-4948-a0c2-7b561658513b</t>
+        </is>
+      </c>
+      <c r="B1778" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1778" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1778" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1778" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1778" t="n">
+        <v>17.84</v>
+      </c>
+      <c r="G1778" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H1778" s="2" t="n">
+        <v>46077.23563897709</v>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="A1779" t="inlineStr">
+        <is>
+          <t>ed14d143-ae93-484f-95bb-f116b5c90a01</t>
+        </is>
+      </c>
+      <c r="B1779" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1779" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1779" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1779" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1779" t="n">
+        <v>185.38</v>
+      </c>
+      <c r="G1779" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H1779" s="2" t="n">
+        <v>46088.23563898017</v>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" t="inlineStr">
+        <is>
+          <t>d941bab9-52f1-4092-9841-a7d35ae84bd1</t>
+        </is>
+      </c>
+      <c r="B1780" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1780" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1780" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1780" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1780" t="n">
+        <v>51.68</v>
+      </c>
+      <c r="G1780" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H1780" s="2" t="n">
+        <v>46068.23563898334</v>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" t="inlineStr">
+        <is>
+          <t>060cd397-9116-416f-8aa7-a068b6214d57</t>
+        </is>
+      </c>
+      <c r="B1781" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1781" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1781" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1781" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1781" t="n">
+        <v>410.01</v>
+      </c>
+      <c r="G1781" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H1781" s="2" t="n">
+        <v>46078.23563898659</v>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" t="inlineStr">
+        <is>
+          <t>b200f386-6524-48b2-a742-872dc159a39e</t>
+        </is>
+      </c>
+      <c r="B1782" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1782" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1782" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1782" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1782" t="n">
+        <v>263.63</v>
+      </c>
+      <c r="G1782" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H1782" s="2" t="n">
+        <v>46083.23563898979</v>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="A1783" t="inlineStr">
+        <is>
+          <t>d0f5c278-22ae-4133-af70-2cda565a1164</t>
+        </is>
+      </c>
+      <c r="B1783" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1783" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1783" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1783" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1783" t="n">
+        <v>476.14</v>
+      </c>
+      <c r="G1783" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="H1783" s="2" t="n">
+        <v>46067.23563899301</v>
+      </c>
+    </row>
+    <row r="1784">
+      <c r="A1784" t="inlineStr">
+        <is>
+          <t>3a6c35cf-7172-4b73-8bcd-867ea1c5358d</t>
+        </is>
+      </c>
+      <c r="B1784" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1784" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1784" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1784" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1784" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="G1784" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H1784" s="2" t="n">
+        <v>46072.23563899614</v>
+      </c>
+    </row>
+    <row r="1785">
+      <c r="A1785" t="inlineStr">
+        <is>
+          <t>3ce9dee6-577f-4c46-b3f0-9459bf39048b</t>
+        </is>
+      </c>
+      <c r="B1785" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1785" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1785" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1785" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1785" t="n">
+        <v>95.87</v>
+      </c>
+      <c r="G1785" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H1785" s="2" t="n">
+        <v>46069.23563899941</v>
+      </c>
+    </row>
+    <row r="1786">
+      <c r="A1786" t="inlineStr">
+        <is>
+          <t>eac6d24d-5ce9-42e5-8402-1346ecbc5adf</t>
+        </is>
+      </c>
+      <c r="B1786" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1786" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1786" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1786" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1786" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="G1786" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H1786" s="2" t="n">
+        <v>46069.23563900251</v>
+      </c>
+    </row>
+    <row r="1787">
+      <c r="A1787" t="inlineStr">
+        <is>
+          <t>98c9891a-f135-435f-8625-5bf2356d80d8</t>
+        </is>
+      </c>
+      <c r="B1787" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1787" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1787" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1787" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1787" t="n">
+        <v>372.04</v>
+      </c>
+      <c r="G1787" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="H1787" s="2" t="n">
+        <v>46068.23563900564</v>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" t="inlineStr">
+        <is>
+          <t>543d97e5-a22a-4276-8b0f-9ec6eb408028</t>
+        </is>
+      </c>
+      <c r="B1788" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1788" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1788" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1788" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1788" t="n">
+        <v>83.56</v>
+      </c>
+      <c r="G1788" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H1788" s="2" t="n">
+        <v>46067.23563900893</v>
+      </c>
+    </row>
+    <row r="1789">
+      <c r="A1789" t="inlineStr">
+        <is>
+          <t>86a1dc05-25d8-4ed1-8c8c-f3a46379ddf2</t>
+        </is>
+      </c>
+      <c r="B1789" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1789" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1789" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1789" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1789" t="n">
+        <v>177.24</v>
+      </c>
+      <c r="G1789" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H1789" s="2" t="n">
+        <v>46096.23563901213</v>
+      </c>
+    </row>
+    <row r="1790">
+      <c r="A1790" t="inlineStr">
+        <is>
+          <t>f7a792c3-13e8-46eb-b89b-6277ab4aa0a1</t>
+        </is>
+      </c>
+      <c r="B1790" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1790" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1790" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1790" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1790" t="n">
+        <v>264.02</v>
+      </c>
+      <c r="G1790" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H1790" s="2" t="n">
+        <v>46073.23563901529</v>
+      </c>
+    </row>
+    <row r="1791">
+      <c r="A1791" t="inlineStr">
+        <is>
+          <t>e4d30515-7fae-41b8-ba0c-0d3f0a8bcc21</t>
+        </is>
+      </c>
+      <c r="B1791" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1791" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1791" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1791" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1791" t="n">
+        <v>253.33</v>
+      </c>
+      <c r="G1791" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="H1791" s="2" t="n">
+        <v>46072.23563901853</v>
+      </c>
+    </row>
+    <row r="1792">
+      <c r="A1792" t="inlineStr">
+        <is>
+          <t>d14ade62-f764-487b-be12-7082714670a2</t>
+        </is>
+      </c>
+      <c r="B1792" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1792" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1792" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1792" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1792" t="n">
+        <v>180.19</v>
+      </c>
+      <c r="G1792" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H1792" s="2" t="n">
+        <v>46067.23563902177</v>
+      </c>
+    </row>
+    <row r="1793">
+      <c r="A1793" t="inlineStr">
+        <is>
+          <t>070eff3b-2627-4eb9-9830-9728777ba993</t>
+        </is>
+      </c>
+      <c r="B1793" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1793" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1793" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1793" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1793" t="n">
+        <v>477.47</v>
+      </c>
+      <c r="G1793" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="H1793" s="2" t="n">
+        <v>46096.23563902505</v>
+      </c>
+    </row>
+    <row r="1794">
+      <c r="A1794" t="inlineStr">
+        <is>
+          <t>067ba303-2e1f-440d-b282-609925848884</t>
+        </is>
+      </c>
+      <c r="B1794" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1794" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1794" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1794" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1794" t="n">
+        <v>412.4</v>
+      </c>
+      <c r="G1794" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="H1794" s="2" t="n">
+        <v>46076.2356390281</v>
+      </c>
+    </row>
+    <row r="1795">
+      <c r="A1795" t="inlineStr">
+        <is>
+          <t>c1c850de-9c05-4e3c-a681-66c9f6257780</t>
+        </is>
+      </c>
+      <c r="B1795" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1795" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1795" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1795" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1795" t="n">
+        <v>49.95</v>
+      </c>
+      <c r="G1795" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1795" s="2" t="n">
+        <v>46095.23563903131</v>
+      </c>
+    </row>
+    <row r="1796">
+      <c r="A1796" t="inlineStr">
+        <is>
+          <t>4a98c36d-6ad8-42d6-9f86-8b6bcd2bc3e8</t>
+        </is>
+      </c>
+      <c r="B1796" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1796" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1796" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1796" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1796" t="n">
+        <v>17.56</v>
+      </c>
+      <c r="G1796" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H1796" s="2" t="n">
+        <v>46094.23563903548</v>
+      </c>
+    </row>
+    <row r="1797">
+      <c r="A1797" t="inlineStr">
+        <is>
+          <t>6444ecc5-7444-4971-8cfe-63fe21a8719f</t>
+        </is>
+      </c>
+      <c r="B1797" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1797" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1797" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1797" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1797" t="n">
+        <v>162.65</v>
+      </c>
+      <c r="G1797" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H1797" s="2" t="n">
+        <v>46090.23563903856</v>
+      </c>
+    </row>
+    <row r="1798">
+      <c r="A1798" t="inlineStr">
+        <is>
+          <t>f1188708-c6c6-42ae-affd-e5a13c8ec51a</t>
+        </is>
+      </c>
+      <c r="B1798" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1798" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1798" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1798" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1798" t="n">
+        <v>282</v>
+      </c>
+      <c r="G1798" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H1798" s="2" t="n">
+        <v>46072.23563904161</v>
+      </c>
+    </row>
+    <row r="1799">
+      <c r="A1799" t="inlineStr">
+        <is>
+          <t>7ea5d8ab-8fe9-4c66-9331-654bfd286b63</t>
+        </is>
+      </c>
+      <c r="B1799" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1799" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1799" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1799" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1799" t="n">
+        <v>84.02</v>
+      </c>
+      <c r="G1799" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H1799" s="2" t="n">
+        <v>46079.23563904529</v>
+      </c>
+    </row>
+    <row r="1800">
+      <c r="A1800" t="inlineStr">
+        <is>
+          <t>ce63100e-276e-447c-8b35-2088592499f9</t>
+        </is>
+      </c>
+      <c r="B1800" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1800" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1800" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1800" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1800" t="n">
+        <v>303.88</v>
+      </c>
+      <c r="G1800" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="H1800" s="2" t="n">
+        <v>46068.23563904837</v>
+      </c>
+    </row>
+    <row r="1801">
+      <c r="A1801" t="inlineStr">
+        <is>
+          <t>592cd027-c468-4054-824b-dbc7b81af69a</t>
+        </is>
+      </c>
+      <c r="B1801" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1801" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1801" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1801" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1801" t="n">
+        <v>408.97</v>
+      </c>
+      <c r="G1801" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="H1801" s="2" t="n">
+        <v>46068.23563905143</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1801"/>
+  <dimension ref="A1:H1851"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60005,7 +60005,7 @@
         <v>0.14</v>
       </c>
       <c r="H1752" s="2" t="n">
-        <v>46088.23563889218</v>
+        <v>46088.23563888889</v>
       </c>
     </row>
     <row r="1753">
@@ -60039,7 +60039,7 @@
         <v>4.21</v>
       </c>
       <c r="H1753" s="2" t="n">
-        <v>46090.23563889649</v>
+        <v>46090.23563890046</v>
       </c>
     </row>
     <row r="1754">
@@ -60073,7 +60073,7 @@
         <v>3.32</v>
       </c>
       <c r="H1754" s="2" t="n">
-        <v>46070.23563889977</v>
+        <v>46070.23563890046</v>
       </c>
     </row>
     <row r="1755">
@@ -60107,7 +60107,7 @@
         <v>0.15</v>
       </c>
       <c r="H1755" s="2" t="n">
-        <v>46069.23563890303</v>
+        <v>46069.23563890046</v>
       </c>
     </row>
     <row r="1756">
@@ -60141,7 +60141,7 @@
         <v>1.58</v>
       </c>
       <c r="H1756" s="2" t="n">
-        <v>46092.2356389063</v>
+        <v>46092.23563891204</v>
       </c>
     </row>
     <row r="1757">
@@ -60175,7 +60175,7 @@
         <v>3.98</v>
       </c>
       <c r="H1757" s="2" t="n">
-        <v>46093.2356389095</v>
+        <v>46093.23563891204</v>
       </c>
     </row>
     <row r="1758">
@@ -60209,7 +60209,7 @@
         <v>2.82</v>
       </c>
       <c r="H1758" s="2" t="n">
-        <v>46079.23563891259</v>
+        <v>46079.23563891204</v>
       </c>
     </row>
     <row r="1759">
@@ -60243,7 +60243,7 @@
         <v>3.45</v>
       </c>
       <c r="H1759" s="2" t="n">
-        <v>46084.23563891614</v>
+        <v>46084.23563891204</v>
       </c>
     </row>
     <row r="1760">
@@ -60277,7 +60277,7 @@
         <v>2.72</v>
       </c>
       <c r="H1760" s="2" t="n">
-        <v>46085.23563891928</v>
+        <v>46085.23563892361</v>
       </c>
     </row>
     <row r="1761">
@@ -60311,7 +60311,7 @@
         <v>4.14</v>
       </c>
       <c r="H1761" s="2" t="n">
-        <v>46094.23563892239</v>
+        <v>46094.23563892361</v>
       </c>
     </row>
     <row r="1762">
@@ -60345,7 +60345,7 @@
         <v>0.48</v>
       </c>
       <c r="H1762" s="2" t="n">
-        <v>46074.23563892567</v>
+        <v>46074.23563892361</v>
       </c>
     </row>
     <row r="1763">
@@ -60379,7 +60379,7 @@
         <v>1.67</v>
       </c>
       <c r="H1763" s="2" t="n">
-        <v>46095.23563892905</v>
+        <v>46095.23563892361</v>
       </c>
     </row>
     <row r="1764">
@@ -60413,7 +60413,7 @@
         <v>4.36</v>
       </c>
       <c r="H1764" s="2" t="n">
-        <v>46096.23563893232</v>
+        <v>46096.23563893518</v>
       </c>
     </row>
     <row r="1765">
@@ -60447,7 +60447,7 @@
         <v>1.76</v>
       </c>
       <c r="H1765" s="2" t="n">
-        <v>46093.23563893538</v>
+        <v>46093.23563893518</v>
       </c>
     </row>
     <row r="1766">
@@ -60481,7 +60481,7 @@
         <v>2.22</v>
       </c>
       <c r="H1766" s="2" t="n">
-        <v>46092.23563893846</v>
+        <v>46092.23563893518</v>
       </c>
     </row>
     <row r="1767">
@@ -60515,7 +60515,7 @@
         <v>2.2</v>
       </c>
       <c r="H1767" s="2" t="n">
-        <v>46075.2356389419</v>
+        <v>46075.23563894676</v>
       </c>
     </row>
     <row r="1768">
@@ -60549,7 +60549,7 @@
         <v>4.6</v>
       </c>
       <c r="H1768" s="2" t="n">
-        <v>46083.23563894499</v>
+        <v>46083.23563894676</v>
       </c>
     </row>
     <row r="1769">
@@ -60583,7 +60583,7 @@
         <v>0.72</v>
       </c>
       <c r="H1769" s="2" t="n">
-        <v>46094.23563894818</v>
+        <v>46094.23563894676</v>
       </c>
     </row>
     <row r="1770">
@@ -60617,7 +60617,7 @@
         <v>3.96</v>
       </c>
       <c r="H1770" s="2" t="n">
-        <v>46074.23563895162</v>
+        <v>46074.23563894676</v>
       </c>
     </row>
     <row r="1771">
@@ -60651,7 +60651,7 @@
         <v>1.59</v>
       </c>
       <c r="H1771" s="2" t="n">
-        <v>46085.2356389547</v>
+        <v>46085.23563895834</v>
       </c>
     </row>
     <row r="1772">
@@ -60685,7 +60685,7 @@
         <v>1.99</v>
       </c>
       <c r="H1772" s="2" t="n">
-        <v>46072.23563895777</v>
+        <v>46072.23563895834</v>
       </c>
     </row>
     <row r="1773">
@@ -60719,7 +60719,7 @@
         <v>4.35</v>
       </c>
       <c r="H1773" s="2" t="n">
-        <v>46080.23563896103</v>
+        <v>46080.23563895834</v>
       </c>
     </row>
     <row r="1774">
@@ -60753,7 +60753,7 @@
         <v>0.1</v>
       </c>
       <c r="H1774" s="2" t="n">
-        <v>46072.23563896459</v>
+        <v>46072.23563896991</v>
       </c>
     </row>
     <row r="1775">
@@ -60787,7 +60787,7 @@
         <v>3.85</v>
       </c>
       <c r="H1775" s="2" t="n">
-        <v>46069.23563896763</v>
+        <v>46069.23563896991</v>
       </c>
     </row>
     <row r="1776">
@@ -60821,7 +60821,7 @@
         <v>1.17</v>
       </c>
       <c r="H1776" s="2" t="n">
-        <v>46069.23563897067</v>
+        <v>46069.23563896991</v>
       </c>
     </row>
     <row r="1777">
@@ -60855,7 +60855,7 @@
         <v>4.84</v>
       </c>
       <c r="H1777" s="2" t="n">
-        <v>46070.23563897398</v>
+        <v>46070.23563896991</v>
       </c>
     </row>
     <row r="1778">
@@ -60889,7 +60889,7 @@
         <v>0.18</v>
       </c>
       <c r="H1778" s="2" t="n">
-        <v>46077.23563897709</v>
+        <v>46077.23563898148</v>
       </c>
     </row>
     <row r="1779">
@@ -60923,7 +60923,7 @@
         <v>1.85</v>
       </c>
       <c r="H1779" s="2" t="n">
-        <v>46088.23563898017</v>
+        <v>46088.23563898148</v>
       </c>
     </row>
     <row r="1780">
@@ -60957,7 +60957,7 @@
         <v>0.52</v>
       </c>
       <c r="H1780" s="2" t="n">
-        <v>46068.23563898334</v>
+        <v>46068.23563898148</v>
       </c>
     </row>
     <row r="1781">
@@ -60991,7 +60991,7 @@
         <v>4.1</v>
       </c>
       <c r="H1781" s="2" t="n">
-        <v>46078.23563898659</v>
+        <v>46078.23563898148</v>
       </c>
     </row>
     <row r="1782">
@@ -61025,7 +61025,7 @@
         <v>2.64</v>
       </c>
       <c r="H1782" s="2" t="n">
-        <v>46083.23563898979</v>
+        <v>46083.23563899306</v>
       </c>
     </row>
     <row r="1783">
@@ -61059,7 +61059,7 @@
         <v>4.76</v>
       </c>
       <c r="H1783" s="2" t="n">
-        <v>46067.23563899301</v>
+        <v>46067.23563899306</v>
       </c>
     </row>
     <row r="1784">
@@ -61093,7 +61093,7 @@
         <v>0.32</v>
       </c>
       <c r="H1784" s="2" t="n">
-        <v>46072.23563899614</v>
+        <v>46072.23563899306</v>
       </c>
     </row>
     <row r="1785">
@@ -61127,7 +61127,7 @@
         <v>0.96</v>
       </c>
       <c r="H1785" s="2" t="n">
-        <v>46069.23563899941</v>
+        <v>46069.23563900463</v>
       </c>
     </row>
     <row r="1786">
@@ -61161,7 +61161,7 @@
         <v>0.05</v>
       </c>
       <c r="H1786" s="2" t="n">
-        <v>46069.23563900251</v>
+        <v>46069.23563900463</v>
       </c>
     </row>
     <row r="1787">
@@ -61195,7 +61195,7 @@
         <v>3.72</v>
       </c>
       <c r="H1787" s="2" t="n">
-        <v>46068.23563900564</v>
+        <v>46068.23563900463</v>
       </c>
     </row>
     <row r="1788">
@@ -61229,7 +61229,7 @@
         <v>0.84</v>
       </c>
       <c r="H1788" s="2" t="n">
-        <v>46067.23563900893</v>
+        <v>46067.23563900463</v>
       </c>
     </row>
     <row r="1789">
@@ -61263,7 +61263,7 @@
         <v>1.77</v>
       </c>
       <c r="H1789" s="2" t="n">
-        <v>46096.23563901213</v>
+        <v>46096.2356390162</v>
       </c>
     </row>
     <row r="1790">
@@ -61297,7 +61297,7 @@
         <v>2.64</v>
       </c>
       <c r="H1790" s="2" t="n">
-        <v>46073.23563901529</v>
+        <v>46073.2356390162</v>
       </c>
     </row>
     <row r="1791">
@@ -61331,7 +61331,7 @@
         <v>2.53</v>
       </c>
       <c r="H1791" s="2" t="n">
-        <v>46072.23563901853</v>
+        <v>46072.2356390162</v>
       </c>
     </row>
     <row r="1792">
@@ -61365,7 +61365,7 @@
         <v>1.8</v>
       </c>
       <c r="H1792" s="2" t="n">
-        <v>46067.23563902177</v>
+        <v>46067.2356390162</v>
       </c>
     </row>
     <row r="1793">
@@ -61399,7 +61399,7 @@
         <v>4.77</v>
       </c>
       <c r="H1793" s="2" t="n">
-        <v>46096.23563902505</v>
+        <v>46096.23563902778</v>
       </c>
     </row>
     <row r="1794">
@@ -61433,7 +61433,7 @@
         <v>4.12</v>
       </c>
       <c r="H1794" s="2" t="n">
-        <v>46076.2356390281</v>
+        <v>46076.23563902778</v>
       </c>
     </row>
     <row r="1795">
@@ -61467,7 +61467,7 @@
         <v>0.5</v>
       </c>
       <c r="H1795" s="2" t="n">
-        <v>46095.23563903131</v>
+        <v>46095.23563902778</v>
       </c>
     </row>
     <row r="1796">
@@ -61501,7 +61501,7 @@
         <v>0.18</v>
       </c>
       <c r="H1796" s="2" t="n">
-        <v>46094.23563903548</v>
+        <v>46094.23563903935</v>
       </c>
     </row>
     <row r="1797">
@@ -61535,7 +61535,7 @@
         <v>1.63</v>
       </c>
       <c r="H1797" s="2" t="n">
-        <v>46090.23563903856</v>
+        <v>46090.23563903935</v>
       </c>
     </row>
     <row r="1798">
@@ -61569,7 +61569,7 @@
         <v>2.82</v>
       </c>
       <c r="H1798" s="2" t="n">
-        <v>46072.23563904161</v>
+        <v>46072.23563903935</v>
       </c>
     </row>
     <row r="1799">
@@ -61603,7 +61603,7 @@
         <v>0.84</v>
       </c>
       <c r="H1799" s="2" t="n">
-        <v>46079.23563904529</v>
+        <v>46079.23563905092</v>
       </c>
     </row>
     <row r="1800">
@@ -61637,7 +61637,7 @@
         <v>3.04</v>
       </c>
       <c r="H1800" s="2" t="n">
-        <v>46068.23563904837</v>
+        <v>46068.23563905092</v>
       </c>
     </row>
     <row r="1801">
@@ -61671,7 +61671,1707 @@
         <v>4.09</v>
       </c>
       <c r="H1801" s="2" t="n">
-        <v>46068.23563905143</v>
+        <v>46068.23563905092</v>
+      </c>
+    </row>
+    <row r="1802">
+      <c r="A1802" t="inlineStr">
+        <is>
+          <t>235b3d11-7234-4c78-a4f7-e6cac1fa631f</t>
+        </is>
+      </c>
+      <c r="B1802" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1802" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1802" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1802" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1802" t="n">
+        <v>181.37</v>
+      </c>
+      <c r="G1802" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H1802" s="2" t="n">
+        <v>46086.275891374</v>
+      </c>
+    </row>
+    <row r="1803">
+      <c r="A1803" t="inlineStr">
+        <is>
+          <t>96e6f4b0-fd8c-4bef-8d6d-6e74c85b380a</t>
+        </is>
+      </c>
+      <c r="B1803" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1803" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1803" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1803" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1803" t="n">
+        <v>122.75</v>
+      </c>
+      <c r="G1803" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="H1803" s="2" t="n">
+        <v>46071.27589137823</v>
+      </c>
+    </row>
+    <row r="1804">
+      <c r="A1804" t="inlineStr">
+        <is>
+          <t>66dd239a-54b2-4ce9-8a63-e24729d86c9e</t>
+        </is>
+      </c>
+      <c r="B1804" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1804" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1804" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1804" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1804" t="n">
+        <v>233.51</v>
+      </c>
+      <c r="G1804" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H1804" s="2" t="n">
+        <v>46072.27589138141</v>
+      </c>
+    </row>
+    <row r="1805">
+      <c r="A1805" t="inlineStr">
+        <is>
+          <t>abba9264-795a-4643-85c0-d4701fd46654</t>
+        </is>
+      </c>
+      <c r="B1805" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1805" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1805" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1805" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1805" t="n">
+        <v>156.18</v>
+      </c>
+      <c r="G1805" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H1805" s="2" t="n">
+        <v>46071.27589138494</v>
+      </c>
+    </row>
+    <row r="1806">
+      <c r="A1806" t="inlineStr">
+        <is>
+          <t>1c958d53-edeb-4f83-b7c4-e9fe07ae64ee</t>
+        </is>
+      </c>
+      <c r="B1806" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1806" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1806" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1806" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1806" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="G1806" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H1806" s="2" t="n">
+        <v>46069.27589138811</v>
+      </c>
+    </row>
+    <row r="1807">
+      <c r="A1807" t="inlineStr">
+        <is>
+          <t>5a91d4c6-f63b-4b05-82f0-17524733a43b</t>
+        </is>
+      </c>
+      <c r="B1807" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1807" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1807" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1807" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1807" t="n">
+        <v>167.19</v>
+      </c>
+      <c r="G1807" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H1807" s="2" t="n">
+        <v>46075.27589139123</v>
+      </c>
+    </row>
+    <row r="1808">
+      <c r="A1808" t="inlineStr">
+        <is>
+          <t>3f29d64d-9c4a-4fd3-b9cf-fe8aaac6005a</t>
+        </is>
+      </c>
+      <c r="B1808" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1808" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1808" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1808" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1808" t="n">
+        <v>330.03</v>
+      </c>
+      <c r="G1808" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H1808" s="2" t="n">
+        <v>46080.27589139454</v>
+      </c>
+    </row>
+    <row r="1809">
+      <c r="A1809" t="inlineStr">
+        <is>
+          <t>3b848b4e-57b3-486c-847c-bbe64e631818</t>
+        </is>
+      </c>
+      <c r="B1809" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1809" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1809" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1809" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1809" t="n">
+        <v>356.27</v>
+      </c>
+      <c r="G1809" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="H1809" s="2" t="n">
+        <v>46085.27589139837</v>
+      </c>
+    </row>
+    <row r="1810">
+      <c r="A1810" t="inlineStr">
+        <is>
+          <t>f110d18a-5352-4f48-9222-1aa9f22ec91a</t>
+        </is>
+      </c>
+      <c r="B1810" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1810" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1810" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1810" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1810" t="n">
+        <v>65.79000000000001</v>
+      </c>
+      <c r="G1810" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H1810" s="2" t="n">
+        <v>46080.27589140169</v>
+      </c>
+    </row>
+    <row r="1811">
+      <c r="A1811" t="inlineStr">
+        <is>
+          <t>5341cd1a-f5ab-425d-8187-802e894793c4</t>
+        </is>
+      </c>
+      <c r="B1811" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1811" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1811" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1811" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1811" t="n">
+        <v>290.73</v>
+      </c>
+      <c r="G1811" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="H1811" s="2" t="n">
+        <v>46084.27589140482</v>
+      </c>
+    </row>
+    <row r="1812">
+      <c r="A1812" t="inlineStr">
+        <is>
+          <t>ed20c832-3148-446c-b14d-bc6ea65eb65b</t>
+        </is>
+      </c>
+      <c r="B1812" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1812" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1812" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1812" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1812" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="G1812" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H1812" s="2" t="n">
+        <v>46081.27589140823</v>
+      </c>
+    </row>
+    <row r="1813">
+      <c r="A1813" t="inlineStr">
+        <is>
+          <t>e689a622-3c9f-4f0c-a59d-600ffcdfa8cc</t>
+        </is>
+      </c>
+      <c r="B1813" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1813" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1813" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1813" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1813" t="n">
+        <v>306.98</v>
+      </c>
+      <c r="G1813" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="H1813" s="2" t="n">
+        <v>46095.27589141133</v>
+      </c>
+    </row>
+    <row r="1814">
+      <c r="A1814" t="inlineStr">
+        <is>
+          <t>6dc487af-7e77-4d23-a9b9-3db228a18371</t>
+        </is>
+      </c>
+      <c r="B1814" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1814" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1814" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1814" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1814" t="n">
+        <v>44.11</v>
+      </c>
+      <c r="G1814" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H1814" s="2" t="n">
+        <v>46087.27589141442</v>
+      </c>
+    </row>
+    <row r="1815">
+      <c r="A1815" t="inlineStr">
+        <is>
+          <t>4063f34c-5c30-4c20-a67e-0177ac0aa92c</t>
+        </is>
+      </c>
+      <c r="B1815" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1815" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1815" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1815" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1815" t="n">
+        <v>340.05</v>
+      </c>
+      <c r="G1815" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H1815" s="2" t="n">
+        <v>46096.27589141779</v>
+      </c>
+    </row>
+    <row r="1816">
+      <c r="A1816" t="inlineStr">
+        <is>
+          <t>c967873b-a6e3-4060-bb9f-2945774e48ea</t>
+        </is>
+      </c>
+      <c r="B1816" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1816" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1816" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1816" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1816" t="n">
+        <v>111.77</v>
+      </c>
+      <c r="G1816" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H1816" s="2" t="n">
+        <v>46078.27589142094</v>
+      </c>
+    </row>
+    <row r="1817">
+      <c r="A1817" t="inlineStr">
+        <is>
+          <t>10a3fd8a-69c9-40e3-bbfb-7042f4801d01</t>
+        </is>
+      </c>
+      <c r="B1817" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1817" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1817" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1817" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1817" t="n">
+        <v>450.46</v>
+      </c>
+      <c r="G1817" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H1817" s="2" t="n">
+        <v>46079.27589142398</v>
+      </c>
+    </row>
+    <row r="1818">
+      <c r="A1818" t="inlineStr">
+        <is>
+          <t>7a01a05b-895c-498b-9ff8-4a57efa27c97</t>
+        </is>
+      </c>
+      <c r="B1818" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1818" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1818" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1818" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1818" t="n">
+        <v>250.1</v>
+      </c>
+      <c r="G1818" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H1818" s="2" t="n">
+        <v>46089.27589142705</v>
+      </c>
+    </row>
+    <row r="1819">
+      <c r="A1819" t="inlineStr">
+        <is>
+          <t>f7f36eda-5a23-4f3a-91d6-c7f8880a740a</t>
+        </is>
+      </c>
+      <c r="B1819" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1819" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1819" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1819" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1819" t="n">
+        <v>484.61</v>
+      </c>
+      <c r="G1819" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="H1819" s="2" t="n">
+        <v>46093.27589143036</v>
+      </c>
+    </row>
+    <row r="1820">
+      <c r="A1820" t="inlineStr">
+        <is>
+          <t>c58335b4-69a7-4ca8-8099-434ee4155d62</t>
+        </is>
+      </c>
+      <c r="B1820" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1820" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1820" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1820" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1820" t="n">
+        <v>156.54</v>
+      </c>
+      <c r="G1820" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H1820" s="2" t="n">
+        <v>46067.27589143366</v>
+      </c>
+    </row>
+    <row r="1821">
+      <c r="A1821" t="inlineStr">
+        <is>
+          <t>7f18fcec-46a1-45ad-be91-e91c90f37edb</t>
+        </is>
+      </c>
+      <c r="B1821" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1821" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1821" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1821" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1821" t="n">
+        <v>129.02</v>
+      </c>
+      <c r="G1821" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H1821" s="2" t="n">
+        <v>46078.27589143672</v>
+      </c>
+    </row>
+    <row r="1822">
+      <c r="A1822" t="inlineStr">
+        <is>
+          <t>5f336d17-545c-4752-bc61-5f6bc5175d74</t>
+        </is>
+      </c>
+      <c r="B1822" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1822" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1822" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1822" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1822" t="n">
+        <v>463.93</v>
+      </c>
+      <c r="G1822" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="H1822" s="2" t="n">
+        <v>46069.27589143992</v>
+      </c>
+    </row>
+    <row r="1823">
+      <c r="A1823" t="inlineStr">
+        <is>
+          <t>1dd699b5-91b4-4bb4-bd0e-3944fbfcc136</t>
+        </is>
+      </c>
+      <c r="B1823" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1823" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1823" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1823" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1823" t="n">
+        <v>122.68</v>
+      </c>
+      <c r="G1823" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="H1823" s="2" t="n">
+        <v>46086.27589144332</v>
+      </c>
+    </row>
+    <row r="1824">
+      <c r="A1824" t="inlineStr">
+        <is>
+          <t>c6db83ed-0aa0-45c7-8454-68e4289ec1e7</t>
+        </is>
+      </c>
+      <c r="B1824" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1824" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1824" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1824" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1824" t="n">
+        <v>52.45</v>
+      </c>
+      <c r="G1824" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H1824" s="2" t="n">
+        <v>46083.27589144638</v>
+      </c>
+    </row>
+    <row r="1825">
+      <c r="A1825" t="inlineStr">
+        <is>
+          <t>eff03056-3aac-4cfe-a6e8-96d378958383</t>
+        </is>
+      </c>
+      <c r="B1825" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1825" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1825" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1825" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1825" t="n">
+        <v>122.21</v>
+      </c>
+      <c r="G1825" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H1825" s="2" t="n">
+        <v>46071.27589144961</v>
+      </c>
+    </row>
+    <row r="1826">
+      <c r="A1826" t="inlineStr">
+        <is>
+          <t>7b507908-613e-4377-ba9e-58cfdd226eb9</t>
+        </is>
+      </c>
+      <c r="B1826" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1826" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1826" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1826" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1826" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="G1826" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H1826" s="2" t="n">
+        <v>46072.2758914529</v>
+      </c>
+    </row>
+    <row r="1827">
+      <c r="A1827" t="inlineStr">
+        <is>
+          <t>1d6752ad-0d5d-47bf-9db6-04a2c6ce9aca</t>
+        </is>
+      </c>
+      <c r="B1827" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1827" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1827" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1827" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1827" t="n">
+        <v>195.3</v>
+      </c>
+      <c r="G1827" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H1827" s="2" t="n">
+        <v>46080.275891456</v>
+      </c>
+    </row>
+    <row r="1828">
+      <c r="A1828" t="inlineStr">
+        <is>
+          <t>43ffe683-6fa5-452b-9483-d24e2d8debd9</t>
+        </is>
+      </c>
+      <c r="B1828" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1828" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1828" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1828" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1828" t="n">
+        <v>171.47</v>
+      </c>
+      <c r="G1828" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H1828" s="2" t="n">
+        <v>46075.27589145905</v>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="A1829" t="inlineStr">
+        <is>
+          <t>2bd4c63b-92a8-44fd-9c2f-6729e6dbbb41</t>
+        </is>
+      </c>
+      <c r="B1829" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1829" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1829" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1829" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1829" t="n">
+        <v>397.43</v>
+      </c>
+      <c r="G1829" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="H1829" s="2" t="n">
+        <v>46069.27589146209</v>
+      </c>
+    </row>
+    <row r="1830">
+      <c r="A1830" t="inlineStr">
+        <is>
+          <t>79b76ddc-2005-4ac6-9fc8-b4f90cd03acc</t>
+        </is>
+      </c>
+      <c r="B1830" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1830" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1830" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1830" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1830" t="n">
+        <v>249.94</v>
+      </c>
+      <c r="G1830" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H1830" s="2" t="n">
+        <v>46094.27589146548</v>
+      </c>
+    </row>
+    <row r="1831">
+      <c r="A1831" t="inlineStr">
+        <is>
+          <t>7529a0fe-c618-4ed5-92ff-0dc0af763225</t>
+        </is>
+      </c>
+      <c r="B1831" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1831" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1831" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1831" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1831" t="n">
+        <v>390.04</v>
+      </c>
+      <c r="G1831" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H1831" s="2" t="n">
+        <v>46072.2758914687</v>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="A1832" t="inlineStr">
+        <is>
+          <t>356a3b0b-b08f-462b-9c33-8224cd74d953</t>
+        </is>
+      </c>
+      <c r="B1832" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1832" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1832" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1832" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1832" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="G1832" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H1832" s="2" t="n">
+        <v>46070.27589147181</v>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" t="inlineStr">
+        <is>
+          <t>c944edcb-9998-4cd3-9e83-f05722a1e985</t>
+        </is>
+      </c>
+      <c r="B1833" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1833" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1833" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1833" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1833" t="n">
+        <v>421.49</v>
+      </c>
+      <c r="G1833" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="H1833" s="2" t="n">
+        <v>46089.27589147492</v>
+      </c>
+    </row>
+    <row r="1834">
+      <c r="A1834" t="inlineStr">
+        <is>
+          <t>9c33ba9d-eb9a-4889-9bca-c4ab31d1ca5d</t>
+        </is>
+      </c>
+      <c r="B1834" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1834" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1834" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1834" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1834" t="n">
+        <v>165.67</v>
+      </c>
+      <c r="G1834" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H1834" s="2" t="n">
+        <v>46086.27589147815</v>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" t="inlineStr">
+        <is>
+          <t>71a48183-f332-4d9d-a4d9-257631c5f356</t>
+        </is>
+      </c>
+      <c r="B1835" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1835" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1835" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1835" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1835" t="n">
+        <v>297.64</v>
+      </c>
+      <c r="G1835" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H1835" s="2" t="n">
+        <v>46084.27589148129</v>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="A1836" t="inlineStr">
+        <is>
+          <t>7291fc97-1f05-4c43-a91d-084fe0b37ec4</t>
+        </is>
+      </c>
+      <c r="B1836" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1836" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1836" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1836" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1836" t="n">
+        <v>131.9</v>
+      </c>
+      <c r="G1836" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H1836" s="2" t="n">
+        <v>46096.27589148443</v>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" t="inlineStr">
+        <is>
+          <t>239080bb-3b80-4eb5-8368-0abf3f5618c3</t>
+        </is>
+      </c>
+      <c r="B1837" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1837" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1837" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1837" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1837" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="G1837" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H1837" s="2" t="n">
+        <v>46081.27589148768</v>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" t="inlineStr">
+        <is>
+          <t>6aaf2cce-13ab-48ed-9854-a6edba1c05dc</t>
+        </is>
+      </c>
+      <c r="B1838" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1838" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1838" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1838" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1838" t="n">
+        <v>140.45</v>
+      </c>
+      <c r="G1838" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H1838" s="2" t="n">
+        <v>46090.27589149073</v>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" t="inlineStr">
+        <is>
+          <t>b3351198-7b92-4a8c-a751-f5b2c9812b39</t>
+        </is>
+      </c>
+      <c r="B1839" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1839" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1839" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1839" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1839" t="n">
+        <v>83.02</v>
+      </c>
+      <c r="G1839" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H1839" s="2" t="n">
+        <v>46086.2758914939</v>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" t="inlineStr">
+        <is>
+          <t>6b1a44d1-55d4-44bc-9194-a185b2353f31</t>
+        </is>
+      </c>
+      <c r="B1840" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1840" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1840" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1840" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1840" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="G1840" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H1840" s="2" t="n">
+        <v>46073.27589149714</v>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" t="inlineStr">
+        <is>
+          <t>1a86857f-b308-4a75-aa76-57ad3b696117</t>
+        </is>
+      </c>
+      <c r="B1841" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1841" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1841" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1841" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1841" t="n">
+        <v>238.92</v>
+      </c>
+      <c r="G1841" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H1841" s="2" t="n">
+        <v>46085.27589150043</v>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" t="inlineStr">
+        <is>
+          <t>21982c69-fd13-4723-b132-aa072e9bea56</t>
+        </is>
+      </c>
+      <c r="B1842" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1842" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1842" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1842" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1842" t="n">
+        <v>444.92</v>
+      </c>
+      <c r="G1842" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="H1842" s="2" t="n">
+        <v>46080.27589150383</v>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" t="inlineStr">
+        <is>
+          <t>cec5b577-10ad-4da2-b223-ff659c100d24</t>
+        </is>
+      </c>
+      <c r="B1843" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1843" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1843" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1843" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1843" t="n">
+        <v>467.62</v>
+      </c>
+      <c r="G1843" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="H1843" s="2" t="n">
+        <v>46082.27589150686</v>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" t="inlineStr">
+        <is>
+          <t>ecf78c76-b34e-48e4-8f45-d00b3d463bcf</t>
+        </is>
+      </c>
+      <c r="B1844" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1844" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1844" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1844" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1844" t="n">
+        <v>218.25</v>
+      </c>
+      <c r="G1844" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H1844" s="2" t="n">
+        <v>46076.27589151002</v>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="A1845" t="inlineStr">
+        <is>
+          <t>9439bb2f-cd39-467f-93fe-3fc10b501b76</t>
+        </is>
+      </c>
+      <c r="B1845" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1845" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1845" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1845" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1845" t="n">
+        <v>254.58</v>
+      </c>
+      <c r="G1845" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H1845" s="2" t="n">
+        <v>46085.2758915133</v>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" t="inlineStr">
+        <is>
+          <t>da2dd4dc-f657-41d8-99bf-4692bbe891c2</t>
+        </is>
+      </c>
+      <c r="B1846" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1846" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1846" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1846" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1846" t="n">
+        <v>239.57</v>
+      </c>
+      <c r="G1846" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H1846" s="2" t="n">
+        <v>46081.27589151638</v>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" t="inlineStr">
+        <is>
+          <t>ec142984-bffb-4424-bfc8-841f464be685</t>
+        </is>
+      </c>
+      <c r="B1847" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1847" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1847" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1847" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1847" t="n">
+        <v>19.13</v>
+      </c>
+      <c r="G1847" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H1847" s="2" t="n">
+        <v>46070.27589151944</v>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" t="inlineStr">
+        <is>
+          <t>c3392225-b4c7-46f8-ab47-62a1a5b3cd28</t>
+        </is>
+      </c>
+      <c r="B1848" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1848" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1848" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1848" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1848" t="n">
+        <v>239.03</v>
+      </c>
+      <c r="G1848" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H1848" s="2" t="n">
+        <v>46091.27589152277</v>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" t="inlineStr">
+        <is>
+          <t>e928e269-a868-4aed-90ac-825c329ba67b</t>
+        </is>
+      </c>
+      <c r="B1849" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1849" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1849" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1849" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1849" t="n">
+        <v>327.14</v>
+      </c>
+      <c r="G1849" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="H1849" s="2" t="n">
+        <v>46068.27589152589</v>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" t="inlineStr">
+        <is>
+          <t>2d1bffa1-2c30-48be-9c2c-5cbf931a1454</t>
+        </is>
+      </c>
+      <c r="B1850" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1850" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1850" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1850" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1850" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="G1850" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H1850" s="2" t="n">
+        <v>46085.27589152903</v>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" t="inlineStr">
+        <is>
+          <t>e839981c-6ffd-4a01-9152-89db0f32775a</t>
+        </is>
+      </c>
+      <c r="B1851" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1851" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1851" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1851" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1851" t="n">
+        <v>452.91</v>
+      </c>
+      <c r="G1851" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="H1851" s="2" t="n">
+        <v>46094.27589153206</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1851"/>
+  <dimension ref="A1:H1901"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61705,7 +61705,7 @@
         <v>1.81</v>
       </c>
       <c r="H1802" s="2" t="n">
-        <v>46086.275891374</v>
+        <v>46086.27589137731</v>
       </c>
     </row>
     <row r="1803">
@@ -61739,7 +61739,7 @@
         <v>1.23</v>
       </c>
       <c r="H1803" s="2" t="n">
-        <v>46071.27589137823</v>
+        <v>46071.27589137731</v>
       </c>
     </row>
     <row r="1804">
@@ -61773,7 +61773,7 @@
         <v>2.34</v>
       </c>
       <c r="H1804" s="2" t="n">
-        <v>46072.27589138141</v>
+        <v>46072.27589137731</v>
       </c>
     </row>
     <row r="1805">
@@ -61807,7 +61807,7 @@
         <v>1.56</v>
       </c>
       <c r="H1805" s="2" t="n">
-        <v>46071.27589138494</v>
+        <v>46071.27589138889</v>
       </c>
     </row>
     <row r="1806">
@@ -61841,7 +61841,7 @@
         <v>0.2</v>
       </c>
       <c r="H1806" s="2" t="n">
-        <v>46069.27589138811</v>
+        <v>46069.27589138889</v>
       </c>
     </row>
     <row r="1807">
@@ -61875,7 +61875,7 @@
         <v>1.67</v>
       </c>
       <c r="H1807" s="2" t="n">
-        <v>46075.27589139123</v>
+        <v>46075.27589138889</v>
       </c>
     </row>
     <row r="1808">
@@ -61909,7 +61909,7 @@
         <v>3.3</v>
       </c>
       <c r="H1808" s="2" t="n">
-        <v>46080.27589139454</v>
+        <v>46080.27589138889</v>
       </c>
     </row>
     <row r="1809">
@@ -61943,7 +61943,7 @@
         <v>3.56</v>
       </c>
       <c r="H1809" s="2" t="n">
-        <v>46085.27589139837</v>
+        <v>46085.27589140047</v>
       </c>
     </row>
     <row r="1810">
@@ -61977,7 +61977,7 @@
         <v>0.66</v>
       </c>
       <c r="H1810" s="2" t="n">
-        <v>46080.27589140169</v>
+        <v>46080.27589140047</v>
       </c>
     </row>
     <row r="1811">
@@ -62011,7 +62011,7 @@
         <v>2.91</v>
       </c>
       <c r="H1811" s="2" t="n">
-        <v>46084.27589140482</v>
+        <v>46084.27589140047</v>
       </c>
     </row>
     <row r="1812">
@@ -62045,7 +62045,7 @@
         <v>0.89</v>
       </c>
       <c r="H1812" s="2" t="n">
-        <v>46081.27589140823</v>
+        <v>46081.27589141203</v>
       </c>
     </row>
     <row r="1813">
@@ -62079,7 +62079,7 @@
         <v>3.07</v>
       </c>
       <c r="H1813" s="2" t="n">
-        <v>46095.27589141133</v>
+        <v>46095.27589141203</v>
       </c>
     </row>
     <row r="1814">
@@ -62113,7 +62113,7 @@
         <v>0.44</v>
       </c>
       <c r="H1814" s="2" t="n">
-        <v>46087.27589141442</v>
+        <v>46087.27589141203</v>
       </c>
     </row>
     <row r="1815">
@@ -62147,7 +62147,7 @@
         <v>3.4</v>
       </c>
       <c r="H1815" s="2" t="n">
-        <v>46096.27589141779</v>
+        <v>46096.27589141203</v>
       </c>
     </row>
     <row r="1816">
@@ -62181,7 +62181,7 @@
         <v>1.12</v>
       </c>
       <c r="H1816" s="2" t="n">
-        <v>46078.27589142094</v>
+        <v>46078.27589142361</v>
       </c>
     </row>
     <row r="1817">
@@ -62215,7 +62215,7 @@
         <v>4.5</v>
       </c>
       <c r="H1817" s="2" t="n">
-        <v>46079.27589142398</v>
+        <v>46079.27589142361</v>
       </c>
     </row>
     <row r="1818">
@@ -62249,7 +62249,7 @@
         <v>2.5</v>
       </c>
       <c r="H1818" s="2" t="n">
-        <v>46089.27589142705</v>
+        <v>46089.27589142361</v>
       </c>
     </row>
     <row r="1819">
@@ -62283,7 +62283,7 @@
         <v>4.85</v>
       </c>
       <c r="H1819" s="2" t="n">
-        <v>46093.27589143036</v>
+        <v>46093.27589143519</v>
       </c>
     </row>
     <row r="1820">
@@ -62317,7 +62317,7 @@
         <v>1.57</v>
       </c>
       <c r="H1820" s="2" t="n">
-        <v>46067.27589143366</v>
+        <v>46067.27589143519</v>
       </c>
     </row>
     <row r="1821">
@@ -62351,7 +62351,7 @@
         <v>1.29</v>
       </c>
       <c r="H1821" s="2" t="n">
-        <v>46078.27589143672</v>
+        <v>46078.27589143519</v>
       </c>
     </row>
     <row r="1822">
@@ -62385,7 +62385,7 @@
         <v>4.64</v>
       </c>
       <c r="H1822" s="2" t="n">
-        <v>46069.27589143992</v>
+        <v>46069.27589143519</v>
       </c>
     </row>
     <row r="1823">
@@ -62419,7 +62419,7 @@
         <v>1.23</v>
       </c>
       <c r="H1823" s="2" t="n">
-        <v>46086.27589144332</v>
+        <v>46086.27589144676</v>
       </c>
     </row>
     <row r="1824">
@@ -62453,7 +62453,7 @@
         <v>0.52</v>
       </c>
       <c r="H1824" s="2" t="n">
-        <v>46083.27589144638</v>
+        <v>46083.27589144676</v>
       </c>
     </row>
     <row r="1825">
@@ -62487,7 +62487,7 @@
         <v>1.22</v>
       </c>
       <c r="H1825" s="2" t="n">
-        <v>46071.27589144961</v>
+        <v>46071.27589144676</v>
       </c>
     </row>
     <row r="1826">
@@ -62521,7 +62521,7 @@
         <v>0.24</v>
       </c>
       <c r="H1826" s="2" t="n">
-        <v>46072.2758914529</v>
+        <v>46072.27589145833</v>
       </c>
     </row>
     <row r="1827">
@@ -62555,7 +62555,7 @@
         <v>1.95</v>
       </c>
       <c r="H1827" s="2" t="n">
-        <v>46080.275891456</v>
+        <v>46080.27589145833</v>
       </c>
     </row>
     <row r="1828">
@@ -62589,7 +62589,7 @@
         <v>1.71</v>
       </c>
       <c r="H1828" s="2" t="n">
-        <v>46075.27589145905</v>
+        <v>46075.27589145833</v>
       </c>
     </row>
     <row r="1829">
@@ -62623,7 +62623,7 @@
         <v>3.97</v>
       </c>
       <c r="H1829" s="2" t="n">
-        <v>46069.27589146209</v>
+        <v>46069.27589145833</v>
       </c>
     </row>
     <row r="1830">
@@ -62657,7 +62657,7 @@
         <v>2.5</v>
       </c>
       <c r="H1830" s="2" t="n">
-        <v>46094.27589146548</v>
+        <v>46094.27589146991</v>
       </c>
     </row>
     <row r="1831">
@@ -62691,7 +62691,7 @@
         <v>3.9</v>
       </c>
       <c r="H1831" s="2" t="n">
-        <v>46072.2758914687</v>
+        <v>46072.27589146991</v>
       </c>
     </row>
     <row r="1832">
@@ -62725,7 +62725,7 @@
         <v>1.04</v>
       </c>
       <c r="H1832" s="2" t="n">
-        <v>46070.27589147181</v>
+        <v>46070.27589146991</v>
       </c>
     </row>
     <row r="1833">
@@ -62759,7 +62759,7 @@
         <v>4.21</v>
       </c>
       <c r="H1833" s="2" t="n">
-        <v>46089.27589147492</v>
+        <v>46089.27589146991</v>
       </c>
     </row>
     <row r="1834">
@@ -62793,7 +62793,7 @@
         <v>1.66</v>
       </c>
       <c r="H1834" s="2" t="n">
-        <v>46086.27589147815</v>
+        <v>46086.27589148148</v>
       </c>
     </row>
     <row r="1835">
@@ -62827,7 +62827,7 @@
         <v>2.98</v>
       </c>
       <c r="H1835" s="2" t="n">
-        <v>46084.27589148129</v>
+        <v>46084.27589148148</v>
       </c>
     </row>
     <row r="1836">
@@ -62861,7 +62861,7 @@
         <v>1.32</v>
       </c>
       <c r="H1836" s="2" t="n">
-        <v>46096.27589148443</v>
+        <v>46096.27589148148</v>
       </c>
     </row>
     <row r="1837">
@@ -62895,7 +62895,7 @@
         <v>0.03</v>
       </c>
       <c r="H1837" s="2" t="n">
-        <v>46081.27589148768</v>
+        <v>46081.27589149305</v>
       </c>
     </row>
     <row r="1838">
@@ -62929,7 +62929,7 @@
         <v>1.4</v>
       </c>
       <c r="H1838" s="2" t="n">
-        <v>46090.27589149073</v>
+        <v>46090.27589149305</v>
       </c>
     </row>
     <row r="1839">
@@ -62963,7 +62963,7 @@
         <v>0.83</v>
       </c>
       <c r="H1839" s="2" t="n">
-        <v>46086.2758914939</v>
+        <v>46086.27589149305</v>
       </c>
     </row>
     <row r="1840">
@@ -62997,7 +62997,7 @@
         <v>0.15</v>
       </c>
       <c r="H1840" s="2" t="n">
-        <v>46073.27589149714</v>
+        <v>46073.27589149305</v>
       </c>
     </row>
     <row r="1841">
@@ -63031,7 +63031,7 @@
         <v>2.39</v>
       </c>
       <c r="H1841" s="2" t="n">
-        <v>46085.27589150043</v>
+        <v>46085.27589150463</v>
       </c>
     </row>
     <row r="1842">
@@ -63065,7 +63065,7 @@
         <v>4.45</v>
       </c>
       <c r="H1842" s="2" t="n">
-        <v>46080.27589150383</v>
+        <v>46080.27589150463</v>
       </c>
     </row>
     <row r="1843">
@@ -63099,7 +63099,7 @@
         <v>4.68</v>
       </c>
       <c r="H1843" s="2" t="n">
-        <v>46082.27589150686</v>
+        <v>46082.27589150463</v>
       </c>
     </row>
     <row r="1844">
@@ -63133,7 +63133,7 @@
         <v>2.18</v>
       </c>
       <c r="H1844" s="2" t="n">
-        <v>46076.27589151002</v>
+        <v>46076.27589150463</v>
       </c>
     </row>
     <row r="1845">
@@ -63167,7 +63167,7 @@
         <v>2.55</v>
       </c>
       <c r="H1845" s="2" t="n">
-        <v>46085.2758915133</v>
+        <v>46085.2758915162</v>
       </c>
     </row>
     <row r="1846">
@@ -63201,7 +63201,7 @@
         <v>2.4</v>
       </c>
       <c r="H1846" s="2" t="n">
-        <v>46081.27589151638</v>
+        <v>46081.2758915162</v>
       </c>
     </row>
     <row r="1847">
@@ -63235,7 +63235,7 @@
         <v>0.19</v>
       </c>
       <c r="H1847" s="2" t="n">
-        <v>46070.27589151944</v>
+        <v>46070.2758915162</v>
       </c>
     </row>
     <row r="1848">
@@ -63269,7 +63269,7 @@
         <v>2.39</v>
       </c>
       <c r="H1848" s="2" t="n">
-        <v>46091.27589152277</v>
+        <v>46091.27589152778</v>
       </c>
     </row>
     <row r="1849">
@@ -63303,7 +63303,7 @@
         <v>3.27</v>
       </c>
       <c r="H1849" s="2" t="n">
-        <v>46068.27589152589</v>
+        <v>46068.27589152778</v>
       </c>
     </row>
     <row r="1850">
@@ -63337,7 +63337,7 @@
         <v>0.76</v>
       </c>
       <c r="H1850" s="2" t="n">
-        <v>46085.27589152903</v>
+        <v>46085.27589152778</v>
       </c>
     </row>
     <row r="1851">
@@ -63371,7 +63371,1707 @@
         <v>4.53</v>
       </c>
       <c r="H1851" s="2" t="n">
-        <v>46094.27589153206</v>
+        <v>46094.27589152778</v>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" t="inlineStr">
+        <is>
+          <t>43b64f9f-f5c9-489d-bb5b-cbf80262e775</t>
+        </is>
+      </c>
+      <c r="B1852" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1852" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1852" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1852" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1852" t="n">
+        <v>129.53</v>
+      </c>
+      <c r="G1852" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H1852" s="2" t="n">
+        <v>46092.31430924147</v>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" t="inlineStr">
+        <is>
+          <t>e9f86acf-c571-48e4-9a94-5de571c52b7d</t>
+        </is>
+      </c>
+      <c r="B1853" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1853" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1853" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1853" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1853" t="n">
+        <v>34.14</v>
+      </c>
+      <c r="G1853" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H1853" s="2" t="n">
+        <v>46069.31430924567</v>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="A1854" t="inlineStr">
+        <is>
+          <t>aa84d5be-7207-428d-b3fb-f7508d8f7987</t>
+        </is>
+      </c>
+      <c r="B1854" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1854" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1854" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1854" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1854" t="n">
+        <v>202.04</v>
+      </c>
+      <c r="G1854" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H1854" s="2" t="n">
+        <v>46070.31430924918</v>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" t="inlineStr">
+        <is>
+          <t>0c73f1e6-6b2f-4d6f-9590-3e1f5ef81877</t>
+        </is>
+      </c>
+      <c r="B1855" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1855" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1855" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1855" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1855" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="G1855" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H1855" s="2" t="n">
+        <v>46072.31430925251</v>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="A1856" t="inlineStr">
+        <is>
+          <t>9b764c7e-7326-4510-bf60-500fe4e3b219</t>
+        </is>
+      </c>
+      <c r="B1856" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1856" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1856" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1856" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1856" t="n">
+        <v>324.5</v>
+      </c>
+      <c r="G1856" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H1856" s="2" t="n">
+        <v>46081.31430925579</v>
+      </c>
+    </row>
+    <row r="1857">
+      <c r="A1857" t="inlineStr">
+        <is>
+          <t>cd308a27-e094-4370-8bed-1c443c24eebc</t>
+        </is>
+      </c>
+      <c r="B1857" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1857" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1857" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1857" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1857" t="n">
+        <v>34.52</v>
+      </c>
+      <c r="G1857" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H1857" s="2" t="n">
+        <v>46080.31430925896</v>
+      </c>
+    </row>
+    <row r="1858">
+      <c r="A1858" t="inlineStr">
+        <is>
+          <t>b983d059-f99e-4e44-9b77-e1824eeb99ef</t>
+        </is>
+      </c>
+      <c r="B1858" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1858" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1858" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1858" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1858" t="n">
+        <v>471.73</v>
+      </c>
+      <c r="G1858" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="H1858" s="2" t="n">
+        <v>46092.31430926249</v>
+      </c>
+    </row>
+    <row r="1859">
+      <c r="A1859" t="inlineStr">
+        <is>
+          <t>3b3038db-30e1-4c62-b331-4b1db6ddc522</t>
+        </is>
+      </c>
+      <c r="B1859" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1859" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1859" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1859" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1859" t="n">
+        <v>296.33</v>
+      </c>
+      <c r="G1859" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="H1859" s="2" t="n">
+        <v>46078.31430926573</v>
+      </c>
+    </row>
+    <row r="1860">
+      <c r="A1860" t="inlineStr">
+        <is>
+          <t>fa6c8de1-0be6-4b97-97bb-63a2ae26eecb</t>
+        </is>
+      </c>
+      <c r="B1860" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1860" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1860" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1860" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1860" t="n">
+        <v>16.05</v>
+      </c>
+      <c r="G1860" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H1860" s="2" t="n">
+        <v>46084.31430926901</v>
+      </c>
+    </row>
+    <row r="1861">
+      <c r="A1861" t="inlineStr">
+        <is>
+          <t>26439b6e-e4f2-46ce-875b-58754711f0dc</t>
+        </is>
+      </c>
+      <c r="B1861" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1861" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1861" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1861" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1861" t="n">
+        <v>397.6</v>
+      </c>
+      <c r="G1861" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="H1861" s="2" t="n">
+        <v>46082.31430927227</v>
+      </c>
+    </row>
+    <row r="1862">
+      <c r="A1862" t="inlineStr">
+        <is>
+          <t>3e5fb4c3-00d7-4683-b2fa-857b14c04e28</t>
+        </is>
+      </c>
+      <c r="B1862" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1862" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1862" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1862" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1862" t="n">
+        <v>334.62</v>
+      </c>
+      <c r="G1862" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H1862" s="2" t="n">
+        <v>46074.31430927559</v>
+      </c>
+    </row>
+    <row r="1863">
+      <c r="A1863" t="inlineStr">
+        <is>
+          <t>9a50a567-91d5-4ed1-b8d9-5c7bd4a13547</t>
+        </is>
+      </c>
+      <c r="B1863" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1863" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1863" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1863" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1863" t="n">
+        <v>424.51</v>
+      </c>
+      <c r="G1863" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="H1863" s="2" t="n">
+        <v>46095.31430927875</v>
+      </c>
+    </row>
+    <row r="1864">
+      <c r="A1864" t="inlineStr">
+        <is>
+          <t>09d010bd-2d49-46a0-b8e7-be71b05928e8</t>
+        </is>
+      </c>
+      <c r="B1864" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1864" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1864" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1864" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1864" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="G1864" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H1864" s="2" t="n">
+        <v>46076.31430928207</v>
+      </c>
+    </row>
+    <row r="1865">
+      <c r="A1865" t="inlineStr">
+        <is>
+          <t>f3b95691-fecc-446f-8c91-ea92d7cac5c2</t>
+        </is>
+      </c>
+      <c r="B1865" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1865" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1865" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1865" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1865" t="n">
+        <v>139.09</v>
+      </c>
+      <c r="G1865" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H1865" s="2" t="n">
+        <v>46078.31430928535</v>
+      </c>
+    </row>
+    <row r="1866">
+      <c r="A1866" t="inlineStr">
+        <is>
+          <t>7c918f57-9203-406e-b7ba-ee20a5b8d84d</t>
+        </is>
+      </c>
+      <c r="B1866" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1866" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1866" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1866" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1866" t="n">
+        <v>82.89</v>
+      </c>
+      <c r="G1866" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H1866" s="2" t="n">
+        <v>46088.31430928847</v>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="A1867" t="inlineStr">
+        <is>
+          <t>74c79a26-6731-4fca-a084-8c7c9c1701a5</t>
+        </is>
+      </c>
+      <c r="B1867" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1867" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1867" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1867" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1867" t="n">
+        <v>186.97</v>
+      </c>
+      <c r="G1867" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H1867" s="2" t="n">
+        <v>46092.31430929169</v>
+      </c>
+    </row>
+    <row r="1868">
+      <c r="A1868" t="inlineStr">
+        <is>
+          <t>fd6bf766-6321-4f31-917e-b3d2c343054b</t>
+        </is>
+      </c>
+      <c r="B1868" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1868" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1868" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1868" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1868" t="n">
+        <v>327.61</v>
+      </c>
+      <c r="G1868" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="H1868" s="2" t="n">
+        <v>46089.31430929509</v>
+      </c>
+    </row>
+    <row r="1869">
+      <c r="A1869" t="inlineStr">
+        <is>
+          <t>5932932e-ef1e-4b81-9b4b-5289219a1071</t>
+        </is>
+      </c>
+      <c r="B1869" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1869" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1869" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1869" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1869" t="n">
+        <v>395.59</v>
+      </c>
+      <c r="G1869" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="H1869" s="2" t="n">
+        <v>46087.31430929821</v>
+      </c>
+    </row>
+    <row r="1870">
+      <c r="A1870" t="inlineStr">
+        <is>
+          <t>756643db-664f-4470-a33d-bea53aae3173</t>
+        </is>
+      </c>
+      <c r="B1870" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1870" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1870" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1870" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1870" t="n">
+        <v>220.6</v>
+      </c>
+      <c r="G1870" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="H1870" s="2" t="n">
+        <v>46093.3143093013</v>
+      </c>
+    </row>
+    <row r="1871">
+      <c r="A1871" t="inlineStr">
+        <is>
+          <t>95dc1b07-7f01-450f-9f0c-99921409053d</t>
+        </is>
+      </c>
+      <c r="B1871" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1871" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1871" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1871" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1871" t="n">
+        <v>430.72</v>
+      </c>
+      <c r="G1871" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="H1871" s="2" t="n">
+        <v>46069.31430930436</v>
+      </c>
+    </row>
+    <row r="1872">
+      <c r="A1872" t="inlineStr">
+        <is>
+          <t>f6252cc0-7331-4e30-9955-0ddc9bdc33be</t>
+        </is>
+      </c>
+      <c r="B1872" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1872" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1872" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1872" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1872" t="n">
+        <v>437.3</v>
+      </c>
+      <c r="G1872" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="H1872" s="2" t="n">
+        <v>46079.31430930771</v>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" t="inlineStr">
+        <is>
+          <t>5ffa703c-e429-4c82-9c3c-2b418eac78d5</t>
+        </is>
+      </c>
+      <c r="B1873" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1873" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1873" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1873" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1873" t="n">
+        <v>69.18000000000001</v>
+      </c>
+      <c r="G1873" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H1873" s="2" t="n">
+        <v>46074.31430931124</v>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="A1874" t="inlineStr">
+        <is>
+          <t>0a3adaf2-1cb7-4baf-9683-26086f06f87a</t>
+        </is>
+      </c>
+      <c r="B1874" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1874" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1874" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1874" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1874" t="n">
+        <v>337.61</v>
+      </c>
+      <c r="G1874" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="H1874" s="2" t="n">
+        <v>46076.31430931453</v>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="A1875" t="inlineStr">
+        <is>
+          <t>b176f2f9-d443-4b5e-92bf-def333af20bd</t>
+        </is>
+      </c>
+      <c r="B1875" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1875" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1875" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1875" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1875" t="n">
+        <v>372.47</v>
+      </c>
+      <c r="G1875" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="H1875" s="2" t="n">
+        <v>46081.31430931774</v>
+      </c>
+    </row>
+    <row r="1876">
+      <c r="A1876" t="inlineStr">
+        <is>
+          <t>e125722d-bdbc-4a8d-bd32-a5f8f99b3d39</t>
+        </is>
+      </c>
+      <c r="B1876" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1876" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1876" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1876" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1876" t="n">
+        <v>249.9</v>
+      </c>
+      <c r="G1876" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H1876" s="2" t="n">
+        <v>46075.31430932119</v>
+      </c>
+    </row>
+    <row r="1877">
+      <c r="A1877" t="inlineStr">
+        <is>
+          <t>bca107da-44b5-400a-b221-c7ef40300feb</t>
+        </is>
+      </c>
+      <c r="B1877" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1877" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1877" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1877" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1877" t="n">
+        <v>77.45999999999999</v>
+      </c>
+      <c r="G1877" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="H1877" s="2" t="n">
+        <v>46091.31430932444</v>
+      </c>
+    </row>
+    <row r="1878">
+      <c r="A1878" t="inlineStr">
+        <is>
+          <t>a197b98f-a68d-4efb-a4e7-4227bb78b6fd</t>
+        </is>
+      </c>
+      <c r="B1878" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1878" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1878" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1878" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1878" t="n">
+        <v>114.69</v>
+      </c>
+      <c r="G1878" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H1878" s="2" t="n">
+        <v>46086.31430932754</v>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="A1879" t="inlineStr">
+        <is>
+          <t>dce50cc6-d29d-4188-a3ce-983e09f7636c</t>
+        </is>
+      </c>
+      <c r="B1879" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1879" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1879" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1879" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1879" t="n">
+        <v>228.13</v>
+      </c>
+      <c r="G1879" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H1879" s="2" t="n">
+        <v>46073.31430933083</v>
+      </c>
+    </row>
+    <row r="1880">
+      <c r="A1880" t="inlineStr">
+        <is>
+          <t>c79c2fd7-1198-45d3-8ed9-a1b14d9750db</t>
+        </is>
+      </c>
+      <c r="B1880" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1880" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1880" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1880" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1880" t="n">
+        <v>104.96</v>
+      </c>
+      <c r="G1880" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H1880" s="2" t="n">
+        <v>46089.31430933387</v>
+      </c>
+    </row>
+    <row r="1881">
+      <c r="A1881" t="inlineStr">
+        <is>
+          <t>48ddbc7e-0e46-426f-80f2-baf4958622c1</t>
+        </is>
+      </c>
+      <c r="B1881" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1881" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1881" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1881" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1881" t="n">
+        <v>186.1</v>
+      </c>
+      <c r="G1881" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H1881" s="2" t="n">
+        <v>46086.31430933707</v>
+      </c>
+    </row>
+    <row r="1882">
+      <c r="A1882" t="inlineStr">
+        <is>
+          <t>333699c3-a5da-4b49-b799-44896039da54</t>
+        </is>
+      </c>
+      <c r="B1882" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1882" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1882" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1882" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1882" t="n">
+        <v>380.25</v>
+      </c>
+      <c r="G1882" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H1882" s="2" t="n">
+        <v>46091.31430934039</v>
+      </c>
+    </row>
+    <row r="1883">
+      <c r="A1883" t="inlineStr">
+        <is>
+          <t>e92811c2-b197-43cf-ae14-6669da8505b4</t>
+        </is>
+      </c>
+      <c r="B1883" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1883" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1883" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1883" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1883" t="n">
+        <v>227.35</v>
+      </c>
+      <c r="G1883" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="H1883" s="2" t="n">
+        <v>46076.31430934368</v>
+      </c>
+    </row>
+    <row r="1884">
+      <c r="A1884" t="inlineStr">
+        <is>
+          <t>809e2c02-375b-48c7-a936-5546992c5cac</t>
+        </is>
+      </c>
+      <c r="B1884" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1884" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1884" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1884" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1884" t="n">
+        <v>86.38</v>
+      </c>
+      <c r="G1884" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H1884" s="2" t="n">
+        <v>46075.31430934693</v>
+      </c>
+    </row>
+    <row r="1885">
+      <c r="A1885" t="inlineStr">
+        <is>
+          <t>b639f2d9-717e-469f-bfd9-c09163492753</t>
+        </is>
+      </c>
+      <c r="B1885" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1885" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1885" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1885" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1885" t="n">
+        <v>91.83</v>
+      </c>
+      <c r="G1885" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H1885" s="2" t="n">
+        <v>46071.31430935</v>
+      </c>
+    </row>
+    <row r="1886">
+      <c r="A1886" t="inlineStr">
+        <is>
+          <t>437dde84-2a87-48e1-b135-a4faca60d0cb</t>
+        </is>
+      </c>
+      <c r="B1886" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1886" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1886" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1886" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1886" t="n">
+        <v>61.14</v>
+      </c>
+      <c r="G1886" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H1886" s="2" t="n">
+        <v>46071.31430935318</v>
+      </c>
+    </row>
+    <row r="1887">
+      <c r="A1887" t="inlineStr">
+        <is>
+          <t>feaafd77-9dc3-4fd6-b588-fa3836d8f985</t>
+        </is>
+      </c>
+      <c r="B1887" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1887" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1887" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1887" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1887" t="n">
+        <v>322.14</v>
+      </c>
+      <c r="G1887" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="H1887" s="2" t="n">
+        <v>46096.31430935644</v>
+      </c>
+    </row>
+    <row r="1888">
+      <c r="A1888" t="inlineStr">
+        <is>
+          <t>5dca3b0f-add6-4da1-9107-636410c0b346</t>
+        </is>
+      </c>
+      <c r="B1888" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1888" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1888" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1888" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1888" t="n">
+        <v>399.78</v>
+      </c>
+      <c r="G1888" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1888" s="2" t="n">
+        <v>46072.31430935964</v>
+      </c>
+    </row>
+    <row r="1889">
+      <c r="A1889" t="inlineStr">
+        <is>
+          <t>f5316215-15aa-4efa-81ac-773dcf4b432a</t>
+        </is>
+      </c>
+      <c r="B1889" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1889" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1889" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1889" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1889" t="n">
+        <v>488.87</v>
+      </c>
+      <c r="G1889" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="H1889" s="2" t="n">
+        <v>46086.31430936286</v>
+      </c>
+    </row>
+    <row r="1890">
+      <c r="A1890" t="inlineStr">
+        <is>
+          <t>6f1ed5cb-330a-41b8-a25a-3d350154da7b</t>
+        </is>
+      </c>
+      <c r="B1890" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1890" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1890" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1890" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1890" t="n">
+        <v>455.68</v>
+      </c>
+      <c r="G1890" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="H1890" s="2" t="n">
+        <v>46069.3143093661</v>
+      </c>
+    </row>
+    <row r="1891">
+      <c r="A1891" t="inlineStr">
+        <is>
+          <t>1f87cd5a-9d9e-4f19-a16b-49c8ca56faca</t>
+        </is>
+      </c>
+      <c r="B1891" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1891" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1891" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1891" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1891" t="n">
+        <v>369.78</v>
+      </c>
+      <c r="G1891" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H1891" s="2" t="n">
+        <v>46079.31430936919</v>
+      </c>
+    </row>
+    <row r="1892">
+      <c r="A1892" t="inlineStr">
+        <is>
+          <t>5956ca8e-84c4-45da-8106-da48ed12f4d7</t>
+        </is>
+      </c>
+      <c r="B1892" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1892" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1892" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1892" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1892" t="n">
+        <v>349.06</v>
+      </c>
+      <c r="G1892" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="H1892" s="2" t="n">
+        <v>46093.31430937217</v>
+      </c>
+    </row>
+    <row r="1893">
+      <c r="A1893" t="inlineStr">
+        <is>
+          <t>3fdd2900-5e75-4f54-889f-12b01b20554c</t>
+        </is>
+      </c>
+      <c r="B1893" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1893" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1893" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1893" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1893" t="n">
+        <v>173.82</v>
+      </c>
+      <c r="G1893" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="H1893" s="2" t="n">
+        <v>46070.31430937523</v>
+      </c>
+    </row>
+    <row r="1894">
+      <c r="A1894" t="inlineStr">
+        <is>
+          <t>a7eae0fd-f5f9-481d-9934-3b8eed490fcb</t>
+        </is>
+      </c>
+      <c r="B1894" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1894" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1894" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1894" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1894" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G1894" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H1894" s="2" t="n">
+        <v>46089.31430937852</v>
+      </c>
+    </row>
+    <row r="1895">
+      <c r="A1895" t="inlineStr">
+        <is>
+          <t>83f1637e-02e2-46fe-ae19-73cfd90ac1c8</t>
+        </is>
+      </c>
+      <c r="B1895" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1895" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1895" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1895" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1895" t="n">
+        <v>474.11</v>
+      </c>
+      <c r="G1895" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="H1895" s="2" t="n">
+        <v>46096.3143093817</v>
+      </c>
+    </row>
+    <row r="1896">
+      <c r="A1896" t="inlineStr">
+        <is>
+          <t>8142865f-248c-47ce-81a0-fce6cc17bafc</t>
+        </is>
+      </c>
+      <c r="B1896" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1896" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1896" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1896" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1896" t="n">
+        <v>120.39</v>
+      </c>
+      <c r="G1896" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H1896" s="2" t="n">
+        <v>46068.31430938493</v>
+      </c>
+    </row>
+    <row r="1897">
+      <c r="A1897" t="inlineStr">
+        <is>
+          <t>4f9639c8-42b2-4f56-af7e-10e6bcc81300</t>
+        </is>
+      </c>
+      <c r="B1897" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1897" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1897" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1897" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1897" t="n">
+        <v>303.09</v>
+      </c>
+      <c r="G1897" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="H1897" s="2" t="n">
+        <v>46069.31430938818</v>
+      </c>
+    </row>
+    <row r="1898">
+      <c r="A1898" t="inlineStr">
+        <is>
+          <t>0ade1855-d0eb-49ec-8326-4c13b86baff1</t>
+        </is>
+      </c>
+      <c r="B1898" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1898" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1898" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1898" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1898" t="n">
+        <v>227.08</v>
+      </c>
+      <c r="G1898" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="H1898" s="2" t="n">
+        <v>46069.3143093914</v>
+      </c>
+    </row>
+    <row r="1899">
+      <c r="A1899" t="inlineStr">
+        <is>
+          <t>72659455-a52c-48c8-a612-9792a3679b00</t>
+        </is>
+      </c>
+      <c r="B1899" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1899" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1899" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1899" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1899" t="n">
+        <v>387.88</v>
+      </c>
+      <c r="G1899" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="H1899" s="2" t="n">
+        <v>46089.31430939458</v>
+      </c>
+    </row>
+    <row r="1900">
+      <c r="A1900" t="inlineStr">
+        <is>
+          <t>77e5ea7c-4a29-4cd6-8d5b-202de0bdd09c</t>
+        </is>
+      </c>
+      <c r="B1900" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1900" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1900" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1900" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1900" t="n">
+        <v>212.53</v>
+      </c>
+      <c r="G1900" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="H1900" s="2" t="n">
+        <v>46096.31430939762</v>
+      </c>
+    </row>
+    <row r="1901">
+      <c r="A1901" t="inlineStr">
+        <is>
+          <t>790b9a5d-f145-4d81-85d8-a60f7acb03b2</t>
+        </is>
+      </c>
+      <c r="B1901" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1901" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1901" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1901" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1901" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="G1901" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H1901" s="2" t="n">
+        <v>46096.31430940087</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1901"/>
+  <dimension ref="A1:H1951"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63405,7 +63405,7 @@
         <v>1.3</v>
       </c>
       <c r="H1852" s="2" t="n">
-        <v>46092.31430924147</v>
+        <v>46092.31430923611</v>
       </c>
     </row>
     <row r="1853">
@@ -63439,7 +63439,7 @@
         <v>0.34</v>
       </c>
       <c r="H1853" s="2" t="n">
-        <v>46069.31430924567</v>
+        <v>46069.31430924768</v>
       </c>
     </row>
     <row r="1854">
@@ -63473,7 +63473,7 @@
         <v>2.02</v>
       </c>
       <c r="H1854" s="2" t="n">
-        <v>46070.31430924918</v>
+        <v>46070.31430924768</v>
       </c>
     </row>
     <row r="1855">
@@ -63507,7 +63507,7 @@
         <v>0.06</v>
       </c>
       <c r="H1855" s="2" t="n">
-        <v>46072.31430925251</v>
+        <v>46072.31430924768</v>
       </c>
     </row>
     <row r="1856">
@@ -63541,7 +63541,7 @@
         <v>3.25</v>
       </c>
       <c r="H1856" s="2" t="n">
-        <v>46081.31430925579</v>
+        <v>46081.31430925926</v>
       </c>
     </row>
     <row r="1857">
@@ -63575,7 +63575,7 @@
         <v>0.35</v>
       </c>
       <c r="H1857" s="2" t="n">
-        <v>46080.31430925896</v>
+        <v>46080.31430925926</v>
       </c>
     </row>
     <row r="1858">
@@ -63609,7 +63609,7 @@
         <v>4.72</v>
       </c>
       <c r="H1858" s="2" t="n">
-        <v>46092.31430926249</v>
+        <v>46092.31430925926</v>
       </c>
     </row>
     <row r="1859">
@@ -63643,7 +63643,7 @@
         <v>2.96</v>
       </c>
       <c r="H1859" s="2" t="n">
-        <v>46078.31430926573</v>
+        <v>46078.31430927083</v>
       </c>
     </row>
     <row r="1860">
@@ -63677,7 +63677,7 @@
         <v>0.16</v>
       </c>
       <c r="H1860" s="2" t="n">
-        <v>46084.31430926901</v>
+        <v>46084.31430927083</v>
       </c>
     </row>
     <row r="1861">
@@ -63711,7 +63711,7 @@
         <v>3.98</v>
       </c>
       <c r="H1861" s="2" t="n">
-        <v>46082.31430927227</v>
+        <v>46082.31430927083</v>
       </c>
     </row>
     <row r="1862">
@@ -63745,7 +63745,7 @@
         <v>3.35</v>
       </c>
       <c r="H1862" s="2" t="n">
-        <v>46074.31430927559</v>
+        <v>46074.31430927083</v>
       </c>
     </row>
     <row r="1863">
@@ -63779,7 +63779,7 @@
         <v>4.25</v>
       </c>
       <c r="H1863" s="2" t="n">
-        <v>46095.31430927875</v>
+        <v>46095.31430928241</v>
       </c>
     </row>
     <row r="1864">
@@ -63813,7 +63813,7 @@
         <v>0.23</v>
       </c>
       <c r="H1864" s="2" t="n">
-        <v>46076.31430928207</v>
+        <v>46076.31430928241</v>
       </c>
     </row>
     <row r="1865">
@@ -63847,7 +63847,7 @@
         <v>1.39</v>
       </c>
       <c r="H1865" s="2" t="n">
-        <v>46078.31430928535</v>
+        <v>46078.31430928241</v>
       </c>
     </row>
     <row r="1866">
@@ -63881,7 +63881,7 @@
         <v>0.83</v>
       </c>
       <c r="H1866" s="2" t="n">
-        <v>46088.31430928847</v>
+        <v>46088.31430929398</v>
       </c>
     </row>
     <row r="1867">
@@ -63915,7 +63915,7 @@
         <v>1.87</v>
       </c>
       <c r="H1867" s="2" t="n">
-        <v>46092.31430929169</v>
+        <v>46092.31430929398</v>
       </c>
     </row>
     <row r="1868">
@@ -63949,7 +63949,7 @@
         <v>3.28</v>
       </c>
       <c r="H1868" s="2" t="n">
-        <v>46089.31430929509</v>
+        <v>46089.31430929398</v>
       </c>
     </row>
     <row r="1869">
@@ -63983,7 +63983,7 @@
         <v>3.96</v>
       </c>
       <c r="H1869" s="2" t="n">
-        <v>46087.31430929821</v>
+        <v>46087.31430929398</v>
       </c>
     </row>
     <row r="1870">
@@ -64017,7 +64017,7 @@
         <v>2.21</v>
       </c>
       <c r="H1870" s="2" t="n">
-        <v>46093.3143093013</v>
+        <v>46093.31430930556</v>
       </c>
     </row>
     <row r="1871">
@@ -64051,7 +64051,7 @@
         <v>4.31</v>
       </c>
       <c r="H1871" s="2" t="n">
-        <v>46069.31430930436</v>
+        <v>46069.31430930556</v>
       </c>
     </row>
     <row r="1872">
@@ -64085,7 +64085,7 @@
         <v>4.37</v>
       </c>
       <c r="H1872" s="2" t="n">
-        <v>46079.31430930771</v>
+        <v>46079.31430930556</v>
       </c>
     </row>
     <row r="1873">
@@ -64119,7 +64119,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="H1873" s="2" t="n">
-        <v>46074.31430931124</v>
+        <v>46074.31430930556</v>
       </c>
     </row>
     <row r="1874">
@@ -64153,7 +64153,7 @@
         <v>3.38</v>
       </c>
       <c r="H1874" s="2" t="n">
-        <v>46076.31430931453</v>
+        <v>46076.31430931713</v>
       </c>
     </row>
     <row r="1875">
@@ -64187,7 +64187,7 @@
         <v>3.72</v>
       </c>
       <c r="H1875" s="2" t="n">
-        <v>46081.31430931774</v>
+        <v>46081.31430931713</v>
       </c>
     </row>
     <row r="1876">
@@ -64221,7 +64221,7 @@
         <v>2.5</v>
       </c>
       <c r="H1876" s="2" t="n">
-        <v>46075.31430932119</v>
+        <v>46075.31430931713</v>
       </c>
     </row>
     <row r="1877">
@@ -64255,7 +64255,7 @@
         <v>0.77</v>
       </c>
       <c r="H1877" s="2" t="n">
-        <v>46091.31430932444</v>
+        <v>46091.31430932871</v>
       </c>
     </row>
     <row r="1878">
@@ -64289,7 +64289,7 @@
         <v>1.15</v>
       </c>
       <c r="H1878" s="2" t="n">
-        <v>46086.31430932754</v>
+        <v>46086.31430932871</v>
       </c>
     </row>
     <row r="1879">
@@ -64323,7 +64323,7 @@
         <v>2.28</v>
       </c>
       <c r="H1879" s="2" t="n">
-        <v>46073.31430933083</v>
+        <v>46073.31430932871</v>
       </c>
     </row>
     <row r="1880">
@@ -64357,7 +64357,7 @@
         <v>1.05</v>
       </c>
       <c r="H1880" s="2" t="n">
-        <v>46089.31430933387</v>
+        <v>46089.31430932871</v>
       </c>
     </row>
     <row r="1881">
@@ -64391,7 +64391,7 @@
         <v>1.86</v>
       </c>
       <c r="H1881" s="2" t="n">
-        <v>46086.31430933707</v>
+        <v>46086.31430934028</v>
       </c>
     </row>
     <row r="1882">
@@ -64425,7 +64425,7 @@
         <v>3.8</v>
       </c>
       <c r="H1882" s="2" t="n">
-        <v>46091.31430934039</v>
+        <v>46091.31430934028</v>
       </c>
     </row>
     <row r="1883">
@@ -64459,7 +64459,7 @@
         <v>2.27</v>
       </c>
       <c r="H1883" s="2" t="n">
-        <v>46076.31430934368</v>
+        <v>46076.31430934028</v>
       </c>
     </row>
     <row r="1884">
@@ -64493,7 +64493,7 @@
         <v>0.86</v>
       </c>
       <c r="H1884" s="2" t="n">
-        <v>46075.31430934693</v>
+        <v>46075.31430935185</v>
       </c>
     </row>
     <row r="1885">
@@ -64527,7 +64527,7 @@
         <v>0.92</v>
       </c>
       <c r="H1885" s="2" t="n">
-        <v>46071.31430935</v>
+        <v>46071.31430935185</v>
       </c>
     </row>
     <row r="1886">
@@ -64561,7 +64561,7 @@
         <v>0.61</v>
       </c>
       <c r="H1886" s="2" t="n">
-        <v>46071.31430935318</v>
+        <v>46071.31430935185</v>
       </c>
     </row>
     <row r="1887">
@@ -64595,7 +64595,7 @@
         <v>3.22</v>
       </c>
       <c r="H1887" s="2" t="n">
-        <v>46096.31430935644</v>
+        <v>46096.31430935185</v>
       </c>
     </row>
     <row r="1888">
@@ -64629,7 +64629,7 @@
         <v>4</v>
       </c>
       <c r="H1888" s="2" t="n">
-        <v>46072.31430935964</v>
+        <v>46072.31430936343</v>
       </c>
     </row>
     <row r="1889">
@@ -64663,7 +64663,7 @@
         <v>4.89</v>
       </c>
       <c r="H1889" s="2" t="n">
-        <v>46086.31430936286</v>
+        <v>46086.31430936343</v>
       </c>
     </row>
     <row r="1890">
@@ -64697,7 +64697,7 @@
         <v>4.56</v>
       </c>
       <c r="H1890" s="2" t="n">
-        <v>46069.3143093661</v>
+        <v>46069.31430936343</v>
       </c>
     </row>
     <row r="1891">
@@ -64731,7 +64731,7 @@
         <v>3.7</v>
       </c>
       <c r="H1891" s="2" t="n">
-        <v>46079.31430936919</v>
+        <v>46079.31430936343</v>
       </c>
     </row>
     <row r="1892">
@@ -64765,7 +64765,7 @@
         <v>3.49</v>
       </c>
       <c r="H1892" s="2" t="n">
-        <v>46093.31430937217</v>
+        <v>46093.314309375</v>
       </c>
     </row>
     <row r="1893">
@@ -64799,7 +64799,7 @@
         <v>1.74</v>
       </c>
       <c r="H1893" s="2" t="n">
-        <v>46070.31430937523</v>
+        <v>46070.314309375</v>
       </c>
     </row>
     <row r="1894">
@@ -64833,7 +64833,7 @@
         <v>0.02</v>
       </c>
       <c r="H1894" s="2" t="n">
-        <v>46089.31430937852</v>
+        <v>46089.314309375</v>
       </c>
     </row>
     <row r="1895">
@@ -64867,7 +64867,7 @@
         <v>4.74</v>
       </c>
       <c r="H1895" s="2" t="n">
-        <v>46096.3143093817</v>
+        <v>46096.31430938657</v>
       </c>
     </row>
     <row r="1896">
@@ -64901,7 +64901,7 @@
         <v>1.2</v>
       </c>
       <c r="H1896" s="2" t="n">
-        <v>46068.31430938493</v>
+        <v>46068.31430938657</v>
       </c>
     </row>
     <row r="1897">
@@ -64935,7 +64935,7 @@
         <v>3.03</v>
       </c>
       <c r="H1897" s="2" t="n">
-        <v>46069.31430938818</v>
+        <v>46069.31430938657</v>
       </c>
     </row>
     <row r="1898">
@@ -64969,7 +64969,7 @@
         <v>2.27</v>
       </c>
       <c r="H1898" s="2" t="n">
-        <v>46069.3143093914</v>
+        <v>46069.31430938657</v>
       </c>
     </row>
     <row r="1899">
@@ -65003,7 +65003,7 @@
         <v>3.88</v>
       </c>
       <c r="H1899" s="2" t="n">
-        <v>46089.31430939458</v>
+        <v>46089.31430939815</v>
       </c>
     </row>
     <row r="1900">
@@ -65037,7 +65037,7 @@
         <v>2.13</v>
       </c>
       <c r="H1900" s="2" t="n">
-        <v>46096.31430939762</v>
+        <v>46096.31430939815</v>
       </c>
     </row>
     <row r="1901">
@@ -65071,7 +65071,1707 @@
         <v>0.06</v>
       </c>
       <c r="H1901" s="2" t="n">
-        <v>46096.31430940087</v>
+        <v>46096.31430939815</v>
+      </c>
+    </row>
+    <row r="1902">
+      <c r="A1902" t="inlineStr">
+        <is>
+          <t>9cae9438-2d6f-475f-8908-724a90753160</t>
+        </is>
+      </c>
+      <c r="B1902" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1902" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1902" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1902" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1902" t="n">
+        <v>218.13</v>
+      </c>
+      <c r="G1902" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H1902" s="2" t="n">
+        <v>46082.35469825191</v>
+      </c>
+    </row>
+    <row r="1903">
+      <c r="A1903" t="inlineStr">
+        <is>
+          <t>9c24f17e-af0a-4e0a-9486-25ae791f16d0</t>
+        </is>
+      </c>
+      <c r="B1903" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1903" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1903" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1903" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1903" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G1903" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1903" s="2" t="n">
+        <v>46078.35469825636</v>
+      </c>
+    </row>
+    <row r="1904">
+      <c r="A1904" t="inlineStr">
+        <is>
+          <t>c6890bc8-fada-4330-b73f-4402e62cbf91</t>
+        </is>
+      </c>
+      <c r="B1904" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1904" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1904" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1904" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1904" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G1904" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1904" s="2" t="n">
+        <v>46091.35469825958</v>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" t="inlineStr">
+        <is>
+          <t>bfd81a3f-2944-4fd7-8f99-444ed362f2b8</t>
+        </is>
+      </c>
+      <c r="B1905" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1905" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1905" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1905" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1905" t="n">
+        <v>136.51</v>
+      </c>
+      <c r="G1905" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H1905" s="2" t="n">
+        <v>46081.35469826269</v>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" t="inlineStr">
+        <is>
+          <t>74f57041-a63e-4da3-b80d-9279f182590e</t>
+        </is>
+      </c>
+      <c r="B1906" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1906" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1906" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1906" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1906" t="n">
+        <v>268.08</v>
+      </c>
+      <c r="G1906" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H1906" s="2" t="n">
+        <v>46071.35469826573</v>
+      </c>
+    </row>
+    <row r="1907">
+      <c r="A1907" t="inlineStr">
+        <is>
+          <t>3a5b84b3-f5f0-4964-9fde-58aaddeb58ff</t>
+        </is>
+      </c>
+      <c r="B1907" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1907" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1907" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1907" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1907" t="n">
+        <v>63.86</v>
+      </c>
+      <c r="G1907" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H1907" s="2" t="n">
+        <v>46090.35469826905</v>
+      </c>
+    </row>
+    <row r="1908">
+      <c r="A1908" t="inlineStr">
+        <is>
+          <t>7d26f32e-f1fa-4816-b839-b0afb8b90511</t>
+        </is>
+      </c>
+      <c r="B1908" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1908" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1908" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1908" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1908" t="n">
+        <v>473.79</v>
+      </c>
+      <c r="G1908" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="H1908" s="2" t="n">
+        <v>46072.35469827223</v>
+      </c>
+    </row>
+    <row r="1909">
+      <c r="A1909" t="inlineStr">
+        <is>
+          <t>b865e09d-4db0-4f4c-999a-144f911fd47d</t>
+        </is>
+      </c>
+      <c r="B1909" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1909" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1909" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1909" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1909" t="n">
+        <v>340.29</v>
+      </c>
+      <c r="G1909" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H1909" s="2" t="n">
+        <v>46074.3546982753</v>
+      </c>
+    </row>
+    <row r="1910">
+      <c r="A1910" t="inlineStr">
+        <is>
+          <t>4e318a22-fc25-4c5d-9c37-4bae546b4e24</t>
+        </is>
+      </c>
+      <c r="B1910" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1910" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1910" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1910" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1910" t="n">
+        <v>79.95</v>
+      </c>
+      <c r="G1910" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H1910" s="2" t="n">
+        <v>46091.3546982789</v>
+      </c>
+    </row>
+    <row r="1911">
+      <c r="A1911" t="inlineStr">
+        <is>
+          <t>ef185591-63f5-49a9-996f-fdd38619119d</t>
+        </is>
+      </c>
+      <c r="B1911" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1911" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1911" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1911" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1911" t="n">
+        <v>348.75</v>
+      </c>
+      <c r="G1911" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="H1911" s="2" t="n">
+        <v>46072.35469828203</v>
+      </c>
+    </row>
+    <row r="1912">
+      <c r="A1912" t="inlineStr">
+        <is>
+          <t>5fa317e1-d049-4166-9cf7-69f6691b9b71</t>
+        </is>
+      </c>
+      <c r="B1912" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1912" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1912" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1912" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1912" t="n">
+        <v>387.09</v>
+      </c>
+      <c r="G1912" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="H1912" s="2" t="n">
+        <v>46083.35469828514</v>
+      </c>
+    </row>
+    <row r="1913">
+      <c r="A1913" t="inlineStr">
+        <is>
+          <t>f05ccbe4-3fe7-492c-9114-6949390dc786</t>
+        </is>
+      </c>
+      <c r="B1913" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1913" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1913" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1913" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1913" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="G1913" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H1913" s="2" t="n">
+        <v>46068.3546982883</v>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" t="inlineStr">
+        <is>
+          <t>568beb64-60e7-4f4e-99ea-42b12486381c</t>
+        </is>
+      </c>
+      <c r="B1914" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1914" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1914" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1914" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1914" t="n">
+        <v>141.27</v>
+      </c>
+      <c r="G1914" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H1914" s="2" t="n">
+        <v>46072.35469829199</v>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" t="inlineStr">
+        <is>
+          <t>0c9d115e-173a-42e8-bb62-7b29209da711</t>
+        </is>
+      </c>
+      <c r="B1915" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1915" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1915" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1915" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1915" t="n">
+        <v>292.14</v>
+      </c>
+      <c r="G1915" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H1915" s="2" t="n">
+        <v>46084.35469829508</v>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" t="inlineStr">
+        <is>
+          <t>b5e8660a-cd9b-4730-aa01-88a641a347ee</t>
+        </is>
+      </c>
+      <c r="B1916" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1916" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1916" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1916" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1916" t="n">
+        <v>490.05</v>
+      </c>
+      <c r="G1916" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H1916" s="2" t="n">
+        <v>46080.35469829809</v>
+      </c>
+    </row>
+    <row r="1917">
+      <c r="A1917" t="inlineStr">
+        <is>
+          <t>ed3bfa9a-8c76-4c23-9333-413aa1909c70</t>
+        </is>
+      </c>
+      <c r="B1917" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1917" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1917" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1917" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1917" t="n">
+        <v>277.32</v>
+      </c>
+      <c r="G1917" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="H1917" s="2" t="n">
+        <v>46090.35469830127</v>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" t="inlineStr">
+        <is>
+          <t>2d3e6f5b-9550-4a29-bee8-189496eb6796</t>
+        </is>
+      </c>
+      <c r="B1918" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1918" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1918" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1918" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1918" t="n">
+        <v>307.95</v>
+      </c>
+      <c r="G1918" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="H1918" s="2" t="n">
+        <v>46093.35469830448</v>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" t="inlineStr">
+        <is>
+          <t>cb618713-04a0-4d21-994f-81fc9714e19f</t>
+        </is>
+      </c>
+      <c r="B1919" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1919" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1919" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1919" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1919" t="n">
+        <v>255.41</v>
+      </c>
+      <c r="G1919" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H1919" s="2" t="n">
+        <v>46079.35469830758</v>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" t="inlineStr">
+        <is>
+          <t>77f95eb5-e8d3-4b4c-b00e-a6055d80b6bc</t>
+        </is>
+      </c>
+      <c r="B1920" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1920" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1920" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1920" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1920" t="n">
+        <v>471.62</v>
+      </c>
+      <c r="G1920" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="H1920" s="2" t="n">
+        <v>46090.35469831073</v>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" t="inlineStr">
+        <is>
+          <t>1f562e3f-de12-49a6-9ec8-07cc11c47bec</t>
+        </is>
+      </c>
+      <c r="B1921" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1921" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1921" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1921" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1921" t="n">
+        <v>393.08</v>
+      </c>
+      <c r="G1921" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="H1921" s="2" t="n">
+        <v>46091.35469831404</v>
+      </c>
+    </row>
+    <row r="1922">
+      <c r="A1922" t="inlineStr">
+        <is>
+          <t>5a91b0fc-6197-41a7-9126-f071451f217f</t>
+        </is>
+      </c>
+      <c r="B1922" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1922" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1922" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1922" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1922" t="n">
+        <v>99.11</v>
+      </c>
+      <c r="G1922" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="H1922" s="2" t="n">
+        <v>46069.35469831715</v>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" t="inlineStr">
+        <is>
+          <t>143bee5e-aaf9-4472-8171-2fa76ad95d34</t>
+        </is>
+      </c>
+      <c r="B1923" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1923" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1923" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1923" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1923" t="n">
+        <v>420.92</v>
+      </c>
+      <c r="G1923" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="H1923" s="2" t="n">
+        <v>46085.35469832031</v>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" t="inlineStr">
+        <is>
+          <t>21b4d5e0-8d14-4bcd-a53a-9547f24f3abc</t>
+        </is>
+      </c>
+      <c r="B1924" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1924" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1924" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1924" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1924" t="n">
+        <v>88.44</v>
+      </c>
+      <c r="G1924" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H1924" s="2" t="n">
+        <v>46079.35469832335</v>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" t="inlineStr">
+        <is>
+          <t>6f5e44e5-b572-4335-bf1f-24886df14045</t>
+        </is>
+      </c>
+      <c r="B1925" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1925" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1925" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1925" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1925" t="n">
+        <v>355.12</v>
+      </c>
+      <c r="G1925" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H1925" s="2" t="n">
+        <v>46095.35469832653</v>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" t="inlineStr">
+        <is>
+          <t>da8d9990-bcf5-4346-b382-458d688af1ca</t>
+        </is>
+      </c>
+      <c r="B1926" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1926" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1926" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1926" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1926" t="n">
+        <v>366.47</v>
+      </c>
+      <c r="G1926" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="H1926" s="2" t="n">
+        <v>46085.35469832952</v>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" t="inlineStr">
+        <is>
+          <t>80a89430-4d89-478c-83af-33922193c816</t>
+        </is>
+      </c>
+      <c r="B1927" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1927" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1927" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1927" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1927" t="n">
+        <v>257.07</v>
+      </c>
+      <c r="G1927" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="H1927" s="2" t="n">
+        <v>46076.35469833275</v>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" t="inlineStr">
+        <is>
+          <t>a69f9295-2385-4682-8e4a-e39936a92d43</t>
+        </is>
+      </c>
+      <c r="B1928" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1928" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1928" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1928" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1928" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="G1928" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H1928" s="2" t="n">
+        <v>46078.35469833589</v>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" t="inlineStr">
+        <is>
+          <t>3e13df0c-b27a-4d2c-bc43-6f39de5eb52f</t>
+        </is>
+      </c>
+      <c r="B1929" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1929" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1929" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1929" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1929" t="n">
+        <v>406.67</v>
+      </c>
+      <c r="G1929" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="H1929" s="2" t="n">
+        <v>46094.35469833962</v>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" t="inlineStr">
+        <is>
+          <t>6426e88b-fdd4-453a-bbce-5542cc62c14f</t>
+        </is>
+      </c>
+      <c r="B1930" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1930" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1930" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1930" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1930" t="n">
+        <v>363.51</v>
+      </c>
+      <c r="G1930" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="H1930" s="2" t="n">
+        <v>46096.35469834265</v>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" t="inlineStr">
+        <is>
+          <t>ba69fe65-61a7-4401-811f-2fcc6bf7704e</t>
+        </is>
+      </c>
+      <c r="B1931" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1931" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1931" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1931" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1931" t="n">
+        <v>87.78</v>
+      </c>
+      <c r="G1931" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H1931" s="2" t="n">
+        <v>46083.35469834563</v>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" t="inlineStr">
+        <is>
+          <t>2d6d13e1-f550-43df-94e2-13ced3971dfd</t>
+        </is>
+      </c>
+      <c r="B1932" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1932" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1932" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1932" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1932" t="n">
+        <v>441.25</v>
+      </c>
+      <c r="G1932" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="H1932" s="2" t="n">
+        <v>46095.35469834894</v>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" t="inlineStr">
+        <is>
+          <t>3d9826ae-2d38-4b9c-9753-0a9ba9e313c5</t>
+        </is>
+      </c>
+      <c r="B1933" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1933" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1933" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1933" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1933" t="n">
+        <v>103</v>
+      </c>
+      <c r="G1933" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H1933" s="2" t="n">
+        <v>46069.35469835192</v>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" t="inlineStr">
+        <is>
+          <t>b77be1bb-2a94-4004-9c28-01d029717973</t>
+        </is>
+      </c>
+      <c r="B1934" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1934" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1934" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1934" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1934" t="n">
+        <v>446.92</v>
+      </c>
+      <c r="G1934" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="H1934" s="2" t="n">
+        <v>46080.35469835497</v>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" t="inlineStr">
+        <is>
+          <t>673846e0-80d0-4f80-84d2-6d198710c084</t>
+        </is>
+      </c>
+      <c r="B1935" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1935" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1935" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1935" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1935" t="n">
+        <v>195.68</v>
+      </c>
+      <c r="G1935" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H1935" s="2" t="n">
+        <v>46077.3546983581</v>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" t="inlineStr">
+        <is>
+          <t>9a0a784e-81cb-4f9c-b01d-64f3af6c87f7</t>
+        </is>
+      </c>
+      <c r="B1936" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1936" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1936" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1936" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1936" t="n">
+        <v>217.76</v>
+      </c>
+      <c r="G1936" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H1936" s="2" t="n">
+        <v>46079.35469836125</v>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" t="inlineStr">
+        <is>
+          <t>fde4fbcc-af3d-4687-a8a1-51eb5cb99240</t>
+        </is>
+      </c>
+      <c r="B1937" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1937" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1937" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1937" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1937" t="n">
+        <v>42.08</v>
+      </c>
+      <c r="G1937" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H1937" s="2" t="n">
+        <v>46095.3546983643</v>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" t="inlineStr">
+        <is>
+          <t>9bc121cb-ccc2-49b7-bf81-80b8b8e941d0</t>
+        </is>
+      </c>
+      <c r="B1938" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1938" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1938" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1938" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1938" t="n">
+        <v>201.84</v>
+      </c>
+      <c r="G1938" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H1938" s="2" t="n">
+        <v>46087.3546983674</v>
+      </c>
+    </row>
+    <row r="1939">
+      <c r="A1939" t="inlineStr">
+        <is>
+          <t>2426081c-5d3a-4ec2-9624-854b733cbc09</t>
+        </is>
+      </c>
+      <c r="B1939" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1939" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1939" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1939" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1939" t="n">
+        <v>50.06</v>
+      </c>
+      <c r="G1939" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1939" s="2" t="n">
+        <v>46076.35469837041</v>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" t="inlineStr">
+        <is>
+          <t>e50a79b9-ac0a-43ea-9819-720ce550a2d3</t>
+        </is>
+      </c>
+      <c r="B1940" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1940" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1940" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1940" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1940" t="n">
+        <v>72.93000000000001</v>
+      </c>
+      <c r="G1940" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H1940" s="2" t="n">
+        <v>46090.35469837364</v>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" t="inlineStr">
+        <is>
+          <t>49443ecb-b3eb-4a0f-8114-33f471474506</t>
+        </is>
+      </c>
+      <c r="B1941" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1941" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1941" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1941" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1941" t="n">
+        <v>246.88</v>
+      </c>
+      <c r="G1941" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="H1941" s="2" t="n">
+        <v>46077.35469837664</v>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" t="inlineStr">
+        <is>
+          <t>e180db79-68e3-4631-be8d-4acb76deda21</t>
+        </is>
+      </c>
+      <c r="B1942" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1942" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1942" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1942" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1942" t="n">
+        <v>52.39</v>
+      </c>
+      <c r="G1942" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H1942" s="2" t="n">
+        <v>46069.35469837979</v>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" t="inlineStr">
+        <is>
+          <t>fbf4fe0c-8655-4890-bba9-d5f93acfce28</t>
+        </is>
+      </c>
+      <c r="B1943" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1943" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1943" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1943" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1943" t="n">
+        <v>410.05</v>
+      </c>
+      <c r="G1943" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H1943" s="2" t="n">
+        <v>46076.35469838334</v>
+      </c>
+    </row>
+    <row r="1944">
+      <c r="A1944" t="inlineStr">
+        <is>
+          <t>5197fdba-c03e-4b53-9840-7cdf5649e5f1</t>
+        </is>
+      </c>
+      <c r="B1944" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1944" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1944" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1944" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1944" t="n">
+        <v>172.66</v>
+      </c>
+      <c r="G1944" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H1944" s="2" t="n">
+        <v>46068.35469838638</v>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" t="inlineStr">
+        <is>
+          <t>674aa5de-d4ed-47fc-99b8-56b3388eb056</t>
+        </is>
+      </c>
+      <c r="B1945" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1945" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1945" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1945" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1945" t="n">
+        <v>415.75</v>
+      </c>
+      <c r="G1945" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="H1945" s="2" t="n">
+        <v>46086.35469838942</v>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" t="inlineStr">
+        <is>
+          <t>59fdcdd0-c519-42d6-b48a-3fad7f372bef</t>
+        </is>
+      </c>
+      <c r="B1946" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1946" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1946" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1946" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1946" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="G1946" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H1946" s="2" t="n">
+        <v>46080.35469839242</v>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="A1947" t="inlineStr">
+        <is>
+          <t>e02808a6-6ac0-4e2e-b966-d1ec6ff7ed5a</t>
+        </is>
+      </c>
+      <c r="B1947" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1947" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1947" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1947" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1947" t="n">
+        <v>34.23</v>
+      </c>
+      <c r="G1947" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H1947" s="2" t="n">
+        <v>46067.3546983958</v>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" t="inlineStr">
+        <is>
+          <t>cf424325-bb0a-470c-9761-365d80be8d84</t>
+        </is>
+      </c>
+      <c r="B1948" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1948" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1948" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1948" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1948" t="n">
+        <v>415.41</v>
+      </c>
+      <c r="G1948" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="H1948" s="2" t="n">
+        <v>46081.35469839891</v>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" t="inlineStr">
+        <is>
+          <t>2cf1c7b2-8580-407b-a13e-cc263bec6411</t>
+        </is>
+      </c>
+      <c r="B1949" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1949" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1949" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1949" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1949" t="n">
+        <v>53.05</v>
+      </c>
+      <c r="G1949" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H1949" s="2" t="n">
+        <v>46086.35469840227</v>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" t="inlineStr">
+        <is>
+          <t>d6abbb41-2f57-45fc-85c3-12dbf5ae7f21</t>
+        </is>
+      </c>
+      <c r="B1950" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1950" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1950" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1950" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1950" t="n">
+        <v>97.14</v>
+      </c>
+      <c r="G1950" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="H1950" s="2" t="n">
+        <v>46096.35469840537</v>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" t="inlineStr">
+        <is>
+          <t>091a525b-b19f-4dd3-915e-49690fa3958b</t>
+        </is>
+      </c>
+      <c r="B1951" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1951" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1951" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1951" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1951" t="n">
+        <v>329.74</v>
+      </c>
+      <c r="G1951" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H1951" s="2" t="n">
+        <v>46085.35469840858</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1951"/>
+  <dimension ref="A1:H2001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65105,7 +65105,7 @@
         <v>2.18</v>
       </c>
       <c r="H1902" s="2" t="n">
-        <v>46082.35469825191</v>
+        <v>46082.35469825231</v>
       </c>
     </row>
     <row r="1903">
@@ -65139,7 +65139,7 @@
         <v>0</v>
       </c>
       <c r="H1903" s="2" t="n">
-        <v>46078.35469825636</v>
+        <v>46078.35469825231</v>
       </c>
     </row>
     <row r="1904">
@@ -65173,7 +65173,7 @@
         <v>0</v>
       </c>
       <c r="H1904" s="2" t="n">
-        <v>46091.35469825958</v>
+        <v>46091.35469826389</v>
       </c>
     </row>
     <row r="1905">
@@ -65207,7 +65207,7 @@
         <v>1.37</v>
       </c>
       <c r="H1905" s="2" t="n">
-        <v>46081.35469826269</v>
+        <v>46081.35469826389</v>
       </c>
     </row>
     <row r="1906">
@@ -65241,7 +65241,7 @@
         <v>2.68</v>
       </c>
       <c r="H1906" s="2" t="n">
-        <v>46071.35469826573</v>
+        <v>46071.35469826389</v>
       </c>
     </row>
     <row r="1907">
@@ -65275,7 +65275,7 @@
         <v>0.64</v>
       </c>
       <c r="H1907" s="2" t="n">
-        <v>46090.35469826905</v>
+        <v>46090.35469826389</v>
       </c>
     </row>
     <row r="1908">
@@ -65309,7 +65309,7 @@
         <v>4.74</v>
       </c>
       <c r="H1908" s="2" t="n">
-        <v>46072.35469827223</v>
+        <v>46072.35469827546</v>
       </c>
     </row>
     <row r="1909">
@@ -65343,7 +65343,7 @@
         <v>3.4</v>
       </c>
       <c r="H1909" s="2" t="n">
-        <v>46074.3546982753</v>
+        <v>46074.35469827546</v>
       </c>
     </row>
     <row r="1910">
@@ -65377,7 +65377,7 @@
         <v>0.8</v>
       </c>
       <c r="H1910" s="2" t="n">
-        <v>46091.3546982789</v>
+        <v>46091.35469827546</v>
       </c>
     </row>
     <row r="1911">
@@ -65411,7 +65411,7 @@
         <v>3.49</v>
       </c>
       <c r="H1911" s="2" t="n">
-        <v>46072.35469828203</v>
+        <v>46072.35469828704</v>
       </c>
     </row>
     <row r="1912">
@@ -65445,7 +65445,7 @@
         <v>3.87</v>
       </c>
       <c r="H1912" s="2" t="n">
-        <v>46083.35469828514</v>
+        <v>46083.35469828704</v>
       </c>
     </row>
     <row r="1913">
@@ -65479,7 +65479,7 @@
         <v>0.15</v>
       </c>
       <c r="H1913" s="2" t="n">
-        <v>46068.3546982883</v>
+        <v>46068.35469828704</v>
       </c>
     </row>
     <row r="1914">
@@ -65513,7 +65513,7 @@
         <v>1.41</v>
       </c>
       <c r="H1914" s="2" t="n">
-        <v>46072.35469829199</v>
+        <v>46072.35469828704</v>
       </c>
     </row>
     <row r="1915">
@@ -65547,7 +65547,7 @@
         <v>2.92</v>
       </c>
       <c r="H1915" s="2" t="n">
-        <v>46084.35469829508</v>
+        <v>46084.35469829861</v>
       </c>
     </row>
     <row r="1916">
@@ -65581,7 +65581,7 @@
         <v>4.9</v>
       </c>
       <c r="H1916" s="2" t="n">
-        <v>46080.35469829809</v>
+        <v>46080.35469829861</v>
       </c>
     </row>
     <row r="1917">
@@ -65615,7 +65615,7 @@
         <v>2.77</v>
       </c>
       <c r="H1917" s="2" t="n">
-        <v>46090.35469830127</v>
+        <v>46090.35469829861</v>
       </c>
     </row>
     <row r="1918">
@@ -65649,7 +65649,7 @@
         <v>3.08</v>
       </c>
       <c r="H1918" s="2" t="n">
-        <v>46093.35469830448</v>
+        <v>46093.35469831018</v>
       </c>
     </row>
     <row r="1919">
@@ -65683,7 +65683,7 @@
         <v>2.55</v>
       </c>
       <c r="H1919" s="2" t="n">
-        <v>46079.35469830758</v>
+        <v>46079.35469831018</v>
       </c>
     </row>
     <row r="1920">
@@ -65717,7 +65717,7 @@
         <v>4.72</v>
       </c>
       <c r="H1920" s="2" t="n">
-        <v>46090.35469831073</v>
+        <v>46090.35469831018</v>
       </c>
     </row>
     <row r="1921">
@@ -65751,7 +65751,7 @@
         <v>3.93</v>
       </c>
       <c r="H1921" s="2" t="n">
-        <v>46091.35469831404</v>
+        <v>46091.35469831018</v>
       </c>
     </row>
     <row r="1922">
@@ -65785,7 +65785,7 @@
         <v>0.99</v>
       </c>
       <c r="H1922" s="2" t="n">
-        <v>46069.35469831715</v>
+        <v>46069.35469832176</v>
       </c>
     </row>
     <row r="1923">
@@ -65819,7 +65819,7 @@
         <v>4.21</v>
       </c>
       <c r="H1923" s="2" t="n">
-        <v>46085.35469832031</v>
+        <v>46085.35469832176</v>
       </c>
     </row>
     <row r="1924">
@@ -65853,7 +65853,7 @@
         <v>0.88</v>
       </c>
       <c r="H1924" s="2" t="n">
-        <v>46079.35469832335</v>
+        <v>46079.35469832176</v>
       </c>
     </row>
     <row r="1925">
@@ -65887,7 +65887,7 @@
         <v>3.55</v>
       </c>
       <c r="H1925" s="2" t="n">
-        <v>46095.35469832653</v>
+        <v>46095.35469832176</v>
       </c>
     </row>
     <row r="1926">
@@ -65921,7 +65921,7 @@
         <v>3.66</v>
       </c>
       <c r="H1926" s="2" t="n">
-        <v>46085.35469832952</v>
+        <v>46085.35469833334</v>
       </c>
     </row>
     <row r="1927">
@@ -65955,7 +65955,7 @@
         <v>2.57</v>
       </c>
       <c r="H1927" s="2" t="n">
-        <v>46076.35469833275</v>
+        <v>46076.35469833334</v>
       </c>
     </row>
     <row r="1928">
@@ -65989,7 +65989,7 @@
         <v>0.64</v>
       </c>
       <c r="H1928" s="2" t="n">
-        <v>46078.35469833589</v>
+        <v>46078.35469833334</v>
       </c>
     </row>
     <row r="1929">
@@ -66023,7 +66023,7 @@
         <v>4.07</v>
       </c>
       <c r="H1929" s="2" t="n">
-        <v>46094.35469833962</v>
+        <v>46094.35469834491</v>
       </c>
     </row>
     <row r="1930">
@@ -66057,7 +66057,7 @@
         <v>3.64</v>
       </c>
       <c r="H1930" s="2" t="n">
-        <v>46096.35469834265</v>
+        <v>46096.35469834491</v>
       </c>
     </row>
     <row r="1931">
@@ -66091,7 +66091,7 @@
         <v>0.88</v>
       </c>
       <c r="H1931" s="2" t="n">
-        <v>46083.35469834563</v>
+        <v>46083.35469834491</v>
       </c>
     </row>
     <row r="1932">
@@ -66125,7 +66125,7 @@
         <v>4.41</v>
       </c>
       <c r="H1932" s="2" t="n">
-        <v>46095.35469834894</v>
+        <v>46095.35469834491</v>
       </c>
     </row>
     <row r="1933">
@@ -66159,7 +66159,7 @@
         <v>1.03</v>
       </c>
       <c r="H1933" s="2" t="n">
-        <v>46069.35469835192</v>
+        <v>46069.35469835648</v>
       </c>
     </row>
     <row r="1934">
@@ -66193,7 +66193,7 @@
         <v>4.47</v>
       </c>
       <c r="H1934" s="2" t="n">
-        <v>46080.35469835497</v>
+        <v>46080.35469835648</v>
       </c>
     </row>
     <row r="1935">
@@ -66227,7 +66227,7 @@
         <v>1.96</v>
       </c>
       <c r="H1935" s="2" t="n">
-        <v>46077.3546983581</v>
+        <v>46077.35469835648</v>
       </c>
     </row>
     <row r="1936">
@@ -66261,7 +66261,7 @@
         <v>2.18</v>
       </c>
       <c r="H1936" s="2" t="n">
-        <v>46079.35469836125</v>
+        <v>46079.35469835648</v>
       </c>
     </row>
     <row r="1937">
@@ -66295,7 +66295,7 @@
         <v>0.42</v>
       </c>
       <c r="H1937" s="2" t="n">
-        <v>46095.3546983643</v>
+        <v>46095.35469836806</v>
       </c>
     </row>
     <row r="1938">
@@ -66329,7 +66329,7 @@
         <v>2.02</v>
       </c>
       <c r="H1938" s="2" t="n">
-        <v>46087.3546983674</v>
+        <v>46087.35469836806</v>
       </c>
     </row>
     <row r="1939">
@@ -66363,7 +66363,7 @@
         <v>0.5</v>
       </c>
       <c r="H1939" s="2" t="n">
-        <v>46076.35469837041</v>
+        <v>46076.35469836806</v>
       </c>
     </row>
     <row r="1940">
@@ -66397,7 +66397,7 @@
         <v>0.73</v>
       </c>
       <c r="H1940" s="2" t="n">
-        <v>46090.35469837364</v>
+        <v>46090.35469836806</v>
       </c>
     </row>
     <row r="1941">
@@ -66431,7 +66431,7 @@
         <v>2.47</v>
       </c>
       <c r="H1941" s="2" t="n">
-        <v>46077.35469837664</v>
+        <v>46077.35469837963</v>
       </c>
     </row>
     <row r="1942">
@@ -66465,7 +66465,7 @@
         <v>0.52</v>
       </c>
       <c r="H1942" s="2" t="n">
-        <v>46069.35469837979</v>
+        <v>46069.35469837963</v>
       </c>
     </row>
     <row r="1943">
@@ -66499,7 +66499,7 @@
         <v>4.1</v>
       </c>
       <c r="H1943" s="2" t="n">
-        <v>46076.35469838334</v>
+        <v>46076.35469837963</v>
       </c>
     </row>
     <row r="1944">
@@ -66533,7 +66533,7 @@
         <v>1.73</v>
       </c>
       <c r="H1944" s="2" t="n">
-        <v>46068.35469838638</v>
+        <v>46068.3546983912</v>
       </c>
     </row>
     <row r="1945">
@@ -66567,7 +66567,7 @@
         <v>4.16</v>
       </c>
       <c r="H1945" s="2" t="n">
-        <v>46086.35469838942</v>
+        <v>46086.3546983912</v>
       </c>
     </row>
     <row r="1946">
@@ -66601,7 +66601,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="H1946" s="2" t="n">
-        <v>46080.35469839242</v>
+        <v>46080.3546983912</v>
       </c>
     </row>
     <row r="1947">
@@ -66635,7 +66635,7 @@
         <v>0.34</v>
       </c>
       <c r="H1947" s="2" t="n">
-        <v>46067.3546983958</v>
+        <v>46067.3546983912</v>
       </c>
     </row>
     <row r="1948">
@@ -66669,7 +66669,7 @@
         <v>4.15</v>
       </c>
       <c r="H1948" s="2" t="n">
-        <v>46081.35469839891</v>
+        <v>46081.35469840278</v>
       </c>
     </row>
     <row r="1949">
@@ -66703,7 +66703,7 @@
         <v>0.53</v>
       </c>
       <c r="H1949" s="2" t="n">
-        <v>46086.35469840227</v>
+        <v>46086.35469840278</v>
       </c>
     </row>
     <row r="1950">
@@ -66737,7 +66737,7 @@
         <v>0.97</v>
       </c>
       <c r="H1950" s="2" t="n">
-        <v>46096.35469840537</v>
+        <v>46096.35469840278</v>
       </c>
     </row>
     <row r="1951">
@@ -66771,7 +66771,1707 @@
         <v>3.3</v>
       </c>
       <c r="H1951" s="2" t="n">
-        <v>46085.35469840858</v>
+        <v>46085.35469841435</v>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" t="inlineStr">
+        <is>
+          <t>e8df55ff-27fd-43a3-98ae-604f4c60bf41</t>
+        </is>
+      </c>
+      <c r="B1952" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1952" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1952" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1952" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1952" t="n">
+        <v>256.46</v>
+      </c>
+      <c r="G1952" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H1952" s="2" t="n">
+        <v>46072.39949894831</v>
+      </c>
+    </row>
+    <row r="1953">
+      <c r="A1953" t="inlineStr">
+        <is>
+          <t>8ec13404-c2ae-4e62-b157-d661c95e956d</t>
+        </is>
+      </c>
+      <c r="B1953" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1953" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1953" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1953" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1953" t="n">
+        <v>164.13</v>
+      </c>
+      <c r="G1953" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H1953" s="2" t="n">
+        <v>46068.39949895244</v>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" t="inlineStr">
+        <is>
+          <t>3920277a-4eca-44f6-a078-cc5deed7c2e1</t>
+        </is>
+      </c>
+      <c r="B1954" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1954" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1954" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1954" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1954" t="n">
+        <v>68.95</v>
+      </c>
+      <c r="G1954" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H1954" s="2" t="n">
+        <v>46096.39949895548</v>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" t="inlineStr">
+        <is>
+          <t>a35f2ff8-5cab-48e7-9761-fd41fa4f300b</t>
+        </is>
+      </c>
+      <c r="B1955" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1955" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1955" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1955" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1955" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="G1955" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H1955" s="2" t="n">
+        <v>46089.39949895888</v>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" t="inlineStr">
+        <is>
+          <t>fb7bbd5d-7616-4a33-bc2f-edff28c235a9</t>
+        </is>
+      </c>
+      <c r="B1956" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1956" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1956" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1956" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1956" t="n">
+        <v>139.96</v>
+      </c>
+      <c r="G1956" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H1956" s="2" t="n">
+        <v>46078.39949896192</v>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" t="inlineStr">
+        <is>
+          <t>541347c8-d8e5-462d-8a85-9565a13bc23d</t>
+        </is>
+      </c>
+      <c r="B1957" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1957" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1957" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1957" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1957" t="n">
+        <v>368.03</v>
+      </c>
+      <c r="G1957" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="H1957" s="2" t="n">
+        <v>46084.39949896483</v>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" t="inlineStr">
+        <is>
+          <t>ed27e6eb-be26-4ae7-ac2d-a4872b07d39d</t>
+        </is>
+      </c>
+      <c r="B1958" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1958" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1958" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1958" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1958" t="n">
+        <v>492.01</v>
+      </c>
+      <c r="G1958" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="H1958" s="2" t="n">
+        <v>46069.39949896766</v>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" t="inlineStr">
+        <is>
+          <t>e7525ac4-356b-4426-9660-aa84ffcac4ca</t>
+        </is>
+      </c>
+      <c r="B1959" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1959" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1959" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1959" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1959" t="n">
+        <v>206.69</v>
+      </c>
+      <c r="G1959" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="H1959" s="2" t="n">
+        <v>46073.39949897063</v>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" t="inlineStr">
+        <is>
+          <t>7243cab6-5d8f-47cb-a027-8ba269247d74</t>
+        </is>
+      </c>
+      <c r="B1960" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1960" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1960" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1960" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1960" t="n">
+        <v>345.17</v>
+      </c>
+      <c r="G1960" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H1960" s="2" t="n">
+        <v>46073.39949897349</v>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" t="inlineStr">
+        <is>
+          <t>ed7c587c-d84e-4b60-8409-a91c56f95ac2</t>
+        </is>
+      </c>
+      <c r="B1961" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1961" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1961" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1961" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1961" t="n">
+        <v>98.14</v>
+      </c>
+      <c r="G1961" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H1961" s="2" t="n">
+        <v>46089.39949897646</v>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" t="inlineStr">
+        <is>
+          <t>f4b8e19c-adc9-4a42-926a-b701b967ad15</t>
+        </is>
+      </c>
+      <c r="B1962" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1962" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1962" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1962" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1962" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="G1962" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1962" s="2" t="n">
+        <v>46096.39949897966</v>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" t="inlineStr">
+        <is>
+          <t>d8b3a84c-ebe3-4f7d-a9ee-11c921b7a51c</t>
+        </is>
+      </c>
+      <c r="B1963" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1963" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1963" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1963" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1963" t="n">
+        <v>78.66</v>
+      </c>
+      <c r="G1963" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H1963" s="2" t="n">
+        <v>46078.39949898252</v>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" t="inlineStr">
+        <is>
+          <t>60a7116f-f5bf-487b-bbaf-b87391334bad</t>
+        </is>
+      </c>
+      <c r="B1964" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1964" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1964" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1964" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1964" t="n">
+        <v>184.34</v>
+      </c>
+      <c r="G1964" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H1964" s="2" t="n">
+        <v>46087.39949898548</v>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" t="inlineStr">
+        <is>
+          <t>1263ef02-e612-430a-8b57-ef00790ca2a4</t>
+        </is>
+      </c>
+      <c r="B1965" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1965" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1965" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1965" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1965" t="n">
+        <v>288.42</v>
+      </c>
+      <c r="G1965" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H1965" s="2" t="n">
+        <v>46079.39949898839</v>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" t="inlineStr">
+        <is>
+          <t>1a49dc48-c949-430c-8803-e49a95ad41b4</t>
+        </is>
+      </c>
+      <c r="B1966" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1966" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1966" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1966" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1966" t="n">
+        <v>245.58</v>
+      </c>
+      <c r="G1966" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H1966" s="2" t="n">
+        <v>46075.39949899139</v>
+      </c>
+    </row>
+    <row r="1967">
+      <c r="A1967" t="inlineStr">
+        <is>
+          <t>6f21c631-712b-4e8c-8d2b-8eda4d9d0b4f</t>
+        </is>
+      </c>
+      <c r="B1967" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1967" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1967" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1967" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1967" t="n">
+        <v>476.55</v>
+      </c>
+      <c r="G1967" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="H1967" s="2" t="n">
+        <v>46086.39949899426</v>
+      </c>
+    </row>
+    <row r="1968">
+      <c r="A1968" t="inlineStr">
+        <is>
+          <t>cd795b4a-2522-439b-aa80-bec36333313a</t>
+        </is>
+      </c>
+      <c r="B1968" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1968" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1968" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1968" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1968" t="n">
+        <v>243.42</v>
+      </c>
+      <c r="G1968" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="H1968" s="2" t="n">
+        <v>46095.39949899706</v>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" t="inlineStr">
+        <is>
+          <t>2325aa40-69c2-41a8-922b-8a0bda2ad7ed</t>
+        </is>
+      </c>
+      <c r="B1969" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1969" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1969" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1969" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1969" t="n">
+        <v>254.13</v>
+      </c>
+      <c r="G1969" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H1969" s="2" t="n">
+        <v>46095.39949899985</v>
+      </c>
+    </row>
+    <row r="1970">
+      <c r="A1970" t="inlineStr">
+        <is>
+          <t>63ab935b-948d-4476-868a-9f88da018472</t>
+        </is>
+      </c>
+      <c r="B1970" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1970" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1970" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1970" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1970" t="n">
+        <v>414.29</v>
+      </c>
+      <c r="G1970" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H1970" s="2" t="n">
+        <v>46090.39949900293</v>
+      </c>
+    </row>
+    <row r="1971">
+      <c r="A1971" t="inlineStr">
+        <is>
+          <t>9e12a349-d062-4e18-ac97-8922fd728020</t>
+        </is>
+      </c>
+      <c r="B1971" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1971" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1971" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1971" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1971" t="n">
+        <v>313.88</v>
+      </c>
+      <c r="G1971" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H1971" s="2" t="n">
+        <v>46076.39949900575</v>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" t="inlineStr">
+        <is>
+          <t>7b0651a5-24ed-4635-9c20-42e8226ad2d0</t>
+        </is>
+      </c>
+      <c r="B1972" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1972" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1972" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1972" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1972" t="n">
+        <v>220.59</v>
+      </c>
+      <c r="G1972" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="H1972" s="2" t="n">
+        <v>46094.3994990086</v>
+      </c>
+    </row>
+    <row r="1973">
+      <c r="A1973" t="inlineStr">
+        <is>
+          <t>90c6355f-4946-4b87-a9d7-3f4ed71fbe0b</t>
+        </is>
+      </c>
+      <c r="B1973" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1973" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1973" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1973" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1973" t="n">
+        <v>481.83</v>
+      </c>
+      <c r="G1973" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="H1973" s="2" t="n">
+        <v>46085.39949901148</v>
+      </c>
+    </row>
+    <row r="1974">
+      <c r="A1974" t="inlineStr">
+        <is>
+          <t>5bbc5c66-07d8-4110-a2ae-7567871dc643</t>
+        </is>
+      </c>
+      <c r="B1974" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1974" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1974" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1974" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1974" t="n">
+        <v>387.28</v>
+      </c>
+      <c r="G1974" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="H1974" s="2" t="n">
+        <v>46091.39949901441</v>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" t="inlineStr">
+        <is>
+          <t>2753f472-9f03-49c3-a7ed-0102cff1539a</t>
+        </is>
+      </c>
+      <c r="B1975" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1975" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1975" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1975" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1975" t="n">
+        <v>219.27</v>
+      </c>
+      <c r="G1975" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="H1975" s="2" t="n">
+        <v>46095.39949901721</v>
+      </c>
+    </row>
+    <row r="1976">
+      <c r="A1976" t="inlineStr">
+        <is>
+          <t>ae56f9ea-e16a-4b3e-8b8b-3ca2cfd5ab97</t>
+        </is>
+      </c>
+      <c r="B1976" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1976" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1976" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1976" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1976" t="n">
+        <v>368.85</v>
+      </c>
+      <c r="G1976" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="H1976" s="2" t="n">
+        <v>46090.39949902004</v>
+      </c>
+    </row>
+    <row r="1977">
+      <c r="A1977" t="inlineStr">
+        <is>
+          <t>27b61076-ce80-48ab-a16a-d7e5f7789397</t>
+        </is>
+      </c>
+      <c r="B1977" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1977" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1977" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1977" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1977" t="n">
+        <v>243.14</v>
+      </c>
+      <c r="G1977" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="H1977" s="2" t="n">
+        <v>46071.39949902306</v>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" t="inlineStr">
+        <is>
+          <t>800a7a7c-043c-4beb-bb1f-c5eb62d717ae</t>
+        </is>
+      </c>
+      <c r="B1978" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1978" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1978" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1978" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1978" t="n">
+        <v>242.41</v>
+      </c>
+      <c r="G1978" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H1978" s="2" t="n">
+        <v>46071.3994990261</v>
+      </c>
+    </row>
+    <row r="1979">
+      <c r="A1979" t="inlineStr">
+        <is>
+          <t>a729c4d0-2dda-4137-bd98-a76ed12e09c3</t>
+        </is>
+      </c>
+      <c r="B1979" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1979" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1979" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1979" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1979" t="n">
+        <v>456.9</v>
+      </c>
+      <c r="G1979" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="H1979" s="2" t="n">
+        <v>46080.39949902906</v>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" t="inlineStr">
+        <is>
+          <t>34006e11-eb4d-4a75-bfac-12b7b1441bce</t>
+        </is>
+      </c>
+      <c r="B1980" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1980" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1980" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1980" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1980" t="n">
+        <v>460.4</v>
+      </c>
+      <c r="G1980" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H1980" s="2" t="n">
+        <v>46083.3994990319</v>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" t="inlineStr">
+        <is>
+          <t>b448bccd-e187-4f92-b931-31a650dba3e2</t>
+        </is>
+      </c>
+      <c r="B1981" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1981" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1981" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1981" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1981" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="G1981" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H1981" s="2" t="n">
+        <v>46067.39949903472</v>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" t="inlineStr">
+        <is>
+          <t>7992cbbf-8169-422c-acca-cc9b2ccbedf1</t>
+        </is>
+      </c>
+      <c r="B1982" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1982" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1982" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1982" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1982" t="n">
+        <v>183.95</v>
+      </c>
+      <c r="G1982" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H1982" s="2" t="n">
+        <v>46082.39949903785</v>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" t="inlineStr">
+        <is>
+          <t>224ee8a3-4d7b-4de2-85d0-d56b94d263a2</t>
+        </is>
+      </c>
+      <c r="B1983" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1983" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1983" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1983" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1983" t="n">
+        <v>255.71</v>
+      </c>
+      <c r="G1983" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H1983" s="2" t="n">
+        <v>46088.39949904069</v>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" t="inlineStr">
+        <is>
+          <t>ea7c0426-b996-45cc-a465-1077bb17cb8a</t>
+        </is>
+      </c>
+      <c r="B1984" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1984" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1984" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1984" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1984" t="n">
+        <v>352.54</v>
+      </c>
+      <c r="G1984" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="H1984" s="2" t="n">
+        <v>46094.3994990436</v>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" t="inlineStr">
+        <is>
+          <t>7be97863-8971-4afa-b811-1cabcda9b6a7</t>
+        </is>
+      </c>
+      <c r="B1985" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1985" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1985" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1985" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1985" t="n">
+        <v>88.66</v>
+      </c>
+      <c r="G1985" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H1985" s="2" t="n">
+        <v>46075.39949904659</v>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" t="inlineStr">
+        <is>
+          <t>d600776c-0197-46c8-8b60-62b89d332466</t>
+        </is>
+      </c>
+      <c r="B1986" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1986" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1986" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1986" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1986" t="n">
+        <v>254.27</v>
+      </c>
+      <c r="G1986" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H1986" s="2" t="n">
+        <v>46080.39949904947</v>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" t="inlineStr">
+        <is>
+          <t>55939fd7-813f-4b53-97be-260fc5ea18e5</t>
+        </is>
+      </c>
+      <c r="B1987" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1987" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1987" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1987" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1987" t="n">
+        <v>377.79</v>
+      </c>
+      <c r="G1987" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="H1987" s="2" t="n">
+        <v>46069.39949905243</v>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" t="inlineStr">
+        <is>
+          <t>1345e873-4cab-426a-825f-f3af3e0d3f75</t>
+        </is>
+      </c>
+      <c r="B1988" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1988" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1988" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1988" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1988" t="n">
+        <v>319.99</v>
+      </c>
+      <c r="G1988" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H1988" s="2" t="n">
+        <v>46081.39949905523</v>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" t="inlineStr">
+        <is>
+          <t>c04f8cbb-e9e4-4fcd-a8f9-2a07f19f6c59</t>
+        </is>
+      </c>
+      <c r="B1989" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1989" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1989" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1989" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1989" t="n">
+        <v>471.61</v>
+      </c>
+      <c r="G1989" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="H1989" s="2" t="n">
+        <v>46073.39949905807</v>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" t="inlineStr">
+        <is>
+          <t>dbcf8f2b-abf3-4a0e-940d-74d8b053c70b</t>
+        </is>
+      </c>
+      <c r="B1990" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1990" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1990" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1990" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1990" t="n">
+        <v>261.66</v>
+      </c>
+      <c r="G1990" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H1990" s="2" t="n">
+        <v>46094.39949906095</v>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" t="inlineStr">
+        <is>
+          <t>5ce56817-2b12-4814-9fa4-e9b9d59e8412</t>
+        </is>
+      </c>
+      <c r="B1991" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1991" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1991" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1991" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1991" t="n">
+        <v>125.39</v>
+      </c>
+      <c r="G1991" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H1991" s="2" t="n">
+        <v>46075.39949906385</v>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" t="inlineStr">
+        <is>
+          <t>18b97689-8265-4500-82bf-c1c9a5fb0001</t>
+        </is>
+      </c>
+      <c r="B1992" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1992" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1992" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1992" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1992" t="n">
+        <v>273.6</v>
+      </c>
+      <c r="G1992" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H1992" s="2" t="n">
+        <v>46074.3994990667</v>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" t="inlineStr">
+        <is>
+          <t>48a0c40d-5036-4684-af47-d344ed1a85e1</t>
+        </is>
+      </c>
+      <c r="B1993" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1993" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1993" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1993" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1993" t="n">
+        <v>498.83</v>
+      </c>
+      <c r="G1993" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="H1993" s="2" t="n">
+        <v>46081.39949906961</v>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" t="inlineStr">
+        <is>
+          <t>e220f895-7e66-4d4c-9064-89814e079e0c</t>
+        </is>
+      </c>
+      <c r="B1994" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1994" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1994" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1994" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1994" t="n">
+        <v>158.18</v>
+      </c>
+      <c r="G1994" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H1994" s="2" t="n">
+        <v>46071.39949907256</v>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" t="inlineStr">
+        <is>
+          <t>f572e262-7cbb-476a-bc5e-df82699b0347</t>
+        </is>
+      </c>
+      <c r="B1995" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1995" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1995" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1995" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1995" t="n">
+        <v>296.14</v>
+      </c>
+      <c r="G1995" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="H1995" s="2" t="n">
+        <v>46074.39949907553</v>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" t="inlineStr">
+        <is>
+          <t>acdc337c-712a-4d83-b41f-2b1d839258f0</t>
+        </is>
+      </c>
+      <c r="B1996" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1996" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1996" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1996" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F1996" t="n">
+        <v>193.63</v>
+      </c>
+      <c r="G1996" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H1996" s="2" t="n">
+        <v>46082.39949907839</v>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" t="inlineStr">
+        <is>
+          <t>318e3450-d48a-4a75-bf6d-51783234c03b</t>
+        </is>
+      </c>
+      <c r="B1997" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1997" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1997" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1997" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F1997" t="n">
+        <v>268.43</v>
+      </c>
+      <c r="G1997" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H1997" s="2" t="n">
+        <v>46074.39949908133</v>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" t="inlineStr">
+        <is>
+          <t>a7df247c-43ed-4a2f-875f-3a270546003d</t>
+        </is>
+      </c>
+      <c r="B1998" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1998" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1998" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1998" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1998" t="n">
+        <v>353.53</v>
+      </c>
+      <c r="G1998" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="H1998" s="2" t="n">
+        <v>46083.3994990844</v>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" t="inlineStr">
+        <is>
+          <t>5c5d9819-ee15-4849-b212-a393a9794699</t>
+        </is>
+      </c>
+      <c r="B1999" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1999" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D1999" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E1999" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F1999" t="n">
+        <v>493.41</v>
+      </c>
+      <c r="G1999" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="H1999" s="2" t="n">
+        <v>46083.39949908742</v>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" t="inlineStr">
+        <is>
+          <t>f3f6d821-b359-41f2-9cb0-c9ffb72a2b7d</t>
+        </is>
+      </c>
+      <c r="B2000" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2000" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2000" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2000" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2000" t="n">
+        <v>275.23</v>
+      </c>
+      <c r="G2000" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H2000" s="2" t="n">
+        <v>46069.39949909023</v>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" t="inlineStr">
+        <is>
+          <t>aac3da22-cd33-49bc-96a2-39507718f78f</t>
+        </is>
+      </c>
+      <c r="B2001" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2001" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2001" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2001" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2001" t="n">
+        <v>53.91</v>
+      </c>
+      <c r="G2001" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H2001" s="2" t="n">
+        <v>46095.39949909318</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2001"/>
+  <dimension ref="A1:H2051"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66805,7 +66805,7 @@
         <v>2.56</v>
       </c>
       <c r="H1952" s="2" t="n">
-        <v>46072.39949894831</v>
+        <v>46072.39949894676</v>
       </c>
     </row>
     <row r="1953">
@@ -66839,7 +66839,7 @@
         <v>1.64</v>
       </c>
       <c r="H1953" s="2" t="n">
-        <v>46068.39949895244</v>
+        <v>46068.39949894676</v>
       </c>
     </row>
     <row r="1954">
@@ -66873,7 +66873,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="H1954" s="2" t="n">
-        <v>46096.39949895548</v>
+        <v>46096.39949895833</v>
       </c>
     </row>
     <row r="1955">
@@ -66907,7 +66907,7 @@
         <v>0.88</v>
       </c>
       <c r="H1955" s="2" t="n">
-        <v>46089.39949895888</v>
+        <v>46089.39949895833</v>
       </c>
     </row>
     <row r="1956">
@@ -66941,7 +66941,7 @@
         <v>1.4</v>
       </c>
       <c r="H1956" s="2" t="n">
-        <v>46078.39949896192</v>
+        <v>46078.39949895833</v>
       </c>
     </row>
     <row r="1957">
@@ -66975,7 +66975,7 @@
         <v>3.68</v>
       </c>
       <c r="H1957" s="2" t="n">
-        <v>46084.39949896483</v>
+        <v>46084.39949896991</v>
       </c>
     </row>
     <row r="1958">
@@ -67009,7 +67009,7 @@
         <v>4.92</v>
       </c>
       <c r="H1958" s="2" t="n">
-        <v>46069.39949896766</v>
+        <v>46069.39949896991</v>
       </c>
     </row>
     <row r="1959">
@@ -67043,7 +67043,7 @@
         <v>2.07</v>
       </c>
       <c r="H1959" s="2" t="n">
-        <v>46073.39949897063</v>
+        <v>46073.39949896991</v>
       </c>
     </row>
     <row r="1960">
@@ -67077,7 +67077,7 @@
         <v>3.45</v>
       </c>
       <c r="H1960" s="2" t="n">
-        <v>46073.39949897349</v>
+        <v>46073.39949896991</v>
       </c>
     </row>
     <row r="1961">
@@ -67111,7 +67111,7 @@
         <v>0.98</v>
       </c>
       <c r="H1961" s="2" t="n">
-        <v>46089.39949897646</v>
+        <v>46089.39949898148</v>
       </c>
     </row>
     <row r="1962">
@@ -67145,7 +67145,7 @@
         <v>1</v>
       </c>
       <c r="H1962" s="2" t="n">
-        <v>46096.39949897966</v>
+        <v>46096.39949898148</v>
       </c>
     </row>
     <row r="1963">
@@ -67179,7 +67179,7 @@
         <v>0.79</v>
       </c>
       <c r="H1963" s="2" t="n">
-        <v>46078.39949898252</v>
+        <v>46078.39949898148</v>
       </c>
     </row>
     <row r="1964">
@@ -67213,7 +67213,7 @@
         <v>1.84</v>
       </c>
       <c r="H1964" s="2" t="n">
-        <v>46087.39949898548</v>
+        <v>46087.39949898148</v>
       </c>
     </row>
     <row r="1965">
@@ -67247,7 +67247,7 @@
         <v>2.88</v>
       </c>
       <c r="H1965" s="2" t="n">
-        <v>46079.39949898839</v>
+        <v>46079.39949899306</v>
       </c>
     </row>
     <row r="1966">
@@ -67281,7 +67281,7 @@
         <v>2.46</v>
       </c>
       <c r="H1966" s="2" t="n">
-        <v>46075.39949899139</v>
+        <v>46075.39949899306</v>
       </c>
     </row>
     <row r="1967">
@@ -67315,7 +67315,7 @@
         <v>4.77</v>
       </c>
       <c r="H1967" s="2" t="n">
-        <v>46086.39949899426</v>
+        <v>46086.39949899306</v>
       </c>
     </row>
     <row r="1968">
@@ -67349,7 +67349,7 @@
         <v>2.43</v>
       </c>
       <c r="H1968" s="2" t="n">
-        <v>46095.39949899706</v>
+        <v>46095.39949899306</v>
       </c>
     </row>
     <row r="1969">
@@ -67383,7 +67383,7 @@
         <v>2.54</v>
       </c>
       <c r="H1969" s="2" t="n">
-        <v>46095.39949899985</v>
+        <v>46095.39949900463</v>
       </c>
     </row>
     <row r="1970">
@@ -67417,7 +67417,7 @@
         <v>4.14</v>
       </c>
       <c r="H1970" s="2" t="n">
-        <v>46090.39949900293</v>
+        <v>46090.39949900463</v>
       </c>
     </row>
     <row r="1971">
@@ -67451,7 +67451,7 @@
         <v>3.14</v>
       </c>
       <c r="H1971" s="2" t="n">
-        <v>46076.39949900575</v>
+        <v>46076.39949900463</v>
       </c>
     </row>
     <row r="1972">
@@ -67485,7 +67485,7 @@
         <v>2.21</v>
       </c>
       <c r="H1972" s="2" t="n">
-        <v>46094.3994990086</v>
+        <v>46094.39949900463</v>
       </c>
     </row>
     <row r="1973">
@@ -67519,7 +67519,7 @@
         <v>4.82</v>
       </c>
       <c r="H1973" s="2" t="n">
-        <v>46085.39949901148</v>
+        <v>46085.3994990162</v>
       </c>
     </row>
     <row r="1974">
@@ -67553,7 +67553,7 @@
         <v>3.87</v>
       </c>
       <c r="H1974" s="2" t="n">
-        <v>46091.39949901441</v>
+        <v>46091.3994990162</v>
       </c>
     </row>
     <row r="1975">
@@ -67587,7 +67587,7 @@
         <v>2.19</v>
       </c>
       <c r="H1975" s="2" t="n">
-        <v>46095.39949901721</v>
+        <v>46095.3994990162</v>
       </c>
     </row>
     <row r="1976">
@@ -67621,7 +67621,7 @@
         <v>3.69</v>
       </c>
       <c r="H1976" s="2" t="n">
-        <v>46090.39949902004</v>
+        <v>46090.3994990162</v>
       </c>
     </row>
     <row r="1977">
@@ -67655,7 +67655,7 @@
         <v>2.43</v>
       </c>
       <c r="H1977" s="2" t="n">
-        <v>46071.39949902306</v>
+        <v>46071.39949902778</v>
       </c>
     </row>
     <row r="1978">
@@ -67689,7 +67689,7 @@
         <v>2.42</v>
       </c>
       <c r="H1978" s="2" t="n">
-        <v>46071.3994990261</v>
+        <v>46071.39949902778</v>
       </c>
     </row>
     <row r="1979">
@@ -67723,7 +67723,7 @@
         <v>4.57</v>
       </c>
       <c r="H1979" s="2" t="n">
-        <v>46080.39949902906</v>
+        <v>46080.39949902778</v>
       </c>
     </row>
     <row r="1980">
@@ -67757,7 +67757,7 @@
         <v>4.6</v>
       </c>
       <c r="H1980" s="2" t="n">
-        <v>46083.3994990319</v>
+        <v>46083.39949902778</v>
       </c>
     </row>
     <row r="1981">
@@ -67791,7 +67791,7 @@
         <v>0.11</v>
       </c>
       <c r="H1981" s="2" t="n">
-        <v>46067.39949903472</v>
+        <v>46067.39949903935</v>
       </c>
     </row>
     <row r="1982">
@@ -67825,7 +67825,7 @@
         <v>1.84</v>
       </c>
       <c r="H1982" s="2" t="n">
-        <v>46082.39949903785</v>
+        <v>46082.39949903935</v>
       </c>
     </row>
     <row r="1983">
@@ -67859,7 +67859,7 @@
         <v>2.56</v>
       </c>
       <c r="H1983" s="2" t="n">
-        <v>46088.39949904069</v>
+        <v>46088.39949903935</v>
       </c>
     </row>
     <row r="1984">
@@ -67893,7 +67893,7 @@
         <v>3.53</v>
       </c>
       <c r="H1984" s="2" t="n">
-        <v>46094.3994990436</v>
+        <v>46094.39949903935</v>
       </c>
     </row>
     <row r="1985">
@@ -67927,7 +67927,7 @@
         <v>0.89</v>
       </c>
       <c r="H1985" s="2" t="n">
-        <v>46075.39949904659</v>
+        <v>46075.39949905092</v>
       </c>
     </row>
     <row r="1986">
@@ -67961,7 +67961,7 @@
         <v>2.54</v>
       </c>
       <c r="H1986" s="2" t="n">
-        <v>46080.39949904947</v>
+        <v>46080.39949905092</v>
       </c>
     </row>
     <row r="1987">
@@ -67995,7 +67995,7 @@
         <v>3.78</v>
       </c>
       <c r="H1987" s="2" t="n">
-        <v>46069.39949905243</v>
+        <v>46069.39949905092</v>
       </c>
     </row>
     <row r="1988">
@@ -68029,7 +68029,7 @@
         <v>3.2</v>
       </c>
       <c r="H1988" s="2" t="n">
-        <v>46081.39949905523</v>
+        <v>46081.39949905092</v>
       </c>
     </row>
     <row r="1989">
@@ -68063,7 +68063,7 @@
         <v>4.72</v>
       </c>
       <c r="H1989" s="2" t="n">
-        <v>46073.39949905807</v>
+        <v>46073.3994990625</v>
       </c>
     </row>
     <row r="1990">
@@ -68097,7 +68097,7 @@
         <v>2.62</v>
       </c>
       <c r="H1990" s="2" t="n">
-        <v>46094.39949906095</v>
+        <v>46094.3994990625</v>
       </c>
     </row>
     <row r="1991">
@@ -68131,7 +68131,7 @@
         <v>1.25</v>
       </c>
       <c r="H1991" s="2" t="n">
-        <v>46075.39949906385</v>
+        <v>46075.3994990625</v>
       </c>
     </row>
     <row r="1992">
@@ -68165,7 +68165,7 @@
         <v>2.74</v>
       </c>
       <c r="H1992" s="2" t="n">
-        <v>46074.3994990667</v>
+        <v>46074.3994990625</v>
       </c>
     </row>
     <row r="1993">
@@ -68199,7 +68199,7 @@
         <v>4.99</v>
       </c>
       <c r="H1993" s="2" t="n">
-        <v>46081.39949906961</v>
+        <v>46081.39949907408</v>
       </c>
     </row>
     <row r="1994">
@@ -68233,7 +68233,7 @@
         <v>1.58</v>
       </c>
       <c r="H1994" s="2" t="n">
-        <v>46071.39949907256</v>
+        <v>46071.39949907408</v>
       </c>
     </row>
     <row r="1995">
@@ -68267,7 +68267,7 @@
         <v>2.96</v>
       </c>
       <c r="H1995" s="2" t="n">
-        <v>46074.39949907553</v>
+        <v>46074.39949907408</v>
       </c>
     </row>
     <row r="1996">
@@ -68301,7 +68301,7 @@
         <v>1.94</v>
       </c>
       <c r="H1996" s="2" t="n">
-        <v>46082.39949907839</v>
+        <v>46082.39949907408</v>
       </c>
     </row>
     <row r="1997">
@@ -68335,7 +68335,7 @@
         <v>2.68</v>
       </c>
       <c r="H1997" s="2" t="n">
-        <v>46074.39949908133</v>
+        <v>46074.39949908565</v>
       </c>
     </row>
     <row r="1998">
@@ -68369,7 +68369,7 @@
         <v>3.54</v>
       </c>
       <c r="H1998" s="2" t="n">
-        <v>46083.3994990844</v>
+        <v>46083.39949908565</v>
       </c>
     </row>
     <row r="1999">
@@ -68403,7 +68403,7 @@
         <v>4.93</v>
       </c>
       <c r="H1999" s="2" t="n">
-        <v>46083.39949908742</v>
+        <v>46083.39949908565</v>
       </c>
     </row>
     <row r="2000">
@@ -68437,7 +68437,7 @@
         <v>2.75</v>
       </c>
       <c r="H2000" s="2" t="n">
-        <v>46069.39949909023</v>
+        <v>46069.39949908565</v>
       </c>
     </row>
     <row r="2001">
@@ -68471,7 +68471,1707 @@
         <v>0.54</v>
       </c>
       <c r="H2001" s="2" t="n">
-        <v>46095.39949909318</v>
+        <v>46095.39949909722</v>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" t="inlineStr">
+        <is>
+          <t>d6962470-d22a-46dc-94b9-ad2a8e1973b9</t>
+        </is>
+      </c>
+      <c r="B2002" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2002" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2002" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2002" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2002" t="n">
+        <v>110.13</v>
+      </c>
+      <c r="G2002" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H2002" s="2" t="n">
+        <v>46075.4378169697</v>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" t="inlineStr">
+        <is>
+          <t>0babc8de-4663-47fd-b7d1-3cb47da498fb</t>
+        </is>
+      </c>
+      <c r="B2003" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2003" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2003" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2003" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2003" t="n">
+        <v>188.33</v>
+      </c>
+      <c r="G2003" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H2003" s="2" t="n">
+        <v>46089.43781697456</v>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" t="inlineStr">
+        <is>
+          <t>4a33b787-ee7a-4d0f-af55-78e55f54edb5</t>
+        </is>
+      </c>
+      <c r="B2004" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2004" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2004" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2004" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2004" t="n">
+        <v>222.5</v>
+      </c>
+      <c r="G2004" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H2004" s="2" t="n">
+        <v>46087.43781697774</v>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" t="inlineStr">
+        <is>
+          <t>14b2b5f9-882d-4910-be44-a5ce08d66961</t>
+        </is>
+      </c>
+      <c r="B2005" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2005" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2005" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2005" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2005" t="n">
+        <v>391.21</v>
+      </c>
+      <c r="G2005" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="H2005" s="2" t="n">
+        <v>46088.43781698091</v>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" t="inlineStr">
+        <is>
+          <t>fdf52d98-33f3-42ac-8081-5d94db6b0927</t>
+        </is>
+      </c>
+      <c r="B2006" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2006" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2006" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2006" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2006" t="n">
+        <v>201.45</v>
+      </c>
+      <c r="G2006" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="H2006" s="2" t="n">
+        <v>46076.43781698418</v>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" t="inlineStr">
+        <is>
+          <t>cfb9efd0-36c2-471f-baaf-7c4f8e9ddee2</t>
+        </is>
+      </c>
+      <c r="B2007" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2007" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2007" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2007" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2007" t="n">
+        <v>483.17</v>
+      </c>
+      <c r="G2007" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="H2007" s="2" t="n">
+        <v>46090.4378169873</v>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="inlineStr">
+        <is>
+          <t>9dbd4538-1945-485b-a2cf-92b03461af10</t>
+        </is>
+      </c>
+      <c r="B2008" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2008" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2008" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2008" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2008" t="n">
+        <v>118.57</v>
+      </c>
+      <c r="G2008" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H2008" s="2" t="n">
+        <v>46090.43781699042</v>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" t="inlineStr">
+        <is>
+          <t>f909aeaf-5210-4c7d-98d4-8f2bb3dfd37f</t>
+        </is>
+      </c>
+      <c r="B2009" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2009" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2009" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2009" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2009" t="n">
+        <v>180.82</v>
+      </c>
+      <c r="G2009" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H2009" s="2" t="n">
+        <v>46072.43781699354</v>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" t="inlineStr">
+        <is>
+          <t>9ad126d7-613c-469c-a162-6b4449305ea7</t>
+        </is>
+      </c>
+      <c r="B2010" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2010" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2010" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2010" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2010" t="n">
+        <v>453.34</v>
+      </c>
+      <c r="G2010" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="H2010" s="2" t="n">
+        <v>46095.43781699693</v>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" t="inlineStr">
+        <is>
+          <t>bea60411-3170-48bb-9de3-4030fcc563e4</t>
+        </is>
+      </c>
+      <c r="B2011" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2011" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2011" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2011" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2011" t="n">
+        <v>159.64</v>
+      </c>
+      <c r="G2011" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H2011" s="2" t="n">
+        <v>46088.43781700027</v>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" t="inlineStr">
+        <is>
+          <t>a39d0f42-a7ee-4622-8f78-2e0e39e6bf5e</t>
+        </is>
+      </c>
+      <c r="B2012" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2012" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2012" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2012" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2012" t="n">
+        <v>217.95</v>
+      </c>
+      <c r="G2012" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H2012" s="2" t="n">
+        <v>46092.43781700351</v>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" t="inlineStr">
+        <is>
+          <t>a461ff1d-aa1f-4851-a646-0cd9f44fd430</t>
+        </is>
+      </c>
+      <c r="B2013" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2013" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2013" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2013" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2013" t="n">
+        <v>129.05</v>
+      </c>
+      <c r="G2013" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H2013" s="2" t="n">
+        <v>46079.4378170067</v>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" t="inlineStr">
+        <is>
+          <t>dc490bde-35c3-49f8-bf98-c443a7c5f89b</t>
+        </is>
+      </c>
+      <c r="B2014" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2014" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2014" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2014" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2014" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="G2014" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H2014" s="2" t="n">
+        <v>46089.43781701</v>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="inlineStr">
+        <is>
+          <t>4eb6714f-e44f-45db-b2a9-97c4c4c913d6</t>
+        </is>
+      </c>
+      <c r="B2015" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2015" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2015" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2015" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2015" t="n">
+        <v>357.73</v>
+      </c>
+      <c r="G2015" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="H2015" s="2" t="n">
+        <v>46075.43781701306</v>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="inlineStr">
+        <is>
+          <t>5e4be80f-cd4a-4c89-a9bf-4279a512e6d4</t>
+        </is>
+      </c>
+      <c r="B2016" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2016" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2016" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2016" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2016" t="n">
+        <v>332.03</v>
+      </c>
+      <c r="G2016" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="H2016" s="2" t="n">
+        <v>46078.43781701608</v>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="inlineStr">
+        <is>
+          <t>a7ecf256-f1cf-4e1f-83bc-4becc43136fd</t>
+        </is>
+      </c>
+      <c r="B2017" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2017" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2017" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2017" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2017" t="n">
+        <v>240.54</v>
+      </c>
+      <c r="G2017" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="H2017" s="2" t="n">
+        <v>46087.43781701934</v>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" t="inlineStr">
+        <is>
+          <t>9dc4f76c-44ae-49c3-a86d-a259bbec8309</t>
+        </is>
+      </c>
+      <c r="B2018" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2018" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2018" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2018" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2018" t="n">
+        <v>169.71</v>
+      </c>
+      <c r="G2018" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H2018" s="2" t="n">
+        <v>46084.43781702256</v>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="inlineStr">
+        <is>
+          <t>83e9e65a-9c70-4898-8730-3c2bad35fcd9</t>
+        </is>
+      </c>
+      <c r="B2019" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2019" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2019" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2019" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2019" t="n">
+        <v>369.55</v>
+      </c>
+      <c r="G2019" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H2019" s="2" t="n">
+        <v>46092.43781702552</v>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="inlineStr">
+        <is>
+          <t>d87036af-d8c0-4313-af57-6f4f66d1f268</t>
+        </is>
+      </c>
+      <c r="B2020" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2020" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2020" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2020" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2020" t="n">
+        <v>140.91</v>
+      </c>
+      <c r="G2020" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H2020" s="2" t="n">
+        <v>46093.43781702872</v>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" t="inlineStr">
+        <is>
+          <t>2119742b-4723-4d21-bc3b-d92bf255690b</t>
+        </is>
+      </c>
+      <c r="B2021" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2021" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2021" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2021" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2021" t="n">
+        <v>477.52</v>
+      </c>
+      <c r="G2021" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H2021" s="2" t="n">
+        <v>46094.43781703206</v>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" t="inlineStr">
+        <is>
+          <t>836a5808-43fb-47cb-8345-5f8cf16d5270</t>
+        </is>
+      </c>
+      <c r="B2022" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2022" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2022" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2022" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2022" t="n">
+        <v>370.26</v>
+      </c>
+      <c r="G2022" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H2022" s="2" t="n">
+        <v>46095.43781703508</v>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" t="inlineStr">
+        <is>
+          <t>4ef79430-7e01-4b11-97ac-e279970fcf6e</t>
+        </is>
+      </c>
+      <c r="B2023" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2023" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2023" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2023" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2023" t="n">
+        <v>176.62</v>
+      </c>
+      <c r="G2023" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H2023" s="2" t="n">
+        <v>46077.43781703824</v>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" t="inlineStr">
+        <is>
+          <t>b64a8ea9-bc2b-4865-8a21-309a1aad9136</t>
+        </is>
+      </c>
+      <c r="B2024" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2024" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2024" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2024" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2024" t="n">
+        <v>350.08</v>
+      </c>
+      <c r="G2024" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H2024" s="2" t="n">
+        <v>46070.4378170414</v>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" t="inlineStr">
+        <is>
+          <t>5a1a04d7-e61c-4d71-91be-9bd81a5052b1</t>
+        </is>
+      </c>
+      <c r="B2025" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2025" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2025" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2025" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2025" t="n">
+        <v>370.97</v>
+      </c>
+      <c r="G2025" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="H2025" s="2" t="n">
+        <v>46074.43781704475</v>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" t="inlineStr">
+        <is>
+          <t>777bf23e-675d-4a75-8289-c52c13ed558d</t>
+        </is>
+      </c>
+      <c r="B2026" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2026" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2026" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2026" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2026" t="n">
+        <v>390.47</v>
+      </c>
+      <c r="G2026" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H2026" s="2" t="n">
+        <v>46085.4378170479</v>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" t="inlineStr">
+        <is>
+          <t>8ca3004b-5f49-4157-8154-f55d1ceca579</t>
+        </is>
+      </c>
+      <c r="B2027" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2027" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2027" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2027" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2027" t="n">
+        <v>320.01</v>
+      </c>
+      <c r="G2027" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H2027" s="2" t="n">
+        <v>46091.43781705109</v>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" t="inlineStr">
+        <is>
+          <t>c3a88e5a-3265-4934-b394-d83e7fab16f6</t>
+        </is>
+      </c>
+      <c r="B2028" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2028" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2028" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2028" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2028" t="n">
+        <v>432.47</v>
+      </c>
+      <c r="G2028" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="H2028" s="2" t="n">
+        <v>46081.43781705428</v>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" t="inlineStr">
+        <is>
+          <t>0f60de93-3481-4811-9188-b22bb5491841</t>
+        </is>
+      </c>
+      <c r="B2029" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2029" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2029" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2029" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2029" t="n">
+        <v>74.97</v>
+      </c>
+      <c r="G2029" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H2029" s="2" t="n">
+        <v>46070.43781705734</v>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" t="inlineStr">
+        <is>
+          <t>39562986-b7a4-4577-8944-df37d1f6a10d</t>
+        </is>
+      </c>
+      <c r="B2030" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2030" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2030" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2030" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2030" t="n">
+        <v>148.52</v>
+      </c>
+      <c r="G2030" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H2030" s="2" t="n">
+        <v>46094.43781706034</v>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" t="inlineStr">
+        <is>
+          <t>ace546ab-b463-40ac-91c1-925e70e30385</t>
+        </is>
+      </c>
+      <c r="B2031" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2031" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2031" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2031" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2031" t="n">
+        <v>209.29</v>
+      </c>
+      <c r="G2031" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="H2031" s="2" t="n">
+        <v>46096.43781706361</v>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" t="inlineStr">
+        <is>
+          <t>e835cb94-ede4-4ddf-bf94-22ac20b9d554</t>
+        </is>
+      </c>
+      <c r="B2032" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2032" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2032" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2032" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2032" t="n">
+        <v>168.69</v>
+      </c>
+      <c r="G2032" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H2032" s="2" t="n">
+        <v>46094.43781706685</v>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" t="inlineStr">
+        <is>
+          <t>68cc14fd-3b58-4c48-93f9-475f54764a81</t>
+        </is>
+      </c>
+      <c r="B2033" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2033" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2033" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2033" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2033" t="n">
+        <v>162.07</v>
+      </c>
+      <c r="G2033" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H2033" s="2" t="n">
+        <v>46068.43781706993</v>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" t="inlineStr">
+        <is>
+          <t>bf1fb2e3-5d13-47cd-a052-886be2603ba7</t>
+        </is>
+      </c>
+      <c r="B2034" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2034" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2034" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2034" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2034" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="G2034" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2034" s="2" t="n">
+        <v>46075.43781707314</v>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" t="inlineStr">
+        <is>
+          <t>31976a4d-1897-42cf-899d-b3bc75381873</t>
+        </is>
+      </c>
+      <c r="B2035" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2035" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2035" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2035" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2035" t="n">
+        <v>345.67</v>
+      </c>
+      <c r="G2035" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="H2035" s="2" t="n">
+        <v>46075.43781707619</v>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" t="inlineStr">
+        <is>
+          <t>1cea1eb7-be30-4136-8d47-ba53fde7ae33</t>
+        </is>
+      </c>
+      <c r="B2036" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2036" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2036" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2036" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2036" t="n">
+        <v>175.23</v>
+      </c>
+      <c r="G2036" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H2036" s="2" t="n">
+        <v>46074.4378170795</v>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" t="inlineStr">
+        <is>
+          <t>76a883dc-3db9-45fe-9fc6-e2c8124da5e2</t>
+        </is>
+      </c>
+      <c r="B2037" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2037" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2037" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2037" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2037" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="G2037" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H2037" s="2" t="n">
+        <v>46084.43781708262</v>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" t="inlineStr">
+        <is>
+          <t>ba80a13c-f27c-40e3-a0f9-542837719508</t>
+        </is>
+      </c>
+      <c r="B2038" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2038" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2038" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2038" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2038" t="n">
+        <v>117.79</v>
+      </c>
+      <c r="G2038" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H2038" s="2" t="n">
+        <v>46094.43781708574</v>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" t="inlineStr">
+        <is>
+          <t>2a522921-1d3c-4a32-8645-c96e74244e32</t>
+        </is>
+      </c>
+      <c r="B2039" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2039" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2039" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2039" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2039" t="n">
+        <v>185.19</v>
+      </c>
+      <c r="G2039" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H2039" s="2" t="n">
+        <v>46080.43781708916</v>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" t="inlineStr">
+        <is>
+          <t>2fca88fb-2585-4813-9b2a-df955c039432</t>
+        </is>
+      </c>
+      <c r="B2040" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2040" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2040" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2040" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2040" t="n">
+        <v>494.1</v>
+      </c>
+      <c r="G2040" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="H2040" s="2" t="n">
+        <v>46083.43781709218</v>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" t="inlineStr">
+        <is>
+          <t>c5bdacdd-5f27-4a51-bc65-b2425705cd19</t>
+        </is>
+      </c>
+      <c r="B2041" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2041" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2041" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2041" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2041" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="G2041" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H2041" s="2" t="n">
+        <v>46090.43781709537</v>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" t="inlineStr">
+        <is>
+          <t>4ad780b3-1786-4623-9122-31153b8e4256</t>
+        </is>
+      </c>
+      <c r="B2042" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2042" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2042" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2042" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2042" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="G2042" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H2042" s="2" t="n">
+        <v>46083.43781709835</v>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" t="inlineStr">
+        <is>
+          <t>1452df0c-4f5b-492a-abe0-040b9fdb839a</t>
+        </is>
+      </c>
+      <c r="B2043" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2043" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2043" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2043" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2043" t="n">
+        <v>472.82</v>
+      </c>
+      <c r="G2043" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="H2043" s="2" t="n">
+        <v>46089.43781710156</v>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" t="inlineStr">
+        <is>
+          <t>b8f872a9-86aa-4613-85d6-fe033fecca63</t>
+        </is>
+      </c>
+      <c r="B2044" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2044" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2044" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2044" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2044" t="n">
+        <v>404.47</v>
+      </c>
+      <c r="G2044" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="H2044" s="2" t="n">
+        <v>46086.43781710466</v>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" t="inlineStr">
+        <is>
+          <t>3800e7d7-b14c-441e-b61a-ad2164ee2a2a</t>
+        </is>
+      </c>
+      <c r="B2045" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2045" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2045" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2045" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2045" t="n">
+        <v>372.4</v>
+      </c>
+      <c r="G2045" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="H2045" s="2" t="n">
+        <v>46093.4378171078</v>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" t="inlineStr">
+        <is>
+          <t>bfacf03a-2136-4881-8d7a-1d7406911d39</t>
+        </is>
+      </c>
+      <c r="B2046" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2046" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2046" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2046" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2046" t="n">
+        <v>363.51</v>
+      </c>
+      <c r="G2046" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="H2046" s="2" t="n">
+        <v>46076.43781711093</v>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" t="inlineStr">
+        <is>
+          <t>ec2b34f2-6519-4a97-be9e-9d086e8298d4</t>
+        </is>
+      </c>
+      <c r="B2047" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2047" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2047" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2047" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2047" t="n">
+        <v>186.52</v>
+      </c>
+      <c r="G2047" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H2047" s="2" t="n">
+        <v>46071.43781711513</v>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" t="inlineStr">
+        <is>
+          <t>ad21fc78-cfd4-4487-94cb-3aa1bb63b781</t>
+        </is>
+      </c>
+      <c r="B2048" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2048" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2048" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2048" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2048" t="n">
+        <v>189.09</v>
+      </c>
+      <c r="G2048" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H2048" s="2" t="n">
+        <v>46081.43781711892</v>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" t="inlineStr">
+        <is>
+          <t>0176c7bb-b2f2-4c7d-83d6-11524d8961f3</t>
+        </is>
+      </c>
+      <c r="B2049" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2049" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2049" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2049" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2049" t="n">
+        <v>104.16</v>
+      </c>
+      <c r="G2049" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H2049" s="2" t="n">
+        <v>46076.43781712349</v>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" t="inlineStr">
+        <is>
+          <t>2cf6abe1-def9-49b2-b69b-0ff50e8ded6a</t>
+        </is>
+      </c>
+      <c r="B2050" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2050" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2050" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2050" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2050" t="n">
+        <v>343.18</v>
+      </c>
+      <c r="G2050" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="H2050" s="2" t="n">
+        <v>46081.43781712712</v>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" t="inlineStr">
+        <is>
+          <t>49c715b6-6db3-4fdd-bff1-1b584d04d45e</t>
+        </is>
+      </c>
+      <c r="B2051" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2051" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2051" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2051" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2051" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="G2051" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2051" s="2" t="n">
+        <v>46080.43781713021</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2051"/>
+  <dimension ref="A1:H2101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68505,7 +68505,7 @@
         <v>1.1</v>
       </c>
       <c r="H2002" s="2" t="n">
-        <v>46075.4378169697</v>
+        <v>46075.43781696759</v>
       </c>
     </row>
     <row r="2003">
@@ -68539,7 +68539,7 @@
         <v>1.88</v>
       </c>
       <c r="H2003" s="2" t="n">
-        <v>46089.43781697456</v>
+        <v>46089.43781697917</v>
       </c>
     </row>
     <row r="2004">
@@ -68573,7 +68573,7 @@
         <v>2.23</v>
       </c>
       <c r="H2004" s="2" t="n">
-        <v>46087.43781697774</v>
+        <v>46087.43781697917</v>
       </c>
     </row>
     <row r="2005">
@@ -68607,7 +68607,7 @@
         <v>3.91</v>
       </c>
       <c r="H2005" s="2" t="n">
-        <v>46088.43781698091</v>
+        <v>46088.43781697917</v>
       </c>
     </row>
     <row r="2006">
@@ -68641,7 +68641,7 @@
         <v>2.01</v>
       </c>
       <c r="H2006" s="2" t="n">
-        <v>46076.43781698418</v>
+        <v>46076.43781697917</v>
       </c>
     </row>
     <row r="2007">
@@ -68675,7 +68675,7 @@
         <v>4.83</v>
       </c>
       <c r="H2007" s="2" t="n">
-        <v>46090.4378169873</v>
+        <v>46090.43781699074</v>
       </c>
     </row>
     <row r="2008">
@@ -68709,7 +68709,7 @@
         <v>1.19</v>
       </c>
       <c r="H2008" s="2" t="n">
-        <v>46090.43781699042</v>
+        <v>46090.43781699074</v>
       </c>
     </row>
     <row r="2009">
@@ -68743,7 +68743,7 @@
         <v>1.81</v>
       </c>
       <c r="H2009" s="2" t="n">
-        <v>46072.43781699354</v>
+        <v>46072.43781699074</v>
       </c>
     </row>
     <row r="2010">
@@ -68777,7 +68777,7 @@
         <v>4.53</v>
       </c>
       <c r="H2010" s="2" t="n">
-        <v>46095.43781699693</v>
+        <v>46095.43781700231</v>
       </c>
     </row>
     <row r="2011">
@@ -68811,7 +68811,7 @@
         <v>1.6</v>
       </c>
       <c r="H2011" s="2" t="n">
-        <v>46088.43781700027</v>
+        <v>46088.43781700231</v>
       </c>
     </row>
     <row r="2012">
@@ -68845,7 +68845,7 @@
         <v>2.18</v>
       </c>
       <c r="H2012" s="2" t="n">
-        <v>46092.43781700351</v>
+        <v>46092.43781700231</v>
       </c>
     </row>
     <row r="2013">
@@ -68879,7 +68879,7 @@
         <v>1.29</v>
       </c>
       <c r="H2013" s="2" t="n">
-        <v>46079.4378170067</v>
+        <v>46079.43781700231</v>
       </c>
     </row>
     <row r="2014">
@@ -68913,7 +68913,7 @@
         <v>1.3</v>
       </c>
       <c r="H2014" s="2" t="n">
-        <v>46089.43781701</v>
+        <v>46089.43781701389</v>
       </c>
     </row>
     <row r="2015">
@@ -68947,7 +68947,7 @@
         <v>3.58</v>
       </c>
       <c r="H2015" s="2" t="n">
-        <v>46075.43781701306</v>
+        <v>46075.43781701389</v>
       </c>
     </row>
     <row r="2016">
@@ -68981,7 +68981,7 @@
         <v>3.32</v>
       </c>
       <c r="H2016" s="2" t="n">
-        <v>46078.43781701608</v>
+        <v>46078.43781701389</v>
       </c>
     </row>
     <row r="2017">
@@ -69015,7 +69015,7 @@
         <v>2.41</v>
       </c>
       <c r="H2017" s="2" t="n">
-        <v>46087.43781701934</v>
+        <v>46087.43781701389</v>
       </c>
     </row>
     <row r="2018">
@@ -69049,7 +69049,7 @@
         <v>1.7</v>
       </c>
       <c r="H2018" s="2" t="n">
-        <v>46084.43781702256</v>
+        <v>46084.43781702546</v>
       </c>
     </row>
     <row r="2019">
@@ -69083,7 +69083,7 @@
         <v>3.7</v>
       </c>
       <c r="H2019" s="2" t="n">
-        <v>46092.43781702552</v>
+        <v>46092.43781702546</v>
       </c>
     </row>
     <row r="2020">
@@ -69117,7 +69117,7 @@
         <v>1.41</v>
       </c>
       <c r="H2020" s="2" t="n">
-        <v>46093.43781702872</v>
+        <v>46093.43781702546</v>
       </c>
     </row>
     <row r="2021">
@@ -69151,7 +69151,7 @@
         <v>4.78</v>
       </c>
       <c r="H2021" s="2" t="n">
-        <v>46094.43781703206</v>
+        <v>46094.43781703704</v>
       </c>
     </row>
     <row r="2022">
@@ -69185,7 +69185,7 @@
         <v>3.7</v>
       </c>
       <c r="H2022" s="2" t="n">
-        <v>46095.43781703508</v>
+        <v>46095.43781703704</v>
       </c>
     </row>
     <row r="2023">
@@ -69219,7 +69219,7 @@
         <v>1.77</v>
       </c>
       <c r="H2023" s="2" t="n">
-        <v>46077.43781703824</v>
+        <v>46077.43781703704</v>
       </c>
     </row>
     <row r="2024">
@@ -69253,7 +69253,7 @@
         <v>3.5</v>
       </c>
       <c r="H2024" s="2" t="n">
-        <v>46070.4378170414</v>
+        <v>46070.43781703704</v>
       </c>
     </row>
     <row r="2025">
@@ -69287,7 +69287,7 @@
         <v>3.71</v>
       </c>
       <c r="H2025" s="2" t="n">
-        <v>46074.43781704475</v>
+        <v>46074.43781704861</v>
       </c>
     </row>
     <row r="2026">
@@ -69321,7 +69321,7 @@
         <v>3.9</v>
       </c>
       <c r="H2026" s="2" t="n">
-        <v>46085.4378170479</v>
+        <v>46085.43781704861</v>
       </c>
     </row>
     <row r="2027">
@@ -69355,7 +69355,7 @@
         <v>3.2</v>
       </c>
       <c r="H2027" s="2" t="n">
-        <v>46091.43781705109</v>
+        <v>46091.43781704861</v>
       </c>
     </row>
     <row r="2028">
@@ -69389,7 +69389,7 @@
         <v>4.32</v>
       </c>
       <c r="H2028" s="2" t="n">
-        <v>46081.43781705428</v>
+        <v>46081.43781704861</v>
       </c>
     </row>
     <row r="2029">
@@ -69423,7 +69423,7 @@
         <v>0.75</v>
       </c>
       <c r="H2029" s="2" t="n">
-        <v>46070.43781705734</v>
+        <v>46070.43781706018</v>
       </c>
     </row>
     <row r="2030">
@@ -69457,7 +69457,7 @@
         <v>1.49</v>
       </c>
       <c r="H2030" s="2" t="n">
-        <v>46094.43781706034</v>
+        <v>46094.43781706018</v>
       </c>
     </row>
     <row r="2031">
@@ -69491,7 +69491,7 @@
         <v>2.09</v>
       </c>
       <c r="H2031" s="2" t="n">
-        <v>46096.43781706361</v>
+        <v>46096.43781706018</v>
       </c>
     </row>
     <row r="2032">
@@ -69525,7 +69525,7 @@
         <v>1.69</v>
       </c>
       <c r="H2032" s="2" t="n">
-        <v>46094.43781706685</v>
+        <v>46094.43781707176</v>
       </c>
     </row>
     <row r="2033">
@@ -69559,7 +69559,7 @@
         <v>1.62</v>
       </c>
       <c r="H2033" s="2" t="n">
-        <v>46068.43781706993</v>
+        <v>46068.43781707176</v>
       </c>
     </row>
     <row r="2034">
@@ -69593,7 +69593,7 @@
         <v>0.3</v>
       </c>
       <c r="H2034" s="2" t="n">
-        <v>46075.43781707314</v>
+        <v>46075.43781707176</v>
       </c>
     </row>
     <row r="2035">
@@ -69627,7 +69627,7 @@
         <v>3.46</v>
       </c>
       <c r="H2035" s="2" t="n">
-        <v>46075.43781707619</v>
+        <v>46075.43781707176</v>
       </c>
     </row>
     <row r="2036">
@@ -69661,7 +69661,7 @@
         <v>1.75</v>
       </c>
       <c r="H2036" s="2" t="n">
-        <v>46074.4378170795</v>
+        <v>46074.43781708333</v>
       </c>
     </row>
     <row r="2037">
@@ -69695,7 +69695,7 @@
         <v>1.04</v>
       </c>
       <c r="H2037" s="2" t="n">
-        <v>46084.43781708262</v>
+        <v>46084.43781708333</v>
       </c>
     </row>
     <row r="2038">
@@ -69729,7 +69729,7 @@
         <v>1.18</v>
       </c>
       <c r="H2038" s="2" t="n">
-        <v>46094.43781708574</v>
+        <v>46094.43781708333</v>
       </c>
     </row>
     <row r="2039">
@@ -69763,7 +69763,7 @@
         <v>1.85</v>
       </c>
       <c r="H2039" s="2" t="n">
-        <v>46080.43781708916</v>
+        <v>46080.43781709491</v>
       </c>
     </row>
     <row r="2040">
@@ -69797,7 +69797,7 @@
         <v>4.94</v>
       </c>
       <c r="H2040" s="2" t="n">
-        <v>46083.43781709218</v>
+        <v>46083.43781709491</v>
       </c>
     </row>
     <row r="2041">
@@ -69831,7 +69831,7 @@
         <v>0.11</v>
       </c>
       <c r="H2041" s="2" t="n">
-        <v>46090.43781709537</v>
+        <v>46090.43781709491</v>
       </c>
     </row>
     <row r="2042">
@@ -69865,7 +69865,7 @@
         <v>0.38</v>
       </c>
       <c r="H2042" s="2" t="n">
-        <v>46083.43781709835</v>
+        <v>46083.43781709491</v>
       </c>
     </row>
     <row r="2043">
@@ -69899,7 +69899,7 @@
         <v>4.73</v>
       </c>
       <c r="H2043" s="2" t="n">
-        <v>46089.43781710156</v>
+        <v>46089.43781710648</v>
       </c>
     </row>
     <row r="2044">
@@ -69933,7 +69933,7 @@
         <v>4.04</v>
       </c>
       <c r="H2044" s="2" t="n">
-        <v>46086.43781710466</v>
+        <v>46086.43781710648</v>
       </c>
     </row>
     <row r="2045">
@@ -69967,7 +69967,7 @@
         <v>3.72</v>
       </c>
       <c r="H2045" s="2" t="n">
-        <v>46093.4378171078</v>
+        <v>46093.43781710648</v>
       </c>
     </row>
     <row r="2046">
@@ -70001,7 +70001,7 @@
         <v>3.64</v>
       </c>
       <c r="H2046" s="2" t="n">
-        <v>46076.43781711093</v>
+        <v>46076.43781710648</v>
       </c>
     </row>
     <row r="2047">
@@ -70035,7 +70035,7 @@
         <v>1.87</v>
       </c>
       <c r="H2047" s="2" t="n">
-        <v>46071.43781711513</v>
+        <v>46071.43781711806</v>
       </c>
     </row>
     <row r="2048">
@@ -70069,7 +70069,7 @@
         <v>1.89</v>
       </c>
       <c r="H2048" s="2" t="n">
-        <v>46081.43781711892</v>
+        <v>46081.43781711806</v>
       </c>
     </row>
     <row r="2049">
@@ -70103,7 +70103,7 @@
         <v>1.04</v>
       </c>
       <c r="H2049" s="2" t="n">
-        <v>46076.43781712349</v>
+        <v>46076.43781711806</v>
       </c>
     </row>
     <row r="2050">
@@ -70137,7 +70137,7 @@
         <v>3.43</v>
       </c>
       <c r="H2050" s="2" t="n">
-        <v>46081.43781712712</v>
+        <v>46081.43781712963</v>
       </c>
     </row>
     <row r="2051">
@@ -70171,7 +70171,1707 @@
         <v>0.2</v>
       </c>
       <c r="H2051" s="2" t="n">
-        <v>46080.43781713021</v>
+        <v>46080.43781712963</v>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" t="inlineStr">
+        <is>
+          <t>b2c54bf1-f437-465a-b709-e9db501ce6a0</t>
+        </is>
+      </c>
+      <c r="B2052" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2052" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2052" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2052" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2052" t="n">
+        <v>237.28</v>
+      </c>
+      <c r="G2052" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="H2052" s="2" t="n">
+        <v>46076.47634565126</v>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" t="inlineStr">
+        <is>
+          <t>5b5a77d3-eab1-4b4e-8386-f1bc108f49f1</t>
+        </is>
+      </c>
+      <c r="B2053" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2053" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2053" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2053" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2053" t="n">
+        <v>46.93</v>
+      </c>
+      <c r="G2053" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H2053" s="2" t="n">
+        <v>46094.47634565546</v>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" t="inlineStr">
+        <is>
+          <t>57a6fb72-aeb8-4936-9d20-5fe9cdff074c</t>
+        </is>
+      </c>
+      <c r="B2054" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2054" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2054" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2054" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2054" t="n">
+        <v>332.86</v>
+      </c>
+      <c r="G2054" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="H2054" s="2" t="n">
+        <v>46073.47634565858</v>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" t="inlineStr">
+        <is>
+          <t>377c8896-2983-4cca-bc8f-14e00b95e05c</t>
+        </is>
+      </c>
+      <c r="B2055" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2055" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2055" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2055" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2055" t="n">
+        <v>419.27</v>
+      </c>
+      <c r="G2055" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="H2055" s="2" t="n">
+        <v>46067.47634566231</v>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" t="inlineStr">
+        <is>
+          <t>6b6f7f35-0752-489f-a52a-b4ab07a2d1c2</t>
+        </is>
+      </c>
+      <c r="B2056" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2056" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2056" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2056" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2056" t="n">
+        <v>112.27</v>
+      </c>
+      <c r="G2056" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H2056" s="2" t="n">
+        <v>46075.47634566553</v>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" t="inlineStr">
+        <is>
+          <t>b9061b6f-ff5d-4e81-a181-e9405a29890a</t>
+        </is>
+      </c>
+      <c r="B2057" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2057" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2057" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2057" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2057" t="n">
+        <v>391.71</v>
+      </c>
+      <c r="G2057" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H2057" s="2" t="n">
+        <v>46073.47634566882</v>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" t="inlineStr">
+        <is>
+          <t>c1fa47de-d377-4d2d-b260-4d558bc7a49b</t>
+        </is>
+      </c>
+      <c r="B2058" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2058" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2058" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2058" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2058" t="n">
+        <v>21.36</v>
+      </c>
+      <c r="G2058" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H2058" s="2" t="n">
+        <v>46073.47634567216</v>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" t="inlineStr">
+        <is>
+          <t>e183a147-ba58-4a7f-92de-b19525326471</t>
+        </is>
+      </c>
+      <c r="B2059" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2059" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2059" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2059" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2059" t="n">
+        <v>465.07</v>
+      </c>
+      <c r="G2059" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="H2059" s="2" t="n">
+        <v>46095.47634567536</v>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" t="inlineStr">
+        <is>
+          <t>9fe46a46-09b4-4125-8940-a123b25cdaaa</t>
+        </is>
+      </c>
+      <c r="B2060" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2060" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2060" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2060" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2060" t="n">
+        <v>124.76</v>
+      </c>
+      <c r="G2060" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H2060" s="2" t="n">
+        <v>46083.47634567843</v>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" t="inlineStr">
+        <is>
+          <t>6622a0bf-51af-443a-a92c-d8e161fc8220</t>
+        </is>
+      </c>
+      <c r="B2061" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2061" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2061" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2061" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2061" t="n">
+        <v>168.69</v>
+      </c>
+      <c r="G2061" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H2061" s="2" t="n">
+        <v>46070.47634568167</v>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" t="inlineStr">
+        <is>
+          <t>1b8337e0-bc17-4000-8736-27b84cd0cafb</t>
+        </is>
+      </c>
+      <c r="B2062" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2062" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2062" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2062" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2062" t="n">
+        <v>146.53</v>
+      </c>
+      <c r="G2062" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H2062" s="2" t="n">
+        <v>46077.47634568515</v>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" t="inlineStr">
+        <is>
+          <t>e2edd1a4-0bc6-47f3-9e70-20f69d830103</t>
+        </is>
+      </c>
+      <c r="B2063" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2063" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2063" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2063" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2063" t="n">
+        <v>484.95</v>
+      </c>
+      <c r="G2063" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="H2063" s="2" t="n">
+        <v>46082.47634568823</v>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" t="inlineStr">
+        <is>
+          <t>c4b4b7de-7878-4e07-877e-0fba370386fd</t>
+        </is>
+      </c>
+      <c r="B2064" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2064" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2064" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2064" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2064" t="n">
+        <v>335.85</v>
+      </c>
+      <c r="G2064" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="H2064" s="2" t="n">
+        <v>46093.47634569146</v>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" t="inlineStr">
+        <is>
+          <t>e05e5f23-3bb2-4e82-8f1d-38fd3bdcc47f</t>
+        </is>
+      </c>
+      <c r="B2065" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2065" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2065" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2065" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2065" t="n">
+        <v>437.86</v>
+      </c>
+      <c r="G2065" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="H2065" s="2" t="n">
+        <v>46086.47634569499</v>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" t="inlineStr">
+        <is>
+          <t>bf20e8a6-1854-4e7f-80e0-70dde5bd374d</t>
+        </is>
+      </c>
+      <c r="B2066" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2066" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2066" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2066" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2066" t="n">
+        <v>169.76</v>
+      </c>
+      <c r="G2066" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H2066" s="2" t="n">
+        <v>46075.47634569817</v>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" t="inlineStr">
+        <is>
+          <t>1f176e64-029e-48e6-8806-2186d7a57432</t>
+        </is>
+      </c>
+      <c r="B2067" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2067" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2067" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2067" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2067" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="G2067" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H2067" s="2" t="n">
+        <v>46069.47634570122</v>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" t="inlineStr">
+        <is>
+          <t>547da2e2-d6b4-478c-9ccf-369d94caca87</t>
+        </is>
+      </c>
+      <c r="B2068" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2068" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2068" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2068" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2068" t="n">
+        <v>468.03</v>
+      </c>
+      <c r="G2068" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="H2068" s="2" t="n">
+        <v>46096.47634570443</v>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="inlineStr">
+        <is>
+          <t>ea6a3b98-143c-48c9-9ec4-dfdda377e544</t>
+        </is>
+      </c>
+      <c r="B2069" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2069" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2069" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2069" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2069" t="n">
+        <v>464.99</v>
+      </c>
+      <c r="G2069" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="H2069" s="2" t="n">
+        <v>46071.47634570798</v>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" t="inlineStr">
+        <is>
+          <t>48dad3a6-0dcc-4b9f-a3dc-8f687fc52ce3</t>
+        </is>
+      </c>
+      <c r="B2070" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2070" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2070" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2070" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2070" t="n">
+        <v>38.41</v>
+      </c>
+      <c r="G2070" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H2070" s="2" t="n">
+        <v>46067.47634571111</v>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" t="inlineStr">
+        <is>
+          <t>3ab69494-0436-4645-85e0-1eea79201401</t>
+        </is>
+      </c>
+      <c r="B2071" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2071" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2071" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2071" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2071" t="n">
+        <v>96.15000000000001</v>
+      </c>
+      <c r="G2071" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H2071" s="2" t="n">
+        <v>46085.47634571427</v>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" t="inlineStr">
+        <is>
+          <t>1f071330-7213-475f-8e39-c92361552732</t>
+        </is>
+      </c>
+      <c r="B2072" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2072" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2072" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2072" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2072" t="n">
+        <v>293.41</v>
+      </c>
+      <c r="G2072" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="H2072" s="2" t="n">
+        <v>46092.47634571734</v>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" t="inlineStr">
+        <is>
+          <t>75d26fce-0215-46c2-92c5-0ab335f05a02</t>
+        </is>
+      </c>
+      <c r="B2073" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2073" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2073" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2073" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2073" t="n">
+        <v>90.02</v>
+      </c>
+      <c r="G2073" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H2073" s="2" t="n">
+        <v>46086.4763457208</v>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" t="inlineStr">
+        <is>
+          <t>7772b027-e5a4-46c0-8b40-9ca48262610c</t>
+        </is>
+      </c>
+      <c r="B2074" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2074" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2074" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2074" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2074" t="n">
+        <v>48.79</v>
+      </c>
+      <c r="G2074" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H2074" s="2" t="n">
+        <v>46085.47634572387</v>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" t="inlineStr">
+        <is>
+          <t>c8ecf297-d2c5-485e-a98b-e3ab978936d5</t>
+        </is>
+      </c>
+      <c r="B2075" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2075" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2075" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2075" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2075" t="n">
+        <v>123.75</v>
+      </c>
+      <c r="G2075" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="H2075" s="2" t="n">
+        <v>46077.47634572689</v>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" t="inlineStr">
+        <is>
+          <t>862398e3-c060-4bd5-b55a-52fc82624a4e</t>
+        </is>
+      </c>
+      <c r="B2076" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2076" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2076" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2076" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2076" t="n">
+        <v>301.73</v>
+      </c>
+      <c r="G2076" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="H2076" s="2" t="n">
+        <v>46075.47634573025</v>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" t="inlineStr">
+        <is>
+          <t>8d203cf9-970c-4de9-9cda-28925962c853</t>
+        </is>
+      </c>
+      <c r="B2077" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2077" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2077" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2077" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2077" t="n">
+        <v>250.68</v>
+      </c>
+      <c r="G2077" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="H2077" s="2" t="n">
+        <v>46080.47634573353</v>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" t="inlineStr">
+        <is>
+          <t>c73f13cc-c638-4dfd-a67b-5842d15fbeda</t>
+        </is>
+      </c>
+      <c r="B2078" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2078" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2078" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2078" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2078" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="G2078" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H2078" s="2" t="n">
+        <v>46077.47634573655</v>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" t="inlineStr">
+        <is>
+          <t>170705d8-00c4-44bd-b018-d25961290ad6</t>
+        </is>
+      </c>
+      <c r="B2079" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2079" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2079" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2079" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2079" t="n">
+        <v>453.36</v>
+      </c>
+      <c r="G2079" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="H2079" s="2" t="n">
+        <v>46073.47634573954</v>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" t="inlineStr">
+        <is>
+          <t>7ebb3379-25a5-4b14-920b-57de92d4f90f</t>
+        </is>
+      </c>
+      <c r="B2080" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2080" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2080" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2080" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2080" t="n">
+        <v>236.47</v>
+      </c>
+      <c r="G2080" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H2080" s="2" t="n">
+        <v>46076.47634574291</v>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" t="inlineStr">
+        <is>
+          <t>89162df3-c372-44d9-99fe-ff0b01b5097b</t>
+        </is>
+      </c>
+      <c r="B2081" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2081" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2081" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2081" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2081" t="n">
+        <v>309</v>
+      </c>
+      <c r="G2081" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="H2081" s="2" t="n">
+        <v>46080.47634574606</v>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" t="inlineStr">
+        <is>
+          <t>8187e3a9-7073-4c87-b66b-a74846264453</t>
+        </is>
+      </c>
+      <c r="B2082" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2082" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2082" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2082" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2082" t="n">
+        <v>499.43</v>
+      </c>
+      <c r="G2082" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="H2082" s="2" t="n">
+        <v>46087.47634574922</v>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" t="inlineStr">
+        <is>
+          <t>e1a6c291-f438-41b4-9d43-de42d6b720a8</t>
+        </is>
+      </c>
+      <c r="B2083" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2083" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2083" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2083" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2083" t="n">
+        <v>251.09</v>
+      </c>
+      <c r="G2083" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="H2083" s="2" t="n">
+        <v>46086.47634575218</v>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" t="inlineStr">
+        <is>
+          <t>c6672032-725e-48ae-b84f-af976e48d865</t>
+        </is>
+      </c>
+      <c r="B2084" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2084" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2084" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2084" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2084" t="n">
+        <v>40.88</v>
+      </c>
+      <c r="G2084" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H2084" s="2" t="n">
+        <v>46096.47634575575</v>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" t="inlineStr">
+        <is>
+          <t>7138cd71-18a4-46c8-9683-2f1102b770bd</t>
+        </is>
+      </c>
+      <c r="B2085" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2085" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2085" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2085" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2085" t="n">
+        <v>381.88</v>
+      </c>
+      <c r="G2085" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="H2085" s="2" t="n">
+        <v>46084.47634575884</v>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" t="inlineStr">
+        <is>
+          <t>eff217fa-288f-40ff-8577-0df217c84848</t>
+        </is>
+      </c>
+      <c r="B2086" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2086" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2086" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2086" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2086" t="n">
+        <v>317.38</v>
+      </c>
+      <c r="G2086" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="H2086" s="2" t="n">
+        <v>46091.47634576205</v>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="inlineStr">
+        <is>
+          <t>043e4181-cba3-4643-bbe2-b5a6222a26ca</t>
+        </is>
+      </c>
+      <c r="B2087" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2087" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2087" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2087" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2087" t="n">
+        <v>284.16</v>
+      </c>
+      <c r="G2087" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="H2087" s="2" t="n">
+        <v>46088.47634576531</v>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" t="inlineStr">
+        <is>
+          <t>51a2a8a4-901a-4fd1-bcb6-9112bd88ef9e</t>
+        </is>
+      </c>
+      <c r="B2088" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2088" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2088" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2088" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2088" t="n">
+        <v>59.21</v>
+      </c>
+      <c r="G2088" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H2088" s="2" t="n">
+        <v>46077.47634576831</v>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="inlineStr">
+        <is>
+          <t>d9af0d63-293e-4bf1-93c8-8a29d08eac3a</t>
+        </is>
+      </c>
+      <c r="B2089" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2089" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2089" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2089" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2089" t="n">
+        <v>469.97</v>
+      </c>
+      <c r="G2089" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H2089" s="2" t="n">
+        <v>46068.47634577147</v>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="inlineStr">
+        <is>
+          <t>7b1e86dc-a154-4593-970b-45e2b1e7fd04</t>
+        </is>
+      </c>
+      <c r="B2090" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2090" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2090" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2090" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2090" t="n">
+        <v>143.39</v>
+      </c>
+      <c r="G2090" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H2090" s="2" t="n">
+        <v>46075.47634577459</v>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="inlineStr">
+        <is>
+          <t>7911e9c7-02a6-4e6b-a8dd-6ae5ff42aac5</t>
+        </is>
+      </c>
+      <c r="B2091" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2091" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2091" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2091" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2091" t="n">
+        <v>213.62</v>
+      </c>
+      <c r="G2091" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H2091" s="2" t="n">
+        <v>46077.4763457778</v>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="inlineStr">
+        <is>
+          <t>19124acc-e350-4768-8fd0-98a1ee583463</t>
+        </is>
+      </c>
+      <c r="B2092" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2092" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2092" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2092" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2092" t="n">
+        <v>423.46</v>
+      </c>
+      <c r="G2092" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="H2092" s="2" t="n">
+        <v>46089.47634578084</v>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="inlineStr">
+        <is>
+          <t>7a1ce4ae-5da5-47cb-96ff-945c59e31727</t>
+        </is>
+      </c>
+      <c r="B2093" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2093" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2093" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2093" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2093" t="n">
+        <v>458.66</v>
+      </c>
+      <c r="G2093" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="H2093" s="2" t="n">
+        <v>46072.47634578386</v>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" t="inlineStr">
+        <is>
+          <t>e66d46aa-a3a8-484c-ae36-899e711944db</t>
+        </is>
+      </c>
+      <c r="B2094" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2094" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2094" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2094" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2094" t="n">
+        <v>266.08</v>
+      </c>
+      <c r="G2094" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H2094" s="2" t="n">
+        <v>46090.47634578686</v>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" t="inlineStr">
+        <is>
+          <t>f4388d7d-1f5d-4190-ba49-8ceeb5ea3117</t>
+        </is>
+      </c>
+      <c r="B2095" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2095" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2095" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2095" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2095" t="n">
+        <v>261.34</v>
+      </c>
+      <c r="G2095" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="H2095" s="2" t="n">
+        <v>46068.47634579032</v>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" t="inlineStr">
+        <is>
+          <t>bcd6743c-c8b2-4a37-a960-5f3fed50b6e1</t>
+        </is>
+      </c>
+      <c r="B2096" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2096" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2096" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2096" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2096" t="n">
+        <v>208.26</v>
+      </c>
+      <c r="G2096" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H2096" s="2" t="n">
+        <v>46070.47634579354</v>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" t="inlineStr">
+        <is>
+          <t>d7c25c9c-16d7-4f99-b1f6-ff8f8fb625e0</t>
+        </is>
+      </c>
+      <c r="B2097" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2097" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2097" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2097" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2097" t="n">
+        <v>121.25</v>
+      </c>
+      <c r="G2097" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="H2097" s="2" t="n">
+        <v>46094.47634579669</v>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" t="inlineStr">
+        <is>
+          <t>0f943838-ba1e-4e06-b5da-934105685046</t>
+        </is>
+      </c>
+      <c r="B2098" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2098" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2098" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2098" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2098" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G2098" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H2098" s="2" t="n">
+        <v>46076.47634580026</v>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" t="inlineStr">
+        <is>
+          <t>699f0e25-45ad-40e5-a8b1-b88f1417d6bd</t>
+        </is>
+      </c>
+      <c r="B2099" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2099" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2099" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2099" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2099" t="n">
+        <v>219.46</v>
+      </c>
+      <c r="G2099" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="H2099" s="2" t="n">
+        <v>46071.47634580339</v>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" t="inlineStr">
+        <is>
+          <t>7d2865f1-7d4f-4bb6-b300-fe31f6752dcc</t>
+        </is>
+      </c>
+      <c r="B2100" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2100" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2100" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2100" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2100" t="n">
+        <v>169.02</v>
+      </c>
+      <c r="G2100" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H2100" s="2" t="n">
+        <v>46096.47634580639</v>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="inlineStr">
+        <is>
+          <t>8daa38f7-e8a0-4e7d-a274-f0b3e3a3f7cf</t>
+        </is>
+      </c>
+      <c r="B2101" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2101" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2101" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2101" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2101" t="n">
+        <v>472.04</v>
+      </c>
+      <c r="G2101" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="H2101" s="2" t="n">
+        <v>46094.47634580957</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2101"/>
+  <dimension ref="A1:H2151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70205,7 +70205,7 @@
         <v>2.37</v>
       </c>
       <c r="H2052" s="2" t="n">
-        <v>46076.47634565126</v>
+        <v>46076.47634564815</v>
       </c>
     </row>
     <row r="2053">
@@ -70239,7 +70239,7 @@
         <v>0.47</v>
       </c>
       <c r="H2053" s="2" t="n">
-        <v>46094.47634565546</v>
+        <v>46094.47634565972</v>
       </c>
     </row>
     <row r="2054">
@@ -70273,7 +70273,7 @@
         <v>3.33</v>
       </c>
       <c r="H2054" s="2" t="n">
-        <v>46073.47634565858</v>
+        <v>46073.47634565972</v>
       </c>
     </row>
     <row r="2055">
@@ -70307,7 +70307,7 @@
         <v>4.19</v>
       </c>
       <c r="H2055" s="2" t="n">
-        <v>46067.47634566231</v>
+        <v>46067.47634565972</v>
       </c>
     </row>
     <row r="2056">
@@ -70341,7 +70341,7 @@
         <v>1.12</v>
       </c>
       <c r="H2056" s="2" t="n">
-        <v>46075.47634566553</v>
+        <v>46075.4763456713</v>
       </c>
     </row>
     <row r="2057">
@@ -70375,7 +70375,7 @@
         <v>3.92</v>
       </c>
       <c r="H2057" s="2" t="n">
-        <v>46073.47634566882</v>
+        <v>46073.4763456713</v>
       </c>
     </row>
     <row r="2058">
@@ -70409,7 +70409,7 @@
         <v>0.21</v>
       </c>
       <c r="H2058" s="2" t="n">
-        <v>46073.47634567216</v>
+        <v>46073.4763456713</v>
       </c>
     </row>
     <row r="2059">
@@ -70443,7 +70443,7 @@
         <v>4.65</v>
       </c>
       <c r="H2059" s="2" t="n">
-        <v>46095.47634567536</v>
+        <v>46095.4763456713</v>
       </c>
     </row>
     <row r="2060">
@@ -70477,7 +70477,7 @@
         <v>1.25</v>
       </c>
       <c r="H2060" s="2" t="n">
-        <v>46083.47634567843</v>
+        <v>46083.47634568287</v>
       </c>
     </row>
     <row r="2061">
@@ -70511,7 +70511,7 @@
         <v>1.69</v>
       </c>
       <c r="H2061" s="2" t="n">
-        <v>46070.47634568167</v>
+        <v>46070.47634568287</v>
       </c>
     </row>
     <row r="2062">
@@ -70545,7 +70545,7 @@
         <v>1.47</v>
       </c>
       <c r="H2062" s="2" t="n">
-        <v>46077.47634568515</v>
+        <v>46077.47634568287</v>
       </c>
     </row>
     <row r="2063">
@@ -70579,7 +70579,7 @@
         <v>4.85</v>
       </c>
       <c r="H2063" s="2" t="n">
-        <v>46082.47634568823</v>
+        <v>46082.47634568287</v>
       </c>
     </row>
     <row r="2064">
@@ -70613,7 +70613,7 @@
         <v>3.36</v>
       </c>
       <c r="H2064" s="2" t="n">
-        <v>46093.47634569146</v>
+        <v>46093.47634569444</v>
       </c>
     </row>
     <row r="2065">
@@ -70647,7 +70647,7 @@
         <v>4.38</v>
       </c>
       <c r="H2065" s="2" t="n">
-        <v>46086.47634569499</v>
+        <v>46086.47634569444</v>
       </c>
     </row>
     <row r="2066">
@@ -70681,7 +70681,7 @@
         <v>1.7</v>
       </c>
       <c r="H2066" s="2" t="n">
-        <v>46075.47634569817</v>
+        <v>46075.47634569444</v>
       </c>
     </row>
     <row r="2067">
@@ -70715,7 +70715,7 @@
         <v>0.36</v>
       </c>
       <c r="H2067" s="2" t="n">
-        <v>46069.47634570122</v>
+        <v>46069.47634570602</v>
       </c>
     </row>
     <row r="2068">
@@ -70749,7 +70749,7 @@
         <v>4.68</v>
       </c>
       <c r="H2068" s="2" t="n">
-        <v>46096.47634570443</v>
+        <v>46096.47634570602</v>
       </c>
     </row>
     <row r="2069">
@@ -70783,7 +70783,7 @@
         <v>4.65</v>
       </c>
       <c r="H2069" s="2" t="n">
-        <v>46071.47634570798</v>
+        <v>46071.47634570602</v>
       </c>
     </row>
     <row r="2070">
@@ -70817,7 +70817,7 @@
         <v>0.38</v>
       </c>
       <c r="H2070" s="2" t="n">
-        <v>46067.47634571111</v>
+        <v>46067.47634570602</v>
       </c>
     </row>
     <row r="2071">
@@ -70851,7 +70851,7 @@
         <v>0.96</v>
       </c>
       <c r="H2071" s="2" t="n">
-        <v>46085.47634571427</v>
+        <v>46085.47634571759</v>
       </c>
     </row>
     <row r="2072">
@@ -70885,7 +70885,7 @@
         <v>2.93</v>
       </c>
       <c r="H2072" s="2" t="n">
-        <v>46092.47634571734</v>
+        <v>46092.47634571759</v>
       </c>
     </row>
     <row r="2073">
@@ -70919,7 +70919,7 @@
         <v>0.9</v>
       </c>
       <c r="H2073" s="2" t="n">
-        <v>46086.4763457208</v>
+        <v>46086.47634571759</v>
       </c>
     </row>
     <row r="2074">
@@ -70953,7 +70953,7 @@
         <v>0.49</v>
       </c>
       <c r="H2074" s="2" t="n">
-        <v>46085.47634572387</v>
+        <v>46085.47634572917</v>
       </c>
     </row>
     <row r="2075">
@@ -70987,7 +70987,7 @@
         <v>1.24</v>
       </c>
       <c r="H2075" s="2" t="n">
-        <v>46077.47634572689</v>
+        <v>46077.47634572917</v>
       </c>
     </row>
     <row r="2076">
@@ -71021,7 +71021,7 @@
         <v>3.02</v>
       </c>
       <c r="H2076" s="2" t="n">
-        <v>46075.47634573025</v>
+        <v>46075.47634572917</v>
       </c>
     </row>
     <row r="2077">
@@ -71055,7 +71055,7 @@
         <v>2.51</v>
       </c>
       <c r="H2077" s="2" t="n">
-        <v>46080.47634573353</v>
+        <v>46080.47634572917</v>
       </c>
     </row>
     <row r="2078">
@@ -71089,7 +71089,7 @@
         <v>0.06</v>
       </c>
       <c r="H2078" s="2" t="n">
-        <v>46077.47634573655</v>
+        <v>46077.47634574074</v>
       </c>
     </row>
     <row r="2079">
@@ -71123,7 +71123,7 @@
         <v>4.53</v>
       </c>
       <c r="H2079" s="2" t="n">
-        <v>46073.47634573954</v>
+        <v>46073.47634574074</v>
       </c>
     </row>
     <row r="2080">
@@ -71157,7 +71157,7 @@
         <v>2.36</v>
       </c>
       <c r="H2080" s="2" t="n">
-        <v>46076.47634574291</v>
+        <v>46076.47634574074</v>
       </c>
     </row>
     <row r="2081">
@@ -71191,7 +71191,7 @@
         <v>3.09</v>
       </c>
       <c r="H2081" s="2" t="n">
-        <v>46080.47634574606</v>
+        <v>46080.47634574074</v>
       </c>
     </row>
     <row r="2082">
@@ -71225,7 +71225,7 @@
         <v>4.99</v>
       </c>
       <c r="H2082" s="2" t="n">
-        <v>46087.47634574922</v>
+        <v>46087.47634575231</v>
       </c>
     </row>
     <row r="2083">
@@ -71259,7 +71259,7 @@
         <v>2.51</v>
       </c>
       <c r="H2083" s="2" t="n">
-        <v>46086.47634575218</v>
+        <v>46086.47634575231</v>
       </c>
     </row>
     <row r="2084">
@@ -71293,7 +71293,7 @@
         <v>0.41</v>
       </c>
       <c r="H2084" s="2" t="n">
-        <v>46096.47634575575</v>
+        <v>46096.47634575231</v>
       </c>
     </row>
     <row r="2085">
@@ -71327,7 +71327,7 @@
         <v>3.82</v>
       </c>
       <c r="H2085" s="2" t="n">
-        <v>46084.47634575884</v>
+        <v>46084.47634576389</v>
       </c>
     </row>
     <row r="2086">
@@ -71361,7 +71361,7 @@
         <v>3.17</v>
       </c>
       <c r="H2086" s="2" t="n">
-        <v>46091.47634576205</v>
+        <v>46091.47634576389</v>
       </c>
     </row>
     <row r="2087">
@@ -71395,7 +71395,7 @@
         <v>2.84</v>
       </c>
       <c r="H2087" s="2" t="n">
-        <v>46088.47634576531</v>
+        <v>46088.47634576389</v>
       </c>
     </row>
     <row r="2088">
@@ -71429,7 +71429,7 @@
         <v>0.59</v>
       </c>
       <c r="H2088" s="2" t="n">
-        <v>46077.47634576831</v>
+        <v>46077.47634576389</v>
       </c>
     </row>
     <row r="2089">
@@ -71463,7 +71463,7 @@
         <v>4.7</v>
       </c>
       <c r="H2089" s="2" t="n">
-        <v>46068.47634577147</v>
+        <v>46068.47634577546</v>
       </c>
     </row>
     <row r="2090">
@@ -71497,7 +71497,7 @@
         <v>1.43</v>
       </c>
       <c r="H2090" s="2" t="n">
-        <v>46075.47634577459</v>
+        <v>46075.47634577546</v>
       </c>
     </row>
     <row r="2091">
@@ -71531,7 +71531,7 @@
         <v>2.14</v>
       </c>
       <c r="H2091" s="2" t="n">
-        <v>46077.4763457778</v>
+        <v>46077.47634577546</v>
       </c>
     </row>
     <row r="2092">
@@ -71565,7 +71565,7 @@
         <v>4.23</v>
       </c>
       <c r="H2092" s="2" t="n">
-        <v>46089.47634578084</v>
+        <v>46089.47634577546</v>
       </c>
     </row>
     <row r="2093">
@@ -71599,7 +71599,7 @@
         <v>4.59</v>
       </c>
       <c r="H2093" s="2" t="n">
-        <v>46072.47634578386</v>
+        <v>46072.47634578704</v>
       </c>
     </row>
     <row r="2094">
@@ -71633,7 +71633,7 @@
         <v>2.66</v>
       </c>
       <c r="H2094" s="2" t="n">
-        <v>46090.47634578686</v>
+        <v>46090.47634578704</v>
       </c>
     </row>
     <row r="2095">
@@ -71667,7 +71667,7 @@
         <v>2.61</v>
       </c>
       <c r="H2095" s="2" t="n">
-        <v>46068.47634579032</v>
+        <v>46068.47634578704</v>
       </c>
     </row>
     <row r="2096">
@@ -71701,7 +71701,7 @@
         <v>2.08</v>
       </c>
       <c r="H2096" s="2" t="n">
-        <v>46070.47634579354</v>
+        <v>46070.47634579861</v>
       </c>
     </row>
     <row r="2097">
@@ -71735,7 +71735,7 @@
         <v>1.21</v>
       </c>
       <c r="H2097" s="2" t="n">
-        <v>46094.47634579669</v>
+        <v>46094.47634579861</v>
       </c>
     </row>
     <row r="2098">
@@ -71769,7 +71769,7 @@
         <v>0.01</v>
       </c>
       <c r="H2098" s="2" t="n">
-        <v>46076.47634580026</v>
+        <v>46076.47634579861</v>
       </c>
     </row>
     <row r="2099">
@@ -71803,7 +71803,7 @@
         <v>2.19</v>
       </c>
       <c r="H2099" s="2" t="n">
-        <v>46071.47634580339</v>
+        <v>46071.47634579861</v>
       </c>
     </row>
     <row r="2100">
@@ -71837,7 +71837,7 @@
         <v>1.69</v>
       </c>
       <c r="H2100" s="2" t="n">
-        <v>46096.47634580639</v>
+        <v>46096.47634581019</v>
       </c>
     </row>
     <row r="2101">
@@ -71871,7 +71871,1707 @@
         <v>4.72</v>
       </c>
       <c r="H2101" s="2" t="n">
-        <v>46094.47634580957</v>
+        <v>46094.47634581019</v>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" t="inlineStr">
+        <is>
+          <t>e40dcebb-e955-4c85-b7e0-a48e5ca40047</t>
+        </is>
+      </c>
+      <c r="B2102" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2102" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2102" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2102" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2102" t="n">
+        <v>431.62</v>
+      </c>
+      <c r="G2102" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="H2102" s="2" t="n">
+        <v>46080.51099775107</v>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" t="inlineStr">
+        <is>
+          <t>36559b45-86d2-4339-b4ac-9b5298e32a1c</t>
+        </is>
+      </c>
+      <c r="B2103" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2103" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2103" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2103" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2103" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="G2103" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H2103" s="2" t="n">
+        <v>46078.51099775542</v>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" t="inlineStr">
+        <is>
+          <t>b63f9594-6b3a-4766-b3ac-ff811d6945c9</t>
+        </is>
+      </c>
+      <c r="B2104" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2104" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2104" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2104" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2104" t="n">
+        <v>321.19</v>
+      </c>
+      <c r="G2104" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="H2104" s="2" t="n">
+        <v>46077.51099775869</v>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" t="inlineStr">
+        <is>
+          <t>19bcd0e5-1973-4182-9d88-51e1bb9c8e7f</t>
+        </is>
+      </c>
+      <c r="B2105" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2105" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2105" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2105" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2105" t="n">
+        <v>306.47</v>
+      </c>
+      <c r="G2105" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="H2105" s="2" t="n">
+        <v>46089.51099776207</v>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" t="inlineStr">
+        <is>
+          <t>977fef6e-86aa-4959-b343-c07c2d208c04</t>
+        </is>
+      </c>
+      <c r="B2106" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2106" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2106" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2106" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2106" t="n">
+        <v>470.55</v>
+      </c>
+      <c r="G2106" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="H2106" s="2" t="n">
+        <v>46075.51099776521</v>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" t="inlineStr">
+        <is>
+          <t>b2ccb522-99b9-4888-b83d-fc76d3f198ad</t>
+        </is>
+      </c>
+      <c r="B2107" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2107" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2107" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2107" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2107" t="n">
+        <v>178.23</v>
+      </c>
+      <c r="G2107" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H2107" s="2" t="n">
+        <v>46075.51099776841</v>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" t="inlineStr">
+        <is>
+          <t>2253c735-1715-4780-960b-68e0c2bfce16</t>
+        </is>
+      </c>
+      <c r="B2108" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2108" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2108" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2108" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2108" t="n">
+        <v>446.46</v>
+      </c>
+      <c r="G2108" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="H2108" s="2" t="n">
+        <v>46093.51099777171</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="inlineStr">
+        <is>
+          <t>bb97cf3e-26da-4919-9aaa-3d571a6508a2</t>
+        </is>
+      </c>
+      <c r="B2109" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2109" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2109" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2109" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2109" t="n">
+        <v>185.4</v>
+      </c>
+      <c r="G2109" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H2109" s="2" t="n">
+        <v>46082.51099777514</v>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" t="inlineStr">
+        <is>
+          <t>c5a2f37c-6fa0-4099-819d-5ce2c5ff2da7</t>
+        </is>
+      </c>
+      <c r="B2110" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2110" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2110" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2110" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2110" t="n">
+        <v>234.36</v>
+      </c>
+      <c r="G2110" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H2110" s="2" t="n">
+        <v>46077.51099777826</v>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="inlineStr">
+        <is>
+          <t>5a9d3a7e-2b45-42e2-aefd-19ee585139ad</t>
+        </is>
+      </c>
+      <c r="B2111" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2111" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2111" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2111" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2111" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="G2111" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="H2111" s="2" t="n">
+        <v>46080.51099778139</v>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="inlineStr">
+        <is>
+          <t>bf6fd1e8-3bcd-4ce6-b093-787fa60dd0a4</t>
+        </is>
+      </c>
+      <c r="B2112" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2112" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2112" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2112" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2112" t="n">
+        <v>467.51</v>
+      </c>
+      <c r="G2112" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="H2112" s="2" t="n">
+        <v>46095.51099778484</v>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="inlineStr">
+        <is>
+          <t>496f5bf2-9aa8-49dc-843e-381abbe652e2</t>
+        </is>
+      </c>
+      <c r="B2113" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2113" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2113" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2113" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2113" t="n">
+        <v>333.35</v>
+      </c>
+      <c r="G2113" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="H2113" s="2" t="n">
+        <v>46088.51099778811</v>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="inlineStr">
+        <is>
+          <t>5e025986-eee3-4278-a323-3b4d69ad9953</t>
+        </is>
+      </c>
+      <c r="B2114" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2114" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2114" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2114" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2114" t="n">
+        <v>221.91</v>
+      </c>
+      <c r="G2114" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H2114" s="2" t="n">
+        <v>46083.51099779146</v>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="inlineStr">
+        <is>
+          <t>e2b22b9b-05c0-485b-9b4c-bcb0523a8180</t>
+        </is>
+      </c>
+      <c r="B2115" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2115" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2115" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2115" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2115" t="n">
+        <v>307.55</v>
+      </c>
+      <c r="G2115" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="H2115" s="2" t="n">
+        <v>46096.51099779455</v>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" t="inlineStr">
+        <is>
+          <t>3f0aeb65-82ec-4578-93e9-e82b158f79d2</t>
+        </is>
+      </c>
+      <c r="B2116" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2116" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2116" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2116" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2116" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="G2116" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2116" s="2" t="n">
+        <v>46080.51099779799</v>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="inlineStr">
+        <is>
+          <t>57a3de1d-0980-4816-8ee8-1962721ca820</t>
+        </is>
+      </c>
+      <c r="B2117" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2117" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2117" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2117" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2117" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="G2117" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2117" s="2" t="n">
+        <v>46073.51099780127</v>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" t="inlineStr">
+        <is>
+          <t>df988a3e-551f-4672-9414-b7910077f50a</t>
+        </is>
+      </c>
+      <c r="B2118" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2118" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2118" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2118" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2118" t="n">
+        <v>259.66</v>
+      </c>
+      <c r="G2118" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H2118" s="2" t="n">
+        <v>46087.51099780456</v>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="inlineStr">
+        <is>
+          <t>b944c5fb-08c3-4e38-abce-73eebe83d26f</t>
+        </is>
+      </c>
+      <c r="B2119" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2119" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2119" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2119" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2119" t="n">
+        <v>414.41</v>
+      </c>
+      <c r="G2119" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H2119" s="2" t="n">
+        <v>46075.51099780796</v>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" t="inlineStr">
+        <is>
+          <t>a0df1052-a5b4-43fa-90cc-a7ec0cfac073</t>
+        </is>
+      </c>
+      <c r="B2120" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2120" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2120" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2120" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2120" t="n">
+        <v>271.11</v>
+      </c>
+      <c r="G2120" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="H2120" s="2" t="n">
+        <v>46084.51099781111</v>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" t="inlineStr">
+        <is>
+          <t>cc05df0f-ad1d-42cc-8d0c-323e4cc87e1c</t>
+        </is>
+      </c>
+      <c r="B2121" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2121" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2121" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2121" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2121" t="n">
+        <v>392.67</v>
+      </c>
+      <c r="G2121" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="H2121" s="2" t="n">
+        <v>46078.51099781419</v>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" t="inlineStr">
+        <is>
+          <t>d0595f61-eeee-4fbf-9d30-d27876d7fe0b</t>
+        </is>
+      </c>
+      <c r="B2122" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2122" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2122" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2122" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2122" t="n">
+        <v>84.02</v>
+      </c>
+      <c r="G2122" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H2122" s="2" t="n">
+        <v>46079.51099781725</v>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" t="inlineStr">
+        <is>
+          <t>788fbe33-19cc-41a8-b3b0-bdeb4b024f07</t>
+        </is>
+      </c>
+      <c r="B2123" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2123" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2123" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2123" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2123" t="n">
+        <v>201.2</v>
+      </c>
+      <c r="G2123" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="H2123" s="2" t="n">
+        <v>46083.51099782068</v>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" t="inlineStr">
+        <is>
+          <t>fff11e19-4093-40bc-a826-73dc30fe22cd</t>
+        </is>
+      </c>
+      <c r="B2124" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2124" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2124" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2124" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2124" t="n">
+        <v>266.85</v>
+      </c>
+      <c r="G2124" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="H2124" s="2" t="n">
+        <v>46076.51099782381</v>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="inlineStr">
+        <is>
+          <t>fda9abab-34a5-470f-a66f-4f91021c389b</t>
+        </is>
+      </c>
+      <c r="B2125" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2125" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2125" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2125" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2125" t="n">
+        <v>128.33</v>
+      </c>
+      <c r="G2125" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="H2125" s="2" t="n">
+        <v>46078.510997827</v>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" t="inlineStr">
+        <is>
+          <t>9f438f4e-90b4-4c99-aca3-8156625c1b65</t>
+        </is>
+      </c>
+      <c r="B2126" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2126" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2126" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2126" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2126" t="n">
+        <v>487</v>
+      </c>
+      <c r="G2126" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="H2126" s="2" t="n">
+        <v>46078.51099783021</v>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="inlineStr">
+        <is>
+          <t>2761f052-058c-46ca-880d-6e9f4d12cb9e</t>
+        </is>
+      </c>
+      <c r="B2127" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2127" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2127" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2127" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2127" t="n">
+        <v>367.94</v>
+      </c>
+      <c r="G2127" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="H2127" s="2" t="n">
+        <v>46076.51099783568</v>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" t="inlineStr">
+        <is>
+          <t>57d062f5-8262-4b9a-9dcc-00f9b8ffbbe8</t>
+        </is>
+      </c>
+      <c r="B2128" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2128" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2128" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2128" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2128" t="n">
+        <v>437.17</v>
+      </c>
+      <c r="G2128" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="H2128" s="2" t="n">
+        <v>46080.510997839</v>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
+        <is>
+          <t>99ca0447-afb1-4079-97a5-d367c2b62f8c</t>
+        </is>
+      </c>
+      <c r="B2129" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2129" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2129" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2129" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2129" t="n">
+        <v>145.16</v>
+      </c>
+      <c r="G2129" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H2129" s="2" t="n">
+        <v>46089.51099784235</v>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" t="inlineStr">
+        <is>
+          <t>4ec28dbd-5a5d-4252-b48a-0fcea0acc93f</t>
+        </is>
+      </c>
+      <c r="B2130" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2130" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2130" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2130" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2130" t="n">
+        <v>91.76000000000001</v>
+      </c>
+      <c r="G2130" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H2130" s="2" t="n">
+        <v>46085.51099784537</v>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" t="inlineStr">
+        <is>
+          <t>914c6429-d02c-404d-b4d4-e38fbc0ca338</t>
+        </is>
+      </c>
+      <c r="B2131" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2131" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2131" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2131" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2131" t="n">
+        <v>279.24</v>
+      </c>
+      <c r="G2131" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="H2131" s="2" t="n">
+        <v>46094.51099784842</v>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" t="inlineStr">
+        <is>
+          <t>fe2e2ecb-8ef1-467e-bc50-e1d1c4529cb8</t>
+        </is>
+      </c>
+      <c r="B2132" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2132" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2132" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2132" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2132" t="n">
+        <v>429.02</v>
+      </c>
+      <c r="G2132" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="H2132" s="2" t="n">
+        <v>46093.51099785164</v>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" t="inlineStr">
+        <is>
+          <t>48a3f3c0-2d42-4bbb-9665-69eef7309b76</t>
+        </is>
+      </c>
+      <c r="B2133" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2133" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2133" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2133" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2133" t="n">
+        <v>317.89</v>
+      </c>
+      <c r="G2133" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H2133" s="2" t="n">
+        <v>46081.51099785489</v>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" t="inlineStr">
+        <is>
+          <t>06aa2e96-9295-4a0f-b530-5c47a1731bb5</t>
+        </is>
+      </c>
+      <c r="B2134" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2134" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2134" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2134" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2134" t="n">
+        <v>452.94</v>
+      </c>
+      <c r="G2134" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="H2134" s="2" t="n">
+        <v>46078.51099785815</v>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" t="inlineStr">
+        <is>
+          <t>59ef2824-da9e-480a-acc1-c6c52be09a78</t>
+        </is>
+      </c>
+      <c r="B2135" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2135" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2135" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2135" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2135" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="G2135" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H2135" s="2" t="n">
+        <v>46086.51099786122</v>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" t="inlineStr">
+        <is>
+          <t>eda7d8f4-0b96-4c2c-a7c2-41c0065f5292</t>
+        </is>
+      </c>
+      <c r="B2136" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2136" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2136" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2136" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2136" t="n">
+        <v>439.4</v>
+      </c>
+      <c r="G2136" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="H2136" s="2" t="n">
+        <v>46083.51099786451</v>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" t="inlineStr">
+        <is>
+          <t>8102a267-2537-420b-b4bd-5eccdcfe8aff</t>
+        </is>
+      </c>
+      <c r="B2137" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2137" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2137" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2137" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2137" t="n">
+        <v>404.36</v>
+      </c>
+      <c r="G2137" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="H2137" s="2" t="n">
+        <v>46072.51099786765</v>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" t="inlineStr">
+        <is>
+          <t>827055d8-ddda-4768-b643-a2fcc9e0d623</t>
+        </is>
+      </c>
+      <c r="B2138" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2138" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2138" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2138" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2138" t="n">
+        <v>251.75</v>
+      </c>
+      <c r="G2138" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H2138" s="2" t="n">
+        <v>46072.51099787076</v>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" t="inlineStr">
+        <is>
+          <t>e3c056df-f0f1-45a3-9f3b-df0ea66b367b</t>
+        </is>
+      </c>
+      <c r="B2139" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2139" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2139" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2139" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2139" t="n">
+        <v>151.61</v>
+      </c>
+      <c r="G2139" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="H2139" s="2" t="n">
+        <v>46089.51099787397</v>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" t="inlineStr">
+        <is>
+          <t>f7ffa53f-19e1-4955-b99f-25f6e2307307</t>
+        </is>
+      </c>
+      <c r="B2140" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2140" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2140" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2140" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2140" t="n">
+        <v>51.22</v>
+      </c>
+      <c r="G2140" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H2140" s="2" t="n">
+        <v>46071.51099787719</v>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" t="inlineStr">
+        <is>
+          <t>93c0a544-ba2d-46fa-b0c1-662652ce82da</t>
+        </is>
+      </c>
+      <c r="B2141" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2141" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2141" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2141" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2141" t="n">
+        <v>201.63</v>
+      </c>
+      <c r="G2141" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H2141" s="2" t="n">
+        <v>46084.51099788044</v>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" t="inlineStr">
+        <is>
+          <t>cd712b09-5fec-4cbc-99ef-04affc2184cb</t>
+        </is>
+      </c>
+      <c r="B2142" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2142" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2142" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2142" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2142" t="n">
+        <v>480.29</v>
+      </c>
+      <c r="G2142" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H2142" s="2" t="n">
+        <v>46082.51099788346</v>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" t="inlineStr">
+        <is>
+          <t>40303aa6-7afc-4c0f-985f-fb70af44ba67</t>
+        </is>
+      </c>
+      <c r="B2143" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2143" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2143" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2143" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2143" t="n">
+        <v>221.73</v>
+      </c>
+      <c r="G2143" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H2143" s="2" t="n">
+        <v>46076.51099788669</v>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" t="inlineStr">
+        <is>
+          <t>29b1f281-a930-4a0a-b45b-0340bd0dff75</t>
+        </is>
+      </c>
+      <c r="B2144" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2144" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2144" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2144" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2144" t="n">
+        <v>149.27</v>
+      </c>
+      <c r="G2144" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H2144" s="2" t="n">
+        <v>46082.51099788988</v>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" t="inlineStr">
+        <is>
+          <t>7b7938f5-eb28-43a4-93a7-879440105e8c</t>
+        </is>
+      </c>
+      <c r="B2145" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2145" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2145" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2145" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2145" t="n">
+        <v>235.39</v>
+      </c>
+      <c r="G2145" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="H2145" s="2" t="n">
+        <v>46067.51099789296</v>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="A2146" t="inlineStr">
+        <is>
+          <t>271c28f9-7d77-41a1-88dc-531678f64ee0</t>
+        </is>
+      </c>
+      <c r="B2146" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2146" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2146" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2146" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2146" t="n">
+        <v>149.98</v>
+      </c>
+      <c r="G2146" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H2146" s="2" t="n">
+        <v>46071.51099789624</v>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" t="inlineStr">
+        <is>
+          <t>bcbe24ee-36f9-4bcb-9bd2-056996e0a523</t>
+        </is>
+      </c>
+      <c r="B2147" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2147" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2147" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2147" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2147" t="n">
+        <v>351.36</v>
+      </c>
+      <c r="G2147" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="H2147" s="2" t="n">
+        <v>46075.5109978996</v>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" t="inlineStr">
+        <is>
+          <t>6d820e97-df12-4c74-887f-c7e445e9c63d</t>
+        </is>
+      </c>
+      <c r="B2148" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2148" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2148" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2148" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2148" t="n">
+        <v>89.11</v>
+      </c>
+      <c r="G2148" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H2148" s="2" t="n">
+        <v>46069.51099790275</v>
+      </c>
+    </row>
+    <row r="2149">
+      <c r="A2149" t="inlineStr">
+        <is>
+          <t>a27bcf74-dd44-4399-90c0-29d91c30d391</t>
+        </is>
+      </c>
+      <c r="B2149" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2149" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2149" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2149" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2149" t="n">
+        <v>92.12</v>
+      </c>
+      <c r="G2149" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H2149" s="2" t="n">
+        <v>46096.51099790641</v>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" t="inlineStr">
+        <is>
+          <t>a9aac943-ce0c-44a9-a54b-ae226e6d2ae7</t>
+        </is>
+      </c>
+      <c r="B2150" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2150" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2150" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2150" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2150" t="n">
+        <v>130.79</v>
+      </c>
+      <c r="G2150" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="H2150" s="2" t="n">
+        <v>46089.51099790943</v>
+      </c>
+    </row>
+    <row r="2151">
+      <c r="A2151" t="inlineStr">
+        <is>
+          <t>987075a0-0883-43bf-a916-b52112048be4</t>
+        </is>
+      </c>
+      <c r="B2151" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2151" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2151" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2151" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2151" t="n">
+        <v>419.03</v>
+      </c>
+      <c r="G2151" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="H2151" s="2" t="n">
+        <v>46073.51099791293</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2151"/>
+  <dimension ref="A1:H2201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71905,7 +71905,7 @@
         <v>4.32</v>
       </c>
       <c r="H2102" s="2" t="n">
-        <v>46080.51099775107</v>
+        <v>46080.51099775463</v>
       </c>
     </row>
     <row r="2103">
@@ -71939,7 +71939,7 @@
         <v>0.18</v>
       </c>
       <c r="H2103" s="2" t="n">
-        <v>46078.51099775542</v>
+        <v>46078.51099775463</v>
       </c>
     </row>
     <row r="2104">
@@ -71973,7 +71973,7 @@
         <v>3.21</v>
       </c>
       <c r="H2104" s="2" t="n">
-        <v>46077.51099775869</v>
+        <v>46077.51099775463</v>
       </c>
     </row>
     <row r="2105">
@@ -72007,7 +72007,7 @@
         <v>3.06</v>
       </c>
       <c r="H2105" s="2" t="n">
-        <v>46089.51099776207</v>
+        <v>46089.51099776621</v>
       </c>
     </row>
     <row r="2106">
@@ -72041,7 +72041,7 @@
         <v>4.71</v>
       </c>
       <c r="H2106" s="2" t="n">
-        <v>46075.51099776521</v>
+        <v>46075.51099776621</v>
       </c>
     </row>
     <row r="2107">
@@ -72075,7 +72075,7 @@
         <v>1.78</v>
       </c>
       <c r="H2107" s="2" t="n">
-        <v>46075.51099776841</v>
+        <v>46075.51099776621</v>
       </c>
     </row>
     <row r="2108">
@@ -72109,7 +72109,7 @@
         <v>4.46</v>
       </c>
       <c r="H2108" s="2" t="n">
-        <v>46093.51099777171</v>
+        <v>46093.51099776621</v>
       </c>
     </row>
     <row r="2109">
@@ -72143,7 +72143,7 @@
         <v>1.85</v>
       </c>
       <c r="H2109" s="2" t="n">
-        <v>46082.51099777514</v>
+        <v>46082.51099777778</v>
       </c>
     </row>
     <row r="2110">
@@ -72177,7 +72177,7 @@
         <v>2.34</v>
       </c>
       <c r="H2110" s="2" t="n">
-        <v>46077.51099777826</v>
+        <v>46077.51099777778</v>
       </c>
     </row>
     <row r="2111">
@@ -72211,7 +72211,7 @@
         <v>0.97</v>
       </c>
       <c r="H2111" s="2" t="n">
-        <v>46080.51099778139</v>
+        <v>46080.51099777778</v>
       </c>
     </row>
     <row r="2112">
@@ -72245,7 +72245,7 @@
         <v>4.68</v>
       </c>
       <c r="H2112" s="2" t="n">
-        <v>46095.51099778484</v>
+        <v>46095.51099778935</v>
       </c>
     </row>
     <row r="2113">
@@ -72279,7 +72279,7 @@
         <v>3.33</v>
       </c>
       <c r="H2113" s="2" t="n">
-        <v>46088.51099778811</v>
+        <v>46088.51099778935</v>
       </c>
     </row>
     <row r="2114">
@@ -72313,7 +72313,7 @@
         <v>2.22</v>
       </c>
       <c r="H2114" s="2" t="n">
-        <v>46083.51099779146</v>
+        <v>46083.51099778935</v>
       </c>
     </row>
     <row r="2115">
@@ -72347,7 +72347,7 @@
         <v>3.08</v>
       </c>
       <c r="H2115" s="2" t="n">
-        <v>46096.51099779455</v>
+        <v>46096.51099778935</v>
       </c>
     </row>
     <row r="2116">
@@ -72381,7 +72381,7 @@
         <v>0.2</v>
       </c>
       <c r="H2116" s="2" t="n">
-        <v>46080.51099779799</v>
+        <v>46080.51099780093</v>
       </c>
     </row>
     <row r="2117">
@@ -72415,7 +72415,7 @@
         <v>0.1</v>
       </c>
       <c r="H2117" s="2" t="n">
-        <v>46073.51099780127</v>
+        <v>46073.51099780093</v>
       </c>
     </row>
     <row r="2118">
@@ -72449,7 +72449,7 @@
         <v>2.6</v>
       </c>
       <c r="H2118" s="2" t="n">
-        <v>46087.51099780456</v>
+        <v>46087.51099780093</v>
       </c>
     </row>
     <row r="2119">
@@ -72483,7 +72483,7 @@
         <v>4.14</v>
       </c>
       <c r="H2119" s="2" t="n">
-        <v>46075.51099780796</v>
+        <v>46075.5109978125</v>
       </c>
     </row>
     <row r="2120">
@@ -72517,7 +72517,7 @@
         <v>2.71</v>
       </c>
       <c r="H2120" s="2" t="n">
-        <v>46084.51099781111</v>
+        <v>46084.5109978125</v>
       </c>
     </row>
     <row r="2121">
@@ -72551,7 +72551,7 @@
         <v>3.93</v>
       </c>
       <c r="H2121" s="2" t="n">
-        <v>46078.51099781419</v>
+        <v>46078.5109978125</v>
       </c>
     </row>
     <row r="2122">
@@ -72585,7 +72585,7 @@
         <v>0.84</v>
       </c>
       <c r="H2122" s="2" t="n">
-        <v>46079.51099781725</v>
+        <v>46079.5109978125</v>
       </c>
     </row>
     <row r="2123">
@@ -72619,7 +72619,7 @@
         <v>2.01</v>
       </c>
       <c r="H2123" s="2" t="n">
-        <v>46083.51099782068</v>
+        <v>46083.51099782407</v>
       </c>
     </row>
     <row r="2124">
@@ -72653,7 +72653,7 @@
         <v>2.67</v>
       </c>
       <c r="H2124" s="2" t="n">
-        <v>46076.51099782381</v>
+        <v>46076.51099782407</v>
       </c>
     </row>
     <row r="2125">
@@ -72687,7 +72687,7 @@
         <v>1.28</v>
       </c>
       <c r="H2125" s="2" t="n">
-        <v>46078.510997827</v>
+        <v>46078.51099782407</v>
       </c>
     </row>
     <row r="2126">
@@ -72721,7 +72721,7 @@
         <v>4.87</v>
       </c>
       <c r="H2126" s="2" t="n">
-        <v>46078.51099783021</v>
+        <v>46078.51099783565</v>
       </c>
     </row>
     <row r="2127">
@@ -72755,7 +72755,7 @@
         <v>3.68</v>
       </c>
       <c r="H2127" s="2" t="n">
-        <v>46076.51099783568</v>
+        <v>46076.51099783565</v>
       </c>
     </row>
     <row r="2128">
@@ -72789,7 +72789,7 @@
         <v>4.37</v>
       </c>
       <c r="H2128" s="2" t="n">
-        <v>46080.510997839</v>
+        <v>46080.51099783565</v>
       </c>
     </row>
     <row r="2129">
@@ -72823,7 +72823,7 @@
         <v>1.45</v>
       </c>
       <c r="H2129" s="2" t="n">
-        <v>46089.51099784235</v>
+        <v>46089.51099784722</v>
       </c>
     </row>
     <row r="2130">
@@ -72857,7 +72857,7 @@
         <v>0.92</v>
       </c>
       <c r="H2130" s="2" t="n">
-        <v>46085.51099784537</v>
+        <v>46085.51099784722</v>
       </c>
     </row>
     <row r="2131">
@@ -72891,7 +72891,7 @@
         <v>2.79</v>
       </c>
       <c r="H2131" s="2" t="n">
-        <v>46094.51099784842</v>
+        <v>46094.51099784722</v>
       </c>
     </row>
     <row r="2132">
@@ -72925,7 +72925,7 @@
         <v>4.29</v>
       </c>
       <c r="H2132" s="2" t="n">
-        <v>46093.51099785164</v>
+        <v>46093.51099784722</v>
       </c>
     </row>
     <row r="2133">
@@ -72959,7 +72959,7 @@
         <v>3.18</v>
       </c>
       <c r="H2133" s="2" t="n">
-        <v>46081.51099785489</v>
+        <v>46081.51099785879</v>
       </c>
     </row>
     <row r="2134">
@@ -72993,7 +72993,7 @@
         <v>4.53</v>
       </c>
       <c r="H2134" s="2" t="n">
-        <v>46078.51099785815</v>
+        <v>46078.51099785879</v>
       </c>
     </row>
     <row r="2135">
@@ -73027,7 +73027,7 @@
         <v>0.49</v>
       </c>
       <c r="H2135" s="2" t="n">
-        <v>46086.51099786122</v>
+        <v>46086.51099785879</v>
       </c>
     </row>
     <row r="2136">
@@ -73061,7 +73061,7 @@
         <v>4.39</v>
       </c>
       <c r="H2136" s="2" t="n">
-        <v>46083.51099786451</v>
+        <v>46083.51099785879</v>
       </c>
     </row>
     <row r="2137">
@@ -73095,7 +73095,7 @@
         <v>4.04</v>
       </c>
       <c r="H2137" s="2" t="n">
-        <v>46072.51099786765</v>
+        <v>46072.51099787037</v>
       </c>
     </row>
     <row r="2138">
@@ -73129,7 +73129,7 @@
         <v>2.52</v>
       </c>
       <c r="H2138" s="2" t="n">
-        <v>46072.51099787076</v>
+        <v>46072.51099787037</v>
       </c>
     </row>
     <row r="2139">
@@ -73163,7 +73163,7 @@
         <v>1.52</v>
       </c>
       <c r="H2139" s="2" t="n">
-        <v>46089.51099787397</v>
+        <v>46089.51099787037</v>
       </c>
     </row>
     <row r="2140">
@@ -73197,7 +73197,7 @@
         <v>0.51</v>
       </c>
       <c r="H2140" s="2" t="n">
-        <v>46071.51099787719</v>
+        <v>46071.51099788195</v>
       </c>
     </row>
     <row r="2141">
@@ -73231,7 +73231,7 @@
         <v>2.02</v>
       </c>
       <c r="H2141" s="2" t="n">
-        <v>46084.51099788044</v>
+        <v>46084.51099788195</v>
       </c>
     </row>
     <row r="2142">
@@ -73265,7 +73265,7 @@
         <v>4.8</v>
       </c>
       <c r="H2142" s="2" t="n">
-        <v>46082.51099788346</v>
+        <v>46082.51099788195</v>
       </c>
     </row>
     <row r="2143">
@@ -73299,7 +73299,7 @@
         <v>2.22</v>
       </c>
       <c r="H2143" s="2" t="n">
-        <v>46076.51099788669</v>
+        <v>46076.51099788195</v>
       </c>
     </row>
     <row r="2144">
@@ -73333,7 +73333,7 @@
         <v>1.49</v>
       </c>
       <c r="H2144" s="2" t="n">
-        <v>46082.51099788988</v>
+        <v>46082.51099789352</v>
       </c>
     </row>
     <row r="2145">
@@ -73367,7 +73367,7 @@
         <v>2.35</v>
       </c>
       <c r="H2145" s="2" t="n">
-        <v>46067.51099789296</v>
+        <v>46067.51099789352</v>
       </c>
     </row>
     <row r="2146">
@@ -73401,7 +73401,7 @@
         <v>1.5</v>
       </c>
       <c r="H2146" s="2" t="n">
-        <v>46071.51099789624</v>
+        <v>46071.51099789352</v>
       </c>
     </row>
     <row r="2147">
@@ -73435,7 +73435,7 @@
         <v>3.51</v>
       </c>
       <c r="H2147" s="2" t="n">
-        <v>46075.5109978996</v>
+        <v>46075.51099790509</v>
       </c>
     </row>
     <row r="2148">
@@ -73469,7 +73469,7 @@
         <v>0.89</v>
       </c>
       <c r="H2148" s="2" t="n">
-        <v>46069.51099790275</v>
+        <v>46069.51099790509</v>
       </c>
     </row>
     <row r="2149">
@@ -73503,7 +73503,7 @@
         <v>0.92</v>
       </c>
       <c r="H2149" s="2" t="n">
-        <v>46096.51099790641</v>
+        <v>46096.51099790509</v>
       </c>
     </row>
     <row r="2150">
@@ -73537,7 +73537,7 @@
         <v>1.31</v>
       </c>
       <c r="H2150" s="2" t="n">
-        <v>46089.51099790943</v>
+        <v>46089.51099790509</v>
       </c>
     </row>
     <row r="2151">
@@ -73571,7 +73571,1707 @@
         <v>4.19</v>
       </c>
       <c r="H2151" s="2" t="n">
-        <v>46073.51099791293</v>
+        <v>46073.51099791667</v>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="A2152" t="inlineStr">
+        <is>
+          <t>f614a25c-d072-407e-858d-cfa7672347c9</t>
+        </is>
+      </c>
+      <c r="B2152" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2152" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2152" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2152" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2152" t="n">
+        <v>380.27</v>
+      </c>
+      <c r="G2152" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H2152" s="2" t="n">
+        <v>46078.56005224503</v>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" t="inlineStr">
+        <is>
+          <t>0262c399-3e16-40f1-9bb0-dd98cacadc9b</t>
+        </is>
+      </c>
+      <c r="B2153" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2153" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2153" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2153" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2153" t="n">
+        <v>290.86</v>
+      </c>
+      <c r="G2153" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="H2153" s="2" t="n">
+        <v>46081.56005224938</v>
+      </c>
+    </row>
+    <row r="2154">
+      <c r="A2154" t="inlineStr">
+        <is>
+          <t>2a25d4e2-88c7-48dd-96eb-2d5d4416d748</t>
+        </is>
+      </c>
+      <c r="B2154" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2154" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2154" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2154" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2154" t="n">
+        <v>451.17</v>
+      </c>
+      <c r="G2154" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="H2154" s="2" t="n">
+        <v>46090.56005225271</v>
+      </c>
+    </row>
+    <row r="2155">
+      <c r="A2155" t="inlineStr">
+        <is>
+          <t>6b7e61ac-d1b1-4335-8714-a5ff3654c395</t>
+        </is>
+      </c>
+      <c r="B2155" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2155" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2155" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2155" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2155" t="n">
+        <v>439.83</v>
+      </c>
+      <c r="G2155" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H2155" s="2" t="n">
+        <v>46096.56005225634</v>
+      </c>
+    </row>
+    <row r="2156">
+      <c r="A2156" t="inlineStr">
+        <is>
+          <t>5eee4774-018b-4ba5-a86f-79b3cab028bc</t>
+        </is>
+      </c>
+      <c r="B2156" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2156" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2156" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2156" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2156" t="n">
+        <v>498.38</v>
+      </c>
+      <c r="G2156" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="H2156" s="2" t="n">
+        <v>46094.56005225951</v>
+      </c>
+    </row>
+    <row r="2157">
+      <c r="A2157" t="inlineStr">
+        <is>
+          <t>8d37ff75-f7bf-453b-9f5b-1f277576e785</t>
+        </is>
+      </c>
+      <c r="B2157" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2157" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2157" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2157" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2157" t="n">
+        <v>164.77</v>
+      </c>
+      <c r="G2157" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H2157" s="2" t="n">
+        <v>46075.56005226282</v>
+      </c>
+    </row>
+    <row r="2158">
+      <c r="A2158" t="inlineStr">
+        <is>
+          <t>3308fcb2-9271-4d13-88c8-6e412e2ab43b</t>
+        </is>
+      </c>
+      <c r="B2158" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2158" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2158" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2158" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2158" t="n">
+        <v>394.58</v>
+      </c>
+      <c r="G2158" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H2158" s="2" t="n">
+        <v>46083.56005226635</v>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" t="inlineStr">
+        <is>
+          <t>f329b0cc-80d6-4b90-a1a1-19409e730532</t>
+        </is>
+      </c>
+      <c r="B2159" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2159" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2159" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2159" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2159" t="n">
+        <v>415.48</v>
+      </c>
+      <c r="G2159" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="H2159" s="2" t="n">
+        <v>46087.56005226964</v>
+      </c>
+    </row>
+    <row r="2160">
+      <c r="A2160" t="inlineStr">
+        <is>
+          <t>6d9d0614-8134-4385-bb3d-7b2495e367ef</t>
+        </is>
+      </c>
+      <c r="B2160" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2160" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2160" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2160" t="n">
+        <v>340.38</v>
+      </c>
+      <c r="G2160" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H2160" s="2" t="n">
+        <v>46072.56005227272</v>
+      </c>
+    </row>
+    <row r="2161">
+      <c r="A2161" t="inlineStr">
+        <is>
+          <t>63b02cf5-9b34-4f85-98df-3bca8d39032c</t>
+        </is>
+      </c>
+      <c r="B2161" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2161" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2161" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2161" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2161" t="n">
+        <v>396.21</v>
+      </c>
+      <c r="G2161" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="H2161" s="2" t="n">
+        <v>46084.56005227612</v>
+      </c>
+    </row>
+    <row r="2162">
+      <c r="A2162" t="inlineStr">
+        <is>
+          <t>da4071cf-3d71-41ec-a07a-0ae0d142923f</t>
+        </is>
+      </c>
+      <c r="B2162" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2162" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2162" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2162" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2162" t="n">
+        <v>246.81</v>
+      </c>
+      <c r="G2162" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="H2162" s="2" t="n">
+        <v>46090.56005227967</v>
+      </c>
+    </row>
+    <row r="2163">
+      <c r="A2163" t="inlineStr">
+        <is>
+          <t>1b463568-f76e-4ec5-bb41-c6cf128fc41a</t>
+        </is>
+      </c>
+      <c r="B2163" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2163" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2163" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2163" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2163" t="n">
+        <v>400.73</v>
+      </c>
+      <c r="G2163" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="H2163" s="2" t="n">
+        <v>46078.5600522829</v>
+      </c>
+    </row>
+    <row r="2164">
+      <c r="A2164" t="inlineStr">
+        <is>
+          <t>e4716410-d205-43f8-ba9c-52bd777c8dc9</t>
+        </is>
+      </c>
+      <c r="B2164" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2164" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2164" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2164" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2164" t="n">
+        <v>69.70999999999999</v>
+      </c>
+      <c r="G2164" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H2164" s="2" t="n">
+        <v>46077.56005228612</v>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="A2165" t="inlineStr">
+        <is>
+          <t>da781823-c864-4d4a-abb7-0cb9082f2fad</t>
+        </is>
+      </c>
+      <c r="B2165" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2165" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2165" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2165" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2165" t="n">
+        <v>257.11</v>
+      </c>
+      <c r="G2165" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="H2165" s="2" t="n">
+        <v>46083.56005228934</v>
+      </c>
+    </row>
+    <row r="2166">
+      <c r="A2166" t="inlineStr">
+        <is>
+          <t>64605030-c110-4b67-a85c-4a5c99c4f45d</t>
+        </is>
+      </c>
+      <c r="B2166" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2166" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2166" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2166" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2166" t="n">
+        <v>169.31</v>
+      </c>
+      <c r="G2166" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H2166" s="2" t="n">
+        <v>46096.56005229243</v>
+      </c>
+    </row>
+    <row r="2167">
+      <c r="A2167" t="inlineStr">
+        <is>
+          <t>45d31780-c46c-4c23-9266-e145539561d0</t>
+        </is>
+      </c>
+      <c r="B2167" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2167" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2167" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2167" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2167" t="n">
+        <v>238.31</v>
+      </c>
+      <c r="G2167" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H2167" s="2" t="n">
+        <v>46076.56005229554</v>
+      </c>
+    </row>
+    <row r="2168">
+      <c r="A2168" t="inlineStr">
+        <is>
+          <t>b7392552-2075-4894-ac81-67fc530e02fa</t>
+        </is>
+      </c>
+      <c r="B2168" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2168" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2168" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2168" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2168" t="n">
+        <v>252.31</v>
+      </c>
+      <c r="G2168" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H2168" s="2" t="n">
+        <v>46095.56005229862</v>
+      </c>
+    </row>
+    <row r="2169">
+      <c r="A2169" t="inlineStr">
+        <is>
+          <t>8832e022-50f7-4f55-92f8-8bdfade18bb2</t>
+        </is>
+      </c>
+      <c r="B2169" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2169" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2169" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2169" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2169" t="n">
+        <v>312.24</v>
+      </c>
+      <c r="G2169" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="H2169" s="2" t="n">
+        <v>46076.56005230208</v>
+      </c>
+    </row>
+    <row r="2170">
+      <c r="A2170" t="inlineStr">
+        <is>
+          <t>278f2a28-4279-42be-897b-6febc5d884eb</t>
+        </is>
+      </c>
+      <c r="B2170" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2170" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2170" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2170" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2170" t="n">
+        <v>340.17</v>
+      </c>
+      <c r="G2170" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H2170" s="2" t="n">
+        <v>46090.56005230531</v>
+      </c>
+    </row>
+    <row r="2171">
+      <c r="A2171" t="inlineStr">
+        <is>
+          <t>57e51cb3-1133-4446-b5d6-d964b57c2bf4</t>
+        </is>
+      </c>
+      <c r="B2171" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2171" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2171" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2171" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2171" t="n">
+        <v>368.4</v>
+      </c>
+      <c r="G2171" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="H2171" s="2" t="n">
+        <v>46094.56005230843</v>
+      </c>
+    </row>
+    <row r="2172">
+      <c r="A2172" t="inlineStr">
+        <is>
+          <t>5b3d5119-02c8-459c-8dba-312907c99be3</t>
+        </is>
+      </c>
+      <c r="B2172" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2172" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2172" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2172" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2172" t="n">
+        <v>229.4</v>
+      </c>
+      <c r="G2172" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H2172" s="2" t="n">
+        <v>46076.56005231145</v>
+      </c>
+    </row>
+    <row r="2173">
+      <c r="A2173" t="inlineStr">
+        <is>
+          <t>433ef83f-ea8c-424c-925a-a2a983714c9a</t>
+        </is>
+      </c>
+      <c r="B2173" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2173" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2173" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2173" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2173" t="n">
+        <v>159.56</v>
+      </c>
+      <c r="G2173" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H2173" s="2" t="n">
+        <v>46083.56005231472</v>
+      </c>
+    </row>
+    <row r="2174">
+      <c r="A2174" t="inlineStr">
+        <is>
+          <t>eb3b6cbf-8faf-4a3a-a6b9-17ec1740b64a</t>
+        </is>
+      </c>
+      <c r="B2174" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2174" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2174" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2174" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2174" t="n">
+        <v>247.33</v>
+      </c>
+      <c r="G2174" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="H2174" s="2" t="n">
+        <v>46084.560052318</v>
+      </c>
+    </row>
+    <row r="2175">
+      <c r="A2175" t="inlineStr">
+        <is>
+          <t>942580a3-ddc3-4a52-9f2c-e5addf17713c</t>
+        </is>
+      </c>
+      <c r="B2175" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2175" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2175" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2175" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2175" t="n">
+        <v>192.95</v>
+      </c>
+      <c r="G2175" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H2175" s="2" t="n">
+        <v>46084.56005232113</v>
+      </c>
+    </row>
+    <row r="2176">
+      <c r="A2176" t="inlineStr">
+        <is>
+          <t>38ee5463-7e24-4816-89d5-56e4c92f4b75</t>
+        </is>
+      </c>
+      <c r="B2176" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2176" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2176" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2176" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2176" t="n">
+        <v>257.46</v>
+      </c>
+      <c r="G2176" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="H2176" s="2" t="n">
+        <v>46093.56005232433</v>
+      </c>
+    </row>
+    <row r="2177">
+      <c r="A2177" t="inlineStr">
+        <is>
+          <t>8917caa0-1b5d-4cf0-8a1b-dd944fdcb4fc</t>
+        </is>
+      </c>
+      <c r="B2177" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2177" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2177" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2177" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2177" t="n">
+        <v>233.49</v>
+      </c>
+      <c r="G2177" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="H2177" s="2" t="n">
+        <v>46070.56005232743</v>
+      </c>
+    </row>
+    <row r="2178">
+      <c r="A2178" t="inlineStr">
+        <is>
+          <t>b51d9141-f138-4c13-bd33-840abdef0c56</t>
+        </is>
+      </c>
+      <c r="B2178" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2178" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2178" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2178" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2178" t="n">
+        <v>252.34</v>
+      </c>
+      <c r="G2178" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H2178" s="2" t="n">
+        <v>46090.56005233061</v>
+      </c>
+    </row>
+    <row r="2179">
+      <c r="A2179" t="inlineStr">
+        <is>
+          <t>4e00cde6-d4c0-4b84-994e-385004d2209b</t>
+        </is>
+      </c>
+      <c r="B2179" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2179" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2179" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2179" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2179" t="n">
+        <v>199.03</v>
+      </c>
+      <c r="G2179" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H2179" s="2" t="n">
+        <v>46095.56005233381</v>
+      </c>
+    </row>
+    <row r="2180">
+      <c r="A2180" t="inlineStr">
+        <is>
+          <t>204f2cc7-1919-46da-aa7f-2625db700d51</t>
+        </is>
+      </c>
+      <c r="B2180" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2180" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2180" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2180" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2180" t="n">
+        <v>319.02</v>
+      </c>
+      <c r="G2180" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="H2180" s="2" t="n">
+        <v>46075.560052337</v>
+      </c>
+    </row>
+    <row r="2181">
+      <c r="A2181" t="inlineStr">
+        <is>
+          <t>b0958a35-3f18-4de5-a04e-66cd80ea1251</t>
+        </is>
+      </c>
+      <c r="B2181" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2181" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2181" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2181" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2181" t="n">
+        <v>239.66</v>
+      </c>
+      <c r="G2181" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H2181" s="2" t="n">
+        <v>46080.56005234009</v>
+      </c>
+    </row>
+    <row r="2182">
+      <c r="A2182" t="inlineStr">
+        <is>
+          <t>f02b4194-8fef-406c-b397-730e5dfe6a3e</t>
+        </is>
+      </c>
+      <c r="B2182" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2182" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2182" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2182" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2182" t="n">
+        <v>382.26</v>
+      </c>
+      <c r="G2182" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="H2182" s="2" t="n">
+        <v>46074.56005234329</v>
+      </c>
+    </row>
+    <row r="2183">
+      <c r="A2183" t="inlineStr">
+        <is>
+          <t>05978b60-2fbf-493f-a9ce-359e7b9308e6</t>
+        </is>
+      </c>
+      <c r="B2183" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2183" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2183" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2183" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2183" t="n">
+        <v>481.83</v>
+      </c>
+      <c r="G2183" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="H2183" s="2" t="n">
+        <v>46074.56005234642</v>
+      </c>
+    </row>
+    <row r="2184">
+      <c r="A2184" t="inlineStr">
+        <is>
+          <t>037e247b-06b0-4702-b29b-e0560f63af9c</t>
+        </is>
+      </c>
+      <c r="B2184" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2184" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2184" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2184" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2184" t="n">
+        <v>101.58</v>
+      </c>
+      <c r="G2184" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H2184" s="2" t="n">
+        <v>46080.56005235016</v>
+      </c>
+    </row>
+    <row r="2185">
+      <c r="A2185" t="inlineStr">
+        <is>
+          <t>e5ef5fa1-f3e4-4215-bf58-7473d08c417f</t>
+        </is>
+      </c>
+      <c r="B2185" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2185" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2185" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2185" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2185" t="n">
+        <v>251.18</v>
+      </c>
+      <c r="G2185" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="H2185" s="2" t="n">
+        <v>46087.56005235326</v>
+      </c>
+    </row>
+    <row r="2186">
+      <c r="A2186" t="inlineStr">
+        <is>
+          <t>dc399a55-f385-438f-96a0-c1689ee83578</t>
+        </is>
+      </c>
+      <c r="B2186" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2186" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2186" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2186" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2186" t="n">
+        <v>493.31</v>
+      </c>
+      <c r="G2186" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="H2186" s="2" t="n">
+        <v>46093.5600523563</v>
+      </c>
+    </row>
+    <row r="2187">
+      <c r="A2187" t="inlineStr">
+        <is>
+          <t>b4085452-deb6-4409-a161-8e0377058351</t>
+        </is>
+      </c>
+      <c r="B2187" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2187" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2187" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2187" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2187" t="n">
+        <v>148.34</v>
+      </c>
+      <c r="G2187" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H2187" s="2" t="n">
+        <v>46073.56005235959</v>
+      </c>
+    </row>
+    <row r="2188">
+      <c r="A2188" t="inlineStr">
+        <is>
+          <t>5810a64b-5fca-48dd-b1b5-3a981545e65b</t>
+        </is>
+      </c>
+      <c r="B2188" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2188" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2188" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2188" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2188" t="n">
+        <v>129.09</v>
+      </c>
+      <c r="G2188" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H2188" s="2" t="n">
+        <v>46069.56005236259</v>
+      </c>
+    </row>
+    <row r="2189">
+      <c r="A2189" t="inlineStr">
+        <is>
+          <t>6a0f527b-8524-4a17-bc4b-450c137479f3</t>
+        </is>
+      </c>
+      <c r="B2189" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2189" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2189" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2189" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2189" t="n">
+        <v>44.79</v>
+      </c>
+      <c r="G2189" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H2189" s="2" t="n">
+        <v>46096.56005236573</v>
+      </c>
+    </row>
+    <row r="2190">
+      <c r="A2190" t="inlineStr">
+        <is>
+          <t>6627a693-06a6-4f48-841b-c476715167fc</t>
+        </is>
+      </c>
+      <c r="B2190" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2190" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2190" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2190" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2190" t="n">
+        <v>472.36</v>
+      </c>
+      <c r="G2190" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="H2190" s="2" t="n">
+        <v>46072.56005236888</v>
+      </c>
+    </row>
+    <row r="2191">
+      <c r="A2191" t="inlineStr">
+        <is>
+          <t>962c29b4-116b-47b5-adfe-28a3b38a7296</t>
+        </is>
+      </c>
+      <c r="B2191" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2191" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2191" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2191" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2191" t="n">
+        <v>257.6</v>
+      </c>
+      <c r="G2191" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H2191" s="2" t="n">
+        <v>46068.56005237241</v>
+      </c>
+    </row>
+    <row r="2192">
+      <c r="A2192" t="inlineStr">
+        <is>
+          <t>9d7fa90b-a2ca-4fff-93eb-8429e527391a</t>
+        </is>
+      </c>
+      <c r="B2192" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2192" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2192" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2192" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2192" t="n">
+        <v>80.69</v>
+      </c>
+      <c r="G2192" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H2192" s="2" t="n">
+        <v>46079.56005237543</v>
+      </c>
+    </row>
+    <row r="2193">
+      <c r="A2193" t="inlineStr">
+        <is>
+          <t>9c449c6f-7073-437b-b1f2-bcdcb8fbe8f1</t>
+        </is>
+      </c>
+      <c r="B2193" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2193" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2193" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2193" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2193" t="n">
+        <v>322.74</v>
+      </c>
+      <c r="G2193" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="H2193" s="2" t="n">
+        <v>46079.56005237865</v>
+      </c>
+    </row>
+    <row r="2194">
+      <c r="A2194" t="inlineStr">
+        <is>
+          <t>57d8ee59-3eb9-4381-aaa2-3d860f57da71</t>
+        </is>
+      </c>
+      <c r="B2194" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2194" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2194" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2194" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2194" t="n">
+        <v>196.44</v>
+      </c>
+      <c r="G2194" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H2194" s="2" t="n">
+        <v>46080.56005238189</v>
+      </c>
+    </row>
+    <row r="2195">
+      <c r="A2195" t="inlineStr">
+        <is>
+          <t>85b67000-0b57-4af6-b18c-fb83c8374daa</t>
+        </is>
+      </c>
+      <c r="B2195" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2195" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2195" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2195" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2195" t="n">
+        <v>242.13</v>
+      </c>
+      <c r="G2195" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H2195" s="2" t="n">
+        <v>46069.56005238499</v>
+      </c>
+    </row>
+    <row r="2196">
+      <c r="A2196" t="inlineStr">
+        <is>
+          <t>d591c8d5-46b3-464b-a8ac-272c65cbfaaa</t>
+        </is>
+      </c>
+      <c r="B2196" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2196" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2196" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2196" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2196" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="G2196" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H2196" s="2" t="n">
+        <v>46087.56005238809</v>
+      </c>
+    </row>
+    <row r="2197">
+      <c r="A2197" t="inlineStr">
+        <is>
+          <t>b8798517-0e00-4cad-9f45-fdb12b97816d</t>
+        </is>
+      </c>
+      <c r="B2197" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2197" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2197" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2197" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2197" t="n">
+        <v>226.93</v>
+      </c>
+      <c r="G2197" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="H2197" s="2" t="n">
+        <v>46078.56005239124</v>
+      </c>
+    </row>
+    <row r="2198">
+      <c r="A2198" t="inlineStr">
+        <is>
+          <t>131d55b8-2775-40df-b5b0-aa18edb79bb9</t>
+        </is>
+      </c>
+      <c r="B2198" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2198" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2198" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2198" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2198" t="n">
+        <v>208.49</v>
+      </c>
+      <c r="G2198" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H2198" s="2" t="n">
+        <v>46086.5600523947</v>
+      </c>
+    </row>
+    <row r="2199">
+      <c r="A2199" t="inlineStr">
+        <is>
+          <t>45e8137a-db7a-45c6-baaa-31b6dd0062f5</t>
+        </is>
+      </c>
+      <c r="B2199" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2199" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2199" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2199" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2199" t="n">
+        <v>302.39</v>
+      </c>
+      <c r="G2199" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="H2199" s="2" t="n">
+        <v>46088.56005239791</v>
+      </c>
+    </row>
+    <row r="2200">
+      <c r="A2200" t="inlineStr">
+        <is>
+          <t>aff41e1b-d7d8-47ef-a566-16669b8cd752</t>
+        </is>
+      </c>
+      <c r="B2200" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2200" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2200" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2200" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2200" t="n">
+        <v>116.27</v>
+      </c>
+      <c r="G2200" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H2200" s="2" t="n">
+        <v>46089.56005240107</v>
+      </c>
+    </row>
+    <row r="2201">
+      <c r="A2201" t="inlineStr">
+        <is>
+          <t>3fedc851-a523-4e5d-b99c-c764cb4d9f9c</t>
+        </is>
+      </c>
+      <c r="B2201" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2201" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2201" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2201" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2201" t="n">
+        <v>142.88</v>
+      </c>
+      <c r="G2201" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H2201" s="2" t="n">
+        <v>46069.56005240422</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2201"/>
+  <dimension ref="A1:H2251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73605,7 +73605,7 @@
         <v>3.8</v>
       </c>
       <c r="H2152" s="2" t="n">
-        <v>46078.56005224503</v>
+        <v>46078.56005224537</v>
       </c>
     </row>
     <row r="2153">
@@ -73639,7 +73639,7 @@
         <v>2.91</v>
       </c>
       <c r="H2153" s="2" t="n">
-        <v>46081.56005224938</v>
+        <v>46081.56005224537</v>
       </c>
     </row>
     <row r="2154">
@@ -73673,7 +73673,7 @@
         <v>4.51</v>
       </c>
       <c r="H2154" s="2" t="n">
-        <v>46090.56005225271</v>
+        <v>46090.56005225694</v>
       </c>
     </row>
     <row r="2155">
@@ -73707,7 +73707,7 @@
         <v>4.4</v>
       </c>
       <c r="H2155" s="2" t="n">
-        <v>46096.56005225634</v>
+        <v>46096.56005225694</v>
       </c>
     </row>
     <row r="2156">
@@ -73741,7 +73741,7 @@
         <v>4.98</v>
       </c>
       <c r="H2156" s="2" t="n">
-        <v>46094.56005225951</v>
+        <v>46094.56005225694</v>
       </c>
     </row>
     <row r="2157">
@@ -73775,7 +73775,7 @@
         <v>1.65</v>
       </c>
       <c r="H2157" s="2" t="n">
-        <v>46075.56005226282</v>
+        <v>46075.56005226852</v>
       </c>
     </row>
     <row r="2158">
@@ -73809,7 +73809,7 @@
         <v>3.95</v>
       </c>
       <c r="H2158" s="2" t="n">
-        <v>46083.56005226635</v>
+        <v>46083.56005226852</v>
       </c>
     </row>
     <row r="2159">
@@ -73843,7 +73843,7 @@
         <v>4.15</v>
       </c>
       <c r="H2159" s="2" t="n">
-        <v>46087.56005226964</v>
+        <v>46087.56005226852</v>
       </c>
     </row>
     <row r="2160">
@@ -73877,7 +73877,7 @@
         <v>3.4</v>
       </c>
       <c r="H2160" s="2" t="n">
-        <v>46072.56005227272</v>
+        <v>46072.56005226852</v>
       </c>
     </row>
     <row r="2161">
@@ -73911,7 +73911,7 @@
         <v>3.96</v>
       </c>
       <c r="H2161" s="2" t="n">
-        <v>46084.56005227612</v>
+        <v>46084.5600522801</v>
       </c>
     </row>
     <row r="2162">
@@ -73945,7 +73945,7 @@
         <v>2.47</v>
       </c>
       <c r="H2162" s="2" t="n">
-        <v>46090.56005227967</v>
+        <v>46090.5600522801</v>
       </c>
     </row>
     <row r="2163">
@@ -73979,7 +73979,7 @@
         <v>4.01</v>
       </c>
       <c r="H2163" s="2" t="n">
-        <v>46078.5600522829</v>
+        <v>46078.5600522801</v>
       </c>
     </row>
     <row r="2164">
@@ -74013,7 +74013,7 @@
         <v>0.7</v>
       </c>
       <c r="H2164" s="2" t="n">
-        <v>46077.56005228612</v>
+        <v>46077.56005229166</v>
       </c>
     </row>
     <row r="2165">
@@ -74047,7 +74047,7 @@
         <v>2.57</v>
       </c>
       <c r="H2165" s="2" t="n">
-        <v>46083.56005228934</v>
+        <v>46083.56005229166</v>
       </c>
     </row>
     <row r="2166">
@@ -74081,7 +74081,7 @@
         <v>1.69</v>
       </c>
       <c r="H2166" s="2" t="n">
-        <v>46096.56005229243</v>
+        <v>46096.56005229166</v>
       </c>
     </row>
     <row r="2167">
@@ -74115,7 +74115,7 @@
         <v>2.38</v>
       </c>
       <c r="H2167" s="2" t="n">
-        <v>46076.56005229554</v>
+        <v>46076.56005229166</v>
       </c>
     </row>
     <row r="2168">
@@ -74149,7 +74149,7 @@
         <v>2.52</v>
       </c>
       <c r="H2168" s="2" t="n">
-        <v>46095.56005229862</v>
+        <v>46095.56005230324</v>
       </c>
     </row>
     <row r="2169">
@@ -74183,7 +74183,7 @@
         <v>3.12</v>
       </c>
       <c r="H2169" s="2" t="n">
-        <v>46076.56005230208</v>
+        <v>46076.56005230324</v>
       </c>
     </row>
     <row r="2170">
@@ -74217,7 +74217,7 @@
         <v>3.4</v>
       </c>
       <c r="H2170" s="2" t="n">
-        <v>46090.56005230531</v>
+        <v>46090.56005230324</v>
       </c>
     </row>
     <row r="2171">
@@ -74251,7 +74251,7 @@
         <v>3.68</v>
       </c>
       <c r="H2171" s="2" t="n">
-        <v>46094.56005230843</v>
+        <v>46094.56005230324</v>
       </c>
     </row>
     <row r="2172">
@@ -74285,7 +74285,7 @@
         <v>2.29</v>
       </c>
       <c r="H2172" s="2" t="n">
-        <v>46076.56005231145</v>
+        <v>46076.56005231482</v>
       </c>
     </row>
     <row r="2173">
@@ -74319,7 +74319,7 @@
         <v>1.6</v>
       </c>
       <c r="H2173" s="2" t="n">
-        <v>46083.56005231472</v>
+        <v>46083.56005231482</v>
       </c>
     </row>
     <row r="2174">
@@ -74353,7 +74353,7 @@
         <v>2.47</v>
       </c>
       <c r="H2174" s="2" t="n">
-        <v>46084.560052318</v>
+        <v>46084.56005231482</v>
       </c>
     </row>
     <row r="2175">
@@ -74387,7 +74387,7 @@
         <v>1.93</v>
       </c>
       <c r="H2175" s="2" t="n">
-        <v>46084.56005232113</v>
+        <v>46084.56005232639</v>
       </c>
     </row>
     <row r="2176">
@@ -74421,7 +74421,7 @@
         <v>2.57</v>
       </c>
       <c r="H2176" s="2" t="n">
-        <v>46093.56005232433</v>
+        <v>46093.56005232639</v>
       </c>
     </row>
     <row r="2177">
@@ -74455,7 +74455,7 @@
         <v>2.33</v>
       </c>
       <c r="H2177" s="2" t="n">
-        <v>46070.56005232743</v>
+        <v>46070.56005232639</v>
       </c>
     </row>
     <row r="2178">
@@ -74489,7 +74489,7 @@
         <v>2.52</v>
       </c>
       <c r="H2178" s="2" t="n">
-        <v>46090.56005233061</v>
+        <v>46090.56005232639</v>
       </c>
     </row>
     <row r="2179">
@@ -74523,7 +74523,7 @@
         <v>1.99</v>
       </c>
       <c r="H2179" s="2" t="n">
-        <v>46095.56005233381</v>
+        <v>46095.56005233796</v>
       </c>
     </row>
     <row r="2180">
@@ -74557,7 +74557,7 @@
         <v>3.19</v>
       </c>
       <c r="H2180" s="2" t="n">
-        <v>46075.560052337</v>
+        <v>46075.56005233796</v>
       </c>
     </row>
     <row r="2181">
@@ -74591,7 +74591,7 @@
         <v>2.4</v>
       </c>
       <c r="H2181" s="2" t="n">
-        <v>46080.56005234009</v>
+        <v>46080.56005233796</v>
       </c>
     </row>
     <row r="2182">
@@ -74625,7 +74625,7 @@
         <v>3.82</v>
       </c>
       <c r="H2182" s="2" t="n">
-        <v>46074.56005234329</v>
+        <v>46074.56005233796</v>
       </c>
     </row>
     <row r="2183">
@@ -74659,7 +74659,7 @@
         <v>4.82</v>
       </c>
       <c r="H2183" s="2" t="n">
-        <v>46074.56005234642</v>
+        <v>46074.56005234954</v>
       </c>
     </row>
     <row r="2184">
@@ -74693,7 +74693,7 @@
         <v>1.02</v>
       </c>
       <c r="H2184" s="2" t="n">
-        <v>46080.56005235016</v>
+        <v>46080.56005234954</v>
       </c>
     </row>
     <row r="2185">
@@ -74727,7 +74727,7 @@
         <v>2.51</v>
       </c>
       <c r="H2185" s="2" t="n">
-        <v>46087.56005235326</v>
+        <v>46087.56005234954</v>
       </c>
     </row>
     <row r="2186">
@@ -74761,7 +74761,7 @@
         <v>4.93</v>
       </c>
       <c r="H2186" s="2" t="n">
-        <v>46093.5600523563</v>
+        <v>46093.56005236111</v>
       </c>
     </row>
     <row r="2187">
@@ -74795,7 +74795,7 @@
         <v>1.48</v>
       </c>
       <c r="H2187" s="2" t="n">
-        <v>46073.56005235959</v>
+        <v>46073.56005236111</v>
       </c>
     </row>
     <row r="2188">
@@ -74829,7 +74829,7 @@
         <v>1.29</v>
       </c>
       <c r="H2188" s="2" t="n">
-        <v>46069.56005236259</v>
+        <v>46069.56005236111</v>
       </c>
     </row>
     <row r="2189">
@@ -74863,7 +74863,7 @@
         <v>0.45</v>
       </c>
       <c r="H2189" s="2" t="n">
-        <v>46096.56005236573</v>
+        <v>46096.56005236111</v>
       </c>
     </row>
     <row r="2190">
@@ -74897,7 +74897,7 @@
         <v>4.72</v>
       </c>
       <c r="H2190" s="2" t="n">
-        <v>46072.56005236888</v>
+        <v>46072.56005237268</v>
       </c>
     </row>
     <row r="2191">
@@ -74931,7 +74931,7 @@
         <v>2.58</v>
       </c>
       <c r="H2191" s="2" t="n">
-        <v>46068.56005237241</v>
+        <v>46068.56005237268</v>
       </c>
     </row>
     <row r="2192">
@@ -74965,7 +74965,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H2192" s="2" t="n">
-        <v>46079.56005237543</v>
+        <v>46079.56005237268</v>
       </c>
     </row>
     <row r="2193">
@@ -74999,7 +74999,7 @@
         <v>3.23</v>
       </c>
       <c r="H2193" s="2" t="n">
-        <v>46079.56005237865</v>
+        <v>46079.56005238426</v>
       </c>
     </row>
     <row r="2194">
@@ -75033,7 +75033,7 @@
         <v>1.96</v>
       </c>
       <c r="H2194" s="2" t="n">
-        <v>46080.56005238189</v>
+        <v>46080.56005238426</v>
       </c>
     </row>
     <row r="2195">
@@ -75067,7 +75067,7 @@
         <v>2.42</v>
       </c>
       <c r="H2195" s="2" t="n">
-        <v>46069.56005238499</v>
+        <v>46069.56005238426</v>
       </c>
     </row>
     <row r="2196">
@@ -75101,7 +75101,7 @@
         <v>0.17</v>
       </c>
       <c r="H2196" s="2" t="n">
-        <v>46087.56005238809</v>
+        <v>46087.56005238426</v>
       </c>
     </row>
     <row r="2197">
@@ -75135,7 +75135,7 @@
         <v>2.27</v>
       </c>
       <c r="H2197" s="2" t="n">
-        <v>46078.56005239124</v>
+        <v>46078.56005239583</v>
       </c>
     </row>
     <row r="2198">
@@ -75169,7 +75169,7 @@
         <v>2.08</v>
       </c>
       <c r="H2198" s="2" t="n">
-        <v>46086.5600523947</v>
+        <v>46086.56005239583</v>
       </c>
     </row>
     <row r="2199">
@@ -75203,7 +75203,7 @@
         <v>3.02</v>
       </c>
       <c r="H2199" s="2" t="n">
-        <v>46088.56005239791</v>
+        <v>46088.56005239583</v>
       </c>
     </row>
     <row r="2200">
@@ -75237,7 +75237,7 @@
         <v>1.16</v>
       </c>
       <c r="H2200" s="2" t="n">
-        <v>46089.56005240107</v>
+        <v>46089.56005239583</v>
       </c>
     </row>
     <row r="2201">
@@ -75271,7 +75271,1707 @@
         <v>1.43</v>
       </c>
       <c r="H2201" s="2" t="n">
-        <v>46069.56005240422</v>
+        <v>46069.56005240741</v>
+      </c>
+    </row>
+    <row r="2202">
+      <c r="A2202" t="inlineStr">
+        <is>
+          <t>a6a56a03-06c3-4bfe-8aca-9b714404dff0</t>
+        </is>
+      </c>
+      <c r="B2202" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2202" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2202" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2202" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2202" t="n">
+        <v>331.66</v>
+      </c>
+      <c r="G2202" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="H2202" s="2" t="n">
+        <v>46093.57448887372</v>
+      </c>
+    </row>
+    <row r="2203">
+      <c r="A2203" t="inlineStr">
+        <is>
+          <t>cc1d5d90-aee6-4a6b-9996-673237cea8ab</t>
+        </is>
+      </c>
+      <c r="B2203" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2203" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2203" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2203" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2203" t="n">
+        <v>47.67</v>
+      </c>
+      <c r="G2203" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H2203" s="2" t="n">
+        <v>46086.57448887834</v>
+      </c>
+    </row>
+    <row r="2204">
+      <c r="A2204" t="inlineStr">
+        <is>
+          <t>4a8cddd7-032e-4e8e-aa75-164c89d54741</t>
+        </is>
+      </c>
+      <c r="B2204" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2204" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2204" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2204" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2204" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="G2204" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H2204" s="2" t="n">
+        <v>46089.57448888168</v>
+      </c>
+    </row>
+    <row r="2205">
+      <c r="A2205" t="inlineStr">
+        <is>
+          <t>5ce527de-483c-4513-9666-9a95418f48f1</t>
+        </is>
+      </c>
+      <c r="B2205" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2205" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2205" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2205" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2205" t="n">
+        <v>416.9</v>
+      </c>
+      <c r="G2205" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="H2205" s="2" t="n">
+        <v>46096.57448888473</v>
+      </c>
+    </row>
+    <row r="2206">
+      <c r="A2206" t="inlineStr">
+        <is>
+          <t>be6452a8-e25d-4d3b-a7fa-fbebbebb9652</t>
+        </is>
+      </c>
+      <c r="B2206" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2206" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2206" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2206" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2206" t="n">
+        <v>484.99</v>
+      </c>
+      <c r="G2206" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="H2206" s="2" t="n">
+        <v>46088.57448888817</v>
+      </c>
+    </row>
+    <row r="2207">
+      <c r="A2207" t="inlineStr">
+        <is>
+          <t>9f2a6347-be91-4b5f-ab1e-72c101cea58d</t>
+        </is>
+      </c>
+      <c r="B2207" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2207" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2207" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2207" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2207" t="n">
+        <v>388.87</v>
+      </c>
+      <c r="G2207" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="H2207" s="2" t="n">
+        <v>46078.57448889134</v>
+      </c>
+    </row>
+    <row r="2208">
+      <c r="A2208" t="inlineStr">
+        <is>
+          <t>c0b80b94-eb35-4bfa-ae40-caf734a08fad</t>
+        </is>
+      </c>
+      <c r="B2208" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2208" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2208" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2208" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2208" t="n">
+        <v>350.17</v>
+      </c>
+      <c r="G2208" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H2208" s="2" t="n">
+        <v>46071.5744888945</v>
+      </c>
+    </row>
+    <row r="2209">
+      <c r="A2209" t="inlineStr">
+        <is>
+          <t>7fcc7b05-587f-4da6-81ba-a8fd1b020f1e</t>
+        </is>
+      </c>
+      <c r="B2209" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2209" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2209" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2209" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2209" t="n">
+        <v>281.44</v>
+      </c>
+      <c r="G2209" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="H2209" s="2" t="n">
+        <v>46085.57448889762</v>
+      </c>
+    </row>
+    <row r="2210">
+      <c r="A2210" t="inlineStr">
+        <is>
+          <t>c0a24de4-147c-4d97-960d-9084fc5ae26c</t>
+        </is>
+      </c>
+      <c r="B2210" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2210" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2210" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2210" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2210" t="n">
+        <v>254.27</v>
+      </c>
+      <c r="G2210" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H2210" s="2" t="n">
+        <v>46092.57448890113</v>
+      </c>
+    </row>
+    <row r="2211">
+      <c r="A2211" t="inlineStr">
+        <is>
+          <t>9b58a981-9e96-43cb-9891-57409e042347</t>
+        </is>
+      </c>
+      <c r="B2211" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2211" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2211" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2211" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2211" t="n">
+        <v>212.91</v>
+      </c>
+      <c r="G2211" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="H2211" s="2" t="n">
+        <v>46084.57448890415</v>
+      </c>
+    </row>
+    <row r="2212">
+      <c r="A2212" t="inlineStr">
+        <is>
+          <t>ca61044f-7eb9-4396-8860-7ad4c5667b97</t>
+        </is>
+      </c>
+      <c r="B2212" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2212" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2212" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2212" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2212" t="n">
+        <v>64.87</v>
+      </c>
+      <c r="G2212" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H2212" s="2" t="n">
+        <v>46082.57448890735</v>
+      </c>
+    </row>
+    <row r="2213">
+      <c r="A2213" t="inlineStr">
+        <is>
+          <t>882a6ceb-d3c0-4276-bf00-06882b13ffb2</t>
+        </is>
+      </c>
+      <c r="B2213" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2213" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2213" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2213" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2213" t="n">
+        <v>172.82</v>
+      </c>
+      <c r="G2213" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H2213" s="2" t="n">
+        <v>46067.57448891052</v>
+      </c>
+    </row>
+    <row r="2214">
+      <c r="A2214" t="inlineStr">
+        <is>
+          <t>f6dc9631-41f9-475f-bb4a-a1cda238dcab</t>
+        </is>
+      </c>
+      <c r="B2214" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2214" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2214" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2214" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2214" t="n">
+        <v>398.86</v>
+      </c>
+      <c r="G2214" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="H2214" s="2" t="n">
+        <v>46085.57448891387</v>
+      </c>
+    </row>
+    <row r="2215">
+      <c r="A2215" t="inlineStr">
+        <is>
+          <t>59769b1d-532c-45a9-955e-28d334e4a218</t>
+        </is>
+      </c>
+      <c r="B2215" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2215" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2215" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2215" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2215" t="n">
+        <v>20.07</v>
+      </c>
+      <c r="G2215" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2215" s="2" t="n">
+        <v>46096.57448891697</v>
+      </c>
+    </row>
+    <row r="2216">
+      <c r="A2216" t="inlineStr">
+        <is>
+          <t>20114673-a31f-435f-8e70-2fa4d61566f3</t>
+        </is>
+      </c>
+      <c r="B2216" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2216" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2216" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2216" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2216" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="G2216" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H2216" s="2" t="n">
+        <v>46085.57448891998</v>
+      </c>
+    </row>
+    <row r="2217">
+      <c r="A2217" t="inlineStr">
+        <is>
+          <t>fe9a2ca4-2d73-48e5-8338-3991812ba0a1</t>
+        </is>
+      </c>
+      <c r="B2217" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2217" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2217" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2217" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2217" t="n">
+        <v>283.94</v>
+      </c>
+      <c r="G2217" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="H2217" s="2" t="n">
+        <v>46080.57448892356</v>
+      </c>
+    </row>
+    <row r="2218">
+      <c r="A2218" t="inlineStr">
+        <is>
+          <t>b9952a85-8881-43d7-b7f5-6bec6f0293ec</t>
+        </is>
+      </c>
+      <c r="B2218" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2218" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2218" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2218" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2218" t="n">
+        <v>90</v>
+      </c>
+      <c r="G2218" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H2218" s="2" t="n">
+        <v>46083.57448892664</v>
+      </c>
+    </row>
+    <row r="2219">
+      <c r="A2219" t="inlineStr">
+        <is>
+          <t>c7cf03fa-3f3d-4d1d-8ffd-93fe15d49bc3</t>
+        </is>
+      </c>
+      <c r="B2219" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2219" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2219" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2219" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2219" t="n">
+        <v>94.02</v>
+      </c>
+      <c r="G2219" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H2219" s="2" t="n">
+        <v>46083.57448892963</v>
+      </c>
+    </row>
+    <row r="2220">
+      <c r="A2220" t="inlineStr">
+        <is>
+          <t>e9f7990b-9aed-4e10-89b1-800ee13c7b4b</t>
+        </is>
+      </c>
+      <c r="B2220" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2220" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2220" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2220" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2220" t="n">
+        <v>311.25</v>
+      </c>
+      <c r="G2220" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="H2220" s="2" t="n">
+        <v>46073.57448893273</v>
+      </c>
+    </row>
+    <row r="2221">
+      <c r="A2221" t="inlineStr">
+        <is>
+          <t>c0966a42-eb7b-4f1b-a105-b33e17193f58</t>
+        </is>
+      </c>
+      <c r="B2221" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2221" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2221" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2221" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2221" t="n">
+        <v>333.93</v>
+      </c>
+      <c r="G2221" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="H2221" s="2" t="n">
+        <v>46082.57448893604</v>
+      </c>
+    </row>
+    <row r="2222">
+      <c r="A2222" t="inlineStr">
+        <is>
+          <t>f2a83d93-a575-472c-8687-85b14b3a762c</t>
+        </is>
+      </c>
+      <c r="B2222" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2222" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2222" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2222" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2222" t="n">
+        <v>82.92</v>
+      </c>
+      <c r="G2222" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H2222" s="2" t="n">
+        <v>46088.57448893908</v>
+      </c>
+    </row>
+    <row r="2223">
+      <c r="A2223" t="inlineStr">
+        <is>
+          <t>a146d35c-4fb1-4f8d-8480-39fb8b87fd6b</t>
+        </is>
+      </c>
+      <c r="B2223" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2223" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2223" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2223" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2223" t="n">
+        <v>84.65000000000001</v>
+      </c>
+      <c r="G2223" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H2223" s="2" t="n">
+        <v>46084.57448894222</v>
+      </c>
+    </row>
+    <row r="2224">
+      <c r="A2224" t="inlineStr">
+        <is>
+          <t>bc6dbf78-8d60-499b-95f7-2034d99dc304</t>
+        </is>
+      </c>
+      <c r="B2224" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2224" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2224" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2224" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2224" t="n">
+        <v>496.53</v>
+      </c>
+      <c r="G2224" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="H2224" s="2" t="n">
+        <v>46069.57448894528</v>
+      </c>
+    </row>
+    <row r="2225">
+      <c r="A2225" t="inlineStr">
+        <is>
+          <t>cc254c37-32a7-4215-9933-cab26199c795</t>
+        </is>
+      </c>
+      <c r="B2225" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2225" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2225" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2225" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2225" t="n">
+        <v>314.36</v>
+      </c>
+      <c r="G2225" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H2225" s="2" t="n">
+        <v>46093.57448894853</v>
+      </c>
+    </row>
+    <row r="2226">
+      <c r="A2226" t="inlineStr">
+        <is>
+          <t>611b19a9-c093-4ffd-b178-a68fef68637e</t>
+        </is>
+      </c>
+      <c r="B2226" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2226" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2226" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2226" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2226" t="n">
+        <v>455.1</v>
+      </c>
+      <c r="G2226" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="H2226" s="2" t="n">
+        <v>46086.57448895169</v>
+      </c>
+    </row>
+    <row r="2227">
+      <c r="A2227" t="inlineStr">
+        <is>
+          <t>9b1cbf10-2f87-4950-a83e-2e0d1d40caf5</t>
+        </is>
+      </c>
+      <c r="B2227" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2227" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2227" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2227" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2227" t="n">
+        <v>282.24</v>
+      </c>
+      <c r="G2227" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H2227" s="2" t="n">
+        <v>46091.57448895492</v>
+      </c>
+    </row>
+    <row r="2228">
+      <c r="A2228" t="inlineStr">
+        <is>
+          <t>88d498f3-188e-48f5-ab00-7a55c3619c29</t>
+        </is>
+      </c>
+      <c r="B2228" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2228" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2228" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2228" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2228" t="n">
+        <v>66.73</v>
+      </c>
+      <c r="G2228" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H2228" s="2" t="n">
+        <v>46083.57448895824</v>
+      </c>
+    </row>
+    <row r="2229">
+      <c r="A2229" t="inlineStr">
+        <is>
+          <t>2c7ff9a6-1a2a-426e-9d35-b2b91ccbfabc</t>
+        </is>
+      </c>
+      <c r="B2229" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2229" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2229" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2229" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2229" t="n">
+        <v>74.68000000000001</v>
+      </c>
+      <c r="G2229" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H2229" s="2" t="n">
+        <v>46090.5744889613</v>
+      </c>
+    </row>
+    <row r="2230">
+      <c r="A2230" t="inlineStr">
+        <is>
+          <t>d0791acc-7bd5-4420-8f7a-6e862678192c</t>
+        </is>
+      </c>
+      <c r="B2230" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2230" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2230" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2230" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2230" t="n">
+        <v>133.62</v>
+      </c>
+      <c r="G2230" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="H2230" s="2" t="n">
+        <v>46076.57448896424</v>
+      </c>
+    </row>
+    <row r="2231">
+      <c r="A2231" t="inlineStr">
+        <is>
+          <t>e23985ed-6e76-48b7-9f7b-2f7895327f91</t>
+        </is>
+      </c>
+      <c r="B2231" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2231" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2231" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2231" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2231" t="n">
+        <v>303.49</v>
+      </c>
+      <c r="G2231" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="H2231" s="2" t="n">
+        <v>46071.57448896733</v>
+      </c>
+    </row>
+    <row r="2232">
+      <c r="A2232" t="inlineStr">
+        <is>
+          <t>2f902437-f306-41dd-9ed8-2eea15ef9c0a</t>
+        </is>
+      </c>
+      <c r="B2232" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2232" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2232" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2232" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2232" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="G2232" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H2232" s="2" t="n">
+        <v>46084.5744889709</v>
+      </c>
+    </row>
+    <row r="2233">
+      <c r="A2233" t="inlineStr">
+        <is>
+          <t>94b08b9d-b525-44c5-b2cf-73eae30a0a88</t>
+        </is>
+      </c>
+      <c r="B2233" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2233" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2233" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2233" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2233" t="n">
+        <v>391.26</v>
+      </c>
+      <c r="G2233" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="H2233" s="2" t="n">
+        <v>46082.57448897407</v>
+      </c>
+    </row>
+    <row r="2234">
+      <c r="A2234" t="inlineStr">
+        <is>
+          <t>b81e49cf-60e2-47d0-aa2d-5ca55b8433df</t>
+        </is>
+      </c>
+      <c r="B2234" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2234" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2234" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2234" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2234" t="n">
+        <v>275.37</v>
+      </c>
+      <c r="G2234" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H2234" s="2" t="n">
+        <v>46075.57448897714</v>
+      </c>
+    </row>
+    <row r="2235">
+      <c r="A2235" t="inlineStr">
+        <is>
+          <t>502b9740-dc11-4dc6-876b-02c85ec6dd3a</t>
+        </is>
+      </c>
+      <c r="B2235" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2235" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2235" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2235" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2235" t="n">
+        <v>411.26</v>
+      </c>
+      <c r="G2235" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="H2235" s="2" t="n">
+        <v>46069.57448898017</v>
+      </c>
+    </row>
+    <row r="2236">
+      <c r="A2236" t="inlineStr">
+        <is>
+          <t>59305006-2161-48d9-b539-cafa7636fdd1</t>
+        </is>
+      </c>
+      <c r="B2236" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2236" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2236" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2236" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2236" t="n">
+        <v>127.57</v>
+      </c>
+      <c r="G2236" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="H2236" s="2" t="n">
+        <v>46079.57448898367</v>
+      </c>
+    </row>
+    <row r="2237">
+      <c r="A2237" t="inlineStr">
+        <is>
+          <t>0bb97304-1907-48bb-8082-2144fd65146f</t>
+        </is>
+      </c>
+      <c r="B2237" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2237" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2237" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2237" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2237" t="n">
+        <v>336.5</v>
+      </c>
+      <c r="G2237" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="H2237" s="2" t="n">
+        <v>46088.57448898679</v>
+      </c>
+    </row>
+    <row r="2238">
+      <c r="A2238" t="inlineStr">
+        <is>
+          <t>690d562f-c32a-4085-92e4-b8b9cd927681</t>
+        </is>
+      </c>
+      <c r="B2238" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2238" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2238" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2238" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2238" t="n">
+        <v>123.97</v>
+      </c>
+      <c r="G2238" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="H2238" s="2" t="n">
+        <v>46094.57448898983</v>
+      </c>
+    </row>
+    <row r="2239">
+      <c r="A2239" t="inlineStr">
+        <is>
+          <t>9d05e077-dcfb-4ed8-9da6-81f8a32d888d</t>
+        </is>
+      </c>
+      <c r="B2239" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2239" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2239" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2239" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2239" t="n">
+        <v>329.05</v>
+      </c>
+      <c r="G2239" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="H2239" s="2" t="n">
+        <v>46094.57448899312</v>
+      </c>
+    </row>
+    <row r="2240">
+      <c r="A2240" t="inlineStr">
+        <is>
+          <t>230b58c7-18c0-453d-871a-c02554970658</t>
+        </is>
+      </c>
+      <c r="B2240" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2240" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2240" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2240" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2240" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="G2240" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H2240" s="2" t="n">
+        <v>46074.57448899616</v>
+      </c>
+    </row>
+    <row r="2241">
+      <c r="A2241" t="inlineStr">
+        <is>
+          <t>0c7f0f25-f5ae-45b1-a8c0-eb76c62c243a</t>
+        </is>
+      </c>
+      <c r="B2241" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2241" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2241" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2241" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2241" t="n">
+        <v>395.96</v>
+      </c>
+      <c r="G2241" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="H2241" s="2" t="n">
+        <v>46078.57448899923</v>
+      </c>
+    </row>
+    <row r="2242">
+      <c r="A2242" t="inlineStr">
+        <is>
+          <t>5dd85d62-a5b9-4f29-b707-5e09b58b5805</t>
+        </is>
+      </c>
+      <c r="B2242" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2242" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2242" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2242" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2242" t="n">
+        <v>432.2</v>
+      </c>
+      <c r="G2242" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="H2242" s="2" t="n">
+        <v>46076.57448900221</v>
+      </c>
+    </row>
+    <row r="2243">
+      <c r="A2243" t="inlineStr">
+        <is>
+          <t>8a0c8bc5-a9f5-499b-bfbc-c6c2c2b2fb5d</t>
+        </is>
+      </c>
+      <c r="B2243" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2243" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2243" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2243" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2243" t="n">
+        <v>342.23</v>
+      </c>
+      <c r="G2243" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="H2243" s="2" t="n">
+        <v>46095.57448900551</v>
+      </c>
+    </row>
+    <row r="2244">
+      <c r="A2244" t="inlineStr">
+        <is>
+          <t>7cbeb8ab-da8c-4f7f-974c-e037966170c1</t>
+        </is>
+      </c>
+      <c r="B2244" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2244" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2244" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2244" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2244" t="n">
+        <v>105.19</v>
+      </c>
+      <c r="G2244" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H2244" s="2" t="n">
+        <v>46091.57448900853</v>
+      </c>
+    </row>
+    <row r="2245">
+      <c r="A2245" t="inlineStr">
+        <is>
+          <t>1b3698df-dd78-4cf0-b965-d296c4b0a592</t>
+        </is>
+      </c>
+      <c r="B2245" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2245" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2245" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2245" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2245" t="n">
+        <v>424.57</v>
+      </c>
+      <c r="G2245" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="H2245" s="2" t="n">
+        <v>46069.57448901156</v>
+      </c>
+    </row>
+    <row r="2246">
+      <c r="A2246" t="inlineStr">
+        <is>
+          <t>5df3bc08-50e8-4b24-96c8-18a314dc764d</t>
+        </is>
+      </c>
+      <c r="B2246" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2246" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2246" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2246" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2246" t="n">
+        <v>327.72</v>
+      </c>
+      <c r="G2246" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="H2246" s="2" t="n">
+        <v>46077.57448901462</v>
+      </c>
+    </row>
+    <row r="2247">
+      <c r="A2247" t="inlineStr">
+        <is>
+          <t>3022ebb8-e23b-48dc-8819-a36a1b869203</t>
+        </is>
+      </c>
+      <c r="B2247" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2247" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2247" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2247" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2247" t="n">
+        <v>405.26</v>
+      </c>
+      <c r="G2247" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="H2247" s="2" t="n">
+        <v>46092.57448901793</v>
+      </c>
+    </row>
+    <row r="2248">
+      <c r="A2248" t="inlineStr">
+        <is>
+          <t>e9a9243d-86f5-4dd6-8747-95957fd6c3bf</t>
+        </is>
+      </c>
+      <c r="B2248" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2248" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2248" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2248" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2248" t="n">
+        <v>284.12</v>
+      </c>
+      <c r="G2248" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="H2248" s="2" t="n">
+        <v>46086.57448902094</v>
+      </c>
+    </row>
+    <row r="2249">
+      <c r="A2249" t="inlineStr">
+        <is>
+          <t>d02ae433-8212-49f1-9082-085710e25e7d</t>
+        </is>
+      </c>
+      <c r="B2249" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2249" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2249" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2249" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2249" t="n">
+        <v>61.22</v>
+      </c>
+      <c r="G2249" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H2249" s="2" t="n">
+        <v>46094.57448902421</v>
+      </c>
+    </row>
+    <row r="2250">
+      <c r="A2250" t="inlineStr">
+        <is>
+          <t>ac2d4673-09c6-4f9e-9dd5-d687ebbce9c7</t>
+        </is>
+      </c>
+      <c r="B2250" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2250" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2250" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2250" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2250" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="G2250" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H2250" s="2" t="n">
+        <v>46086.57448902742</v>
+      </c>
+    </row>
+    <row r="2251">
+      <c r="A2251" t="inlineStr">
+        <is>
+          <t>ebe5a21e-a72e-4385-aa88-2b45d7dfc91a</t>
+        </is>
+      </c>
+      <c r="B2251" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2251" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2251" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2251" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2251" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="G2251" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H2251" s="2" t="n">
+        <v>46070.57448903046</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2251"/>
+  <dimension ref="A1:H2301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75305,7 +75305,7 @@
         <v>3.32</v>
       </c>
       <c r="H2202" s="2" t="n">
-        <v>46093.57448887372</v>
+        <v>46093.57448887731</v>
       </c>
     </row>
     <row r="2203">
@@ -75339,7 +75339,7 @@
         <v>0.48</v>
       </c>
       <c r="H2203" s="2" t="n">
-        <v>46086.57448887834</v>
+        <v>46086.57448887731</v>
       </c>
     </row>
     <row r="2204">
@@ -75373,7 +75373,7 @@
         <v>1.13</v>
       </c>
       <c r="H2204" s="2" t="n">
-        <v>46089.57448888168</v>
+        <v>46089.57448887731</v>
       </c>
     </row>
     <row r="2205">
@@ -75407,7 +75407,7 @@
         <v>4.17</v>
       </c>
       <c r="H2205" s="2" t="n">
-        <v>46096.57448888473</v>
+        <v>46096.57448888889</v>
       </c>
     </row>
     <row r="2206">
@@ -75441,7 +75441,7 @@
         <v>4.85</v>
       </c>
       <c r="H2206" s="2" t="n">
-        <v>46088.57448888817</v>
+        <v>46088.57448888889</v>
       </c>
     </row>
     <row r="2207">
@@ -75475,7 +75475,7 @@
         <v>3.89</v>
       </c>
       <c r="H2207" s="2" t="n">
-        <v>46078.57448889134</v>
+        <v>46078.57448888889</v>
       </c>
     </row>
     <row r="2208">
@@ -75509,7 +75509,7 @@
         <v>3.5</v>
       </c>
       <c r="H2208" s="2" t="n">
-        <v>46071.5744888945</v>
+        <v>46071.57448888889</v>
       </c>
     </row>
     <row r="2209">
@@ -75543,7 +75543,7 @@
         <v>2.81</v>
       </c>
       <c r="H2209" s="2" t="n">
-        <v>46085.57448889762</v>
+        <v>46085.57448890046</v>
       </c>
     </row>
     <row r="2210">
@@ -75577,7 +75577,7 @@
         <v>2.54</v>
       </c>
       <c r="H2210" s="2" t="n">
-        <v>46092.57448890113</v>
+        <v>46092.57448890046</v>
       </c>
     </row>
     <row r="2211">
@@ -75611,7 +75611,7 @@
         <v>2.13</v>
       </c>
       <c r="H2211" s="2" t="n">
-        <v>46084.57448890415</v>
+        <v>46084.57448890046</v>
       </c>
     </row>
     <row r="2212">
@@ -75645,7 +75645,7 @@
         <v>0.65</v>
       </c>
       <c r="H2212" s="2" t="n">
-        <v>46082.57448890735</v>
+        <v>46082.57448891204</v>
       </c>
     </row>
     <row r="2213">
@@ -75679,7 +75679,7 @@
         <v>1.73</v>
       </c>
       <c r="H2213" s="2" t="n">
-        <v>46067.57448891052</v>
+        <v>46067.57448891204</v>
       </c>
     </row>
     <row r="2214">
@@ -75713,7 +75713,7 @@
         <v>3.99</v>
       </c>
       <c r="H2214" s="2" t="n">
-        <v>46085.57448891387</v>
+        <v>46085.57448891204</v>
       </c>
     </row>
     <row r="2215">
@@ -75747,7 +75747,7 @@
         <v>0.2</v>
       </c>
       <c r="H2215" s="2" t="n">
-        <v>46096.57448891697</v>
+        <v>46096.57448891204</v>
       </c>
     </row>
     <row r="2216">
@@ -75781,7 +75781,7 @@
         <v>0.19</v>
       </c>
       <c r="H2216" s="2" t="n">
-        <v>46085.57448891998</v>
+        <v>46085.57448892361</v>
       </c>
     </row>
     <row r="2217">
@@ -75815,7 +75815,7 @@
         <v>2.84</v>
       </c>
       <c r="H2217" s="2" t="n">
-        <v>46080.57448892356</v>
+        <v>46080.57448892361</v>
       </c>
     </row>
     <row r="2218">
@@ -75849,7 +75849,7 @@
         <v>0.9</v>
       </c>
       <c r="H2218" s="2" t="n">
-        <v>46083.57448892664</v>
+        <v>46083.57448892361</v>
       </c>
     </row>
     <row r="2219">
@@ -75883,7 +75883,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="H2219" s="2" t="n">
-        <v>46083.57448892963</v>
+        <v>46083.57448893518</v>
       </c>
     </row>
     <row r="2220">
@@ -75917,7 +75917,7 @@
         <v>3.11</v>
       </c>
       <c r="H2220" s="2" t="n">
-        <v>46073.57448893273</v>
+        <v>46073.57448893518</v>
       </c>
     </row>
     <row r="2221">
@@ -75951,7 +75951,7 @@
         <v>3.34</v>
       </c>
       <c r="H2221" s="2" t="n">
-        <v>46082.57448893604</v>
+        <v>46082.57448893518</v>
       </c>
     </row>
     <row r="2222">
@@ -75985,7 +75985,7 @@
         <v>0.83</v>
       </c>
       <c r="H2222" s="2" t="n">
-        <v>46088.57448893908</v>
+        <v>46088.57448893518</v>
       </c>
     </row>
     <row r="2223">
@@ -76019,7 +76019,7 @@
         <v>0.85</v>
       </c>
       <c r="H2223" s="2" t="n">
-        <v>46084.57448894222</v>
+        <v>46084.57448894676</v>
       </c>
     </row>
     <row r="2224">
@@ -76053,7 +76053,7 @@
         <v>4.97</v>
       </c>
       <c r="H2224" s="2" t="n">
-        <v>46069.57448894528</v>
+        <v>46069.57448894676</v>
       </c>
     </row>
     <row r="2225">
@@ -76087,7 +76087,7 @@
         <v>3.14</v>
       </c>
       <c r="H2225" s="2" t="n">
-        <v>46093.57448894853</v>
+        <v>46093.57448894676</v>
       </c>
     </row>
     <row r="2226">
@@ -76121,7 +76121,7 @@
         <v>4.55</v>
       </c>
       <c r="H2226" s="2" t="n">
-        <v>46086.57448895169</v>
+        <v>46086.57448894676</v>
       </c>
     </row>
     <row r="2227">
@@ -76155,7 +76155,7 @@
         <v>2.82</v>
       </c>
       <c r="H2227" s="2" t="n">
-        <v>46091.57448895492</v>
+        <v>46091.57448895834</v>
       </c>
     </row>
     <row r="2228">
@@ -76189,7 +76189,7 @@
         <v>0.67</v>
       </c>
       <c r="H2228" s="2" t="n">
-        <v>46083.57448895824</v>
+        <v>46083.57448895834</v>
       </c>
     </row>
     <row r="2229">
@@ -76223,7 +76223,7 @@
         <v>0.75</v>
       </c>
       <c r="H2229" s="2" t="n">
-        <v>46090.5744889613</v>
+        <v>46090.57448895834</v>
       </c>
     </row>
     <row r="2230">
@@ -76257,7 +76257,7 @@
         <v>1.34</v>
       </c>
       <c r="H2230" s="2" t="n">
-        <v>46076.57448896424</v>
+        <v>46076.57448896991</v>
       </c>
     </row>
     <row r="2231">
@@ -76291,7 +76291,7 @@
         <v>3.03</v>
       </c>
       <c r="H2231" s="2" t="n">
-        <v>46071.57448896733</v>
+        <v>46071.57448896991</v>
       </c>
     </row>
     <row r="2232">
@@ -76325,7 +76325,7 @@
         <v>0.17</v>
       </c>
       <c r="H2232" s="2" t="n">
-        <v>46084.5744889709</v>
+        <v>46084.57448896991</v>
       </c>
     </row>
     <row r="2233">
@@ -76359,7 +76359,7 @@
         <v>3.91</v>
       </c>
       <c r="H2233" s="2" t="n">
-        <v>46082.57448897407</v>
+        <v>46082.57448896991</v>
       </c>
     </row>
     <row r="2234">
@@ -76393,7 +76393,7 @@
         <v>2.75</v>
       </c>
       <c r="H2234" s="2" t="n">
-        <v>46075.57448897714</v>
+        <v>46075.57448898148</v>
       </c>
     </row>
     <row r="2235">
@@ -76427,7 +76427,7 @@
         <v>4.11</v>
       </c>
       <c r="H2235" s="2" t="n">
-        <v>46069.57448898017</v>
+        <v>46069.57448898148</v>
       </c>
     </row>
     <row r="2236">
@@ -76461,7 +76461,7 @@
         <v>1.28</v>
       </c>
       <c r="H2236" s="2" t="n">
-        <v>46079.57448898367</v>
+        <v>46079.57448898148</v>
       </c>
     </row>
     <row r="2237">
@@ -76495,7 +76495,7 @@
         <v>3.36</v>
       </c>
       <c r="H2237" s="2" t="n">
-        <v>46088.57448898679</v>
+        <v>46088.57448898148</v>
       </c>
     </row>
     <row r="2238">
@@ -76529,7 +76529,7 @@
         <v>1.24</v>
       </c>
       <c r="H2238" s="2" t="n">
-        <v>46094.57448898983</v>
+        <v>46094.57448899306</v>
       </c>
     </row>
     <row r="2239">
@@ -76563,7 +76563,7 @@
         <v>3.29</v>
       </c>
       <c r="H2239" s="2" t="n">
-        <v>46094.57448899312</v>
+        <v>46094.57448899306</v>
       </c>
     </row>
     <row r="2240">
@@ -76597,7 +76597,7 @@
         <v>0.73</v>
       </c>
       <c r="H2240" s="2" t="n">
-        <v>46074.57448899616</v>
+        <v>46074.57448899306</v>
       </c>
     </row>
     <row r="2241">
@@ -76631,7 +76631,7 @@
         <v>3.96</v>
       </c>
       <c r="H2241" s="2" t="n">
-        <v>46078.57448899923</v>
+        <v>46078.57448900463</v>
       </c>
     </row>
     <row r="2242">
@@ -76665,7 +76665,7 @@
         <v>4.32</v>
       </c>
       <c r="H2242" s="2" t="n">
-        <v>46076.57448900221</v>
+        <v>46076.57448900463</v>
       </c>
     </row>
     <row r="2243">
@@ -76699,7 +76699,7 @@
         <v>3.42</v>
       </c>
       <c r="H2243" s="2" t="n">
-        <v>46095.57448900551</v>
+        <v>46095.57448900463</v>
       </c>
     </row>
     <row r="2244">
@@ -76733,7 +76733,7 @@
         <v>1.05</v>
       </c>
       <c r="H2244" s="2" t="n">
-        <v>46091.57448900853</v>
+        <v>46091.57448900463</v>
       </c>
     </row>
     <row r="2245">
@@ -76767,7 +76767,7 @@
         <v>4.25</v>
       </c>
       <c r="H2245" s="2" t="n">
-        <v>46069.57448901156</v>
+        <v>46069.5744890162</v>
       </c>
     </row>
     <row r="2246">
@@ -76801,7 +76801,7 @@
         <v>3.28</v>
       </c>
       <c r="H2246" s="2" t="n">
-        <v>46077.57448901462</v>
+        <v>46077.5744890162</v>
       </c>
     </row>
     <row r="2247">
@@ -76835,7 +76835,7 @@
         <v>4.05</v>
       </c>
       <c r="H2247" s="2" t="n">
-        <v>46092.57448901793</v>
+        <v>46092.5744890162</v>
       </c>
     </row>
     <row r="2248">
@@ -76869,7 +76869,7 @@
         <v>2.84</v>
       </c>
       <c r="H2248" s="2" t="n">
-        <v>46086.57448902094</v>
+        <v>46086.5744890162</v>
       </c>
     </row>
     <row r="2249">
@@ -76903,7 +76903,7 @@
         <v>0.61</v>
       </c>
       <c r="H2249" s="2" t="n">
-        <v>46094.57448902421</v>
+        <v>46094.57448902778</v>
       </c>
     </row>
     <row r="2250">
@@ -76937,7 +76937,7 @@
         <v>1.83</v>
       </c>
       <c r="H2250" s="2" t="n">
-        <v>46086.57448902742</v>
+        <v>46086.57448902778</v>
       </c>
     </row>
     <row r="2251">
@@ -76971,7 +76971,1707 @@
         <v>0.86</v>
       </c>
       <c r="H2251" s="2" t="n">
-        <v>46070.57448903046</v>
+        <v>46070.57448902778</v>
+      </c>
+    </row>
+    <row r="2252">
+      <c r="A2252" t="inlineStr">
+        <is>
+          <t>1e6951c1-f598-4ab6-8442-a0750c265751</t>
+        </is>
+      </c>
+      <c r="B2252" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2252" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2252" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2252" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2252" t="n">
+        <v>355.67</v>
+      </c>
+      <c r="G2252" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="H2252" s="2" t="n">
+        <v>46069.61316210512</v>
+      </c>
+    </row>
+    <row r="2253">
+      <c r="A2253" t="inlineStr">
+        <is>
+          <t>0eef6099-ca3e-47f6-9700-ca87a69e85be</t>
+        </is>
+      </c>
+      <c r="B2253" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2253" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2253" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2253" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2253" t="n">
+        <v>263.88</v>
+      </c>
+      <c r="G2253" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H2253" s="2" t="n">
+        <v>46094.61316210942</v>
+      </c>
+    </row>
+    <row r="2254">
+      <c r="A2254" t="inlineStr">
+        <is>
+          <t>48b7b47b-84a0-4c07-84b9-ca9792b0a913</t>
+        </is>
+      </c>
+      <c r="B2254" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2254" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2254" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2254" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2254" t="n">
+        <v>94.97</v>
+      </c>
+      <c r="G2254" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H2254" s="2" t="n">
+        <v>46074.6131621129</v>
+      </c>
+    </row>
+    <row r="2255">
+      <c r="A2255" t="inlineStr">
+        <is>
+          <t>fd011df1-8eee-46b5-8cb5-d1ba1d2dffc8</t>
+        </is>
+      </c>
+      <c r="B2255" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2255" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2255" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2255" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2255" t="n">
+        <v>203.6</v>
+      </c>
+      <c r="G2255" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H2255" s="2" t="n">
+        <v>46092.61316211607</v>
+      </c>
+    </row>
+    <row r="2256">
+      <c r="A2256" t="inlineStr">
+        <is>
+          <t>c335e9eb-105f-4bd0-94bd-81ad33cd108a</t>
+        </is>
+      </c>
+      <c r="B2256" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2256" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2256" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2256" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2256" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="G2256" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H2256" s="2" t="n">
+        <v>46079.61316211925</v>
+      </c>
+    </row>
+    <row r="2257">
+      <c r="A2257" t="inlineStr">
+        <is>
+          <t>27689719-57a6-4887-9e2b-38d6cef2c0bd</t>
+        </is>
+      </c>
+      <c r="B2257" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2257" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2257" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2257" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2257" t="n">
+        <v>70.73</v>
+      </c>
+      <c r="G2257" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H2257" s="2" t="n">
+        <v>46073.61316212291</v>
+      </c>
+    </row>
+    <row r="2258">
+      <c r="A2258" t="inlineStr">
+        <is>
+          <t>8e2681c2-c1e8-48c2-abed-abe53b38c330</t>
+        </is>
+      </c>
+      <c r="B2258" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2258" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2258" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2258" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2258" t="n">
+        <v>64.31999999999999</v>
+      </c>
+      <c r="G2258" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H2258" s="2" t="n">
+        <v>46082.6131621262</v>
+      </c>
+    </row>
+    <row r="2259">
+      <c r="A2259" t="inlineStr">
+        <is>
+          <t>21f36d8b-e867-4ebe-802a-5931ea0f532b</t>
+        </is>
+      </c>
+      <c r="B2259" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2259" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2259" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2259" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2259" t="n">
+        <v>192.78</v>
+      </c>
+      <c r="G2259" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H2259" s="2" t="n">
+        <v>46090.61316212934</v>
+      </c>
+    </row>
+    <row r="2260">
+      <c r="A2260" t="inlineStr">
+        <is>
+          <t>1ac7c148-4650-4b17-8aa5-6a8ee19d5072</t>
+        </is>
+      </c>
+      <c r="B2260" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2260" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2260" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2260" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2260" t="n">
+        <v>464.9</v>
+      </c>
+      <c r="G2260" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="H2260" s="2" t="n">
+        <v>46096.61316213241</v>
+      </c>
+    </row>
+    <row r="2261">
+      <c r="A2261" t="inlineStr">
+        <is>
+          <t>4a37fedc-b464-4fb9-8ea0-90da1e29c5bc</t>
+        </is>
+      </c>
+      <c r="B2261" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2261" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2261" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2261" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2261" t="n">
+        <v>356.53</v>
+      </c>
+      <c r="G2261" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="H2261" s="2" t="n">
+        <v>46096.61316213571</v>
+      </c>
+    </row>
+    <row r="2262">
+      <c r="A2262" t="inlineStr">
+        <is>
+          <t>86e0a63f-d508-42fd-b26b-c953db713ecc</t>
+        </is>
+      </c>
+      <c r="B2262" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2262" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2262" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2262" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2262" t="n">
+        <v>371.47</v>
+      </c>
+      <c r="G2262" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="H2262" s="2" t="n">
+        <v>46076.61316213899</v>
+      </c>
+    </row>
+    <row r="2263">
+      <c r="A2263" t="inlineStr">
+        <is>
+          <t>5c637bb2-2689-45a6-af6a-552b70aca271</t>
+        </is>
+      </c>
+      <c r="B2263" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2263" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2263" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2263" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2263" t="n">
+        <v>286.27</v>
+      </c>
+      <c r="G2263" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H2263" s="2" t="n">
+        <v>46073.61316214204</v>
+      </c>
+    </row>
+    <row r="2264">
+      <c r="A2264" t="inlineStr">
+        <is>
+          <t>a02c5ed1-cb85-4c5b-92c2-2bfe26745e94</t>
+        </is>
+      </c>
+      <c r="B2264" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2264" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2264" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2264" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2264" t="n">
+        <v>189.31</v>
+      </c>
+      <c r="G2264" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H2264" s="2" t="n">
+        <v>46091.61316214537</v>
+      </c>
+    </row>
+    <row r="2265">
+      <c r="A2265" t="inlineStr">
+        <is>
+          <t>95c5eb3d-9e40-46d4-9029-2fe9d96f269d</t>
+        </is>
+      </c>
+      <c r="B2265" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2265" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2265" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2265" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2265" t="n">
+        <v>127.37</v>
+      </c>
+      <c r="G2265" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H2265" s="2" t="n">
+        <v>46091.61316214842</v>
+      </c>
+    </row>
+    <row r="2266">
+      <c r="A2266" t="inlineStr">
+        <is>
+          <t>16b6b3b6-5ed6-4c64-b6a4-b9edb3fa487c</t>
+        </is>
+      </c>
+      <c r="B2266" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2266" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2266" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2266" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2266" t="n">
+        <v>125.73</v>
+      </c>
+      <c r="G2266" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="H2266" s="2" t="n">
+        <v>46093.6131621515</v>
+      </c>
+    </row>
+    <row r="2267">
+      <c r="A2267" t="inlineStr">
+        <is>
+          <t>eaf3c3c2-4a0b-4095-b526-492ae01a6f72</t>
+        </is>
+      </c>
+      <c r="B2267" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2267" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2267" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2267" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2267" t="n">
+        <v>430.9</v>
+      </c>
+      <c r="G2267" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="H2267" s="2" t="n">
+        <v>46071.61316215451</v>
+      </c>
+    </row>
+    <row r="2268">
+      <c r="A2268" t="inlineStr">
+        <is>
+          <t>15ee1d98-01d6-49c5-9465-d3b295bb69bf</t>
+        </is>
+      </c>
+      <c r="B2268" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2268" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2268" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2268" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2268" t="n">
+        <v>443.08</v>
+      </c>
+      <c r="G2268" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="H2268" s="2" t="n">
+        <v>46082.61316215841</v>
+      </c>
+    </row>
+    <row r="2269">
+      <c r="A2269" t="inlineStr">
+        <is>
+          <t>a0d499e0-04d4-42d0-a998-55babce4d307</t>
+        </is>
+      </c>
+      <c r="B2269" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2269" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2269" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2269" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2269" t="n">
+        <v>47.23</v>
+      </c>
+      <c r="G2269" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H2269" s="2" t="n">
+        <v>46081.61316216155</v>
+      </c>
+    </row>
+    <row r="2270">
+      <c r="A2270" t="inlineStr">
+        <is>
+          <t>943c49bc-0e0b-48c3-96be-135ae6b13af0</t>
+        </is>
+      </c>
+      <c r="B2270" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2270" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2270" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2270" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2270" t="n">
+        <v>194.72</v>
+      </c>
+      <c r="G2270" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H2270" s="2" t="n">
+        <v>46095.61316216477</v>
+      </c>
+    </row>
+    <row r="2271">
+      <c r="A2271" t="inlineStr">
+        <is>
+          <t>f90f84d6-d1a6-4a25-9f3e-37bea9a84b1a</t>
+        </is>
+      </c>
+      <c r="B2271" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2271" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2271" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2271" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2271" t="n">
+        <v>310.68</v>
+      </c>
+      <c r="G2271" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="H2271" s="2" t="n">
+        <v>46096.61316216784</v>
+      </c>
+    </row>
+    <row r="2272">
+      <c r="A2272" t="inlineStr">
+        <is>
+          <t>0e625f9b-f6c3-40e0-8102-a8ce2ee66976</t>
+        </is>
+      </c>
+      <c r="B2272" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2272" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2272" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2272" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2272" t="n">
+        <v>143.54</v>
+      </c>
+      <c r="G2272" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H2272" s="2" t="n">
+        <v>46081.61316217227</v>
+      </c>
+    </row>
+    <row r="2273">
+      <c r="A2273" t="inlineStr">
+        <is>
+          <t>8a5bdab3-96d8-4cc9-a096-fe6501830bad</t>
+        </is>
+      </c>
+      <c r="B2273" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2273" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2273" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2273" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2273" t="n">
+        <v>122.53</v>
+      </c>
+      <c r="G2273" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="H2273" s="2" t="n">
+        <v>46077.61316217545</v>
+      </c>
+    </row>
+    <row r="2274">
+      <c r="A2274" t="inlineStr">
+        <is>
+          <t>ea6d6372-745c-4558-9488-0ce73161f665</t>
+        </is>
+      </c>
+      <c r="B2274" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2274" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2274" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2274" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2274" t="n">
+        <v>325.48</v>
+      </c>
+      <c r="G2274" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H2274" s="2" t="n">
+        <v>46072.6131621786</v>
+      </c>
+    </row>
+    <row r="2275">
+      <c r="A2275" t="inlineStr">
+        <is>
+          <t>047d7aaf-76e1-48ee-b2c3-4530cffa1db6</t>
+        </is>
+      </c>
+      <c r="B2275" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2275" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2275" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2275" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2275" t="n">
+        <v>173.82</v>
+      </c>
+      <c r="G2275" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="H2275" s="2" t="n">
+        <v>46096.61316218183</v>
+      </c>
+    </row>
+    <row r="2276">
+      <c r="A2276" t="inlineStr">
+        <is>
+          <t>b9989966-62e3-4760-8802-b097eeec6cdc</t>
+        </is>
+      </c>
+      <c r="B2276" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2276" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2276" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2276" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2276" t="n">
+        <v>29.06</v>
+      </c>
+      <c r="G2276" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H2276" s="2" t="n">
+        <v>46093.613162185</v>
+      </c>
+    </row>
+    <row r="2277">
+      <c r="A2277" t="inlineStr">
+        <is>
+          <t>27bc08a2-66fe-4df3-a7ea-9a4df69dc832</t>
+        </is>
+      </c>
+      <c r="B2277" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2277" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2277" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2277" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2277" t="n">
+        <v>247.91</v>
+      </c>
+      <c r="G2277" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H2277" s="2" t="n">
+        <v>46095.61316218818</v>
+      </c>
+    </row>
+    <row r="2278">
+      <c r="A2278" t="inlineStr">
+        <is>
+          <t>1389c92b-3901-4921-ac11-c996ae19ea84</t>
+        </is>
+      </c>
+      <c r="B2278" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2278" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2278" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2278" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2278" t="n">
+        <v>319.74</v>
+      </c>
+      <c r="G2278" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H2278" s="2" t="n">
+        <v>46068.61316219132</v>
+      </c>
+    </row>
+    <row r="2279">
+      <c r="A2279" t="inlineStr">
+        <is>
+          <t>263c631a-a04e-4d59-bfe0-a33952b650f1</t>
+        </is>
+      </c>
+      <c r="B2279" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2279" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2279" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2279" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2279" t="n">
+        <v>330.97</v>
+      </c>
+      <c r="G2279" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="H2279" s="2" t="n">
+        <v>46089.61316219468</v>
+      </c>
+    </row>
+    <row r="2280">
+      <c r="A2280" t="inlineStr">
+        <is>
+          <t>f12324aa-8e77-472d-8b32-e8c7a9d6a221</t>
+        </is>
+      </c>
+      <c r="B2280" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2280" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2280" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2280" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2280" t="n">
+        <v>237.6</v>
+      </c>
+      <c r="G2280" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H2280" s="2" t="n">
+        <v>46085.61316219768</v>
+      </c>
+    </row>
+    <row r="2281">
+      <c r="A2281" t="inlineStr">
+        <is>
+          <t>4b225f5e-fef6-44d9-985d-9930ddc5f3c0</t>
+        </is>
+      </c>
+      <c r="B2281" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2281" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2281" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2281" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2281" t="n">
+        <v>411.54</v>
+      </c>
+      <c r="G2281" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="H2281" s="2" t="n">
+        <v>46073.61316220093</v>
+      </c>
+    </row>
+    <row r="2282">
+      <c r="A2282" t="inlineStr">
+        <is>
+          <t>30d17ff1-d2f7-4872-a3ed-dff3a075b7ef</t>
+        </is>
+      </c>
+      <c r="B2282" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2282" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2282" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2282" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2282" t="n">
+        <v>491.26</v>
+      </c>
+      <c r="G2282" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="H2282" s="2" t="n">
+        <v>46092.61316220418</v>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" t="inlineStr">
+        <is>
+          <t>681ccee1-96be-4a37-8e98-069a094fe940</t>
+        </is>
+      </c>
+      <c r="B2283" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2283" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2283" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2283" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2283" t="n">
+        <v>472.09</v>
+      </c>
+      <c r="G2283" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="H2283" s="2" t="n">
+        <v>46083.6131622074</v>
+      </c>
+    </row>
+    <row r="2284">
+      <c r="A2284" t="inlineStr">
+        <is>
+          <t>d3404a7d-b99f-4d8d-9351-f33e54831a37</t>
+        </is>
+      </c>
+      <c r="B2284" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2284" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2284" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2284" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2284" t="n">
+        <v>455.47</v>
+      </c>
+      <c r="G2284" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="H2284" s="2" t="n">
+        <v>46080.61316221086</v>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="A2285" t="inlineStr">
+        <is>
+          <t>5e31f4e7-0503-49b8-a957-f2a025cf8577</t>
+        </is>
+      </c>
+      <c r="B2285" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2285" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2285" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2285" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2285" t="n">
+        <v>146.62</v>
+      </c>
+      <c r="G2285" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H2285" s="2" t="n">
+        <v>46084.61316221407</v>
+      </c>
+    </row>
+    <row r="2286">
+      <c r="A2286" t="inlineStr">
+        <is>
+          <t>06b43726-f791-4c54-b288-1a97e9f49614</t>
+        </is>
+      </c>
+      <c r="B2286" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2286" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2286" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2286" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2286" t="n">
+        <v>314.1</v>
+      </c>
+      <c r="G2286" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H2286" s="2" t="n">
+        <v>46067.6131622179</v>
+      </c>
+    </row>
+    <row r="2287">
+      <c r="A2287" t="inlineStr">
+        <is>
+          <t>0b223b52-b8ce-422f-815b-9ead4d8ae26e</t>
+        </is>
+      </c>
+      <c r="B2287" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2287" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2287" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2287" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2287" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="G2287" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H2287" s="2" t="n">
+        <v>46082.61316222097</v>
+      </c>
+    </row>
+    <row r="2288">
+      <c r="A2288" t="inlineStr">
+        <is>
+          <t>cb2eb52c-14ba-4424-8f7f-97b594d37bb7</t>
+        </is>
+      </c>
+      <c r="B2288" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2288" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2288" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2288" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2288" t="n">
+        <v>44.73</v>
+      </c>
+      <c r="G2288" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H2288" s="2" t="n">
+        <v>46080.61316222404</v>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="A2289" t="inlineStr">
+        <is>
+          <t>dec91fe5-e30f-4429-92ad-7f405cf8a591</t>
+        </is>
+      </c>
+      <c r="B2289" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2289" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2289" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2289" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2289" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="G2289" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H2289" s="2" t="n">
+        <v>46070.6131622274</v>
+      </c>
+    </row>
+    <row r="2290">
+      <c r="A2290" t="inlineStr">
+        <is>
+          <t>1e93a7a8-a3d9-40ee-95e2-1bc98e9c8613</t>
+        </is>
+      </c>
+      <c r="B2290" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2290" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2290" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2290" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2290" t="n">
+        <v>470.19</v>
+      </c>
+      <c r="G2290" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H2290" s="2" t="n">
+        <v>46080.61316223053</v>
+      </c>
+    </row>
+    <row r="2291">
+      <c r="A2291" t="inlineStr">
+        <is>
+          <t>84f4c07a-5985-43f0-941c-dab6ccdf33d4</t>
+        </is>
+      </c>
+      <c r="B2291" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2291" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2291" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2291" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2291" t="n">
+        <v>489.05</v>
+      </c>
+      <c r="G2291" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="H2291" s="2" t="n">
+        <v>46096.61316223374</v>
+      </c>
+    </row>
+    <row r="2292">
+      <c r="A2292" t="inlineStr">
+        <is>
+          <t>cc1158e5-3400-4125-ac99-d5af89fa43e8</t>
+        </is>
+      </c>
+      <c r="B2292" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2292" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2292" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2292" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2292" t="n">
+        <v>83.67</v>
+      </c>
+      <c r="G2292" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H2292" s="2" t="n">
+        <v>46086.61316223686</v>
+      </c>
+    </row>
+    <row r="2293">
+      <c r="A2293" t="inlineStr">
+        <is>
+          <t>51b8b468-cc7b-433c-acbe-e7db91774452</t>
+        </is>
+      </c>
+      <c r="B2293" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2293" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2293" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2293" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2293" t="n">
+        <v>133.95</v>
+      </c>
+      <c r="G2293" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="H2293" s="2" t="n">
+        <v>46080.61316224038</v>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" t="inlineStr">
+        <is>
+          <t>997dc4b8-aec0-4b21-aebd-97c431a1fda7</t>
+        </is>
+      </c>
+      <c r="B2294" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2294" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2294" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2294" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2294" t="n">
+        <v>275.2</v>
+      </c>
+      <c r="G2294" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H2294" s="2" t="n">
+        <v>46070.61316224358</v>
+      </c>
+    </row>
+    <row r="2295">
+      <c r="A2295" t="inlineStr">
+        <is>
+          <t>c3d9d026-c031-4675-890d-48610f2c4ea1</t>
+        </is>
+      </c>
+      <c r="B2295" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2295" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2295" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2295" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2295" t="n">
+        <v>404.15</v>
+      </c>
+      <c r="G2295" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="H2295" s="2" t="n">
+        <v>46085.61316224661</v>
+      </c>
+    </row>
+    <row r="2296">
+      <c r="A2296" t="inlineStr">
+        <is>
+          <t>598bf867-908d-4207-bdeb-aae0576139df</t>
+        </is>
+      </c>
+      <c r="B2296" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2296" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2296" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2296" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2296" t="n">
+        <v>332.86</v>
+      </c>
+      <c r="G2296" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="H2296" s="2" t="n">
+        <v>46095.61316224997</v>
+      </c>
+    </row>
+    <row r="2297">
+      <c r="A2297" t="inlineStr">
+        <is>
+          <t>39828ec6-d3c2-4b39-8b7f-bb6e6de2ead4</t>
+        </is>
+      </c>
+      <c r="B2297" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2297" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2297" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2297" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2297" t="n">
+        <v>129.87</v>
+      </c>
+      <c r="G2297" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H2297" s="2" t="n">
+        <v>46092.61316225318</v>
+      </c>
+    </row>
+    <row r="2298">
+      <c r="A2298" t="inlineStr">
+        <is>
+          <t>bc5f805b-b677-410e-9f12-18cf352aca1a</t>
+        </is>
+      </c>
+      <c r="B2298" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2298" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2298" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2298" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2298" t="n">
+        <v>87.98</v>
+      </c>
+      <c r="G2298" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H2298" s="2" t="n">
+        <v>46069.61316225617</v>
+      </c>
+    </row>
+    <row r="2299">
+      <c r="A2299" t="inlineStr">
+        <is>
+          <t>5e33481d-99d0-45e9-a5eb-d4fb2917df41</t>
+        </is>
+      </c>
+      <c r="B2299" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2299" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2299" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2299" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2299" t="n">
+        <v>72.67</v>
+      </c>
+      <c r="G2299" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H2299" s="2" t="n">
+        <v>46088.61316225928</v>
+      </c>
+    </row>
+    <row r="2300">
+      <c r="A2300" t="inlineStr">
+        <is>
+          <t>67469293-8114-4714-822a-0d1409dfa3d2</t>
+        </is>
+      </c>
+      <c r="B2300" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2300" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2300" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2300" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2300" t="n">
+        <v>98.11</v>
+      </c>
+      <c r="G2300" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H2300" s="2" t="n">
+        <v>46070.61316226301</v>
+      </c>
+    </row>
+    <row r="2301">
+      <c r="A2301" t="inlineStr">
+        <is>
+          <t>0ea5bc69-7c9f-4f71-81c2-93bbb79e16bf</t>
+        </is>
+      </c>
+      <c r="B2301" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2301" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2301" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2301" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2301" t="n">
+        <v>210.14</v>
+      </c>
+      <c r="G2301" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H2301" s="2" t="n">
+        <v>46085.61316226609</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2301"/>
+  <dimension ref="A1:H2351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77005,7 +77005,7 @@
         <v>3.56</v>
       </c>
       <c r="H2252" s="2" t="n">
-        <v>46069.61316210512</v>
+        <v>46069.61316210649</v>
       </c>
     </row>
     <row r="2253">
@@ -77039,7 +77039,7 @@
         <v>2.64</v>
       </c>
       <c r="H2253" s="2" t="n">
-        <v>46094.61316210942</v>
+        <v>46094.61316210649</v>
       </c>
     </row>
     <row r="2254">
@@ -77073,7 +77073,7 @@
         <v>0.95</v>
       </c>
       <c r="H2254" s="2" t="n">
-        <v>46074.6131621129</v>
+        <v>46074.61316211805</v>
       </c>
     </row>
     <row r="2255">
@@ -77107,7 +77107,7 @@
         <v>2.04</v>
       </c>
       <c r="H2255" s="2" t="n">
-        <v>46092.61316211607</v>
+        <v>46092.61316211805</v>
       </c>
     </row>
     <row r="2256">
@@ -77141,7 +77141,7 @@
         <v>0.49</v>
       </c>
       <c r="H2256" s="2" t="n">
-        <v>46079.61316211925</v>
+        <v>46079.61316211805</v>
       </c>
     </row>
     <row r="2257">
@@ -77175,7 +77175,7 @@
         <v>0.71</v>
       </c>
       <c r="H2257" s="2" t="n">
-        <v>46073.61316212291</v>
+        <v>46073.61316211805</v>
       </c>
     </row>
     <row r="2258">
@@ -77209,7 +77209,7 @@
         <v>0.64</v>
       </c>
       <c r="H2258" s="2" t="n">
-        <v>46082.6131621262</v>
+        <v>46082.61316212963</v>
       </c>
     </row>
     <row r="2259">
@@ -77243,7 +77243,7 @@
         <v>1.93</v>
       </c>
       <c r="H2259" s="2" t="n">
-        <v>46090.61316212934</v>
+        <v>46090.61316212963</v>
       </c>
     </row>
     <row r="2260">
@@ -77277,7 +77277,7 @@
         <v>4.65</v>
       </c>
       <c r="H2260" s="2" t="n">
-        <v>46096.61316213241</v>
+        <v>46096.61316212963</v>
       </c>
     </row>
     <row r="2261">
@@ -77311,7 +77311,7 @@
         <v>3.57</v>
       </c>
       <c r="H2261" s="2" t="n">
-        <v>46096.61316213571</v>
+        <v>46096.61316214121</v>
       </c>
     </row>
     <row r="2262">
@@ -77345,7 +77345,7 @@
         <v>3.71</v>
       </c>
       <c r="H2262" s="2" t="n">
-        <v>46076.61316213899</v>
+        <v>46076.61316214121</v>
       </c>
     </row>
     <row r="2263">
@@ -77379,7 +77379,7 @@
         <v>2.86</v>
       </c>
       <c r="H2263" s="2" t="n">
-        <v>46073.61316214204</v>
+        <v>46073.61316214121</v>
       </c>
     </row>
     <row r="2264">
@@ -77413,7 +77413,7 @@
         <v>1.89</v>
       </c>
       <c r="H2264" s="2" t="n">
-        <v>46091.61316214537</v>
+        <v>46091.61316214121</v>
       </c>
     </row>
     <row r="2265">
@@ -77447,7 +77447,7 @@
         <v>1.27</v>
       </c>
       <c r="H2265" s="2" t="n">
-        <v>46091.61316214842</v>
+        <v>46091.61316215277</v>
       </c>
     </row>
     <row r="2266">
@@ -77481,7 +77481,7 @@
         <v>1.26</v>
       </c>
       <c r="H2266" s="2" t="n">
-        <v>46093.6131621515</v>
+        <v>46093.61316215277</v>
       </c>
     </row>
     <row r="2267">
@@ -77515,7 +77515,7 @@
         <v>4.31</v>
       </c>
       <c r="H2267" s="2" t="n">
-        <v>46071.61316215451</v>
+        <v>46071.61316215277</v>
       </c>
     </row>
     <row r="2268">
@@ -77549,7 +77549,7 @@
         <v>4.43</v>
       </c>
       <c r="H2268" s="2" t="n">
-        <v>46082.61316215841</v>
+        <v>46082.61316215277</v>
       </c>
     </row>
     <row r="2269">
@@ -77583,7 +77583,7 @@
         <v>0.47</v>
       </c>
       <c r="H2269" s="2" t="n">
-        <v>46081.61316216155</v>
+        <v>46081.61316216435</v>
       </c>
     </row>
     <row r="2270">
@@ -77617,7 +77617,7 @@
         <v>1.95</v>
       </c>
       <c r="H2270" s="2" t="n">
-        <v>46095.61316216477</v>
+        <v>46095.61316216435</v>
       </c>
     </row>
     <row r="2271">
@@ -77651,7 +77651,7 @@
         <v>3.11</v>
       </c>
       <c r="H2271" s="2" t="n">
-        <v>46096.61316216784</v>
+        <v>46096.61316216435</v>
       </c>
     </row>
     <row r="2272">
@@ -77685,7 +77685,7 @@
         <v>1.44</v>
       </c>
       <c r="H2272" s="2" t="n">
-        <v>46081.61316217227</v>
+        <v>46081.61316217593</v>
       </c>
     </row>
     <row r="2273">
@@ -77719,7 +77719,7 @@
         <v>1.23</v>
       </c>
       <c r="H2273" s="2" t="n">
-        <v>46077.61316217545</v>
+        <v>46077.61316217593</v>
       </c>
     </row>
     <row r="2274">
@@ -77753,7 +77753,7 @@
         <v>3.25</v>
       </c>
       <c r="H2274" s="2" t="n">
-        <v>46072.6131621786</v>
+        <v>46072.61316217593</v>
       </c>
     </row>
     <row r="2275">
@@ -77787,7 +77787,7 @@
         <v>1.74</v>
       </c>
       <c r="H2275" s="2" t="n">
-        <v>46096.61316218183</v>
+        <v>46096.6131621875</v>
       </c>
     </row>
     <row r="2276">
@@ -77821,7 +77821,7 @@
         <v>0.29</v>
       </c>
       <c r="H2276" s="2" t="n">
-        <v>46093.613162185</v>
+        <v>46093.6131621875</v>
       </c>
     </row>
     <row r="2277">
@@ -77855,7 +77855,7 @@
         <v>2.48</v>
       </c>
       <c r="H2277" s="2" t="n">
-        <v>46095.61316218818</v>
+        <v>46095.6131621875</v>
       </c>
     </row>
     <row r="2278">
@@ -77889,7 +77889,7 @@
         <v>3.2</v>
       </c>
       <c r="H2278" s="2" t="n">
-        <v>46068.61316219132</v>
+        <v>46068.6131621875</v>
       </c>
     </row>
     <row r="2279">
@@ -77923,7 +77923,7 @@
         <v>3.31</v>
       </c>
       <c r="H2279" s="2" t="n">
-        <v>46089.61316219468</v>
+        <v>46089.61316219907</v>
       </c>
     </row>
     <row r="2280">
@@ -77957,7 +77957,7 @@
         <v>2.38</v>
       </c>
       <c r="H2280" s="2" t="n">
-        <v>46085.61316219768</v>
+        <v>46085.61316219907</v>
       </c>
     </row>
     <row r="2281">
@@ -77991,7 +77991,7 @@
         <v>4.12</v>
       </c>
       <c r="H2281" s="2" t="n">
-        <v>46073.61316220093</v>
+        <v>46073.61316219907</v>
       </c>
     </row>
     <row r="2282">
@@ -78025,7 +78025,7 @@
         <v>4.91</v>
       </c>
       <c r="H2282" s="2" t="n">
-        <v>46092.61316220418</v>
+        <v>46092.61316219907</v>
       </c>
     </row>
     <row r="2283">
@@ -78059,7 +78059,7 @@
         <v>4.72</v>
       </c>
       <c r="H2283" s="2" t="n">
-        <v>46083.6131622074</v>
+        <v>46083.61316221065</v>
       </c>
     </row>
     <row r="2284">
@@ -78093,7 +78093,7 @@
         <v>4.55</v>
       </c>
       <c r="H2284" s="2" t="n">
-        <v>46080.61316221086</v>
+        <v>46080.61316221065</v>
       </c>
     </row>
     <row r="2285">
@@ -78127,7 +78127,7 @@
         <v>1.47</v>
       </c>
       <c r="H2285" s="2" t="n">
-        <v>46084.61316221407</v>
+        <v>46084.61316221065</v>
       </c>
     </row>
     <row r="2286">
@@ -78161,7 +78161,7 @@
         <v>3.14</v>
       </c>
       <c r="H2286" s="2" t="n">
-        <v>46067.6131622179</v>
+        <v>46067.61316222222</v>
       </c>
     </row>
     <row r="2287">
@@ -78195,7 +78195,7 @@
         <v>0.39</v>
       </c>
       <c r="H2287" s="2" t="n">
-        <v>46082.61316222097</v>
+        <v>46082.61316222222</v>
       </c>
     </row>
     <row r="2288">
@@ -78229,7 +78229,7 @@
         <v>0.45</v>
       </c>
       <c r="H2288" s="2" t="n">
-        <v>46080.61316222404</v>
+        <v>46080.61316222222</v>
       </c>
     </row>
     <row r="2289">
@@ -78263,7 +78263,7 @@
         <v>0.08</v>
       </c>
       <c r="H2289" s="2" t="n">
-        <v>46070.6131622274</v>
+        <v>46070.61316222222</v>
       </c>
     </row>
     <row r="2290">
@@ -78297,7 +78297,7 @@
         <v>4.7</v>
       </c>
       <c r="H2290" s="2" t="n">
-        <v>46080.61316223053</v>
+        <v>46080.6131622338</v>
       </c>
     </row>
     <row r="2291">
@@ -78331,7 +78331,7 @@
         <v>4.89</v>
       </c>
       <c r="H2291" s="2" t="n">
-        <v>46096.61316223374</v>
+        <v>46096.6131622338</v>
       </c>
     </row>
     <row r="2292">
@@ -78365,7 +78365,7 @@
         <v>0.84</v>
       </c>
       <c r="H2292" s="2" t="n">
-        <v>46086.61316223686</v>
+        <v>46086.6131622338</v>
       </c>
     </row>
     <row r="2293">
@@ -78399,7 +78399,7 @@
         <v>1.34</v>
       </c>
       <c r="H2293" s="2" t="n">
-        <v>46080.61316224038</v>
+        <v>46080.61316224537</v>
       </c>
     </row>
     <row r="2294">
@@ -78433,7 +78433,7 @@
         <v>2.75</v>
       </c>
       <c r="H2294" s="2" t="n">
-        <v>46070.61316224358</v>
+        <v>46070.61316224537</v>
       </c>
     </row>
     <row r="2295">
@@ -78467,7 +78467,7 @@
         <v>4.04</v>
       </c>
       <c r="H2295" s="2" t="n">
-        <v>46085.61316224661</v>
+        <v>46085.61316224537</v>
       </c>
     </row>
     <row r="2296">
@@ -78501,7 +78501,7 @@
         <v>3.33</v>
       </c>
       <c r="H2296" s="2" t="n">
-        <v>46095.61316224997</v>
+        <v>46095.61316224537</v>
       </c>
     </row>
     <row r="2297">
@@ -78535,7 +78535,7 @@
         <v>1.3</v>
       </c>
       <c r="H2297" s="2" t="n">
-        <v>46092.61316225318</v>
+        <v>46092.61316225694</v>
       </c>
     </row>
     <row r="2298">
@@ -78569,7 +78569,7 @@
         <v>0.88</v>
       </c>
       <c r="H2298" s="2" t="n">
-        <v>46069.61316225617</v>
+        <v>46069.61316225694</v>
       </c>
     </row>
     <row r="2299">
@@ -78603,7 +78603,7 @@
         <v>0.73</v>
       </c>
       <c r="H2299" s="2" t="n">
-        <v>46088.61316225928</v>
+        <v>46088.61316225694</v>
       </c>
     </row>
     <row r="2300">
@@ -78637,7 +78637,7 @@
         <v>0.98</v>
       </c>
       <c r="H2300" s="2" t="n">
-        <v>46070.61316226301</v>
+        <v>46070.61316226852</v>
       </c>
     </row>
     <row r="2301">
@@ -78671,7 +78671,1707 @@
         <v>2.1</v>
       </c>
       <c r="H2301" s="2" t="n">
-        <v>46085.61316226609</v>
+        <v>46085.61316226852</v>
+      </c>
+    </row>
+    <row r="2302">
+      <c r="A2302" t="inlineStr">
+        <is>
+          <t>6cbaff8f-e779-4410-a270-44f1b24d6790</t>
+        </is>
+      </c>
+      <c r="B2302" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2302" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2302" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2302" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2302" t="n">
+        <v>323.85</v>
+      </c>
+      <c r="G2302" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="H2302" s="2" t="n">
+        <v>46068.66290954581</v>
+      </c>
+    </row>
+    <row r="2303">
+      <c r="A2303" t="inlineStr">
+        <is>
+          <t>60080435-3891-4f2c-aeb1-ea9b7432afd8</t>
+        </is>
+      </c>
+      <c r="B2303" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2303" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2303" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2303" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2303" t="n">
+        <v>71.73</v>
+      </c>
+      <c r="G2303" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H2303" s="2" t="n">
+        <v>46096.66290955008</v>
+      </c>
+    </row>
+    <row r="2304">
+      <c r="A2304" t="inlineStr">
+        <is>
+          <t>dd7e921e-3824-490b-8544-f2415ecbf1d4</t>
+        </is>
+      </c>
+      <c r="B2304" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2304" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2304" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2304" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2304" t="n">
+        <v>289.46</v>
+      </c>
+      <c r="G2304" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="H2304" s="2" t="n">
+        <v>46081.66290955381</v>
+      </c>
+    </row>
+    <row r="2305">
+      <c r="A2305" t="inlineStr">
+        <is>
+          <t>ac1a82ab-d1fa-4356-abb3-e0fa62693e5f</t>
+        </is>
+      </c>
+      <c r="B2305" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2305" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2305" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2305" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2305" t="n">
+        <v>38.19</v>
+      </c>
+      <c r="G2305" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H2305" s="2" t="n">
+        <v>46080.66290955698</v>
+      </c>
+    </row>
+    <row r="2306">
+      <c r="A2306" t="inlineStr">
+        <is>
+          <t>452b3483-a519-4ee8-97ee-aa41e3518141</t>
+        </is>
+      </c>
+      <c r="B2306" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2306" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2306" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2306" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2306" t="n">
+        <v>251.5</v>
+      </c>
+      <c r="G2306" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="H2306" s="2" t="n">
+        <v>46084.66290956017</v>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="A2307" t="inlineStr">
+        <is>
+          <t>42502538-fe40-475e-a32c-2e40608c963b</t>
+        </is>
+      </c>
+      <c r="B2307" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2307" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2307" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2307" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2307" t="n">
+        <v>253.24</v>
+      </c>
+      <c r="G2307" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="H2307" s="2" t="n">
+        <v>46080.66290956341</v>
+      </c>
+    </row>
+    <row r="2308">
+      <c r="A2308" t="inlineStr">
+        <is>
+          <t>5bfb0cc4-bc5a-4785-a923-72dba5785684</t>
+        </is>
+      </c>
+      <c r="B2308" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2308" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2308" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2308" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2308" t="n">
+        <v>349.29</v>
+      </c>
+      <c r="G2308" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="H2308" s="2" t="n">
+        <v>46077.66290956706</v>
+      </c>
+    </row>
+    <row r="2309">
+      <c r="A2309" t="inlineStr">
+        <is>
+          <t>dd05a3b0-15fa-42d1-82e6-d629446d7475</t>
+        </is>
+      </c>
+      <c r="B2309" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2309" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2309" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2309" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2309" t="n">
+        <v>111.49</v>
+      </c>
+      <c r="G2309" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="H2309" s="2" t="n">
+        <v>46090.66290957036</v>
+      </c>
+    </row>
+    <row r="2310">
+      <c r="A2310" t="inlineStr">
+        <is>
+          <t>e7877c05-9483-45fd-8705-4c2ea876eacc</t>
+        </is>
+      </c>
+      <c r="B2310" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2310" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2310" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2310" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2310" t="n">
+        <v>153.86</v>
+      </c>
+      <c r="G2310" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="H2310" s="2" t="n">
+        <v>46085.66290957366</v>
+      </c>
+    </row>
+    <row r="2311">
+      <c r="A2311" t="inlineStr">
+        <is>
+          <t>a4e376f6-e634-4592-a8c1-b5498748d6d2</t>
+        </is>
+      </c>
+      <c r="B2311" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2311" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2311" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2311" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2311" t="n">
+        <v>260.63</v>
+      </c>
+      <c r="G2311" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="H2311" s="2" t="n">
+        <v>46082.66290957711</v>
+      </c>
+    </row>
+    <row r="2312">
+      <c r="A2312" t="inlineStr">
+        <is>
+          <t>8dd43136-0d52-47b2-922c-d689d5d8c114</t>
+        </is>
+      </c>
+      <c r="B2312" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2312" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2312" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2312" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2312" t="n">
+        <v>415.81</v>
+      </c>
+      <c r="G2312" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="H2312" s="2" t="n">
+        <v>46091.66290958024</v>
+      </c>
+    </row>
+    <row r="2313">
+      <c r="A2313" t="inlineStr">
+        <is>
+          <t>f4a4ebc2-e6a1-42eb-906f-ad94aa0aeae0</t>
+        </is>
+      </c>
+      <c r="B2313" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2313" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2313" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2313" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2313" t="n">
+        <v>209.36</v>
+      </c>
+      <c r="G2313" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="H2313" s="2" t="n">
+        <v>46080.6629095833</v>
+      </c>
+    </row>
+    <row r="2314">
+      <c r="A2314" t="inlineStr">
+        <is>
+          <t>1929eb70-7d3b-455b-ab13-934fdd9120ff</t>
+        </is>
+      </c>
+      <c r="B2314" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2314" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2314" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2314" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2314" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="G2314" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H2314" s="2" t="n">
+        <v>46083.66290958641</v>
+      </c>
+    </row>
+    <row r="2315">
+      <c r="A2315" t="inlineStr">
+        <is>
+          <t>8e2b822c-8537-4a8a-b0dd-90c75003cfea</t>
+        </is>
+      </c>
+      <c r="B2315" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2315" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2315" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2315" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2315" t="n">
+        <v>109.76</v>
+      </c>
+      <c r="G2315" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H2315" s="2" t="n">
+        <v>46090.66290958982</v>
+      </c>
+    </row>
+    <row r="2316">
+      <c r="A2316" t="inlineStr">
+        <is>
+          <t>adcfa67e-cf9a-48ce-9df2-212951326a05</t>
+        </is>
+      </c>
+      <c r="B2316" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2316" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2316" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2316" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2316" t="n">
+        <v>285.06</v>
+      </c>
+      <c r="G2316" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="H2316" s="2" t="n">
+        <v>46067.66290959282</v>
+      </c>
+    </row>
+    <row r="2317">
+      <c r="A2317" t="inlineStr">
+        <is>
+          <t>817ba1f6-f97e-4c78-832f-fda58dbac078</t>
+        </is>
+      </c>
+      <c r="B2317" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2317" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2317" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2317" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2317" t="n">
+        <v>399.29</v>
+      </c>
+      <c r="G2317" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="H2317" s="2" t="n">
+        <v>46072.6629095959</v>
+      </c>
+    </row>
+    <row r="2318">
+      <c r="A2318" t="inlineStr">
+        <is>
+          <t>f5b195a5-88ad-4b17-8df9-f257ee7ad024</t>
+        </is>
+      </c>
+      <c r="B2318" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2318" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2318" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2318" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2318" t="n">
+        <v>38.62</v>
+      </c>
+      <c r="G2318" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H2318" s="2" t="n">
+        <v>46074.66290959925</v>
+      </c>
+    </row>
+    <row r="2319">
+      <c r="A2319" t="inlineStr">
+        <is>
+          <t>e5affd22-4972-408c-ba7e-2a9015a7a859</t>
+        </is>
+      </c>
+      <c r="B2319" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2319" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2319" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2319" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2319" t="n">
+        <v>298.55</v>
+      </c>
+      <c r="G2319" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H2319" s="2" t="n">
+        <v>46094.66290960226</v>
+      </c>
+    </row>
+    <row r="2320">
+      <c r="A2320" t="inlineStr">
+        <is>
+          <t>3c045790-a9ef-4a3b-ad78-c30e0d72ce7a</t>
+        </is>
+      </c>
+      <c r="B2320" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2320" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2320" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2320" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2320" t="n">
+        <v>408.79</v>
+      </c>
+      <c r="G2320" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="H2320" s="2" t="n">
+        <v>46096.6629096055</v>
+      </c>
+    </row>
+    <row r="2321">
+      <c r="A2321" t="inlineStr">
+        <is>
+          <t>583390b3-44d5-43ef-b65a-86093ce85588</t>
+        </is>
+      </c>
+      <c r="B2321" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2321" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2321" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2321" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2321" t="n">
+        <v>250.15</v>
+      </c>
+      <c r="G2321" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H2321" s="2" t="n">
+        <v>46095.66290960865</v>
+      </c>
+    </row>
+    <row r="2322">
+      <c r="A2322" t="inlineStr">
+        <is>
+          <t>55739f2a-d54b-4a3d-a0ae-7e9d0edbbf40</t>
+        </is>
+      </c>
+      <c r="B2322" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2322" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2322" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2322" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2322" t="n">
+        <v>413.37</v>
+      </c>
+      <c r="G2322" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="H2322" s="2" t="n">
+        <v>46086.66290961237</v>
+      </c>
+    </row>
+    <row r="2323">
+      <c r="A2323" t="inlineStr">
+        <is>
+          <t>0967913f-89e4-4f17-8a39-79ea3194c3c3</t>
+        </is>
+      </c>
+      <c r="B2323" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2323" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2323" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2323" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2323" t="n">
+        <v>351.13</v>
+      </c>
+      <c r="G2323" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="H2323" s="2" t="n">
+        <v>46068.66290961545</v>
+      </c>
+    </row>
+    <row r="2324">
+      <c r="A2324" t="inlineStr">
+        <is>
+          <t>0df3f32a-ed9c-42da-843d-052c2af62cf9</t>
+        </is>
+      </c>
+      <c r="B2324" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2324" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2324" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2324" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2324" t="n">
+        <v>377.28</v>
+      </c>
+      <c r="G2324" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="H2324" s="2" t="n">
+        <v>46074.66290961864</v>
+      </c>
+    </row>
+    <row r="2325">
+      <c r="A2325" t="inlineStr">
+        <is>
+          <t>25720c5d-281d-40af-aac2-5ec0ef91211e</t>
+        </is>
+      </c>
+      <c r="B2325" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2325" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2325" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2325" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2325" t="n">
+        <v>429.52</v>
+      </c>
+      <c r="G2325" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H2325" s="2" t="n">
+        <v>46081.66290962209</v>
+      </c>
+    </row>
+    <row r="2326">
+      <c r="A2326" t="inlineStr">
+        <is>
+          <t>cfc98887-9447-4485-a616-36d215834962</t>
+        </is>
+      </c>
+      <c r="B2326" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2326" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2326" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2326" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2326" t="n">
+        <v>466.41</v>
+      </c>
+      <c r="G2326" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="H2326" s="2" t="n">
+        <v>46084.66290962511</v>
+      </c>
+    </row>
+    <row r="2327">
+      <c r="A2327" t="inlineStr">
+        <is>
+          <t>28915f33-c682-4c87-bdcc-040edc91d6ff</t>
+        </is>
+      </c>
+      <c r="B2327" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2327" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2327" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2327" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2327" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="G2327" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H2327" s="2" t="n">
+        <v>46095.66290962824</v>
+      </c>
+    </row>
+    <row r="2328">
+      <c r="A2328" t="inlineStr">
+        <is>
+          <t>7e270059-e913-4c91-ab0d-f634c6c856a6</t>
+        </is>
+      </c>
+      <c r="B2328" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2328" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2328" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2328" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2328" t="n">
+        <v>481.74</v>
+      </c>
+      <c r="G2328" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="H2328" s="2" t="n">
+        <v>46095.66290963128</v>
+      </c>
+    </row>
+    <row r="2329">
+      <c r="A2329" t="inlineStr">
+        <is>
+          <t>2732eac1-aabc-4d99-8d07-4aeefd50528e</t>
+        </is>
+      </c>
+      <c r="B2329" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2329" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2329" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2329" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2329" t="n">
+        <v>245.8</v>
+      </c>
+      <c r="G2329" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H2329" s="2" t="n">
+        <v>46094.66290963476</v>
+      </c>
+    </row>
+    <row r="2330">
+      <c r="A2330" t="inlineStr">
+        <is>
+          <t>62a76233-a35c-43f0-976f-8849a7461a08</t>
+        </is>
+      </c>
+      <c r="B2330" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2330" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2330" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2330" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2330" t="n">
+        <v>218.86</v>
+      </c>
+      <c r="G2330" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="H2330" s="2" t="n">
+        <v>46084.66290963793</v>
+      </c>
+    </row>
+    <row r="2331">
+      <c r="A2331" t="inlineStr">
+        <is>
+          <t>fe23df8f-caea-4bd8-a871-fed9ccbe14c4</t>
+        </is>
+      </c>
+      <c r="B2331" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2331" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2331" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2331" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2331" t="n">
+        <v>307.29</v>
+      </c>
+      <c r="G2331" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="H2331" s="2" t="n">
+        <v>46092.66290964109</v>
+      </c>
+    </row>
+    <row r="2332">
+      <c r="A2332" t="inlineStr">
+        <is>
+          <t>8d84fd1f-af80-4348-a90e-a5625cef2683</t>
+        </is>
+      </c>
+      <c r="B2332" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2332" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2332" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2332" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2332" t="n">
+        <v>113.98</v>
+      </c>
+      <c r="G2332" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H2332" s="2" t="n">
+        <v>46084.6629096444</v>
+      </c>
+    </row>
+    <row r="2333">
+      <c r="A2333" t="inlineStr">
+        <is>
+          <t>a4b5b38d-d66c-40f7-b304-5fa65f9938ad</t>
+        </is>
+      </c>
+      <c r="B2333" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2333" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2333" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2333" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2333" t="n">
+        <v>377.87</v>
+      </c>
+      <c r="G2333" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="H2333" s="2" t="n">
+        <v>46068.662909648</v>
+      </c>
+    </row>
+    <row r="2334">
+      <c r="A2334" t="inlineStr">
+        <is>
+          <t>6425aba6-bf69-47f8-b5b8-26a342f83c94</t>
+        </is>
+      </c>
+      <c r="B2334" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2334" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2334" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2334" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2334" t="n">
+        <v>431.21</v>
+      </c>
+      <c r="G2334" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="H2334" s="2" t="n">
+        <v>46071.66290965124</v>
+      </c>
+    </row>
+    <row r="2335">
+      <c r="A2335" t="inlineStr">
+        <is>
+          <t>5b2d358a-489a-4911-96e0-fdf9a9c8a1eb</t>
+        </is>
+      </c>
+      <c r="B2335" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2335" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2335" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2335" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2335" t="n">
+        <v>217.78</v>
+      </c>
+      <c r="G2335" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H2335" s="2" t="n">
+        <v>46088.66290965427</v>
+      </c>
+    </row>
+    <row r="2336">
+      <c r="A2336" t="inlineStr">
+        <is>
+          <t>0c1a1f78-4074-4b07-9742-19630e50f220</t>
+        </is>
+      </c>
+      <c r="B2336" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2336" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2336" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2336" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2336" t="n">
+        <v>243.97</v>
+      </c>
+      <c r="G2336" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H2336" s="2" t="n">
+        <v>46088.66290965791</v>
+      </c>
+    </row>
+    <row r="2337">
+      <c r="A2337" t="inlineStr">
+        <is>
+          <t>1d66a9be-0310-49af-8ad0-346af846c364</t>
+        </is>
+      </c>
+      <c r="B2337" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2337" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2337" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2337" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2337" t="n">
+        <v>491.93</v>
+      </c>
+      <c r="G2337" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="H2337" s="2" t="n">
+        <v>46082.66290966102</v>
+      </c>
+    </row>
+    <row r="2338">
+      <c r="A2338" t="inlineStr">
+        <is>
+          <t>8798528e-9231-4df1-9d84-5511f80fe0f6</t>
+        </is>
+      </c>
+      <c r="B2338" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2338" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2338" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2338" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2338" t="n">
+        <v>414.99</v>
+      </c>
+      <c r="G2338" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="H2338" s="2" t="n">
+        <v>46073.66290966402</v>
+      </c>
+    </row>
+    <row r="2339">
+      <c r="A2339" t="inlineStr">
+        <is>
+          <t>bef8b53d-9eb0-4249-9b4a-45fd6fa2076f</t>
+        </is>
+      </c>
+      <c r="B2339" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2339" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2339" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2339" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2339" t="n">
+        <v>188.02</v>
+      </c>
+      <c r="G2339" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H2339" s="2" t="n">
+        <v>46079.66290966727</v>
+      </c>
+    </row>
+    <row r="2340">
+      <c r="A2340" t="inlineStr">
+        <is>
+          <t>28763725-6f9a-47bb-b4a6-6dda7b11d2f0</t>
+        </is>
+      </c>
+      <c r="B2340" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2340" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2340" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2340" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2340" t="n">
+        <v>278.98</v>
+      </c>
+      <c r="G2340" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="H2340" s="2" t="n">
+        <v>46071.66290967065</v>
+      </c>
+    </row>
+    <row r="2341">
+      <c r="A2341" t="inlineStr">
+        <is>
+          <t>5e90a8a1-e230-4e51-bcfe-c1aae6d9642f</t>
+        </is>
+      </c>
+      <c r="B2341" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2341" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2341" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2341" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2341" t="n">
+        <v>402.16</v>
+      </c>
+      <c r="G2341" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="H2341" s="2" t="n">
+        <v>46070.6629096737</v>
+      </c>
+    </row>
+    <row r="2342">
+      <c r="A2342" t="inlineStr">
+        <is>
+          <t>84dd387b-3539-4550-8575-181bf1bc8746</t>
+        </is>
+      </c>
+      <c r="B2342" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2342" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2342" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2342" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2342" t="n">
+        <v>397.78</v>
+      </c>
+      <c r="G2342" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="H2342" s="2" t="n">
+        <v>46088.66290967681</v>
+      </c>
+    </row>
+    <row r="2343">
+      <c r="A2343" t="inlineStr">
+        <is>
+          <t>2f0bc7a1-0df3-4afa-ab68-5d92f20db075</t>
+        </is>
+      </c>
+      <c r="B2343" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2343" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2343" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2343" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2343" t="n">
+        <v>429.94</v>
+      </c>
+      <c r="G2343" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H2343" s="2" t="n">
+        <v>46072.66290968032</v>
+      </c>
+    </row>
+    <row r="2344">
+      <c r="A2344" t="inlineStr">
+        <is>
+          <t>020ec405-a29a-4371-adec-a2e0f626ea17</t>
+        </is>
+      </c>
+      <c r="B2344" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2344" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2344" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2344" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2344" t="n">
+        <v>138.97</v>
+      </c>
+      <c r="G2344" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H2344" s="2" t="n">
+        <v>46077.66290968398</v>
+      </c>
+    </row>
+    <row r="2345">
+      <c r="A2345" t="inlineStr">
+        <is>
+          <t>5cae5db7-bfe1-42c3-92d3-70e24c389ff2</t>
+        </is>
+      </c>
+      <c r="B2345" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2345" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2345" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2345" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2345" t="n">
+        <v>286.29</v>
+      </c>
+      <c r="G2345" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H2345" s="2" t="n">
+        <v>46088.66290968713</v>
+      </c>
+    </row>
+    <row r="2346">
+      <c r="A2346" t="inlineStr">
+        <is>
+          <t>16f3ed75-63ac-4039-a36e-4c8ce4640a92</t>
+        </is>
+      </c>
+      <c r="B2346" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2346" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2346" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2346" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2346" t="n">
+        <v>233.53</v>
+      </c>
+      <c r="G2346" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H2346" s="2" t="n">
+        <v>46068.66290969027</v>
+      </c>
+    </row>
+    <row r="2347">
+      <c r="A2347" t="inlineStr">
+        <is>
+          <t>92833f02-f426-4a52-a889-0713c8f63b5b</t>
+        </is>
+      </c>
+      <c r="B2347" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2347" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2347" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2347" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2347" t="n">
+        <v>319.5</v>
+      </c>
+      <c r="G2347" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="H2347" s="2" t="n">
+        <v>46088.6629096939</v>
+      </c>
+    </row>
+    <row r="2348">
+      <c r="A2348" t="inlineStr">
+        <is>
+          <t>65955dc3-c0bc-4515-84b8-2035612ffbde</t>
+        </is>
+      </c>
+      <c r="B2348" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2348" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2348" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2348" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2348" t="n">
+        <v>288.58</v>
+      </c>
+      <c r="G2348" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="H2348" s="2" t="n">
+        <v>46088.662909697</v>
+      </c>
+    </row>
+    <row r="2349">
+      <c r="A2349" t="inlineStr">
+        <is>
+          <t>1ea1f901-3f79-49aa-b848-6194430629a3</t>
+        </is>
+      </c>
+      <c r="B2349" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2349" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2349" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2349" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2349" t="n">
+        <v>231.51</v>
+      </c>
+      <c r="G2349" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H2349" s="2" t="n">
+        <v>46087.66290970007</v>
+      </c>
+    </row>
+    <row r="2350">
+      <c r="A2350" t="inlineStr">
+        <is>
+          <t>1c5141f7-1e41-4c98-8beb-9e74d20a77c5</t>
+        </is>
+      </c>
+      <c r="B2350" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2350" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2350" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2350" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2350" t="n">
+        <v>256.71</v>
+      </c>
+      <c r="G2350" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="H2350" s="2" t="n">
+        <v>46084.6629097037</v>
+      </c>
+    </row>
+    <row r="2351">
+      <c r="A2351" t="inlineStr">
+        <is>
+          <t>1e0217bc-f659-452c-98c1-e602e1a7f434</t>
+        </is>
+      </c>
+      <c r="B2351" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2351" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2351" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2351" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2351" t="n">
+        <v>21.31</v>
+      </c>
+      <c r="G2351" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H2351" s="2" t="n">
+        <v>46075.66290970679</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2351"/>
+  <dimension ref="A1:H2401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78705,7 +78705,7 @@
         <v>3.24</v>
       </c>
       <c r="H2302" s="2" t="n">
-        <v>46068.66290954581</v>
+        <v>46068.66290954861</v>
       </c>
     </row>
     <row r="2303">
@@ -78739,7 +78739,7 @@
         <v>0.72</v>
       </c>
       <c r="H2303" s="2" t="n">
-        <v>46096.66290955008</v>
+        <v>46096.66290954861</v>
       </c>
     </row>
     <row r="2304">
@@ -78773,7 +78773,7 @@
         <v>2.89</v>
       </c>
       <c r="H2304" s="2" t="n">
-        <v>46081.66290955381</v>
+        <v>46081.66290954861</v>
       </c>
     </row>
     <row r="2305">
@@ -78807,7 +78807,7 @@
         <v>0.38</v>
       </c>
       <c r="H2305" s="2" t="n">
-        <v>46080.66290955698</v>
+        <v>46080.66290956018</v>
       </c>
     </row>
     <row r="2306">
@@ -78841,7 +78841,7 @@
         <v>2.51</v>
       </c>
       <c r="H2306" s="2" t="n">
-        <v>46084.66290956017</v>
+        <v>46084.66290956018</v>
       </c>
     </row>
     <row r="2307">
@@ -78875,7 +78875,7 @@
         <v>2.53</v>
       </c>
       <c r="H2307" s="2" t="n">
-        <v>46080.66290956341</v>
+        <v>46080.66290956018</v>
       </c>
     </row>
     <row r="2308">
@@ -78909,7 +78909,7 @@
         <v>3.49</v>
       </c>
       <c r="H2308" s="2" t="n">
-        <v>46077.66290956706</v>
+        <v>46077.66290957176</v>
       </c>
     </row>
     <row r="2309">
@@ -78943,7 +78943,7 @@
         <v>1.11</v>
       </c>
       <c r="H2309" s="2" t="n">
-        <v>46090.66290957036</v>
+        <v>46090.66290957176</v>
       </c>
     </row>
     <row r="2310">
@@ -78977,7 +78977,7 @@
         <v>1.54</v>
       </c>
       <c r="H2310" s="2" t="n">
-        <v>46085.66290957366</v>
+        <v>46085.66290957176</v>
       </c>
     </row>
     <row r="2311">
@@ -79011,7 +79011,7 @@
         <v>2.61</v>
       </c>
       <c r="H2311" s="2" t="n">
-        <v>46082.66290957711</v>
+        <v>46082.66290957176</v>
       </c>
     </row>
     <row r="2312">
@@ -79045,7 +79045,7 @@
         <v>4.16</v>
       </c>
       <c r="H2312" s="2" t="n">
-        <v>46091.66290958024</v>
+        <v>46091.66290958333</v>
       </c>
     </row>
     <row r="2313">
@@ -79079,7 +79079,7 @@
         <v>2.09</v>
       </c>
       <c r="H2313" s="2" t="n">
-        <v>46080.6629095833</v>
+        <v>46080.66290958333</v>
       </c>
     </row>
     <row r="2314">
@@ -79113,7 +79113,7 @@
         <v>0.92</v>
       </c>
       <c r="H2314" s="2" t="n">
-        <v>46083.66290958641</v>
+        <v>46083.66290958333</v>
       </c>
     </row>
     <row r="2315">
@@ -79147,7 +79147,7 @@
         <v>1.1</v>
       </c>
       <c r="H2315" s="2" t="n">
-        <v>46090.66290958982</v>
+        <v>46090.66290959491</v>
       </c>
     </row>
     <row r="2316">
@@ -79181,7 +79181,7 @@
         <v>2.85</v>
       </c>
       <c r="H2316" s="2" t="n">
-        <v>46067.66290959282</v>
+        <v>46067.66290959491</v>
       </c>
     </row>
     <row r="2317">
@@ -79215,7 +79215,7 @@
         <v>3.99</v>
       </c>
       <c r="H2317" s="2" t="n">
-        <v>46072.6629095959</v>
+        <v>46072.66290959491</v>
       </c>
     </row>
     <row r="2318">
@@ -79249,7 +79249,7 @@
         <v>0.39</v>
       </c>
       <c r="H2318" s="2" t="n">
-        <v>46074.66290959925</v>
+        <v>46074.66290959491</v>
       </c>
     </row>
     <row r="2319">
@@ -79283,7 +79283,7 @@
         <v>2.99</v>
       </c>
       <c r="H2319" s="2" t="n">
-        <v>46094.66290960226</v>
+        <v>46094.66290960648</v>
       </c>
     </row>
     <row r="2320">
@@ -79317,7 +79317,7 @@
         <v>4.09</v>
       </c>
       <c r="H2320" s="2" t="n">
-        <v>46096.6629096055</v>
+        <v>46096.66290960648</v>
       </c>
     </row>
     <row r="2321">
@@ -79351,7 +79351,7 @@
         <v>2.5</v>
       </c>
       <c r="H2321" s="2" t="n">
-        <v>46095.66290960865</v>
+        <v>46095.66290960648</v>
       </c>
     </row>
     <row r="2322">
@@ -79385,7 +79385,7 @@
         <v>4.13</v>
       </c>
       <c r="H2322" s="2" t="n">
-        <v>46086.66290961237</v>
+        <v>46086.66290961805</v>
       </c>
     </row>
     <row r="2323">
@@ -79419,7 +79419,7 @@
         <v>3.51</v>
       </c>
       <c r="H2323" s="2" t="n">
-        <v>46068.66290961545</v>
+        <v>46068.66290961805</v>
       </c>
     </row>
     <row r="2324">
@@ -79453,7 +79453,7 @@
         <v>3.77</v>
       </c>
       <c r="H2324" s="2" t="n">
-        <v>46074.66290961864</v>
+        <v>46074.66290961805</v>
       </c>
     </row>
     <row r="2325">
@@ -79487,7 +79487,7 @@
         <v>4.3</v>
       </c>
       <c r="H2325" s="2" t="n">
-        <v>46081.66290962209</v>
+        <v>46081.66290961805</v>
       </c>
     </row>
     <row r="2326">
@@ -79521,7 +79521,7 @@
         <v>4.66</v>
       </c>
       <c r="H2326" s="2" t="n">
-        <v>46084.66290962511</v>
+        <v>46084.66290962963</v>
       </c>
     </row>
     <row r="2327">
@@ -79555,7 +79555,7 @@
         <v>0.05</v>
       </c>
       <c r="H2327" s="2" t="n">
-        <v>46095.66290962824</v>
+        <v>46095.66290962963</v>
       </c>
     </row>
     <row r="2328">
@@ -79589,7 +79589,7 @@
         <v>4.82</v>
       </c>
       <c r="H2328" s="2" t="n">
-        <v>46095.66290963128</v>
+        <v>46095.66290962963</v>
       </c>
     </row>
     <row r="2329">
@@ -79623,7 +79623,7 @@
         <v>2.46</v>
       </c>
       <c r="H2329" s="2" t="n">
-        <v>46094.66290963476</v>
+        <v>46094.66290962963</v>
       </c>
     </row>
     <row r="2330">
@@ -79657,7 +79657,7 @@
         <v>2.19</v>
       </c>
       <c r="H2330" s="2" t="n">
-        <v>46084.66290963793</v>
+        <v>46084.66290964121</v>
       </c>
     </row>
     <row r="2331">
@@ -79691,7 +79691,7 @@
         <v>3.07</v>
       </c>
       <c r="H2331" s="2" t="n">
-        <v>46092.66290964109</v>
+        <v>46092.66290964121</v>
       </c>
     </row>
     <row r="2332">
@@ -79725,7 +79725,7 @@
         <v>1.14</v>
       </c>
       <c r="H2332" s="2" t="n">
-        <v>46084.6629096444</v>
+        <v>46084.66290964121</v>
       </c>
     </row>
     <row r="2333">
@@ -79759,7 +79759,7 @@
         <v>3.78</v>
       </c>
       <c r="H2333" s="2" t="n">
-        <v>46068.662909648</v>
+        <v>46068.66290965278</v>
       </c>
     </row>
     <row r="2334">
@@ -79793,7 +79793,7 @@
         <v>4.31</v>
       </c>
       <c r="H2334" s="2" t="n">
-        <v>46071.66290965124</v>
+        <v>46071.66290965278</v>
       </c>
     </row>
     <row r="2335">
@@ -79827,7 +79827,7 @@
         <v>2.18</v>
       </c>
       <c r="H2335" s="2" t="n">
-        <v>46088.66290965427</v>
+        <v>46088.66290965278</v>
       </c>
     </row>
     <row r="2336">
@@ -79861,7 +79861,7 @@
         <v>2.44</v>
       </c>
       <c r="H2336" s="2" t="n">
-        <v>46088.66290965791</v>
+        <v>46088.66290965278</v>
       </c>
     </row>
     <row r="2337">
@@ -79895,7 +79895,7 @@
         <v>4.92</v>
       </c>
       <c r="H2337" s="2" t="n">
-        <v>46082.66290966102</v>
+        <v>46082.66290966435</v>
       </c>
     </row>
     <row r="2338">
@@ -79929,7 +79929,7 @@
         <v>4.15</v>
       </c>
       <c r="H2338" s="2" t="n">
-        <v>46073.66290966402</v>
+        <v>46073.66290966435</v>
       </c>
     </row>
     <row r="2339">
@@ -79963,7 +79963,7 @@
         <v>1.88</v>
       </c>
       <c r="H2339" s="2" t="n">
-        <v>46079.66290966727</v>
+        <v>46079.66290966435</v>
       </c>
     </row>
     <row r="2340">
@@ -79997,7 +79997,7 @@
         <v>2.79</v>
       </c>
       <c r="H2340" s="2" t="n">
-        <v>46071.66290967065</v>
+        <v>46071.66290967593</v>
       </c>
     </row>
     <row r="2341">
@@ -80031,7 +80031,7 @@
         <v>4.02</v>
       </c>
       <c r="H2341" s="2" t="n">
-        <v>46070.6629096737</v>
+        <v>46070.66290967593</v>
       </c>
     </row>
     <row r="2342">
@@ -80065,7 +80065,7 @@
         <v>3.98</v>
       </c>
       <c r="H2342" s="2" t="n">
-        <v>46088.66290967681</v>
+        <v>46088.66290967593</v>
       </c>
     </row>
     <row r="2343">
@@ -80099,7 +80099,7 @@
         <v>4.3</v>
       </c>
       <c r="H2343" s="2" t="n">
-        <v>46072.66290968032</v>
+        <v>46072.66290967593</v>
       </c>
     </row>
     <row r="2344">
@@ -80133,7 +80133,7 @@
         <v>1.39</v>
       </c>
       <c r="H2344" s="2" t="n">
-        <v>46077.66290968398</v>
+        <v>46077.6629096875</v>
       </c>
     </row>
     <row r="2345">
@@ -80167,7 +80167,7 @@
         <v>2.86</v>
       </c>
       <c r="H2345" s="2" t="n">
-        <v>46088.66290968713</v>
+        <v>46088.6629096875</v>
       </c>
     </row>
     <row r="2346">
@@ -80201,7 +80201,7 @@
         <v>2.34</v>
       </c>
       <c r="H2346" s="2" t="n">
-        <v>46068.66290969027</v>
+        <v>46068.6629096875</v>
       </c>
     </row>
     <row r="2347">
@@ -80235,7 +80235,7 @@
         <v>3.19</v>
       </c>
       <c r="H2347" s="2" t="n">
-        <v>46088.6629096939</v>
+        <v>46088.66290969907</v>
       </c>
     </row>
     <row r="2348">
@@ -80269,7 +80269,7 @@
         <v>2.89</v>
       </c>
       <c r="H2348" s="2" t="n">
-        <v>46088.662909697</v>
+        <v>46088.66290969907</v>
       </c>
     </row>
     <row r="2349">
@@ -80303,7 +80303,7 @@
         <v>2.32</v>
       </c>
       <c r="H2349" s="2" t="n">
-        <v>46087.66290970007</v>
+        <v>46087.66290969907</v>
       </c>
     </row>
     <row r="2350">
@@ -80337,7 +80337,7 @@
         <v>2.57</v>
       </c>
       <c r="H2350" s="2" t="n">
-        <v>46084.6629097037</v>
+        <v>46084.66290969907</v>
       </c>
     </row>
     <row r="2351">
@@ -80371,7 +80371,1707 @@
         <v>0.21</v>
       </c>
       <c r="H2351" s="2" t="n">
-        <v>46075.66290970679</v>
+        <v>46075.66290971065</v>
+      </c>
+    </row>
+    <row r="2352">
+      <c r="A2352" t="inlineStr">
+        <is>
+          <t>8ee53f92-00b5-4e9b-a345-b6ba8c3b8ace</t>
+        </is>
+      </c>
+      <c r="B2352" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2352" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2352" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2352" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2352" t="n">
+        <v>84.67</v>
+      </c>
+      <c r="G2352" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H2352" s="2" t="n">
+        <v>46094.69755767121</v>
+      </c>
+    </row>
+    <row r="2353">
+      <c r="A2353" t="inlineStr">
+        <is>
+          <t>5a1cbc0d-ef35-4054-a0fc-cffa8d3b8aaa</t>
+        </is>
+      </c>
+      <c r="B2353" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2353" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2353" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2353" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2353" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="G2353" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H2353" s="2" t="n">
+        <v>46077.69755767562</v>
+      </c>
+    </row>
+    <row r="2354">
+      <c r="A2354" t="inlineStr">
+        <is>
+          <t>126b1ccf-3d8e-4c4a-af67-f9b3be3c5b16</t>
+        </is>
+      </c>
+      <c r="B2354" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2354" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2354" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2354" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2354" t="n">
+        <v>234.02</v>
+      </c>
+      <c r="G2354" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H2354" s="2" t="n">
+        <v>46084.69755767885</v>
+      </c>
+    </row>
+    <row r="2355">
+      <c r="A2355" t="inlineStr">
+        <is>
+          <t>88085fa3-eede-4aeb-9d7a-b7a7258158c9</t>
+        </is>
+      </c>
+      <c r="B2355" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2355" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2355" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2355" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2355" t="n">
+        <v>176.44</v>
+      </c>
+      <c r="G2355" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H2355" s="2" t="n">
+        <v>46087.697557682</v>
+      </c>
+    </row>
+    <row r="2356">
+      <c r="A2356" t="inlineStr">
+        <is>
+          <t>5fdcc6b8-cfd3-453c-b2c0-05a7d5970b49</t>
+        </is>
+      </c>
+      <c r="B2356" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2356" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2356" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2356" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2356" t="n">
+        <v>56.07</v>
+      </c>
+      <c r="G2356" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H2356" s="2" t="n">
+        <v>46093.69755768512</v>
+      </c>
+    </row>
+    <row r="2357">
+      <c r="A2357" t="inlineStr">
+        <is>
+          <t>67a5bb11-ba4a-44f7-bfed-b87f1106825f</t>
+        </is>
+      </c>
+      <c r="B2357" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2357" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2357" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2357" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2357" t="n">
+        <v>261.56</v>
+      </c>
+      <c r="G2357" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H2357" s="2" t="n">
+        <v>46074.69755768875</v>
+      </c>
+    </row>
+    <row r="2358">
+      <c r="A2358" t="inlineStr">
+        <is>
+          <t>dc1a8e75-13bc-49a3-b836-0345e77522d8</t>
+        </is>
+      </c>
+      <c r="B2358" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2358" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2358" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2358" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2358" t="n">
+        <v>247.94</v>
+      </c>
+      <c r="G2358" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H2358" s="2" t="n">
+        <v>46083.69755769186</v>
+      </c>
+    </row>
+    <row r="2359">
+      <c r="A2359" t="inlineStr">
+        <is>
+          <t>563c08df-a4ab-4b6a-bc4f-6a55406a1efb</t>
+        </is>
+      </c>
+      <c r="B2359" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2359" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2359" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2359" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2359" t="n">
+        <v>249.58</v>
+      </c>
+      <c r="G2359" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H2359" s="2" t="n">
+        <v>46090.69755769501</v>
+      </c>
+    </row>
+    <row r="2360">
+      <c r="A2360" t="inlineStr">
+        <is>
+          <t>e88c669b-0165-46b0-a624-706f17ed899a</t>
+        </is>
+      </c>
+      <c r="B2360" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2360" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2360" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2360" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2360" t="n">
+        <v>50.84</v>
+      </c>
+      <c r="G2360" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H2360" s="2" t="n">
+        <v>46083.69755769839</v>
+      </c>
+    </row>
+    <row r="2361">
+      <c r="A2361" t="inlineStr">
+        <is>
+          <t>1349bdca-e4c5-483e-a555-47399dd4aba2</t>
+        </is>
+      </c>
+      <c r="B2361" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2361" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2361" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2361" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2361" t="n">
+        <v>219.05</v>
+      </c>
+      <c r="G2361" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="H2361" s="2" t="n">
+        <v>46088.69755770161</v>
+      </c>
+    </row>
+    <row r="2362">
+      <c r="A2362" t="inlineStr">
+        <is>
+          <t>8e81b166-9423-437d-bb0b-8ba3a57a3b7d</t>
+        </is>
+      </c>
+      <c r="B2362" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2362" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2362" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2362" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2362" t="n">
+        <v>205.58</v>
+      </c>
+      <c r="G2362" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H2362" s="2" t="n">
+        <v>46086.69755770486</v>
+      </c>
+    </row>
+    <row r="2363">
+      <c r="A2363" t="inlineStr">
+        <is>
+          <t>817d0d72-1a27-4618-8a74-4143da57ea33</t>
+        </is>
+      </c>
+      <c r="B2363" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2363" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2363" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2363" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2363" t="n">
+        <v>357.56</v>
+      </c>
+      <c r="G2363" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="H2363" s="2" t="n">
+        <v>46087.69755770793</v>
+      </c>
+    </row>
+    <row r="2364">
+      <c r="A2364" t="inlineStr">
+        <is>
+          <t>545b967f-d66d-4c52-81ba-3d33eaf5aecb</t>
+        </is>
+      </c>
+      <c r="B2364" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2364" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2364" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2364" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2364" t="n">
+        <v>319.49</v>
+      </c>
+      <c r="G2364" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="H2364" s="2" t="n">
+        <v>46077.69755771124</v>
+      </c>
+    </row>
+    <row r="2365">
+      <c r="A2365" t="inlineStr">
+        <is>
+          <t>c625a015-dd88-4d06-b2a0-aef1a164483a</t>
+        </is>
+      </c>
+      <c r="B2365" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2365" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2365" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2365" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2365" t="n">
+        <v>178.73</v>
+      </c>
+      <c r="G2365" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="H2365" s="2" t="n">
+        <v>46094.69755771443</v>
+      </c>
+    </row>
+    <row r="2366">
+      <c r="A2366" t="inlineStr">
+        <is>
+          <t>a0eec741-d1b6-4ae5-bec7-ffdcb194b7f2</t>
+        </is>
+      </c>
+      <c r="B2366" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2366" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2366" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2366" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2366" t="n">
+        <v>56.84</v>
+      </c>
+      <c r="G2366" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H2366" s="2" t="n">
+        <v>46077.69755771765</v>
+      </c>
+    </row>
+    <row r="2367">
+      <c r="A2367" t="inlineStr">
+        <is>
+          <t>17956eb1-a53c-4dd9-9d6f-117df8c2019a</t>
+        </is>
+      </c>
+      <c r="B2367" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2367" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2367" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2367" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2367" t="n">
+        <v>363.74</v>
+      </c>
+      <c r="G2367" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="H2367" s="2" t="n">
+        <v>46091.69755772117</v>
+      </c>
+    </row>
+    <row r="2368">
+      <c r="A2368" t="inlineStr">
+        <is>
+          <t>ca7b7f10-f5d0-4288-b8b2-8d71d5b7f2c1</t>
+        </is>
+      </c>
+      <c r="B2368" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2368" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2368" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2368" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2368" t="n">
+        <v>412.99</v>
+      </c>
+      <c r="G2368" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="H2368" s="2" t="n">
+        <v>46088.69755772442</v>
+      </c>
+    </row>
+    <row r="2369">
+      <c r="A2369" t="inlineStr">
+        <is>
+          <t>29ec5eb3-96fb-48ab-b1c0-18c40e58a1a9</t>
+        </is>
+      </c>
+      <c r="B2369" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2369" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2369" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2369" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2369" t="n">
+        <v>217.72</v>
+      </c>
+      <c r="G2369" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H2369" s="2" t="n">
+        <v>46093.6975577276</v>
+      </c>
+    </row>
+    <row r="2370">
+      <c r="A2370" t="inlineStr">
+        <is>
+          <t>1734a7f8-472b-4c0a-8d13-d5640959cb96</t>
+        </is>
+      </c>
+      <c r="B2370" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2370" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2370" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2370" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2370" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="G2370" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H2370" s="2" t="n">
+        <v>46079.69755773085</v>
+      </c>
+    </row>
+    <row r="2371">
+      <c r="A2371" t="inlineStr">
+        <is>
+          <t>8787d25e-fb77-4ea4-939c-12f1c0fa7957</t>
+        </is>
+      </c>
+      <c r="B2371" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2371" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2371" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2371" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2371" t="n">
+        <v>52</v>
+      </c>
+      <c r="G2371" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H2371" s="2" t="n">
+        <v>46084.69755773411</v>
+      </c>
+    </row>
+    <row r="2372">
+      <c r="A2372" t="inlineStr">
+        <is>
+          <t>f7b78729-3212-4c3e-9d3c-2c0e43541a14</t>
+        </is>
+      </c>
+      <c r="B2372" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2372" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2372" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2372" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2372" t="n">
+        <v>352.08</v>
+      </c>
+      <c r="G2372" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="H2372" s="2" t="n">
+        <v>46081.69755773732</v>
+      </c>
+    </row>
+    <row r="2373">
+      <c r="A2373" t="inlineStr">
+        <is>
+          <t>b560c6e4-517a-4a3b-a643-041c169c4d9b</t>
+        </is>
+      </c>
+      <c r="B2373" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2373" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2373" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2373" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2373" t="n">
+        <v>139.81</v>
+      </c>
+      <c r="G2373" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H2373" s="2" t="n">
+        <v>46090.69755774058</v>
+      </c>
+    </row>
+    <row r="2374">
+      <c r="A2374" t="inlineStr">
+        <is>
+          <t>82c3ceae-3cae-452b-ae21-8e182e3eafff</t>
+        </is>
+      </c>
+      <c r="B2374" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2374" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2374" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2374" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2374" t="n">
+        <v>247.11</v>
+      </c>
+      <c r="G2374" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="H2374" s="2" t="n">
+        <v>46074.69755774397</v>
+      </c>
+    </row>
+    <row r="2375">
+      <c r="A2375" t="inlineStr">
+        <is>
+          <t>50e6e260-bdf5-423d-91b8-f2c4f2d2e378</t>
+        </is>
+      </c>
+      <c r="B2375" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2375" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2375" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2375" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2375" t="n">
+        <v>442.59</v>
+      </c>
+      <c r="G2375" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="H2375" s="2" t="n">
+        <v>46075.6975577472</v>
+      </c>
+    </row>
+    <row r="2376">
+      <c r="A2376" t="inlineStr">
+        <is>
+          <t>9f8575ec-dc9a-4ea0-b12b-1b5347ccc8cb</t>
+        </is>
+      </c>
+      <c r="B2376" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2376" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2376" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2376" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2376" t="n">
+        <v>414.31</v>
+      </c>
+      <c r="G2376" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H2376" s="2" t="n">
+        <v>46076.69755775029</v>
+      </c>
+    </row>
+    <row r="2377">
+      <c r="A2377" t="inlineStr">
+        <is>
+          <t>db81d2a5-1e18-413a-9064-e38927c52d3a</t>
+        </is>
+      </c>
+      <c r="B2377" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2377" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2377" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2377" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2377" t="n">
+        <v>291.11</v>
+      </c>
+      <c r="G2377" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="H2377" s="2" t="n">
+        <v>46095.69755775353</v>
+      </c>
+    </row>
+    <row r="2378">
+      <c r="A2378" t="inlineStr">
+        <is>
+          <t>1c0612d5-755a-46f5-aa2a-c057576cb095</t>
+        </is>
+      </c>
+      <c r="B2378" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2378" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2378" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2378" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2378" t="n">
+        <v>208.09</v>
+      </c>
+      <c r="G2378" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H2378" s="2" t="n">
+        <v>46081.69755775675</v>
+      </c>
+    </row>
+    <row r="2379">
+      <c r="A2379" t="inlineStr">
+        <is>
+          <t>bc77bce4-9b7d-40d5-aa33-e2f6d812d634</t>
+        </is>
+      </c>
+      <c r="B2379" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2379" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2379" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2379" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2379" t="n">
+        <v>255.66</v>
+      </c>
+      <c r="G2379" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H2379" s="2" t="n">
+        <v>46076.69755775985</v>
+      </c>
+    </row>
+    <row r="2380">
+      <c r="A2380" t="inlineStr">
+        <is>
+          <t>ac2d4a18-fd16-4aac-a931-d2c3d402f2b4</t>
+        </is>
+      </c>
+      <c r="B2380" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2380" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2380" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2380" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2380" t="n">
+        <v>305.48</v>
+      </c>
+      <c r="G2380" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H2380" s="2" t="n">
+        <v>46075.69755776288</v>
+      </c>
+    </row>
+    <row r="2381">
+      <c r="A2381" t="inlineStr">
+        <is>
+          <t>70714f33-29c6-4cfe-8bf1-34e86c4045e5</t>
+        </is>
+      </c>
+      <c r="B2381" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2381" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2381" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2381" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2381" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="G2381" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H2381" s="2" t="n">
+        <v>46080.69755776592</v>
+      </c>
+    </row>
+    <row r="2382">
+      <c r="A2382" t="inlineStr">
+        <is>
+          <t>f21a1aeb-be4c-41b0-9df1-9c6d593db47e</t>
+        </is>
+      </c>
+      <c r="B2382" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2382" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2382" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2382" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2382" t="n">
+        <v>496.97</v>
+      </c>
+      <c r="G2382" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="H2382" s="2" t="n">
+        <v>46075.69755776941</v>
+      </c>
+    </row>
+    <row r="2383">
+      <c r="A2383" t="inlineStr">
+        <is>
+          <t>d94cb259-7a3f-4296-ac2f-8f19a2a5ac16</t>
+        </is>
+      </c>
+      <c r="B2383" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2383" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2383" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2383" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2383" t="n">
+        <v>277.62</v>
+      </c>
+      <c r="G2383" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="H2383" s="2" t="n">
+        <v>46074.69755777259</v>
+      </c>
+    </row>
+    <row r="2384">
+      <c r="A2384" t="inlineStr">
+        <is>
+          <t>ad00dbe2-a5bb-4839-a50c-d5f8a19300dc</t>
+        </is>
+      </c>
+      <c r="B2384" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2384" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2384" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2384" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2384" t="n">
+        <v>206.22</v>
+      </c>
+      <c r="G2384" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H2384" s="2" t="n">
+        <v>46095.69755777582</v>
+      </c>
+    </row>
+    <row r="2385">
+      <c r="A2385" t="inlineStr">
+        <is>
+          <t>7995fc49-ca7d-492a-b622-4c4663454c55</t>
+        </is>
+      </c>
+      <c r="B2385" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2385" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2385" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2385" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2385" t="n">
+        <v>180.38</v>
+      </c>
+      <c r="G2385" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H2385" s="2" t="n">
+        <v>46077.69755777964</v>
+      </c>
+    </row>
+    <row r="2386">
+      <c r="A2386" t="inlineStr">
+        <is>
+          <t>58c1e21f-b64d-4c7a-b385-c5e0ff5ac63a</t>
+        </is>
+      </c>
+      <c r="B2386" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2386" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2386" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2386" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2386" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="G2386" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H2386" s="2" t="n">
+        <v>46084.69755778291</v>
+      </c>
+    </row>
+    <row r="2387">
+      <c r="A2387" t="inlineStr">
+        <is>
+          <t>ad3bd7e7-0637-4efd-90c2-caea62717344</t>
+        </is>
+      </c>
+      <c r="B2387" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2387" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2387" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2387" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2387" t="n">
+        <v>337.22</v>
+      </c>
+      <c r="G2387" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="H2387" s="2" t="n">
+        <v>46095.69755778616</v>
+      </c>
+    </row>
+    <row r="2388">
+      <c r="A2388" t="inlineStr">
+        <is>
+          <t>93dbde4d-8c8c-4289-a46d-dd8c08cbe862</t>
+        </is>
+      </c>
+      <c r="B2388" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2388" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2388" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2388" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2388" t="n">
+        <v>186.99</v>
+      </c>
+      <c r="G2388" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H2388" s="2" t="n">
+        <v>46095.6975577894</v>
+      </c>
+    </row>
+    <row r="2389">
+      <c r="A2389" t="inlineStr">
+        <is>
+          <t>c38cd175-8579-40b8-b364-bbc1f0a471a1</t>
+        </is>
+      </c>
+      <c r="B2389" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2389" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2389" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2389" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2389" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="G2389" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H2389" s="2" t="n">
+        <v>46076.69755779304</v>
+      </c>
+    </row>
+    <row r="2390">
+      <c r="A2390" t="inlineStr">
+        <is>
+          <t>4a26d1be-1adc-4ce4-ba57-c86fae5ce1e3</t>
+        </is>
+      </c>
+      <c r="B2390" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2390" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2390" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2390" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2390" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="G2390" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2390" s="2" t="n">
+        <v>46078.69755779609</v>
+      </c>
+    </row>
+    <row r="2391">
+      <c r="A2391" t="inlineStr">
+        <is>
+          <t>2834e73a-ab31-454e-a016-ac73c636849d</t>
+        </is>
+      </c>
+      <c r="B2391" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2391" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2391" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2391" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2391" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="G2391" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="H2391" s="2" t="n">
+        <v>46086.69755779931</v>
+      </c>
+    </row>
+    <row r="2392">
+      <c r="A2392" t="inlineStr">
+        <is>
+          <t>8041be33-7439-47b7-bff2-b240a37e8f00</t>
+        </is>
+      </c>
+      <c r="B2392" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2392" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2392" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2392" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2392" t="n">
+        <v>276.24</v>
+      </c>
+      <c r="G2392" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H2392" s="2" t="n">
+        <v>46082.69755780254</v>
+      </c>
+    </row>
+    <row r="2393">
+      <c r="A2393" t="inlineStr">
+        <is>
+          <t>3f4de967-6232-4ab8-ba6b-18ab1a0c7771</t>
+        </is>
+      </c>
+      <c r="B2393" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2393" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2393" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2393" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2393" t="n">
+        <v>192.89</v>
+      </c>
+      <c r="G2393" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H2393" s="2" t="n">
+        <v>46074.69755780578</v>
+      </c>
+    </row>
+    <row r="2394">
+      <c r="A2394" t="inlineStr">
+        <is>
+          <t>1c8172dc-1d70-4598-a183-1bb1e9c92597</t>
+        </is>
+      </c>
+      <c r="B2394" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2394" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2394" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2394" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2394" t="n">
+        <v>136.75</v>
+      </c>
+      <c r="G2394" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H2394" s="2" t="n">
+        <v>46069.69755780883</v>
+      </c>
+    </row>
+    <row r="2395">
+      <c r="A2395" t="inlineStr">
+        <is>
+          <t>8171f951-9992-4b9a-8df5-17515bc80fe4</t>
+        </is>
+      </c>
+      <c r="B2395" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2395" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2395" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2395" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2395" t="n">
+        <v>32.04</v>
+      </c>
+      <c r="G2395" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H2395" s="2" t="n">
+        <v>46080.69755781193</v>
+      </c>
+    </row>
+    <row r="2396">
+      <c r="A2396" t="inlineStr">
+        <is>
+          <t>a707730f-2d23-4299-95ab-0578b89410a4</t>
+        </is>
+      </c>
+      <c r="B2396" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2396" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2396" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2396" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2396" t="n">
+        <v>67.38</v>
+      </c>
+      <c r="G2396" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H2396" s="2" t="n">
+        <v>46075.69755781522</v>
+      </c>
+    </row>
+    <row r="2397">
+      <c r="A2397" t="inlineStr">
+        <is>
+          <t>d59db450-a4b3-4ae5-9f9f-a3c7fd7d089e</t>
+        </is>
+      </c>
+      <c r="B2397" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2397" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2397" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2397" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2397" t="n">
+        <v>324.79</v>
+      </c>
+      <c r="G2397" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H2397" s="2" t="n">
+        <v>46082.69755781844</v>
+      </c>
+    </row>
+    <row r="2398">
+      <c r="A2398" t="inlineStr">
+        <is>
+          <t>4fc79177-fb8f-4956-b3fd-d5aa2e4990fc</t>
+        </is>
+      </c>
+      <c r="B2398" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2398" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2398" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2398" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2398" t="n">
+        <v>173.96</v>
+      </c>
+      <c r="G2398" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="H2398" s="2" t="n">
+        <v>46084.69755782148</v>
+      </c>
+    </row>
+    <row r="2399">
+      <c r="A2399" t="inlineStr">
+        <is>
+          <t>ef0cd6a6-bcce-4f0d-971b-303624ae411f</t>
+        </is>
+      </c>
+      <c r="B2399" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2399" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2399" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2399" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2399" t="n">
+        <v>246.09</v>
+      </c>
+      <c r="G2399" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H2399" s="2" t="n">
+        <v>46093.69755782468</v>
+      </c>
+    </row>
+    <row r="2400">
+      <c r="A2400" t="inlineStr">
+        <is>
+          <t>a6967ce5-0a9a-40ea-9b6b-2048a24c3717</t>
+        </is>
+      </c>
+      <c r="B2400" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2400" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2400" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2400" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2400" t="n">
+        <v>258.55</v>
+      </c>
+      <c r="G2400" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="H2400" s="2" t="n">
+        <v>46093.69755782837</v>
+      </c>
+    </row>
+    <row r="2401">
+      <c r="A2401" t="inlineStr">
+        <is>
+          <t>f23c30b6-0274-4df2-b763-c85e77ce4017</t>
+        </is>
+      </c>
+      <c r="B2401" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2401" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2401" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2401" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2401" t="n">
+        <v>156.58</v>
+      </c>
+      <c r="G2401" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H2401" s="2" t="n">
+        <v>46078.69755783154</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2401"/>
+  <dimension ref="A1:H2451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80405,7 +80405,7 @@
         <v>0.85</v>
       </c>
       <c r="H2352" s="2" t="n">
-        <v>46094.69755767121</v>
+        <v>46094.69755767361</v>
       </c>
     </row>
     <row r="2353">
@@ -80439,7 +80439,7 @@
         <v>1.18</v>
       </c>
       <c r="H2353" s="2" t="n">
-        <v>46077.69755767562</v>
+        <v>46077.69755767361</v>
       </c>
     </row>
     <row r="2354">
@@ -80473,7 +80473,7 @@
         <v>2.34</v>
       </c>
       <c r="H2354" s="2" t="n">
-        <v>46084.69755767885</v>
+        <v>46084.69755767361</v>
       </c>
     </row>
     <row r="2355">
@@ -80507,7 +80507,7 @@
         <v>1.76</v>
       </c>
       <c r="H2355" s="2" t="n">
-        <v>46087.697557682</v>
+        <v>46087.69755768518</v>
       </c>
     </row>
     <row r="2356">
@@ -80541,7 +80541,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="H2356" s="2" t="n">
-        <v>46093.69755768512</v>
+        <v>46093.69755768518</v>
       </c>
     </row>
     <row r="2357">
@@ -80575,7 +80575,7 @@
         <v>2.62</v>
       </c>
       <c r="H2357" s="2" t="n">
-        <v>46074.69755768875</v>
+        <v>46074.69755768518</v>
       </c>
     </row>
     <row r="2358">
@@ -80609,7 +80609,7 @@
         <v>2.48</v>
       </c>
       <c r="H2358" s="2" t="n">
-        <v>46083.69755769186</v>
+        <v>46083.69755769676</v>
       </c>
     </row>
     <row r="2359">
@@ -80643,7 +80643,7 @@
         <v>2.5</v>
       </c>
       <c r="H2359" s="2" t="n">
-        <v>46090.69755769501</v>
+        <v>46090.69755769676</v>
       </c>
     </row>
     <row r="2360">
@@ -80677,7 +80677,7 @@
         <v>0.51</v>
       </c>
       <c r="H2360" s="2" t="n">
-        <v>46083.69755769839</v>
+        <v>46083.69755769676</v>
       </c>
     </row>
     <row r="2361">
@@ -80711,7 +80711,7 @@
         <v>2.19</v>
       </c>
       <c r="H2361" s="2" t="n">
-        <v>46088.69755770161</v>
+        <v>46088.69755769676</v>
       </c>
     </row>
     <row r="2362">
@@ -80745,7 +80745,7 @@
         <v>2.06</v>
       </c>
       <c r="H2362" s="2" t="n">
-        <v>46086.69755770486</v>
+        <v>46086.69755770834</v>
       </c>
     </row>
     <row r="2363">
@@ -80779,7 +80779,7 @@
         <v>3.58</v>
       </c>
       <c r="H2363" s="2" t="n">
-        <v>46087.69755770793</v>
+        <v>46087.69755770834</v>
       </c>
     </row>
     <row r="2364">
@@ -80813,7 +80813,7 @@
         <v>3.19</v>
       </c>
       <c r="H2364" s="2" t="n">
-        <v>46077.69755771124</v>
+        <v>46077.69755770834</v>
       </c>
     </row>
     <row r="2365">
@@ -80847,7 +80847,7 @@
         <v>1.79</v>
       </c>
       <c r="H2365" s="2" t="n">
-        <v>46094.69755771443</v>
+        <v>46094.6975577199</v>
       </c>
     </row>
     <row r="2366">
@@ -80881,7 +80881,7 @@
         <v>0.57</v>
       </c>
       <c r="H2366" s="2" t="n">
-        <v>46077.69755771765</v>
+        <v>46077.6975577199</v>
       </c>
     </row>
     <row r="2367">
@@ -80915,7 +80915,7 @@
         <v>3.64</v>
       </c>
       <c r="H2367" s="2" t="n">
-        <v>46091.69755772117</v>
+        <v>46091.6975577199</v>
       </c>
     </row>
     <row r="2368">
@@ -80949,7 +80949,7 @@
         <v>4.13</v>
       </c>
       <c r="H2368" s="2" t="n">
-        <v>46088.69755772442</v>
+        <v>46088.6975577199</v>
       </c>
     </row>
     <row r="2369">
@@ -80983,7 +80983,7 @@
         <v>2.18</v>
       </c>
       <c r="H2369" s="2" t="n">
-        <v>46093.6975577276</v>
+        <v>46093.69755773148</v>
       </c>
     </row>
     <row r="2370">
@@ -81017,7 +81017,7 @@
         <v>0.02</v>
       </c>
       <c r="H2370" s="2" t="n">
-        <v>46079.69755773085</v>
+        <v>46079.69755773148</v>
       </c>
     </row>
     <row r="2371">
@@ -81051,7 +81051,7 @@
         <v>0.52</v>
       </c>
       <c r="H2371" s="2" t="n">
-        <v>46084.69755773411</v>
+        <v>46084.69755773148</v>
       </c>
     </row>
     <row r="2372">
@@ -81085,7 +81085,7 @@
         <v>3.52</v>
       </c>
       <c r="H2372" s="2" t="n">
-        <v>46081.69755773732</v>
+        <v>46081.69755774306</v>
       </c>
     </row>
     <row r="2373">
@@ -81119,7 +81119,7 @@
         <v>1.4</v>
       </c>
       <c r="H2373" s="2" t="n">
-        <v>46090.69755774058</v>
+        <v>46090.69755774306</v>
       </c>
     </row>
     <row r="2374">
@@ -81153,7 +81153,7 @@
         <v>2.47</v>
       </c>
       <c r="H2374" s="2" t="n">
-        <v>46074.69755774397</v>
+        <v>46074.69755774306</v>
       </c>
     </row>
     <row r="2375">
@@ -81187,7 +81187,7 @@
         <v>4.43</v>
       </c>
       <c r="H2375" s="2" t="n">
-        <v>46075.6975577472</v>
+        <v>46075.69755774306</v>
       </c>
     </row>
     <row r="2376">
@@ -81221,7 +81221,7 @@
         <v>4.14</v>
       </c>
       <c r="H2376" s="2" t="n">
-        <v>46076.69755775029</v>
+        <v>46076.69755775463</v>
       </c>
     </row>
     <row r="2377">
@@ -81255,7 +81255,7 @@
         <v>2.91</v>
       </c>
       <c r="H2377" s="2" t="n">
-        <v>46095.69755775353</v>
+        <v>46095.69755775463</v>
       </c>
     </row>
     <row r="2378">
@@ -81289,7 +81289,7 @@
         <v>2.08</v>
       </c>
       <c r="H2378" s="2" t="n">
-        <v>46081.69755775675</v>
+        <v>46081.69755775463</v>
       </c>
     </row>
     <row r="2379">
@@ -81323,7 +81323,7 @@
         <v>2.56</v>
       </c>
       <c r="H2379" s="2" t="n">
-        <v>46076.69755775985</v>
+        <v>46076.69755775463</v>
       </c>
     </row>
     <row r="2380">
@@ -81357,7 +81357,7 @@
         <v>3.05</v>
       </c>
       <c r="H2380" s="2" t="n">
-        <v>46075.69755776288</v>
+        <v>46075.6975577662</v>
       </c>
     </row>
     <row r="2381">
@@ -81391,7 +81391,7 @@
         <v>0.22</v>
       </c>
       <c r="H2381" s="2" t="n">
-        <v>46080.69755776592</v>
+        <v>46080.6975577662</v>
       </c>
     </row>
     <row r="2382">
@@ -81425,7 +81425,7 @@
         <v>4.97</v>
       </c>
       <c r="H2382" s="2" t="n">
-        <v>46075.69755776941</v>
+        <v>46075.6975577662</v>
       </c>
     </row>
     <row r="2383">
@@ -81459,7 +81459,7 @@
         <v>2.78</v>
       </c>
       <c r="H2383" s="2" t="n">
-        <v>46074.69755777259</v>
+        <v>46074.69755777778</v>
       </c>
     </row>
     <row r="2384">
@@ -81493,7 +81493,7 @@
         <v>2.06</v>
       </c>
       <c r="H2384" s="2" t="n">
-        <v>46095.69755777582</v>
+        <v>46095.69755777778</v>
       </c>
     </row>
     <row r="2385">
@@ -81527,7 +81527,7 @@
         <v>1.8</v>
       </c>
       <c r="H2385" s="2" t="n">
-        <v>46077.69755777964</v>
+        <v>46077.69755777778</v>
       </c>
     </row>
     <row r="2386">
@@ -81561,7 +81561,7 @@
         <v>0.13</v>
       </c>
       <c r="H2386" s="2" t="n">
-        <v>46084.69755778291</v>
+        <v>46084.69755777778</v>
       </c>
     </row>
     <row r="2387">
@@ -81595,7 +81595,7 @@
         <v>3.37</v>
       </c>
       <c r="H2387" s="2" t="n">
-        <v>46095.69755778616</v>
+        <v>46095.69755778935</v>
       </c>
     </row>
     <row r="2388">
@@ -81629,7 +81629,7 @@
         <v>1.87</v>
       </c>
       <c r="H2388" s="2" t="n">
-        <v>46095.6975577894</v>
+        <v>46095.69755778935</v>
       </c>
     </row>
     <row r="2389">
@@ -81663,7 +81663,7 @@
         <v>1.14</v>
       </c>
       <c r="H2389" s="2" t="n">
-        <v>46076.69755779304</v>
+        <v>46076.69755778935</v>
       </c>
     </row>
     <row r="2390">
@@ -81697,7 +81697,7 @@
         <v>0.1</v>
       </c>
       <c r="H2390" s="2" t="n">
-        <v>46078.69755779609</v>
+        <v>46078.69755780092</v>
       </c>
     </row>
     <row r="2391">
@@ -81731,7 +81731,7 @@
         <v>2.27</v>
       </c>
       <c r="H2391" s="2" t="n">
-        <v>46086.69755779931</v>
+        <v>46086.69755780092</v>
       </c>
     </row>
     <row r="2392">
@@ -81765,7 +81765,7 @@
         <v>2.76</v>
       </c>
       <c r="H2392" s="2" t="n">
-        <v>46082.69755780254</v>
+        <v>46082.69755780092</v>
       </c>
     </row>
     <row r="2393">
@@ -81799,7 +81799,7 @@
         <v>1.93</v>
       </c>
       <c r="H2393" s="2" t="n">
-        <v>46074.69755780578</v>
+        <v>46074.69755780092</v>
       </c>
     </row>
     <row r="2394">
@@ -81833,7 +81833,7 @@
         <v>1.37</v>
       </c>
       <c r="H2394" s="2" t="n">
-        <v>46069.69755780883</v>
+        <v>46069.6975578125</v>
       </c>
     </row>
     <row r="2395">
@@ -81867,7 +81867,7 @@
         <v>0.32</v>
       </c>
       <c r="H2395" s="2" t="n">
-        <v>46080.69755781193</v>
+        <v>46080.6975578125</v>
       </c>
     </row>
     <row r="2396">
@@ -81901,7 +81901,7 @@
         <v>0.67</v>
       </c>
       <c r="H2396" s="2" t="n">
-        <v>46075.69755781522</v>
+        <v>46075.6975578125</v>
       </c>
     </row>
     <row r="2397">
@@ -81935,7 +81935,7 @@
         <v>3.25</v>
       </c>
       <c r="H2397" s="2" t="n">
-        <v>46082.69755781844</v>
+        <v>46082.69755782407</v>
       </c>
     </row>
     <row r="2398">
@@ -81969,7 +81969,7 @@
         <v>1.74</v>
       </c>
       <c r="H2398" s="2" t="n">
-        <v>46084.69755782148</v>
+        <v>46084.69755782407</v>
       </c>
     </row>
     <row r="2399">
@@ -82003,7 +82003,7 @@
         <v>2.46</v>
       </c>
       <c r="H2399" s="2" t="n">
-        <v>46093.69755782468</v>
+        <v>46093.69755782407</v>
       </c>
     </row>
     <row r="2400">
@@ -82037,7 +82037,7 @@
         <v>2.59</v>
       </c>
       <c r="H2400" s="2" t="n">
-        <v>46093.69755782837</v>
+        <v>46093.69755782407</v>
       </c>
     </row>
     <row r="2401">
@@ -82071,7 +82071,1707 @@
         <v>1.57</v>
       </c>
       <c r="H2401" s="2" t="n">
-        <v>46078.69755783154</v>
+        <v>46078.69755783565</v>
+      </c>
+    </row>
+    <row r="2402">
+      <c r="A2402" t="inlineStr">
+        <is>
+          <t>24445bb1-b2be-4ee2-a3e5-b0cff7079b1b</t>
+        </is>
+      </c>
+      <c r="B2402" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2402" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2402" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2402" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2402" t="n">
+        <v>66.36</v>
+      </c>
+      <c r="G2402" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H2402" s="2" t="n">
+        <v>46077.09886646964</v>
+      </c>
+    </row>
+    <row r="2403">
+      <c r="A2403" t="inlineStr">
+        <is>
+          <t>2fe40e26-020d-4a77-83c8-5cf1095b18bd</t>
+        </is>
+      </c>
+      <c r="B2403" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2403" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2403" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2403" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2403" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="G2403" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H2403" s="2" t="n">
+        <v>46068.09886647403</v>
+      </c>
+    </row>
+    <row r="2404">
+      <c r="A2404" t="inlineStr">
+        <is>
+          <t>44051e06-8a8d-4544-90bb-75c2ec61e0dd</t>
+        </is>
+      </c>
+      <c r="B2404" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2404" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2404" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2404" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2404" t="n">
+        <v>437.35</v>
+      </c>
+      <c r="G2404" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="H2404" s="2" t="n">
+        <v>46084.09886647718</v>
+      </c>
+    </row>
+    <row r="2405">
+      <c r="A2405" t="inlineStr">
+        <is>
+          <t>43f046a0-e8f6-4053-993d-943602cdd01a</t>
+        </is>
+      </c>
+      <c r="B2405" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2405" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2405" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2405" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2405" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="G2405" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H2405" s="2" t="n">
+        <v>46075.09886648028</v>
+      </c>
+    </row>
+    <row r="2406">
+      <c r="A2406" t="inlineStr">
+        <is>
+          <t>1a91ff77-2dca-4ad1-a822-1b390fc62777</t>
+        </is>
+      </c>
+      <c r="B2406" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2406" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2406" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2406" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2406" t="n">
+        <v>486.99</v>
+      </c>
+      <c r="G2406" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="H2406" s="2" t="n">
+        <v>46091.0988664833</v>
+      </c>
+    </row>
+    <row r="2407">
+      <c r="A2407" t="inlineStr">
+        <is>
+          <t>216aa74a-a686-404b-a317-cd7228ada186</t>
+        </is>
+      </c>
+      <c r="B2407" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2407" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2407" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2407" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2407" t="n">
+        <v>284.09</v>
+      </c>
+      <c r="G2407" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="H2407" s="2" t="n">
+        <v>46093.09886648663</v>
+      </c>
+    </row>
+    <row r="2408">
+      <c r="A2408" t="inlineStr">
+        <is>
+          <t>333e61c3-893e-4e71-bbc2-df766cd70213</t>
+        </is>
+      </c>
+      <c r="B2408" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2408" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2408" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2408" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2408" t="n">
+        <v>171.16</v>
+      </c>
+      <c r="G2408" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H2408" s="2" t="n">
+        <v>46093.09886648942</v>
+      </c>
+    </row>
+    <row r="2409">
+      <c r="A2409" t="inlineStr">
+        <is>
+          <t>9f9299b7-5b94-4000-90c6-4761fc6bd124</t>
+        </is>
+      </c>
+      <c r="B2409" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2409" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2409" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2409" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2409" t="n">
+        <v>108.19</v>
+      </c>
+      <c r="G2409" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="H2409" s="2" t="n">
+        <v>46095.09886649226</v>
+      </c>
+    </row>
+    <row r="2410">
+      <c r="A2410" t="inlineStr">
+        <is>
+          <t>a0e4fbef-f6cc-4ac9-9095-b9732953e0ce</t>
+        </is>
+      </c>
+      <c r="B2410" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2410" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2410" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2410" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2410" t="n">
+        <v>108.74</v>
+      </c>
+      <c r="G2410" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H2410" s="2" t="n">
+        <v>46069.09886649519</v>
+      </c>
+    </row>
+    <row r="2411">
+      <c r="A2411" t="inlineStr">
+        <is>
+          <t>2ca29d33-4246-452e-9901-ed3094e5d080</t>
+        </is>
+      </c>
+      <c r="B2411" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2411" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2411" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2411" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2411" t="n">
+        <v>87.51000000000001</v>
+      </c>
+      <c r="G2411" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H2411" s="2" t="n">
+        <v>46089.09886649823</v>
+      </c>
+    </row>
+    <row r="2412">
+      <c r="A2412" t="inlineStr">
+        <is>
+          <t>da9fca0b-1c40-42c3-a735-59e6cb0cf343</t>
+        </is>
+      </c>
+      <c r="B2412" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2412" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2412" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2412" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2412" t="n">
+        <v>225.57</v>
+      </c>
+      <c r="G2412" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H2412" s="2" t="n">
+        <v>46097.0988665013</v>
+      </c>
+    </row>
+    <row r="2413">
+      <c r="A2413" t="inlineStr">
+        <is>
+          <t>d19d8f3c-2b4a-4349-b004-707ca90a24ba</t>
+        </is>
+      </c>
+      <c r="B2413" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2413" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2413" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2413" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2413" t="n">
+        <v>248.19</v>
+      </c>
+      <c r="G2413" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H2413" s="2" t="n">
+        <v>46085.09886650425</v>
+      </c>
+    </row>
+    <row r="2414">
+      <c r="A2414" t="inlineStr">
+        <is>
+          <t>33b48840-c335-4474-9eee-78430e04f7ee</t>
+        </is>
+      </c>
+      <c r="B2414" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2414" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2414" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2414" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2414" t="n">
+        <v>240.28</v>
+      </c>
+      <c r="G2414" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H2414" s="2" t="n">
+        <v>46081.09886650755</v>
+      </c>
+    </row>
+    <row r="2415">
+      <c r="A2415" t="inlineStr">
+        <is>
+          <t>cb3742fd-c3d1-43ee-813f-02c4fe0057b3</t>
+        </is>
+      </c>
+      <c r="B2415" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2415" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2415" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2415" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2415" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="G2415" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H2415" s="2" t="n">
+        <v>46087.09886651049</v>
+      </c>
+    </row>
+    <row r="2416">
+      <c r="A2416" t="inlineStr">
+        <is>
+          <t>d48dfa77-5bdc-4b11-a06a-0a0db3b818f8</t>
+        </is>
+      </c>
+      <c r="B2416" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2416" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2416" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2416" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2416" t="n">
+        <v>161.12</v>
+      </c>
+      <c r="G2416" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H2416" s="2" t="n">
+        <v>46090.09886651341</v>
+      </c>
+    </row>
+    <row r="2417">
+      <c r="A2417" t="inlineStr">
+        <is>
+          <t>15ba3b94-e7d2-4c5b-9226-02a613abdd85</t>
+        </is>
+      </c>
+      <c r="B2417" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2417" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2417" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2417" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2417" t="n">
+        <v>220.36</v>
+      </c>
+      <c r="G2417" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H2417" s="2" t="n">
+        <v>46094.09886651627</v>
+      </c>
+    </row>
+    <row r="2418">
+      <c r="A2418" t="inlineStr">
+        <is>
+          <t>86c98db0-b356-4ff5-be7b-b2acbd788f8c</t>
+        </is>
+      </c>
+      <c r="B2418" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2418" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2418" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2418" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2418" t="n">
+        <v>336.48</v>
+      </c>
+      <c r="G2418" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="H2418" s="2" t="n">
+        <v>46069.09886651917</v>
+      </c>
+    </row>
+    <row r="2419">
+      <c r="A2419" t="inlineStr">
+        <is>
+          <t>69b68105-7363-4183-b329-793fea245f17</t>
+        </is>
+      </c>
+      <c r="B2419" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2419" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2419" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2419" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2419" t="n">
+        <v>156.34</v>
+      </c>
+      <c r="G2419" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H2419" s="2" t="n">
+        <v>46077.09886652207</v>
+      </c>
+    </row>
+    <row r="2420">
+      <c r="A2420" t="inlineStr">
+        <is>
+          <t>fb2a3646-ccaf-4f66-8fc8-153e864c707d</t>
+        </is>
+      </c>
+      <c r="B2420" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2420" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2420" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2420" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2420" t="n">
+        <v>320.72</v>
+      </c>
+      <c r="G2420" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="H2420" s="2" t="n">
+        <v>46089.0988665249</v>
+      </c>
+    </row>
+    <row r="2421">
+      <c r="A2421" t="inlineStr">
+        <is>
+          <t>3328a968-1fde-4ef0-a9d0-23167ea27668</t>
+        </is>
+      </c>
+      <c r="B2421" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2421" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2421" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2421" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2421" t="n">
+        <v>316.66</v>
+      </c>
+      <c r="G2421" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="H2421" s="2" t="n">
+        <v>46080.09886652783</v>
+      </c>
+    </row>
+    <row r="2422">
+      <c r="A2422" t="inlineStr">
+        <is>
+          <t>4dd523fd-01fc-48be-a8c4-c43bbbfb6ce3</t>
+        </is>
+      </c>
+      <c r="B2422" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2422" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2422" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2422" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2422" t="n">
+        <v>471.06</v>
+      </c>
+      <c r="G2422" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="H2422" s="2" t="n">
+        <v>46097.09886653071</v>
+      </c>
+    </row>
+    <row r="2423">
+      <c r="A2423" t="inlineStr">
+        <is>
+          <t>af55e2e4-0c2a-49d6-83c8-0956a3023db5</t>
+        </is>
+      </c>
+      <c r="B2423" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2423" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2423" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2423" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2423" t="n">
+        <v>479.38</v>
+      </c>
+      <c r="G2423" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="H2423" s="2" t="n">
+        <v>46070.09886653395</v>
+      </c>
+    </row>
+    <row r="2424">
+      <c r="A2424" t="inlineStr">
+        <is>
+          <t>f2c0eb21-aed2-4153-8c57-d7f056964ff6</t>
+        </is>
+      </c>
+      <c r="B2424" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2424" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2424" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2424" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2424" t="n">
+        <v>199.17</v>
+      </c>
+      <c r="G2424" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H2424" s="2" t="n">
+        <v>46084.09886653691</v>
+      </c>
+    </row>
+    <row r="2425">
+      <c r="A2425" t="inlineStr">
+        <is>
+          <t>39c6c53f-269f-41e8-8a28-0d0720307161</t>
+        </is>
+      </c>
+      <c r="B2425" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2425" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2425" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2425" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2425" t="n">
+        <v>177.31</v>
+      </c>
+      <c r="G2425" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H2425" s="2" t="n">
+        <v>46075.09886653969</v>
+      </c>
+    </row>
+    <row r="2426">
+      <c r="A2426" t="inlineStr">
+        <is>
+          <t>ccb6cf24-22ee-4821-8365-7214f97514b7</t>
+        </is>
+      </c>
+      <c r="B2426" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2426" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2426" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2426" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2426" t="n">
+        <v>120.43</v>
+      </c>
+      <c r="G2426" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H2426" s="2" t="n">
+        <v>46082.09886654245</v>
+      </c>
+    </row>
+    <row r="2427">
+      <c r="A2427" t="inlineStr">
+        <is>
+          <t>9d4d43ba-54ba-4303-b8ed-9b0800989f98</t>
+        </is>
+      </c>
+      <c r="B2427" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2427" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2427" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2427" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2427" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="G2427" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H2427" s="2" t="n">
+        <v>46073.09886654545</v>
+      </c>
+    </row>
+    <row r="2428">
+      <c r="A2428" t="inlineStr">
+        <is>
+          <t>f11774bb-1f05-4f98-8175-bdc99b58ef21</t>
+        </is>
+      </c>
+      <c r="B2428" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2428" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2428" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2428" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2428" t="n">
+        <v>64.09</v>
+      </c>
+      <c r="G2428" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H2428" s="2" t="n">
+        <v>46079.09886654835</v>
+      </c>
+    </row>
+    <row r="2429">
+      <c r="A2429" t="inlineStr">
+        <is>
+          <t>8ff4a30d-94d4-4606-ad6d-dd4c3d91e772</t>
+        </is>
+      </c>
+      <c r="B2429" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2429" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2429" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2429" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2429" t="n">
+        <v>252.57</v>
+      </c>
+      <c r="G2429" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="H2429" s="2" t="n">
+        <v>46080.09886655115</v>
+      </c>
+    </row>
+    <row r="2430">
+      <c r="A2430" t="inlineStr">
+        <is>
+          <t>24cebfb1-9858-45ec-af50-8878e636ce2f</t>
+        </is>
+      </c>
+      <c r="B2430" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2430" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2430" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2430" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2430" t="n">
+        <v>360.48</v>
+      </c>
+      <c r="G2430" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H2430" s="2" t="n">
+        <v>46095.09886655395</v>
+      </c>
+    </row>
+    <row r="2431">
+      <c r="A2431" t="inlineStr">
+        <is>
+          <t>e7b9bde4-48c6-437a-8f41-b9e22c95ca49</t>
+        </is>
+      </c>
+      <c r="B2431" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2431" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2431" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2431" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2431" t="n">
+        <v>450.24</v>
+      </c>
+      <c r="G2431" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H2431" s="2" t="n">
+        <v>46080.09886655681</v>
+      </c>
+    </row>
+    <row r="2432">
+      <c r="A2432" t="inlineStr">
+        <is>
+          <t>68a3a77c-4398-43ce-91a1-a78628f2fb93</t>
+        </is>
+      </c>
+      <c r="B2432" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2432" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2432" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2432" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2432" t="n">
+        <v>79.03</v>
+      </c>
+      <c r="G2432" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H2432" s="2" t="n">
+        <v>46074.09886655973</v>
+      </c>
+    </row>
+    <row r="2433">
+      <c r="A2433" t="inlineStr">
+        <is>
+          <t>3a1d9b59-8d89-4b62-a2ef-157574e7a80d</t>
+        </is>
+      </c>
+      <c r="B2433" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2433" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2433" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2433" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2433" t="n">
+        <v>290.44</v>
+      </c>
+      <c r="G2433" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H2433" s="2" t="n">
+        <v>46094.09886656251</v>
+      </c>
+    </row>
+    <row r="2434">
+      <c r="A2434" t="inlineStr">
+        <is>
+          <t>7ced2e5f-7534-4561-922e-bc22dfbbee98</t>
+        </is>
+      </c>
+      <c r="B2434" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2434" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2434" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2434" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2434" t="n">
+        <v>407.95</v>
+      </c>
+      <c r="G2434" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="H2434" s="2" t="n">
+        <v>46078.09886656541</v>
+      </c>
+    </row>
+    <row r="2435">
+      <c r="A2435" t="inlineStr">
+        <is>
+          <t>3ae1536d-5adf-4de8-8104-52401ad2b48a</t>
+        </is>
+      </c>
+      <c r="B2435" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2435" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2435" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2435" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2435" t="n">
+        <v>474.98</v>
+      </c>
+      <c r="G2435" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="H2435" s="2" t="n">
+        <v>46092.09886656858</v>
+      </c>
+    </row>
+    <row r="2436">
+      <c r="A2436" t="inlineStr">
+        <is>
+          <t>62d2de30-8314-483d-b798-abc21e9e57dc</t>
+        </is>
+      </c>
+      <c r="B2436" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2436" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2436" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2436" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2436" t="n">
+        <v>274.13</v>
+      </c>
+      <c r="G2436" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H2436" s="2" t="n">
+        <v>46089.09886657134</v>
+      </c>
+    </row>
+    <row r="2437">
+      <c r="A2437" t="inlineStr">
+        <is>
+          <t>5e3c1de7-d945-406e-a87b-dfabfc8e2891</t>
+        </is>
+      </c>
+      <c r="B2437" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2437" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2437" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2437" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2437" t="n">
+        <v>273.6</v>
+      </c>
+      <c r="G2437" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H2437" s="2" t="n">
+        <v>46081.09886657418</v>
+      </c>
+    </row>
+    <row r="2438">
+      <c r="A2438" t="inlineStr">
+        <is>
+          <t>d0487723-0c63-4025-b78c-546ca069f583</t>
+        </is>
+      </c>
+      <c r="B2438" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2438" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2438" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2438" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2438" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="G2438" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H2438" s="2" t="n">
+        <v>46079.09886657697</v>
+      </c>
+    </row>
+    <row r="2439">
+      <c r="A2439" t="inlineStr">
+        <is>
+          <t>7e97f9c4-a051-487d-be32-1452c8cca0af</t>
+        </is>
+      </c>
+      <c r="B2439" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2439" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2439" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2439" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2439" t="n">
+        <v>150.94</v>
+      </c>
+      <c r="G2439" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="H2439" s="2" t="n">
+        <v>46082.09886658011</v>
+      </c>
+    </row>
+    <row r="2440">
+      <c r="A2440" t="inlineStr">
+        <is>
+          <t>957cc7ba-a113-4e76-8faf-0ef1f039565b</t>
+        </is>
+      </c>
+      <c r="B2440" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2440" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2440" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2440" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2440" t="n">
+        <v>261.73</v>
+      </c>
+      <c r="G2440" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H2440" s="2" t="n">
+        <v>46076.09886658291</v>
+      </c>
+    </row>
+    <row r="2441">
+      <c r="A2441" t="inlineStr">
+        <is>
+          <t>b1d812a9-4a54-4dbf-bbd9-341b87f7e525</t>
+        </is>
+      </c>
+      <c r="B2441" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2441" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2441" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2441" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2441" t="n">
+        <v>474.45</v>
+      </c>
+      <c r="G2441" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="H2441" s="2" t="n">
+        <v>46087.09886658566</v>
+      </c>
+    </row>
+    <row r="2442">
+      <c r="A2442" t="inlineStr">
+        <is>
+          <t>2e104d03-c72a-4eb2-8c70-51ebf16a51b5</t>
+        </is>
+      </c>
+      <c r="B2442" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2442" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2442" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2442" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2442" t="n">
+        <v>256.65</v>
+      </c>
+      <c r="G2442" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="H2442" s="2" t="n">
+        <v>46076.09886658847</v>
+      </c>
+    </row>
+    <row r="2443">
+      <c r="A2443" t="inlineStr">
+        <is>
+          <t>e00c4f1f-0d60-401c-9124-990b900bfc20</t>
+        </is>
+      </c>
+      <c r="B2443" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2443" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2443" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2443" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2443" t="n">
+        <v>349.17</v>
+      </c>
+      <c r="G2443" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="H2443" s="2" t="n">
+        <v>46071.09886659164</v>
+      </c>
+    </row>
+    <row r="2444">
+      <c r="A2444" t="inlineStr">
+        <is>
+          <t>7035fc72-ba05-4325-a63c-6895776f04c9</t>
+        </is>
+      </c>
+      <c r="B2444" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2444" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2444" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2444" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2444" t="n">
+        <v>123.09</v>
+      </c>
+      <c r="G2444" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="H2444" s="2" t="n">
+        <v>46068.09886659442</v>
+      </c>
+    </row>
+    <row r="2445">
+      <c r="A2445" t="inlineStr">
+        <is>
+          <t>ed62a6a3-3f4e-4623-98de-c5e6c6c547c9</t>
+        </is>
+      </c>
+      <c r="B2445" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2445" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2445" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2445" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2445" t="n">
+        <v>227.7</v>
+      </c>
+      <c r="G2445" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H2445" s="2" t="n">
+        <v>46096.09886659731</v>
+      </c>
+    </row>
+    <row r="2446">
+      <c r="A2446" t="inlineStr">
+        <is>
+          <t>65676154-590c-4467-b7f5-45dba31a4159</t>
+        </is>
+      </c>
+      <c r="B2446" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2446" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2446" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2446" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2446" t="n">
+        <v>203.32</v>
+      </c>
+      <c r="G2446" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="H2446" s="2" t="n">
+        <v>46086.09886660008</v>
+      </c>
+    </row>
+    <row r="2447">
+      <c r="A2447" t="inlineStr">
+        <is>
+          <t>c238bd6a-5062-4373-bfa6-2112ee4ee671</t>
+        </is>
+      </c>
+      <c r="B2447" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2447" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2447" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2447" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2447" t="n">
+        <v>186.43</v>
+      </c>
+      <c r="G2447" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H2447" s="2" t="n">
+        <v>46091.09886660307</v>
+      </c>
+    </row>
+    <row r="2448">
+      <c r="A2448" t="inlineStr">
+        <is>
+          <t>55e095da-14fc-4b66-a7ad-aa8052c20812</t>
+        </is>
+      </c>
+      <c r="B2448" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2448" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2448" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2448" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2448" t="n">
+        <v>420.24</v>
+      </c>
+      <c r="G2448" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H2448" s="2" t="n">
+        <v>46091.09886660595</v>
+      </c>
+    </row>
+    <row r="2449">
+      <c r="A2449" t="inlineStr">
+        <is>
+          <t>5b887d9d-4efc-4dab-863f-7393aafb13b4</t>
+        </is>
+      </c>
+      <c r="B2449" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2449" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2449" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2449" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2449" t="n">
+        <v>344.67</v>
+      </c>
+      <c r="G2449" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H2449" s="2" t="n">
+        <v>46069.09886660889</v>
+      </c>
+    </row>
+    <row r="2450">
+      <c r="A2450" t="inlineStr">
+        <is>
+          <t>dd7c38fb-8e35-41bd-8e9c-ce8e1f6ccbe4</t>
+        </is>
+      </c>
+      <c r="B2450" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2450" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2450" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2450" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2450" t="n">
+        <v>45.12</v>
+      </c>
+      <c r="G2450" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H2450" s="2" t="n">
+        <v>46072.09886661163</v>
+      </c>
+    </row>
+    <row r="2451">
+      <c r="A2451" t="inlineStr">
+        <is>
+          <t>2024e075-6e10-42e9-b320-a8a706813f99</t>
+        </is>
+      </c>
+      <c r="B2451" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2451" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2451" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2451" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2451" t="n">
+        <v>166.64</v>
+      </c>
+      <c r="G2451" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H2451" s="2" t="n">
+        <v>46095.09886661496</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2451"/>
+  <dimension ref="A1:H2501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82105,7 +82105,7 @@
         <v>0.66</v>
       </c>
       <c r="H2402" s="2" t="n">
-        <v>46077.09886646964</v>
+        <v>46077.09886646991</v>
       </c>
     </row>
     <row r="2403">
@@ -82139,7 +82139,7 @@
         <v>0.09</v>
       </c>
       <c r="H2403" s="2" t="n">
-        <v>46068.09886647403</v>
+        <v>46068.09886646991</v>
       </c>
     </row>
     <row r="2404">
@@ -82173,7 +82173,7 @@
         <v>4.37</v>
       </c>
       <c r="H2404" s="2" t="n">
-        <v>46084.09886647718</v>
+        <v>46084.09886648148</v>
       </c>
     </row>
     <row r="2405">
@@ -82207,7 +82207,7 @@
         <v>0.23</v>
       </c>
       <c r="H2405" s="2" t="n">
-        <v>46075.09886648028</v>
+        <v>46075.09886648148</v>
       </c>
     </row>
     <row r="2406">
@@ -82241,7 +82241,7 @@
         <v>4.87</v>
       </c>
       <c r="H2406" s="2" t="n">
-        <v>46091.0988664833</v>
+        <v>46091.09886648148</v>
       </c>
     </row>
     <row r="2407">
@@ -82275,7 +82275,7 @@
         <v>2.84</v>
       </c>
       <c r="H2407" s="2" t="n">
-        <v>46093.09886648663</v>
+        <v>46093.09886648148</v>
       </c>
     </row>
     <row r="2408">
@@ -82309,7 +82309,7 @@
         <v>1.71</v>
       </c>
       <c r="H2408" s="2" t="n">
-        <v>46093.09886648942</v>
+        <v>46093.09886649306</v>
       </c>
     </row>
     <row r="2409">
@@ -82343,7 +82343,7 @@
         <v>1.08</v>
       </c>
       <c r="H2409" s="2" t="n">
-        <v>46095.09886649226</v>
+        <v>46095.09886649306</v>
       </c>
     </row>
     <row r="2410">
@@ -82377,7 +82377,7 @@
         <v>1.09</v>
       </c>
       <c r="H2410" s="2" t="n">
-        <v>46069.09886649519</v>
+        <v>46069.09886649306</v>
       </c>
     </row>
     <row r="2411">
@@ -82411,7 +82411,7 @@
         <v>0.88</v>
       </c>
       <c r="H2411" s="2" t="n">
-        <v>46089.09886649823</v>
+        <v>46089.09886649306</v>
       </c>
     </row>
     <row r="2412">
@@ -82445,7 +82445,7 @@
         <v>2.26</v>
       </c>
       <c r="H2412" s="2" t="n">
-        <v>46097.0988665013</v>
+        <v>46097.09886650463</v>
       </c>
     </row>
     <row r="2413">
@@ -82479,7 +82479,7 @@
         <v>2.48</v>
       </c>
       <c r="H2413" s="2" t="n">
-        <v>46085.09886650425</v>
+        <v>46085.09886650463</v>
       </c>
     </row>
     <row r="2414">
@@ -82513,7 +82513,7 @@
         <v>2.4</v>
       </c>
       <c r="H2414" s="2" t="n">
-        <v>46081.09886650755</v>
+        <v>46081.09886650463</v>
       </c>
     </row>
     <row r="2415">
@@ -82547,7 +82547,7 @@
         <v>0.32</v>
       </c>
       <c r="H2415" s="2" t="n">
-        <v>46087.09886651049</v>
+        <v>46087.0988665162</v>
       </c>
     </row>
     <row r="2416">
@@ -82581,7 +82581,7 @@
         <v>1.61</v>
       </c>
       <c r="H2416" s="2" t="n">
-        <v>46090.09886651341</v>
+        <v>46090.0988665162</v>
       </c>
     </row>
     <row r="2417">
@@ -82615,7 +82615,7 @@
         <v>2.2</v>
       </c>
       <c r="H2417" s="2" t="n">
-        <v>46094.09886651627</v>
+        <v>46094.0988665162</v>
       </c>
     </row>
     <row r="2418">
@@ -82649,7 +82649,7 @@
         <v>3.36</v>
       </c>
       <c r="H2418" s="2" t="n">
-        <v>46069.09886651917</v>
+        <v>46069.0988665162</v>
       </c>
     </row>
     <row r="2419">
@@ -82683,7 +82683,7 @@
         <v>1.56</v>
       </c>
       <c r="H2419" s="2" t="n">
-        <v>46077.09886652207</v>
+        <v>46077.09886652778</v>
       </c>
     </row>
     <row r="2420">
@@ -82717,7 +82717,7 @@
         <v>3.21</v>
       </c>
       <c r="H2420" s="2" t="n">
-        <v>46089.0988665249</v>
+        <v>46089.09886652778</v>
       </c>
     </row>
     <row r="2421">
@@ -82751,7 +82751,7 @@
         <v>3.17</v>
       </c>
       <c r="H2421" s="2" t="n">
-        <v>46080.09886652783</v>
+        <v>46080.09886652778</v>
       </c>
     </row>
     <row r="2422">
@@ -82785,7 +82785,7 @@
         <v>4.71</v>
       </c>
       <c r="H2422" s="2" t="n">
-        <v>46097.09886653071</v>
+        <v>46097.09886652778</v>
       </c>
     </row>
     <row r="2423">
@@ -82819,7 +82819,7 @@
         <v>4.79</v>
       </c>
       <c r="H2423" s="2" t="n">
-        <v>46070.09886653395</v>
+        <v>46070.09886653935</v>
       </c>
     </row>
     <row r="2424">
@@ -82853,7 +82853,7 @@
         <v>1.99</v>
       </c>
       <c r="H2424" s="2" t="n">
-        <v>46084.09886653691</v>
+        <v>46084.09886653935</v>
       </c>
     </row>
     <row r="2425">
@@ -82887,7 +82887,7 @@
         <v>1.77</v>
       </c>
       <c r="H2425" s="2" t="n">
-        <v>46075.09886653969</v>
+        <v>46075.09886653935</v>
       </c>
     </row>
     <row r="2426">
@@ -82921,7 +82921,7 @@
         <v>1.2</v>
       </c>
       <c r="H2426" s="2" t="n">
-        <v>46082.09886654245</v>
+        <v>46082.09886653935</v>
       </c>
     </row>
     <row r="2427">
@@ -82955,7 +82955,7 @@
         <v>0.17</v>
       </c>
       <c r="H2427" s="2" t="n">
-        <v>46073.09886654545</v>
+        <v>46073.09886655093</v>
       </c>
     </row>
     <row r="2428">
@@ -82989,7 +82989,7 @@
         <v>0.64</v>
       </c>
       <c r="H2428" s="2" t="n">
-        <v>46079.09886654835</v>
+        <v>46079.09886655093</v>
       </c>
     </row>
     <row r="2429">
@@ -83023,7 +83023,7 @@
         <v>2.53</v>
       </c>
       <c r="H2429" s="2" t="n">
-        <v>46080.09886655115</v>
+        <v>46080.09886655093</v>
       </c>
     </row>
     <row r="2430">
@@ -83057,7 +83057,7 @@
         <v>3.6</v>
       </c>
       <c r="H2430" s="2" t="n">
-        <v>46095.09886655395</v>
+        <v>46095.09886655093</v>
       </c>
     </row>
     <row r="2431">
@@ -83091,7 +83091,7 @@
         <v>4.5</v>
       </c>
       <c r="H2431" s="2" t="n">
-        <v>46080.09886655681</v>
+        <v>46080.0988665625</v>
       </c>
     </row>
     <row r="2432">
@@ -83125,7 +83125,7 @@
         <v>0.79</v>
       </c>
       <c r="H2432" s="2" t="n">
-        <v>46074.09886655973</v>
+        <v>46074.0988665625</v>
       </c>
     </row>
     <row r="2433">
@@ -83159,7 +83159,7 @@
         <v>2.9</v>
       </c>
       <c r="H2433" s="2" t="n">
-        <v>46094.09886656251</v>
+        <v>46094.0988665625</v>
       </c>
     </row>
     <row r="2434">
@@ -83193,7 +83193,7 @@
         <v>4.08</v>
       </c>
       <c r="H2434" s="2" t="n">
-        <v>46078.09886656541</v>
+        <v>46078.0988665625</v>
       </c>
     </row>
     <row r="2435">
@@ -83227,7 +83227,7 @@
         <v>4.75</v>
       </c>
       <c r="H2435" s="2" t="n">
-        <v>46092.09886656858</v>
+        <v>46092.09886657407</v>
       </c>
     </row>
     <row r="2436">
@@ -83261,7 +83261,7 @@
         <v>2.74</v>
       </c>
       <c r="H2436" s="2" t="n">
-        <v>46089.09886657134</v>
+        <v>46089.09886657407</v>
       </c>
     </row>
     <row r="2437">
@@ -83295,7 +83295,7 @@
         <v>2.74</v>
       </c>
       <c r="H2437" s="2" t="n">
-        <v>46081.09886657418</v>
+        <v>46081.09886657407</v>
       </c>
     </row>
     <row r="2438">
@@ -83329,7 +83329,7 @@
         <v>0.17</v>
       </c>
       <c r="H2438" s="2" t="n">
-        <v>46079.09886657697</v>
+        <v>46079.09886657407</v>
       </c>
     </row>
     <row r="2439">
@@ -83363,7 +83363,7 @@
         <v>1.51</v>
       </c>
       <c r="H2439" s="2" t="n">
-        <v>46082.09886658011</v>
+        <v>46082.09886658565</v>
       </c>
     </row>
     <row r="2440">
@@ -83397,7 +83397,7 @@
         <v>2.62</v>
       </c>
       <c r="H2440" s="2" t="n">
-        <v>46076.09886658291</v>
+        <v>46076.09886658565</v>
       </c>
     </row>
     <row r="2441">
@@ -83431,7 +83431,7 @@
         <v>4.74</v>
       </c>
       <c r="H2441" s="2" t="n">
-        <v>46087.09886658566</v>
+        <v>46087.09886658565</v>
       </c>
     </row>
     <row r="2442">
@@ -83465,7 +83465,7 @@
         <v>2.57</v>
       </c>
       <c r="H2442" s="2" t="n">
-        <v>46076.09886658847</v>
+        <v>46076.09886658565</v>
       </c>
     </row>
     <row r="2443">
@@ -83499,7 +83499,7 @@
         <v>3.49</v>
       </c>
       <c r="H2443" s="2" t="n">
-        <v>46071.09886659164</v>
+        <v>46071.09886659723</v>
       </c>
     </row>
     <row r="2444">
@@ -83533,7 +83533,7 @@
         <v>1.23</v>
       </c>
       <c r="H2444" s="2" t="n">
-        <v>46068.09886659442</v>
+        <v>46068.09886659723</v>
       </c>
     </row>
     <row r="2445">
@@ -83567,7 +83567,7 @@
         <v>2.28</v>
       </c>
       <c r="H2445" s="2" t="n">
-        <v>46096.09886659731</v>
+        <v>46096.09886659723</v>
       </c>
     </row>
     <row r="2446">
@@ -83601,7 +83601,7 @@
         <v>2.03</v>
       </c>
       <c r="H2446" s="2" t="n">
-        <v>46086.09886660008</v>
+        <v>46086.09886659723</v>
       </c>
     </row>
     <row r="2447">
@@ -83635,7 +83635,7 @@
         <v>1.86</v>
       </c>
       <c r="H2447" s="2" t="n">
-        <v>46091.09886660307</v>
+        <v>46091.09886660879</v>
       </c>
     </row>
     <row r="2448">
@@ -83669,7 +83669,7 @@
         <v>4.2</v>
       </c>
       <c r="H2448" s="2" t="n">
-        <v>46091.09886660595</v>
+        <v>46091.09886660879</v>
       </c>
     </row>
     <row r="2449">
@@ -83703,7 +83703,7 @@
         <v>3.45</v>
       </c>
       <c r="H2449" s="2" t="n">
-        <v>46069.09886660889</v>
+        <v>46069.09886660879</v>
       </c>
     </row>
     <row r="2450">
@@ -83737,7 +83737,7 @@
         <v>0.45</v>
       </c>
       <c r="H2450" s="2" t="n">
-        <v>46072.09886661163</v>
+        <v>46072.09886660879</v>
       </c>
     </row>
     <row r="2451">
@@ -83771,7 +83771,1707 @@
         <v>1.67</v>
       </c>
       <c r="H2451" s="2" t="n">
-        <v>46095.09886661496</v>
+        <v>46095.09886662037</v>
+      </c>
+    </row>
+    <row r="2452">
+      <c r="A2452" t="inlineStr">
+        <is>
+          <t>7694080a-9591-4ed8-a749-b792a4179872</t>
+        </is>
+      </c>
+      <c r="B2452" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2452" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2452" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2452" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2452" t="n">
+        <v>209.06</v>
+      </c>
+      <c r="G2452" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="H2452" s="2" t="n">
+        <v>46078.21803770729</v>
+      </c>
+    </row>
+    <row r="2453">
+      <c r="A2453" t="inlineStr">
+        <is>
+          <t>f2992ffc-3535-4f2d-83b2-70408dcd405c</t>
+        </is>
+      </c>
+      <c r="B2453" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2453" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2453" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2453" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2453" t="n">
+        <v>433.58</v>
+      </c>
+      <c r="G2453" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="H2453" s="2" t="n">
+        <v>46095.21803771161</v>
+      </c>
+    </row>
+    <row r="2454">
+      <c r="A2454" t="inlineStr">
+        <is>
+          <t>8bb544d8-970b-44b5-8c50-debe8bce6c1c</t>
+        </is>
+      </c>
+      <c r="B2454" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2454" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2454" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2454" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2454" t="n">
+        <v>325.36</v>
+      </c>
+      <c r="G2454" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H2454" s="2" t="n">
+        <v>46083.21803771537</v>
+      </c>
+    </row>
+    <row r="2455">
+      <c r="A2455" t="inlineStr">
+        <is>
+          <t>ddbc038c-54a4-4c0c-99c6-b28b7d205e92</t>
+        </is>
+      </c>
+      <c r="B2455" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2455" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2455" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2455" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2455" t="n">
+        <v>45.43</v>
+      </c>
+      <c r="G2455" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H2455" s="2" t="n">
+        <v>46088.21803771866</v>
+      </c>
+    </row>
+    <row r="2456">
+      <c r="A2456" t="inlineStr">
+        <is>
+          <t>bc953821-1421-4570-8eec-7833e4953a0e</t>
+        </is>
+      </c>
+      <c r="B2456" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2456" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2456" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2456" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2456" t="n">
+        <v>346.02</v>
+      </c>
+      <c r="G2456" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="H2456" s="2" t="n">
+        <v>46074.2180377218</v>
+      </c>
+    </row>
+    <row r="2457">
+      <c r="A2457" t="inlineStr">
+        <is>
+          <t>459ec4a5-8d87-432e-94a6-7da3d11ecc67</t>
+        </is>
+      </c>
+      <c r="B2457" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2457" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2457" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2457" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2457" t="n">
+        <v>323.32</v>
+      </c>
+      <c r="G2457" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="H2457" s="2" t="n">
+        <v>46079.21803772495</v>
+      </c>
+    </row>
+    <row r="2458">
+      <c r="A2458" t="inlineStr">
+        <is>
+          <t>2411b222-36cf-45ec-9688-2960c52248d6</t>
+        </is>
+      </c>
+      <c r="B2458" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2458" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2458" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2458" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2458" t="n">
+        <v>481.66</v>
+      </c>
+      <c r="G2458" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="H2458" s="2" t="n">
+        <v>46088.21803772818</v>
+      </c>
+    </row>
+    <row r="2459">
+      <c r="A2459" t="inlineStr">
+        <is>
+          <t>10a341a1-ef4d-473b-8b48-434f63ee7ba8</t>
+        </is>
+      </c>
+      <c r="B2459" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2459" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2459" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2459" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2459" t="n">
+        <v>287.72</v>
+      </c>
+      <c r="G2459" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H2459" s="2" t="n">
+        <v>46086.21803773132</v>
+      </c>
+    </row>
+    <row r="2460">
+      <c r="A2460" t="inlineStr">
+        <is>
+          <t>2565eda5-482d-414e-b423-e81ae8576ded</t>
+        </is>
+      </c>
+      <c r="B2460" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2460" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2460" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2460" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2460" t="n">
+        <v>351.5</v>
+      </c>
+      <c r="G2460" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="H2460" s="2" t="n">
+        <v>46070.21803773443</v>
+      </c>
+    </row>
+    <row r="2461">
+      <c r="A2461" t="inlineStr">
+        <is>
+          <t>317e6836-3baf-4332-aab5-23b9a98b90c0</t>
+        </is>
+      </c>
+      <c r="B2461" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2461" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2461" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2461" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2461" t="n">
+        <v>293.33</v>
+      </c>
+      <c r="G2461" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="H2461" s="2" t="n">
+        <v>46089.21803773775</v>
+      </c>
+    </row>
+    <row r="2462">
+      <c r="A2462" t="inlineStr">
+        <is>
+          <t>470cb4b5-30ba-4d8b-970e-3dd746e6e5f2</t>
+        </is>
+      </c>
+      <c r="B2462" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2462" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2462" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2462" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2462" t="n">
+        <v>393.49</v>
+      </c>
+      <c r="G2462" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="H2462" s="2" t="n">
+        <v>46096.218037741</v>
+      </c>
+    </row>
+    <row r="2463">
+      <c r="A2463" t="inlineStr">
+        <is>
+          <t>302e9559-daeb-4863-85b7-d2bc0c3e7001</t>
+        </is>
+      </c>
+      <c r="B2463" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2463" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2463" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2463" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2463" t="n">
+        <v>313.77</v>
+      </c>
+      <c r="G2463" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H2463" s="2" t="n">
+        <v>46074.21803774412</v>
+      </c>
+    </row>
+    <row r="2464">
+      <c r="A2464" t="inlineStr">
+        <is>
+          <t>51225ce1-08d2-417e-a5fb-162a243152f0</t>
+        </is>
+      </c>
+      <c r="B2464" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2464" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2464" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2464" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2464" t="n">
+        <v>93.67</v>
+      </c>
+      <c r="G2464" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H2464" s="2" t="n">
+        <v>46076.21803774723</v>
+      </c>
+    </row>
+    <row r="2465">
+      <c r="A2465" t="inlineStr">
+        <is>
+          <t>dff4bac8-7d26-404d-bbf8-64cb47f386ba</t>
+        </is>
+      </c>
+      <c r="B2465" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2465" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2465" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2465" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2465" t="n">
+        <v>420.51</v>
+      </c>
+      <c r="G2465" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="H2465" s="2" t="n">
+        <v>46092.21803775062</v>
+      </c>
+    </row>
+    <row r="2466">
+      <c r="A2466" t="inlineStr">
+        <is>
+          <t>bf7ceb15-b987-4891-9f6c-c2a0558937d6</t>
+        </is>
+      </c>
+      <c r="B2466" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2466" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2466" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2466" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2466" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="G2466" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H2466" s="2" t="n">
+        <v>46086.21803775369</v>
+      </c>
+    </row>
+    <row r="2467">
+      <c r="A2467" t="inlineStr">
+        <is>
+          <t>4e3227fc-bdfd-4205-80cc-e9d318e2952c</t>
+        </is>
+      </c>
+      <c r="B2467" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2467" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2467" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2467" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2467" t="n">
+        <v>79.18000000000001</v>
+      </c>
+      <c r="G2467" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H2467" s="2" t="n">
+        <v>46083.21803775692</v>
+      </c>
+    </row>
+    <row r="2468">
+      <c r="A2468" t="inlineStr">
+        <is>
+          <t>5aa76050-b039-47f6-b160-971a0af3b0e2</t>
+        </is>
+      </c>
+      <c r="B2468" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2468" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2468" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2468" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2468" t="n">
+        <v>68.02</v>
+      </c>
+      <c r="G2468" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H2468" s="2" t="n">
+        <v>46093.21803776028</v>
+      </c>
+    </row>
+    <row r="2469">
+      <c r="A2469" t="inlineStr">
+        <is>
+          <t>7e346a37-20bb-4f91-8a16-471100b6a9a9</t>
+        </is>
+      </c>
+      <c r="B2469" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2469" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2469" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2469" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2469" t="n">
+        <v>473.27</v>
+      </c>
+      <c r="G2469" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="H2469" s="2" t="n">
+        <v>46090.21803776352</v>
+      </c>
+    </row>
+    <row r="2470">
+      <c r="A2470" t="inlineStr">
+        <is>
+          <t>7c0d22c8-79c1-4429-9fb8-84363b5d0b38</t>
+        </is>
+      </c>
+      <c r="B2470" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2470" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2470" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2470" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2470" t="n">
+        <v>331.71</v>
+      </c>
+      <c r="G2470" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="H2470" s="2" t="n">
+        <v>46087.21803776663</v>
+      </c>
+    </row>
+    <row r="2471">
+      <c r="A2471" t="inlineStr">
+        <is>
+          <t>1e19be16-93a4-4e24-8b0a-566322e0b8ca</t>
+        </is>
+      </c>
+      <c r="B2471" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2471" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2471" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2471" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2471" t="n">
+        <v>36.44</v>
+      </c>
+      <c r="G2471" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H2471" s="2" t="n">
+        <v>46078.21803776966</v>
+      </c>
+    </row>
+    <row r="2472">
+      <c r="A2472" t="inlineStr">
+        <is>
+          <t>0ad32fea-dffe-4229-a25e-d42a4663998e</t>
+        </is>
+      </c>
+      <c r="B2472" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2472" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2472" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2472" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2472" t="n">
+        <v>199.81</v>
+      </c>
+      <c r="G2472" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2472" s="2" t="n">
+        <v>46074.21803777293</v>
+      </c>
+    </row>
+    <row r="2473">
+      <c r="A2473" t="inlineStr">
+        <is>
+          <t>461a52ed-7640-41ef-b455-1d8347e9f91c</t>
+        </is>
+      </c>
+      <c r="B2473" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2473" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2473" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2473" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2473" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="G2473" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H2473" s="2" t="n">
+        <v>46093.21803777617</v>
+      </c>
+    </row>
+    <row r="2474">
+      <c r="A2474" t="inlineStr">
+        <is>
+          <t>d5362288-df39-41db-91d7-a9f0b7253b4f</t>
+        </is>
+      </c>
+      <c r="B2474" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2474" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2474" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2474" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2474" t="n">
+        <v>168.78</v>
+      </c>
+      <c r="G2474" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H2474" s="2" t="n">
+        <v>46086.21803777938</v>
+      </c>
+    </row>
+    <row r="2475">
+      <c r="A2475" t="inlineStr">
+        <is>
+          <t>87c4d937-1d69-4c07-843a-4a7849644c22</t>
+        </is>
+      </c>
+      <c r="B2475" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2475" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2475" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2475" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2475" t="n">
+        <v>98.39</v>
+      </c>
+      <c r="G2475" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H2475" s="2" t="n">
+        <v>46081.21803778256</v>
+      </c>
+    </row>
+    <row r="2476">
+      <c r="A2476" t="inlineStr">
+        <is>
+          <t>99bce355-958e-4323-968c-a2dab0758887</t>
+        </is>
+      </c>
+      <c r="B2476" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2476" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2476" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2476" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2476" t="n">
+        <v>474.35</v>
+      </c>
+      <c r="G2476" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="H2476" s="2" t="n">
+        <v>46069.21803778585</v>
+      </c>
+    </row>
+    <row r="2477">
+      <c r="A2477" t="inlineStr">
+        <is>
+          <t>623457d2-fef0-4c0f-992c-2981b7f2c2a0</t>
+        </is>
+      </c>
+      <c r="B2477" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2477" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2477" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2477" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2477" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="G2477" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H2477" s="2" t="n">
+        <v>46078.21803778906</v>
+      </c>
+    </row>
+    <row r="2478">
+      <c r="A2478" t="inlineStr">
+        <is>
+          <t>53f67020-e844-43ca-a17d-be977e4dc3b9</t>
+        </is>
+      </c>
+      <c r="B2478" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2478" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2478" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2478" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2478" t="n">
+        <v>267.13</v>
+      </c>
+      <c r="G2478" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="H2478" s="2" t="n">
+        <v>46093.21803779222</v>
+      </c>
+    </row>
+    <row r="2479">
+      <c r="A2479" t="inlineStr">
+        <is>
+          <t>d7d658f8-c747-40fc-b190-79ac2b93cbbe</t>
+        </is>
+      </c>
+      <c r="B2479" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2479" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2479" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2479" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2479" t="n">
+        <v>187.56</v>
+      </c>
+      <c r="G2479" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H2479" s="2" t="n">
+        <v>46094.21803779552</v>
+      </c>
+    </row>
+    <row r="2480">
+      <c r="A2480" t="inlineStr">
+        <is>
+          <t>3ba425e0-63b4-41b9-8549-fc52661497f0</t>
+        </is>
+      </c>
+      <c r="B2480" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2480" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2480" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2480" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2480" t="n">
+        <v>44.42</v>
+      </c>
+      <c r="G2480" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H2480" s="2" t="n">
+        <v>46081.21803779868</v>
+      </c>
+    </row>
+    <row r="2481">
+      <c r="A2481" t="inlineStr">
+        <is>
+          <t>ad097711-3840-43bd-94c0-9e1c77d17066</t>
+        </is>
+      </c>
+      <c r="B2481" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2481" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2481" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2481" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2481" t="n">
+        <v>42.37</v>
+      </c>
+      <c r="G2481" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H2481" s="2" t="n">
+        <v>46078.21803780182</v>
+      </c>
+    </row>
+    <row r="2482">
+      <c r="A2482" t="inlineStr">
+        <is>
+          <t>5081f611-a2a6-4534-8f24-9a7512e620ca</t>
+        </is>
+      </c>
+      <c r="B2482" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2482" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2482" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2482" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2482" t="n">
+        <v>220.59</v>
+      </c>
+      <c r="G2482" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="H2482" s="2" t="n">
+        <v>46095.21803780495</v>
+      </c>
+    </row>
+    <row r="2483">
+      <c r="A2483" t="inlineStr">
+        <is>
+          <t>8b36a0a6-0039-462d-92bf-1cffe22ea5c2</t>
+        </is>
+      </c>
+      <c r="B2483" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2483" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2483" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2483" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2483" t="n">
+        <v>418.94</v>
+      </c>
+      <c r="G2483" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="H2483" s="2" t="n">
+        <v>46070.2180378081</v>
+      </c>
+    </row>
+    <row r="2484">
+      <c r="A2484" t="inlineStr">
+        <is>
+          <t>1d458302-bef6-4da7-aac2-17b4e14cffb0</t>
+        </is>
+      </c>
+      <c r="B2484" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2484" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2484" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2484" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2484" t="n">
+        <v>486.97</v>
+      </c>
+      <c r="G2484" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="H2484" s="2" t="n">
+        <v>46088.21803781114</v>
+      </c>
+    </row>
+    <row r="2485">
+      <c r="A2485" t="inlineStr">
+        <is>
+          <t>c3952d90-429a-400e-bf0e-45a1933175fd</t>
+        </is>
+      </c>
+      <c r="B2485" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2485" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2485" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2485" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2485" t="n">
+        <v>467.26</v>
+      </c>
+      <c r="G2485" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="H2485" s="2" t="n">
+        <v>46088.21803781436</v>
+      </c>
+    </row>
+    <row r="2486">
+      <c r="A2486" t="inlineStr">
+        <is>
+          <t>fbf2e675-9599-4205-a6c1-c33b52913fe0</t>
+        </is>
+      </c>
+      <c r="B2486" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2486" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2486" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2486" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2486" t="n">
+        <v>474.53</v>
+      </c>
+      <c r="G2486" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="H2486" s="2" t="n">
+        <v>46087.21803781747</v>
+      </c>
+    </row>
+    <row r="2487">
+      <c r="A2487" t="inlineStr">
+        <is>
+          <t>d67afdea-9b70-4438-a834-22b8ab90cda9</t>
+        </is>
+      </c>
+      <c r="B2487" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2487" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2487" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2487" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2487" t="n">
+        <v>121.82</v>
+      </c>
+      <c r="G2487" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H2487" s="2" t="n">
+        <v>46071.21803782066</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" t="inlineStr">
+        <is>
+          <t>d3022633-325c-44af-91a5-d0d9518ce523</t>
+        </is>
+      </c>
+      <c r="B2488" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2488" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2488" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2488" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2488" t="n">
+        <v>386.97</v>
+      </c>
+      <c r="G2488" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="H2488" s="2" t="n">
+        <v>46090.2180378237</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" t="inlineStr">
+        <is>
+          <t>42df9e32-3f3f-4e8d-9bb6-c90e37d24770</t>
+        </is>
+      </c>
+      <c r="B2489" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2489" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2489" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2489" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2489" t="n">
+        <v>379.44</v>
+      </c>
+      <c r="G2489" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="H2489" s="2" t="n">
+        <v>46091.21803782676</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" t="inlineStr">
+        <is>
+          <t>5b3b50f8-7465-47a1-92bf-f7ebc0218cae</t>
+        </is>
+      </c>
+      <c r="B2490" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2490" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2490" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2490" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2490" t="n">
+        <v>361.97</v>
+      </c>
+      <c r="G2490" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="H2490" s="2" t="n">
+        <v>46070.21803782993</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" t="inlineStr">
+        <is>
+          <t>0861e009-e229-465e-bfa8-ba1b2fa377cf</t>
+        </is>
+      </c>
+      <c r="B2491" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2491" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2491" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2491" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2491" t="n">
+        <v>307.34</v>
+      </c>
+      <c r="G2491" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="H2491" s="2" t="n">
+        <v>46070.21803783295</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" t="inlineStr">
+        <is>
+          <t>14b1fd26-885c-4f2b-9823-4a77907c2be1</t>
+        </is>
+      </c>
+      <c r="B2492" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2492" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2492" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2492" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2492" t="n">
+        <v>274.26</v>
+      </c>
+      <c r="G2492" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H2492" s="2" t="n">
+        <v>46090.21803783601</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" t="inlineStr">
+        <is>
+          <t>ff3548a6-40c8-4cad-8f2b-0e9df8766d45</t>
+        </is>
+      </c>
+      <c r="B2493" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2493" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2493" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2493" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2493" t="n">
+        <v>396.18</v>
+      </c>
+      <c r="G2493" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="H2493" s="2" t="n">
+        <v>46083.21803783905</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" t="inlineStr">
+        <is>
+          <t>b5c2359c-fb85-4c20-aa1c-b979a817c8f5</t>
+        </is>
+      </c>
+      <c r="B2494" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2494" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2494" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2494" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2494" t="n">
+        <v>297.25</v>
+      </c>
+      <c r="G2494" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="H2494" s="2" t="n">
+        <v>46073.21803784247</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" t="inlineStr">
+        <is>
+          <t>f40513b3-747c-4710-9442-f657a8e69161</t>
+        </is>
+      </c>
+      <c r="B2495" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2495" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2495" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2495" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2495" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="G2495" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H2495" s="2" t="n">
+        <v>46096.21803784568</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" t="inlineStr">
+        <is>
+          <t>dee47a55-e269-468d-85fb-056822547e07</t>
+        </is>
+      </c>
+      <c r="B2496" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2496" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2496" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2496" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2496" t="n">
+        <v>251.57</v>
+      </c>
+      <c r="G2496" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H2496" s="2" t="n">
+        <v>46086.2180378488</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" t="inlineStr">
+        <is>
+          <t>58887578-eb9c-4e54-ba2c-a867d3ebb917</t>
+        </is>
+      </c>
+      <c r="B2497" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2497" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2497" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2497" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2497" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G2497" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H2497" s="2" t="n">
+        <v>46087.21803785186</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" t="inlineStr">
+        <is>
+          <t>c59ac968-04dd-4a0f-b0fe-2f4bfb991c88</t>
+        </is>
+      </c>
+      <c r="B2498" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2498" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2498" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2498" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2498" t="n">
+        <v>348.59</v>
+      </c>
+      <c r="G2498" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="H2498" s="2" t="n">
+        <v>46082.21803785503</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" t="inlineStr">
+        <is>
+          <t>4456e32a-19f6-404a-9301-0edfa67874ae</t>
+        </is>
+      </c>
+      <c r="B2499" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2499" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2499" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2499" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2499" t="n">
+        <v>388.34</v>
+      </c>
+      <c r="G2499" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="H2499" s="2" t="n">
+        <v>46092.21803785815</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" t="inlineStr">
+        <is>
+          <t>b9667581-2d6b-4de4-afe9-8e15b5c078bd</t>
+        </is>
+      </c>
+      <c r="B2500" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2500" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2500" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2500" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2500" t="n">
+        <v>314.51</v>
+      </c>
+      <c r="G2500" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H2500" s="2" t="n">
+        <v>46095.21803786132</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" t="inlineStr">
+        <is>
+          <t>6c1ca2a9-2955-4520-ac0a-68b590a96b59</t>
+        </is>
+      </c>
+      <c r="B2501" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2501" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2501" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2501" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2501" t="n">
+        <v>40.07</v>
+      </c>
+      <c r="G2501" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2501" s="2" t="n">
+        <v>46082.21803786448</v>
       </c>
     </row>
   </sheetData>

--- a/quality_outcomes.xlsx
+++ b/quality_outcomes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2501"/>
+  <dimension ref="A1:H2551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83805,7 +83805,7 @@
         <v>2.09</v>
       </c>
       <c r="H2452" s="2" t="n">
-        <v>46078.21803770729</v>
+        <v>46078.21803770834</v>
       </c>
     </row>
     <row r="2453">
@@ -83839,7 +83839,7 @@
         <v>4.34</v>
       </c>
       <c r="H2453" s="2" t="n">
-        <v>46095.21803771161</v>
+        <v>46095.21803770834</v>
       </c>
     </row>
     <row r="2454">
@@ -83873,7 +83873,7 @@
         <v>3.25</v>
       </c>
       <c r="H2454" s="2" t="n">
-        <v>46083.21803771537</v>
+        <v>46083.2180377199</v>
       </c>
     </row>
     <row r="2455">
@@ -83907,7 +83907,7 @@
         <v>0.45</v>
       </c>
       <c r="H2455" s="2" t="n">
-        <v>46088.21803771866</v>
+        <v>46088.2180377199</v>
       </c>
     </row>
     <row r="2456">
@@ -83941,7 +83941,7 @@
         <v>3.46</v>
       </c>
       <c r="H2456" s="2" t="n">
-        <v>46074.2180377218</v>
+        <v>46074.2180377199</v>
       </c>
     </row>
     <row r="2457">
@@ -83975,7 +83975,7 @@
         <v>3.23</v>
       </c>
       <c r="H2457" s="2" t="n">
-        <v>46079.21803772495</v>
+        <v>46079.2180377199</v>
       </c>
     </row>
     <row r="2458">
@@ -84009,7 +84009,7 @@
         <v>4.82</v>
       </c>
       <c r="H2458" s="2" t="n">
-        <v>46088.21803772818</v>
+        <v>46088.21803773148</v>
       </c>
     </row>
     <row r="2459">
@@ -84043,7 +84043,7 @@
         <v>2.88</v>
       </c>
       <c r="H2459" s="2" t="n">
-        <v>46086.21803773132</v>
+        <v>46086.21803773148</v>
       </c>
     </row>
     <row r="2460">
@@ -84077,7 +84077,7 @@
         <v>3.52</v>
       </c>
       <c r="H2460" s="2" t="n">
-        <v>46070.21803773443</v>
+        <v>46070.21803773148</v>
       </c>
     </row>
     <row r="2461">
@@ -84111,7 +84111,7 @@
         <v>2.93</v>
       </c>
       <c r="H2461" s="2" t="n">
-        <v>46089.21803773775</v>
+        <v>46089.21803774306</v>
       </c>
     </row>
     <row r="2462">
@@ -84145,7 +84145,7 @@
         <v>3.93</v>
       </c>
       <c r="H2462" s="2" t="n">
-        <v>46096.218037741</v>
+        <v>46096.21803774306</v>
       </c>
     </row>
     <row r="2463">
@@ -84179,7 +84179,7 @@
         <v>3.14</v>
       </c>
       <c r="H2463" s="2" t="n">
-        <v>46074.21803774412</v>
+        <v>46074.21803774306</v>
       </c>
     </row>
     <row r="2464">
@@ -84213,7 +84213,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="H2464" s="2" t="n">
-        <v>46076.21803774723</v>
+        <v>46076.21803774306</v>
       </c>
     </row>
     <row r="2465">
@@ -84247,7 +84247,7 @@
         <v>4.21</v>
       </c>
       <c r="H2465" s="2" t="n">
-        <v>46092.21803775062</v>
+        <v>46092.21803775463</v>
       </c>
     </row>
     <row r="2466">
@@ -84281,7 +84281,7 @@
         <v>0.62</v>
       </c>
       <c r="H2466" s="2" t="n">
-        <v>46086.21803775369</v>
+        <v>46086.21803775463</v>
       </c>
     </row>
     <row r="2467">
@@ -84315,7 +84315,7 @@
         <v>0.79</v>
       </c>
       <c r="H2467" s="2" t="n">
-        <v>46083.21803775692</v>
+        <v>46083.21803775463</v>
       </c>
     </row>
     <row r="2468">
@@ -84349,7 +84349,7 @@
         <v>0.68</v>
       </c>
       <c r="H2468" s="2" t="n">
-        <v>46093.21803776028</v>
+        <v>46093.21803775463</v>
       </c>
     </row>
     <row r="2469">
@@ -84383,7 +84383,7 @@
         <v>4.73</v>
       </c>
       <c r="H2469" s="2" t="n">
-        <v>46090.21803776352</v>
+        <v>46090.2180377662</v>
       </c>
     </row>
     <row r="2470">
@@ -84417,7 +84417,7 @@
         <v>3.32</v>
       </c>
       <c r="H2470" s="2" t="n">
-        <v>46087.21803776663</v>
+        <v>46087.2180377662</v>
       </c>
     </row>
     <row r="2471">
@@ -84451,7 +84451,7 @@
         <v>0.36</v>
       </c>
       <c r="H2471" s="2" t="n">
-        <v>46078.21803776966</v>
+        <v>46078.2180377662</v>
       </c>
     </row>
     <row r="2472">
@@ -84485,7 +84485,7 @@
         <v>2</v>
       </c>
       <c r="H2472" s="2" t="n">
-        <v>46074.21803777293</v>
+        <v>46074.21803777778</v>
       </c>
     </row>
     <row r="2473">
@@ -84519,7 +84519,7 @@
         <v>0.03</v>
       </c>
       <c r="H2473" s="2" t="n">
-        <v>46093.21803777617</v>
+        <v>46093.21803777778</v>
       </c>
     </row>
     <row r="2474">
@@ -84553,7 +84553,7 @@
         <v>1.69</v>
       </c>
       <c r="H2474" s="2" t="n">
-        <v>46086.21803777938</v>
+        <v>46086.21803777778</v>
       </c>
     </row>
     <row r="2475">
@@ -84587,7 +84587,7 @@
         <v>0.98</v>
       </c>
       <c r="H2475" s="2" t="n">
-        <v>46081.21803778256</v>
+        <v>46081.21803777778</v>
       </c>
     </row>
     <row r="2476">
@@ -84621,7 +84621,7 @@
         <v>4.74</v>
       </c>
       <c r="H2476" s="2" t="n">
-        <v>46069.21803778585</v>
+        <v>46069.21803778935</v>
       </c>
     </row>
     <row r="2477">
@@ -84655,7 +84655,7 @@
         <v>0.05</v>
       </c>
       <c r="H2477" s="2" t="n">
-        <v>46078.21803778906</v>
+        <v>46078.21803778935</v>
       </c>
     </row>
     <row r="2478">
@@ -84689,7 +84689,7 @@
         <v>2.67</v>
       </c>
       <c r="H2478" s="2" t="n">
-        <v>46093.21803779222</v>
+        <v>46093.21803778935</v>
       </c>
     </row>
     <row r="2479">
@@ -84723,7 +84723,7 @@
         <v>1.88</v>
       </c>
       <c r="H2479" s="2" t="n">
-        <v>46094.21803779552</v>
+        <v>46094.21803780093</v>
       </c>
     </row>
     <row r="2480">
@@ -84757,7 +84757,7 @@
         <v>0.44</v>
       </c>
       <c r="H2480" s="2" t="n">
-        <v>46081.21803779868</v>
+        <v>46081.21803780093</v>
       </c>
     </row>
     <row r="2481">
@@ -84791,7 +84791,7 @@
         <v>0.42</v>
       </c>
       <c r="H2481" s="2" t="n">
-        <v>46078.21803780182</v>
+        <v>46078.21803780093</v>
       </c>
     </row>
     <row r="2482">
@@ -84825,7 +84825,7 @@
         <v>2.21</v>
       </c>
       <c r="H2482" s="2" t="n">
-        <v>46095.21803780495</v>
+        <v>46095.21803780093</v>
       </c>
     </row>
     <row r="2483">
@@ -84859,7 +84859,7 @@
         <v>4.19</v>
       </c>
       <c r="H2483" s="2" t="n">
-        <v>46070.2180378081</v>
+        <v>46070.2180378125</v>
       </c>
     </row>
     <row r="2484">
@@ -84893,7 +84893,7 @@
         <v>4.87</v>
       </c>
       <c r="H2484" s="2" t="n">
-        <v>46088.21803781114</v>
+        <v>46088.2180378125</v>
       </c>
     </row>
     <row r="2485">
@@ -84927,7 +84927,7 @@
         <v>4.67</v>
       </c>
       <c r="H2485" s="2" t="n">
-        <v>46088.21803781436</v>
+        <v>46088.2180378125</v>
       </c>
     </row>
     <row r="2486">
@@ -84961,7 +84961,7 @@
         <v>4.75</v>
       </c>
       <c r="H2486" s="2" t="n">
-        <v>46087.21803781747</v>
+        <v>46087.2180378125</v>
       </c>
     </row>
     <row r="2487">
@@ -84995,7 +84995,7 @@
         <v>1.22</v>
       </c>
       <c r="H2487" s="2" t="n">
-        <v>46071.21803782066</v>
+        <v>46071.21803782407</v>
       </c>
     </row>
     <row r="2488">
@@ -85029,7 +85029,7 @@
         <v>3.87</v>
       </c>
       <c r="H2488" s="2" t="n">
-        <v>46090.2180378237</v>
+        <v>46090.21803782407</v>
       </c>
     </row>
     <row r="2489">
@@ -85063,7 +85063,7 @@
         <v>3.79</v>
       </c>
       <c r="H2489" s="2" t="n">
-        <v>46091.21803782676</v>
+        <v>46091.21803782407</v>
       </c>
     </row>
     <row r="2490">
@@ -85097,7 +85097,7 @@
         <v>3.62</v>
       </c>
       <c r="H2490" s="2" t="n">
-        <v>46070.21803782993</v>
+        <v>46070.21803783565</v>
       </c>
     </row>
     <row r="2491">
@@ -85131,7 +85131,7 @@
         <v>3.07</v>
       </c>
       <c r="H2491" s="2" t="n">
-        <v>46070.21803783295</v>
+        <v>46070.21803783565</v>
       </c>
     </row>
     <row r="2492">
@@ -85165,7 +85165,7 @@
         <v>2.74</v>
       </c>
       <c r="H2492" s="2" t="n">
-        <v>46090.21803783601</v>
+        <v>46090.21803783565</v>
       </c>
     </row>
     <row r="2493">
@@ -85199,7 +85199,7 @@
         <v>3.96</v>
       </c>
       <c r="H2493" s="2" t="n">
-        <v>46083.21803783905</v>
+        <v>46083.21803783565</v>
       </c>
     </row>
     <row r="2494">
@@ -85233,7 +85233,7 @@
         <v>2.97</v>
       </c>
       <c r="H2494" s="2" t="n">
-        <v>46073.21803784247</v>
+        <v>46073.21803784723</v>
       </c>
     </row>
     <row r="2495">
@@ -85267,7 +85267,7 @@
         <v>1.6</v>
       </c>
       <c r="H2495" s="2" t="n">
-        <v>46096.21803784568</v>
+        <v>46096.21803784723</v>
       </c>
     </row>
     <row r="2496">
@@ -85301,7 +85301,7 @@
         <v>2.52</v>
       </c>
       <c r="H2496" s="2" t="n">
-        <v>46086.2180378488</v>
+        <v>46086.21803784723</v>
       </c>
     </row>
     <row r="2497">
@@ -85335,7 +85335,7 @@
         <v>0.03</v>
       </c>
       <c r="H2497" s="2" t="n">
-        <v>46087.21803785186</v>
+        <v>46087.21803784723</v>
       </c>
     </row>
     <row r="2498">
@@ -85369,7 +85369,7 @@
         <v>3.49</v>
       </c>
       <c r="H2498" s="2" t="n">
-        <v>46082.21803785503</v>
+        <v>46082.21803785879</v>
       </c>
     </row>
     <row r="2499">
@@ -85403,7 +85403,7 @@
         <v>3.88</v>
       </c>
       <c r="H2499" s="2" t="n">
-        <v>46092.21803785815</v>
+        <v>46092.21803785879</v>
       </c>
     </row>
     <row r="2500">
@@ -85437,7 +85437,7 @@
         <v>3.15</v>
       </c>
       <c r="H2500" s="2" t="n">
-        <v>46095.21803786132</v>
+        <v>46095.21803785879</v>
       </c>
     </row>
     <row r="2501">
@@ -85471,7 +85471,1707 @@
         <v>0.4</v>
       </c>
       <c r="H2501" s="2" t="n">
-        <v>46082.21803786448</v>
+        <v>46082.21803785879</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" t="inlineStr">
+        <is>
+          <t>739d2c34-86a1-4c1c-9c14-0a1e3cd4deca</t>
+        </is>
+      </c>
+      <c r="B2502" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2502" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2502" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2502" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2502" t="n">
+        <v>307.87</v>
+      </c>
+      <c r="G2502" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="H2502" s="2" t="n">
+        <v>46083.29489169428</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" t="inlineStr">
+        <is>
+          <t>4c390817-73b9-489b-8764-73bdb2346539</t>
+        </is>
+      </c>
+      <c r="B2503" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2503" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2503" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2503" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2503" t="n">
+        <v>398.22</v>
+      </c>
+      <c r="G2503" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="H2503" s="2" t="n">
+        <v>46097.29489169913</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" t="inlineStr">
+        <is>
+          <t>d0c71655-e40f-42a1-b97c-df8de2fcb032</t>
+        </is>
+      </c>
+      <c r="B2504" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2504" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2504" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2504" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2504" t="n">
+        <v>385.48</v>
+      </c>
+      <c r="G2504" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H2504" s="2" t="n">
+        <v>46089.29489170236</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" t="inlineStr">
+        <is>
+          <t>ad3955f3-f8e1-4c6a-844c-f2c9948ca011</t>
+        </is>
+      </c>
+      <c r="B2505" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2505" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2505" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2505" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2505" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="G2505" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H2505" s="2" t="n">
+        <v>46096.29489170575</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" t="inlineStr">
+        <is>
+          <t>87a0e36f-22b2-4ae1-8866-d38bff3bfed4</t>
+        </is>
+      </c>
+      <c r="B2506" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2506" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2506" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2506" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2506" t="n">
+        <v>205.04</v>
+      </c>
+      <c r="G2506" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H2506" s="2" t="n">
+        <v>46073.29489170919</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" t="inlineStr">
+        <is>
+          <t>c96e94bf-dd55-4c73-9997-19555b71a086</t>
+        </is>
+      </c>
+      <c r="B2507" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2507" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2507" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2507" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2507" t="n">
+        <v>122.11</v>
+      </c>
+      <c r="G2507" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H2507" s="2" t="n">
+        <v>46081.29489171235</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" t="inlineStr">
+        <is>
+          <t>7659997a-134a-4e6d-95d8-582e65ec7095</t>
+        </is>
+      </c>
+      <c r="B2508" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2508" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2508" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2508" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2508" t="n">
+        <v>272.57</v>
+      </c>
+      <c r="G2508" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H2508" s="2" t="n">
+        <v>46072.2948917155</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" t="inlineStr">
+        <is>
+          <t>c2694a2b-2fac-4da3-b83b-9a2a08b9657f</t>
+        </is>
+      </c>
+      <c r="B2509" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2509" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2509" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2509" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2509" t="n">
+        <v>351.18</v>
+      </c>
+      <c r="G2509" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="H2509" s="2" t="n">
+        <v>46088.29489171862</v>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" t="inlineStr">
+        <is>
+          <t>5f69bd4e-a6ab-4d65-888d-4fc7c96048c1</t>
+        </is>
+      </c>
+      <c r="B2510" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2510" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2510" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2510" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2510" t="n">
+        <v>289.56</v>
+      </c>
+      <c r="G2510" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H2510" s="2" t="n">
+        <v>46094.29489172203</v>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" t="inlineStr">
+        <is>
+          <t>4051b7b9-1fe1-4cbe-ac7b-e8048a0d75ea</t>
+        </is>
+      </c>
+      <c r="B2511" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2511" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2511" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2511" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2511" t="n">
+        <v>137.4</v>
+      </c>
+      <c r="G2511" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H2511" s="2" t="n">
+        <v>46072.29489172513</v>
+      </c>
+    </row>
+    <row r="2512">
+      <c r="A2512" t="inlineStr">
+        <is>
+          <t>dc6cf66f-b722-4ea9-96f3-1b883c3ef28a</t>
+        </is>
+      </c>
+      <c r="B2512" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2512" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2512" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2512" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2512" t="n">
+        <v>472.61</v>
+      </c>
+      <c r="G2512" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="H2512" s="2" t="n">
+        <v>46093.29489172823</v>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" t="inlineStr">
+        <is>
+          <t>a579465f-186a-4758-b666-c81b12f3f5b7</t>
+        </is>
+      </c>
+      <c r="B2513" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2513" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2513" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2513" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2513" t="n">
+        <v>404.63</v>
+      </c>
+      <c r="G2513" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="H2513" s="2" t="n">
+        <v>46086.29489173146</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" t="inlineStr">
+        <is>
+          <t>b08ca869-1100-4dd9-b2fb-5b2425405df1</t>
+        </is>
+      </c>
+      <c r="B2514" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2514" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2514" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2514" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2514" t="n">
+        <v>95.31</v>
+      </c>
+      <c r="G2514" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H2514" s="2" t="n">
+        <v>46097.29489173457</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" t="inlineStr">
+        <is>
+          <t>7cf27bc4-fb06-4f3c-a2bb-204ed7c36207</t>
+        </is>
+      </c>
+      <c r="B2515" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2515" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2515" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2515" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2515" t="n">
+        <v>92.08</v>
+      </c>
+      <c r="G2515" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H2515" s="2" t="n">
+        <v>46096.29489173761</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" t="inlineStr">
+        <is>
+          <t>160f603d-b4db-4d44-b986-4d72a28dd16e</t>
+        </is>
+      </c>
+      <c r="B2516" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2516" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2516" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2516" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2516" t="n">
+        <v>110.82</v>
+      </c>
+      <c r="G2516" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="H2516" s="2" t="n">
+        <v>46084.29489174067</v>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" t="inlineStr">
+        <is>
+          <t>ea9d9fbf-ce9e-4a9c-9104-6d5af399e0fc</t>
+        </is>
+      </c>
+      <c r="B2517" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2517" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2517" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2517" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2517" t="n">
+        <v>91.93000000000001</v>
+      </c>
+      <c r="G2517" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H2517" s="2" t="n">
+        <v>46084.29489174407</v>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" t="inlineStr">
+        <is>
+          <t>41846353-3582-4dcd-9804-50fee33f2bfe</t>
+        </is>
+      </c>
+      <c r="B2518" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2518" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2518" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2518" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2518" t="n">
+        <v>305.41</v>
+      </c>
+      <c r="G2518" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H2518" s="2" t="n">
+        <v>46070.29489174711</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" t="inlineStr">
+        <is>
+          <t>8b271bb7-e0e9-4ac7-8726-0287c8f43a68</t>
+        </is>
+      </c>
+      <c r="B2519" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2519" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2519" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2519" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2519" t="n">
+        <v>205.98</v>
+      </c>
+      <c r="G2519" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H2519" s="2" t="n">
+        <v>46082.29489175017</v>
+      </c>
+    </row>
+    <row r="2520">
+      <c r="A2520" t="inlineStr">
+        <is>
+          <t>a171a7b8-63ef-4dd4-b70d-106a9129df7c</t>
+        </is>
+      </c>
+      <c r="B2520" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2520" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2520" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2520" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2520" t="n">
+        <v>413.55</v>
+      </c>
+      <c r="G2520" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H2520" s="2" t="n">
+        <v>46083.29489175322</v>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" t="inlineStr">
+        <is>
+          <t>27b6c056-032b-44dd-9d27-3ee0eb41a2aa</t>
+        </is>
+      </c>
+      <c r="B2521" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2521" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2521" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2521" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2521" t="n">
+        <v>54.37</v>
+      </c>
+      <c r="G2521" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H2521" s="2" t="n">
+        <v>46084.29489175661</v>
+      </c>
+    </row>
+    <row r="2522">
+      <c r="A2522" t="inlineStr">
+        <is>
+          <t>0e642536-e161-4bb3-8c8c-ac70d524d33f</t>
+        </is>
+      </c>
+      <c r="B2522" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2522" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2522" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2522" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2522" t="n">
+        <v>283.51</v>
+      </c>
+      <c r="G2522" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="H2522" s="2" t="n">
+        <v>46079.29489175967</v>
+      </c>
+    </row>
+    <row r="2523">
+      <c r="A2523" t="inlineStr">
+        <is>
+          <t>9de8e151-467c-4d87-aa98-f3e5624ce458</t>
+        </is>
+      </c>
+      <c r="B2523" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2523" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2523" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2523" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2523" t="n">
+        <v>457.7</v>
+      </c>
+      <c r="G2523" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="H2523" s="2" t="n">
+        <v>46080.29489176271</v>
+      </c>
+    </row>
+    <row r="2524">
+      <c r="A2524" t="inlineStr">
+        <is>
+          <t>b30aafc8-9696-4e0a-b2ea-1b9dd920442d</t>
+        </is>
+      </c>
+      <c r="B2524" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2524" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2524" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2524" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2524" t="n">
+        <v>474.17</v>
+      </c>
+      <c r="G2524" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="H2524" s="2" t="n">
+        <v>46073.29489176608</v>
+      </c>
+    </row>
+    <row r="2525">
+      <c r="A2525" t="inlineStr">
+        <is>
+          <t>d595157c-142b-4258-8449-bf5d541591b7</t>
+        </is>
+      </c>
+      <c r="B2525" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2525" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2525" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2525" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2525" t="n">
+        <v>391.7</v>
+      </c>
+      <c r="G2525" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H2525" s="2" t="n">
+        <v>46093.29489176931</v>
+      </c>
+    </row>
+    <row r="2526">
+      <c r="A2526" t="inlineStr">
+        <is>
+          <t>35698f3a-66a5-49c6-b30f-1db4f7f86261</t>
+        </is>
+      </c>
+      <c r="B2526" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2526" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2526" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2526" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2526" t="n">
+        <v>217.65</v>
+      </c>
+      <c r="G2526" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H2526" s="2" t="n">
+        <v>46068.29489177234</v>
+      </c>
+    </row>
+    <row r="2527">
+      <c r="A2527" t="inlineStr">
+        <is>
+          <t>7b530e6b-876f-48c0-8c48-71ac2c610257</t>
+        </is>
+      </c>
+      <c r="B2527" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2527" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2527" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2527" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2527" t="n">
+        <v>433.16</v>
+      </c>
+      <c r="G2527" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="H2527" s="2" t="n">
+        <v>46080.2948917754</v>
+      </c>
+    </row>
+    <row r="2528">
+      <c r="A2528" t="inlineStr">
+        <is>
+          <t>0715d3d0-e89a-468a-bc03-c6b9533e65be</t>
+        </is>
+      </c>
+      <c r="B2528" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2528" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2528" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2528" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2528" t="n">
+        <v>160.44</v>
+      </c>
+      <c r="G2528" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H2528" s="2" t="n">
+        <v>46095.29489177859</v>
+      </c>
+    </row>
+    <row r="2529">
+      <c r="A2529" t="inlineStr">
+        <is>
+          <t>b8be1af3-aaea-495e-921a-ff02a3a5707c</t>
+        </is>
+      </c>
+      <c r="B2529" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2529" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2529" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2529" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2529" t="n">
+        <v>95.88</v>
+      </c>
+      <c r="G2529" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H2529" s="2" t="n">
+        <v>46092.29489178163</v>
+      </c>
+    </row>
+    <row r="2530">
+      <c r="A2530" t="inlineStr">
+        <is>
+          <t>738ab999-fb33-402b-9da1-8fad42e62a80</t>
+        </is>
+      </c>
+      <c r="B2530" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2530" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2530" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2530" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2530" t="n">
+        <v>410.18</v>
+      </c>
+      <c r="G2530" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H2530" s="2" t="n">
+        <v>46087.29489178496</v>
+      </c>
+    </row>
+    <row r="2531">
+      <c r="A2531" t="inlineStr">
+        <is>
+          <t>b1482b7a-c136-496c-9f1b-f08a09a212b9</t>
+        </is>
+      </c>
+      <c r="B2531" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2531" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2531" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2531" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2531" t="n">
+        <v>393.48</v>
+      </c>
+      <c r="G2531" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="H2531" s="2" t="n">
+        <v>46095.29489178804</v>
+      </c>
+    </row>
+    <row r="2532">
+      <c r="A2532" t="inlineStr">
+        <is>
+          <t>50dc187c-b085-43d6-94e3-fdb828cd2603</t>
+        </is>
+      </c>
+      <c r="B2532" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2532" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2532" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2532" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2532" t="n">
+        <v>373.43</v>
+      </c>
+      <c r="G2532" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="H2532" s="2" t="n">
+        <v>46069.29489179132</v>
+      </c>
+    </row>
+    <row r="2533">
+      <c r="A2533" t="inlineStr">
+        <is>
+          <t>8c3e47e9-070c-4f4a-875d-3e4aeb60b4d8</t>
+        </is>
+      </c>
+      <c r="B2533" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2533" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2533" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2533" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2533" t="n">
+        <v>354.61</v>
+      </c>
+      <c r="G2533" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H2533" s="2" t="n">
+        <v>46074.29489179448</v>
+      </c>
+    </row>
+    <row r="2534">
+      <c r="A2534" t="inlineStr">
+        <is>
+          <t>c062637c-f047-410f-b740-8e72f40e54e5</t>
+        </is>
+      </c>
+      <c r="B2534" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2534" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2534" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2534" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2534" t="n">
+        <v>162.52</v>
+      </c>
+      <c r="G2534" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H2534" s="2" t="n">
+        <v>46087.29489179772</v>
+      </c>
+    </row>
+    <row r="2535">
+      <c r="A2535" t="inlineStr">
+        <is>
+          <t>d55d80e3-8df2-459b-8f5e-be6d34c1ab8e</t>
+        </is>
+      </c>
+      <c r="B2535" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2535" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2535" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2535" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2535" t="n">
+        <v>19.24</v>
+      </c>
+      <c r="G2535" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H2535" s="2" t="n">
+        <v>46093.29489180097</v>
+      </c>
+    </row>
+    <row r="2536">
+      <c r="A2536" t="inlineStr">
+        <is>
+          <t>ceaef7a6-69df-46f6-8f35-5bd527348e1c</t>
+        </is>
+      </c>
+      <c r="B2536" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2536" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2536" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2536" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2536" t="n">
+        <v>284.43</v>
+      </c>
+      <c r="G2536" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="H2536" s="2" t="n">
+        <v>46077.29489180409</v>
+      </c>
+    </row>
+    <row r="2537">
+      <c r="A2537" t="inlineStr">
+        <is>
+          <t>bb4bba52-bb13-4eec-94fa-ce037b60f21b</t>
+        </is>
+      </c>
+      <c r="B2537" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2537" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2537" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2537" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2537" t="n">
+        <v>278.26</v>
+      </c>
+      <c r="G2537" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="H2537" s="2" t="n">
+        <v>46088.29489180716</v>
+      </c>
+    </row>
+    <row r="2538">
+      <c r="A2538" t="inlineStr">
+        <is>
+          <t>67183120-5ab6-4113-98e4-e1fec0971ca2</t>
+        </is>
+      </c>
+      <c r="B2538" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2538" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2538" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2538" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2538" t="n">
+        <v>52.82</v>
+      </c>
+      <c r="G2538" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H2538" s="2" t="n">
+        <v>46079.2948918103</v>
+      </c>
+    </row>
+    <row r="2539">
+      <c r="A2539" t="inlineStr">
+        <is>
+          <t>7e2ac0c4-48ac-43f2-b69d-b7ec29bf9430</t>
+        </is>
+      </c>
+      <c r="B2539" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2539" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2539" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2539" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2539" t="n">
+        <v>334.42</v>
+      </c>
+      <c r="G2539" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="H2539" s="2" t="n">
+        <v>46073.29489181375</v>
+      </c>
+    </row>
+    <row r="2540">
+      <c r="A2540" t="inlineStr">
+        <is>
+          <t>63cfc09c-18cd-42c9-9461-e89aec6de221</t>
+        </is>
+      </c>
+      <c r="B2540" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2540" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2540" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2540" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2540" t="n">
+        <v>375.36</v>
+      </c>
+      <c r="G2540" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H2540" s="2" t="n">
+        <v>46086.29489181692</v>
+      </c>
+    </row>
+    <row r="2541">
+      <c r="A2541" t="inlineStr">
+        <is>
+          <t>986bf6a6-d99a-4d07-9569-a36546850f2c</t>
+        </is>
+      </c>
+      <c r="B2541" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2541" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2541" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2541" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2541" t="n">
+        <v>350.81</v>
+      </c>
+      <c r="G2541" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="H2541" s="2" t="n">
+        <v>46095.29489182009</v>
+      </c>
+    </row>
+    <row r="2542">
+      <c r="A2542" t="inlineStr">
+        <is>
+          <t>e4c0f636-306d-4c57-b795-d0a632a2211e</t>
+        </is>
+      </c>
+      <c r="B2542" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2542" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2542" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2542" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2542" t="n">
+        <v>352.74</v>
+      </c>
+      <c r="G2542" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="H2542" s="2" t="n">
+        <v>46095.29489182308</v>
+      </c>
+    </row>
+    <row r="2543">
+      <c r="A2543" t="inlineStr">
+        <is>
+          <t>49e471b7-7521-4361-b296-a1730d60121a</t>
+        </is>
+      </c>
+      <c r="B2543" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2543" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2543" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2543" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2543" t="n">
+        <v>454.67</v>
+      </c>
+      <c r="G2543" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="H2543" s="2" t="n">
+        <v>46094.29489182626</v>
+      </c>
+    </row>
+    <row r="2544">
+      <c r="A2544" t="inlineStr">
+        <is>
+          <t>3878d99c-651b-45ea-8ed9-2bf00b313558</t>
+        </is>
+      </c>
+      <c r="B2544" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2544" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2544" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2544" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2544" t="n">
+        <v>151.07</v>
+      </c>
+      <c r="G2544" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="H2544" s="2" t="n">
+        <v>46096.29489182944</v>
+      </c>
+    </row>
+    <row r="2545">
+      <c r="A2545" t="inlineStr">
+        <is>
+          <t>9e37bcd8-a2a3-4217-8b66-3e6fd2085a9e</t>
+        </is>
+      </c>
+      <c r="B2545" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2545" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2545" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2545" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2545" t="n">
+        <v>53.74</v>
+      </c>
+      <c r="G2545" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H2545" s="2" t="n">
+        <v>46086.2948918325</v>
+      </c>
+    </row>
+    <row r="2546">
+      <c r="A2546" t="inlineStr">
+        <is>
+          <t>3ac748eb-9cfe-4f51-8626-578eeeceba15</t>
+        </is>
+      </c>
+      <c r="B2546" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2546" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2546" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2546" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="F2546" t="n">
+        <v>228.26</v>
+      </c>
+      <c r="G2546" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H2546" s="2" t="n">
+        <v>46091.29489183586</v>
+      </c>
+    </row>
+    <row r="2547">
+      <c r="A2547" t="inlineStr">
+        <is>
+          <t>05c0ed7e-4015-4df4-92aa-b0363f41ea9d</t>
+        </is>
+      </c>
+      <c r="B2547" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2547" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2547" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2547" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="F2547" t="n">
+        <v>98.18000000000001</v>
+      </c>
+      <c r="G2547" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H2547" s="2" t="n">
+        <v>46095.29489183902</v>
+      </c>
+    </row>
+    <row r="2548">
+      <c r="A2548" t="inlineStr">
+        <is>
+          <t>d41676fe-d2f3-4415-a727-0ade855fc176</t>
+        </is>
+      </c>
+      <c r="B2548" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2548" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2548" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2548" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2548" t="n">
+        <v>442.31</v>
+      </c>
+      <c r="G2548" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="H2548" s="2" t="n">
+        <v>46074.29489184202</v>
+      </c>
+    </row>
+    <row r="2549">
+      <c r="A2549" t="inlineStr">
+        <is>
+          <t>d0d83647-283b-49aa-9d1a-de78594c5353</t>
+        </is>
+      </c>
+      <c r="B2549" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2549" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2549" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="E2549" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="F2549" t="n">
+        <v>474.57</v>
+      </c>
+      <c r="G2549" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="H2549" s="2" t="n">
+        <v>46075.29489184508</v>
+      </c>
+    </row>
+    <row r="2550">
+      <c r="A2550" t="inlineStr">
+        <is>
+          <t>d2dbcc3b-135e-40e3-944b-5dbdfde013c0</t>
+        </is>
+      </c>
+      <c r="B2550" t="n">
+        <v>95</v>
+      </c>
+      <c r="C2550" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D2550" t="inlineStr">
+        <is>
+         